--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -187,9 +187,6 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -198,6 +195,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -752,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>＋1pt</t>
+          <t>＋2pt</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>＋4pt</t>
+          <t>＋6pt</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.786</v>
+        <v>0.7890000000000001</v>
       </c>
       <c r="D18" s="11" t="inlineStr"/>
       <c r="E18" s="11" t="inlineStr"/>
@@ -1237,20 +1237,38 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>9c17709</t>
+          <t>241932b</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>日次のWBS更新と翌日の作業順位（スキルと日次の表）</t>
+          <t>既定値の仮置き（未決160件）と据え置き区分Aの更新</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
       <c r="E23" s="6" t="inlineStr"/>
       <c r="F23" s="6" t="inlineStr"/>
     </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="14" t="inlineStr">
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>9c17709</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>日次のWBS更新と翌日の作業順位（スキルと日次の表）</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
@@ -1258,12 +1276,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1439,7 +1457,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>一律の伸びのまま概算し、補正の効き（月額▲58円又は＋48円）を併記する</t>
+          <t>サービス別の趨勢を反映する補正は行わない（見込量は要介護度別の伸びによる）。補正を行った場合の月額への効きは計画素案 第6章第6節2に併記する</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1541,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節は利用者数のみを掲げたまま概算する</t>
+          <t>計画素案 第6章第2節に利用回（日）数を、第3節2に介護予防・日常生活支援総合事業及び一般介護予防事業の量の見込みを掲げた現行のまま確定する。必要利用定員総数の第2節への再掲は行わない（第4節4による）</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2049,7 @@
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する。差は月額＋8円である</t>
+          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6847,7 @@
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t>決着しない場合は、現状のまま（東川町の整備を見込まない）第10期の目標値を置く</t>
+          <t>現状のまま（東川町の整備を見込まない）第10期の目標値を置く</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6889,7 @@
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
-          <t>決着しない場合は、現に確認できる取組の範囲で記述し目標値は置かない</t>
+          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
         </is>
       </c>
     </row>
@@ -6913,7 +6931,7 @@
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
-          <t>決着しない場合は、東川町の取組として記述し3町展開は記述しない</t>
+          <t>東川町の取組として記述し3町展開は記述しない</t>
         </is>
       </c>
     </row>
@@ -6955,7 +6973,7 @@
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
-          <t>決着しない場合は、令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残す</t>
+          <t>令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残す</t>
         </is>
       </c>
     </row>
@@ -6997,7 +7015,7 @@
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
-          <t>決着しない場合は、美瑛町の取組として記述し3町展開は記述しない</t>
+          <t>美瑛町の取組として記述し3町展開は記述しない</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7057,7 @@
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
-          <t>決着しない場合は、現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
+          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7099,7 @@
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
-          <t>決着しない場合は、現に確認できる取組の範囲で記述する</t>
+          <t>現に確認できる取組の範囲で記述する</t>
         </is>
       </c>
     </row>
@@ -7123,7 +7141,7 @@
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
-          <t>決着しない場合は、令和6年度の水準が続くものとして目標値を置く</t>
+          <t>令和6年度の水準が続くものとして目標値を置く</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7183,7 @@
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
-          <t>決着しない場合は、現に確認できる取組の範囲で記述し目標値は置かない</t>
+          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7267,7 @@
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
-          <t>決着しない場合の当方の扱い＝掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。</t>
+          <t>の当方の扱い＝掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
         </is>
       </c>
     </row>
@@ -7877,7 +7895,7 @@
       </c>
       <c r="I160" s="6" t="inlineStr">
         <is>
-          <t>決着しない場合は、町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。</t>
+          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7979,7 @@
       </c>
       <c r="I162" s="6" t="inlineStr">
         <is>
-          <t>決着しない場合の当方の扱い＝現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。</t>
+          <t>の当方の扱い＝現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9552,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>2件</t>
+          <t>4件</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -9559,7 +9577,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>2件</t>
+          <t>0件</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -9637,7 +9655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F159"/>
+  <dimension ref="A1:F163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9665,7 +9683,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　当方の作業だけで進められるもの　150件</t>
+          <t>1　当方の作業だけで進められるもの　154件</t>
         </is>
       </c>
     </row>
@@ -9698,22 +9716,22 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>据え置き（区分A）</t>
+          <t>既定値で進める</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>要介護度の構成（要介護度別の将来推計）</t>
+          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定した。年齢構成の変化による重度化は反映される。国の様式も見える化システムも要介護度別の推計を出力しない。令和8年度は4か月分（月報）しかなく、構成を取り直す基礎にならない（令和8年10月1日に再確認した）</t>
+          <t>1人1月あたり給付費は令和7年度で固定して概算する（月額で＋185〜＋374円に当たる）</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>見込量算定の据え置き 4</t>
+          <t>確認事項No.137（点7）</t>
         </is>
       </c>
     </row>
@@ -9723,22 +9741,22 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>据え置き（区分A）</t>
+          <t>既定値で進める</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>季節補正</t>
+          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>季節指数の和が12となり換算係数が1.0000で恒等的に消える。補正を行わない。基準年度を完結年度に採る限り効きは0円であり、測定できても採用値は動かない。採用パターンP3は令和7年度（完結年度）を基準とする。利用状況統計表（審査月別）を継続して受領できれば季節性を測定できるが、24か月分を要し、現在は1か月分である（令和8年10月1日に再確認した）</t>
+          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>見込量算定の据え置き 12</t>
+          <t>確認事項No.110（点7）</t>
         </is>
       </c>
     </row>
@@ -9746,24 +9764,24 @@
       <c r="A8" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域ごとの必要利用定員総数（法定記載事項）</t>
+          <t>認知症総合支援事業の実績のご提供</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>3町（3圏域）を基盤整備単位とする案のまま概算する。必要利用定員総数は［要協議］のまま残す</t>
+          <t>6事業別の事業費を受領できないものとして、認知症総合支援事業の量の見込みは立てず、3町の取組の回数のみを掲げる</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.88（点8）</t>
+          <t>確認事項No.150（点7）</t>
         </is>
       </c>
     </row>
@@ -9771,24 +9789,24 @@
       <c r="A9" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを一律からサービス別の趨勢を半分反映する置き方に改めるか</t>
+          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>一律の伸びのまま概算し、補正の効き（月額▲58円又は＋48円）を併記する</t>
+          <t>省令上の類型を計画に掲げないまま概算する</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.106（点8）</t>
+          <t>確認事項No.98（点6）</t>
         </is>
       </c>
     </row>
@@ -9796,24 +9814,24 @@
       <c r="A10" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設の必要利用定員総数を定めるか</t>
+          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設の必要利用定員総数を定めないまま概算する</t>
+          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）で概算する</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.113（点8）</t>
+          <t>確認事項No.100（点6）</t>
         </is>
       </c>
     </row>
@@ -9821,24 +9839,24 @@
       <c r="A11" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="21" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の見込量の表に何を掲げるか</t>
+          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節は利用者数のみを掲げたまま概算する</t>
+          <t>素案 第6章第2節の表は見える化の自然体推計値のまま置き、P3による値を別掲する</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.131（点8）</t>
+          <t>確認事項No.101（点6）</t>
         </is>
       </c>
     </row>
@@ -9846,24 +9864,24 @@
       <c r="A12" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の量の見込みを算定してよいか</t>
+          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の利用者実人数を据え置いて延ばした量の見込みを掲げ、令和7年度の実施状況は単位が異なるため別の表として示す</t>
+          <t>令和8年度を基準年度に用いず、季節補正も行わないまま概算する</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.112（点8）</t>
+          <t>確認事項No.103（点6）</t>
         </is>
       </c>
     </row>
@@ -9871,24 +9889,24 @@
       <c r="A13" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行うか。行う場合の対象と歯止め</t>
+          <t>施設・居住系の実績の減少を将来へ延長するか</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行わないまま概算する（安全側）</t>
+          <t>施設・居住系の実績の減少を将来へ延長しないまま概算する</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.105（点7）</t>
+          <t>確認事項No.107（点6）</t>
         </is>
       </c>
     </row>
@@ -9896,24 +9914,24 @@
       <c r="A14" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
+          <t>区域を越えた施設利用の扱い</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費は令和7年度で固定して概算する（月額で＋185〜＋374円に当たる）</t>
+          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.137（点7）</t>
+          <t>確認事項No.141（点6）</t>
         </is>
       </c>
     </row>
@@ -9921,24 +9939,24 @@
       <c r="A15" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
+          <t>見込量の伸びを要介護度別に改めてよいか</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
+          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.110（点7）</t>
+          <t>確認事項No.146（点6）</t>
         </is>
       </c>
     </row>
@@ -9946,24 +9964,24 @@
       <c r="A16" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実績のご提供</t>
+          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>6事業別の事業費を受領できないものとして、認知症総合支援事業の量の見込みは立てず、3町の取組の回数のみを掲げる</t>
+          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.150（点7）</t>
+          <t>確認事項No.151（点6）</t>
         </is>
       </c>
     </row>
@@ -9971,24 +9989,24 @@
       <c r="A17" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
+          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>省令上の類型を計画に掲げないまま概算する</t>
+          <t>財政調整交付金の算定に給付適正化主要3事業の取組状況を勘案しないものとして算定する（調整交付金7.3755％のまま。安全側）</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.98（点6）</t>
+          <t>確認事項No.93（点6）</t>
         </is>
       </c>
     </row>
@@ -9996,24 +10014,24 @@
       <c r="A18" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
+          <t>構成町の一般会計繰入金の町別按分の方法</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）で概算する</t>
+          <t>町別按分は当方の案（第1次概算）のまま示す</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.100（点6）</t>
+          <t>確認事項No.82（点5）</t>
         </is>
       </c>
     </row>
@@ -10021,24 +10039,24 @@
       <c r="A19" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
+          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第2節の表は見える化の自然体推計値のまま置き、P3による値を別掲する</t>
+          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.101（点6）</t>
+          <t>確認事項No.123（点5）</t>
         </is>
       </c>
     </row>
@@ -10046,24 +10064,24 @@
       <c r="A20" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
+          <t>見える化システムの推計方式は基本推計でよいか</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節補正も行わないまま概算する</t>
+          <t>基本推計に近いP3で概算する</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.103（点6）</t>
+          <t>確認事項No.126（点5）</t>
         </is>
       </c>
     </row>
@@ -10071,24 +10089,24 @@
       <c r="A21" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長するか</t>
+          <t>認知症基本法第13条の市町村認知症施策推進計画をどう扱うか</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長しないまま概算する</t>
+          <t>案B（3町がそれぞれ市町村計画を策定する）のまま素案に反映する</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.107（点6）</t>
+          <t>確認事項No.130（点5）</t>
         </is>
       </c>
     </row>
@@ -10096,24 +10114,24 @@
       <c r="A22" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>区域を越えた施設利用の扱い</t>
+          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
+          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.141（点6）</t>
+          <t>確認事項No.132（点5）</t>
         </is>
       </c>
     </row>
@@ -10121,24 +10139,24 @@
       <c r="A23" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを要介護度別に改めてよいか</t>
+          <t>第1次概算を既定値のまま出してよいか</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する。差は月額＋8円である</t>
+          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.146（点6）</t>
+          <t>確認事項No.142（点5）</t>
         </is>
       </c>
     </row>
@@ -10146,24 +10164,24 @@
       <c r="A24" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
+          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
+          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.151（点6）</t>
+          <t>確認事項No.145（点5）</t>
         </is>
       </c>
     </row>
@@ -10171,24 +10189,24 @@
       <c r="A25" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
+          <t>見える化システムの伸びの選択肢をどれとするか</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定に給付適正化主要3事業の取組状況を勘案しないものとして算定する（調整交付金7.3755％のまま。安全側）</t>
+          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.93（点6）</t>
+          <t>確認事項No.147（点5）</t>
         </is>
       </c>
     </row>
@@ -10196,24 +10214,24 @@
       <c r="A26" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="21" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>構成町の一般会計繰入金の町別按分の方法</t>
+          <t>東川町の施設整備・サービス提供方針</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>町別按分は当方の案（第1次概算）のまま示す</t>
+          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.82（点5）</t>
+          <t>確認事項No.84（点5）</t>
         </is>
       </c>
     </row>
@@ -10221,24 +10239,24 @@
       <c r="A27" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
+          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
+          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.123（点5）</t>
+          <t>確認事項No.104（点5）</t>
         </is>
       </c>
     </row>
@@ -10246,24 +10264,24 @@
       <c r="A28" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B28" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計方式は基本推計でよいか</t>
+          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>基本推計に近いP3で概算する</t>
+          <t>単価を令和7年度で固定する（安全側）。実績の趨勢（年率1.75％）を置いた場合の差（月額＋185円から＋374円）は据え置きの一覧に示す</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.126（点5）</t>
+          <t>確認事項No.109（点5）</t>
         </is>
       </c>
     </row>
@@ -10271,24 +10289,24 @@
       <c r="A29" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B29" s="21" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法第13条の市町村認知症施策推進計画をどう扱うか</t>
+          <t>令和22年度までの中長期推計をどこまで算定するか</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>案B（3町がそれぞれ市町村計画を策定する）のまま素案に反映する</t>
+          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.130（点5）</t>
+          <t>確認事項No.114（点5）</t>
         </is>
       </c>
     </row>
@@ -10296,24 +10314,24 @@
       <c r="A30" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
+          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
+          <t>供給の制約（人材）を見込量に反映しない（需要のみで算定する）</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.132（点5）</t>
+          <t>確認事項No.116（点5）</t>
         </is>
       </c>
     </row>
@@ -10321,24 +10339,24 @@
       <c r="A31" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第1次概算を既定値のまま出してよいか</t>
+          <t>町別の人口の将来推計を計画本文に掲げるか</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
+          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.142（点5）</t>
+          <t>確認事項No.152（点5）</t>
         </is>
       </c>
     </row>
@@ -10346,24 +10364,24 @@
       <c r="A32" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
+          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
+          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.145（点5）</t>
+          <t>確認事項No.153（点5）</t>
         </is>
       </c>
     </row>
@@ -10371,24 +10389,24 @@
       <c r="A33" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの伸びの選択肢をどれとするか</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>第9期の自己評価と北海道への報告の実績を確認できないものとして、第10期の進行管理に自己評価の仕組みを置く</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.147（点5）</t>
+          <t>確認事項No.7（点4）</t>
         </is>
       </c>
     </row>
@@ -10396,24 +10414,24 @@
       <c r="A34" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B34" s="21" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>東川町の施設整備・サービス提供方針</t>
+          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残す</t>
+          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.84（点5）</t>
+          <t>確認事項No.86（点4）</t>
         </is>
       </c>
     </row>
@@ -10421,24 +10439,24 @@
       <c r="A35" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
+          <t>給付適正化計画の位置づけ（案Bの採用）と毎年度の目標の記載場所</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
+          <t>給付適正化計画の位置づけは案B（第9期と同じく施策として置き、施策名のかっこ書きで第7期給付適正化計画であることを示す）のままとする（令和8年9月10日 了承済み）</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.104（点5）</t>
+          <t>確認事項No.94（点4）</t>
         </is>
       </c>
     </row>
@@ -10446,24 +10464,24 @@
       <c r="A36" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B36" s="21" t="inlineStr">
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
+          <t>令和8年度の実績見込み値を編集するか</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。実績の趨勢（年率1.75％）を置いた場合の差（月額＋185円から＋374円）は据え置きの一覧に示す</t>
+          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.109（点5）</t>
+          <t>確認事項No.128（点4）</t>
         </is>
       </c>
     </row>
@@ -10471,24 +10489,24 @@
       <c r="A37" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="B37" s="21" t="inlineStr">
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>令和22年度までの中長期推計をどこまで算定するか</t>
+          <t>見える化システムの利用率等の伸びの選択</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
+          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.114（点5）</t>
+          <t>確認事項No.129（点4）</t>
         </is>
       </c>
     </row>
@@ -10496,24 +10514,24 @@
       <c r="A38" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B38" s="21" t="inlineStr">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
+          <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>供給の制約（人材）を見込量に反映しない（需要のみで算定する）</t>
+          <t>第9期条例の16段階・乗率（公費軽減前）を据え置いて算定し、政令の公布後に再算定する</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.116（点5）</t>
+          <t>確認事項No.33（点4）</t>
         </is>
       </c>
     </row>
@@ -10521,24 +10539,24 @@
       <c r="A39" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="B39" s="21" t="inlineStr">
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>町別の人口の将来推計を計画本文に掲げるか</t>
+          <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
+          <t>中間報告・施策体系新旧対照表・骨子案は提出した内容のままとする</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.152（点5）</t>
+          <t>確認事項No.39（点3）</t>
         </is>
       </c>
     </row>
@@ -10546,24 +10564,24 @@
       <c r="A40" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B40" s="21" t="inlineStr">
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
+          <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
+          <t>同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.153（点5）</t>
+          <t>確認事項No.40（点3）</t>
         </is>
       </c>
     </row>
@@ -10571,24 +10589,24 @@
       <c r="A41" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="B41" s="21" t="inlineStr">
+      <c r="B41" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>認定に要する日数の扱い</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績を確認できないものとして、第10期の進行管理に自己評価の仕組みを置く</t>
+          <t>令和8年8月28日受領の集計帳票による</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.7（点4）</t>
+          <t>確認事項No.43（点3）</t>
         </is>
       </c>
     </row>
@@ -10596,24 +10614,24 @@
       <c r="A42" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="B42" s="21" t="inlineStr">
+      <c r="B42" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
+          <t>代表KPI H15の分母の定義</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
+          <t>代表KPI H15の分母は標準給付費見込額とする（受託者案）</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.86（点4）</t>
+          <t>確認事項No.45（点3）</t>
         </is>
       </c>
     </row>
@@ -10621,24 +10639,24 @@
       <c r="A43" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="B43" s="21" t="inlineStr">
+      <c r="B43" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけ（案Bの採用）と毎年度の目標の記載場所</t>
+          <t>計画値を0としたサービスに実績がある2件</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけは案B（第9期と同じく施策として置き、施策名のかっこ書きで第7期給付適正化計画であることを示す）のままとする（令和8年9月10日 了承済み）</t>
+          <t>第10期は計画値を0とせず、算定値を置く（対計画比が算出され評価の対象となるようにする）</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.94（点4）</t>
+          <t>確認事項No.57（点3）</t>
         </is>
       </c>
     </row>
@@ -10646,24 +10664,24 @@
       <c r="A44" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B44" s="21" t="inlineStr">
+      <c r="B44" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の実績見込み値を編集するか</t>
+          <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
+          <t>定期巡回・随時対応型訪問介護看護は自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.128（点4）</t>
+          <t>確認事項No.58（点3）</t>
         </is>
       </c>
     </row>
@@ -10671,24 +10689,24 @@
       <c r="A45" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B45" s="21" t="inlineStr">
+      <c r="B45" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの利用率等の伸びの選択</t>
+          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.129（点4）</t>
+          <t>確認事項No.63（点3）</t>
         </is>
       </c>
     </row>
@@ -10696,24 +10714,24 @@
       <c r="A46" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="B46" s="21" t="inlineStr">
+      <c r="B46" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階）</t>
+          <t>広域連合において行うべき事業の優先順位</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>第9期条例の16段階・乗率（公費軽減前）を据え置いて算定し、政令の公布後に再算定する</t>
+          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.33（点4）</t>
+          <t>確認事項No.65（点3）</t>
         </is>
       </c>
     </row>
@@ -10721,24 +10739,24 @@
       <c r="A47" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="B47" s="21" t="inlineStr">
+      <c r="B47" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
+          <t>サービスガイドに掲載する事業所の範囲</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>中間報告・施策体系新旧対照表・骨子案は提出した内容のままとする</t>
+          <t>サービスガイドに掲載する事業所の範囲は北海道の指定事業所一覧（最新のもの）による</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.39（点3）</t>
+          <t>確認事項No.66（点3）</t>
         </is>
       </c>
     </row>
@@ -10746,24 +10764,24 @@
       <c r="A48" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="B48" s="21" t="inlineStr">
+      <c r="B48" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の扱い</t>
+          <t>算定方法の国の様式との整合（点検結果）</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
+          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.40（点3）</t>
+          <t>確認事項No.67（点3）</t>
         </is>
       </c>
     </row>
@@ -10771,24 +10789,24 @@
       <c r="A49" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="B49" s="21" t="inlineStr">
+      <c r="B49" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>認定に要する日数の扱い</t>
+          <t>見える化システムの自然体推計の再出力のお願い</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の集計帳票による</t>
+          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.43（点3）</t>
+          <t>確認事項No.68（点3）</t>
         </is>
       </c>
     </row>
@@ -10796,24 +10814,24 @@
       <c r="A50" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="B50" s="21" t="inlineStr">
+      <c r="B50" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H15の分母の定義</t>
+          <t>交付金の全国順位の計画本文への掲載</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H15の分母は標準給付費見込額とする（受託者案）</t>
+          <t>交付金の全国順位は計画本文に掲載せず、策定委員会資料にとどめる（確認事項No.71のとおり）</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.45（点3）</t>
+          <t>確認事項No.70（点3）</t>
         </is>
       </c>
     </row>
@@ -10821,24 +10839,24 @@
       <c r="A51" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="B51" s="21" t="inlineStr">
+      <c r="B51" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>計画値を0としたサービスに実績がある2件</t>
+          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>第10期は計画値を0とせず、算定値を置く（対計画比が算出され評価の対象となるようにする）</t>
+          <t>ケアプラン点検実施要領（案）は協議資料にとどめ素案に入れない</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.57（点3）</t>
+          <t>確認事項No.73（点3）</t>
         </is>
       </c>
     </row>
@@ -10846,24 +10864,24 @@
       <c r="A52" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="B52" s="21" t="inlineStr">
+      <c r="B52" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
+          <t>代表KPIと改善事項の再整理案</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護は自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+          <t>代表KPIと改善事項は当方の再整理案のままとする</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.58（点3）</t>
+          <t>確認事項No.75（点3）</t>
         </is>
       </c>
     </row>
@@ -10871,24 +10889,24 @@
       <c r="A53" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="B53" s="21" t="inlineStr">
+      <c r="B53" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
+          <t>介護リームスから抽出できる項目</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
+          <t>介護リームスから抽出できないものとして、代表KPI H03は未算定のままとする</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.63（点3）</t>
+          <t>確認事項No.76（点3）</t>
         </is>
       </c>
     </row>
@@ -10896,24 +10914,24 @@
       <c r="A54" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="B54" s="21" t="inlineStr">
+      <c r="B54" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位</t>
+          <t>北海道の評価指標⑥の団体別の公表値</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
+          <t>北海道の評価指標⑥の団体別の公表値を引用できないものとして、当該指標は計画本文に掲げない</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.65（点3）</t>
+          <t>確認事項No.77（点3）</t>
         </is>
       </c>
     </row>
@@ -10921,24 +10939,24 @@
       <c r="A55" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B55" s="21" t="inlineStr">
+      <c r="B55" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>サービスガイドに掲載する事業所の範囲</t>
+          <t>グループホームびえいの郷の定員減の時期</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>サービスガイドに掲載する事業所の範囲は北海道の指定事業所一覧（最新のもの）による</t>
+          <t>北海道の名簿の定員のまま概算する</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.66（点3）</t>
+          <t>確認事項No.78（点3）</t>
         </is>
       </c>
     </row>
@@ -10946,24 +10964,24 @@
       <c r="A56" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="B56" s="21" t="inlineStr">
+      <c r="B56" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>算定方法の国の様式との整合（点検結果）</t>
+          <t>第5章の施策数の見直しの範囲</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
+          <t>第9期の19施策の体系を維持する（施策数を見直さない）</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.67（点3）</t>
+          <t>確認事項No.79（点3）</t>
         </is>
       </c>
     </row>
@@ -10971,24 +10989,24 @@
       <c r="A57" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="B57" s="21" t="inlineStr">
+      <c r="B57" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの自然体推計の再出力のお願い</t>
+          <t>代表KPI H16のデータ源（国保連の給付実績の明細情報）</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
+          <t>国保連の給付実績の明細を受領できないものとして、代表KPI H16は地域密着型サービスに限った確認件数を代理指標とする</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.68（点3）</t>
+          <t>確認事項No.81（点3）</t>
         </is>
       </c>
     </row>
@@ -10996,24 +11014,24 @@
       <c r="A58" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="B58" s="21" t="inlineStr">
+      <c r="B58" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>交付金の全国順位の計画本文への掲載</t>
+          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>交付金の全国順位は計画本文に掲載せず、策定委員会資料にとどめる（確認事項No.71のとおり）</t>
+          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.70（点3）</t>
+          <t>確認事項No.95（点3）</t>
         </is>
       </c>
     </row>
@@ -11021,24 +11039,24 @@
       <c r="A59" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="B59" s="21" t="inlineStr">
+      <c r="B59" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
+          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）は協議資料にとどめ素案に入れない</t>
+          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.73（点3）</t>
+          <t>確認事項No.96（点3）</t>
         </is>
       </c>
     </row>
@@ -11046,24 +11064,24 @@
       <c r="A60" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="B60" s="21" t="inlineStr">
+      <c r="B60" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>代表KPIと改善事項の再整理案</t>
+          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>代表KPIと改善事項は当方の再整理案のままとする</t>
+          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.75（点3）</t>
+          <t>確認事項No.102（点3）</t>
         </is>
       </c>
     </row>
@@ -11071,24 +11089,24 @@
       <c r="A61" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="B61" s="21" t="inlineStr">
+      <c r="B61" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>介護リームスから抽出できる項目</t>
+          <t>地域ケア会議関係資料の取扱いの確認</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>介護リームスから抽出できないものとして、代表KPI H03は未算定のままとする</t>
+          <t>転載を禁ずる旨の記載がある2件は成果品に用いず、原典（厚労省の市町村マニュアル及び別冊事例集）のみを引く</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.76（点3）</t>
+          <t>確認事項No.122（点3）</t>
         </is>
       </c>
     </row>
@@ -11096,24 +11114,24 @@
       <c r="A62" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="B62" s="21" t="inlineStr">
+      <c r="B62" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥の団体別の公表値</t>
+          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥の団体別の公表値を引用できないものとして、当該指標は計画本文に掲げない</t>
+          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.77（点3）</t>
+          <t>確認事項No.124（点3）</t>
         </is>
       </c>
     </row>
@@ -11121,24 +11139,24 @@
       <c r="A63" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="B63" s="21" t="inlineStr">
+      <c r="B63" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>グループホームびえいの郷の定員減の時期</t>
+          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>北海道の名簿の定員のまま概算する</t>
+          <t>在宅生活改善調査の結果は「在宅で困難を抱える方の状況」として引き、在宅の認定者全体の割合としては引かない</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.78（点3）</t>
+          <t>確認事項No.140（点3）</t>
         </is>
       </c>
     </row>
@@ -11146,24 +11164,24 @@
       <c r="A64" s="5" t="n">
         <v>59</v>
       </c>
-      <c r="B64" s="21" t="inlineStr">
+      <c r="B64" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第5章の施策数の見直しの範囲</t>
+          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策の体系を維持する（施策数を見直さない）</t>
+          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.79（点3）</t>
+          <t>確認事項No.149（点3）</t>
         </is>
       </c>
     </row>
@@ -11171,24 +11189,24 @@
       <c r="A65" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B65" s="21" t="inlineStr">
+      <c r="B65" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H16のデータ源（国保連の給付実績の明細情報）</t>
+          <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>国保連の給付実績の明細を受領できないものとして、代表KPI H16は地域密着型サービスに限った確認件数を代理指標とする</t>
+          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.81（点3）</t>
+          <t>確認事項No.30（点3）</t>
         </is>
       </c>
     </row>
@@ -11196,24 +11214,24 @@
       <c r="A66" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="B66" s="21" t="inlineStr">
+      <c r="B66" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
+          <t>第9段階の乗率の経緯</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
+          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.95（点3）</t>
+          <t>確認事項No.34（点3）</t>
         </is>
       </c>
     </row>
@@ -11221,24 +11239,24 @@
       <c r="A67" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="B67" s="21" t="inlineStr">
+      <c r="B67" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+          <t>上川管内の保険者の所得段階数と乗率</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
+          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.96（点3）</t>
+          <t>確認事項No.35（点3）</t>
         </is>
       </c>
     </row>
@@ -11246,24 +11264,24 @@
       <c r="A68" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="B68" s="21" t="inlineStr">
+      <c r="B68" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
+          <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
+          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.102（点3）</t>
+          <t>確認事項No.36（点3）</t>
         </is>
       </c>
     </row>
@@ -11271,24 +11289,24 @@
       <c r="A69" s="5" t="n">
         <v>64</v>
       </c>
-      <c r="B69" s="21" t="inlineStr">
+      <c r="B69" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議関係資料の取扱いの確認</t>
+          <t>令和9年4月に新設される区分を見込量に立てるか</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>転載を禁ずる旨の記載がある2件は成果品に用いず、原典（厚労省の市町村マニュアル及び別冊事例集）のみを引く</t>
+          <t>令和9年4月新設の3区分を0として立てる</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.122（点3）</t>
+          <t>確認事項No.115（点3）</t>
         </is>
       </c>
     </row>
@@ -11296,24 +11314,24 @@
       <c r="A70" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="B70" s="21" t="inlineStr">
+      <c r="B70" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
+          <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
+          <t>代表KPI H07・H08・H12・H16は代理指標への振替案のとおりとする</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.124（点3）</t>
+          <t>確認事項No.4（点2）</t>
         </is>
       </c>
     </row>
@@ -11321,24 +11339,24 @@
       <c r="A71" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="B71" s="21" t="inlineStr">
+      <c r="B71" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
+          <t>第9期の施策・事業実績</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果は「在宅で困難を抱える方の状況」として引き、在宅の認定者全体の割合としては引かない</t>
+          <t>第9期の施策・事業実績を受領できないものとして、公表資料（交付金の評価結果・総合事業の実施状況に関する調査・年報）により評価する</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.140（点3）</t>
+          <t>確認事項No.5（点2）</t>
         </is>
       </c>
     </row>
@@ -11346,24 +11364,24 @@
       <c r="A72" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="B72" s="21" t="inlineStr">
+      <c r="B72" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
+          <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
+          <t>3調査の点検事項は当方の判定のままとする</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.149（点3）</t>
+          <t>確認事項No.8（点2）</t>
         </is>
       </c>
     </row>
@@ -11371,24 +11389,24 @@
       <c r="A73" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="B73" s="21" t="inlineStr">
+      <c r="B73" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けた要介護度の変化</t>
+          <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
+          <t>会議日程及びパブリックコメントの期間は仕様書５の工程による</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.30（点3）</t>
+          <t>確認事項No.19（点2）</t>
         </is>
       </c>
     </row>
@@ -11396,24 +11414,24 @@
       <c r="A74" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="B74" s="21" t="inlineStr">
+      <c r="B74" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率の経緯</t>
+          <t>キックオフ会議資料への工程表の反映</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
+          <t>現行の工程表のまま進める</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.34（点3）</t>
+          <t>確認事項No.42（点2）</t>
         </is>
       </c>
     </row>
@@ -11421,24 +11439,24 @@
       <c r="A75" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="B75" s="21" t="inlineStr">
+      <c r="B75" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
+          <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
+          <t>告示を確認できないものとして、特別地域加算の判定を計画素案に書かず［要確認］のまま残す</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.35（点3）</t>
+          <t>確認事項No.1（点2）</t>
         </is>
       </c>
     </row>
@@ -11446,24 +11464,24 @@
       <c r="A76" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="B76" s="21" t="inlineStr">
+      <c r="B76" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績と収納率</t>
+          <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
+          <t>類似保険者との比較は公表されている同規模保険者40団体による</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.36（点3）</t>
+          <t>確認事項No.3（点2）</t>
         </is>
       </c>
     </row>
@@ -11471,24 +11489,24 @@
       <c r="A77" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="B77" s="21" t="inlineStr">
+      <c r="B77" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+          <t>交付金の評価調書</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月新設の3区分を0として立てる</t>
+          <t>評価調書を受領できないものとして、得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できない旨を注記する</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.115（点3）</t>
+          <t>確認事項No.6（点2）</t>
         </is>
       </c>
     </row>
@@ -11496,24 +11514,24 @@
       <c r="A78" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="B78" s="21" t="inlineStr">
+      <c r="B78" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16の代理指標</t>
+          <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16は代理指標への振替案のとおりとする</t>
+          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.4（点2）</t>
+          <t>確認事項No.9（点2）</t>
         </is>
       </c>
     </row>
@@ -11521,24 +11539,24 @@
       <c r="A79" s="5" t="n">
         <v>74</v>
       </c>
-      <c r="B79" s="21" t="inlineStr">
+      <c r="B79" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績</t>
+          <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績を受領できないものとして、公表資料（交付金の評価結果・総合事業の実施状況に関する調査・年報）により評価する</t>
+          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.5（点2）</t>
+          <t>確認事項No.10（点2）</t>
         </is>
       </c>
     </row>
@@ -11546,24 +11564,24 @@
       <c r="A80" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="B80" s="21" t="inlineStr">
+      <c r="B80" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項の取扱い</t>
+          <t>町別の人口・世帯データ</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項は当方の判定のままとする</t>
+          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.8（点2）</t>
+          <t>確認事項No.11（点2）</t>
         </is>
       </c>
     </row>
@@ -11571,24 +11589,24 @@
       <c r="A81" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="B81" s="21" t="inlineStr">
+      <c r="B81" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>会議日程とパブリックコメントの期間</t>
+          <t>日常生活圏域別のデータ</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>会議日程及びパブリックコメントの期間は仕様書５の工程による</t>
+          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.19（点2）</t>
+          <t>確認事項No.12（点2）</t>
         </is>
       </c>
     </row>
@@ -11596,24 +11614,24 @@
       <c r="A82" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="B82" s="21" t="inlineStr">
+      <c r="B82" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料への工程表の反映</t>
+          <t>骨子案の内容の確認</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>現行の工程表のまま進める</t>
+          <t>骨子案は提出した内容のままとする</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.42（点2）</t>
+          <t>確認事項No.18（点2）</t>
         </is>
       </c>
     </row>
@@ -11621,24 +11639,24 @@
       <c r="A83" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="B83" s="21" t="inlineStr">
+      <c r="B83" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>特別地域加算の対象地域告示</t>
+          <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>告示を確認できないものとして、特別地域加算の判定を計画素案に書かず［要確認］のまま残す</t>
+          <t>北海道の評価指標の読替えは当方の案のままとする</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.1（点2）</t>
+          <t>確認事項No.22（点2）</t>
         </is>
       </c>
     </row>
@@ -11646,24 +11664,24 @@
       <c r="A84" s="5" t="n">
         <v>79</v>
       </c>
-      <c r="B84" s="21" t="inlineStr">
+      <c r="B84" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較分析の対象</t>
+          <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較は公表されている同規模保険者40団体による</t>
+          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.3（点2）</t>
+          <t>確認事項No.27（点2）</t>
         </is>
       </c>
     </row>
@@ -11671,24 +11689,24 @@
       <c r="A85" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="B85" s="21" t="inlineStr">
+      <c r="B85" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価調書</t>
+          <t>調査対象者の範囲の確認</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>評価調書を受領できないものとして、得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できない旨を注記する</t>
+          <t>現に収録している調査対象者の範囲による</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.6（点2）</t>
+          <t>確認事項No.28（点2）</t>
         </is>
       </c>
     </row>
@@ -11696,24 +11714,24 @@
       <c r="A86" s="5" t="n">
         <v>81</v>
       </c>
-      <c r="B86" s="21" t="inlineStr">
+      <c r="B86" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>調査の対象者範囲と回収率</t>
+          <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
+          <t>公表されている全国集計の値による</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.9（点2）</t>
+          <t>確認事項No.38（点2）</t>
         </is>
       </c>
     </row>
@@ -11721,24 +11739,24 @@
       <c r="A87" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="B87" s="21" t="inlineStr">
+      <c r="B87" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>介護人材実態調査の採用者数・退職者数</t>
+          <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
+          <t>令和8年9月25日の再提供により決着済み。再提供を受けたファイルの値（3町合計と円単位一致）による</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.10（点2）</t>
+          <t>確認事項No.46（点2）</t>
         </is>
       </c>
     </row>
@@ -11746,24 +11764,24 @@
       <c r="A88" s="5" t="n">
         <v>83</v>
       </c>
-      <c r="B88" s="21" t="inlineStr">
+      <c r="B88" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>町別の人口・世帯データ</t>
+          <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
+          <t>総括表（保険者単位）を用い、計画作成支援ツールの実績値シートは比較のためにのみ用いる</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.11（点2）</t>
+          <t>確認事項No.47（点2）</t>
         </is>
       </c>
     </row>
@@ -11771,24 +11789,24 @@
       <c r="A89" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="B89" s="21" t="inlineStr">
+      <c r="B89" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域別のデータ</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
+          <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値による</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.12（点2）</t>
+          <t>確認事項No.48（点2）</t>
         </is>
       </c>
     </row>
@@ -11796,24 +11814,24 @@
       <c r="A90" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="B90" s="21" t="inlineStr">
+      <c r="B90" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>骨子案の内容の確認</t>
+          <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>骨子案は提出した内容のままとする</t>
+          <t>受領済みの年報・月報の値による</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.18（点2）</t>
+          <t>確認事項No.50（点2）</t>
         </is>
       </c>
     </row>
@@ -11821,24 +11839,24 @@
       <c r="A91" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="B91" s="21" t="inlineStr">
+      <c r="B91" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標の読替えの考え方</t>
+          <t>月報の値の接続のずれ（ご報告）</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標の読替えは当方の案のままとする</t>
+          <t>月報の値の接続のずれは記録として残し、計画本文には用いない</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.22（点2）</t>
+          <t>確認事項No.51（点2）</t>
         </is>
       </c>
     </row>
@@ -11846,24 +11864,24 @@
       <c r="A92" s="5" t="n">
         <v>87</v>
       </c>
-      <c r="B92" s="21" t="inlineStr">
+      <c r="B92" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>令和4年度 健康とくらしの調査の集計表</t>
+          <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
+          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.27（点2）</t>
+          <t>確認事項No.52（点2）</t>
         </is>
       </c>
     </row>
@@ -11871,24 +11889,24 @@
       <c r="A93" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="B93" s="21" t="inlineStr">
+      <c r="B93" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>調査対象者の範囲の確認</t>
+          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>現に収録している調査対象者の範囲による</t>
+          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合は1億円あたり月額約▲310円となることを併記する</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.28（点2）</t>
+          <t>確認事項No.53（点2）</t>
         </is>
       </c>
     </row>
@@ -11896,24 +11914,24 @@
       <c r="A94" s="5" t="n">
         <v>89</v>
       </c>
-      <c r="B94" s="21" t="inlineStr">
+      <c r="B94" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の令和6年・令和7年調査の結果</t>
+          <t>議事録の文書プロパティに個人名が再度入る</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>公表されている全国集計の値による</t>
+          <t>議事録は作成者名を落として再出力する（当方で対応する）</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.38（点2）</t>
+          <t>確認事項No.54（点2）</t>
         </is>
       </c>
     </row>
@@ -11921,24 +11939,24 @@
       <c r="A95" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="B95" s="21" t="inlineStr">
+      <c r="B95" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の給付費の集計が一致しない</t>
+          <t>議事録の表記に関するご提案3件</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月25日の再提供により決着済み。再提供を受けたファイルの値（3町合計と円単位一致）による</t>
+          <t>議事録の表記はご提案3件のとおり改める</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.46（点2）</t>
+          <t>確認事項No.55（点2）</t>
         </is>
       </c>
     </row>
@@ -11946,24 +11964,24 @@
       <c r="A96" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="B96" s="21" t="inlineStr">
+      <c r="B96" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの実績値シートの確認</t>
+          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>総括表（保険者単位）を用い、計画作成支援ツールの実績値シートは比較のためにのみ用いる</t>
+          <t>他団体の集計帳票6件は成果品に用いない</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.47（点2）</t>
+          <t>確認事項No.56（点2）</t>
         </is>
       </c>
     </row>
@@ -11971,24 +11989,24 @@
       <c r="A97" s="5" t="n">
         <v>92</v>
       </c>
-      <c r="B97" s="21" t="inlineStr">
+      <c r="B97" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
+          <t>調整交付金の算定基礎の確認</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値による</t>
+          <t>現行の扱い（第9期の算定を再現し公表値6,428円と一致する扱い）による</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.48（点2）</t>
+          <t>確認事項No.59（点2）</t>
         </is>
       </c>
     </row>
@@ -11996,24 +12014,24 @@
       <c r="A98" s="5" t="n">
         <v>93</v>
       </c>
-      <c r="B98" s="21" t="inlineStr">
+      <c r="B98" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>年報・月報の受領に伴う確認</t>
+          <t>交付金の評価項目と19施策の割当て</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>受領済みの年報・月報の値による</t>
+          <t>交付金の評価項目と19施策の割当ては当方の案のままとする</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.50（点2）</t>
+          <t>確認事項No.61（点2）</t>
         </is>
       </c>
     </row>
@@ -12021,24 +12039,24 @@
       <c r="A99" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="B99" s="21" t="inlineStr">
+      <c r="B99" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれ（ご報告）</t>
+          <t>職員個票のリストによる重複確認の可否</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれは記録として残し、計画本文には用いない</t>
+          <t>職員個票を突き合わせず、事業所への照会により重複を判別する</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.51（点2）</t>
+          <t>確認事項No.80（点2）</t>
         </is>
       </c>
     </row>
@@ -12046,24 +12064,24 @@
       <c r="A100" s="5" t="n">
         <v>95</v>
       </c>
-      <c r="B100" s="21" t="inlineStr">
+      <c r="B100" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領に伴う確認</t>
+          <t>構成町との意見交換会の実施方法と町別データシート</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
+          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで進める</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.52（点2）</t>
+          <t>確認事項No.83（点2）</t>
         </is>
       </c>
     </row>
@@ -12071,24 +12089,24 @@
       <c r="A101" s="5" t="n">
         <v>96</v>
       </c>
-      <c r="B101" s="21" t="inlineStr">
+      <c r="B101" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
+          <t>町別データシートの内容と配付</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合は1億円あたり月額約▲310円となることを併記する</t>
+          <t>町別データシートは現行の内容のまま配付する</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.53（点2）</t>
+          <t>確認事項No.85（点2）</t>
         </is>
       </c>
     </row>
@@ -12096,24 +12114,24 @@
       <c r="A102" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="B102" s="21" t="inlineStr">
+      <c r="B102" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>議事録の文書プロパティに個人名が再度入る</t>
+          <t>成果品の統合の方針</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>議事録は作成者名を落として再出力する（当方で対応する）</t>
+          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す（現行）</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.54（点2）</t>
+          <t>確認事項No.117（点2）</t>
         </is>
       </c>
     </row>
@@ -12121,24 +12139,24 @@
       <c r="A103" s="5" t="n">
         <v>98</v>
       </c>
-      <c r="B103" s="21" t="inlineStr">
+      <c r="B103" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記に関するご提案3件</t>
+          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記はご提案3件のとおり改める</t>
+          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.55（点2）</t>
+          <t>確認事項No.138（点2）</t>
         </is>
       </c>
     </row>
@@ -12146,24 +12164,24 @@
       <c r="A104" s="5" t="n">
         <v>99</v>
       </c>
-      <c r="B104" s="21" t="inlineStr">
+      <c r="B104" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
+          <t>健康とくらしの調査の個票の再提供の要否</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>他団体の集計帳票6件は成果品に用いない</t>
+          <t>健康とくらしの調査の個票の再提供を依頼しない（成果品は収録済みで内容が確定しており、現時点で不足がない）</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.56（点2）</t>
+          <t>確認事項No.139（点2）</t>
         </is>
       </c>
     </row>
@@ -12171,24 +12189,24 @@
       <c r="A105" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="B105" s="21" t="inlineStr">
+      <c r="B105" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>調整交付金の算定基礎の確認</t>
+          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>現行の扱い（第9期の算定を再現し公表値6,428円と一致する扱い）による</t>
+          <t>受領済みの画面の写しの範囲で概算し、確認できていない項目はその旨を明記する</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.59（点2）</t>
+          <t>確認事項No.148（点2）</t>
         </is>
       </c>
     </row>
@@ -12196,24 +12214,24 @@
       <c r="A106" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="B106" s="21" t="inlineStr">
+      <c r="B106" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当て</t>
+          <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当ては当方の案のままとする</t>
+          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.61（点2）</t>
+          <t>確認事項No.60（点2）</t>
         </is>
       </c>
     </row>
@@ -12221,24 +12239,24 @@
       <c r="A107" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="B107" s="21" t="inlineStr">
+      <c r="B107" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>職員個票のリストによる重複確認の可否</t>
+          <t>区域内に事業所がないサービスの住民向けの記載</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>職員個票を突き合わせず、事業所への照会により重複を判別する</t>
+          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.80（点2）</t>
+          <t>確認事項No.64（点2）</t>
         </is>
       </c>
     </row>
@@ -12246,24 +12264,24 @@
       <c r="A108" s="5" t="n">
         <v>103</v>
       </c>
-      <c r="B108" s="21" t="inlineStr">
+      <c r="B108" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>構成町との意見交換会の実施方法と町別データシート</t>
+          <t>成果指向型配分枠（令和8年度新設）への対応</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで進める</t>
+          <t>成果指向型配分枠への対応状況を確認できないものとして、第10期の施策には位置づけず、確認でき次第加える</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.83（点2）</t>
+          <t>確認事項No.69（点2）</t>
         </is>
       </c>
     </row>
@@ -12271,24 +12289,24 @@
       <c r="A109" s="5" t="n">
         <v>104</v>
       </c>
-      <c r="B109" s="21" t="inlineStr">
+      <c r="B109" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>町別データシートの内容と配付</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>町別データシートは現行の内容のまま配付する</t>
+          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.85（点2）</t>
+          <t>確認事項No.89（点2）</t>
         </is>
       </c>
     </row>
@@ -12296,24 +12314,24 @@
       <c r="A110" s="5" t="n">
         <v>105</v>
       </c>
-      <c r="B110" s="21" t="inlineStr">
+      <c r="B110" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>成果品の統合の方針</t>
+          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す（現行）</t>
+          <t>第9期計画の本文及び前回調査の原集計表を受領できないものとして、前回調査との比較は割合のみとし、指標別の分母を確認できない旨を注記する</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.117（点2）</t>
+          <t>確認事項No.90（点2）</t>
         </is>
       </c>
     </row>
@@ -12321,24 +12339,24 @@
       <c r="A111" s="5" t="n">
         <v>106</v>
       </c>
-      <c r="B111" s="21" t="inlineStr">
+      <c r="B111" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
+          <t>介護給付費通知及び給付実績の活用による確認等</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ</t>
+          <t>介護給付費通知の実施状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.138（点2）</t>
+          <t>確認事項No.91（点2）</t>
         </is>
       </c>
     </row>
@@ -12346,24 +12364,24 @@
       <c r="A112" s="5" t="n">
         <v>107</v>
       </c>
-      <c r="B112" s="21" t="inlineStr">
+      <c r="B112" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供の要否</t>
+          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供を依頼しない（成果品は収録済みで内容が確定しており、現時点で不足がない）</t>
+          <t>認定調査の委託の状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.139（点2）</t>
+          <t>確認事項No.92（点2）</t>
         </is>
       </c>
     </row>
@@ -12371,24 +12389,24 @@
       <c r="A113" s="5" t="n">
         <v>108</v>
       </c>
-      <c r="B113" s="21" t="inlineStr">
+      <c r="B113" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
+          <t>令和9年4月1日から義務となる2件への対応</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>受領済みの画面の写しの範囲で概算し、確認できていない項目はその旨を明記する</t>
+          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.148（点2）</t>
+          <t>確認事項No.97（点2）</t>
         </is>
       </c>
     </row>
@@ -12396,24 +12414,24 @@
       <c r="A114" s="5" t="n">
         <v>109</v>
       </c>
-      <c r="B114" s="21" t="inlineStr">
+      <c r="B114" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提（受託者案）</t>
+          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
+          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.60（点2）</t>
+          <t>確認事項No.99（点2）</t>
         </is>
       </c>
     </row>
@@ -12421,24 +12439,24 @@
       <c r="A115" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="B115" s="21" t="inlineStr">
+      <c r="B115" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスの住民向けの記載</t>
+          <t>補正しても外れるサービス6件の理由</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
+          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.64（点2）</t>
+          <t>確認事項No.108（点2）</t>
         </is>
       </c>
     </row>
@@ -12446,24 +12464,24 @@
       <c r="A116" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="B116" s="21" t="inlineStr">
+      <c r="B116" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠（令和8年度新設）への対応</t>
+          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠への対応状況を確認できないものとして、第10期の施策には位置づけず、確認でき次第加える</t>
+          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.69（点2）</t>
+          <t>確認事項No.111（点2）</t>
         </is>
       </c>
     </row>
@@ -12471,24 +12489,24 @@
       <c r="A117" s="5" t="n">
         <v>112</v>
       </c>
-      <c r="B117" s="21" t="inlineStr">
+      <c r="B117" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
+          <t>施策2-5の代表KPIはO2（提起された地域課題のうち翌年度の事業・予算に反映されたものの割合）とする（当方案）</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.89（点2）</t>
+          <t>確認事項No.118（点2）</t>
         </is>
       </c>
     </row>
@@ -12496,24 +12514,24 @@
       <c r="A118" s="5" t="n">
         <v>113</v>
       </c>
-      <c r="B118" s="21" t="inlineStr">
+      <c r="B118" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
+          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文及び前回調査の原集計表を受領できないものとして、前回調査との比較は割合のみとし、指標別の分母を確認できない旨を注記する</t>
+          <t>地域ケア会議の記録様式は協議資料にとどめ、令和9年度に整える</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.90（点2）</t>
+          <t>確認事項No.119（点2）</t>
         </is>
       </c>
     </row>
@@ -12521,24 +12539,24 @@
       <c r="A119" s="5" t="n">
         <v>114</v>
       </c>
-      <c r="B119" s="21" t="inlineStr">
+      <c r="B119" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知及び給付実績の活用による確認等</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知の実施状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.91（点2）</t>
+          <t>確認事項No.120（点2）</t>
         </is>
       </c>
     </row>
@@ -12546,24 +12564,24 @@
       <c r="A120" s="5" t="n">
         <v>115</v>
       </c>
-      <c r="B120" s="21" t="inlineStr">
+      <c r="B120" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
+          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>認定調査の委託の状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
+          <t>令和7年度の実施報告書により把握できる範囲で記述する</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.92（点2）</t>
+          <t>確認事項No.121（点2）</t>
         </is>
       </c>
     </row>
@@ -12571,24 +12589,24 @@
       <c r="A121" s="5" t="n">
         <v>116</v>
       </c>
-      <c r="B121" s="21" t="inlineStr">
+      <c r="B121" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月1日から義務となる2件への対応</t>
+          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
+          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.97（点2）</t>
+          <t>確認事項No.125（点2）</t>
         </is>
       </c>
     </row>
@@ -12596,24 +12614,24 @@
       <c r="A122" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="B122" s="21" t="inlineStr">
+      <c r="B122" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
+          <t>見える化システムの総人口の設定を案Cに改めるか</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
+          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.99（点2）</t>
+          <t>確認事項No.127（点2）</t>
         </is>
       </c>
     </row>
@@ -12621,24 +12639,24 @@
       <c r="A123" s="5" t="n">
         <v>118</v>
       </c>
-      <c r="B123" s="21" t="inlineStr">
+      <c r="B123" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れるサービス6件の理由</t>
+          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
+          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.108（点2）</t>
+          <t>確認事項No.133（点2）</t>
         </is>
       </c>
     </row>
@@ -12646,24 +12664,24 @@
       <c r="A124" s="5" t="n">
         <v>119</v>
       </c>
-      <c r="B124" s="21" t="inlineStr">
+      <c r="B124" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
+          <t>画面の令和7年度と年報の月平均の食い違い</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
+          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.111（点2）</t>
+          <t>確認事項No.136（点2）</t>
         </is>
       </c>
     </row>
@@ -12671,24 +12689,24 @@
       <c r="A125" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="B125" s="21" t="inlineStr">
+      <c r="B125" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
+          <t>計画素案の未確定箇所の表示の統一</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIはO2（提起された地域課題のうち翌年度の事業・予算に反映されたものの割合）とする（当方案）</t>
+          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとする</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.118（点2）</t>
+          <t>確認事項No.143（点2）</t>
         </is>
       </c>
     </row>
@@ -12696,24 +12714,24 @@
       <c r="A126" s="5" t="n">
         <v>121</v>
       </c>
-      <c r="B126" s="21" t="inlineStr">
+      <c r="B126" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
+          <t>計画素案 第2章第1節に町別の図を加えるか</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の記録様式は協議資料にとどめ、令和9年度に整える</t>
+          <t>計画素案 第2章第1節に町別の図を加えない。加筆分は協議用の資料にとどめる</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.119（点2）</t>
+          <t>確認事項No.154（点2）</t>
         </is>
       </c>
     </row>
@@ -12721,24 +12739,24 @@
       <c r="A127" s="5" t="n">
         <v>122</v>
       </c>
-      <c r="B127" s="21" t="inlineStr">
+      <c r="B127" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
+          <t>中長期推計を令和12・27・32年度まで広げるか</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
+          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.120（点2）</t>
+          <t>確認事項No.157（点2）</t>
         </is>
       </c>
     </row>
@@ -12746,24 +12764,24 @@
       <c r="A128" s="5" t="n">
         <v>123</v>
       </c>
-      <c r="B128" s="21" t="inlineStr">
+      <c r="B128" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
+          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の実施報告書により把握できる範囲で記述する</t>
+          <t>設問ごとの有効回答を分母とし、町別の値は掲げない（令和8年9月25日に是正済み）</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.121（点2）</t>
+          <t>確認事項No.158（点2）</t>
         </is>
       </c>
     </row>
@@ -12771,24 +12789,24 @@
       <c r="A129" s="5" t="n">
         <v>124</v>
       </c>
-      <c r="B129" s="21" t="inlineStr">
+      <c r="B129" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
+          <t>東川町の通いの場の整備と担い手の確保</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
+          <t>現状のまま（東川町の整備を見込まない）第10期の目標値を置く</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.125（点2）</t>
+          <t>確認事項No.159（点2）</t>
         </is>
       </c>
     </row>
@@ -12796,24 +12814,24 @@
       <c r="A130" s="5" t="n">
         <v>125</v>
       </c>
-      <c r="B130" s="21" t="inlineStr">
+      <c r="B130" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総人口の設定を案Cに改めるか</t>
+          <t>東川町の認知症サポーター養成講座の実施状況</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
+          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.127（点2）</t>
+          <t>確認事項No.160（点2）</t>
         </is>
       </c>
     </row>
@@ -12821,24 +12839,24 @@
       <c r="A131" s="5" t="n">
         <v>126</v>
       </c>
-      <c r="B131" s="21" t="inlineStr">
+      <c r="B131" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+          <t>東川町のチームオレンジ事業の位置づけ</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
+          <t>東川町の取組として記述し3町展開は記述しない</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.133（点2）</t>
+          <t>確認事項No.161（点2）</t>
         </is>
       </c>
     </row>
@@ -12846,24 +12864,24 @@
       <c r="A132" s="5" t="n">
         <v>127</v>
       </c>
-      <c r="B132" s="21" t="inlineStr">
+      <c r="B132" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度と年報の月平均の食い違い</t>
+          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
+          <t>令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.136（点2）</t>
+          <t>確認事項No.162（点2）</t>
         </is>
       </c>
     </row>
@@ -12871,24 +12889,24 @@
       <c r="A133" s="5" t="n">
         <v>128</v>
       </c>
-      <c r="B133" s="21" t="inlineStr">
+      <c r="B133" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所の表示の統一</t>
+          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとする</t>
+          <t>美瑛町の取組として記述し3町展開は記述しない</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.143（点2）</t>
+          <t>確認事項No.163（点2）</t>
         </is>
       </c>
     </row>
@@ -12896,24 +12914,24 @@
       <c r="A134" s="5" t="n">
         <v>129</v>
       </c>
-      <c r="B134" s="21" t="inlineStr">
+      <c r="B134" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えるか</t>
+          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えない。加筆分は協議用の資料にとどめる</t>
+          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.154（点2）</t>
+          <t>確認事項No.164（点2）</t>
         </is>
       </c>
     </row>
@@ -12921,24 +12939,24 @@
       <c r="A135" s="5" t="n">
         <v>130</v>
       </c>
-      <c r="B135" s="21" t="inlineStr">
+      <c r="B135" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>中長期推計を令和12・27・32年度まで広げるか</t>
+          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
+          <t>現に確認できる取組の範囲で記述する</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.157（点2）</t>
+          <t>確認事項No.165（点2）</t>
         </is>
       </c>
     </row>
@@ -12946,24 +12964,24 @@
       <c r="A136" s="5" t="n">
         <v>131</v>
       </c>
-      <c r="B136" s="21" t="inlineStr">
+      <c r="B136" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
+          <t>東神楽町の通いの場の維持</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>設問ごとの有効回答を分母とし、町別の値は掲げない（令和8年9月25日に是正済み）</t>
+          <t>令和6年度の水準が続くものとして目標値を置く</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.158（点2）</t>
+          <t>確認事項No.166（点2）</t>
         </is>
       </c>
     </row>
@@ -12971,24 +12989,24 @@
       <c r="A137" s="5" t="n">
         <v>132</v>
       </c>
-      <c r="B137" s="21" t="inlineStr">
+      <c r="B137" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
+          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
+          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.170（点2）</t>
+          <t>確認事項No.167（点2）</t>
         </is>
       </c>
     </row>
@@ -12996,24 +13014,24 @@
       <c r="A138" s="5" t="n">
         <v>133</v>
       </c>
-      <c r="B138" s="21" t="inlineStr">
+      <c r="B138" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提</t>
+          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
+          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.16（点2）</t>
+          <t>確認事項No.170（点2）</t>
         </is>
       </c>
     </row>
@@ -13021,24 +13039,24 @@
       <c r="A139" s="5" t="n">
         <v>134</v>
       </c>
-      <c r="B139" s="21" t="inlineStr">
+      <c r="B139" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
+          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
+          <t>の当方の扱い＝掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.2（点1）</t>
+          <t>確認事項No.172（点2）</t>
         </is>
       </c>
     </row>
@@ -13046,24 +13064,24 @@
       <c r="A140" s="5" t="n">
         <v>135</v>
       </c>
-      <c r="B140" s="21" t="inlineStr">
+      <c r="B140" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域の判定資料</t>
+          <t>保険料算定の前提</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
+          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.13（点1）</t>
+          <t>確認事項No.16（点2）</t>
         </is>
       </c>
     </row>
@@ -13071,24 +13089,24 @@
       <c r="A141" s="5" t="n">
         <v>136</v>
       </c>
-      <c r="B141" s="21" t="inlineStr">
+      <c r="B141" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎とする系列</t>
+          <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
+          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.14（点1）</t>
+          <t>確認事項No.2（点1）</t>
         </is>
       </c>
     </row>
@@ -13096,24 +13114,24 @@
       <c r="A142" s="5" t="n">
         <v>137</v>
       </c>
-      <c r="B142" s="21" t="inlineStr">
+      <c r="B142" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>認定者数の基準月と月次推移</t>
+          <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
+          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.15（点1）</t>
+          <t>確認事項No.13（点1）</t>
         </is>
       </c>
     </row>
@@ -13121,24 +13139,24 @@
       <c r="A143" s="5" t="n">
         <v>138</v>
       </c>
-      <c r="B143" s="21" t="inlineStr">
+      <c r="B143" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>3町計画への共通指標の掲載</t>
+          <t>人口推計の基礎とする系列</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
+          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.17（点1）</t>
+          <t>確認事項No.14（点1）</t>
         </is>
       </c>
     </row>
@@ -13146,24 +13164,24 @@
       <c r="A144" s="5" t="n">
         <v>139</v>
       </c>
-      <c r="B144" s="21" t="inlineStr">
+      <c r="B144" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場</t>
+          <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
+          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.20（点1）</t>
+          <t>確認事項No.15（点1）</t>
         </is>
       </c>
     </row>
@@ -13171,24 +13189,24 @@
       <c r="A145" s="5" t="n">
         <v>140</v>
       </c>
-      <c r="B145" s="21" t="inlineStr">
+      <c r="B145" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様</t>
+          <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
+          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.21（点1）</t>
+          <t>確認事項No.17（点1）</t>
         </is>
       </c>
     </row>
@@ -13196,24 +13214,24 @@
       <c r="A146" s="5" t="n">
         <v>141</v>
       </c>
-      <c r="B146" s="21" t="inlineStr">
+      <c r="B146" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>事業所の定員・稼働率データ</t>
+          <t>北海道・圏域との調整の場</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
+          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.23（点1）</t>
+          <t>確認事項No.20（点1）</t>
         </is>
       </c>
     </row>
@@ -13221,24 +13239,24 @@
       <c r="A147" s="5" t="n">
         <v>142</v>
       </c>
-      <c r="B147" s="21" t="inlineStr">
+      <c r="B147" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>認知症・医療介護連携の実績データ</t>
+          <t>成果品の仕様</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr">
         <is>
-          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
+          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.26（点1）</t>
+          <t>確認事項No.21（点1）</t>
         </is>
       </c>
     </row>
@@ -13246,24 +13264,24 @@
       <c r="A148" s="5" t="n">
         <v>143</v>
       </c>
-      <c r="B148" s="21" t="inlineStr">
+      <c r="B148" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提</t>
+          <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
+          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.29（点1）</t>
+          <t>確認事項No.23（点1）</t>
         </is>
       </c>
     </row>
@@ -13271,24 +13289,24 @@
       <c r="A149" s="5" t="n">
         <v>144</v>
       </c>
-      <c r="B149" s="21" t="inlineStr">
+      <c r="B149" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の実施予定と推計での扱い</t>
+          <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr">
         <is>
-          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
+          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.31（点1）</t>
+          <t>確認事項No.26（点1）</t>
         </is>
       </c>
     </row>
@@ -13296,24 +13314,24 @@
       <c r="A150" s="5" t="n">
         <v>145</v>
       </c>
-      <c r="B150" s="21" t="inlineStr">
+      <c r="B150" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>統合した成果品の元の資料を残すか</t>
+          <t>重度化の速度の前提</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>統合した成果品の元の資料を残す</t>
+          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.144（点1）</t>
+          <t>確認事項No.29（点1）</t>
         </is>
       </c>
     </row>
@@ -13321,24 +13339,24 @@
       <c r="A151" s="5" t="n">
         <v>146</v>
       </c>
-      <c r="B151" s="21" t="inlineStr">
+      <c r="B151" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
+          <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr">
         <is>
-          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
+          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.156（点1）</t>
+          <t>確認事項No.31（点1）</t>
         </is>
       </c>
     </row>
@@ -13346,24 +13364,24 @@
       <c r="A152" s="5" t="n">
         <v>147</v>
       </c>
-      <c r="B152" s="21" t="inlineStr">
+      <c r="B152" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
+          <t>統合した成果品の元の資料を残すか</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
+          <t>統合した成果品の元の資料を残す</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.171（点1）</t>
+          <t>確認事項No.144（点1）</t>
         </is>
       </c>
     </row>
@@ -13371,24 +13389,24 @@
       <c r="A153" s="5" t="n">
         <v>148</v>
       </c>
-      <c r="B153" s="21" t="inlineStr">
+      <c r="B153" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
+          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
         </is>
       </c>
       <c r="D153" s="6" t="inlineStr">
         <is>
-          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
+          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.74（点1）</t>
+          <t>確認事項No.156（点1）</t>
         </is>
       </c>
     </row>
@@ -13396,24 +13414,24 @@
       <c r="A154" s="5" t="n">
         <v>149</v>
       </c>
-      <c r="B154" s="21" t="inlineStr">
+      <c r="B154" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスの確保方策の決定</t>
+          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.24（点0）</t>
+          <t>確認事項No.169（点1）</t>
         </is>
       </c>
     </row>
@@ -13421,46 +13439,147 @@
       <c r="A155" s="5" t="n">
         <v>150</v>
       </c>
-      <c r="B155" s="21" t="inlineStr">
+      <c r="B155" s="20" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
+          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
+        </is>
+      </c>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.171（点1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="44" customHeight="1">
+      <c r="A156" s="5" t="n">
+        <v>151</v>
+      </c>
+      <c r="B156" s="20" t="inlineStr">
+        <is>
+          <t>既定値で進める</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>の当方の扱い＝現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.173（点1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="44" customHeight="1">
+      <c r="A157" s="5" t="n">
+        <v>152</v>
+      </c>
+      <c r="B157" s="20" t="inlineStr">
+        <is>
+          <t>既定値で進める</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
+        </is>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.74（点1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="44" customHeight="1">
+      <c r="A158" s="5" t="n">
+        <v>153</v>
+      </c>
+      <c r="B158" s="20" t="inlineStr">
+        <is>
+          <t>既定値で進める</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>24時間対応サービスの確保方策の決定</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.24（点0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="44" customHeight="1">
+      <c r="A159" s="5" t="n">
+        <v>154</v>
+      </c>
+      <c r="B159" s="20" t="inlineStr">
+        <is>
+          <t>既定値で進める</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="D155" s="6" t="inlineStr">
+      <c r="D159" s="6" t="inlineStr">
         <is>
           <t>代表KPIの目標値は、令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置く</t>
         </is>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="E159" s="6" t="inlineStr">
         <is>
           <t>確認事項No.25（点0）</t>
         </is>
       </c>
     </row>
-    <row r="156" ht="62" customHeight="1">
-      <c r="A156" s="14" t="inlineStr">
+    <row r="160" ht="76" customHeight="1">
+      <c r="A160" s="14" t="inlineStr">
         <is>
           <t>注1）「据え置き（区分A）」は、資料の受領を待たずに当方の側で確定できるものです。
 注2）「既定値で進める」は、決着しない場合の扱いを置けているため決定を待たずに作業を進められるものです。決定を受けた時点で見直します。
-注3）ここに現れないもの（既定値を置けていない確認事項）は、扱いを決めること自体が翌日の作業になります。02シートを見ます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="157"/>
-    <row r="158" ht="20" customHeight="1">
-      <c r="A158" s="3" t="inlineStr">
+注3）ここに現れないもの（既定値を置けていない確認事項）は、扱いを決めること自体が翌日の作業になります。02シートを見ます。
+注4）既定値のとおり計画素案へ反映し終えたもの6件（確認事項No.88・No.105・No.106・No.112・No.113・No.131）は、作業としては終わっているため本表から除いています。ご決定はなお待っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="161"/>
+    <row r="162" ht="20" customHeight="1">
+      <c r="A162" s="3" t="inlineStr">
         <is>
           <t>2　先に扱いを決めるもの（既定値を置けていない）　0件</t>
         </is>
       </c>
     </row>
-    <row r="159" ht="18" customHeight="1">
-      <c r="A159" s="22" t="inlineStr">
+    <row r="163" ht="18" customHeight="1">
+      <c r="A163" s="21" t="inlineStr">
         <is>
           <t>ありません。未決の確認事項の全件に扱いを置けています。</t>
         </is>
@@ -13470,10 +13589,10 @@
   <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A156:E156"/>
+    <mergeCell ref="A163:E163"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A159:E159"/>
-    <mergeCell ref="A158:E158"/>
+    <mergeCell ref="A160:E160"/>
+    <mergeCell ref="A162:E162"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13548,17 +13667,17 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>要介護度の構成（要介護度別の将来推計）</t>
+          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定した。年齢構成の変化による重度化は反映される。国の様式も見える化システムも要介護度別の推計を出力しない。令和8年度は4か月分（月報）しかなく、構成を取り直す基礎にならない（令和8年10月1日に再確認した）</t>
+          <t>1人1月あたり給付費は令和7年度で固定して概算する（月額で＋185〜＋374円に当たる）</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>見込量算定の据え置き 4</t>
+          <t>確認事項No.137（点7）</t>
         </is>
       </c>
     </row>
@@ -13573,17 +13692,17 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>季節補正</t>
+          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>季節指数の和が12となり換算係数が1.0000で恒等的に消える。補正を行わない。基準年度を完結年度に採る限り効きは0円であり、測定できても採用値は動かない。採用パターンP3は令和7年度（完結年度）を基準とする。利用状況統計表（審査月別）を継続して受領できれば季節性を測定できるが、24か月分を要し、現在は1か月分である（令和8年10月1日に再確認した）</t>
+          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>見込量算定の据え置き 12</t>
+          <t>確認事項No.110（点7）</t>
         </is>
       </c>
     </row>
@@ -13598,17 +13717,17 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域ごとの必要利用定員総数（法定記載事項）</t>
+          <t>認知症総合支援事業の実績のご提供</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>3町（3圏域）を基盤整備単位とする案のまま概算する。必要利用定員総数は［要協議］のまま残す</t>
+          <t>6事業別の事業費を受領できないものとして、認知症総合支援事業の量の見込みは立てず、3町の取組の回数のみを掲げる</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.88（点8）</t>
+          <t>確認事項No.150（点7）</t>
         </is>
       </c>
     </row>
@@ -13623,17 +13742,17 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを一律からサービス別の趨勢を半分反映する置き方に改めるか</t>
+          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>一律の伸びのまま概算し、補正の効き（月額▲58円又は＋48円）を併記する</t>
+          <t>省令上の類型を計画に掲げないまま概算する</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.106（点8）</t>
+          <t>確認事項No.98（点6）</t>
         </is>
       </c>
     </row>
@@ -13648,17 +13767,17 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設の必要利用定員総数を定めるか</t>
+          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設の必要利用定員総数を定めないまま概算する</t>
+          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）で概算する</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.113（点8）</t>
+          <t>確認事項No.100（点6）</t>
         </is>
       </c>
     </row>
@@ -13673,17 +13792,17 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の見込量の表に何を掲げるか</t>
+          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節は利用者数のみを掲げたまま概算する</t>
+          <t>素案 第6章第2節の表は見える化の自然体推計値のまま置き、P3による値を別掲する</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.131（点8）</t>
+          <t>確認事項No.101（点6）</t>
         </is>
       </c>
     </row>
@@ -13698,17 +13817,17 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の量の見込みを算定してよいか</t>
+          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の利用者実人数を据え置いて延ばした量の見込みを掲げ、令和7年度の実施状況は単位が異なるため別の表として示す</t>
+          <t>令和8年度を基準年度に用いず、季節補正も行わないまま概算する</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.112（点8）</t>
+          <t>確認事項No.103（点6）</t>
         </is>
       </c>
     </row>
@@ -13723,17 +13842,17 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行うか。行う場合の対象と歯止め</t>
+          <t>施設・居住系の実績の減少を将来へ延長するか</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行わないまま概算する（安全側）</t>
+          <t>施設・居住系の実績の減少を将来へ延長しないまま概算する</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.105（点7）</t>
+          <t>確認事項No.107（点6）</t>
         </is>
       </c>
     </row>
@@ -13939,7 +14058,7 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="23" t="n">
+      <c r="A5" s="22" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -13957,14 +14076,14 @@
           <t>173件／欠番 なし／重複 なし</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="23" t="n">
+      <c r="A6" s="22" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -13982,14 +14101,14 @@
           <t>確認事項160件／資料提供依頼20件</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="23" t="n">
+      <c r="A7" s="22" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -14007,14 +14126,14 @@
           <t>160件／合わない なし</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="23" t="n">
+      <c r="A8" s="22" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -14032,14 +14151,14 @@
           <t>降順 適合</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="23" t="n">
+      <c r="A9" s="22" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -14057,14 +14176,14 @@
           <t>内訳5種／規則6種／載っていない なし</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="23" t="n">
+      <c r="A10" s="22" t="n">
         <v>5.5</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -14082,14 +14201,14 @@
           <t>7件を拾った（最大374円）／上限超え なし</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="23" t="n">
+      <c r="A11" s="22" t="n">
         <v>6</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -14104,17 +14223,17 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>2＋2＋15＋4＝23／据え置き23件</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="inlineStr">
+          <t>4＋0＋15＋4＝23／据え置き23件</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="23" t="n">
+      <c r="A12" s="22" t="n">
         <v>7</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -14132,14 +14251,14 @@
           <t>最小0.00・最大0.99・全体79％</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="23" t="n">
+      <c r="A13" s="22" t="n">
         <v>8</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -14157,14 +14276,14 @@
           <t>記録 令和8年10月1日／本表 令和8年10月1日</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="23" t="n">
+      <c r="A14" s="22" t="n">
         <v>9</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -14182,14 +14301,14 @@
           <t>記録7件（最新 令和8年9月28日）</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="23" t="n">
+      <c r="A15" s="22" t="n">
         <v>10</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -14207,14 +14326,14 @@
           <t>13件（進める8・催促5）</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="23" t="n">
+      <c r="A16" s="22" t="n">
         <v>11</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -14229,17 +14348,17 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>150件（区分A 2・既定値 148）</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr">
+          <t>154件（区分A 0・既定値 154）</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="23" t="n">
+      <c r="A17" s="22" t="n">
         <v>12</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -14257,14 +14376,14 @@
           <t>0件</t>
         </is>
       </c>
-      <c r="E17" s="20" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="23" t="n">
+      <c r="A18" s="22" t="n">
         <v>13</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -14282,14 +14401,14 @@
           <t>0件</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="23" t="n">
+      <c r="A19" s="22" t="n">
         <v>14</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -14307,7 +14426,7 @@
           <t>残り0件</t>
         </is>
       </c>
-      <c r="E19" s="20" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -752,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>241932b</t>
+          <t>666b8ee</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>既定値の仮置き（未決160件）と据え置き区分Aの更新</t>
+          <t>3町合同意見交換会の資料と作業継続可能8件の処理</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
@@ -1255,20 +1255,38 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>9c17709</t>
+          <t>241932b</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>日次のWBS更新と翌日の作業順位（スキルと日次の表）</t>
+          <t>既定値の仮置き（未決160件）と据え置き区分Aの更新</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
       <c r="E24" s="6" t="inlineStr"/>
       <c r="F24" s="6" t="inlineStr"/>
     </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>9c17709</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>日次のWBS更新と翌日の作業順位（スキルと日次の表）</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
@@ -1280,8 +1298,8 @@
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1662,12 +1680,12 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 概算（+3）／月額への効き 最大374円（第10期の介護報酬改定率）（+4）／当方で動かせるか 国の告示・公布待ち（-2）</t>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 概算（+3）／月額への効き 最大327円（第10期の介護報酬改定率）（+4）／当方で動かせるか 国の告示・公布待ち（-2）</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費は令和7年度で固定して概算する（月額で＋185〜＋374円に当たる）</t>
+          <t>1人1月あたり給付費は令和7年度で固定して概算する（単価の趨勢を織り込まないことによる効きは計画素案 第6章第6節2に掲げる）</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1722,7 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）／月額への効き 最大374円（第10期の介護報酬改定率）（+4）／当方で動かせるか 国の告示・公布待ち（-2）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）／月額への効き 最大327円（第10期の介護報酬改定率）（+4）／当方で動かせるか 国の告示・公布待ち（-2）</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1838,7 +1856,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）で概算する</t>
+          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）により、要介護度別の伸びで概算する</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1898,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第2節の表は見える化の自然体推計値のまま置き、P3による値を別掲する</t>
+          <t>計画素案 第6章第2節の表は当方の算定（令和7年度の実績に要介護度別の認定者数の伸びを乗じたもの）による値とし、見える化システムの自然体推計による値は第6節2に対比として掲げる</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2615,7 @@
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。実績の趨勢（年率1.75％）を置いた場合の差（月額＋185円から＋374円）は据え置きの一覧に示す</t>
+          <t>単価を令和7年度で固定する（安全側）。実績の趨勢を置いた場合の差は据え置きの一覧及び計画素案 第6章第6節2に示す</t>
         </is>
       </c>
     </row>
@@ -9655,7 +9673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F163"/>
+  <dimension ref="A1:F155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9683,7 +9701,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　当方の作業だけで進められるもの　154件</t>
+          <t>1　当方の作業だけで進められるもの　146件</t>
         </is>
       </c>
     </row>
@@ -9721,17 +9739,17 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
+          <t>区域を越えた施設利用の扱い</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費は令和7年度で固定して概算する（月額で＋185〜＋374円に当たる）</t>
+          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.137（点7）</t>
+          <t>確認事項No.141（点6）</t>
         </is>
       </c>
     </row>
@@ -9746,17 +9764,17 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
+          <t>見込量の伸びを要介護度別に改めてよいか</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
+          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.110（点7）</t>
+          <t>確認事項No.146（点6）</t>
         </is>
       </c>
     </row>
@@ -9771,17 +9789,17 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実績のご提供</t>
+          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>6事業別の事業費を受領できないものとして、認知症総合支援事業の量の見込みは立てず、3町の取組の回数のみを掲げる</t>
+          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.150（点7）</t>
+          <t>確認事項No.151（点6）</t>
         </is>
       </c>
     </row>
@@ -9796,17 +9814,17 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
+          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>省令上の類型を計画に掲げないまま概算する</t>
+          <t>財政調整交付金の算定に給付適正化主要3事業の取組状況を勘案しないものとして算定する（調整交付金7.3755％のまま。安全側）</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.98（点6）</t>
+          <t>確認事項No.93（点6）</t>
         </is>
       </c>
     </row>
@@ -9821,17 +9839,17 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
+          <t>構成町の一般会計繰入金の町別按分の方法</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）で概算する</t>
+          <t>町別按分は当方の案（第1次概算）のまま示す</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.100（点6）</t>
+          <t>確認事項No.82（点5）</t>
         </is>
       </c>
     </row>
@@ -9846,17 +9864,17 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
+          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第2節の表は見える化の自然体推計値のまま置き、P3による値を別掲する</t>
+          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.101（点6）</t>
+          <t>確認事項No.123（点5）</t>
         </is>
       </c>
     </row>
@@ -9871,17 +9889,17 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
+          <t>見える化システムの推計方式は基本推計でよいか</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節補正も行わないまま概算する</t>
+          <t>基本推計に近いP3で概算する</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.103（点6）</t>
+          <t>確認事項No.126（点5）</t>
         </is>
       </c>
     </row>
@@ -9896,17 +9914,17 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長するか</t>
+          <t>認知症基本法第13条の市町村認知症施策推進計画をどう扱うか</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長しないまま概算する</t>
+          <t>案B（3町がそれぞれ市町村計画を策定する）のまま素案に反映する</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.107（点6）</t>
+          <t>確認事項No.130（点5）</t>
         </is>
       </c>
     </row>
@@ -9921,17 +9939,17 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>区域を越えた施設利用の扱い</t>
+          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
+          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.141（点6）</t>
+          <t>確認事項No.132（点5）</t>
         </is>
       </c>
     </row>
@@ -9946,17 +9964,17 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを要介護度別に改めてよいか</t>
+          <t>第1次概算を既定値のまま出してよいか</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
+          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.146（点6）</t>
+          <t>確認事項No.142（点5）</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9989,17 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
+          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
+          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.151（点6）</t>
+          <t>確認事項No.145（点5）</t>
         </is>
       </c>
     </row>
@@ -9996,17 +10014,17 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
+          <t>見える化システムの伸びの選択肢をどれとするか</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定に給付適正化主要3事業の取組状況を勘案しないものとして算定する（調整交付金7.3755％のまま。安全側）</t>
+          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.93（点6）</t>
+          <t>確認事項No.147（点5）</t>
         </is>
       </c>
     </row>
@@ -10021,17 +10039,17 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>構成町の一般会計繰入金の町別按分の方法</t>
+          <t>東川町の施設整備・サービス提供方針</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>町別按分は当方の案（第1次概算）のまま示す</t>
+          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.82（点5）</t>
+          <t>確認事項No.84（点5）</t>
         </is>
       </c>
     </row>
@@ -10046,17 +10064,17 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
+          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
+          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.123（点5）</t>
+          <t>確認事項No.104（点5）</t>
         </is>
       </c>
     </row>
@@ -10071,17 +10089,17 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計方式は基本推計でよいか</t>
+          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>基本推計に近いP3で概算する</t>
+          <t>単価を令和7年度で固定する（安全側）。実績の趨勢を置いた場合の差は据え置きの一覧及び計画素案 第6章第6節2に示す</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.126（点5）</t>
+          <t>確認事項No.109（点5）</t>
         </is>
       </c>
     </row>
@@ -10096,17 +10114,17 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法第13条の市町村認知症施策推進計画をどう扱うか</t>
+          <t>令和22年度までの中長期推計をどこまで算定するか</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>案B（3町がそれぞれ市町村計画を策定する）のまま素案に反映する</t>
+          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.130（点5）</t>
+          <t>確認事項No.114（点5）</t>
         </is>
       </c>
     </row>
@@ -10121,17 +10139,17 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
+          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
+          <t>供給の制約（人材）を見込量に反映しない（需要のみで算定する）</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.132（点5）</t>
+          <t>確認事項No.116（点5）</t>
         </is>
       </c>
     </row>
@@ -10146,17 +10164,17 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第1次概算を既定値のまま出してよいか</t>
+          <t>町別の人口の将来推計を計画本文に掲げるか</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
+          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.142（点5）</t>
+          <t>確認事項No.152（点5）</t>
         </is>
       </c>
     </row>
@@ -10171,17 +10189,17 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
+          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
+          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.145（点5）</t>
+          <t>確認事項No.153（点5）</t>
         </is>
       </c>
     </row>
@@ -10196,17 +10214,17 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの伸びの選択肢をどれとするか</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>第9期の自己評価と北海道への報告の実績を確認できないものとして、第10期の進行管理に自己評価の仕組みを置く</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.147（点5）</t>
+          <t>確認事項No.7（点4）</t>
         </is>
       </c>
     </row>
@@ -10221,17 +10239,17 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>東川町の施設整備・サービス提供方針</t>
+          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残す</t>
+          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.84（点5）</t>
+          <t>確認事項No.86（点4）</t>
         </is>
       </c>
     </row>
@@ -10246,17 +10264,17 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
+          <t>給付適正化計画の位置づけ（案Bの採用）と毎年度の目標の記載場所</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
+          <t>給付適正化計画の位置づけは案B（第9期と同じく施策として置き、施策名のかっこ書きで第7期給付適正化計画であることを示す）のままとする（令和8年9月10日 了承済み）</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.104（点5）</t>
+          <t>確認事項No.94（点4）</t>
         </is>
       </c>
     </row>
@@ -10271,17 +10289,17 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
+          <t>令和8年度の実績見込み値を編集するか</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。実績の趨勢（年率1.75％）を置いた場合の差（月額＋185円から＋374円）は据え置きの一覧に示す</t>
+          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.109（点5）</t>
+          <t>確認事項No.128（点4）</t>
         </is>
       </c>
     </row>
@@ -10296,17 +10314,17 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>令和22年度までの中長期推計をどこまで算定するか</t>
+          <t>見える化システムの利用率等の伸びの選択</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
+          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.114（点5）</t>
+          <t>確認事項No.129（点4）</t>
         </is>
       </c>
     </row>
@@ -10321,17 +10339,17 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
+          <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>供給の制約（人材）を見込量に反映しない（需要のみで算定する）</t>
+          <t>第9期条例の16段階・乗率（公費軽減前）を据え置いて算定し、政令の公布後に再算定する</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.116（点5）</t>
+          <t>確認事項No.33（点4）</t>
         </is>
       </c>
     </row>
@@ -10346,17 +10364,17 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>町別の人口の将来推計を計画本文に掲げるか</t>
+          <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
+          <t>中間報告・施策体系新旧対照表・骨子案は提出した内容のままとする</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.152（点5）</t>
+          <t>確認事項No.39（点3）</t>
         </is>
       </c>
     </row>
@@ -10371,17 +10389,17 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
+          <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
+          <t>同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.153（点5）</t>
+          <t>確認事項No.40（点3）</t>
         </is>
       </c>
     </row>
@@ -10396,17 +10414,17 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>認定に要する日数の扱い</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績を確認できないものとして、第10期の進行管理に自己評価の仕組みを置く</t>
+          <t>令和8年8月28日受領の集計帳票による</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.7（点4）</t>
+          <t>確認事項No.43（点3）</t>
         </is>
       </c>
     </row>
@@ -10421,17 +10439,17 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
+          <t>代表KPI H15の分母の定義</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
+          <t>代表KPI H15の分母は標準給付費見込額とする（受託者案）</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.86（点4）</t>
+          <t>確認事項No.45（点3）</t>
         </is>
       </c>
     </row>
@@ -10446,17 +10464,17 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけ（案Bの採用）と毎年度の目標の記載場所</t>
+          <t>計画値を0としたサービスに実績がある2件</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけは案B（第9期と同じく施策として置き、施策名のかっこ書きで第7期給付適正化計画であることを示す）のままとする（令和8年9月10日 了承済み）</t>
+          <t>第10期は計画値を0とせず、算定値を置く（対計画比が算出され評価の対象となるようにする）</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.94（点4）</t>
+          <t>確認事項No.57（点3）</t>
         </is>
       </c>
     </row>
@@ -10471,17 +10489,17 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の実績見込み値を編集するか</t>
+          <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
+          <t>定期巡回・随時対応型訪問介護看護は自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.128（点4）</t>
+          <t>確認事項No.58（点3）</t>
         </is>
       </c>
     </row>
@@ -10496,17 +10514,17 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの利用率等の伸びの選択</t>
+          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.129（点4）</t>
+          <t>確認事項No.63（点3）</t>
         </is>
       </c>
     </row>
@@ -10521,17 +10539,17 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階）</t>
+          <t>広域連合において行うべき事業の優先順位</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>第9期条例の16段階・乗率（公費軽減前）を据え置いて算定し、政令の公布後に再算定する</t>
+          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.33（点4）</t>
+          <t>確認事項No.65（点3）</t>
         </is>
       </c>
     </row>
@@ -10546,17 +10564,17 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
+          <t>サービスガイドに掲載する事業所の範囲</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>中間報告・施策体系新旧対照表・骨子案は提出した内容のままとする</t>
+          <t>サービスガイドに掲載する事業所の範囲は北海道の指定事業所一覧（最新のもの）による</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.39（点3）</t>
+          <t>確認事項No.66（点3）</t>
         </is>
       </c>
     </row>
@@ -10571,17 +10589,17 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の扱い</t>
+          <t>算定方法の国の様式との整合（点検結果）</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
+          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.40（点3）</t>
+          <t>確認事項No.67（点3）</t>
         </is>
       </c>
     </row>
@@ -10596,17 +10614,17 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>認定に要する日数の扱い</t>
+          <t>見える化システムの自然体推計の再出力のお願い</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の集計帳票による</t>
+          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.43（点3）</t>
+          <t>確認事項No.68（点3）</t>
         </is>
       </c>
     </row>
@@ -10621,17 +10639,17 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H15の分母の定義</t>
+          <t>交付金の全国順位の計画本文への掲載</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H15の分母は標準給付費見込額とする（受託者案）</t>
+          <t>交付金の全国順位は計画本文に掲載せず、策定委員会資料にとどめる（確認事項No.71のとおり）</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.45（点3）</t>
+          <t>確認事項No.70（点3）</t>
         </is>
       </c>
     </row>
@@ -10646,17 +10664,17 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>計画値を0としたサービスに実績がある2件</t>
+          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>第10期は計画値を0とせず、算定値を置く（対計画比が算出され評価の対象となるようにする）</t>
+          <t>ケアプラン点検実施要領（案）は協議資料にとどめ素案に入れない</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.57（点3）</t>
+          <t>確認事項No.73（点3）</t>
         </is>
       </c>
     </row>
@@ -10671,17 +10689,17 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
+          <t>代表KPIと改善事項の再整理案</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護は自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+          <t>代表KPIと改善事項は当方の再整理案のままとする</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.58（点3）</t>
+          <t>確認事項No.75（点3）</t>
         </is>
       </c>
     </row>
@@ -10696,17 +10714,17 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
+          <t>介護リームスから抽出できる項目</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
+          <t>介護リームスから抽出できないものとして、代表KPI H03は未算定のままとする</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.63（点3）</t>
+          <t>確認事項No.76（点3）</t>
         </is>
       </c>
     </row>
@@ -10721,17 +10739,17 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位</t>
+          <t>北海道の評価指標⑥の団体別の公表値</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
+          <t>北海道の評価指標⑥の団体別の公表値を引用できないものとして、当該指標は計画本文に掲げない</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.65（点3）</t>
+          <t>確認事項No.77（点3）</t>
         </is>
       </c>
     </row>
@@ -10746,17 +10764,17 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>サービスガイドに掲載する事業所の範囲</t>
+          <t>グループホームびえいの郷の定員減の時期</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>サービスガイドに掲載する事業所の範囲は北海道の指定事業所一覧（最新のもの）による</t>
+          <t>北海道の名簿の定員のまま概算する</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.66（点3）</t>
+          <t>確認事項No.78（点3）</t>
         </is>
       </c>
     </row>
@@ -10771,17 +10789,17 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>算定方法の国の様式との整合（点検結果）</t>
+          <t>第5章の施策数の見直しの範囲</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
+          <t>第9期の19施策の体系を維持する（施策数を見直さない）</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.67（点3）</t>
+          <t>確認事項No.79（点3）</t>
         </is>
       </c>
     </row>
@@ -10796,17 +10814,17 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの自然体推計の再出力のお願い</t>
+          <t>代表KPI H16のデータ源（国保連の給付実績の明細情報）</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
+          <t>国保連の給付実績の明細を受領できないものとして、代表KPI H16は地域密着型サービスに限った確認件数を代理指標とする</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.68（点3）</t>
+          <t>確認事項No.81（点3）</t>
         </is>
       </c>
     </row>
@@ -10821,17 +10839,17 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>交付金の全国順位の計画本文への掲載</t>
+          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>交付金の全国順位は計画本文に掲載せず、策定委員会資料にとどめる（確認事項No.71のとおり）</t>
+          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.70（点3）</t>
+          <t>確認事項No.95（点3）</t>
         </is>
       </c>
     </row>
@@ -10846,17 +10864,17 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
+          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）は協議資料にとどめ素案に入れない</t>
+          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.73（点3）</t>
+          <t>確認事項No.96（点3）</t>
         </is>
       </c>
     </row>
@@ -10871,17 +10889,17 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>代表KPIと改善事項の再整理案</t>
+          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>代表KPIと改善事項は当方の再整理案のままとする</t>
+          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.75（点3）</t>
+          <t>確認事項No.102（点3）</t>
         </is>
       </c>
     </row>
@@ -10896,17 +10914,17 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>介護リームスから抽出できる項目</t>
+          <t>地域ケア会議関係資料の取扱いの確認</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>介護リームスから抽出できないものとして、代表KPI H03は未算定のままとする</t>
+          <t>転載を禁ずる旨の記載がある2件は成果品に用いず、原典（厚労省の市町村マニュアル及び別冊事例集）のみを引く</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.76（点3）</t>
+          <t>確認事項No.122（点3）</t>
         </is>
       </c>
     </row>
@@ -10921,17 +10939,17 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥の団体別の公表値</t>
+          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥の団体別の公表値を引用できないものとして、当該指標は計画本文に掲げない</t>
+          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.77（点3）</t>
+          <t>確認事項No.124（点3）</t>
         </is>
       </c>
     </row>
@@ -10946,17 +10964,17 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>グループホームびえいの郷の定員減の時期</t>
+          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>北海道の名簿の定員のまま概算する</t>
+          <t>在宅生活改善調査の結果は「在宅で困難を抱える方の状況」として引き、在宅の認定者全体の割合としては引かない</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.78（点3）</t>
+          <t>確認事項No.140（点3）</t>
         </is>
       </c>
     </row>
@@ -10971,17 +10989,17 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第5章の施策数の見直しの範囲</t>
+          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策の体系を維持する（施策数を見直さない）</t>
+          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.79（点3）</t>
+          <t>確認事項No.149（点3）</t>
         </is>
       </c>
     </row>
@@ -10996,17 +11014,17 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H16のデータ源（国保連の給付実績の明細情報）</t>
+          <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>国保連の給付実績の明細を受領できないものとして、代表KPI H16は地域密着型サービスに限った確認件数を代理指標とする</t>
+          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.81（点3）</t>
+          <t>確認事項No.30（点3）</t>
         </is>
       </c>
     </row>
@@ -11021,17 +11039,17 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
+          <t>第9段階の乗率の経緯</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
+          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.95（点3）</t>
+          <t>確認事項No.34（点3）</t>
         </is>
       </c>
     </row>
@@ -11046,17 +11064,17 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+          <t>上川管内の保険者の所得段階数と乗率</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
+          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.96（点3）</t>
+          <t>確認事項No.35（点3）</t>
         </is>
       </c>
     </row>
@@ -11071,17 +11089,17 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
+          <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
+          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.102（点3）</t>
+          <t>確認事項No.36（点3）</t>
         </is>
       </c>
     </row>
@@ -11096,17 +11114,17 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議関係資料の取扱いの確認</t>
+          <t>令和9年4月に新設される区分を見込量に立てるか</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>転載を禁ずる旨の記載がある2件は成果品に用いず、原典（厚労省の市町村マニュアル及び別冊事例集）のみを引く</t>
+          <t>令和9年4月新設の3区分を0として立てる</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.122（点3）</t>
+          <t>確認事項No.115（点3）</t>
         </is>
       </c>
     </row>
@@ -11121,17 +11139,17 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
+          <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
+          <t>代表KPI H07・H08・H12・H16は代理指標への振替案のとおりとする</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.124（点3）</t>
+          <t>確認事項No.4（点2）</t>
         </is>
       </c>
     </row>
@@ -11146,17 +11164,17 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
+          <t>第9期の施策・事業実績</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果は「在宅で困難を抱える方の状況」として引き、在宅の認定者全体の割合としては引かない</t>
+          <t>第9期の施策・事業実績を受領できないものとして、公表資料（交付金の評価結果・総合事業の実施状況に関する調査・年報）により評価する</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.140（点3）</t>
+          <t>確認事項No.5（点2）</t>
         </is>
       </c>
     </row>
@@ -11171,17 +11189,17 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
+          <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
+          <t>3調査の点検事項は当方の判定のままとする</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.149（点3）</t>
+          <t>確認事項No.8（点2）</t>
         </is>
       </c>
     </row>
@@ -11196,17 +11214,17 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けた要介護度の変化</t>
+          <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
+          <t>会議日程及びパブリックコメントの期間は仕様書５の工程による</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.30（点3）</t>
+          <t>確認事項No.19（点2）</t>
         </is>
       </c>
     </row>
@@ -11221,17 +11239,17 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率の経緯</t>
+          <t>キックオフ会議資料への工程表の反映</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
+          <t>現行の工程表のまま進める</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.34（点3）</t>
+          <t>確認事項No.42（点2）</t>
         </is>
       </c>
     </row>
@@ -11246,17 +11264,17 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
+          <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
+          <t>告示を確認できないものとして、特別地域加算の判定を計画素案に書かず［要確認］のまま残す</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.35（点3）</t>
+          <t>確認事項No.1（点2）</t>
         </is>
       </c>
     </row>
@@ -11271,17 +11289,17 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績と収納率</t>
+          <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
+          <t>類似保険者との比較は公表されている同規模保険者40団体による</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.36（点3）</t>
+          <t>確認事項No.3（点2）</t>
         </is>
       </c>
     </row>
@@ -11296,17 +11314,17 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+          <t>交付金の評価調書</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月新設の3区分を0として立てる</t>
+          <t>評価調書を受領できないものとして、得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できない旨を注記する</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.115（点3）</t>
+          <t>確認事項No.6（点2）</t>
         </is>
       </c>
     </row>
@@ -11321,17 +11339,17 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16の代理指標</t>
+          <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16は代理指標への振替案のとおりとする</t>
+          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.4（点2）</t>
+          <t>確認事項No.9（点2）</t>
         </is>
       </c>
     </row>
@@ -11346,17 +11364,17 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績</t>
+          <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績を受領できないものとして、公表資料（交付金の評価結果・総合事業の実施状況に関する調査・年報）により評価する</t>
+          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.5（点2）</t>
+          <t>確認事項No.10（点2）</t>
         </is>
       </c>
     </row>
@@ -11371,17 +11389,17 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項の取扱い</t>
+          <t>町別の人口・世帯データ</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項は当方の判定のままとする</t>
+          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.8（点2）</t>
+          <t>確認事項No.11（点2）</t>
         </is>
       </c>
     </row>
@@ -11396,17 +11414,17 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>会議日程とパブリックコメントの期間</t>
+          <t>日常生活圏域別のデータ</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>会議日程及びパブリックコメントの期間は仕様書５の工程による</t>
+          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.19（点2）</t>
+          <t>確認事項No.12（点2）</t>
         </is>
       </c>
     </row>
@@ -11421,17 +11439,17 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料への工程表の反映</t>
+          <t>骨子案の内容の確認</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>現行の工程表のまま進める</t>
+          <t>骨子案は提出した内容のままとする</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.42（点2）</t>
+          <t>確認事項No.18（点2）</t>
         </is>
       </c>
     </row>
@@ -11446,17 +11464,17 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>特別地域加算の対象地域告示</t>
+          <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>告示を確認できないものとして、特別地域加算の判定を計画素案に書かず［要確認］のまま残す</t>
+          <t>北海道の評価指標の読替えは当方の案のままとする</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.1（点2）</t>
+          <t>確認事項No.22（点2）</t>
         </is>
       </c>
     </row>
@@ -11471,17 +11489,17 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較分析の対象</t>
+          <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較は公表されている同規模保険者40団体による</t>
+          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.3（点2）</t>
+          <t>確認事項No.27（点2）</t>
         </is>
       </c>
     </row>
@@ -11496,17 +11514,17 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価調書</t>
+          <t>調査対象者の範囲の確認</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>評価調書を受領できないものとして、得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できない旨を注記する</t>
+          <t>現に収録している調査対象者の範囲による</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.6（点2）</t>
+          <t>確認事項No.28（点2）</t>
         </is>
       </c>
     </row>
@@ -11521,17 +11539,17 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>調査の対象者範囲と回収率</t>
+          <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
+          <t>公表されている全国集計の値による</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.9（点2）</t>
+          <t>確認事項No.38（点2）</t>
         </is>
       </c>
     </row>
@@ -11546,17 +11564,17 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>介護人材実態調査の採用者数・退職者数</t>
+          <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
+          <t>令和8年9月25日の再提供により決着済み。再提供を受けたファイルの値（3町合計と円単位一致）による</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.10（点2）</t>
+          <t>確認事項No.46（点2）</t>
         </is>
       </c>
     </row>
@@ -11571,17 +11589,17 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>町別の人口・世帯データ</t>
+          <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
+          <t>総括表（保険者単位）を用い、計画作成支援ツールの実績値シートは比較のためにのみ用いる</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.11（点2）</t>
+          <t>確認事項No.47（点2）</t>
         </is>
       </c>
     </row>
@@ -11596,17 +11614,17 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域別のデータ</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
+          <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値による</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.12（点2）</t>
+          <t>確認事項No.48（点2）</t>
         </is>
       </c>
     </row>
@@ -11621,17 +11639,17 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>骨子案の内容の確認</t>
+          <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>骨子案は提出した内容のままとする</t>
+          <t>受領済みの年報・月報の値による</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.18（点2）</t>
+          <t>確認事項No.50（点2）</t>
         </is>
       </c>
     </row>
@@ -11646,17 +11664,17 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標の読替えの考え方</t>
+          <t>月報の値の接続のずれ（ご報告）</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標の読替えは当方の案のままとする</t>
+          <t>月報の値の接続のずれは記録として残し、計画本文には用いない</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.22（点2）</t>
+          <t>確認事項No.51（点2）</t>
         </is>
       </c>
     </row>
@@ -11671,17 +11689,17 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>令和4年度 健康とくらしの調査の集計表</t>
+          <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
+          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.27（点2）</t>
+          <t>確認事項No.52（点2）</t>
         </is>
       </c>
     </row>
@@ -11696,17 +11714,17 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>調査対象者の範囲の確認</t>
+          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>現に収録している調査対象者の範囲による</t>
+          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合は1億円あたり月額約▲310円となることを併記する</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.28（点2）</t>
+          <t>確認事項No.53（点2）</t>
         </is>
       </c>
     </row>
@@ -11721,17 +11739,17 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の令和6年・令和7年調査の結果</t>
+          <t>議事録の文書プロパティに個人名が再度入る</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>公表されている全国集計の値による</t>
+          <t>議事録は作成者名を落として再出力する（当方で対応する）</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.38（点2）</t>
+          <t>確認事項No.54（点2）</t>
         </is>
       </c>
     </row>
@@ -11746,17 +11764,17 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の給付費の集計が一致しない</t>
+          <t>議事録の表記に関するご提案3件</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月25日の再提供により決着済み。再提供を受けたファイルの値（3町合計と円単位一致）による</t>
+          <t>議事録の表記はご提案3件のとおり改める</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.46（点2）</t>
+          <t>確認事項No.55（点2）</t>
         </is>
       </c>
     </row>
@@ -11771,17 +11789,17 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの実績値シートの確認</t>
+          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>総括表（保険者単位）を用い、計画作成支援ツールの実績値シートは比較のためにのみ用いる</t>
+          <t>他団体の集計帳票6件は成果品に用いない</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.47（点2）</t>
+          <t>確認事項No.56（点2）</t>
         </is>
       </c>
     </row>
@@ -11796,17 +11814,17 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
+          <t>調整交付金の算定基礎の確認</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値による</t>
+          <t>現行の扱い（第9期の算定を再現し公表値6,428円と一致する扱い）による</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.48（点2）</t>
+          <t>確認事項No.59（点2）</t>
         </is>
       </c>
     </row>
@@ -11821,17 +11839,17 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>年報・月報の受領に伴う確認</t>
+          <t>交付金の評価項目と19施策の割当て</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>受領済みの年報・月報の値による</t>
+          <t>交付金の評価項目と19施策の割当ては当方の案のままとする</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.50（点2）</t>
+          <t>確認事項No.61（点2）</t>
         </is>
       </c>
     </row>
@@ -11846,17 +11864,17 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれ（ご報告）</t>
+          <t>職員個票のリストによる重複確認の可否</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれは記録として残し、計画本文には用いない</t>
+          <t>職員個票を突き合わせず、事業所への照会により重複を判別する</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.51（点2）</t>
+          <t>確認事項No.80（点2）</t>
         </is>
       </c>
     </row>
@@ -11871,17 +11889,17 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領に伴う確認</t>
+          <t>構成町との意見交換会の実施方法と町別データシート</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
+          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで進める</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.52（点2）</t>
+          <t>確認事項No.83（点2）</t>
         </is>
       </c>
     </row>
@@ -11896,17 +11914,17 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
+          <t>町別データシートの内容と配付</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合は1億円あたり月額約▲310円となることを併記する</t>
+          <t>町別データシートは現行の内容のまま配付する</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.53（点2）</t>
+          <t>確認事項No.85（点2）</t>
         </is>
       </c>
     </row>
@@ -11921,17 +11939,17 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>議事録の文書プロパティに個人名が再度入る</t>
+          <t>成果品の統合の方針</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>議事録は作成者名を落として再出力する（当方で対応する）</t>
+          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す（現行）</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.54（点2）</t>
+          <t>確認事項No.117（点2）</t>
         </is>
       </c>
     </row>
@@ -11946,17 +11964,17 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記に関するご提案3件</t>
+          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記はご提案3件のとおり改める</t>
+          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.55（点2）</t>
+          <t>確認事項No.138（点2）</t>
         </is>
       </c>
     </row>
@@ -11971,17 +11989,17 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
+          <t>健康とくらしの調査の個票の再提供の要否</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>他団体の集計帳票6件は成果品に用いない</t>
+          <t>健康とくらしの調査の個票の再提供を依頼しない（成果品は収録済みで内容が確定しており、現時点で不足がない）</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.56（点2）</t>
+          <t>確認事項No.139（点2）</t>
         </is>
       </c>
     </row>
@@ -11996,17 +12014,17 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>調整交付金の算定基礎の確認</t>
+          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>現行の扱い（第9期の算定を再現し公表値6,428円と一致する扱い）による</t>
+          <t>受領済みの画面の写しの範囲で概算し、確認できていない項目はその旨を明記する</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.59（点2）</t>
+          <t>確認事項No.148（点2）</t>
         </is>
       </c>
     </row>
@@ -12021,17 +12039,17 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当て</t>
+          <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当ては当方の案のままとする</t>
+          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.61（点2）</t>
+          <t>確認事項No.60（点2）</t>
         </is>
       </c>
     </row>
@@ -12046,17 +12064,17 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>職員個票のリストによる重複確認の可否</t>
+          <t>区域内に事業所がないサービスの住民向けの記載</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>職員個票を突き合わせず、事業所への照会により重複を判別する</t>
+          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.80（点2）</t>
+          <t>確認事項No.64（点2）</t>
         </is>
       </c>
     </row>
@@ -12071,17 +12089,17 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>構成町との意見交換会の実施方法と町別データシート</t>
+          <t>成果指向型配分枠（令和8年度新設）への対応</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで進める</t>
+          <t>成果指向型配分枠への対応状況を確認できないものとして、第10期の施策には位置づけず、確認でき次第加える</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.83（点2）</t>
+          <t>確認事項No.69（点2）</t>
         </is>
       </c>
     </row>
@@ -12096,17 +12114,17 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>町別データシートの内容と配付</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>町別データシートは現行の内容のまま配付する</t>
+          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.85（点2）</t>
+          <t>確認事項No.89（点2）</t>
         </is>
       </c>
     </row>
@@ -12121,17 +12139,17 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>成果品の統合の方針</t>
+          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す（現行）</t>
+          <t>第9期計画の本文及び前回調査の原集計表を受領できないものとして、前回調査との比較は割合のみとし、指標別の分母を確認できない旨を注記する</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.117（点2）</t>
+          <t>確認事項No.90（点2）</t>
         </is>
       </c>
     </row>
@@ -12146,17 +12164,17 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
+          <t>介護給付費通知及び給付実績の活用による確認等</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ</t>
+          <t>介護給付費通知の実施状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.138（点2）</t>
+          <t>確認事項No.91（点2）</t>
         </is>
       </c>
     </row>
@@ -12171,17 +12189,17 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供の要否</t>
+          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供を依頼しない（成果品は収録済みで内容が確定しており、現時点で不足がない）</t>
+          <t>認定調査の委託の状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.139（点2）</t>
+          <t>確認事項No.92（点2）</t>
         </is>
       </c>
     </row>
@@ -12196,17 +12214,17 @@
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
+          <t>令和9年4月1日から義務となる2件への対応</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>受領済みの画面の写しの範囲で概算し、確認できていない項目はその旨を明記する</t>
+          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.148（点2）</t>
+          <t>確認事項No.97（点2）</t>
         </is>
       </c>
     </row>
@@ -12221,17 +12239,17 @@
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提（受託者案）</t>
+          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
+          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.60（点2）</t>
+          <t>確認事項No.99（点2）</t>
         </is>
       </c>
     </row>
@@ -12246,17 +12264,17 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスの住民向けの記載</t>
+          <t>補正しても外れるサービス6件の理由</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
+          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.64（点2）</t>
+          <t>確認事項No.108（点2）</t>
         </is>
       </c>
     </row>
@@ -12271,17 +12289,17 @@
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠（令和8年度新設）への対応</t>
+          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠への対応状況を確認できないものとして、第10期の施策には位置づけず、確認でき次第加える</t>
+          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.69（点2）</t>
+          <t>確認事項No.111（点2）</t>
         </is>
       </c>
     </row>
@@ -12296,17 +12314,17 @@
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
+          <t>施策2-5の代表KPIはO2（提起された地域課題のうち翌年度の事業・予算に反映されたものの割合）とする（当方案）</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.89（点2）</t>
+          <t>確認事項No.118（点2）</t>
         </is>
       </c>
     </row>
@@ -12321,17 +12339,17 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
+          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文及び前回調査の原集計表を受領できないものとして、前回調査との比較は割合のみとし、指標別の分母を確認できない旨を注記する</t>
+          <t>地域ケア会議の記録様式は協議資料にとどめ、令和9年度に整える</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.90（点2）</t>
+          <t>確認事項No.119（点2）</t>
         </is>
       </c>
     </row>
@@ -12346,17 +12364,17 @@
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知及び給付実績の活用による確認等</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知の実施状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.91（点2）</t>
+          <t>確認事項No.120（点2）</t>
         </is>
       </c>
     </row>
@@ -12371,17 +12389,17 @@
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
+          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>認定調査の委託の状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
+          <t>令和7年度の実施報告書により把握できる範囲で記述する</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.92（点2）</t>
+          <t>確認事項No.121（点2）</t>
         </is>
       </c>
     </row>
@@ -12396,17 +12414,17 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月1日から義務となる2件への対応</t>
+          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
+          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.97（点2）</t>
+          <t>確認事項No.125（点2）</t>
         </is>
       </c>
     </row>
@@ -12421,17 +12439,17 @@
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
+          <t>見える化システムの総人口の設定を案Cに改めるか</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
+          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.99（点2）</t>
+          <t>確認事項No.127（点2）</t>
         </is>
       </c>
     </row>
@@ -12446,17 +12464,17 @@
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れるサービス6件の理由</t>
+          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
+          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.108（点2）</t>
+          <t>確認事項No.133（点2）</t>
         </is>
       </c>
     </row>
@@ -12471,17 +12489,17 @@
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
+          <t>画面の令和7年度と年報の月平均の食い違い</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
+          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.111（点2）</t>
+          <t>確認事項No.136（点2）</t>
         </is>
       </c>
     </row>
@@ -12496,17 +12514,17 @@
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
+          <t>計画素案の未確定箇所の表示の統一</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIはO2（提起された地域課題のうち翌年度の事業・予算に反映されたものの割合）とする（当方案）</t>
+          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとする</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.118（点2）</t>
+          <t>確認事項No.143（点2）</t>
         </is>
       </c>
     </row>
@@ -12521,17 +12539,17 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
+          <t>計画素案 第2章第1節に町別の図を加えるか</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の記録様式は協議資料にとどめ、令和9年度に整える</t>
+          <t>計画素案 第2章第1節に町別の図を加えない。加筆分は協議用の資料にとどめる</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.119（点2）</t>
+          <t>確認事項No.154（点2）</t>
         </is>
       </c>
     </row>
@@ -12546,17 +12564,17 @@
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
+          <t>中長期推計を令和12・27・32年度まで広げるか</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
+          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.120（点2）</t>
+          <t>確認事項No.157（点2）</t>
         </is>
       </c>
     </row>
@@ -12571,17 +12589,17 @@
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
+          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の実施報告書により把握できる範囲で記述する</t>
+          <t>設問ごとの有効回答を分母とし、町別の値は掲げない（令和8年9月25日に是正済み）</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.121（点2）</t>
+          <t>確認事項No.158（点2）</t>
         </is>
       </c>
     </row>
@@ -12596,17 +12614,17 @@
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
+          <t>東川町の通いの場の整備と担い手の確保</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
+          <t>現状のまま（東川町の整備を見込まない）第10期の目標値を置く</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.125（点2）</t>
+          <t>確認事項No.159（点2）</t>
         </is>
       </c>
     </row>
@@ -12621,17 +12639,17 @@
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総人口の設定を案Cに改めるか</t>
+          <t>東川町の認知症サポーター養成講座の実施状況</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
+          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.127（点2）</t>
+          <t>確認事項No.160（点2）</t>
         </is>
       </c>
     </row>
@@ -12646,17 +12664,17 @@
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+          <t>東川町のチームオレンジ事業の位置づけ</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
+          <t>東川町の取組として記述し3町展開は記述しない</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.133（点2）</t>
+          <t>確認事項No.161（点2）</t>
         </is>
       </c>
     </row>
@@ -12671,17 +12689,17 @@
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度と年報の月平均の食い違い</t>
+          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
+          <t>令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.136（点2）</t>
+          <t>確認事項No.162（点2）</t>
         </is>
       </c>
     </row>
@@ -12696,17 +12714,17 @@
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所の表示の統一</t>
+          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとする</t>
+          <t>美瑛町の取組として記述し3町展開は記述しない</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.143（点2）</t>
+          <t>確認事項No.163（点2）</t>
         </is>
       </c>
     </row>
@@ -12721,17 +12739,17 @@
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えるか</t>
+          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えない。加筆分は協議用の資料にとどめる</t>
+          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.154（点2）</t>
+          <t>確認事項No.164（点2）</t>
         </is>
       </c>
     </row>
@@ -12746,17 +12764,17 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>中長期推計を令和12・27・32年度まで広げるか</t>
+          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
+          <t>現に確認できる取組の範囲で記述する</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.157（点2）</t>
+          <t>確認事項No.165（点2）</t>
         </is>
       </c>
     </row>
@@ -12771,17 +12789,17 @@
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
+          <t>東神楽町の通いの場の維持</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>設問ごとの有効回答を分母とし、町別の値は掲げない（令和8年9月25日に是正済み）</t>
+          <t>令和6年度の水準が続くものとして目標値を置く</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.158（点2）</t>
+          <t>確認事項No.166（点2）</t>
         </is>
       </c>
     </row>
@@ -12796,17 +12814,17 @@
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>東川町の通いの場の整備と担い手の確保</t>
+          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>現状のまま（東川町の整備を見込まない）第10期の目標値を置く</t>
+          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.159（点2）</t>
+          <t>確認事項No.167（点2）</t>
         </is>
       </c>
     </row>
@@ -12821,17 +12839,17 @@
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>東川町の認知症サポーター養成講座の実施状況</t>
+          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
+          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.160（点2）</t>
+          <t>確認事項No.170（点2）</t>
         </is>
       </c>
     </row>
@@ -12846,17 +12864,17 @@
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>東川町のチームオレンジ事業の位置づけ</t>
+          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>東川町の取組として記述し3町展開は記述しない</t>
+          <t>の当方の扱い＝掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.161（点2）</t>
+          <t>確認事項No.172（点2）</t>
         </is>
       </c>
     </row>
@@ -12871,17 +12889,17 @@
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
+          <t>保険料算定の前提</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残す</t>
+          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.162（点2）</t>
+          <t>確認事項No.16（点2）</t>
         </is>
       </c>
     </row>
@@ -12896,17 +12914,17 @@
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
+          <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の取組として記述し3町展開は記述しない</t>
+          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.163（点2）</t>
+          <t>確認事項No.2（点1）</t>
         </is>
       </c>
     </row>
@@ -12921,17 +12939,17 @@
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
+          <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
+          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.164（点2）</t>
+          <t>確認事項No.13（点1）</t>
         </is>
       </c>
     </row>
@@ -12946,17 +12964,17 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
+          <t>人口推計の基礎とする系列</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述する</t>
+          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.165（点2）</t>
+          <t>確認事項No.14（点1）</t>
         </is>
       </c>
     </row>
@@ -12971,17 +12989,17 @@
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の通いの場の維持</t>
+          <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の水準が続くものとして目標値を置く</t>
+          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.166（点2）</t>
+          <t>確認事項No.15（点1）</t>
         </is>
       </c>
     </row>
@@ -12996,17 +13014,17 @@
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
+          <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
+          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.167（点2）</t>
+          <t>確認事項No.17（点1）</t>
         </is>
       </c>
     </row>
@@ -13021,17 +13039,17 @@
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
+          <t>北海道・圏域との調整の場</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
+          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.170（点2）</t>
+          <t>確認事項No.20（点1）</t>
         </is>
       </c>
     </row>
@@ -13046,17 +13064,17 @@
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
+          <t>成果品の仕様</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>の当方の扱い＝掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
+          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.172（点2）</t>
+          <t>確認事項No.21（点1）</t>
         </is>
       </c>
     </row>
@@ -13071,17 +13089,17 @@
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提</t>
+          <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
+          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.16（点2）</t>
+          <t>確認事項No.23（点1）</t>
         </is>
       </c>
     </row>
@@ -13096,17 +13114,17 @@
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
+          <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
+          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.2（点1）</t>
+          <t>確認事項No.26（点1）</t>
         </is>
       </c>
     </row>
@@ -13121,17 +13139,17 @@
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域の判定資料</t>
+          <t>重度化の速度の前提</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
+          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.13（点1）</t>
+          <t>確認事項No.29（点1）</t>
         </is>
       </c>
     </row>
@@ -13146,17 +13164,17 @@
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎とする系列</t>
+          <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
+          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.14（点1）</t>
+          <t>確認事項No.31（点1）</t>
         </is>
       </c>
     </row>
@@ -13171,17 +13189,17 @@
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>認定者数の基準月と月次推移</t>
+          <t>統合した成果品の元の資料を残すか</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
+          <t>統合した成果品の元の資料を残す</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.15（点1）</t>
+          <t>確認事項No.144（点1）</t>
         </is>
       </c>
     </row>
@@ -13196,17 +13214,17 @@
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>3町計画への共通指標の掲載</t>
+          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr">
         <is>
-          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
+          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
         </is>
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.17（点1）</t>
+          <t>確認事項No.156（点1）</t>
         </is>
       </c>
     </row>
@@ -13221,17 +13239,17 @@
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場</t>
+          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
+          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.20（点1）</t>
+          <t>確認事項No.169（点1）</t>
         </is>
       </c>
     </row>
@@ -13246,17 +13264,17 @@
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様</t>
+          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
+          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.21（点1）</t>
+          <t>確認事項No.171（点1）</t>
         </is>
       </c>
     </row>
@@ -13271,17 +13289,17 @@
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>事業所の定員・稼働率データ</t>
+          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
+          <t>の当方の扱い＝現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.23（点1）</t>
+          <t>確認事項No.173（点1）</t>
         </is>
       </c>
     </row>
@@ -13296,17 +13314,17 @@
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>認知症・医療介護連携の実績データ</t>
+          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr">
         <is>
-          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
+          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.26（点1）</t>
+          <t>確認事項No.74（点1）</t>
         </is>
       </c>
     </row>
@@ -13321,17 +13339,17 @@
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提</t>
+          <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
+          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.29（点1）</t>
+          <t>確認事項No.24（点0）</t>
         </is>
       </c>
     </row>
@@ -13346,240 +13364,40 @@
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の実施予定と推計での扱い</t>
+          <t>代表KPIの目標値の決定</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr">
         <is>
-          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
+          <t>代表KPIの目標値は、令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置く</t>
         </is>
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.31（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="44" customHeight="1">
-      <c r="A152" s="5" t="n">
-        <v>147</v>
-      </c>
-      <c r="B152" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C152" s="6" t="inlineStr">
-        <is>
-          <t>統合した成果品の元の資料を残すか</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr">
-        <is>
-          <t>統合した成果品の元の資料を残す</t>
-        </is>
-      </c>
-      <c r="E152" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.144（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="44" customHeight="1">
-      <c r="A153" s="5" t="n">
-        <v>148</v>
-      </c>
-      <c r="B153" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C153" s="6" t="inlineStr">
-        <is>
-          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
-        </is>
-      </c>
-      <c r="D153" s="6" t="inlineStr">
-        <is>
-          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
-        </is>
-      </c>
-      <c r="E153" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.156（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="44" customHeight="1">
-      <c r="A154" s="5" t="n">
-        <v>149</v>
-      </c>
-      <c r="B154" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C154" s="6" t="inlineStr">
-        <is>
-          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
-        </is>
-      </c>
-      <c r="D154" s="6" t="inlineStr">
-        <is>
-          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
-        </is>
-      </c>
-      <c r="E154" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.169（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="44" customHeight="1">
-      <c r="A155" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="B155" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C155" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
-        </is>
-      </c>
-      <c r="D155" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
-        </is>
-      </c>
-      <c r="E155" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.171（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="44" customHeight="1">
-      <c r="A156" s="5" t="n">
-        <v>151</v>
-      </c>
-      <c r="B156" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C156" s="6" t="inlineStr">
-        <is>
-          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
-        </is>
-      </c>
-      <c r="D156" s="6" t="inlineStr">
-        <is>
-          <t>の当方の扱い＝現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
-        </is>
-      </c>
-      <c r="E156" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.173（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="44" customHeight="1">
-      <c r="A157" s="5" t="n">
-        <v>152</v>
-      </c>
-      <c r="B157" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C157" s="6" t="inlineStr">
-        <is>
-          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
-        </is>
-      </c>
-      <c r="D157" s="6" t="inlineStr">
-        <is>
-          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
-        </is>
-      </c>
-      <c r="E157" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.74（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="44" customHeight="1">
-      <c r="A158" s="5" t="n">
-        <v>153</v>
-      </c>
-      <c r="B158" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C158" s="6" t="inlineStr">
-        <is>
-          <t>24時間対応サービスの確保方策の決定</t>
-        </is>
-      </c>
-      <c r="D158" s="6" t="inlineStr">
-        <is>
-          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
-        </is>
-      </c>
-      <c r="E158" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.24（点0）</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="44" customHeight="1">
-      <c r="A159" s="5" t="n">
-        <v>154</v>
-      </c>
-      <c r="B159" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C159" s="6" t="inlineStr">
-        <is>
-          <t>代表KPIの目標値の決定</t>
-        </is>
-      </c>
-      <c r="D159" s="6" t="inlineStr">
-        <is>
-          <t>代表KPIの目標値は、令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置く</t>
-        </is>
-      </c>
-      <c r="E159" s="6" t="inlineStr">
-        <is>
           <t>確認事項No.25（点0）</t>
         </is>
       </c>
     </row>
-    <row r="160" ht="76" customHeight="1">
-      <c r="A160" s="14" t="inlineStr">
+    <row r="152" ht="76" customHeight="1">
+      <c r="A152" s="14" t="inlineStr">
         <is>
           <t>注1）「据え置き（区分A）」は、資料の受領を待たずに当方の側で確定できるものです。
 注2）「既定値で進める」は、決着しない場合の扱いを置けているため決定を待たずに作業を進められるものです。決定を受けた時点で見直します。
 注3）ここに現れないもの（既定値を置けていない確認事項）は、扱いを決めること自体が翌日の作業になります。02シートを見ます。
-注4）既定値のとおり計画素案へ反映し終えたもの6件（確認事項No.88・No.105・No.106・No.112・No.113・No.131）は、作業としては終わっているため本表から除いています。ご決定はなお待っています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="161"/>
-    <row r="162" ht="20" customHeight="1">
-      <c r="A162" s="3" t="inlineStr">
+注4）既定値のとおり計画素案へ反映し終えたもの14件（確認事項No.88・No.98・No.100・No.101・No.103・No.105・No.106・No.107・No.110・No.112・No.113・No.131・No.137・No.150）は、作業としては終わっているため本表から除いています。ご決定はなお待っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="153"/>
+    <row r="154" ht="20" customHeight="1">
+      <c r="A154" s="3" t="inlineStr">
         <is>
           <t>2　先に扱いを決めるもの（既定値を置けていない）　0件</t>
         </is>
       </c>
     </row>
-    <row r="163" ht="18" customHeight="1">
-      <c r="A163" s="21" t="inlineStr">
+    <row r="155" ht="18" customHeight="1">
+      <c r="A155" s="21" t="inlineStr">
         <is>
           <t>ありません。未決の確認事項の全件に扱いを置けています。</t>
         </is>
@@ -13587,12 +13405,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A154:E154"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A163:E163"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A160:E160"/>
-    <mergeCell ref="A162:E162"/>
+    <mergeCell ref="A152:E152"/>
+    <mergeCell ref="A155:E155"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13667,17 +13485,17 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
+          <t>区域を越えた施設利用の扱い</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費は令和7年度で固定して概算する（月額で＋185〜＋374円に当たる）</t>
+          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.137（点7）</t>
+          <t>確認事項No.141（点6）</t>
         </is>
       </c>
     </row>
@@ -13692,17 +13510,17 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
+          <t>見込量の伸びを要介護度別に改めてよいか</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
+          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.110（点7）</t>
+          <t>確認事項No.146（点6）</t>
         </is>
       </c>
     </row>
@@ -13717,17 +13535,17 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実績のご提供</t>
+          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>6事業別の事業費を受領できないものとして、認知症総合支援事業の量の見込みは立てず、3町の取組の回数のみを掲げる</t>
+          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.150（点7）</t>
+          <t>確認事項No.151（点6）</t>
         </is>
       </c>
     </row>
@@ -13742,17 +13560,17 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
+          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>省令上の類型を計画に掲げないまま概算する</t>
+          <t>財政調整交付金の算定に給付適正化主要3事業の取組状況を勘案しないものとして算定する（調整交付金7.3755％のまま。安全側）</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.98（点6）</t>
+          <t>確認事項No.93（点6）</t>
         </is>
       </c>
     </row>
@@ -13767,17 +13585,17 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
+          <t>構成町の一般会計繰入金の町別按分の方法</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）で概算する</t>
+          <t>町別按分は当方の案（第1次概算）のまま示す</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.100（点6）</t>
+          <t>確認事項No.82（点5）</t>
         </is>
       </c>
     </row>
@@ -13792,17 +13610,17 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
+          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第2節の表は見える化の自然体推計値のまま置き、P3による値を別掲する</t>
+          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.101（点6）</t>
+          <t>確認事項No.123（点5）</t>
         </is>
       </c>
     </row>
@@ -13817,17 +13635,17 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
+          <t>見える化システムの推計方式は基本推計でよいか</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節補正も行わないまま概算する</t>
+          <t>基本推計に近いP3で概算する</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.103（点6）</t>
+          <t>確認事項No.126（点5）</t>
         </is>
       </c>
     </row>
@@ -13842,17 +13660,17 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長するか</t>
+          <t>認知症基本法第13条の市町村認知症施策推進計画をどう扱うか</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長しないまま概算する</t>
+          <t>案B（3町がそれぞれ市町村計画を策定する）のまま素案に反映する</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.107（点6）</t>
+          <t>確認事項No.130（点5）</t>
         </is>
       </c>
     </row>
@@ -14006,7 +13824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -14198,7 +14016,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>7件を拾った（最大374円）／上限超え なし</t>
+          <t>7件を拾った（最大327円）／上限超え なし</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -14348,7 +14166,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>154件（区分A 0・既定値 154）</t>
+          <t>146件（区分A 0・既定値 146）</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -14432,20 +14250,45 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="11" t="inlineStr"/>
-      <c r="B20" s="11" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>台帳に書かれた単価の趨勢の効きが算定と一致すること</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>算定 ＋245〜＋327円（年率1.32％〜1.75％）</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>台帳にあり／古い記述 なし</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="11" t="inlineStr"/>
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>自己点検の結果</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr"/>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>適合15件・不適合0件</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr"/>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>適合16件・不適合0件</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -752,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>666b8ee</t>
+          <t>52c9b69</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>3町合同意見交換会の資料と作業継続可能8件の処理</t>
+          <t>翌日の作業順位8件の処理と単価の趨勢の効きの是正</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>241932b</t>
+          <t>666b8ee</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>既定値の仮置き（未決160件）と据え置き区分Aの更新</t>
+          <t>3町合同意見交換会の資料と作業継続可能8件の処理</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
@@ -1273,20 +1273,38 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>9c17709</t>
+          <t>241932b</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>日次のWBS更新と翌日の作業順位（スキルと日次の表）</t>
+          <t>既定値の仮置き（未決160件）と据え置き区分Aの更新</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr"/>
       <c r="E25" s="6" t="inlineStr"/>
       <c r="F25" s="6" t="inlineStr"/>
     </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="14" t="inlineStr">
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>9c17709</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>日次のWBS更新と翌日の作業順位（スキルと日次の表）</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
@@ -1297,8 +1315,8 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2194,7 +2212,7 @@
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>町別按分は当方の案（第1次概算）のまま示す</t>
+          <t>町別への按分は広域連合の規約によるものであり算定できないため、構成町の一般会計繰入金は3町計の概算のみを示す（按分の方法のご教示を受けた時点で町別までお示しする）</t>
         </is>
       </c>
     </row>
@@ -9673,7 +9691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F155"/>
+  <dimension ref="A1:F131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9701,7 +9719,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　当方の作業だけで進められるもの　146件</t>
+          <t>1　当方の作業だけで進められるもの　122件</t>
         </is>
       </c>
     </row>
@@ -9739,17 +9757,17 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>区域を越えた施設利用の扱い</t>
+          <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
+          <t>第9期条例の16段階・乗率（公費軽減前）を据え置いて算定し、政令の公布後に再算定する</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.141（点6）</t>
+          <t>確認事項No.33（点4）</t>
         </is>
       </c>
     </row>
@@ -9764,17 +9782,17 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを要介護度別に改めてよいか</t>
+          <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
+          <t>中間報告・施策体系新旧対照表・骨子案は提出した内容のままとする</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.146（点6）</t>
+          <t>確認事項No.39（点3）</t>
         </is>
       </c>
     </row>
@@ -9789,17 +9807,17 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
+          <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
+          <t>同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.151（点6）</t>
+          <t>確認事項No.40（点3）</t>
         </is>
       </c>
     </row>
@@ -9814,17 +9832,17 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
+          <t>認定に要する日数の扱い</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定に給付適正化主要3事業の取組状況を勘案しないものとして算定する（調整交付金7.3755％のまま。安全側）</t>
+          <t>令和8年8月28日受領の集計帳票による</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.93（点6）</t>
+          <t>確認事項No.43（点3）</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9857,17 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>構成町の一般会計繰入金の町別按分の方法</t>
+          <t>代表KPI H15の分母の定義</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>町別按分は当方の案（第1次概算）のまま示す</t>
+          <t>代表KPI H15の分母は標準給付費見込額とする（受託者案）</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.82（点5）</t>
+          <t>確認事項No.45（点3）</t>
         </is>
       </c>
     </row>
@@ -9864,17 +9882,17 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
+          <t>計画値を0としたサービスに実績がある2件</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
+          <t>第10期は計画値を0とせず、算定値を置く（対計画比が算出され評価の対象となるようにする）</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.123（点5）</t>
+          <t>確認事項No.57（点3）</t>
         </is>
       </c>
     </row>
@@ -9889,17 +9907,17 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計方式は基本推計でよいか</t>
+          <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>基本推計に近いP3で概算する</t>
+          <t>定期巡回・随時対応型訪問介護看護は自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.126（点5）</t>
+          <t>確認事項No.58（点3）</t>
         </is>
       </c>
     </row>
@@ -9914,17 +9932,17 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法第13条の市町村認知症施策推進計画をどう扱うか</t>
+          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>案B（3町がそれぞれ市町村計画を策定する）のまま素案に反映する</t>
+          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.130（点5）</t>
+          <t>確認事項No.63（点3）</t>
         </is>
       </c>
     </row>
@@ -9939,17 +9957,17 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
+          <t>広域連合において行うべき事業の優先順位</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
+          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.132（点5）</t>
+          <t>確認事項No.65（点3）</t>
         </is>
       </c>
     </row>
@@ -9964,17 +9982,17 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>第1次概算を既定値のまま出してよいか</t>
+          <t>サービスガイドに掲載する事業所の範囲</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
+          <t>サービスガイドに掲載する事業所の範囲は北海道の指定事業所一覧（最新のもの）による</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.142（点5）</t>
+          <t>確認事項No.66（点3）</t>
         </is>
       </c>
     </row>
@@ -9989,17 +10007,17 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
+          <t>算定方法の国の様式との整合（点検結果）</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
+          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.145（点5）</t>
+          <t>確認事項No.67（点3）</t>
         </is>
       </c>
     </row>
@@ -10014,17 +10032,17 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの伸びの選択肢をどれとするか</t>
+          <t>見える化システムの自然体推計の再出力のお願い</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.147（点5）</t>
+          <t>確認事項No.68（点3）</t>
         </is>
       </c>
     </row>
@@ -10039,17 +10057,17 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>東川町の施設整備・サービス提供方針</t>
+          <t>交付金の全国順位の計画本文への掲載</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残す</t>
+          <t>交付金の全国順位は計画本文に掲載せず、策定委員会資料にとどめる（確認事項No.71のとおり）</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.84（点5）</t>
+          <t>確認事項No.70（点3）</t>
         </is>
       </c>
     </row>
@@ -10064,17 +10082,17 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
+          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
+          <t>ケアプラン点検実施要領（案）は協議資料にとどめ素案に入れない</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.104（点5）</t>
+          <t>確認事項No.73（点3）</t>
         </is>
       </c>
     </row>
@@ -10089,17 +10107,17 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
+          <t>代表KPIと改善事項の再整理案</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。実績の趨勢を置いた場合の差は据え置きの一覧及び計画素案 第6章第6節2に示す</t>
+          <t>代表KPIと改善事項は当方の再整理案のままとする</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.109（点5）</t>
+          <t>確認事項No.75（点3）</t>
         </is>
       </c>
     </row>
@@ -10114,17 +10132,17 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>令和22年度までの中長期推計をどこまで算定するか</t>
+          <t>介護リームスから抽出できる項目</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
+          <t>介護リームスから抽出できないものとして、代表KPI H03は未算定のままとする</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.114（点5）</t>
+          <t>確認事項No.76（点3）</t>
         </is>
       </c>
     </row>
@@ -10139,17 +10157,17 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
+          <t>北海道の評価指標⑥の団体別の公表値</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>供給の制約（人材）を見込量に反映しない（需要のみで算定する）</t>
+          <t>北海道の評価指標⑥の団体別の公表値を引用できないものとして、当該指標は計画本文に掲げない</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.116（点5）</t>
+          <t>確認事項No.77（点3）</t>
         </is>
       </c>
     </row>
@@ -10164,17 +10182,17 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>町別の人口の将来推計を計画本文に掲げるか</t>
+          <t>グループホームびえいの郷の定員減の時期</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
+          <t>北海道の名簿の定員のまま概算する</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.152（点5）</t>
+          <t>確認事項No.78（点3）</t>
         </is>
       </c>
     </row>
@@ -10189,17 +10207,17 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
+          <t>第5章の施策数の見直しの範囲</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
+          <t>第9期の19施策の体系を維持する（施策数を見直さない）</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.153（点5）</t>
+          <t>確認事項No.79（点3）</t>
         </is>
       </c>
     </row>
@@ -10214,17 +10232,17 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>代表KPI H16のデータ源（国保連の給付実績の明細情報）</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績を確認できないものとして、第10期の進行管理に自己評価の仕組みを置く</t>
+          <t>国保連の給付実績の明細を受領できないものとして、代表KPI H16は地域密着型サービスに限った確認件数を代理指標とする</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.7（点4）</t>
+          <t>確認事項No.81（点3）</t>
         </is>
       </c>
     </row>
@@ -10239,17 +10257,17 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
+          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
+          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.86（点4）</t>
+          <t>確認事項No.95（点3）</t>
         </is>
       </c>
     </row>
@@ -10264,17 +10282,17 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけ（案Bの採用）と毎年度の目標の記載場所</t>
+          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけは案B（第9期と同じく施策として置き、施策名のかっこ書きで第7期給付適正化計画であることを示す）のままとする（令和8年9月10日 了承済み）</t>
+          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.94（点4）</t>
+          <t>確認事項No.96（点3）</t>
         </is>
       </c>
     </row>
@@ -10289,17 +10307,17 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の実績見込み値を編集するか</t>
+          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
+          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.128（点4）</t>
+          <t>確認事項No.102（点3）</t>
         </is>
       </c>
     </row>
@@ -10314,17 +10332,17 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの利用率等の伸びの選択</t>
+          <t>地域ケア会議関係資料の取扱いの確認</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>転載を禁ずる旨の記載がある2件は成果品に用いず、原典（厚労省の市町村マニュアル及び別冊事例集）のみを引く</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.129（点4）</t>
+          <t>確認事項No.122（点3）</t>
         </is>
       </c>
     </row>
@@ -10339,17 +10357,17 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階）</t>
+          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>第9期条例の16段階・乗率（公費軽減前）を据え置いて算定し、政令の公布後に再算定する</t>
+          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.33（点4）</t>
+          <t>確認事項No.124（点3）</t>
         </is>
       </c>
     </row>
@@ -10364,17 +10382,17 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
+          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>中間報告・施策体系新旧対照表・骨子案は提出した内容のままとする</t>
+          <t>在宅生活改善調査の結果は「在宅で困難を抱える方の状況」として引き、在宅の認定者全体の割合としては引かない</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.39（点3）</t>
+          <t>確認事項No.140（点3）</t>
         </is>
       </c>
     </row>
@@ -10389,17 +10407,17 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の扱い</t>
+          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
+          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.40（点3）</t>
+          <t>確認事項No.149（点3）</t>
         </is>
       </c>
     </row>
@@ -10414,17 +10432,17 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>認定に要する日数の扱い</t>
+          <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の集計帳票による</t>
+          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.43（点3）</t>
+          <t>確認事項No.30（点3）</t>
         </is>
       </c>
     </row>
@@ -10439,17 +10457,17 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H15の分母の定義</t>
+          <t>第9段階の乗率の経緯</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H15の分母は標準給付費見込額とする（受託者案）</t>
+          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.45（点3）</t>
+          <t>確認事項No.34（点3）</t>
         </is>
       </c>
     </row>
@@ -10464,17 +10482,17 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>計画値を0としたサービスに実績がある2件</t>
+          <t>上川管内の保険者の所得段階数と乗率</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>第10期は計画値を0とせず、算定値を置く（対計画比が算出され評価の対象となるようにする）</t>
+          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.57（点3）</t>
+          <t>確認事項No.35（点3）</t>
         </is>
       </c>
     </row>
@@ -10489,17 +10507,17 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
+          <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護は自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.58（点3）</t>
+          <t>確認事項No.36（点3）</t>
         </is>
       </c>
     </row>
@@ -10514,17 +10532,17 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
+          <t>令和9年4月に新設される区分を見込量に立てるか</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
+          <t>令和9年4月新設の3区分を0として立てる</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.63（点3）</t>
+          <t>確認事項No.115（点3）</t>
         </is>
       </c>
     </row>
@@ -10539,17 +10557,17 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位</t>
+          <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
+          <t>代表KPI H07・H08・H12・H16は代理指標への振替案のとおりとする</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.65（点3）</t>
+          <t>確認事項No.4（点2）</t>
         </is>
       </c>
     </row>
@@ -10564,17 +10582,17 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>サービスガイドに掲載する事業所の範囲</t>
+          <t>第9期の施策・事業実績</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>サービスガイドに掲載する事業所の範囲は北海道の指定事業所一覧（最新のもの）による</t>
+          <t>第9期の施策・事業実績を受領できないものとして、公表資料（交付金の評価結果・総合事業の実施状況に関する調査・年報）により評価する</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.66（点3）</t>
+          <t>確認事項No.5（点2）</t>
         </is>
       </c>
     </row>
@@ -10589,17 +10607,17 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>算定方法の国の様式との整合（点検結果）</t>
+          <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
+          <t>3調査の点検事項は当方の判定のままとする</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.67（点3）</t>
+          <t>確認事項No.8（点2）</t>
         </is>
       </c>
     </row>
@@ -10614,17 +10632,17 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの自然体推計の再出力のお願い</t>
+          <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
+          <t>会議日程及びパブリックコメントの期間は仕様書５の工程による</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.68（点3）</t>
+          <t>確認事項No.19（点2）</t>
         </is>
       </c>
     </row>
@@ -10639,17 +10657,17 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>交付金の全国順位の計画本文への掲載</t>
+          <t>キックオフ会議資料への工程表の反映</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>交付金の全国順位は計画本文に掲載せず、策定委員会資料にとどめる（確認事項No.71のとおり）</t>
+          <t>現行の工程表のまま進める</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.70（点3）</t>
+          <t>確認事項No.42（点2）</t>
         </is>
       </c>
     </row>
@@ -10664,17 +10682,17 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
+          <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）は協議資料にとどめ素案に入れない</t>
+          <t>告示を確認できないものとして、特別地域加算の判定を計画素案に書かず［要確認］のまま残す</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.73（点3）</t>
+          <t>確認事項No.1（点2）</t>
         </is>
       </c>
     </row>
@@ -10689,17 +10707,17 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>代表KPIと改善事項の再整理案</t>
+          <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>代表KPIと改善事項は当方の再整理案のままとする</t>
+          <t>類似保険者との比較は公表されている同規模保険者40団体による</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.75（点3）</t>
+          <t>確認事項No.3（点2）</t>
         </is>
       </c>
     </row>
@@ -10714,17 +10732,17 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>介護リームスから抽出できる項目</t>
+          <t>交付金の評価調書</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>介護リームスから抽出できないものとして、代表KPI H03は未算定のままとする</t>
+          <t>評価調書を受領できないものとして、得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できない旨を注記する</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.76（点3）</t>
+          <t>確認事項No.6（点2）</t>
         </is>
       </c>
     </row>
@@ -10739,17 +10757,17 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥の団体別の公表値</t>
+          <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥の団体別の公表値を引用できないものとして、当該指標は計画本文に掲げない</t>
+          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.77（点3）</t>
+          <t>確認事項No.9（点2）</t>
         </is>
       </c>
     </row>
@@ -10764,17 +10782,17 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>グループホームびえいの郷の定員減の時期</t>
+          <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>北海道の名簿の定員のまま概算する</t>
+          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.78（点3）</t>
+          <t>確認事項No.10（点2）</t>
         </is>
       </c>
     </row>
@@ -10789,17 +10807,17 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第5章の施策数の見直しの範囲</t>
+          <t>町別の人口・世帯データ</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策の体系を維持する（施策数を見直さない）</t>
+          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.79（点3）</t>
+          <t>確認事項No.11（点2）</t>
         </is>
       </c>
     </row>
@@ -10814,17 +10832,17 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H16のデータ源（国保連の給付実績の明細情報）</t>
+          <t>日常生活圏域別のデータ</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>国保連の給付実績の明細を受領できないものとして、代表KPI H16は地域密着型サービスに限った確認件数を代理指標とする</t>
+          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.81（点3）</t>
+          <t>確認事項No.12（点2）</t>
         </is>
       </c>
     </row>
@@ -10839,17 +10857,17 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
+          <t>骨子案の内容の確認</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
+          <t>骨子案は提出した内容のままとする</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.95（点3）</t>
+          <t>確認事項No.18（点2）</t>
         </is>
       </c>
     </row>
@@ -10864,17 +10882,17 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+          <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
+          <t>北海道の評価指標の読替えは当方の案のままとする</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.96（点3）</t>
+          <t>確認事項No.22（点2）</t>
         </is>
       </c>
     </row>
@@ -10889,17 +10907,17 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
+          <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
+          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.102（点3）</t>
+          <t>確認事項No.27（点2）</t>
         </is>
       </c>
     </row>
@@ -10914,17 +10932,17 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議関係資料の取扱いの確認</t>
+          <t>調査対象者の範囲の確認</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>転載を禁ずる旨の記載がある2件は成果品に用いず、原典（厚労省の市町村マニュアル及び別冊事例集）のみを引く</t>
+          <t>現に収録している調査対象者の範囲による</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.122（点3）</t>
+          <t>確認事項No.28（点2）</t>
         </is>
       </c>
     </row>
@@ -10939,17 +10957,17 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
+          <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
+          <t>公表されている全国集計の値による</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.124（点3）</t>
+          <t>確認事項No.38（点2）</t>
         </is>
       </c>
     </row>
@@ -10964,17 +10982,17 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
+          <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果は「在宅で困難を抱える方の状況」として引き、在宅の認定者全体の割合としては引かない</t>
+          <t>令和8年9月25日の再提供により決着済み。再提供を受けたファイルの値（3町合計と円単位一致）による</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.140（点3）</t>
+          <t>確認事項No.46（点2）</t>
         </is>
       </c>
     </row>
@@ -10989,17 +11007,17 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
+          <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
+          <t>総括表（保険者単位）を用い、計画作成支援ツールの実績値シートは比較のためにのみ用いる</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.149（点3）</t>
+          <t>確認事項No.47（点2）</t>
         </is>
       </c>
     </row>
@@ -11014,17 +11032,17 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けた要介護度の変化</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
+          <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値による</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.30（点3）</t>
+          <t>確認事項No.48（点2）</t>
         </is>
       </c>
     </row>
@@ -11039,17 +11057,17 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率の経緯</t>
+          <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
+          <t>受領済みの年報・月報の値による</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.34（点3）</t>
+          <t>確認事項No.50（点2）</t>
         </is>
       </c>
     </row>
@@ -11064,17 +11082,17 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
+          <t>月報の値の接続のずれ（ご報告）</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
+          <t>月報の値の接続のずれは記録として残し、計画本文には用いない</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.35（点3）</t>
+          <t>確認事項No.51（点2）</t>
         </is>
       </c>
     </row>
@@ -11089,17 +11107,17 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績と収納率</t>
+          <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
+          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.36（点3）</t>
+          <t>確認事項No.52（点2）</t>
         </is>
       </c>
     </row>
@@ -11114,17 +11132,17 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月新設の3区分を0として立てる</t>
+          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合は1億円あたり月額約▲310円となることを併記する</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.115（点3）</t>
+          <t>確認事項No.53（点2）</t>
         </is>
       </c>
     </row>
@@ -11139,17 +11157,17 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16の代理指標</t>
+          <t>議事録の文書プロパティに個人名が再度入る</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16は代理指標への振替案のとおりとする</t>
+          <t>議事録は作成者名を落として再出力する（当方で対応する）</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.4（点2）</t>
+          <t>確認事項No.54（点2）</t>
         </is>
       </c>
     </row>
@@ -11164,17 +11182,17 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績</t>
+          <t>議事録の表記に関するご提案3件</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績を受領できないものとして、公表資料（交付金の評価結果・総合事業の実施状況に関する調査・年報）により評価する</t>
+          <t>議事録の表記はご提案3件のとおり改める</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.5（点2）</t>
+          <t>確認事項No.55（点2）</t>
         </is>
       </c>
     </row>
@@ -11189,17 +11207,17 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項の取扱い</t>
+          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項は当方の判定のままとする</t>
+          <t>他団体の集計帳票6件は成果品に用いない</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.8（点2）</t>
+          <t>確認事項No.56（点2）</t>
         </is>
       </c>
     </row>
@@ -11214,17 +11232,17 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>会議日程とパブリックコメントの期間</t>
+          <t>調整交付金の算定基礎の確認</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>会議日程及びパブリックコメントの期間は仕様書５の工程による</t>
+          <t>現行の扱い（第9期の算定を再現し公表値6,428円と一致する扱い）による</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.19（点2）</t>
+          <t>確認事項No.59（点2）</t>
         </is>
       </c>
     </row>
@@ -11239,17 +11257,17 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料への工程表の反映</t>
+          <t>交付金の評価項目と19施策の割当て</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>現行の工程表のまま進める</t>
+          <t>交付金の評価項目と19施策の割当ては当方の案のままとする</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.42（点2）</t>
+          <t>確認事項No.61（点2）</t>
         </is>
       </c>
     </row>
@@ -11264,17 +11282,17 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>特別地域加算の対象地域告示</t>
+          <t>職員個票のリストによる重複確認の可否</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>告示を確認できないものとして、特別地域加算の判定を計画素案に書かず［要確認］のまま残す</t>
+          <t>職員個票を突き合わせず、事業所への照会により重複を判別する</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.1（点2）</t>
+          <t>確認事項No.80（点2）</t>
         </is>
       </c>
     </row>
@@ -11289,17 +11307,17 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較分析の対象</t>
+          <t>構成町との意見交換会の実施方法と町別データシート</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較は公表されている同規模保険者40団体による</t>
+          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで進める</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.3（点2）</t>
+          <t>確認事項No.83（点2）</t>
         </is>
       </c>
     </row>
@@ -11314,17 +11332,17 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価調書</t>
+          <t>町別データシートの内容と配付</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>評価調書を受領できないものとして、得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できない旨を注記する</t>
+          <t>町別データシートは現行の内容のまま配付する</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.6（点2）</t>
+          <t>確認事項No.85（点2）</t>
         </is>
       </c>
     </row>
@@ -11339,17 +11357,17 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>調査の対象者範囲と回収率</t>
+          <t>成果品の統合の方針</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
+          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す（現行）</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.9（点2）</t>
+          <t>確認事項No.117（点2）</t>
         </is>
       </c>
     </row>
@@ -11364,17 +11382,17 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>介護人材実態調査の採用者数・退職者数</t>
+          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
+          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.10（点2）</t>
+          <t>確認事項No.138（点2）</t>
         </is>
       </c>
     </row>
@@ -11389,17 +11407,17 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>町別の人口・世帯データ</t>
+          <t>健康とくらしの調査の個票の再提供の要否</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
+          <t>健康とくらしの調査の個票の再提供を依頼しない（成果品は収録済みで内容が確定しており、現時点で不足がない）</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.11（点2）</t>
+          <t>確認事項No.139（点2）</t>
         </is>
       </c>
     </row>
@@ -11414,17 +11432,17 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域別のデータ</t>
+          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
+          <t>受領済みの画面の写しの範囲で概算し、確認できていない項目はその旨を明記する</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.12（点2）</t>
+          <t>確認事項No.148（点2）</t>
         </is>
       </c>
     </row>
@@ -11439,17 +11457,17 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>骨子案の内容の確認</t>
+          <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>骨子案は提出した内容のままとする</t>
+          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.18（点2）</t>
+          <t>確認事項No.60（点2）</t>
         </is>
       </c>
     </row>
@@ -11464,17 +11482,17 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標の読替えの考え方</t>
+          <t>区域内に事業所がないサービスの住民向けの記載</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標の読替えは当方の案のままとする</t>
+          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.22（点2）</t>
+          <t>確認事項No.64（点2）</t>
         </is>
       </c>
     </row>
@@ -11489,17 +11507,17 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>令和4年度 健康とくらしの調査の集計表</t>
+          <t>成果指向型配分枠（令和8年度新設）への対応</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
+          <t>成果指向型配分枠への対応状況を確認できないものとして、第10期の施策には位置づけず、確認でき次第加える</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.27（点2）</t>
+          <t>確認事項No.69（点2）</t>
         </is>
       </c>
     </row>
@@ -11514,17 +11532,17 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>調査対象者の範囲の確認</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>現に収録している調査対象者の範囲による</t>
+          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.28（点2）</t>
+          <t>確認事項No.89（点2）</t>
         </is>
       </c>
     </row>
@@ -11539,17 +11557,17 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の令和6年・令和7年調査の結果</t>
+          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>公表されている全国集計の値による</t>
+          <t>第9期計画の本文及び前回調査の原集計表を受領できないものとして、前回調査との比較は割合のみとし、指標別の分母を確認できない旨を注記する</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.38（点2）</t>
+          <t>確認事項No.90（点2）</t>
         </is>
       </c>
     </row>
@@ -11564,17 +11582,17 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の給付費の集計が一致しない</t>
+          <t>介護給付費通知及び給付実績の活用による確認等</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月25日の再提供により決着済み。再提供を受けたファイルの値（3町合計と円単位一致）による</t>
+          <t>介護給付費通知の実施状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.46（点2）</t>
+          <t>確認事項No.91（点2）</t>
         </is>
       </c>
     </row>
@@ -11589,17 +11607,17 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの実績値シートの確認</t>
+          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>総括表（保険者単位）を用い、計画作成支援ツールの実績値シートは比較のためにのみ用いる</t>
+          <t>認定調査の委託の状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.47（点2）</t>
+          <t>確認事項No.92（点2）</t>
         </is>
       </c>
     </row>
@@ -11614,17 +11632,17 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
+          <t>令和9年4月1日から義務となる2件への対応</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値による</t>
+          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.48（点2）</t>
+          <t>確認事項No.97（点2）</t>
         </is>
       </c>
     </row>
@@ -11639,17 +11657,17 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>年報・月報の受領に伴う確認</t>
+          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>受領済みの年報・月報の値による</t>
+          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.50（点2）</t>
+          <t>確認事項No.99（点2）</t>
         </is>
       </c>
     </row>
@@ -11664,17 +11682,17 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれ（ご報告）</t>
+          <t>補正しても外れるサービス6件の理由</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれは記録として残し、計画本文には用いない</t>
+          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.51（点2）</t>
+          <t>確認事項No.108（点2）</t>
         </is>
       </c>
     </row>
@@ -11689,17 +11707,17 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領に伴う確認</t>
+          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
+          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.52（点2）</t>
+          <t>確認事項No.111（点2）</t>
         </is>
       </c>
     </row>
@@ -11714,17 +11732,17 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
+          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合は1億円あたり月額約▲310円となることを併記する</t>
+          <t>施策2-5の代表KPIはO2（提起された地域課題のうち翌年度の事業・予算に反映されたものの割合）とする（当方案）</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.53（点2）</t>
+          <t>確認事項No.118（点2）</t>
         </is>
       </c>
     </row>
@@ -11739,17 +11757,17 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>議事録の文書プロパティに個人名が再度入る</t>
+          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>議事録は作成者名を落として再出力する（当方で対応する）</t>
+          <t>地域ケア会議の記録様式は協議資料にとどめ、令和9年度に整える</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.54（点2）</t>
+          <t>確認事項No.119（点2）</t>
         </is>
       </c>
     </row>
@@ -11764,17 +11782,17 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記に関するご提案3件</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記はご提案3件のとおり改める</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.55（点2）</t>
+          <t>確認事項No.120（点2）</t>
         </is>
       </c>
     </row>
@@ -11789,17 +11807,17 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
+          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>他団体の集計帳票6件は成果品に用いない</t>
+          <t>令和7年度の実施報告書により把握できる範囲で記述する</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.56（点2）</t>
+          <t>確認事項No.121（点2）</t>
         </is>
       </c>
     </row>
@@ -11814,17 +11832,17 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>調整交付金の算定基礎の確認</t>
+          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>現行の扱い（第9期の算定を再現し公表値6,428円と一致する扱い）による</t>
+          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.59（点2）</t>
+          <t>確認事項No.125（点2）</t>
         </is>
       </c>
     </row>
@@ -11839,17 +11857,17 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当て</t>
+          <t>見える化システムの総人口の設定を案Cに改めるか</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当ては当方の案のままとする</t>
+          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.61（点2）</t>
+          <t>確認事項No.127（点2）</t>
         </is>
       </c>
     </row>
@@ -11864,17 +11882,17 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>職員個票のリストによる重複確認の可否</t>
+          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>職員個票を突き合わせず、事業所への照会により重複を判別する</t>
+          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.80（点2）</t>
+          <t>確認事項No.133（点2）</t>
         </is>
       </c>
     </row>
@@ -11889,17 +11907,17 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>構成町との意見交換会の実施方法と町別データシート</t>
+          <t>画面の令和7年度と年報の月平均の食い違い</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで進める</t>
+          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.83（点2）</t>
+          <t>確認事項No.136（点2）</t>
         </is>
       </c>
     </row>
@@ -11914,17 +11932,17 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>町別データシートの内容と配付</t>
+          <t>計画素案の未確定箇所の表示の統一</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>町別データシートは現行の内容のまま配付する</t>
+          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとする</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.85（点2）</t>
+          <t>確認事項No.143（点2）</t>
         </is>
       </c>
     </row>
@@ -11939,17 +11957,17 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>成果品の統合の方針</t>
+          <t>計画素案 第2章第1節に町別の図を加えるか</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す（現行）</t>
+          <t>計画素案 第2章第1節に町別の図を加えない。加筆分は協議用の資料にとどめる</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.117（点2）</t>
+          <t>確認事項No.154（点2）</t>
         </is>
       </c>
     </row>
@@ -11964,17 +11982,17 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
+          <t>中長期推計を令和12・27・32年度まで広げるか</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ</t>
+          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.138（点2）</t>
+          <t>確認事項No.157（点2）</t>
         </is>
       </c>
     </row>
@@ -11989,17 +12007,17 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供の要否</t>
+          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供を依頼しない（成果品は収録済みで内容が確定しており、現時点で不足がない）</t>
+          <t>設問ごとの有効回答を分母とし、町別の値は掲げない（令和8年9月25日に是正済み）</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.139（点2）</t>
+          <t>確認事項No.158（点2）</t>
         </is>
       </c>
     </row>
@@ -12014,17 +12032,17 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
+          <t>東川町の通いの場の整備と担い手の確保</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>受領済みの画面の写しの範囲で概算し、確認できていない項目はその旨を明記する</t>
+          <t>現状のまま（東川町の整備を見込まない）第10期の目標値を置く</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.148（点2）</t>
+          <t>確認事項No.159（点2）</t>
         </is>
       </c>
     </row>
@@ -12039,17 +12057,17 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提（受託者案）</t>
+          <t>東川町の認知症サポーター養成講座の実施状況</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
+          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.60（点2）</t>
+          <t>確認事項No.160（点2）</t>
         </is>
       </c>
     </row>
@@ -12064,17 +12082,17 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスの住民向けの記載</t>
+          <t>東川町のチームオレンジ事業の位置づけ</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
+          <t>東川町の取組として記述し3町展開は記述しない</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.64（点2）</t>
+          <t>確認事項No.161（点2）</t>
         </is>
       </c>
     </row>
@@ -12089,17 +12107,17 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠（令和8年度新設）への対応</t>
+          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠への対応状況を確認できないものとして、第10期の施策には位置づけず、確認でき次第加える</t>
+          <t>令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.69（点2）</t>
+          <t>確認事項No.162（点2）</t>
         </is>
       </c>
     </row>
@@ -12114,17 +12132,17 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
+          <t>美瑛町の取組として記述し3町展開は記述しない</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.89（点2）</t>
+          <t>確認事項No.163（点2）</t>
         </is>
       </c>
     </row>
@@ -12139,17 +12157,17 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
+          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文及び前回調査の原集計表を受領できないものとして、前回調査との比較は割合のみとし、指標別の分母を確認できない旨を注記する</t>
+          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.90（点2）</t>
+          <t>確認事項No.164（点2）</t>
         </is>
       </c>
     </row>
@@ -12164,17 +12182,17 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知及び給付実績の活用による確認等</t>
+          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知の実施状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
+          <t>現に確認できる取組の範囲で記述する</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.91（点2）</t>
+          <t>確認事項No.165（点2）</t>
         </is>
       </c>
     </row>
@@ -12189,17 +12207,17 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
+          <t>東神楽町の通いの場の維持</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>認定調査の委託の状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
+          <t>令和6年度の水準が続くものとして目標値を置く</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.92（点2）</t>
+          <t>確認事項No.166（点2）</t>
         </is>
       </c>
     </row>
@@ -12214,17 +12232,17 @@
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月1日から義務となる2件への対応</t>
+          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
+          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.97（点2）</t>
+          <t>確認事項No.167（点2）</t>
         </is>
       </c>
     </row>
@@ -12239,17 +12257,17 @@
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
+          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
+          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.99（点2）</t>
+          <t>確認事項No.170（点2）</t>
         </is>
       </c>
     </row>
@@ -12264,17 +12282,17 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れるサービス6件の理由</t>
+          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
+          <t>の当方の扱い＝掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.108（点2）</t>
+          <t>確認事項No.172（点2）</t>
         </is>
       </c>
     </row>
@@ -12289,17 +12307,17 @@
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
+          <t>保険料算定の前提</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
+          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.111（点2）</t>
+          <t>確認事項No.16（点2）</t>
         </is>
       </c>
     </row>
@@ -12314,17 +12332,17 @@
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
+          <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIはO2（提起された地域課題のうち翌年度の事業・予算に反映されたものの割合）とする（当方案）</t>
+          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.118（点2）</t>
+          <t>確認事項No.2（点1）</t>
         </is>
       </c>
     </row>
@@ -12339,17 +12357,17 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
+          <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の記録様式は協議資料にとどめ、令和9年度に整える</t>
+          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.119（点2）</t>
+          <t>確認事項No.13（点1）</t>
         </is>
       </c>
     </row>
@@ -12364,17 +12382,17 @@
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
+          <t>人口推計の基礎とする系列</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
+          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.120（点2）</t>
+          <t>確認事項No.14（点1）</t>
         </is>
       </c>
     </row>
@@ -12389,17 +12407,17 @@
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
+          <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の実施報告書により把握できる範囲で記述する</t>
+          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.121（点2）</t>
+          <t>確認事項No.15（点1）</t>
         </is>
       </c>
     </row>
@@ -12414,17 +12432,17 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
+          <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
+          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.125（点2）</t>
+          <t>確認事項No.17（点1）</t>
         </is>
       </c>
     </row>
@@ -12439,17 +12457,17 @@
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総人口の設定を案Cに改めるか</t>
+          <t>北海道・圏域との調整の場</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
+          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.127（点2）</t>
+          <t>確認事項No.20（点1）</t>
         </is>
       </c>
     </row>
@@ -12464,17 +12482,17 @@
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+          <t>成果品の仕様</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
+          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.133（点2）</t>
+          <t>確認事項No.21（点1）</t>
         </is>
       </c>
     </row>
@@ -12489,17 +12507,17 @@
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度と年報の月平均の食い違い</t>
+          <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
+          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.136（点2）</t>
+          <t>確認事項No.23（点1）</t>
         </is>
       </c>
     </row>
@@ -12514,17 +12532,17 @@
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所の表示の統一</t>
+          <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとする</t>
+          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.143（点2）</t>
+          <t>確認事項No.26（点1）</t>
         </is>
       </c>
     </row>
@@ -12539,17 +12557,17 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えるか</t>
+          <t>重度化の速度の前提</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えない。加筆分は協議用の資料にとどめる</t>
+          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.154（点2）</t>
+          <t>確認事項No.29（点1）</t>
         </is>
       </c>
     </row>
@@ -12564,17 +12582,17 @@
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>中長期推計を令和12・27・32年度まで広げるか</t>
+          <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
+          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.157（点2）</t>
+          <t>確認事項No.31（点1）</t>
         </is>
       </c>
     </row>
@@ -12589,17 +12607,17 @@
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
+          <t>統合した成果品の元の資料を残すか</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>設問ごとの有効回答を分母とし、町別の値は掲げない（令和8年9月25日に是正済み）</t>
+          <t>統合した成果品の元の資料を残す</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.158（点2）</t>
+          <t>確認事項No.144（点1）</t>
         </is>
       </c>
     </row>
@@ -12614,17 +12632,17 @@
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>東川町の通いの場の整備と担い手の確保</t>
+          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>現状のまま（東川町の整備を見込まない）第10期の目標値を置く</t>
+          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.159（点2）</t>
+          <t>確認事項No.156（点1）</t>
         </is>
       </c>
     </row>
@@ -12639,17 +12657,17 @@
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>東川町の認知症サポーター養成講座の実施状況</t>
+          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
+          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.160（点2）</t>
+          <t>確認事項No.169（点1）</t>
         </is>
       </c>
     </row>
@@ -12664,17 +12682,17 @@
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>東川町のチームオレンジ事業の位置づけ</t>
+          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>東川町の取組として記述し3町展開は記述しない</t>
+          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.161（点2）</t>
+          <t>確認事項No.171（点1）</t>
         </is>
       </c>
     </row>
@@ -12689,17 +12707,17 @@
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
+          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残す</t>
+          <t>の当方の扱い＝現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.162（点2）</t>
+          <t>確認事項No.173（点1）</t>
         </is>
       </c>
     </row>
@@ -12714,17 +12732,17 @@
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
+          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の取組として記述し3町展開は記述しない</t>
+          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.163（点2）</t>
+          <t>確認事項No.74（点1）</t>
         </is>
       </c>
     </row>
@@ -12739,17 +12757,17 @@
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
+          <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
+          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.164（点2）</t>
+          <t>確認事項No.24（点0）</t>
         </is>
       </c>
     </row>
@@ -12764,640 +12782,40 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
+          <t>代表KPIの目標値の決定</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述する</t>
+          <t>代表KPIの目標値は、令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置く</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.165（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="128" ht="44" customHeight="1">
-      <c r="A128" s="5" t="n">
-        <v>123</v>
-      </c>
-      <c r="B128" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr">
-        <is>
-          <t>東神楽町の通いの場の維持</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>令和6年度の水準が続くものとして目標値を置く</t>
-        </is>
-      </c>
-      <c r="E128" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.166（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="44" customHeight="1">
-      <c r="A129" s="5" t="n">
-        <v>124</v>
-      </c>
-      <c r="B129" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
-        </is>
-      </c>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
-        </is>
-      </c>
-      <c r="E129" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.167（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="44" customHeight="1">
-      <c r="A130" s="5" t="n">
-        <v>125</v>
-      </c>
-      <c r="B130" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
-        </is>
-      </c>
-      <c r="E130" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.170（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="44" customHeight="1">
-      <c r="A131" s="5" t="n">
-        <v>126</v>
-      </c>
-      <c r="B131" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>の当方の扱い＝掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
-        </is>
-      </c>
-      <c r="E131" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.172（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="44" customHeight="1">
-      <c r="A132" s="5" t="n">
-        <v>127</v>
-      </c>
-      <c r="B132" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>保険料算定の前提</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
-        </is>
-      </c>
-      <c r="E132" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.16（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="44" customHeight="1">
-      <c r="A133" s="5" t="n">
-        <v>128</v>
-      </c>
-      <c r="B133" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
-        </is>
-      </c>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
-        </is>
-      </c>
-      <c r="E133" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.2（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="44" customHeight="1">
-      <c r="A134" s="5" t="n">
-        <v>129</v>
-      </c>
-      <c r="B134" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>訪問・通所困難地域の判定資料</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
-        <is>
-          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
-        </is>
-      </c>
-      <c r="E134" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.13（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="44" customHeight="1">
-      <c r="A135" s="5" t="n">
-        <v>130</v>
-      </c>
-      <c r="B135" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>人口推計の基礎とする系列</t>
-        </is>
-      </c>
-      <c r="D135" s="6" t="inlineStr">
-        <is>
-          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
-        </is>
-      </c>
-      <c r="E135" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.14（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="44" customHeight="1">
-      <c r="A136" s="5" t="n">
-        <v>131</v>
-      </c>
-      <c r="B136" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>認定者数の基準月と月次推移</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
-        </is>
-      </c>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.15（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="44" customHeight="1">
-      <c r="A137" s="5" t="n">
-        <v>132</v>
-      </c>
-      <c r="B137" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C137" s="6" t="inlineStr">
-        <is>
-          <t>3町計画への共通指標の掲載</t>
-        </is>
-      </c>
-      <c r="D137" s="6" t="inlineStr">
-        <is>
-          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
-        </is>
-      </c>
-      <c r="E137" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.17（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="44" customHeight="1">
-      <c r="A138" s="5" t="n">
-        <v>133</v>
-      </c>
-      <c r="B138" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C138" s="6" t="inlineStr">
-        <is>
-          <t>北海道・圏域との調整の場</t>
-        </is>
-      </c>
-      <c r="D138" s="6" t="inlineStr">
-        <is>
-          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
-        </is>
-      </c>
-      <c r="E138" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.20（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="44" customHeight="1">
-      <c r="A139" s="5" t="n">
-        <v>134</v>
-      </c>
-      <c r="B139" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C139" s="6" t="inlineStr">
-        <is>
-          <t>成果品の仕様</t>
-        </is>
-      </c>
-      <c r="D139" s="6" t="inlineStr">
-        <is>
-          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
-        </is>
-      </c>
-      <c r="E139" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.21（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="44" customHeight="1">
-      <c r="A140" s="5" t="n">
-        <v>135</v>
-      </c>
-      <c r="B140" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>事業所の定員・稼働率データ</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr">
-        <is>
-          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
-        </is>
-      </c>
-      <c r="E140" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.23（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="44" customHeight="1">
-      <c r="A141" s="5" t="n">
-        <v>136</v>
-      </c>
-      <c r="B141" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C141" s="6" t="inlineStr">
-        <is>
-          <t>認知症・医療介護連携の実績データ</t>
-        </is>
-      </c>
-      <c r="D141" s="6" t="inlineStr">
-        <is>
-          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
-        </is>
-      </c>
-      <c r="E141" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.26（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="44" customHeight="1">
-      <c r="A142" s="5" t="n">
-        <v>137</v>
-      </c>
-      <c r="B142" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C142" s="6" t="inlineStr">
-        <is>
-          <t>重度化の速度の前提</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="inlineStr">
-        <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
-        </is>
-      </c>
-      <c r="E142" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.29（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="44" customHeight="1">
-      <c r="A143" s="5" t="n">
-        <v>138</v>
-      </c>
-      <c r="B143" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C143" s="6" t="inlineStr">
-        <is>
-          <t>給付適正化の実施予定と推計での扱い</t>
-        </is>
-      </c>
-      <c r="D143" s="6" t="inlineStr">
-        <is>
-          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
-        </is>
-      </c>
-      <c r="E143" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.31（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="44" customHeight="1">
-      <c r="A144" s="5" t="n">
-        <v>139</v>
-      </c>
-      <c r="B144" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C144" s="6" t="inlineStr">
-        <is>
-          <t>統合した成果品の元の資料を残すか</t>
-        </is>
-      </c>
-      <c r="D144" s="6" t="inlineStr">
-        <is>
-          <t>統合した成果品の元の資料を残す</t>
-        </is>
-      </c>
-      <c r="E144" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.144（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="44" customHeight="1">
-      <c r="A145" s="5" t="n">
-        <v>140</v>
-      </c>
-      <c r="B145" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C145" s="6" t="inlineStr">
-        <is>
-          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
-        </is>
-      </c>
-      <c r="D145" s="6" t="inlineStr">
-        <is>
-          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
-        </is>
-      </c>
-      <c r="E145" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.156（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="44" customHeight="1">
-      <c r="A146" s="5" t="n">
-        <v>141</v>
-      </c>
-      <c r="B146" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C146" s="6" t="inlineStr">
-        <is>
-          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr">
-        <is>
-          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
-        </is>
-      </c>
-      <c r="E146" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.169（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="44" customHeight="1">
-      <c r="A147" s="5" t="n">
-        <v>142</v>
-      </c>
-      <c r="B147" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C147" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
-        </is>
-      </c>
-      <c r="D147" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
-        </is>
-      </c>
-      <c r="E147" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.171（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="44" customHeight="1">
-      <c r="A148" s="5" t="n">
-        <v>143</v>
-      </c>
-      <c r="B148" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C148" s="6" t="inlineStr">
-        <is>
-          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
-        </is>
-      </c>
-      <c r="D148" s="6" t="inlineStr">
-        <is>
-          <t>の当方の扱い＝現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
-        </is>
-      </c>
-      <c r="E148" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.173（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="44" customHeight="1">
-      <c r="A149" s="5" t="n">
-        <v>144</v>
-      </c>
-      <c r="B149" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C149" s="6" t="inlineStr">
-        <is>
-          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
-        </is>
-      </c>
-      <c r="D149" s="6" t="inlineStr">
-        <is>
-          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
-        </is>
-      </c>
-      <c r="E149" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.74（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="44" customHeight="1">
-      <c r="A150" s="5" t="n">
-        <v>145</v>
-      </c>
-      <c r="B150" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C150" s="6" t="inlineStr">
-        <is>
-          <t>24時間対応サービスの確保方策の決定</t>
-        </is>
-      </c>
-      <c r="D150" s="6" t="inlineStr">
-        <is>
-          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
-        </is>
-      </c>
-      <c r="E150" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.24（点0）</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="44" customHeight="1">
-      <c r="A151" s="5" t="n">
-        <v>146</v>
-      </c>
-      <c r="B151" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C151" s="6" t="inlineStr">
-        <is>
-          <t>代表KPIの目標値の決定</t>
-        </is>
-      </c>
-      <c r="D151" s="6" t="inlineStr">
-        <is>
-          <t>代表KPIの目標値は、令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置く</t>
-        </is>
-      </c>
-      <c r="E151" s="6" t="inlineStr">
-        <is>
           <t>確認事項No.25（点0）</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="76" customHeight="1">
-      <c r="A152" s="14" t="inlineStr">
+    <row r="128" ht="76" customHeight="1">
+      <c r="A128" s="14" t="inlineStr">
         <is>
           <t>注1）「据え置き（区分A）」は、資料の受領を待たずに当方の側で確定できるものです。
 注2）「既定値で進める」は、決着しない場合の扱いを置けているため決定を待たずに作業を進められるものです。決定を受けた時点で見直します。
 注3）ここに現れないもの（既定値を置けていない確認事項）は、扱いを決めること自体が翌日の作業になります。02シートを見ます。
-注4）既定値のとおり計画素案へ反映し終えたもの14件（確認事項No.88・No.98・No.100・No.101・No.103・No.105・No.106・No.107・No.110・No.112・No.113・No.131・No.137・No.150）は、作業としては終わっているため本表から除いています。ご決定はなお待っています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="153"/>
-    <row r="154" ht="20" customHeight="1">
-      <c r="A154" s="3" t="inlineStr">
+注4）既定値のとおり計画素案へ反映し終えたもの38件（確認事項No.7・No.82・No.84・No.86・No.88・No.93・No.94・No.98・No.100・No.101・No.103・No.104・No.105・No.106・No.107・No.109・No.110・No.112・No.113・No.114・No.116・No.123・No.126・No.128・No.129・No.130・No.131・No.132・No.137・No.141・No.142・No.145・No.146・No.147・No.150・No.151・No.152・No.153）は、作業としては終わっているため本表から除いています。ご決定はなお待っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129"/>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="3" t="inlineStr">
         <is>
           <t>2　先に扱いを決めるもの（既定値を置けていない）　0件</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="18" customHeight="1">
-      <c r="A155" s="21" t="inlineStr">
+    <row r="131" ht="18" customHeight="1">
+      <c r="A131" s="21" t="inlineStr">
         <is>
           <t>ありません。未決の確認事項の全件に扱いを置けています。</t>
         </is>
@@ -13405,12 +12823,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A154:E154"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A131:E131"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A152:E152"/>
-    <mergeCell ref="A155:E155"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A130:E130"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13485,17 +12903,17 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>区域を越えた施設利用の扱い</t>
+          <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
+          <t>第9期条例の16段階・乗率（公費軽減前）を据え置いて算定し、政令の公布後に再算定する</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.141（点6）</t>
+          <t>確認事項No.33（点4）</t>
         </is>
       </c>
     </row>
@@ -13510,17 +12928,17 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを要介護度別に改めてよいか</t>
+          <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
+          <t>中間報告・施策体系新旧対照表・骨子案は提出した内容のままとする</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.146（点6）</t>
+          <t>確認事項No.39（点3）</t>
         </is>
       </c>
     </row>
@@ -13535,17 +12953,17 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
+          <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
+          <t>同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.151（点6）</t>
+          <t>確認事項No.40（点3）</t>
         </is>
       </c>
     </row>
@@ -13560,17 +12978,17 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
+          <t>認定に要する日数の扱い</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定に給付適正化主要3事業の取組状況を勘案しないものとして算定する（調整交付金7.3755％のまま。安全側）</t>
+          <t>令和8年8月28日受領の集計帳票による</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.93（点6）</t>
+          <t>確認事項No.43（点3）</t>
         </is>
       </c>
     </row>
@@ -13585,17 +13003,17 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>構成町の一般会計繰入金の町別按分の方法</t>
+          <t>代表KPI H15の分母の定義</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>町別按分は当方の案（第1次概算）のまま示す</t>
+          <t>代表KPI H15の分母は標準給付費見込額とする（受託者案）</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.82（点5）</t>
+          <t>確認事項No.45（点3）</t>
         </is>
       </c>
     </row>
@@ -13610,17 +13028,17 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
+          <t>計画値を0としたサービスに実績がある2件</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
+          <t>第10期は計画値を0とせず、算定値を置く（対計画比が算出され評価の対象となるようにする）</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.123（点5）</t>
+          <t>確認事項No.57（点3）</t>
         </is>
       </c>
     </row>
@@ -13635,17 +13053,17 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計方式は基本推計でよいか</t>
+          <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>基本推計に近いP3で概算する</t>
+          <t>定期巡回・随時対応型訪問介護看護は自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.126（点5）</t>
+          <t>確認事項No.58（点3）</t>
         </is>
       </c>
     </row>
@@ -13660,17 +13078,17 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法第13条の市町村認知症施策推進計画をどう扱うか</t>
+          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>案B（3町がそれぞれ市町村計画を策定する）のまま素案に反映する</t>
+          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.130（点5）</t>
+          <t>確認事項No.63（点3）</t>
         </is>
       </c>
     </row>
@@ -14166,7 +13584,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>146件（区分A 0・既定値 146）</t>
+          <t>122件（区分A 0・既定値 122）</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -752,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>＋6pt</t>
+          <t>＋8pt</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.7890000000000001</v>
+        <v>0.7910000000000001</v>
       </c>
       <c r="D18" s="11" t="inlineStr"/>
       <c r="E18" s="11" t="inlineStr"/>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>52c9b69</t>
+          <t>6adcdee</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>翌日の作業順位8件の処理と単価の趨勢の効きの是正</t>
+          <t>既定値による計画素案への反映を38件まで進めた</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>666b8ee</t>
+          <t>52c9b69</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>3町合同意見交換会の資料と作業継続可能8件の処理</t>
+          <t>翌日の作業順位8件の処理と単価の趨勢の効きの是正</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>241932b</t>
+          <t>666b8ee</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>既定値の仮置き（未決160件）と据え置き区分Aの更新</t>
+          <t>3町合同意見交換会の資料と作業継続可能8件の処理</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr"/>
@@ -1291,20 +1291,38 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>9c17709</t>
+          <t>241932b</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>日次のWBS更新と翌日の作業順位（スキルと日次の表）</t>
+          <t>既定値の仮置き（未決160件）と据え置き区分Aの更新</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr"/>
       <c r="E26" s="6" t="inlineStr"/>
       <c r="F26" s="6" t="inlineStr"/>
     </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="14" t="inlineStr">
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>9c17709</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>日次のWBS更新と翌日の作業順位（スキルと日次の表）</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
@@ -1313,9 +1331,9 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A21:F21"/>
   </mergeCells>
@@ -1417,27 +1435,27 @@
         <v>1</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域ごとの必要利用定員総数（法定記載事項）</t>
+          <t>地域支援事業の量の見込みを算定してよいか</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第7節・第6章第4節4
-サービス見込量 第1次概算</t>
+          <t>サービス見込量 第2次概算
+計画素案 第6章第3節</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G6" s="15" t="n">
@@ -1445,12 +1463,12 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）／法定記載事項 法第117条に直結（+2）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）／月額への効き 最大7円（令和7年度の総合事業の事業費）（+1）／法定記載事項 法第117条に直結（+2）</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>3町（3圏域）を基盤整備単位とする案のまま概算する。必要利用定員総数は［要協議］のまま残す</t>
+          <t>令和6年度の利用者実人数を据え置いて延ばした量の見込みを掲げ、令和7年度の実施状況は単位が異なるため別の表として示す</t>
         </is>
       </c>
     </row>
@@ -1459,18 +1477,18 @@
         <v>2</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを一律からサービス別の趨勢を半分反映する置き方に改めるか</t>
+          <t>認知症総合支援事業の実績のご提供</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第1次概算
-将来推計 第3段階
-計画素案 第6章第2節2</t>
+          <t>サービス見込量 第2次概算
+計画素案 第6章第3節2
+令和8年9月25日受領資料の受領点検</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1480,20 +1498,20 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G7" s="15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）／月額への効き 最大58円（補正を行うかどうかのご判断）（+2）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）／法定記載事項 法第117条に直結（+2）</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>サービス別の趨勢を反映する補正は行わない（見込量は要介護度別の伸びによる）。補正を行った場合の月額への効きは計画素案 第6章第6節2に併記する</t>
+          <t>6事業別の事業費を受領できないものとして、認知症総合支援事業の量の見込みは立てず、3町の取組の回数のみを掲げる</t>
         </is>
       </c>
     </row>
@@ -1502,17 +1520,18 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設の必要利用定員総数を定めるか</t>
+          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第1次概算
-計画素案 第6章第4節4</t>
+          <t>将来推計 第3段階
+計画素案 第6章第6節
+サービス見込量 第2次概算</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1522,20 +1541,20 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G8" s="15" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）／法定記載事項 法第117条に直結（+2）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）／月額への効き 最大47円（第7期給付適正化計画の目標のご判断）（+1）</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設の必要利用定員総数を定めないまま概算する</t>
+          <t>財政調整交付金の算定に給付適正化主要3事業の取組状況を勘案しないものとして算定する（調整交付金7.3755％のまま。安全側）</t>
         </is>
       </c>
     </row>
@@ -1544,22 +1563,22 @@
         <v>4</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の見込量の表に何を掲げるか</t>
+          <t>日常生活圏域ごとの必要利用定員総数（法定記載事項）</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節・第3節
-サービス見込量 第1次概算</t>
+          <t>計画素案 第1章第7節・第6章第4節4
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -1567,17 +1586,17 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G9" s="15" t="n">
-        <v>8</v>
+      <c r="G9" s="16" t="n">
+        <v>5</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）／法定記載事項 法第117条に直結（+2）</t>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）／法定記載事項 法第117条に直結（+2）</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節に利用回（日）数を、第3節2に介護予防・日常生活支援総合事業及び一般介護予防事業の量の見込みを掲げた現行のまま確定する。必要利用定員総数の第2節への再掲は行わない（第4節4による）</t>
+          <t>3町（3圏域）を基盤整備単位とする案のまま概算する。必要利用定員総数は［要協議］のまま残す</t>
         </is>
       </c>
     </row>
@@ -1586,17 +1605,18 @@
         <v>5</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の量の見込みを算定してよいか</t>
+          <t>見込量の伸びを一律からサービス別の趨勢を半分反映する置き方に改めるか</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算
-計画素案 第6章第3節</t>
+          <t>サービス見込量の算定
+将来推計 第3段階
+計画素案 第6章第2節2</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1606,20 +1626,20 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>8</v>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>5</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）／月額への効き 最大7円（令和7年度の総合事業の事業費）（+1）／法定記載事項 法第117条に直結（+2）</t>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）／月額への効き 最大58円（補正を行うかどうかのご判断）（+2）</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の利用者実人数を据え置いて延ばした量の見込みを掲げ、令和7年度の実施状況は単位が異なるため別の表として示す</t>
+          <t>サービス別の趨勢を反映する補正は行わない（見込量は要介護度別の伸びによる）。補正を行った場合の月額への効きは計画素案 第6章第6節2に併記する</t>
         </is>
       </c>
     </row>
@@ -1628,22 +1648,22 @@
         <v>6</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行うか。行う場合の対象と歯止め</t>
+          <t>混合型特定施設の必要利用定員総数を定めるか</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第1次概算
-計画素案 第4章第3節・第6章第2節</t>
+          <t>サービス見込量の算定
+計画素案 第6章第4節4</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -1651,17 +1671,17 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G11" s="15" t="n">
-        <v>7</v>
+      <c r="G11" s="16" t="n">
+        <v>5</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）／月額への効き 最大13円（施策の達成目標のご判断）（+1）</t>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）／法定記載事項 法第117条に直結（+2）</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行わないまま概算する（安全側）</t>
+          <t>混合型特定施設の必要利用定員総数を定めないまま概算する</t>
         </is>
       </c>
     </row>
@@ -1670,22 +1690,21 @@
         <v>7</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
+          <t>認知症基本法第13条の市町村認知症施策推進計画をどう扱うか</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階
-サービス見込量 第1次概算</t>
+          <t>計画素案 第1章第2節・第5章 基本目標2</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1693,17 +1712,17 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G12" s="15" t="n">
-        <v>7</v>
+      <c r="G12" s="16" t="n">
+        <v>5</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 概算（+3）／月額への効き 最大327円（第10期の介護報酬改定率）（+4）／当方で動かせるか 国の告示・公布待ち（-2）</t>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）／法定記載事項 法第117条に直結（+2）</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費は令和7年度で固定して概算する（単価の趨勢を織り込まないことによる効きは計画素案 第6章第6節2に掲げる）</t>
+          <t>案B（3町がそれぞれ市町村計画を策定する）のまま素案に反映する</t>
         </is>
       </c>
     </row>
@@ -1712,17 +1731,17 @@
         <v>8</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
+          <t>第6章第2節の見込量の表に何を掲げるか</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第1次概算
-計画素案 第5章 基本目標5・第6章第2節</t>
+          <t>計画素案 第6章第2節・第3節
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1732,20 +1751,20 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>7</v>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>5</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）／月額への効き 最大327円（第10期の介護報酬改定率）（+4）／当方で動かせるか 国の告示・公布待ち（-2）</t>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）／法定記載事項 法第117条に直結（+2）</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
+          <t>計画素案 第6章第2節に利用回（日）数を、第3節2に介護予防・日常生活支援総合事業及び一般介護予防事業の量の見込みを掲げた現行のまま確定する。必要利用定員総数の第2節への再掲は行わない（第4節4による）</t>
         </is>
       </c>
     </row>
@@ -1754,23 +1773,23 @@
         <v>9</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実績のご提供</t>
+          <t>東川町の施設整備・サービス提供方針</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
           <t>サービス見込量 第2次概算
-計画素案 第6章第3節2
-令和8年9月25日受領資料の受領点検</t>
+計画素案 第2章第2節・第6章第2節・第4節
+構成町の意見への回答 6</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・東川町</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1778,17 +1797,17 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G14" s="15" t="n">
-        <v>7</v>
+      <c r="G14" s="16" t="n">
+        <v>5</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）／法定記載事項 法第117条に直結（+2）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>6事業別の事業費を受領できないものとして、認知症総合支援事業の量の見込みは立てず、3町の取組の回数のみを掲げる</t>
+          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残す</t>
         </is>
       </c>
     </row>
@@ -1797,18 +1816,18 @@
         <v>10</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
+          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第4節1
-計画素案 第6章第2節2（2）
-サービス見込量 第1次概算</t>
+          <t>サービス見込量 第2次概算
+将来推計 第3段階
+計画素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1818,20 +1837,20 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G15" s="15" t="n">
-        <v>6</v>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>5</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>省令上の類型を計画に掲げないまま概算する</t>
+          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
         </is>
       </c>
     </row>
@@ -1840,18 +1859,18 @@
         <v>11</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
+          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第1次概算
+          <t>サービス見込量 第2次概算
 将来推計 第3段階
-計画素案 第6章第2節・第3節・第6節</t>
+計画素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1861,20 +1880,20 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G16" s="15" t="n">
-        <v>6</v>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="n">
+        <v>5</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）により、要介護度別の伸びで概算する</t>
+          <t>単価を令和7年度で固定する（安全側）。実績の趨勢を置いた場合の差は据え置きの一覧及び計画素案 第6章第6節2に示す</t>
         </is>
       </c>
     </row>
@@ -1883,17 +1902,18 @@
         <v>12</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
+          <t>令和22年度までの中長期推計をどこまで算定するか</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節2
-サービス見込量 第1次概算</t>
+          <t>サービス見込量 第2次概算
+将来推計 第3段階
+計画素案 第2章第8節・第6章第2節</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -1903,20 +1923,20 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G17" s="15" t="n">
-        <v>6</v>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>5</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節の表は当方の算定（令和7年度の実績に要介護度別の認定者数の伸びを乗じたもの）による値とし、見える化システムの自然体推計による値は第6節2に対比として掲げる</t>
+          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
         </is>
       </c>
     </row>
@@ -1925,41 +1945,40 @@
         <v>13</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
+          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第1次概算
-将来推計 第3段階
-計画素案 第6章第2節2</t>
+          <t>サービス見込量 第2次概算
+計画素案 第6章第2節・第4節</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G18" s="15" t="n">
-        <v>6</v>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="n">
+        <v>5</v>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節補正も行わないまま概算する</t>
+          <t>供給の制約（人材）を見込量に反映しない（需要のみで算定する）</t>
         </is>
       </c>
     </row>
@@ -1968,40 +1987,40 @@
         <v>14</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長するか</t>
+          <t>町別の人口の将来推計を計画本文に掲げるか</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第1次概算
-計画素案 第6章第4節4</t>
+          <t>サービス見込量 第2次概算
+計画素案 第2章第1節・第6章第1節</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G19" s="15" t="n">
-        <v>6</v>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G19" s="16" t="n">
+        <v>5</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長しないまま概算する</t>
+          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
         </is>
       </c>
     </row>
@@ -2010,17 +2029,17 @@
         <v>15</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>区域を越えた施設利用の扱い</t>
+          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第4節4
-サービス見込量 第1次概算</t>
+          <t>サービス見込量 第2次概算
+計画素案 第2章第1節・第6章第1節</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -2030,20 +2049,20 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G20" s="15" t="n">
-        <v>6</v>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G20" s="16" t="n">
+        <v>5</v>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
+          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
         </is>
       </c>
     </row>
@@ -2052,17 +2071,16 @@
         <v>16</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>146</v>
+        <v>7</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを要介護度別に改めてよいか</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第1次概算
-計画素案 第6章第2節</t>
+          <t>素案 第1章第6節・第3章第4節</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2075,17 +2093,17 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G21" s="15" t="n">
-        <v>6</v>
+      <c r="G21" s="16" t="n">
+        <v>4</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
+          <t>期限 超過（R8.9）（+2）／法定記載事項 法第117条に直結（+2）</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
+          <t>第9期の自己評価と北海道への報告の実績を確認できないものとして、第10期の進行管理に自己評価の仕組みを置く</t>
         </is>
       </c>
     </row>
@@ -2094,17 +2112,17 @@
         <v>17</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
+          <t>施策反映を行うか。行う場合の対象と歯止め</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第1次概算
-計画素案 第6章第2節</t>
+          <t>サービス見込量の算定
+計画素案 第4章第3節・第6章第2節</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -2117,17 +2135,17 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G22" s="15" t="n">
-        <v>6</v>
+      <c r="G22" s="16" t="n">
+        <v>4</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）／月額への効き 最大13円（施策の達成目標のご判断）（+1）</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
+          <t>施策反映を行わないまま概算する（安全側）</t>
         </is>
       </c>
     </row>
@@ -2136,41 +2154,40 @@
         <v>18</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案</t>
+          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階
-計画素案 第6章第6節
-サービス見込量 第2次概算</t>
+          <t>将来推計 第2段階
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G23" s="15" t="n">
-        <v>6</v>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="n">
+        <v>4</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）／月額への効き 最大47円（第7期給付適正化計画の目標のご判断）（+1）</t>
+          <t>期限 超過（R8.9）（+2）／月額への効き 最大327円（第10期の介護報酬改定率）（+4）／当方で動かせるか 国の告示・公布待ち（-2）</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>財政調整交付金の算定に給付適正化主要3事業の取組状況を勘案しないものとして算定する（調整交付金7.3755％のまま。安全側）</t>
+          <t>1人1月あたり給付費は令和7年度で固定して概算する（単価の趨勢を織り込まないことによる効きは計画素案 第6章第6節2に掲げる）</t>
         </is>
       </c>
     </row>
@@ -2179,17 +2196,18 @@
         <v>19</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>構成町の一般会計繰入金の町別按分の方法</t>
+          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第1次概算（R8.9.26）
-構成町の意見への回答 4</t>
+          <t>計画素案 第6章第6節
+将来推計 第3段階
+保険料算定式の国の様式との対照</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -2199,20 +2217,20 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>R8.9.24</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G24" s="16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9.24）（+2）／止めている成果物 概算（+3）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 保険料（+2）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>町別への按分は広域連合の規約によるものであり算定できないため、構成町の一般会計繰入金は3町計の概算のみを示す（按分の方法のご教示を受けた時点で町別までお示しする）</t>
+          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
         </is>
       </c>
     </row>
@@ -2221,17 +2239,17 @@
         <v>20</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
+          <t>給付適正化計画の位置づけ（案Bの採用）と毎年度の目標の記載場所</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階・第3段階
-サービス見込量 第1次概算</t>
+          <t>計画素案 第1章第2節・第5章 基本目標5・資料5
+給付適正化計画の位置づけと追加検討事項</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -2241,20 +2259,20 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G25" s="16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 概算（+3）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）／法定記載事項 法第117条に直結（+2）</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
+          <t>給付適正化計画の位置づけは案B（第9期と同じく施策として置き、施策名のかっこ書きで第7期給付適正化計画であることを示す）のままとする（令和8年9月10日 了承済み）</t>
         </is>
       </c>
     </row>
@@ -2263,17 +2281,17 @@
         <v>21</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計方式は基本推計でよいか</t>
+          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階
-サービス見込量 第1次概算</t>
+          <t>サービス見込量の算定
+計画素案 第5章 基本目標5・第6章第2節</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -2283,20 +2301,20 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G26" s="16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 概算（+3）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）／月額への効き 最大327円（第10期の介護報酬改定率）（+4）／当方で動かせるか 国の告示・公布待ち（-2）</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>基本推計に近いP3で概算する</t>
+          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
         </is>
       </c>
     </row>
@@ -2305,39 +2323,40 @@
         <v>22</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>130</v>
+        <v>33</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法第13条の市町村認知症施策推進計画をどう扱うか</t>
+          <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第2節・第5章 基本目標2</t>
+          <t>第10期の段階設計
+保険料の算定</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>国の情報</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>告示後</t>
         </is>
       </c>
       <c r="G27" s="16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）／法定記載事項 法第117条に直結（+2）</t>
+          <t>止めている成果物 保険料（+2）／月額への効き 最大290円（第10期の政令）（+4）／当方で動かせるか 国の告示・公布待ち（-2）</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>案B（3町がそれぞれ市町村計画を策定する）のまま素案に反映する</t>
+          <t>第9期条例の16段階・乗率（公費軽減前）を据え置いて算定し、政令の公布後に再算定する</t>
         </is>
       </c>
     </row>
@@ -2346,17 +2365,18 @@
         <v>23</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>132</v>
+        <v>39</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
+          <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階
-サービス見込量 第1次概算</t>
+          <t>計画骨子案
+施策体系新旧対照表
+計画素案 第4章・第5章</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -2366,20 +2386,20 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.9.2</t>
         </is>
       </c>
       <c r="G28" s="16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 概算（+3）</t>
+          <t>期限 超過（R8.9.2）（+2）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
+          <t>中間報告・施策体系新旧対照表・骨子案は提出した内容のままとする</t>
         </is>
       </c>
     </row>
@@ -2388,21 +2408,22 @@
         <v>24</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>142</v>
+        <v>40</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第1次概算を既定値のまま出してよいか</t>
+          <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第1次概算</t>
+          <t>従業員数の重複計上の整理
+計画素案 第2章第3節・第6章第2節</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2411,16 +2432,16 @@
         </is>
       </c>
       <c r="G29" s="16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 概算（+3）</t>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
+          <t>同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
         </is>
       </c>
     </row>
@@ -2429,17 +2450,17 @@
         <v>25</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>145</v>
+        <v>43</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
+          <t>認定に要する日数の扱い</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>町別データシート
-サービス見込量 第1次概算</t>
+          <t>中間報告 第3節
+計画素案 第2章・第5章</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2453,16 +2474,16 @@
         </is>
       </c>
       <c r="G30" s="16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 概算（+3）</t>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
+          <t>令和8年8月28日受領の集計帳票による</t>
         </is>
       </c>
     </row>
@@ -2471,17 +2492,17 @@
         <v>26</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>147</v>
+        <v>45</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの伸びの選択肢をどれとするか</t>
+          <t>代表KPI H15の分母の定義</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力
-サービス見込量 第1次概算</t>
+          <t>計画素案 第4章 資料1
+中間報告 第3節</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -2495,16 +2516,16 @@
         </is>
       </c>
       <c r="G31" s="16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 概算（+3）</t>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>代表KPI H15の分母は標準給付費見込額とする（受託者案）</t>
         </is>
       </c>
     </row>
@@ -2513,41 +2534,40 @@
         <v>27</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>東川町の施設整備・サービス提供方針</t>
+          <t>計画値を0としたサービスに実績がある2件</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算
-計画素案 第2章第2節・第6章第2節・第4節
-構成町の意見への回答 6</t>
+          <t>見える化総括表の受領点検 02シート
+計画素案 第4章</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>発注者・東川町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G32" s="16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残す</t>
+          <t>第10期は計画値を0とせず、算定値を置く（対計画比が算出され評価の対象となるようにする）</t>
         </is>
       </c>
     </row>
@@ -2556,18 +2576,17 @@
         <v>28</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
+          <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算
-将来推計 第3段階
-計画素案 第6章第3節・第6節</t>
+          <t>見える化総括表の受領点検 02シート
+計画素案 第4章</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -2577,20 +2596,20 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G33" s="16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
+          <t>定期巡回・随時対応型訪問介護看護は自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
         </is>
       </c>
     </row>
@@ -2599,18 +2618,18 @@
         <v>29</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
+          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算
-将来推計 第3段階
-計画素案 第6章第3節・第6節</t>
+          <t>人口推計の基礎の変更_総合戦略ベース
+将来推計 第1〜3段階
+計画素案 第2章第1節・第6章</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2620,20 +2639,20 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G34" s="16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。実績の趨勢を置いた場合の差は据え置きの一覧及び計画素案 第6章第6節2に示す</t>
+          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
         </is>
       </c>
     </row>
@@ -2642,18 +2661,18 @@
         <v>30</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>令和22年度までの中長期推計をどこまで算定するか</t>
+          <t>広域連合において行うべき事業の優先順位</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算
-将来推計 第3段階
-計画素案 第2章第8節・第6章第2節</t>
+          <t>広域連合において行うべき事業の優先順位
+介護高齢者福祉サービスガイド_構成案
+計画素案 第5章・第6章第3節2</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -2663,20 +2682,20 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G35" s="16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
+          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
         </is>
       </c>
     </row>
@@ -2685,40 +2704,41 @@
         <v>31</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
+          <t>サービスガイドに掲載する事業所の範囲</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算
-計画素案 第6章第2節・第4節</t>
+          <t>介護高齢者福祉サービスガイド_構成案
+3町の社会資源一覧との突合 06シート
+計画素案 第2章第3節</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G36" s="16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>供給の制約（人材）を見込量に反映しない（需要のみで算定する）</t>
+          <t>サービスガイドに掲載する事業所の範囲は北海道の指定事業所一覧（最新のもの）による</t>
         </is>
       </c>
     </row>
@@ -2727,17 +2747,18 @@
         <v>32</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>152</v>
+        <v>67</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>町別の人口の将来推計を計画本文に掲げるか</t>
+          <t>算定方法の国の様式との整合（点検結果）</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算
-計画素案 第2章第1節・第6章第1節</t>
+          <t>算定方法の整合確認（国と見える化）
+将来推計 第2段階・第3段階
+計画素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2747,20 +2768,20 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G37" s="16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
+          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
         </is>
       </c>
     </row>
@@ -2769,17 +2790,18 @@
         <v>33</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>153</v>
+        <v>68</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
+          <t>見える化システムの自然体推計の再出力のお願い</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算
-計画素案 第2章第1節・第6章第1節</t>
+          <t>将来推計 第3段階 01シート
+算定方法の整合確認 04シート・07シート
+計画素案 第6章第3節</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -2789,20 +2811,20 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G38" s="16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
+          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
         </is>
       </c>
     </row>
@@ -2811,16 +2833,18 @@
         <v>34</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>交付金の全国順位の計画本文への掲載</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第6節・第3章第4節</t>
+          <t>計画素案 第4章第4節
+図表集 27シート
+交付金評価指標と全国集計の受領点検 04シート</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -2834,16 +2858,16 @@
         </is>
       </c>
       <c r="G39" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／法定記載事項 法第117条に直結（+2）</t>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績を確認できないものとして、第10期の進行管理に自己評価の仕組みを置く</t>
+          <t>交付金の全国順位は計画本文に掲載せず、策定委員会資料にとどめる（確認事項No.71のとおり）</t>
         </is>
       </c>
     </row>
@@ -2852,41 +2876,40 @@
         <v>35</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
+          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第6節
-将来推計 第3段階
-保険料算定式の国の様式との対照</t>
+          <t>ケアプラン点検実施要領（案）
+計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G40" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 保険料（+2）／止めている成果物 計画素案（+1）</t>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
+          <t>ケアプラン点検実施要領（案）は協議資料にとどめ素案に入れない</t>
         </is>
       </c>
     </row>
@@ -2895,735 +2918,14 @@
         <v>36</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけ（案Bの採用）と毎年度の目標の記載場所</t>
+          <t>代表KPIと改善事項の再整理案</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>計画素案 第1章第2節・第5章 基本目標5・資料5
-給付適正化計画の位置づけと追加検討事項</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G41" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）／法定記載事項 法第117条に直結（+2）</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>給付適正化計画の位置づけは案B（第9期と同じく施策として置き、施策名のかっこ書きで第7期給付適正化計画であることを示す）のままとする（令和8年9月10日 了承済み）</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="48" customHeight="1">
-      <c r="A42" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="n">
-        <v>128</v>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>令和8年度の実績見込み値を編集するか</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>将来推計 第2段階
-サービス見込量 第1次概算</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G42" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）</t>
-        </is>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="48" customHeight="1">
-      <c r="A43" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="n">
-        <v>129</v>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>見える化システムの利用率等の伸びの選択</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>将来推計 第2段階
-サービス見込量 第1次概算</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G43" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）</t>
-        </is>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="48" customHeight="1">
-      <c r="A44" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>第10期の政令改正の内容（所得段階）</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>第10期の段階設計
-保険料の算定</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>国の情報</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>告示後</t>
-        </is>
-      </c>
-      <c r="G44" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="H44" s="6" t="inlineStr">
-        <is>
-          <t>止めている成果物 保険料（+2）／月額への効き 最大290円（第10期の政令）（+4）／当方で動かせるか 国の告示・公布待ち（-2）</t>
-        </is>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>第9期条例の16段階・乗率（公費軽減前）を据え置いて算定し、政令の公布後に再算定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="48" customHeight="1">
-      <c r="A45" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>計画骨子案
-施策体系新旧対照表
-計画素案 第4章・第5章</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>R8.9.2</t>
-        </is>
-      </c>
-      <c r="G45" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>期限 超過（R8.9.2）（+2）／止めている成果物 計画素案（+1）</t>
-        </is>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>中間報告・施策体系新旧対照表・骨子案は提出した内容のままとする</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="48" customHeight="1">
-      <c r="A46" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>社会資源一覧の従業員数の重複計上の扱い</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>従業員数の重複計上の整理
-計画素案 第2章第3節・第6章第2節</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G46" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
-        </is>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="48" customHeight="1">
-      <c r="A47" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="B47" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>認定に要する日数の扱い</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>中間報告 第3節
-計画素案 第2章・第5章</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G47" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
-        </is>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>令和8年8月28日受領の集計帳票による</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="48" customHeight="1">
-      <c r="A48" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="B48" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>代表KPI H15の分母の定義</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>計画素案 第4章 資料1
-中間報告 第3節</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G48" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
-        </is>
-      </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>代表KPI H15の分母は標準給付費見込額とする（受託者案）</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="48" customHeight="1">
-      <c r="A49" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="B49" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>計画値を0としたサービスに実績がある2件</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>見える化総括表の受領点検 02シート
-計画素案 第4章</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G49" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
-        </is>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>第10期は計画値を0とせず、算定値を置く（対計画比が算出され評価の対象となるようにする）</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="48" customHeight="1">
-      <c r="A50" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="B50" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>見える化総括表の受領点検 02シート
-計画素案 第4章</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G50" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
-        </is>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>定期巡回・随時対応型訪問介護看護は自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="48" customHeight="1">
-      <c r="A51" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>人口推計の基礎の変更_総合戦略ベース
-将来推計 第1〜3段階
-計画素案 第2章第1節・第6章</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G51" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
-        </is>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="48" customHeight="1">
-      <c r="A52" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="B52" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>広域連合において行うべき事業の優先順位</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>広域連合において行うべき事業の優先順位
-介護高齢者福祉サービスガイド_構成案
-計画素案 第5章・第6章第3節2</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G52" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
-        </is>
-      </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="48" customHeight="1">
-      <c r="A53" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>サービスガイドに掲載する事業所の範囲</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>介護高齢者福祉サービスガイド_構成案
-3町の社会資源一覧との突合 06シート
-計画素案 第2章第3節</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G53" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>サービスガイドに掲載する事業所の範囲は北海道の指定事業所一覧（最新のもの）による</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="48" customHeight="1">
-      <c r="A54" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>67</v>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>算定方法の国の様式との整合（点検結果）</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>算定方法の整合確認（国と見える化）
-将来推計 第2段階・第3段階
-計画素案 第6章第3節・第6節</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G54" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H54" s="6" t="inlineStr">
-        <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
-        </is>
-      </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="48" customHeight="1">
-      <c r="A55" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B55" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>見える化システムの自然体推計の再出力のお願い</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>将来推計 第3段階 01シート
-算定方法の整合確認 04シート・07シート
-計画素案 第6章第3節</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G55" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="48" customHeight="1">
-      <c r="A56" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="B56" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>交付金の全国順位の計画本文への掲載</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>計画素案 第4章第4節
-図表集 27シート
-交付金評価指標と全国集計の受領点検 04シート</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G56" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
-        </is>
-      </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>交付金の全国順位は計画本文に掲載せず、策定委員会資料にとどめる（確認事項No.71のとおり）</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="48" customHeight="1">
-      <c r="A57" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="B57" s="5" t="n">
-        <v>73</v>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>ケアプラン点検実施要領（案）
-計画素案 第5章 基本目標5</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G57" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
-        </is>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>ケアプラン点検実施要領（案）は協議資料にとどめ素案に入れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="48" customHeight="1">
-      <c r="A58" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="B58" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>代表KPIと改善事項の再整理案</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
         <is>
           <t>計画素案 第4章第3節・第5章・資料1
 骨子案 第4節
@@ -3631,6 +2933,724 @@
 代表KPIの振替案と確認事項の精査</t>
         </is>
       </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G41" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>代表KPIと改善事項は当方の再整理案のままとする</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="48" customHeight="1">
+      <c r="A42" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>介護リームスから抽出できる項目</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第4章第3節・資料1
+図表集31シート</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G42" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>介護リームスから抽出できないものとして、代表KPI H03は未算定のままとする</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="48" customHeight="1">
+      <c r="A43" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>北海道の評価指標⑥の団体別の公表値</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第4章第3節・資料1
+内部確認結果への対応整理 04</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G43" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>北海道の評価指標⑥の団体別の公表値を引用できないものとして、当該指標は計画本文に掲げない</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="48" customHeight="1">
+      <c r="A44" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>グループホームびえいの郷の定員減の時期</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第2章第3節・第6章第2節
+将来推計 第2・第3段階</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>発注者・美瑛町</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G44" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>北海道の名簿の定員のまま概算する</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="48" customHeight="1">
+      <c r="A45" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>第5章の施策数の見直しの範囲</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第5章
+骨子案 第5節</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G45" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>第9期の19施策の体系を維持する（施策数を見直さない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="48" customHeight="1">
+      <c r="A46" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>81</v>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>代表KPI H16のデータ源（国保連の給付実績の明細情報）</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第4章第3節・第5章 基本目標5・資料1
+給付実績データの受領点検 05
+内部確認結果への対応整理 04・09</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G46" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>国保連の給付実績の明細を受領できないものとして、代表KPI H16は地域密着型サービスに限った確認件数を代理指標とする</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="48" customHeight="1">
+      <c r="A47" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>地域密着型サービス基準省令の論点整理
+計画素案 第6章第4節</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G47" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="48" customHeight="1">
+      <c r="A48" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第2章第3節6
+計画素案 第6章第4節4
+地域密着型サービス基準省令の論点整理</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G48" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="48" customHeight="1">
+      <c r="A49" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第6章第4節1
+計画素案 第6章第2節2（2）
+サービス見込量の算定</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G49" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>省令上の類型を計画に掲げないまま概算する</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="48" customHeight="1">
+      <c r="A50" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量の算定
+将来推計 第3段階
+計画素案 第6章第2節・第3節・第6節</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G50" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）により、要介護度別の伸びで概算する</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="48" customHeight="1">
+      <c r="A51" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>101</v>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第6章第2節2
+サービス見込量の算定</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G51" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第6章第2節の表は当方の算定（令和7年度の実績に要介護度別の認定者数の伸びを乗じたもの）による値とし、見える化システムの自然体推計による値は第6節2に対比として掲げる</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="48" customHeight="1">
+      <c r="A52" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>102</v>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量の算定
+計画素案 第6章第2節2</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G52" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="48" customHeight="1">
+      <c r="A53" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>103</v>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量の算定
+将来推計 第3段階
+計画素案 第6章第2節2</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G53" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度を基準年度に用いず、季節補正も行わないまま概算する</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="48" customHeight="1">
+      <c r="A54" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>107</v>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>施設・居住系の実績の減少を将来へ延長するか</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量の算定
+計画素案 第6章第4節4</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G54" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>施設・居住系の実績の減少を将来へ延長しないまま概算する</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="48" customHeight="1">
+      <c r="A55" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>122</v>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>地域ケア会議関係資料の取扱いの確認</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>地域ケア会議の受領点検とKPI設計案
+計画素案 第5章 基本目標2</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G55" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>転載を禁ずる旨の記載がある2件は成果品に用いず、原典（厚労省の市町村マニュアル及び別冊事例集）のみを引く</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="48" customHeight="1">
+      <c r="A56" s="5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>124</v>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>将来推計 第2段階
+計画素案 第6章第2節・第4節</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G56" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="48" customHeight="1">
+      <c r="A57" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第2章第4節・第4章第3節</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G57" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>在宅生活改善調査の結果は「在宅で困難を抱える方の状況」として引き、在宅の認定者全体の割合としては引かない</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="48" customHeight="1">
+      <c r="A58" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>141</v>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>区域を越えた施設利用の扱い</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第6章第4節4
+サービス見込量の算定</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
@@ -3651,7 +3671,7 @@
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>代表KPIと改善事項は当方の再整理案のままとする</t>
+          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
         </is>
       </c>
     </row>
@@ -3660,17 +3680,17 @@
         <v>54</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>76</v>
+        <v>146</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>介護リームスから抽出できる項目</t>
+          <t>見込量の伸びを要介護度別に改めてよいか</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・資料1
-図表集31シート</t>
+          <t>サービス見込量の算定
+計画素案 第6章第2節</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -3693,7 +3713,7 @@
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>介護リームスから抽出できないものとして、代表KPI H03は未算定のままとする</t>
+          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
         </is>
       </c>
     </row>
@@ -3702,22 +3722,22 @@
         <v>55</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>77</v>
+        <v>149</v>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥の団体別の公表値</t>
+          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・資料1
-内部確認結果への対応整理 04</t>
+          <t>計画素案 第1章第2節・第5章 基本目標2
+認知症施策推進計画の位置づけと見込量への反映</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
@@ -3735,7 +3755,7 @@
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥の団体別の公表値を引用できないものとして、当該指標は計画本文に掲げない</t>
+          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
         </is>
       </c>
     </row>
@@ -3744,22 +3764,22 @@
         <v>56</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>グループホームびえいの郷の定員減の時期</t>
+          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第3節・第6章第2節
-将来推計 第2・第3段階</t>
+          <t>サービス見込量の算定
+計画素案 第6章第2節</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>発注者・美瑛町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
@@ -3777,7 +3797,7 @@
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>北海道の名簿の定員のまま概算する</t>
+          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
         </is>
       </c>
     </row>
@@ -3786,17 +3806,17 @@
         <v>57</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>79</v>
+        <v>30</v>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第5章の施策数の見直しの範囲</t>
+          <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章
-骨子案 第5節</t>
+          <t>重度化の速度の前提
+保険料と施策評価の他団体比較 05シート</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -3806,7 +3826,7 @@
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G62" s="16" t="n">
@@ -3814,12 +3834,12 @@
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 保険料（+2）</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策の体系を維持する（施策数を見直さない）</t>
+          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
         </is>
       </c>
     </row>
@@ -3828,18 +3848,17 @@
         <v>58</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H16のデータ源（国保連の給付実績の明細情報）</t>
+          <t>第9段階の乗率の経緯</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・第5章 基本目標5・資料1
-給付実績データの受領点検 05
-内部確認結果への対応整理 04・09</t>
+          <t>第10期の段階設計
+保険料の所得段階と低所得者軽減の検証 08シート</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -3849,7 +3868,7 @@
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G63" s="16" t="n">
@@ -3857,12 +3876,12 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 保険料（+2）</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>国保連の給付実績の明細を受領できないものとして、代表KPI H16は地域密着型サービスに限った確認件数を代理指標とする</t>
+          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
         </is>
       </c>
     </row>
@@ -3871,27 +3890,26 @@
         <v>59</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
+          <t>上川管内の保険者の所得段階数と乗率</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>地域密着型サービス基準省令の論点整理
-計画素案 第6章第4節</t>
+          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G64" s="16" t="n">
@@ -3899,12 +3917,12 @@
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 保険料（+2）</t>
         </is>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
+          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
         </is>
       </c>
     </row>
@@ -3913,28 +3931,28 @@
         <v>60</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+          <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第3節6
-計画素案 第6章第4節4
-地域密着型サービス基準省令の論点整理</t>
+          <t>所得段階別被保険者数の推計
+保険料の算定
+素案 第6章第7節</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G65" s="16" t="n">
@@ -3942,12 +3960,12 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 保険料（+2）</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
+          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
         </is>
       </c>
     </row>
@@ -3956,27 +3974,27 @@
         <v>61</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
+          <t>令和9年4月に新設される区分を見込量に立てるか</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定
-計画素案 第6章第2節2</t>
+          <t>サービス見込量 第2次概算
+計画素案 第1章第9節・第6章第2節・第4節</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G66" s="16" t="n">
@@ -3984,12 +4002,12 @@
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）／当方で動かせるか 国の告示・公布待ち（-2）</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
+          <t>令和9年4月新設の3区分を0として立てる</t>
         </is>
       </c>
     </row>
@@ -3998,17 +4016,17 @@
         <v>62</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>122</v>
+        <v>4</v>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議関係資料の取扱いの確認</t>
+          <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の受領点検とKPI設計案
-計画素案 第5章 基本目標2</t>
+          <t>素案 第4章第3節・資料1
+全16KPIの4項目</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -4018,20 +4036,20 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G67" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+          <t>期限 超過（R8.8）（+2）</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>転載を禁ずる旨の記載がある2件は成果品に用いず、原典（厚労省の市町村マニュアル及び別冊事例集）のみを引く</t>
+          <t>代表KPI H07・H08・H12・H16は代理指標への振替案のとおりとする</t>
         </is>
       </c>
     </row>
@@ -4040,17 +4058,17 @@
         <v>63</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>124</v>
+        <v>5</v>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
+          <t>第9期の施策・事業実績</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階
-計画素案 第6章第2節・第4節</t>
+          <t>素案 第3章第2節・第3節・第5節
+妥当性検証報告書 12シート</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -4060,20 +4078,20 @@
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G68" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+          <t>期限 超過（R8.8）（+2）</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
+          <t>第9期の施策・事業実績を受領できないものとして、公表資料（交付金の評価結果・総合事業の実施状況に関する調査・年報）により評価する</t>
         </is>
       </c>
     </row>
@@ -4082,16 +4100,17 @@
         <v>64</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>140</v>
+        <v>8</v>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
+          <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第4節・第4章第3節</t>
+          <t>素案 第2章第5・6節
+H06・H11・H13・H14の基準値</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -4101,20 +4120,20 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G69" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+          <t>期限 超過（R8.8）（+2）</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果は「在宅で困難を抱える方の状況」として引き、在宅の認定者全体の割合としては引かない</t>
+          <t>3調査の点検事項は当方の判定のままとする</t>
         </is>
       </c>
     </row>
@@ -4123,17 +4142,17 @@
         <v>65</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>149</v>
+        <v>19</v>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
+          <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第2節・第5章 基本目標2
-認知症施策推進計画の位置づけと見込量への反映</t>
+          <t>委員会資料原案
+パブリックコメント資料</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -4143,20 +4162,20 @@
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G70" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+          <t>期限 超過（R8.8）（+2）</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
+          <t>会議日程及びパブリックコメントの期間は仕様書５の工程による</t>
         </is>
       </c>
     </row>
@@ -4165,40 +4184,39 @@
         <v>66</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けた要介護度の変化</t>
+          <t>キックオフ会議資料への工程表の反映</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提
-保険料と施策評価の他団体比較 05シート</t>
+          <t>キックオフ会議資料</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G71" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 保険料（+2）</t>
+          <t>期限 超過（R8.8）（+2）</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
+          <t>現行の工程表のまま進める</t>
         </is>
       </c>
     </row>
@@ -4207,40 +4225,40 @@
         <v>67</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率の経緯</t>
+          <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>第10期の段階設計
-保険料の所得段階と低所得者軽減の検証 08シート</t>
+          <t>素案 第1章第9節
+追加調査報告書 01シート</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G72" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 保険料（+2）</t>
+          <t>期限 超過（R8.9）（+2）</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
+          <t>告示を確認できないものとして、特別地域加算の判定を計画素案に書かず［要確認］のまま残す</t>
         </is>
       </c>
     </row>
@@ -4249,39 +4267,40 @@
         <v>68</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
+          <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
+          <t>素案 第2章第2節
+分析資料</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G73" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 保険料（+2）</t>
+          <t>期限 超過（R8.9）（+2）</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
+          <t>類似保険者との比較は公表されている同規模保険者40団体による</t>
         </is>
       </c>
     </row>
@@ -4290,18 +4309,17 @@
         <v>69</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績と収納率</t>
+          <t>交付金の評価調書</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の推計
-保険料の算定
-素案 第6章第7節</t>
+          <t>素案 第3章第4節
+追加調査報告書 02シート</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -4311,20 +4329,20 @@
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G74" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 保険料（+2）</t>
+          <t>期限 超過（R8.9）（+2）</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
+          <t>評価調書を受領できないものとして、得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できない旨を注記する</t>
         </is>
       </c>
     </row>
@@ -4333,40 +4351,40 @@
         <v>70</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>115</v>
+        <v>9</v>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+          <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算
-計画素案 第1章第9節・第6章第2節・第4節</t>
+          <t>素案 第2章第4〜6節
+クロス集計表</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G75" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）／当方で動かせるか 国の告示・公布待ち（-2）</t>
+          <t>期限 超過（R8.9）（+2）</t>
         </is>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月新設の3区分を0として立てる</t>
+          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
         </is>
       </c>
     </row>
@@ -4375,17 +4393,17 @@
         <v>71</v>
       </c>
       <c r="B76" s="5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16の代理指標</t>
+          <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>素案 第4章第3節・資料1
-全16KPIの4項目</t>
+          <t>素案 第4章第3節
+H14の基準値</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -4395,7 +4413,7 @@
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G76" s="16" t="n">
@@ -4403,12 +4421,12 @@
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.8）（+2）</t>
+          <t>期限 超過（R8.9）（+2）</t>
         </is>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16は代理指標への振替案のとおりとする</t>
+          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
         </is>
       </c>
     </row>
@@ -4417,27 +4435,27 @@
         <v>72</v>
       </c>
       <c r="B77" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績</t>
+          <t>町別の人口・世帯データ</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>素案 第3章第2節・第3節・第5節
-妥当性検証報告書 12シート</t>
+          <t>素案 第2章第1節
+図1・図2・図3</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G77" s="16" t="n">
@@ -4445,12 +4463,12 @@
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.8）（+2）</t>
+          <t>期限 超過（R8.9）（+2）</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績を受領できないものとして、公表資料（交付金の評価結果・総合事業の実施状況に関する調査・年報）により評価する</t>
+          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
         </is>
       </c>
     </row>
@@ -4459,27 +4477,28 @@
         <v>73</v>
       </c>
       <c r="B78" s="5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項の取扱い</t>
+          <t>日常生活圏域別のデータ</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第5・6節
-H06・H11・H13・H14の基準値</t>
+          <t>素案 第1章第7節・第2章
+圏域別分析資料
+調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G78" s="16" t="n">
@@ -4487,12 +4506,12 @@
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.8）（+2）</t>
+          <t>期限 超過（R8.9）（+2）</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項は当方の判定のままとする</t>
+          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
         </is>
       </c>
     </row>
@@ -4501,17 +4520,17 @@
         <v>74</v>
       </c>
       <c r="B79" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>会議日程とパブリックコメントの期間</t>
+          <t>骨子案の内容の確認</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>委員会資料原案
-パブリックコメント資料</t>
+          <t>骨子案
+素案の次稿</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
@@ -4521,7 +4540,7 @@
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G79" s="16" t="n">
@@ -4529,12 +4548,12 @@
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.8）（+2）</t>
+          <t>期限 超過（R8.9）（+2）</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>会議日程及びパブリックコメントの期間は仕様書５の工程による</t>
+          <t>骨子案は提出した内容のままとする</t>
         </is>
       </c>
     </row>
@@ -4543,26 +4562,27 @@
         <v>75</v>
       </c>
       <c r="B80" s="5" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料への工程表の反映</t>
+          <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料</t>
+          <t>素案 第1章第6節
+追加調査報告書 04シート</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G80" s="16" t="n">
@@ -4570,12 +4590,12 @@
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.8）（+2）</t>
+          <t>期限 超過（R8.9）（+2）</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>現行の工程表のまま進める</t>
+          <t>北海道の評価指標の読替えは当方の案のままとする</t>
         </is>
       </c>
     </row>
@@ -4584,22 +4604,22 @@
         <v>76</v>
       </c>
       <c r="B81" s="5" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>特別地域加算の対象地域告示</t>
+          <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第9節
-追加調査報告書 01シート</t>
+          <t>調査クロス集計・分析 14シート
+素案 第2章第4節</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
@@ -4617,7 +4637,7 @@
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>告示を確認できないものとして、特別地域加算の判定を計画素案に書かず［要確認］のまま残す</t>
+          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
         </is>
       </c>
     </row>
@@ -4626,17 +4646,17 @@
         <v>77</v>
       </c>
       <c r="B82" s="5" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較分析の対象</t>
+          <t>調査対象者の範囲の確認</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第2節
-分析資料</t>
+          <t>調査クロス集計・分析 13・14シート
+H06・H11の基準値</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -4659,7 +4679,7 @@
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較は公表されている同規模保険者40団体による</t>
+          <t>現に収録している調査対象者の範囲による</t>
         </is>
       </c>
     </row>
@@ -4668,17 +4688,17 @@
         <v>78</v>
       </c>
       <c r="B83" s="5" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価調書</t>
+          <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
           <t>素案 第3章第4節
-追加調査報告書 02シート</t>
+妥当性検証 所見18・19</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -4701,7 +4721,7 @@
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>評価調書を受領できないものとして、得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できない旨を注記する</t>
+          <t>公表されている全国集計の値による</t>
         </is>
       </c>
     </row>
@@ -4710,17 +4730,17 @@
         <v>79</v>
       </c>
       <c r="B84" s="5" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>調査の対象者範囲と回収率</t>
+          <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第4〜6節
-クロス集計表</t>
+          <t>給付実績データの受領点検
+将来推計 第2・3段階</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -4743,7 +4763,7 @@
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
-          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
+          <t>令和8年9月25日の再提供により決着済み。再提供を受けたファイルの値（3町合計と円単位一致）による</t>
         </is>
       </c>
     </row>
@@ -4752,17 +4772,17 @@
         <v>80</v>
       </c>
       <c r="B85" s="5" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>介護人材実態調査の採用者数・退職者数</t>
+          <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>素案 第4章第3節
-H14の基準値</t>
+          <t>給付実績データの受領点検 04シート
+将来推計 第3段階</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -4785,7 +4805,7 @@
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
-          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
+          <t>総括表（保険者単位）を用い、計画作成支援ツールの実績値シートは比較のためにのみ用いる</t>
         </is>
       </c>
     </row>
@@ -4794,22 +4814,23 @@
         <v>81</v>
       </c>
       <c r="B86" s="5" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>町別の人口・世帯データ</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第1節
-図1・図2・図3</t>
+          <t>総合事業実施状況調査の受領点検
+素案 第3章第1節・第2節
+H05の基準値</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
@@ -4827,7 +4848,7 @@
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
+          <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値による</t>
         </is>
       </c>
     </row>
@@ -4836,23 +4857,23 @@
         <v>82</v>
       </c>
       <c r="B87" s="5" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域別のデータ</t>
+          <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第7節・第2章
-圏域別分析資料
-調査クロス集計・分析 01・18シート</t>
+          <t>年報月報の受領点検
+将来推計 第3段階
+素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
@@ -4870,7 +4891,7 @@
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
+          <t>受領済みの年報・月報の値による</t>
         </is>
       </c>
     </row>
@@ -4879,17 +4900,16 @@
         <v>83</v>
       </c>
       <c r="B88" s="5" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>骨子案の内容の確認</t>
+          <t>月報の値の接続のずれ（ご報告）</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>骨子案
-素案の次稿</t>
+          <t>年報月報の受領点検 04シート</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -4912,7 +4932,7 @@
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
-          <t>骨子案は提出した内容のままとする</t>
+          <t>月報の値の接続のずれは記録として残し、計画本文には用いない</t>
         </is>
       </c>
     </row>
@@ -4921,22 +4941,22 @@
         <v>84</v>
       </c>
       <c r="B89" s="5" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標の読替えの考え方</t>
+          <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第6節
-追加調査報告書 04シート</t>
+          <t>令和6年度決算書の受領点検 03シート
+素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
@@ -4954,7 +4974,7 @@
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標の読替えは当方の案のままとする</t>
+          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
         </is>
       </c>
     </row>
@@ -4963,17 +4983,18 @@
         <v>85</v>
       </c>
       <c r="B90" s="5" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>令和4年度 健康とくらしの調査の集計表</t>
+          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析 14シート
-素案 第2章第4節</t>
+          <t>基金条例の確認 02シート
+素案 第6章第6節
+将来推計 第3段階</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -4996,7 +5017,7 @@
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
-          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
+          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合は1億円あたり月額約▲310円となることを併記する</t>
         </is>
       </c>
     </row>
@@ -5005,17 +5026,17 @@
         <v>86</v>
       </c>
       <c r="B91" s="5" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>調査対象者の範囲の確認</t>
+          <t>議事録の文書プロパティに個人名が再度入る</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析 13・14シート
-H06・H11の基準値</t>
+          <t>中間報告会議議事録
+業務工程管理表</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -5038,7 +5059,7 @@
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
-          <t>現に収録している調査対象者の範囲による</t>
+          <t>議事録は作成者名を落として再出力する（当方で対応する）</t>
         </is>
       </c>
     </row>
@@ -5047,17 +5068,17 @@
         <v>87</v>
       </c>
       <c r="B92" s="5" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の令和6年・令和7年調査の結果</t>
+          <t>議事録の表記に関するご提案3件</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>素案 第3章第4節
-妥当性検証 所見18・19</t>
+          <t>中間報告会議議事録
+業務工程管理表</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -5080,7 +5101,7 @@
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
-          <t>公表されている全国集計の値による</t>
+          <t>議事録の表記はご提案3件のとおり改める</t>
         </is>
       </c>
     </row>
@@ -5089,17 +5110,16 @@
         <v>88</v>
       </c>
       <c r="B93" s="5" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の給付費の集計が一致しない</t>
+          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>給付実績データの受領点検
-将来推計 第2・3段階</t>
+          <t>見える化総括表の受領点検 00シート</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -5122,7 +5142,7 @@
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月25日の再提供により決着済み。再提供を受けたファイルの値（3町合計と円単位一致）による</t>
+          <t>他団体の集計帳票6件は成果品に用いない</t>
         </is>
       </c>
     </row>
@@ -5131,17 +5151,16 @@
         <v>89</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの実績値シートの確認</t>
+          <t>調整交付金の算定基礎の確認</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>給付実績データの受領点検 04シート
-将来推計 第3段階</t>
+          <t>将来推計 第3段階 00・03シート</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -5164,7 +5183,7 @@
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
-          <t>総括表（保険者単位）を用い、計画作成支援ツールの実績値シートは比較のためにのみ用いる</t>
+          <t>現行の扱い（第9期の算定を再現し公表値6,428円と一致する扱い）による</t>
         </is>
       </c>
     </row>
@@ -5173,18 +5192,16 @@
         <v>90</v>
       </c>
       <c r="B95" s="5" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
+          <t>交付金の評価項目と19施策の割当て</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>総合事業実施状況調査の受領点検
-素案 第3章第1節・第2節
-H05の基準値</t>
+          <t>第9期施策別評価表 06シート</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -5207,7 +5224,7 @@
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
-          <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値による</t>
+          <t>交付金の評価項目と19施策の割当ては当方の案のままとする</t>
         </is>
       </c>
     </row>
@@ -5216,18 +5233,17 @@
         <v>91</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>年報・月報の受領に伴う確認</t>
+          <t>職員個票のリストによる重複確認の可否</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>年報月報の受領点検
-将来推計 第3段階
-素案 第6章第3節・第6節</t>
+          <t>内部確認結果への対応整理 03・08
+実施済み3調査の受領点検と集計 06・07</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -5250,7 +5266,7 @@
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
-          <t>受領済みの年報・月報の値による</t>
+          <t>職員個票を突き合わせず、事業所への照会により重複を判別する</t>
         </is>
       </c>
     </row>
@@ -5259,16 +5275,17 @@
         <v>92</v>
       </c>
       <c r="B97" s="5" t="n">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれ（ご報告）</t>
+          <t>構成町の一般会計繰入金の町別按分の方法</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>年報月報の受領点検 04シート</t>
+          <t>サービス見込量の算定（R8.9.26）
+構成町の意見への回答 4</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -5278,7 +5295,7 @@
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.9.24</t>
         </is>
       </c>
       <c r="G97" s="16" t="n">
@@ -5286,12 +5303,12 @@
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）</t>
+          <t>期限 超過（R8.9.24）（+2）</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれは記録として残し、計画本文には用いない</t>
+          <t>町別への按分は広域連合の規約によるものであり算定できないため、構成町の一般会計繰入金は3町計の概算のみを示す（按分の方法のご教示を受けた時点で町別までお示しする）</t>
         </is>
       </c>
     </row>
@@ -5300,22 +5317,23 @@
         <v>93</v>
       </c>
       <c r="B98" s="5" t="n">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領に伴う確認</t>
+          <t>構成町との意見交換会の実施方法と町別データシート</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領点検 03シート
-素案 第6章第3節・第6節</t>
+          <t>意見交換会資料
+町別データシート
+構成町の意見への回答 2・3</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
@@ -5333,7 +5351,7 @@
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
-          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
+          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで進める</t>
         </is>
       </c>
     </row>
@@ -5342,23 +5360,22 @@
         <v>94</v>
       </c>
       <c r="B99" s="5" t="n">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
+          <t>町別データシートの内容と配付</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>基金条例の確認 02シート
-素案 第6章第6節
-将来推計 第3段階</t>
+          <t>町別データシート
+構成町の意見への回答 2</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
@@ -5376,7 +5393,7 @@
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合は1億円あたり月額約▲310円となることを併記する</t>
+          <t>町別データシートは現行の内容のまま配付する</t>
         </is>
       </c>
     </row>
@@ -5385,17 +5402,17 @@
         <v>95</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>議事録の文書プロパティに個人名が再度入る</t>
+          <t>成果品の統合の方針</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>中間報告会議議事録
-業務工程管理表</t>
+          <t>成果品一覧
+送付資料一覧</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -5418,7 +5435,7 @@
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
-          <t>議事録は作成者名を落として再出力する（当方で対応する）</t>
+          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す（現行）</t>
         </is>
       </c>
     </row>
@@ -5427,17 +5444,17 @@
         <v>96</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記に関するご提案3件</t>
+          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>中間報告会議議事録
-業務工程管理表</t>
+          <t>将来推計 第2段階・第3段階
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -5460,7 +5477,7 @@
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記はご提案3件のとおり改める</t>
+          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
         </is>
       </c>
     </row>
@@ -5469,16 +5486,17 @@
         <v>97</v>
       </c>
       <c r="B102" s="5" t="n">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
+          <t>見える化システムの推計方式は基本推計でよいか</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>見える化総括表の受領点検 00シート</t>
+          <t>将来推計 第2段階
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -5501,7 +5519,7 @@
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
-          <t>他団体の集計帳票6件は成果品に用いない</t>
+          <t>基本推計に近いP3で概算する</t>
         </is>
       </c>
     </row>
@@ -5510,16 +5528,17 @@
         <v>98</v>
       </c>
       <c r="B103" s="5" t="n">
-        <v>59</v>
+        <v>132</v>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>調整交付金の算定基礎の確認</t>
+          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階 00・03シート</t>
+          <t>将来推計 第2段階
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -5542,7 +5561,7 @@
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
-          <t>現行の扱い（第9期の算定を再現し公表値6,428円と一致する扱い）による</t>
+          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
         </is>
       </c>
     </row>
@@ -5551,16 +5570,16 @@
         <v>99</v>
       </c>
       <c r="B104" s="5" t="n">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当て</t>
+          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>第9期施策別評価表 06シート</t>
+          <t>将来推計 第2段階</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -5583,7 +5602,7 @@
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当ては当方の案のままとする</t>
+          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ</t>
         </is>
       </c>
     </row>
@@ -5592,17 +5611,16 @@
         <v>100</v>
       </c>
       <c r="B105" s="5" t="n">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>職員個票のリストによる重複確認の可否</t>
+          <t>健康とくらしの調査の個票の再提供の要否</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>内部確認結果への対応整理 03・08
-実施済み3調査の受領点検と集計 06・07</t>
+          <t>調査クロス集計・分析の更新</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -5625,7 +5643,7 @@
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>職員個票を突き合わせず、事業所への照会により重複を判別する</t>
+          <t>健康とくらしの調査の個票の再提供を依頼しない（成果品は収録済みで内容が確定しており、現時点で不足がない）</t>
         </is>
       </c>
     </row>
@@ -5634,23 +5652,21 @@
         <v>101</v>
       </c>
       <c r="B106" s="5" t="n">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>構成町との意見交換会の実施方法と町別データシート</t>
+          <t>第1次概算を既定値のまま出してよいか</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>意見交換会資料
-町別データシート
-構成町の意見への回答 2・3</t>
+          <t>サービス見込量の算定</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
@@ -5668,7 +5684,7 @@
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
-          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで進める</t>
+          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
         </is>
       </c>
     </row>
@@ -5677,22 +5693,22 @@
         <v>102</v>
       </c>
       <c r="B107" s="5" t="n">
-        <v>85</v>
+        <v>145</v>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>町別データシートの内容と配付</t>
+          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
           <t>町別データシート
-構成町の意見への回答 2</t>
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
@@ -5710,7 +5726,7 @@
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
-          <t>町別データシートは現行の内容のまま配付する</t>
+          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
         </is>
       </c>
     </row>
@@ -5719,17 +5735,17 @@
         <v>103</v>
       </c>
       <c r="B108" s="5" t="n">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>成果品の統合の方針</t>
+          <t>見える化システムの伸びの選択肢をどれとするか</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>成果品一覧
-送付資料一覧</t>
+          <t>見える化システムへの入力
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -5752,7 +5768,7 @@
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
-          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す（現行）</t>
+          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
         </is>
       </c>
     </row>
@@ -5761,16 +5777,17 @@
         <v>104</v>
       </c>
       <c r="B109" s="5" t="n">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
+          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階</t>
+          <t>見える化システムへの入力
+将来推計 第2段階</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -5793,7 +5810,7 @@
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ</t>
+          <t>受領済みの画面の写しの範囲で概算し、確認できていない項目はその旨を明記する</t>
         </is>
       </c>
     </row>
@@ -5802,16 +5819,17 @@
         <v>105</v>
       </c>
       <c r="B110" s="5" t="n">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供の要否</t>
+          <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析の更新</t>
+          <t>将来推計 第3段階 05・06シート
+計画素案 第6章第6節</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -5821,7 +5839,7 @@
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G110" s="16" t="n">
@@ -5829,12 +5847,12 @@
       </c>
       <c r="H110" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供を依頼しない（成果品は収録済みで内容が確定しており、現時点で不足がない）</t>
+          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
         </is>
       </c>
     </row>
@@ -5843,17 +5861,17 @@
         <v>106</v>
       </c>
       <c r="B111" s="5" t="n">
-        <v>148</v>
+        <v>64</v>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
+          <t>区域内に事業所がないサービスの住民向けの記載</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力
-将来推計 第2段階</t>
+          <t>介護高齢者福祉サービスガイド_構成案
+計画素案 第6章第4節</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -5863,7 +5881,7 @@
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G111" s="16" t="n">
@@ -5871,12 +5889,12 @@
       </c>
       <c r="H111" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
-          <t>受領済みの画面の写しの範囲で概算し、確認できていない項目はその旨を明記する</t>
+          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
         </is>
       </c>
     </row>
@@ -5885,17 +5903,17 @@
         <v>107</v>
       </c>
       <c r="B112" s="5" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提（受託者案）</t>
+          <t>成果指向型配分枠（令和8年度新設）への対応</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階 05・06シート
-計画素案 第6章第6節</t>
+          <t>計画素案 第5章
+交付金評価指標と全国集計の受領点検 06シート</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -5918,7 +5936,7 @@
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
-          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
+          <t>成果指向型配分枠への対応状況を確認できないものとして、第10期の施策には位置づけず、確認でき次第加える</t>
         </is>
       </c>
     </row>
@@ -5927,17 +5945,17 @@
         <v>108</v>
       </c>
       <c r="B113" s="5" t="n">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスの住民向けの記載</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>介護高齢者福祉サービスガイド_構成案
-計画素案 第6章第4節</t>
+          <t>計画素案 第1章第9節・第2章第8節・第5章・第6章第2節・第6章第4節
+ケアプラン点検実施要領</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -5960,7 +5978,7 @@
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
+          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
         </is>
       </c>
     </row>
@@ -5969,17 +5987,18 @@
         <v>109</v>
       </c>
       <c r="B114" s="5" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠（令和8年度新設）への対応</t>
+          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章
-交付金評価指標と全国集計の受領点検 06シート</t>
+          <t>給付適正化計画の位置づけと追加検討事項 01シート
+計画素案 第5章 基本目標5・第2章第4節
+アンケート調査の分析 令和8年9月業務報告 第4節</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -6002,7 +6021,7 @@
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠への対応状況を確認できないものとして、第10期の施策には位置づけず、確認でき次第加える</t>
+          <t>第9期計画の本文及び前回調査の原集計表を受領できないものとして、前回調査との比較は割合のみとし、指標別の分母を確認できない旨を注記する</t>
         </is>
       </c>
     </row>
@@ -6011,17 +6030,17 @@
         <v>110</v>
       </c>
       <c r="B115" s="5" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+          <t>介護給付費通知及び給付実績の活用による確認等</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節・第2章第8節・第5章・第6章第2節・第6章第4節
-ケアプラン点検実施要領</t>
+          <t>給付適正化計画の位置づけと追加検討事項 02シート
+計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -6044,7 +6063,7 @@
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
+          <t>介護給付費通知の実施状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
         </is>
       </c>
     </row>
@@ -6053,18 +6072,17 @@
         <v>111</v>
       </c>
       <c r="B116" s="5" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
+          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけと追加検討事項 01シート
-計画素案 第5章 基本目標5・第2章第4節
-アンケート調査の分析 令和8年9月業務報告 第4節</t>
+          <t>給付適正化計画の位置づけと追加検討事項 04シート
+計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -6087,7 +6105,7 @@
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文及び前回調査の原集計表を受領できないものとして、前回調査との比較は割合のみとし、指標別の分母を確認できない旨を注記する</t>
+          <t>認定調査の委託の状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
         </is>
       </c>
     </row>
@@ -6096,17 +6114,18 @@
         <v>112</v>
       </c>
       <c r="B117" s="5" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知及び給付実績の活用による確認等</t>
+          <t>令和9年4月1日から義務となる2件への対応</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけと追加検討事項 02シート
-計画素案 第5章 基本目標5</t>
+          <t>計画素案 第1章第9節
+計画素案 第5章 基本目標3・4
+計画素案 第6章第4節3</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -6129,7 +6148,7 @@
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知の実施状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
+          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
         </is>
       </c>
     </row>
@@ -6138,17 +6157,18 @@
         <v>113</v>
       </c>
       <c r="B118" s="5" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
+          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけと追加検討事項 04シート
-計画素案 第5章 基本目標5</t>
+          <t>計画素案 第6章第4節
+計画素案 第6章第2節2（2）
+地域密着型サービス基準省令の論点整理</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -6171,7 +6191,7 @@
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
-          <t>認定調査の委託の状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
+          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
         </is>
       </c>
     </row>
@@ -6180,23 +6200,22 @@
         <v>114</v>
       </c>
       <c r="B119" s="5" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月1日から義務となる2件への対応</t>
+          <t>補正しても外れるサービス6件の理由</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節
-計画素案 第5章 基本目標3・4
-計画素案 第6章第4節3</t>
+          <t>対計画比の偏りの補正試算
+計画素案 第6章第2節2</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
@@ -6214,7 +6233,7 @@
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
-          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
+          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
         </is>
       </c>
     </row>
@@ -6223,23 +6242,21 @@
         <v>115</v>
       </c>
       <c r="B120" s="5" t="n">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
+          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第4節
-計画素案 第6章第2節2（2）
-地域密着型サービス基準省令の論点整理</t>
+          <t>計画素案 第1章第8節・第2章第3節6・第5章 基本目標2・第6章第2節</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
@@ -6257,7 +6274,7 @@
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
+          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
         </is>
       </c>
     </row>
@@ -6266,22 +6283,22 @@
         <v>116</v>
       </c>
       <c r="B121" s="5" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れるサービス6件の理由</t>
+          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>対計画比の偏りの補正試算
-計画素案 第6章第2節2</t>
+          <t>計画素案 第5章 基本目標2
+第9期評価（施策2-5）</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
@@ -6299,7 +6316,7 @@
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
+          <t>施策2-5の代表KPIはO2（提起された地域課題のうち翌年度の事業・予算に反映されたものの割合）とする（当方案）</t>
         </is>
       </c>
     </row>
@@ -6308,16 +6325,16 @@
         <v>117</v>
       </c>
       <c r="B122" s="5" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
+          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第8節・第2章第3節6・第5章 基本目標2・第6章第2節</t>
+          <t>計画素案 第5章 基本目標2</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -6340,7 +6357,7 @@
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
-          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
+          <t>地域ケア会議の記録様式は協議資料にとどめ、令和9年度に整える</t>
         </is>
       </c>
     </row>
@@ -6349,22 +6366,21 @@
         <v>118</v>
       </c>
       <c r="B123" s="5" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2
-第9期評価（施策2-5）</t>
+          <t>計画素案 第5章 基本目標2・第6章第4節4</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
@@ -6382,7 +6398,7 @@
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIはO2（提起された地域課題のうち翌年度の事業・予算に反映されたものの割合）とする（当方案）</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
         </is>
       </c>
     </row>
@@ -6391,21 +6407,22 @@
         <v>119</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
+          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2</t>
+          <t>計画素案 第5章 基本目標2
+第9期評価（施策2-5）</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
@@ -6423,7 +6440,7 @@
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の記録様式は協議資料にとどめ、令和9年度に整える</t>
+          <t>令和7年度の実施報告書により把握できる範囲で記述する</t>
         </is>
       </c>
     </row>
@@ -6432,21 +6449,22 @@
         <v>120</v>
       </c>
       <c r="B125" s="5" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
+          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2・第6章第4節4</t>
+          <t>計画素案 第2章第1節3・第6章第1節
+将来推計 第1段階・第2段階</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
@@ -6464,7 +6482,7 @@
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
+          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
         </is>
       </c>
     </row>
@@ -6473,22 +6491,22 @@
         <v>121</v>
       </c>
       <c r="B126" s="5" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
+          <t>見える化システムの総人口の設定を案Cに改めるか</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2
-第9期評価（施策2-5）</t>
+          <t>将来推計 第1段階
+計画素案 第2章第1節・第6章第1節</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
@@ -6506,7 +6524,7 @@
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の実施報告書により把握できる範囲で記述する</t>
+          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
         </is>
       </c>
     </row>
@@ -6515,22 +6533,22 @@
         <v>122</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
+          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節3・第6章第1節
-将来推計 第1段階・第2段階</t>
+          <t>将来推計 第2段階
+計画素案 第6章第4節2</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
@@ -6548,7 +6566,7 @@
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
+          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
         </is>
       </c>
     </row>
@@ -6557,17 +6575,17 @@
         <v>123</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総人口の設定を案Cに改めるか</t>
+          <t>画面の令和7年度と年報の月平均の食い違い</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第1段階
-計画素案 第2章第1節・第6章第1節</t>
+          <t>将来推計 第2段階
+計画素案 第6章第2節</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -6590,7 +6608,7 @@
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
-          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
+          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
         </is>
       </c>
     </row>
@@ -6599,22 +6617,21 @@
         <v>124</v>
       </c>
       <c r="B129" s="5" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+          <t>計画素案の未確定箇所の表示の統一</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階
-計画素案 第6章第4節2</t>
+          <t>計画素案（策定委員会用）</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F129" s="5" t="inlineStr">
@@ -6632,7 +6649,7 @@
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
+          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとする</t>
         </is>
       </c>
     </row>
@@ -6641,17 +6658,17 @@
         <v>125</v>
       </c>
       <c r="B130" s="5" t="n">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度と年報の月平均の食い違い</t>
+          <t>計画素案 第2章第1節に町別の図を加えるか</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階
-計画素案 第6章第2節</t>
+          <t>計画素案 第2章第1節
+図表集</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -6674,7 +6691,7 @@
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
-          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
+          <t>計画素案 第2章第1節に町別の図を加えない。加筆分は協議用の資料にとどめる</t>
         </is>
       </c>
     </row>
@@ -6683,16 +6700,17 @@
         <v>126</v>
       </c>
       <c r="B131" s="5" t="n">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所の表示の統一</t>
+          <t>中長期推計を令和12・27・32年度まで広げるか</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>計画素案（策定委員会用）</t>
+          <t>見える化システムへの入力
+計画素案 第6章第1節・第3節</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -6715,7 +6733,7 @@
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
-          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとする</t>
+          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
         </is>
       </c>
     </row>
@@ -6724,17 +6742,17 @@
         <v>127</v>
       </c>
       <c r="B132" s="5" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えるか</t>
+          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節
-図表集</t>
+          <t>計画素案 第5章第3節・基本目標3・資料1
+アンケート調査の集計分析報告書 02・14シート</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -6757,7 +6775,7 @@
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えない。加筆分は協議用の資料にとどめる</t>
+          <t>設問ごとの有効回答を分母とし、町別の値は掲げない（令和8年9月25日に是正済み）</t>
         </is>
       </c>
     </row>
@@ -6766,22 +6784,22 @@
         <v>128</v>
       </c>
       <c r="B133" s="5" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>中長期推計を令和12・27・32年度まで広げるか</t>
+          <t>東川町の通いの場の整備と担い手の確保</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力
-計画素案 第6章第1節・第3節</t>
+          <t>計画素案 第3章第1節・第5章 基本目標2
+10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・東川町</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
@@ -6799,7 +6817,7 @@
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
-          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
+          <t>現状のまま（東川町の整備を見込まない）第10期の目標値を置く</t>
         </is>
       </c>
     </row>
@@ -6808,22 +6826,22 @@
         <v>129</v>
       </c>
       <c r="B134" s="5" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
+          <t>東川町の認知症サポーター養成講座の実施状況</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章第3節・基本目標3・資料1
-アンケート調査の集計分析報告書 02・14シート</t>
+          <t>計画素案 第5章 基本目標2
+10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・東川町</t>
         </is>
       </c>
       <c r="F134" s="5" t="inlineStr">
@@ -6841,7 +6859,7 @@
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
-          <t>設問ごとの有効回答を分母とし、町別の値は掲げない（令和8年9月25日に是正済み）</t>
+          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
         </is>
       </c>
     </row>
@@ -6850,16 +6868,16 @@
         <v>130</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>東川町の通いの場の整備と担い手の確保</t>
+          <t>東川町のチームオレンジ事業の位置づけ</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第3章第1節・第5章 基本目標2
+          <t>計画素案 第5章 基本目標2
 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
@@ -6883,7 +6901,7 @@
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t>現状のまま（東川町の整備を見込まない）第10期の目標値を置く</t>
+          <t>東川町の取組として記述し3町展開は記述しない</t>
         </is>
       </c>
     </row>
@@ -6892,11 +6910,11 @@
         <v>131</v>
       </c>
       <c r="B136" s="5" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>東川町の認知症サポーター養成講座の実施状況</t>
+          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
@@ -6907,7 +6925,7 @@
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>発注者・東川町</t>
+          <t>発注者・美瑛町</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
@@ -6925,7 +6943,7 @@
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
+          <t>令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残す</t>
         </is>
       </c>
     </row>
@@ -6934,11 +6952,11 @@
         <v>132</v>
       </c>
       <c r="B137" s="5" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>東川町のチームオレンジ事業の位置づけ</t>
+          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
@@ -6949,7 +6967,7 @@
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>発注者・東川町</t>
+          <t>発注者・美瑛町</t>
         </is>
       </c>
       <c r="F137" s="5" t="inlineStr">
@@ -6967,7 +6985,7 @@
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
-          <t>東川町の取組として記述し3町展開は記述しない</t>
+          <t>美瑛町の取組として記述し3町展開は記述しない</t>
         </is>
       </c>
     </row>
@@ -6976,16 +6994,16 @@
         <v>133</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
+          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2
+          <t>計画素案 第6章第4節・第6章第5節
 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
@@ -7009,7 +7027,7 @@
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残す</t>
+          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
         </is>
       </c>
     </row>
@@ -7018,11 +7036,11 @@
         <v>134</v>
       </c>
       <c r="B139" s="5" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
+          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
@@ -7051,7 +7069,7 @@
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の取組として記述し3町展開は記述しない</t>
+          <t>現に確認できる取組の範囲で記述する</t>
         </is>
       </c>
     </row>
@@ -7060,22 +7078,22 @@
         <v>135</v>
       </c>
       <c r="B140" s="5" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
+          <t>東神楽町の通いの場の維持</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第4節・第6章第5節
+          <t>計画素案 第3章第1節・第5章 基本目標2
 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>発注者・美瑛町</t>
+          <t>発注者・東神楽町</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
@@ -7093,7 +7111,7 @@
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
+          <t>令和6年度の水準が続くものとして目標値を置く</t>
         </is>
       </c>
     </row>
@@ -7102,11 +7120,11 @@
         <v>136</v>
       </c>
       <c r="B141" s="5" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
+          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
@@ -7117,7 +7135,7 @@
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>発注者・美瑛町</t>
+          <t>発注者・東神楽町</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
@@ -7135,7 +7153,7 @@
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述する</t>
+          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
         </is>
       </c>
     </row>
@@ -7144,22 +7162,22 @@
         <v>137</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の通いの場の維持</t>
+          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第3章第1節・第5章 基本目標2
-10月 地域課題の整理と3町協議の確認事項</t>
+          <t>計画素案の記載内容の洗い出しと対比 06シート・07シート
+計画素案 第1章第6節・第2章第3節・第2章第6節・第3章第2節・第4章第3節・第6章第6節</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>発注者・東神楽町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
@@ -7177,7 +7195,7 @@
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の水準が続くものとして目標値を置く</t>
+          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
         </is>
       </c>
     </row>
@@ -7186,22 +7204,22 @@
         <v>138</v>
       </c>
       <c r="B143" s="5" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
+          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2
-10月 地域課題の整理と3町協議の確認事項</t>
+          <t>図表データ管理台帳 03シート
+計画素案 第3章第4節・資料7</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>発注者・東神楽町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F143" s="5" t="inlineStr">
@@ -7219,7 +7237,7 @@
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
+          <t>の当方の扱い＝掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
         </is>
       </c>
     </row>
@@ -7228,17 +7246,17 @@
         <v>139</v>
       </c>
       <c r="B144" s="5" t="n">
-        <v>170</v>
+        <v>16</v>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
+          <t>保険料算定の前提</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>計画素案の記載内容の洗い出しと対比 06シート・07シート
-計画素案 第1章第6節・第2章第3節・第2章第6節・第3章第2節・第4章第3節・第6章第6節</t>
+          <t>素案 第6章第3節・第6節
+保険料算定表</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -7248,7 +7266,7 @@
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G144" s="16" t="n">
@@ -7256,12 +7274,12 @@
       </c>
       <c r="H144" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）</t>
+          <t>止めている成果物 保険料（+2）</t>
         </is>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
-          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
+          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
         </is>
       </c>
     </row>
@@ -7270,22 +7288,21 @@
         <v>140</v>
       </c>
       <c r="B145" s="5" t="n">
-        <v>172</v>
+        <v>2</v>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
+          <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr">
         <is>
-          <t>図表データ管理台帳 03シート
-計画素案 第3章第4節・資料7</t>
+          <t>素案 第1章第9節・第6章第4節</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
@@ -7294,16 +7311,16 @@
         </is>
       </c>
       <c r="G145" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H145" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）</t>
+          <t>期限 当月（R8.10）（+1）</t>
         </is>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
-          <t>の当方の扱い＝掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
+          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
         </is>
       </c>
     </row>
@@ -7312,40 +7329,41 @@
         <v>141</v>
       </c>
       <c r="B146" s="5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提</t>
+          <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第3節・第6節
-保険料算定表</t>
+          <t>素案 第1章第7節
+追加調査報告書 03シート
+住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G146" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H146" s="6" t="inlineStr">
         <is>
-          <t>止めている成果物 保険料（+2）</t>
+          <t>期限 当月（R8.10）（+1）</t>
         </is>
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
+          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
         </is>
       </c>
     </row>
@@ -7354,21 +7372,22 @@
         <v>142</v>
       </c>
       <c r="B147" s="5" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
+          <t>人口推計の基礎とする系列</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第9節・第6章第4節</t>
+          <t>素案 第6章第1節
+将来推計</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
@@ -7386,7 +7405,7 @@
       </c>
       <c r="I147" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
+          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
         </is>
       </c>
     </row>
@@ -7395,23 +7414,22 @@
         <v>143</v>
       </c>
       <c r="B148" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域の判定資料</t>
+          <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第7節
-追加調査報告書 03シート
-住まいと施設の公表名簿との突合 08シート</t>
+          <t>素案 第6章第1節
+将来推計</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
@@ -7429,7 +7447,7 @@
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
-          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
+          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
         </is>
       </c>
     </row>
@@ -7438,17 +7456,17 @@
         <v>144</v>
       </c>
       <c r="B149" s="5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎とする系列</t>
+          <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第1節
-将来推計</t>
+          <t>素案 資料2
+3町協議資料</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -7471,7 +7489,7 @@
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
-          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
+          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
         </is>
       </c>
     </row>
@@ -7480,22 +7498,21 @@
         <v>145</v>
       </c>
       <c r="B150" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>認定者数の基準月と月次推移</t>
+          <t>北海道・圏域との調整の場</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第1節
-将来推計</t>
+          <t>素案 第6章第4節</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
@@ -7513,7 +7530,7 @@
       </c>
       <c r="I150" s="6" t="inlineStr">
         <is>
-          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
+          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
         </is>
       </c>
     </row>
@@ -7522,22 +7539,22 @@
         <v>146</v>
       </c>
       <c r="B151" s="5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>3町計画への共通指標の掲載</t>
+          <t>成果品の仕様</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr">
         <is>
-          <t>素案 資料2
-3町協議資料</t>
+          <t>計画書（印刷200部）
+概要版</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
@@ -7555,7 +7572,7 @@
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
-          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
+          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
         </is>
       </c>
     </row>
@@ -7564,21 +7581,22 @@
         <v>147</v>
       </c>
       <c r="B152" s="5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場</t>
+          <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第4節</t>
+          <t>素案 第2章第3節・第6章第4節
+図21・図22</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
@@ -7596,7 +7614,7 @@
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
+          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
         </is>
       </c>
     </row>
@@ -7605,22 +7623,22 @@
         <v>148</v>
       </c>
       <c r="B153" s="5" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様</t>
+          <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
       <c r="D153" s="6" t="inlineStr">
         <is>
-          <t>計画書（印刷200部）
-概要版</t>
+          <t>素案 第5章 基本目標1・5
+図表集 認知症・医療連携</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町・北海道</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
@@ -7638,7 +7656,7 @@
       </c>
       <c r="I153" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
+          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
         </is>
       </c>
     </row>
@@ -7647,22 +7665,22 @@
         <v>149</v>
       </c>
       <c r="B154" s="5" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>事業所の定員・稼働率データ</t>
+          <t>重度化の速度の前提</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第3節・第6章第4節
-図21・図22</t>
+          <t>素案 第6章第1節
+認定者数・給付費の推計</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
@@ -7680,7 +7698,7 @@
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
-          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
+          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
         </is>
       </c>
     </row>
@@ -7689,22 +7707,22 @@
         <v>150</v>
       </c>
       <c r="B155" s="5" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>認知症・医療介護連携の実績データ</t>
+          <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
-          <t>素案 第5章 基本目標1・5
-図表集 認知症・医療連携</t>
+          <t>素案 第6章第2節・第5章・第7章
+給付費の推計</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
@@ -7722,7 +7740,7 @@
       </c>
       <c r="I155" s="6" t="inlineStr">
         <is>
-          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
+          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
         </is>
       </c>
     </row>
@@ -7731,17 +7749,17 @@
         <v>151</v>
       </c>
       <c r="B156" s="5" t="n">
-        <v>29</v>
+        <v>128</v>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提</t>
+          <t>令和8年度の実績見込み値を編集するか</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第1節
-認定者数・給付費の推計</t>
+          <t>将来推計 第2段階
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -7764,7 +7782,7 @@
       </c>
       <c r="I156" s="6" t="inlineStr">
         <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
+          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
         </is>
       </c>
     </row>
@@ -7773,17 +7791,17 @@
         <v>152</v>
       </c>
       <c r="B157" s="5" t="n">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の実施予定と推計での扱い</t>
+          <t>見える化システムの利用率等の伸びの選択</t>
         </is>
       </c>
       <c r="D157" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第2節・第5章・第7章
-給付費の推計</t>
+          <t>将来推計 第2段階
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -7806,7 +7824,7 @@
       </c>
       <c r="I157" s="6" t="inlineStr">
         <is>
-          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
+          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9256,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>35件</t>
+          <t>11件</t>
         </is>
       </c>
     </row>
@@ -9507,7 +9525,7 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>18件</t>
+          <t>3件</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -9532,7 +9550,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>142件</t>
+          <t>157件</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -12840,7 +12858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -13103,17 +13121,17 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域ごとの必要利用定員総数（法定記載事項）（発注者・3町）</t>
+          <t>地域支援事業の量の見込みを算定してよいか（発注者）</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>点8。期限 超過（R8.9）／止めている成果物 概算／止めている成果物 計画素案／法定記載事項 法第117条に直結</t>
+          <t>点8。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／月額への効き 最大7円（令和7年度の総合事業の事業費）／法定記載事項 法第117条に直結</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.88</t>
+          <t>確認事項No.112</t>
         </is>
       </c>
     </row>
@@ -13128,17 +13146,17 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを一律からサービス別の趨勢を半分反映する置き方に改めるか（発注者）</t>
+          <t>認知症総合支援事業の実績のご提供（発注者）</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>点8。期限 超過（R8.9）／止めている成果物 概算／止めている成果物 計画素案／月額への効き 最大58円（補正を行うかどうかのご判断）</t>
+          <t>点7。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／法定記載事項 法第117条に直結</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.106</t>
+          <t>確認事項No.150</t>
         </is>
       </c>
     </row>
@@ -13153,72 +13171,22 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設の必要利用定員総数を定めるか（発注者・北海道）</t>
+          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案（発注者・北海道）</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>点8。期限 超過（R8.9）／止めている成果物 概算／止めている成果物 計画素案／法定記載事項 法第117条に直結</t>
+          <t>点6。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／月額への効き 最大47円（第7期給付適正化計画の目標のご判断）</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.113</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>催促・照会</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>第6章第2節の見込量の表に何を掲げるか（発注者）</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>点8。期限 超過（R8.9）／止めている成果物 概算／止めている成果物 計画素案／法定記載事項 法第117条に直結</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.131</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="44" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>催促・照会</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>地域支援事業の量の見込みを算定してよいか（発注者）</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>点8。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／月額への効き 最大7円（令和7年度の総合事業の事業費）／法定記載事項 法第117条に直結</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.112</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="62" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
+          <t>確認事項No.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="62" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>注1）「進める」は決定を待たずに着手できるもの、「催促・照会」は相手のある作業です。相手のある作業は午前のうちに出します（返事に日数がかかるため）。
 注2）04シートの作業継続可能なものは上位8件まで、催促・照会は優先以上の上位5件までを掲げています。残りは02・04シートを見ます。
@@ -13228,9 +13196,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A18:E18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13559,7 +13527,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>13件（進める8・催促5）</t>
+          <t>11件（進める8・催促3）</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -586,7 +586,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>毎日の終わりにWBSの現況・ペンディングの優先順位・当方の作業だけで進められるもの・翌日の作業順位を1枚にしたものです。基準日 令和8年10月1日。内部保管。</t>
+          <t>毎日の終わりにWBSの現況・ペンディングの優先順位・当方の作業だけで進められるもの・翌日の作業順位を1枚にしたものです。基準日 令和8年10月4日。内部保管。</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -773,7 +773,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）ごとの進捗率と、前に報告した時点からの動きです。基準日 令和8年10月1日。</t>
+          <t>仕様書４（1）〜（12）ごとの進捗率と、前に報告した時点からの動きです。基準日 令和8年10月4日。</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>＋5pt</t>
+          <t>±0pt</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>＋2pt</t>
+          <t>±0pt</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>＋1pt</t>
+          <t>±0pt</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>＋8pt</t>
+          <t>＋2pt</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.7910000000000001</v>
+        <v>0.7930000000000001</v>
       </c>
       <c r="D18" s="11" t="inlineStr"/>
       <c r="E18" s="11" t="inlineStr"/>
@@ -1202,7 +1202,7 @@
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>注1）進捗の記録の基準日は 令和8年10月1日 です。本表の基準日（令和8年10月1日）と違うときは、進捗の更新がまだ行われていません。
+          <t>注1）進捗の記録の基準日は 令和8年10月4日 です。本表の基準日（令和8年10月4日）と違うときは、進捗の更新がまだ行われていません。
 注2）進捗率を更新したら、更新前の値を記録へ移します。移さないと、過去の時点を記す資料（月次の報告・議事録）の数値が書き換わります。</t>
         </is>
       </c>
@@ -1215,125 +1215,27 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="4" t="inlineStr"/>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>コミット</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>6adcdee</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>既定値による計画素案への反映を38件まで進めた</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr"/>
-      <c r="E23" s="6" t="inlineStr"/>
-      <c r="F23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>52c9b69</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>翌日の作業順位8件の処理と単価の趨勢の効きの是正</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr"/>
-      <c r="E24" s="6" t="inlineStr"/>
-      <c r="F24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>666b8ee</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>3町合同意見交換会の資料と作業継続可能8件の処理</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>241932b</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>既定値の仮置き（未決160件）と据え置き区分Aの更新</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>9c17709</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>日次のWBS更新と翌日の作業順位（スキルと日次の表）</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="14" t="inlineStr">
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>基準日のコミットはありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A21:F21"/>
   </mergeCells>
@@ -1347,7 +1249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I190"/>
+  <dimension ref="A1:I188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1371,7 +1273,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>完了していない確認事項と資料提供依頼を、影響度の点の高い順に並べたものです。点の付け方は03シートに全て書いています。基準日 令和8年10月1日。</t>
+          <t>完了していない確認事項と資料提供依頼を、影響度の点の高い順に並べたものです。点の付け方は03シートに全て書いています。基準日 令和8年10月4日。</t>
         </is>
       </c>
     </row>
@@ -8176,7 +8078,7 @@
     <row r="168" ht="20" customHeight="1">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>2　資料提供依頼（資料の提供を求めるもの）　20件</t>
+          <t>2　資料提供依頼（資料の提供を求めるもの）　18件</t>
         </is>
       </c>
     </row>
@@ -8318,26 +8220,26 @@
         <v>3</v>
       </c>
       <c r="B172" s="5" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告　年報（令和6年度・令和7年度）</t>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>第3段階の給付費の算定、H15の基準値</t>
+          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G172" s="15" t="inlineStr">
@@ -8347,12 +8249,12 @@
       </c>
       <c r="H172" s="5" t="inlineStr">
         <is>
-          <t>提供予定（即時）</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I172" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -8361,16 +8263,16 @@
         <v>4</v>
       </c>
       <c r="B173" s="5" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告　月報（令和8年4月〜7月分）</t>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
         </is>
       </c>
       <c r="D173" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の推定、第9期の中間評価の更新</t>
+          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
         </is>
       </c>
       <c r="E173" s="6" t="inlineStr">
@@ -8380,7 +8282,7 @@
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G173" s="15" t="inlineStr">
@@ -8390,12 +8292,12 @@
       </c>
       <c r="H173" s="5" t="inlineStr">
         <is>
-          <t>提供予定（即時）</t>
+          <t>代替により解消</t>
         </is>
       </c>
       <c r="I173" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
     </row>
@@ -8404,26 +8306,26 @@
         <v>5</v>
       </c>
       <c r="B174" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
+          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
+          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G174" s="15" t="inlineStr">
@@ -8433,12 +8335,12 @@
       </c>
       <c r="H174" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I174" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -8447,26 +8349,26 @@
         <v>6</v>
       </c>
       <c r="B175" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
+          <t>事業所・施設の定員と稼働の実績</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
+          <t>稼働率の低下の有無、定員減少の経緯</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G175" s="15" t="inlineStr">
@@ -8476,12 +8378,12 @@
       </c>
       <c r="H175" s="5" t="inlineStr">
         <is>
-          <t>代替により解消</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -8490,21 +8392,21 @@
         <v>7</v>
       </c>
       <c r="B176" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
+          <t>未利用認定者の内訳とケアプランのサービス構成</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
+          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
@@ -8519,12 +8421,12 @@
       </c>
       <c r="H176" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
     </row>
@@ -8533,21 +8435,21 @@
         <v>8</v>
       </c>
       <c r="B177" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>事業所・施設の定員と稼働の実績</t>
+          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
         </is>
       </c>
       <c r="D177" s="6" t="inlineStr">
         <is>
-          <t>稼働率の低下の有無、定員減少の経緯</t>
+          <t>第9期の剰余額（現在は概算）</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F177" s="5" t="inlineStr">
@@ -8567,7 +8469,7 @@
       </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
     </row>
@@ -8576,21 +8478,21 @@
         <v>9</v>
       </c>
       <c r="B178" s="5" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t>未利用認定者の内訳とケアプランのサービス構成</t>
+          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
+          <t>給付費の地域内還流の議論</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
@@ -8610,7 +8512,7 @@
       </c>
       <c r="I178" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -8619,21 +8521,21 @@
         <v>10</v>
       </c>
       <c r="B179" s="5" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
+          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
         </is>
       </c>
       <c r="D179" s="6" t="inlineStr">
         <is>
-          <t>第9期の剰余額（現在は概算）</t>
+          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
         </is>
       </c>
       <c r="E179" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
@@ -8653,7 +8555,7 @@
       </c>
       <c r="I179" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -8662,21 +8564,21 @@
         <v>11</v>
       </c>
       <c r="B180" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
+          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t>給付費の地域内還流の議論</t>
+          <t>サービス種別ごとの見込量の様式</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
@@ -8691,12 +8593,12 @@
       </c>
       <c r="H180" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -8705,26 +8607,26 @@
         <v>12</v>
       </c>
       <c r="B181" s="5" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
+          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
         </is>
       </c>
       <c r="D181" s="6" t="inlineStr">
         <is>
-          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
+          <t>第10期の段階設計と保険料算定</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>国の情報</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>告示後</t>
         </is>
       </c>
       <c r="G181" s="15" t="inlineStr">
@@ -8734,12 +8636,12 @@
       </c>
       <c r="H181" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I181" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
     </row>
@@ -8748,41 +8650,41 @@
         <v>13</v>
       </c>
       <c r="B182" s="5" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
+          <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>サービス種別ごとの見込量の様式</t>
+          <t>圏域別の分析、圏域設定の見直し</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>美瑛町・3町</t>
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G182" s="15" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G182" s="16" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H182" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I182" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -8791,41 +8693,41 @@
         <v>14</v>
       </c>
       <c r="B183" s="5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr">
         <is>
-          <t>第10期の段階設計と保険料算定</t>
+          <t>評価の枠組みの整理</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>告示後</t>
-        </is>
-      </c>
-      <c r="G183" s="15" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G183" s="16" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H183" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
     </row>
@@ -8834,26 +8736,26 @@
         <v>15</v>
       </c>
       <c r="B184" s="5" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>小学校区と日常生活圏域の対応関係</t>
+          <t>見える化システムD49の指標定義</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>圏域別の分析、圏域設定の見直し</t>
+          <t>地域差指数の分解の可否</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
-          <t>美瑛町・3町</t>
+          <t>見える化システム・厚生労働省</t>
         </is>
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G184" s="16" t="inlineStr">
@@ -8863,12 +8765,12 @@
       </c>
       <c r="H184" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -8877,26 +8779,26 @@
         <v>16</v>
       </c>
       <c r="B185" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
         <is>
-          <t>評価の枠組みの整理</t>
+          <t>会議資料・委員会資料の記述の正確性</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>随時</t>
         </is>
       </c>
       <c r="G185" s="16" t="inlineStr">
@@ -8906,12 +8808,12 @@
       </c>
       <c r="H185" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I185" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -8920,31 +8822,31 @@
         <v>17</v>
       </c>
       <c r="B186" s="5" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD49の指標定義</t>
+          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
-          <t>地域差指数の分解の可否</t>
+          <t>中重度・軽度の認定率の推移</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>見える化システム・厚生労働省</t>
+          <t>見える化システム</t>
         </is>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G186" s="16" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G186" s="18" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H186" s="5" t="inlineStr">
@@ -8954,7 +8856,7 @@
       </c>
       <c r="I186" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -8963,132 +8865,46 @@
         <v>18</v>
       </c>
       <c r="B187" s="5" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+          <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
       <c r="D187" s="6" t="inlineStr">
         <is>
-          <t>会議資料・委員会資料の記述の正確性</t>
+          <t>世帯構成の現状</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>総務省・3町</t>
         </is>
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>随時</t>
-        </is>
-      </c>
-      <c r="G187" s="16" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>公表後</t>
+        </is>
+      </c>
+      <c r="G187" s="18" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H187" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I187" s="5" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="40" customHeight="1">
-      <c r="A188" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B188" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C188" s="6" t="inlineStr">
-        <is>
-          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
-        </is>
-      </c>
-      <c r="D188" s="6" t="inlineStr">
-        <is>
-          <t>中重度・軽度の認定率の推移</t>
-        </is>
-      </c>
-      <c r="E188" s="6" t="inlineStr">
-        <is>
-          <t>見える化システム</t>
-        </is>
-      </c>
-      <c r="F188" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G188" s="18" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="H188" s="5" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I188" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="40" customHeight="1">
-      <c r="A189" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B189" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C189" s="6" t="inlineStr">
-        <is>
-          <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
-        </is>
-      </c>
-      <c r="D189" s="6" t="inlineStr">
-        <is>
-          <t>世帯構成の現状</t>
-        </is>
-      </c>
-      <c r="E189" s="6" t="inlineStr">
-        <is>
-          <t>総務省・3町</t>
-        </is>
-      </c>
-      <c r="F189" s="5" t="inlineStr">
-        <is>
-          <t>公表後</t>
-        </is>
-      </c>
-      <c r="G189" s="18" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="H189" s="5" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I189" s="5" t="inlineStr">
-        <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="28" customHeight="1">
-      <c r="A190" s="14" t="inlineStr">
+    <row r="188" ht="28" customHeight="1">
+      <c r="A188" s="14" t="inlineStr">
         <is>
           <t>注）03シートの確認事項が「決定」を求めるものであるのに対し、本表は「資料の提供」を求めるものです。資料が届かない場合の扱いは04シートの区分で示しています。</t>
         </is>
@@ -9098,8 +8914,8 @@
   <mergeCells count="6">
     <mergeCell ref="A166:I166"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A190:I190"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A188:I188"/>
     <mergeCell ref="A168:I168"/>
     <mergeCell ref="A4:I4"/>
   </mergeCells>
@@ -9133,7 +8949,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02シートの点は次の規則だけで付けています。規則を変えれば02シートの並びも変わります。基準日 令和8年10月1日。</t>
+          <t>02シートの点は次の規則だけで付けています。規則を変えれば02シートの並びも変わります。基準日 令和8年10月4日。</t>
         </is>
       </c>
     </row>
@@ -9729,7 +9545,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>決定・資料の受領を待たずに当方の作業だけで進められるものです。基準日 令和8年10月1日。</t>
+          <t>決定・資料の受領を待たずに当方の作業だけで進められるものです。基準日 令和8年10月4日。</t>
         </is>
       </c>
     </row>
@@ -12871,7 +12687,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>翌日（令和8年10月2日）の作業順位</t>
+          <t>翌日（令和8年10月5日）の作業順位</t>
         </is>
       </c>
     </row>
@@ -13302,7 +13118,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>確認事項160件／資料提供依頼20件</t>
+          <t>確認事項160件／資料提供依頼18件</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
@@ -13477,7 +13293,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>記録 令和8年10月1日／本表 令和8年10月1日</t>
+          <t>記録 令和8年10月4日／本表 令和8年10月4日</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -13502,7 +13318,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>記録7件（最新 令和8年9月28日）</t>
+          <t>記録8件（最新 令和8年9月28日）</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -752,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1215,27 +1215,53 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>基準日のコミットはありません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="4" t="inlineStr"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>コミット</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>f1839d4</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>令和8年10月2日のご照会への回答と、送付成果品の記述の是正</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr"/>
+      <c r="E23" s="6" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A21:F21"/>
   </mergeCells>

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -752,7 +752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1237,20 +1237,38 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>f1839d4</t>
+          <t>4cf7703</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>令和8年10月2日のご照会への回答と、送付成果品の記述の是正</t>
+          <t>成果品が作業領域の消失により失われないかを点検し、公表版の図2点を是正</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
       <c r="E23" s="6" t="inlineStr"/>
       <c r="F23" s="6" t="inlineStr"/>
     </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="14" t="inlineStr">
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>f1839d4</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>令和8年10月2日のご照会への回答と、送付成果品の記述の是正</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
@@ -1258,12 +1276,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -92,17 +92,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DEEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -132,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -157,13 +157,10 @@
     <xf numFmtId="9" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -175,31 +172,31 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -586,7 +583,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>毎日の終わりにWBSの現況・ペンディングの優先順位・当方の作業だけで進められるもの・翌日の作業順位を1枚にしたものです。基準日 令和8年10月4日。内部保管。</t>
+          <t>毎日の終わりにWBSの現況・ペンディングの優先順位・当方の作業だけで進められるもの・翌日の作業順位を1枚にしたものです。基準日 令和8年10月5日。内部保管。</t>
         </is>
       </c>
     </row>
@@ -752,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -773,7 +770,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）ごとの進捗率と、前に報告した時点からの動きです。基準日 令和8年10月4日。</t>
+          <t>仕様書４（1）〜（12）ごとの進捗率と、前に報告した時点からの動きです。基準日 令和8年10月5日。</t>
         </is>
       </c>
     </row>
@@ -829,7 +826,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>0.92</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
@@ -838,7 +835,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>±0pt</t>
+          <t>▲9pt</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -858,8 +855,8 @@
           <t>第9期計画の評価・検証</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
-        <v>0.96</v>
+      <c r="C7" s="8" t="n">
+        <v>0.9285714285714286</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
@@ -868,7 +865,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>±0pt</t>
+          <t>▲3pt</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -888,8 +885,8 @@
           <t>実施済み調査結果の集計・分析</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n">
-        <v>0.99</v>
+      <c r="C8" s="8" t="n">
+        <v>0.7857142857142857</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
@@ -898,7 +895,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>±0pt</t>
+          <t>▲20pt</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -918,8 +915,8 @@
           <t>現状分析及び地域課題の整理</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
-        <v>0.99</v>
+      <c r="C9" s="8" t="n">
+        <v>0.9444444444444444</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
@@ -928,7 +925,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>±0pt</t>
+          <t>▲5pt</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -948,8 +945,8 @@
           <t>将来推計</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
-        <v>0.99</v>
+      <c r="C10" s="8" t="n">
+        <v>0.8125</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
@@ -958,7 +955,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>±0pt</t>
+          <t>▲18pt</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -978,8 +975,8 @@
           <t>計画書の作成</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
-        <v>0.99</v>
+      <c r="C11" s="8" t="n">
+        <v>0.5</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -988,7 +985,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>±0pt</t>
+          <t>▲49pt</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -1008,8 +1005,8 @@
           <t>計画策定支援</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
-        <v>0.99</v>
+      <c r="C12" s="8" t="n">
+        <v>0.625</v>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
@@ -1018,7 +1015,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>±0pt</t>
+          <t>▲36pt</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1038,8 +1035,8 @@
           <t>各種会議への技術的支援</t>
         </is>
       </c>
-      <c r="C13" s="10" t="n">
-        <v>0.2</v>
+      <c r="C13" s="8" t="n">
+        <v>0.5</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
@@ -1048,7 +1045,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>±0pt</t>
+          <t>＋30pt</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1068,17 +1065,17 @@
           <t>パブリックコメント支援</t>
         </is>
       </c>
-      <c r="C14" s="10" t="n">
-        <v>0</v>
+      <c r="C14" s="9" t="n">
+        <v>0.125</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>＋12pt</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1099,7 +1096,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>0.9</v>
+        <v>0.625</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -1108,7 +1105,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>＋2pt</t>
+          <t>▲28pt</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1128,7 +1125,7 @@
           <t>成果品の帰属</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1160,7 +1157,7 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -1182,27 +1179,27 @@
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="11" t="inlineStr"/>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr"/>
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>全体（数値で表せる10件の平均）</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n">
-        <v>0.7930000000000001</v>
-      </c>
-      <c r="D18" s="11" t="inlineStr"/>
-      <c r="E18" s="11" t="inlineStr"/>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="C18" s="11" t="n">
+        <v>0.6679563492063492</v>
+      </c>
+      <c r="D18" s="10" t="inlineStr"/>
+      <c r="E18" s="10" t="inlineStr"/>
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
     </row>
     <row r="19" ht="46" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>注1）進捗の記録の基準日は 令和8年10月4日 です。本表の基準日（令和8年10月4日）と違うときは、進捗の更新がまだ行われていません。
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>注1）進捗の記録の基準日は 令和8年10月5日 です。本表の基準日（令和8年10月5日）と違うときは、進捗の更新がまだ行われていません。
 注2）進捗率を更新したら、更新前の値を記録へ移します。移さないと、過去の時点を記す資料（月次の報告・議事録）の数値が書き換わります。</t>
         </is>
       </c>
@@ -1215,73 +1212,29 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="4" t="inlineStr"/>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>コミット</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>4cf7703</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>成果品が作業領域の消失により失われないかを点検し、公表版の図2点を是正</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr"/>
-      <c r="E23" s="6" t="inlineStr"/>
-      <c r="F23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>f1839d4</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>令和8年10月2日のご照会への回答と、送付成果品の記述の是正</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr"/>
-      <c r="E24" s="6" t="inlineStr"/>
-      <c r="F24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>基準日のコミットはありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1317,7 +1270,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>完了していない確認事項と資料提供依頼を、影響度の点の高い順に並べたものです。点の付け方は03シートに全て書いています。基準日 令和8年10月4日。</t>
+          <t>完了していない確認事項と資料提供依頼を、影響度の点の高い順に並べたものです。点の付け方は03シートに全て書いています。基準日 令和8年10月5日。</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1357,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G6" s="15" t="n">
+      <c r="G6" s="14" t="n">
         <v>8</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
@@ -1447,7 +1400,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G7" s="15" t="n">
+      <c r="G7" s="14" t="n">
         <v>7</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -1490,7 +1443,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G8" s="15" t="n">
+      <c r="G8" s="14" t="n">
         <v>6</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -1532,7 +1485,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="15" t="n">
         <v>5</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -1575,7 +1528,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G10" s="16" t="n">
+      <c r="G10" s="15" t="n">
         <v>5</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
@@ -1617,7 +1570,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G11" s="16" t="n">
+      <c r="G11" s="15" t="n">
         <v>5</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
@@ -1658,7 +1611,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G12" s="16" t="n">
+      <c r="G12" s="15" t="n">
         <v>5</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
@@ -1700,7 +1653,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="15" t="n">
         <v>5</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -1743,7 +1696,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G14" s="16" t="n">
+      <c r="G14" s="15" t="n">
         <v>5</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
@@ -1786,7 +1739,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G15" s="16" t="n">
+      <c r="G15" s="15" t="n">
         <v>5</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
@@ -1829,7 +1782,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G16" s="16" t="n">
+      <c r="G16" s="15" t="n">
         <v>5</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -1872,7 +1825,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G17" s="16" t="n">
+      <c r="G17" s="15" t="n">
         <v>5</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -1914,7 +1867,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G18" s="16" t="n">
+      <c r="G18" s="15" t="n">
         <v>5</v>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -1956,7 +1909,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G19" s="16" t="n">
+      <c r="G19" s="15" t="n">
         <v>5</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
@@ -1998,7 +1951,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G20" s="16" t="n">
+      <c r="G20" s="15" t="n">
         <v>5</v>
       </c>
       <c r="H20" s="6" t="inlineStr">
@@ -2039,7 +1992,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G21" s="16" t="n">
+      <c r="G21" s="15" t="n">
         <v>4</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
@@ -2081,7 +2034,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G22" s="16" t="n">
+      <c r="G22" s="15" t="n">
         <v>4</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -2123,7 +2076,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G23" s="16" t="n">
+      <c r="G23" s="15" t="n">
         <v>4</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
@@ -2166,7 +2119,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G24" s="16" t="n">
+      <c r="G24" s="15" t="n">
         <v>4</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
@@ -2208,7 +2161,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G25" s="16" t="n">
+      <c r="G25" s="15" t="n">
         <v>4</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
@@ -2250,7 +2203,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G26" s="16" t="n">
+      <c r="G26" s="15" t="n">
         <v>4</v>
       </c>
       <c r="H26" s="6" t="inlineStr">
@@ -2292,7 +2245,7 @@
           <t>告示後</t>
         </is>
       </c>
-      <c r="G27" s="16" t="n">
+      <c r="G27" s="15" t="n">
         <v>4</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
@@ -2335,7 +2288,7 @@
           <t>R8.9.2</t>
         </is>
       </c>
-      <c r="G28" s="16" t="n">
+      <c r="G28" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H28" s="6" t="inlineStr">
@@ -2377,7 +2330,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G29" s="16" t="n">
+      <c r="G29" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H29" s="6" t="inlineStr">
@@ -2419,7 +2372,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G30" s="16" t="n">
+      <c r="G30" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H30" s="6" t="inlineStr">
@@ -2461,7 +2414,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G31" s="16" t="n">
+      <c r="G31" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H31" s="6" t="inlineStr">
@@ -2503,7 +2456,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G32" s="16" t="n">
+      <c r="G32" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -2545,7 +2498,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G33" s="16" t="n">
+      <c r="G33" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H33" s="6" t="inlineStr">
@@ -2588,7 +2541,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G34" s="16" t="n">
+      <c r="G34" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H34" s="6" t="inlineStr">
@@ -2631,7 +2584,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G35" s="16" t="n">
+      <c r="G35" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H35" s="6" t="inlineStr">
@@ -2674,7 +2627,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G36" s="16" t="n">
+      <c r="G36" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H36" s="6" t="inlineStr">
@@ -2717,7 +2670,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G37" s="16" t="n">
+      <c r="G37" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H37" s="6" t="inlineStr">
@@ -2760,7 +2713,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G38" s="16" t="n">
+      <c r="G38" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H38" s="6" t="inlineStr">
@@ -2803,7 +2756,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G39" s="16" t="n">
+      <c r="G39" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H39" s="6" t="inlineStr">
@@ -2845,7 +2798,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G40" s="16" t="n">
+      <c r="G40" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H40" s="6" t="inlineStr">
@@ -2889,7 +2842,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G41" s="16" t="n">
+      <c r="G41" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H41" s="6" t="inlineStr">
@@ -2931,7 +2884,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G42" s="16" t="n">
+      <c r="G42" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H42" s="6" t="inlineStr">
@@ -2973,7 +2926,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G43" s="16" t="n">
+      <c r="G43" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H43" s="6" t="inlineStr">
@@ -3015,7 +2968,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G44" s="16" t="n">
+      <c r="G44" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H44" s="6" t="inlineStr">
@@ -3057,7 +3010,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G45" s="16" t="n">
+      <c r="G45" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H45" s="6" t="inlineStr">
@@ -3100,7 +3053,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G46" s="16" t="n">
+      <c r="G46" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H46" s="6" t="inlineStr">
@@ -3142,7 +3095,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G47" s="16" t="n">
+      <c r="G47" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H47" s="6" t="inlineStr">
@@ -3185,7 +3138,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G48" s="16" t="n">
+      <c r="G48" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H48" s="6" t="inlineStr">
@@ -3228,7 +3181,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G49" s="16" t="n">
+      <c r="G49" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H49" s="6" t="inlineStr">
@@ -3271,7 +3224,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G50" s="16" t="n">
+      <c r="G50" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H50" s="6" t="inlineStr">
@@ -3313,7 +3266,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G51" s="16" t="n">
+      <c r="G51" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H51" s="6" t="inlineStr">
@@ -3355,7 +3308,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G52" s="16" t="n">
+      <c r="G52" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H52" s="6" t="inlineStr">
@@ -3398,7 +3351,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G53" s="16" t="n">
+      <c r="G53" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H53" s="6" t="inlineStr">
@@ -3440,7 +3393,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G54" s="16" t="n">
+      <c r="G54" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H54" s="6" t="inlineStr">
@@ -3482,7 +3435,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G55" s="16" t="n">
+      <c r="G55" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H55" s="6" t="inlineStr">
@@ -3524,7 +3477,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G56" s="16" t="n">
+      <c r="G56" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H56" s="6" t="inlineStr">
@@ -3565,7 +3518,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G57" s="16" t="n">
+      <c r="G57" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H57" s="6" t="inlineStr">
@@ -3607,7 +3560,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G58" s="16" t="n">
+      <c r="G58" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H58" s="6" t="inlineStr">
@@ -3649,7 +3602,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G59" s="16" t="n">
+      <c r="G59" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H59" s="6" t="inlineStr">
@@ -3691,7 +3644,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G60" s="16" t="n">
+      <c r="G60" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H60" s="6" t="inlineStr">
@@ -3733,7 +3686,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G61" s="16" t="n">
+      <c r="G61" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H61" s="6" t="inlineStr">
@@ -3775,7 +3728,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G62" s="16" t="n">
+      <c r="G62" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H62" s="6" t="inlineStr">
@@ -3817,7 +3770,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G63" s="16" t="n">
+      <c r="G63" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H63" s="6" t="inlineStr">
@@ -3858,7 +3811,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G64" s="16" t="n">
+      <c r="G64" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H64" s="6" t="inlineStr">
@@ -3901,7 +3854,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G65" s="16" t="n">
+      <c r="G65" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H65" s="6" t="inlineStr">
@@ -3943,7 +3896,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G66" s="16" t="n">
+      <c r="G66" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H66" s="6" t="inlineStr">
@@ -3985,7 +3938,7 @@
           <t>R8.8</t>
         </is>
       </c>
-      <c r="G67" s="16" t="n">
+      <c r="G67" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H67" s="6" t="inlineStr">
@@ -4027,7 +3980,7 @@
           <t>R8.8</t>
         </is>
       </c>
-      <c r="G68" s="16" t="n">
+      <c r="G68" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H68" s="6" t="inlineStr">
@@ -4069,7 +4022,7 @@
           <t>R8.8</t>
         </is>
       </c>
-      <c r="G69" s="16" t="n">
+      <c r="G69" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H69" s="6" t="inlineStr">
@@ -4111,7 +4064,7 @@
           <t>R8.8</t>
         </is>
       </c>
-      <c r="G70" s="16" t="n">
+      <c r="G70" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H70" s="6" t="inlineStr">
@@ -4152,7 +4105,7 @@
           <t>R8.8</t>
         </is>
       </c>
-      <c r="G71" s="16" t="n">
+      <c r="G71" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H71" s="6" t="inlineStr">
@@ -4194,7 +4147,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G72" s="16" t="n">
+      <c r="G72" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H72" s="6" t="inlineStr">
@@ -4236,7 +4189,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G73" s="16" t="n">
+      <c r="G73" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H73" s="6" t="inlineStr">
@@ -4278,7 +4231,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G74" s="16" t="n">
+      <c r="G74" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
@@ -4320,7 +4273,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G75" s="16" t="n">
+      <c r="G75" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H75" s="6" t="inlineStr">
@@ -4362,7 +4315,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G76" s="16" t="n">
+      <c r="G76" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H76" s="6" t="inlineStr">
@@ -4404,7 +4357,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G77" s="16" t="n">
+      <c r="G77" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H77" s="6" t="inlineStr">
@@ -4447,7 +4400,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G78" s="16" t="n">
+      <c r="G78" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H78" s="6" t="inlineStr">
@@ -4489,7 +4442,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G79" s="16" t="n">
+      <c r="G79" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H79" s="6" t="inlineStr">
@@ -4531,7 +4484,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G80" s="16" t="n">
+      <c r="G80" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H80" s="6" t="inlineStr">
@@ -4573,7 +4526,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G81" s="16" t="n">
+      <c r="G81" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H81" s="6" t="inlineStr">
@@ -4615,7 +4568,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G82" s="16" t="n">
+      <c r="G82" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H82" s="6" t="inlineStr">
@@ -4657,7 +4610,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G83" s="16" t="n">
+      <c r="G83" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H83" s="6" t="inlineStr">
@@ -4699,7 +4652,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G84" s="16" t="n">
+      <c r="G84" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H84" s="6" t="inlineStr">
@@ -4741,7 +4694,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G85" s="16" t="n">
+      <c r="G85" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H85" s="6" t="inlineStr">
@@ -4784,7 +4737,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G86" s="16" t="n">
+      <c r="G86" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H86" s="6" t="inlineStr">
@@ -4827,7 +4780,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G87" s="16" t="n">
+      <c r="G87" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H87" s="6" t="inlineStr">
@@ -4868,7 +4821,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G88" s="16" t="n">
+      <c r="G88" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H88" s="6" t="inlineStr">
@@ -4910,7 +4863,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G89" s="16" t="n">
+      <c r="G89" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H89" s="6" t="inlineStr">
@@ -4953,7 +4906,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G90" s="16" t="n">
+      <c r="G90" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H90" s="6" t="inlineStr">
@@ -4995,7 +4948,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G91" s="16" t="n">
+      <c r="G91" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H91" s="6" t="inlineStr">
@@ -5037,7 +4990,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G92" s="16" t="n">
+      <c r="G92" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H92" s="6" t="inlineStr">
@@ -5078,7 +5031,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G93" s="16" t="n">
+      <c r="G93" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H93" s="6" t="inlineStr">
@@ -5119,7 +5072,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G94" s="16" t="n">
+      <c r="G94" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H94" s="6" t="inlineStr">
@@ -5160,7 +5113,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G95" s="16" t="n">
+      <c r="G95" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H95" s="6" t="inlineStr">
@@ -5202,7 +5155,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G96" s="16" t="n">
+      <c r="G96" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H96" s="6" t="inlineStr">
@@ -5244,7 +5197,7 @@
           <t>R8.9.24</t>
         </is>
       </c>
-      <c r="G97" s="16" t="n">
+      <c r="G97" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H97" s="6" t="inlineStr">
@@ -5287,7 +5240,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G98" s="16" t="n">
+      <c r="G98" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H98" s="6" t="inlineStr">
@@ -5329,7 +5282,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G99" s="16" t="n">
+      <c r="G99" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H99" s="6" t="inlineStr">
@@ -5371,7 +5324,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G100" s="16" t="n">
+      <c r="G100" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H100" s="6" t="inlineStr">
@@ -5413,7 +5366,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G101" s="16" t="n">
+      <c r="G101" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H101" s="6" t="inlineStr">
@@ -5455,7 +5408,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G102" s="16" t="n">
+      <c r="G102" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H102" s="6" t="inlineStr">
@@ -5497,7 +5450,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G103" s="16" t="n">
+      <c r="G103" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H103" s="6" t="inlineStr">
@@ -5538,7 +5491,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G104" s="16" t="n">
+      <c r="G104" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H104" s="6" t="inlineStr">
@@ -5579,7 +5532,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G105" s="16" t="n">
+      <c r="G105" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H105" s="6" t="inlineStr">
@@ -5620,7 +5573,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G106" s="16" t="n">
+      <c r="G106" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H106" s="6" t="inlineStr">
@@ -5662,7 +5615,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G107" s="16" t="n">
+      <c r="G107" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H107" s="6" t="inlineStr">
@@ -5704,7 +5657,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G108" s="16" t="n">
+      <c r="G108" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H108" s="6" t="inlineStr">
@@ -5746,7 +5699,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G109" s="16" t="n">
+      <c r="G109" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H109" s="6" t="inlineStr">
@@ -5788,7 +5741,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G110" s="16" t="n">
+      <c r="G110" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H110" s="6" t="inlineStr">
@@ -5830,7 +5783,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G111" s="16" t="n">
+      <c r="G111" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H111" s="6" t="inlineStr">
@@ -5872,7 +5825,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G112" s="16" t="n">
+      <c r="G112" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H112" s="6" t="inlineStr">
@@ -5914,7 +5867,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G113" s="16" t="n">
+      <c r="G113" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H113" s="6" t="inlineStr">
@@ -5957,7 +5910,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G114" s="16" t="n">
+      <c r="G114" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H114" s="6" t="inlineStr">
@@ -5999,7 +5952,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G115" s="16" t="n">
+      <c r="G115" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H115" s="6" t="inlineStr">
@@ -6041,7 +5994,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G116" s="16" t="n">
+      <c r="G116" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H116" s="6" t="inlineStr">
@@ -6084,7 +6037,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G117" s="16" t="n">
+      <c r="G117" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H117" s="6" t="inlineStr">
@@ -6127,7 +6080,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G118" s="16" t="n">
+      <c r="G118" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H118" s="6" t="inlineStr">
@@ -6169,7 +6122,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G119" s="16" t="n">
+      <c r="G119" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H119" s="6" t="inlineStr">
@@ -6210,7 +6163,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G120" s="16" t="n">
+      <c r="G120" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H120" s="6" t="inlineStr">
@@ -6252,7 +6205,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G121" s="16" t="n">
+      <c r="G121" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H121" s="6" t="inlineStr">
@@ -6293,7 +6246,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G122" s="16" t="n">
+      <c r="G122" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H122" s="6" t="inlineStr">
@@ -6334,7 +6287,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G123" s="16" t="n">
+      <c r="G123" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H123" s="6" t="inlineStr">
@@ -6376,7 +6329,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G124" s="16" t="n">
+      <c r="G124" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H124" s="6" t="inlineStr">
@@ -6418,7 +6371,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G125" s="16" t="n">
+      <c r="G125" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H125" s="6" t="inlineStr">
@@ -6460,7 +6413,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G126" s="16" t="n">
+      <c r="G126" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H126" s="6" t="inlineStr">
@@ -6502,7 +6455,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G127" s="16" t="n">
+      <c r="G127" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H127" s="6" t="inlineStr">
@@ -6544,7 +6497,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G128" s="16" t="n">
+      <c r="G128" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H128" s="6" t="inlineStr">
@@ -6585,7 +6538,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G129" s="16" t="n">
+      <c r="G129" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H129" s="6" t="inlineStr">
@@ -6627,7 +6580,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G130" s="16" t="n">
+      <c r="G130" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H130" s="6" t="inlineStr">
@@ -6669,7 +6622,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G131" s="16" t="n">
+      <c r="G131" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H131" s="6" t="inlineStr">
@@ -6711,7 +6664,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G132" s="16" t="n">
+      <c r="G132" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H132" s="6" t="inlineStr">
@@ -6753,7 +6706,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G133" s="16" t="n">
+      <c r="G133" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H133" s="6" t="inlineStr">
@@ -6795,7 +6748,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G134" s="16" t="n">
+      <c r="G134" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H134" s="6" t="inlineStr">
@@ -6837,7 +6790,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G135" s="16" t="n">
+      <c r="G135" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H135" s="6" t="inlineStr">
@@ -6879,7 +6832,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G136" s="16" t="n">
+      <c r="G136" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H136" s="6" t="inlineStr">
@@ -6921,7 +6874,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G137" s="16" t="n">
+      <c r="G137" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H137" s="6" t="inlineStr">
@@ -6963,7 +6916,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G138" s="16" t="n">
+      <c r="G138" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H138" s="6" t="inlineStr">
@@ -7005,7 +6958,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G139" s="16" t="n">
+      <c r="G139" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H139" s="6" t="inlineStr">
@@ -7047,7 +7000,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G140" s="16" t="n">
+      <c r="G140" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H140" s="6" t="inlineStr">
@@ -7089,7 +7042,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G141" s="16" t="n">
+      <c r="G141" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H141" s="6" t="inlineStr">
@@ -7131,7 +7084,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G142" s="16" t="n">
+      <c r="G142" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H142" s="6" t="inlineStr">
@@ -7173,7 +7126,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G143" s="16" t="n">
+      <c r="G143" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H143" s="6" t="inlineStr">
@@ -7215,7 +7168,7 @@
           <t>R8.11</t>
         </is>
       </c>
-      <c r="G144" s="16" t="n">
+      <c r="G144" s="15" t="n">
         <v>2</v>
       </c>
       <c r="H144" s="6" t="inlineStr">
@@ -7256,7 +7209,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G145" s="16" t="n">
+      <c r="G145" s="15" t="n">
         <v>1</v>
       </c>
       <c r="H145" s="6" t="inlineStr">
@@ -7299,7 +7252,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G146" s="16" t="n">
+      <c r="G146" s="15" t="n">
         <v>1</v>
       </c>
       <c r="H146" s="6" t="inlineStr">
@@ -7341,7 +7294,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G147" s="16" t="n">
+      <c r="G147" s="15" t="n">
         <v>1</v>
       </c>
       <c r="H147" s="6" t="inlineStr">
@@ -7383,7 +7336,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G148" s="16" t="n">
+      <c r="G148" s="15" t="n">
         <v>1</v>
       </c>
       <c r="H148" s="6" t="inlineStr">
@@ -7425,7 +7378,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G149" s="16" t="n">
+      <c r="G149" s="15" t="n">
         <v>1</v>
       </c>
       <c r="H149" s="6" t="inlineStr">
@@ -7466,7 +7419,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G150" s="16" t="n">
+      <c r="G150" s="15" t="n">
         <v>1</v>
       </c>
       <c r="H150" s="6" t="inlineStr">
@@ -7508,7 +7461,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G151" s="16" t="n">
+      <c r="G151" s="15" t="n">
         <v>1</v>
       </c>
       <c r="H151" s="6" t="inlineStr">
@@ -7550,7 +7503,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G152" s="16" t="n">
+      <c r="G152" s="15" t="n">
         <v>1</v>
       </c>
       <c r="H152" s="6" t="inlineStr">
@@ -7592,7 +7545,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G153" s="16" t="n">
+      <c r="G153" s="15" t="n">
         <v>1</v>
       </c>
       <c r="H153" s="6" t="inlineStr">
@@ -7634,7 +7587,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G154" s="16" t="n">
+      <c r="G154" s="15" t="n">
         <v>1</v>
       </c>
       <c r="H154" s="6" t="inlineStr">
@@ -7676,7 +7629,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G155" s="16" t="n">
+      <c r="G155" s="15" t="n">
         <v>1</v>
       </c>
       <c r="H155" s="6" t="inlineStr">
@@ -7718,7 +7671,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G156" s="16" t="n">
+      <c r="G156" s="15" t="n">
         <v>1</v>
       </c>
       <c r="H156" s="6" t="inlineStr">
@@ -7760,7 +7713,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G157" s="16" t="n">
+      <c r="G157" s="15" t="n">
         <v>1</v>
       </c>
       <c r="H157" s="6" t="inlineStr">
@@ -7801,7 +7754,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G158" s="16" t="n">
+      <c r="G158" s="15" t="n">
         <v>1</v>
       </c>
       <c r="H158" s="6" t="inlineStr">
@@ -7843,7 +7796,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G159" s="16" t="n">
+      <c r="G159" s="15" t="n">
         <v>1</v>
       </c>
       <c r="H159" s="6" t="inlineStr">
@@ -7885,7 +7838,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G160" s="16" t="n">
+      <c r="G160" s="15" t="n">
         <v>1</v>
       </c>
       <c r="H160" s="6" t="inlineStr">
@@ -7927,7 +7880,7 @@
           <t>R8.11</t>
         </is>
       </c>
-      <c r="G161" s="16" t="n">
+      <c r="G161" s="15" t="n">
         <v>1</v>
       </c>
       <c r="H161" s="6" t="inlineStr">
@@ -7969,7 +7922,7 @@
           <t>R8.11</t>
         </is>
       </c>
-      <c r="G162" s="16" t="n">
+      <c r="G162" s="15" t="n">
         <v>1</v>
       </c>
       <c r="H162" s="6" t="inlineStr">
@@ -8011,7 +7964,7 @@
           <t>R9.4</t>
         </is>
       </c>
-      <c r="G163" s="16" t="n">
+      <c r="G163" s="15" t="n">
         <v>1</v>
       </c>
       <c r="H163" s="6" t="inlineStr">
@@ -8053,7 +8006,7 @@
           <t>R8.11</t>
         </is>
       </c>
-      <c r="G164" s="16" t="n">
+      <c r="G164" s="15" t="n">
         <v>0</v>
       </c>
       <c r="H164" s="6" t="inlineStr">
@@ -8095,7 +8048,7 @@
           <t>R8.12</t>
         </is>
       </c>
-      <c r="G165" s="16" t="n">
+      <c r="G165" s="15" t="n">
         <v>0</v>
       </c>
       <c r="H165" s="6" t="inlineStr">
@@ -8110,7 +8063,7 @@
       </c>
     </row>
     <row r="166" ht="56" customHeight="1">
-      <c r="A166" s="14" t="inlineStr">
+      <c r="A166" s="13" t="inlineStr">
         <is>
           <t>注1）点が9以上を至急、6以上8以下を優先、5以下を通常とみます（03シート）。
 注2）「決着しない場合の当方の扱い」が空のものは、決まらないと当方の作業が止まります。 先に扱いを決めます。
@@ -8200,7 +8153,7 @@
           <t>R8.8</t>
         </is>
       </c>
-      <c r="G170" s="17" t="inlineStr">
+      <c r="G170" s="16" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
@@ -8243,7 +8196,7 @@
           <t>R8.8</t>
         </is>
       </c>
-      <c r="G171" s="15" t="inlineStr">
+      <c r="G171" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -8286,7 +8239,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G172" s="15" t="inlineStr">
+      <c r="G172" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -8329,7 +8282,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G173" s="15" t="inlineStr">
+      <c r="G173" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -8372,7 +8325,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G174" s="15" t="inlineStr">
+      <c r="G174" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -8415,7 +8368,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G175" s="15" t="inlineStr">
+      <c r="G175" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -8458,7 +8411,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G176" s="15" t="inlineStr">
+      <c r="G176" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -8501,7 +8454,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G177" s="15" t="inlineStr">
+      <c r="G177" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -8544,7 +8497,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G178" s="15" t="inlineStr">
+      <c r="G178" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -8587,7 +8540,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G179" s="15" t="inlineStr">
+      <c r="G179" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -8630,7 +8583,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G180" s="15" t="inlineStr">
+      <c r="G180" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -8673,7 +8626,7 @@
           <t>告示後</t>
         </is>
       </c>
-      <c r="G181" s="15" t="inlineStr">
+      <c r="G181" s="14" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -8716,7 +8669,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G182" s="16" t="inlineStr">
+      <c r="G182" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -8759,7 +8712,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G183" s="16" t="inlineStr">
+      <c r="G183" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -8802,7 +8755,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G184" s="16" t="inlineStr">
+      <c r="G184" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -8845,7 +8798,7 @@
           <t>随時</t>
         </is>
       </c>
-      <c r="G185" s="16" t="inlineStr">
+      <c r="G185" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -8888,7 +8841,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G186" s="18" t="inlineStr">
+      <c r="G186" s="17" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -8931,7 +8884,7 @@
           <t>公表後</t>
         </is>
       </c>
-      <c r="G187" s="18" t="inlineStr">
+      <c r="G187" s="17" t="inlineStr">
         <is>
           <t>低</t>
         </is>
@@ -8948,7 +8901,7 @@
       </c>
     </row>
     <row r="188" ht="28" customHeight="1">
-      <c r="A188" s="14" t="inlineStr">
+      <c r="A188" s="13" t="inlineStr">
         <is>
           <t>注）03シートの確認事項が「決定」を求めるものであるのに対し、本表は「資料の提供」を求めるものです。資料が届かない場合の扱いは04シートの区分で示しています。</t>
         </is>
@@ -8993,7 +8946,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02シートの点は次の規則だけで付けています。規則を変えれば02シートの並びも変わります。基準日 令和8年10月4日。</t>
+          <t>02シートの点は次の規則だけで付けています。規則を変えれば02シートの並びも変わります。基準日 令和8年10月5日。</t>
         </is>
       </c>
     </row>
@@ -9042,7 +8995,7 @@
           <t>回答期限が基準日の月より前（超過している）</t>
         </is>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="14" t="n">
         <v>2</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -9065,7 +9018,7 @@
           <t>回答期限が基準日と同じ月</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -9088,7 +9041,7 @@
           <t>回答期限が翌月</t>
         </is>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="17" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -9111,7 +9064,7 @@
           <t>概算（第1次・第2次）を止めている</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="16" t="n">
         <v>3</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -9134,7 +9087,7 @@
           <t>保険料に関わるものを止めている</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="14" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -9157,7 +9110,7 @@
           <t>計画素案を止めている</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -9180,7 +9133,7 @@
           <t>据え置きに紐づき月額100円以上を動かし得る</t>
         </is>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="16" t="n">
         <v>4</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -9203,7 +9156,7 @@
           <t>同 50円以上100円未満</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="14" t="n">
         <v>2</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -9226,7 +9179,7 @@
           <t>同 50円未満（効きの記載がある）</t>
         </is>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -9249,7 +9202,7 @@
           <t>介護保険法第117条の記載事項に直結する</t>
         </is>
       </c>
-      <c r="D15" s="15" t="n">
+      <c r="D15" s="14" t="n">
         <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -9272,7 +9225,7 @@
           <t>決着しない場合の当方の扱いを置けていない</t>
         </is>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="16" t="n">
         <v>3</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -9295,7 +9248,7 @@
           <t>国の告示・公布を待つもの（催促できない）</t>
         </is>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="17" t="n">
         <v>-2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -9305,7 +9258,7 @@
       </c>
     </row>
     <row r="18" ht="78" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>注1）「止めている成果物」は重ねて当たることがあるため、合計%d点で頭打ちにしています（概算・保険料・計画素案の全てを止めていても%d点）。
 注2）「月額への効き」は、据え置きの一覧の「効き」の欄に現れる円のうち最も大きいものを採り、紐づく確認事項に割り当てています。据え置きに紐づかない確認事項には点が付きません（効きが無いという意味ではなく、測っていないという意味です）。
@@ -9348,7 +9301,7 @@
       <c r="A22" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>至急</t>
         </is>
@@ -9373,7 +9326,7 @@
       <c r="A23" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>優先</t>
         </is>
@@ -9398,7 +9351,7 @@
       <c r="A24" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
@@ -9454,7 +9407,7 @@
       <c r="A28" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>解消済み</t>
         </is>
@@ -9479,7 +9432,7 @@
       <c r="A29" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B29" s="19" t="inlineStr">
+      <c r="B29" s="18" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -9504,7 +9457,7 @@
       <c r="A30" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -9529,7 +9482,7 @@
       <c r="A31" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>C</t>
         </is>
@@ -9589,7 +9542,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>決定・資料の受領を待たずに当方の作業だけで進められるものです。基準日 令和8年10月4日。</t>
+          <t>決定・資料の受領を待たずに当方の作業だけで進められるものです。基準日 令和8年10月5日。</t>
         </is>
       </c>
     </row>
@@ -9628,7 +9581,7 @@
       <c r="A6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -9653,7 +9606,7 @@
       <c r="A7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -9678,7 +9631,7 @@
       <c r="A8" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -9703,7 +9656,7 @@
       <c r="A9" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -9728,7 +9681,7 @@
       <c r="A10" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -9753,7 +9706,7 @@
       <c r="A11" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -9778,7 +9731,7 @@
       <c r="A12" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -9803,7 +9756,7 @@
       <c r="A13" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -9828,7 +9781,7 @@
       <c r="A14" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -9853,7 +9806,7 @@
       <c r="A15" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -9878,7 +9831,7 @@
       <c r="A16" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -9903,7 +9856,7 @@
       <c r="A17" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -9928,7 +9881,7 @@
       <c r="A18" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -9953,7 +9906,7 @@
       <c r="A19" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -9978,7 +9931,7 @@
       <c r="A20" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10003,7 +9956,7 @@
       <c r="A21" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10028,7 +9981,7 @@
       <c r="A22" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10053,7 +10006,7 @@
       <c r="A23" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10078,7 +10031,7 @@
       <c r="A24" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10103,7 +10056,7 @@
       <c r="A25" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10128,7 +10081,7 @@
       <c r="A26" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10153,7 +10106,7 @@
       <c r="A27" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="20" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10178,7 +10131,7 @@
       <c r="A28" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10203,7 +10156,7 @@
       <c r="A29" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10228,7 +10181,7 @@
       <c r="A30" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10253,7 +10206,7 @@
       <c r="A31" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10278,7 +10231,7 @@
       <c r="A32" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10303,7 +10256,7 @@
       <c r="A33" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B33" s="20" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10328,7 +10281,7 @@
       <c r="A34" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B34" s="20" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10353,7 +10306,7 @@
       <c r="A35" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B35" s="20" t="inlineStr">
+      <c r="B35" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10378,7 +10331,7 @@
       <c r="A36" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B36" s="20" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10403,7 +10356,7 @@
       <c r="A37" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="B37" s="20" t="inlineStr">
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10428,7 +10381,7 @@
       <c r="A38" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B38" s="20" t="inlineStr">
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10453,7 +10406,7 @@
       <c r="A39" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="B39" s="20" t="inlineStr">
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10478,7 +10431,7 @@
       <c r="A40" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B40" s="20" t="inlineStr">
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10503,7 +10456,7 @@
       <c r="A41" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="B41" s="20" t="inlineStr">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10528,7 +10481,7 @@
       <c r="A42" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="B42" s="20" t="inlineStr">
+      <c r="B42" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10553,7 +10506,7 @@
       <c r="A43" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="B43" s="20" t="inlineStr">
+      <c r="B43" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10578,7 +10531,7 @@
       <c r="A44" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B44" s="20" t="inlineStr">
+      <c r="B44" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10603,7 +10556,7 @@
       <c r="A45" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B45" s="20" t="inlineStr">
+      <c r="B45" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10628,7 +10581,7 @@
       <c r="A46" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="B46" s="20" t="inlineStr">
+      <c r="B46" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10653,7 +10606,7 @@
       <c r="A47" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="B47" s="20" t="inlineStr">
+      <c r="B47" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10678,7 +10631,7 @@
       <c r="A48" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="B48" s="20" t="inlineStr">
+      <c r="B48" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10703,7 +10656,7 @@
       <c r="A49" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="B49" s="20" t="inlineStr">
+      <c r="B49" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10728,7 +10681,7 @@
       <c r="A50" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="B50" s="20" t="inlineStr">
+      <c r="B50" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10753,7 +10706,7 @@
       <c r="A51" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="B51" s="20" t="inlineStr">
+      <c r="B51" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10778,7 +10731,7 @@
       <c r="A52" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="B52" s="20" t="inlineStr">
+      <c r="B52" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10803,7 +10756,7 @@
       <c r="A53" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="B53" s="20" t="inlineStr">
+      <c r="B53" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10828,7 +10781,7 @@
       <c r="A54" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="B54" s="20" t="inlineStr">
+      <c r="B54" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10853,7 +10806,7 @@
       <c r="A55" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B55" s="20" t="inlineStr">
+      <c r="B55" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10878,7 +10831,7 @@
       <c r="A56" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="B56" s="20" t="inlineStr">
+      <c r="B56" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10903,7 +10856,7 @@
       <c r="A57" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="B57" s="20" t="inlineStr">
+      <c r="B57" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10928,7 +10881,7 @@
       <c r="A58" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="B58" s="20" t="inlineStr">
+      <c r="B58" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10953,7 +10906,7 @@
       <c r="A59" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="B59" s="20" t="inlineStr">
+      <c r="B59" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -10978,7 +10931,7 @@
       <c r="A60" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="B60" s="20" t="inlineStr">
+      <c r="B60" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11003,7 +10956,7 @@
       <c r="A61" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="B61" s="20" t="inlineStr">
+      <c r="B61" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11028,7 +10981,7 @@
       <c r="A62" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="B62" s="20" t="inlineStr">
+      <c r="B62" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11053,7 +11006,7 @@
       <c r="A63" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="B63" s="20" t="inlineStr">
+      <c r="B63" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11078,7 +11031,7 @@
       <c r="A64" s="5" t="n">
         <v>59</v>
       </c>
-      <c r="B64" s="20" t="inlineStr">
+      <c r="B64" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11103,7 +11056,7 @@
       <c r="A65" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B65" s="20" t="inlineStr">
+      <c r="B65" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11128,7 +11081,7 @@
       <c r="A66" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="B66" s="20" t="inlineStr">
+      <c r="B66" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11153,7 +11106,7 @@
       <c r="A67" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="B67" s="20" t="inlineStr">
+      <c r="B67" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11178,7 +11131,7 @@
       <c r="A68" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="B68" s="20" t="inlineStr">
+      <c r="B68" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11203,7 +11156,7 @@
       <c r="A69" s="5" t="n">
         <v>64</v>
       </c>
-      <c r="B69" s="20" t="inlineStr">
+      <c r="B69" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11228,7 +11181,7 @@
       <c r="A70" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="B70" s="20" t="inlineStr">
+      <c r="B70" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11253,7 +11206,7 @@
       <c r="A71" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="B71" s="20" t="inlineStr">
+      <c r="B71" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11278,7 +11231,7 @@
       <c r="A72" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="B72" s="20" t="inlineStr">
+      <c r="B72" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11303,7 +11256,7 @@
       <c r="A73" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="B73" s="20" t="inlineStr">
+      <c r="B73" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11328,7 +11281,7 @@
       <c r="A74" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="B74" s="20" t="inlineStr">
+      <c r="B74" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11353,7 +11306,7 @@
       <c r="A75" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="B75" s="20" t="inlineStr">
+      <c r="B75" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11378,7 +11331,7 @@
       <c r="A76" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="B76" s="20" t="inlineStr">
+      <c r="B76" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11403,7 +11356,7 @@
       <c r="A77" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="B77" s="20" t="inlineStr">
+      <c r="B77" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11428,7 +11381,7 @@
       <c r="A78" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="B78" s="20" t="inlineStr">
+      <c r="B78" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11453,7 +11406,7 @@
       <c r="A79" s="5" t="n">
         <v>74</v>
       </c>
-      <c r="B79" s="20" t="inlineStr">
+      <c r="B79" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11478,7 +11431,7 @@
       <c r="A80" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="B80" s="20" t="inlineStr">
+      <c r="B80" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11503,7 +11456,7 @@
       <c r="A81" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="B81" s="20" t="inlineStr">
+      <c r="B81" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11528,7 +11481,7 @@
       <c r="A82" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="B82" s="20" t="inlineStr">
+      <c r="B82" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11553,7 +11506,7 @@
       <c r="A83" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="B83" s="20" t="inlineStr">
+      <c r="B83" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11578,7 +11531,7 @@
       <c r="A84" s="5" t="n">
         <v>79</v>
       </c>
-      <c r="B84" s="20" t="inlineStr">
+      <c r="B84" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11603,7 +11556,7 @@
       <c r="A85" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="B85" s="20" t="inlineStr">
+      <c r="B85" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11628,7 +11581,7 @@
       <c r="A86" s="5" t="n">
         <v>81</v>
       </c>
-      <c r="B86" s="20" t="inlineStr">
+      <c r="B86" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11653,7 +11606,7 @@
       <c r="A87" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="B87" s="20" t="inlineStr">
+      <c r="B87" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11678,7 +11631,7 @@
       <c r="A88" s="5" t="n">
         <v>83</v>
       </c>
-      <c r="B88" s="20" t="inlineStr">
+      <c r="B88" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11703,7 +11656,7 @@
       <c r="A89" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="B89" s="20" t="inlineStr">
+      <c r="B89" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11728,7 +11681,7 @@
       <c r="A90" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="B90" s="20" t="inlineStr">
+      <c r="B90" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11753,7 +11706,7 @@
       <c r="A91" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="B91" s="20" t="inlineStr">
+      <c r="B91" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11778,7 +11731,7 @@
       <c r="A92" s="5" t="n">
         <v>87</v>
       </c>
-      <c r="B92" s="20" t="inlineStr">
+      <c r="B92" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11803,7 +11756,7 @@
       <c r="A93" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="B93" s="20" t="inlineStr">
+      <c r="B93" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11828,7 +11781,7 @@
       <c r="A94" s="5" t="n">
         <v>89</v>
       </c>
-      <c r="B94" s="20" t="inlineStr">
+      <c r="B94" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11853,7 +11806,7 @@
       <c r="A95" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="B95" s="20" t="inlineStr">
+      <c r="B95" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11878,7 +11831,7 @@
       <c r="A96" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="B96" s="20" t="inlineStr">
+      <c r="B96" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11903,7 +11856,7 @@
       <c r="A97" s="5" t="n">
         <v>92</v>
       </c>
-      <c r="B97" s="20" t="inlineStr">
+      <c r="B97" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11928,7 +11881,7 @@
       <c r="A98" s="5" t="n">
         <v>93</v>
       </c>
-      <c r="B98" s="20" t="inlineStr">
+      <c r="B98" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11953,7 +11906,7 @@
       <c r="A99" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="B99" s="20" t="inlineStr">
+      <c r="B99" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -11978,7 +11931,7 @@
       <c r="A100" s="5" t="n">
         <v>95</v>
       </c>
-      <c r="B100" s="20" t="inlineStr">
+      <c r="B100" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12003,7 +11956,7 @@
       <c r="A101" s="5" t="n">
         <v>96</v>
       </c>
-      <c r="B101" s="20" t="inlineStr">
+      <c r="B101" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12028,7 +11981,7 @@
       <c r="A102" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="B102" s="20" t="inlineStr">
+      <c r="B102" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12053,7 +12006,7 @@
       <c r="A103" s="5" t="n">
         <v>98</v>
       </c>
-      <c r="B103" s="20" t="inlineStr">
+      <c r="B103" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12078,7 +12031,7 @@
       <c r="A104" s="5" t="n">
         <v>99</v>
       </c>
-      <c r="B104" s="20" t="inlineStr">
+      <c r="B104" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12103,7 +12056,7 @@
       <c r="A105" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="B105" s="20" t="inlineStr">
+      <c r="B105" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12128,7 +12081,7 @@
       <c r="A106" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="B106" s="20" t="inlineStr">
+      <c r="B106" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12153,7 +12106,7 @@
       <c r="A107" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="B107" s="20" t="inlineStr">
+      <c r="B107" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12178,7 +12131,7 @@
       <c r="A108" s="5" t="n">
         <v>103</v>
       </c>
-      <c r="B108" s="20" t="inlineStr">
+      <c r="B108" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12203,7 +12156,7 @@
       <c r="A109" s="5" t="n">
         <v>104</v>
       </c>
-      <c r="B109" s="20" t="inlineStr">
+      <c r="B109" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12228,7 +12181,7 @@
       <c r="A110" s="5" t="n">
         <v>105</v>
       </c>
-      <c r="B110" s="20" t="inlineStr">
+      <c r="B110" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12253,7 +12206,7 @@
       <c r="A111" s="5" t="n">
         <v>106</v>
       </c>
-      <c r="B111" s="20" t="inlineStr">
+      <c r="B111" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12278,7 +12231,7 @@
       <c r="A112" s="5" t="n">
         <v>107</v>
       </c>
-      <c r="B112" s="20" t="inlineStr">
+      <c r="B112" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12303,7 +12256,7 @@
       <c r="A113" s="5" t="n">
         <v>108</v>
       </c>
-      <c r="B113" s="20" t="inlineStr">
+      <c r="B113" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12328,7 +12281,7 @@
       <c r="A114" s="5" t="n">
         <v>109</v>
       </c>
-      <c r="B114" s="20" t="inlineStr">
+      <c r="B114" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12353,7 +12306,7 @@
       <c r="A115" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="B115" s="20" t="inlineStr">
+      <c r="B115" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12378,7 +12331,7 @@
       <c r="A116" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="B116" s="20" t="inlineStr">
+      <c r="B116" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12403,7 +12356,7 @@
       <c r="A117" s="5" t="n">
         <v>112</v>
       </c>
-      <c r="B117" s="20" t="inlineStr">
+      <c r="B117" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12428,7 +12381,7 @@
       <c r="A118" s="5" t="n">
         <v>113</v>
       </c>
-      <c r="B118" s="20" t="inlineStr">
+      <c r="B118" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12453,7 +12406,7 @@
       <c r="A119" s="5" t="n">
         <v>114</v>
       </c>
-      <c r="B119" s="20" t="inlineStr">
+      <c r="B119" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12478,7 +12431,7 @@
       <c r="A120" s="5" t="n">
         <v>115</v>
       </c>
-      <c r="B120" s="20" t="inlineStr">
+      <c r="B120" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12503,7 +12456,7 @@
       <c r="A121" s="5" t="n">
         <v>116</v>
       </c>
-      <c r="B121" s="20" t="inlineStr">
+      <c r="B121" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12528,7 +12481,7 @@
       <c r="A122" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="B122" s="20" t="inlineStr">
+      <c r="B122" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12553,7 +12506,7 @@
       <c r="A123" s="5" t="n">
         <v>118</v>
       </c>
-      <c r="B123" s="20" t="inlineStr">
+      <c r="B123" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12578,7 +12531,7 @@
       <c r="A124" s="5" t="n">
         <v>119</v>
       </c>
-      <c r="B124" s="20" t="inlineStr">
+      <c r="B124" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12603,7 +12556,7 @@
       <c r="A125" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="B125" s="20" t="inlineStr">
+      <c r="B125" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12628,7 +12581,7 @@
       <c r="A126" s="5" t="n">
         <v>121</v>
       </c>
-      <c r="B126" s="20" t="inlineStr">
+      <c r="B126" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12653,7 +12606,7 @@
       <c r="A127" s="5" t="n">
         <v>122</v>
       </c>
-      <c r="B127" s="20" t="inlineStr">
+      <c r="B127" s="19" t="inlineStr">
         <is>
           <t>既定値で進める</t>
         </is>
@@ -12675,7 +12628,7 @@
       </c>
     </row>
     <row r="128" ht="76" customHeight="1">
-      <c r="A128" s="14" t="inlineStr">
+      <c r="A128" s="13" t="inlineStr">
         <is>
           <t>注1）「据え置き（区分A）」は、資料の受領を待たずに当方の側で確定できるものです。
 注2）「既定値で進める」は、決着しない場合の扱いを置けているため決定を待たずに作業を進められるものです。決定を受けた時点で見直します。
@@ -12693,7 +12646,7 @@
       </c>
     </row>
     <row r="131" ht="18" customHeight="1">
-      <c r="A131" s="21" t="inlineStr">
+      <c r="A131" s="20" t="inlineStr">
         <is>
           <t>ありません。未決の確認事項の全件に扱いを置けています。</t>
         </is>
@@ -12731,7 +12684,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>翌日（令和8年10月5日）の作業順位</t>
+          <t>翌日（令和8年10月6日）の作業順位</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12727,7 @@
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>進める</t>
         </is>
@@ -12799,7 +12752,7 @@
       <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>進める</t>
         </is>
@@ -12824,7 +12777,7 @@
       <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>進める</t>
         </is>
@@ -12849,7 +12802,7 @@
       <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>進める</t>
         </is>
@@ -12874,7 +12827,7 @@
       <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>進める</t>
         </is>
@@ -12899,7 +12852,7 @@
       <c r="A10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>進める</t>
         </is>
@@ -12924,7 +12877,7 @@
       <c r="A11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>進める</t>
         </is>
@@ -12949,7 +12902,7 @@
       <c r="A12" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>進める</t>
         </is>
@@ -12974,7 +12927,7 @@
       <c r="A13" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>催促・照会</t>
         </is>
@@ -12999,7 +12952,7 @@
       <c r="A14" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>催促・照会</t>
         </is>
@@ -13024,7 +12977,7 @@
       <c r="A15" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>催促・照会</t>
         </is>
@@ -13046,7 +12999,7 @@
       </c>
     </row>
     <row r="16" ht="62" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>注1）「進める」は決定を待たずに着手できるもの、「催促・照会」は相手のある作業です。相手のある作業は午前のうちに出します（返事に日数がかかるため）。
 注2）04シートの作業継続可能なものは上位8件まで、催促・照会は優先以上の上位5件までを掲げています。残りは02・04シートを見ます。
@@ -13122,7 +13075,7 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="22" t="n">
+      <c r="A5" s="21" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -13140,14 +13093,14 @@
           <t>173件／欠番 なし／重複 なし</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="22" t="n">
+      <c r="A6" s="21" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -13165,14 +13118,14 @@
           <t>確認事項160件／資料提供依頼18件</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="22" t="n">
+      <c r="A7" s="21" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -13190,14 +13143,14 @@
           <t>160件／合わない なし</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="22" t="n">
+      <c r="A8" s="21" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -13215,14 +13168,14 @@
           <t>降順 適合</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="22" t="n">
+      <c r="A9" s="21" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -13240,14 +13193,14 @@
           <t>内訳5種／規則6種／載っていない なし</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="22" t="n">
+      <c r="A10" s="21" t="n">
         <v>5.5</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -13265,14 +13218,14 @@
           <t>7件を拾った（最大327円）／上限超え なし</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="22" t="n">
+      <c r="A11" s="21" t="n">
         <v>6</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -13290,14 +13243,14 @@
           <t>4＋0＋15＋4＝23／据え置き23件</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="22" t="n">
+      <c r="A12" s="21" t="n">
         <v>7</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -13312,17 +13265,17 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>最小0.00・最大0.99・全体79％</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="inlineStr">
+          <t>最小0.12・最大0.94・全体67％</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="22" t="n">
+      <c r="A13" s="21" t="n">
         <v>8</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -13337,17 +13290,17 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>記録 令和8年10月4日／本表 令和8年10月4日</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="inlineStr">
+          <t>記録 令和8年10月5日／本表 令和8年10月5日</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="22" t="n">
+      <c r="A14" s="21" t="n">
         <v>9</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -13362,17 +13315,17 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>記録8件（最新 令和8年9月28日）</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr">
+          <t>記録9件（最新 令和8年9月28日）</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="22" t="n">
+      <c r="A15" s="21" t="n">
         <v>10</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -13390,14 +13343,14 @@
           <t>11件（進める8・催促3）</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="22" t="n">
+      <c r="A16" s="21" t="n">
         <v>11</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -13415,14 +13368,14 @@
           <t>122件（区分A 0・既定値 122）</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="22" t="n">
+      <c r="A17" s="21" t="n">
         <v>12</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -13440,14 +13393,14 @@
           <t>0件</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="22" t="n">
+      <c r="A18" s="21" t="n">
         <v>13</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -13465,14 +13418,14 @@
           <t>0件</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="22" t="n">
+      <c r="A19" s="21" t="n">
         <v>14</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -13490,14 +13443,14 @@
           <t>残り0件</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="22" t="n">
+      <c r="A20" s="21" t="n">
         <v>15</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -13515,26 +13468,26 @@
           <t>台帳にあり／古い記述 なし</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="11" t="inlineStr"/>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr"/>
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>自己点検の結果</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr"/>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr"/>
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>適合16件・不適合0件</t>
         </is>
       </c>
-      <c r="E21" s="24" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -749,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1212,27 +1212,53 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>基準日のコミットはありません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="13" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="4" t="inlineStr"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>コミット</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>749b920</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>業務内容別の進捗を作業項目の達成状況による算定に改め、重大6件を全文掲載</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr"/>
+      <c r="E23" s="6" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A21:F21"/>
   </mergeCells>
@@ -2340,7 +2366,7 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
+          <t>社会資源一覧の従業員数は施設単位の実人数を用い、延べの値は用いない（同一の施設が複数のサービスで登録されている分を除く）。介護人材実態調査の採用者数・離職者数も同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F131"/>
+  <dimension ref="A1:F123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9550,7 +9576,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　当方の作業だけで進められるもの　122件</t>
+          <t>1　当方の作業だけで進められるもの　114件</t>
         </is>
       </c>
     </row>
@@ -9588,17 +9614,17 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階）</t>
+          <t>広域連合において行うべき事業の優先順位</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>第9期条例の16段階・乗率（公費軽減前）を据え置いて算定し、政令の公布後に再算定する</t>
+          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.33（点4）</t>
+          <t>確認事項No.65（点3）</t>
         </is>
       </c>
     </row>
@@ -9613,17 +9639,17 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
+          <t>サービスガイドに掲載する事業所の範囲</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>中間報告・施策体系新旧対照表・骨子案は提出した内容のままとする</t>
+          <t>サービスガイドに掲載する事業所の範囲は北海道の指定事業所一覧（最新のもの）による</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.39（点3）</t>
+          <t>確認事項No.66（点3）</t>
         </is>
       </c>
     </row>
@@ -9638,17 +9664,17 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の扱い</t>
+          <t>算定方法の国の様式との整合（点検結果）</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
+          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.40（点3）</t>
+          <t>確認事項No.67（点3）</t>
         </is>
       </c>
     </row>
@@ -9663,17 +9689,17 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>認定に要する日数の扱い</t>
+          <t>見える化システムの自然体推計の再出力のお願い</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の集計帳票による</t>
+          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.43（点3）</t>
+          <t>確認事項No.68（点3）</t>
         </is>
       </c>
     </row>
@@ -9688,17 +9714,17 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H15の分母の定義</t>
+          <t>交付金の全国順位の計画本文への掲載</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H15の分母は標準給付費見込額とする（受託者案）</t>
+          <t>交付金の全国順位は計画本文に掲載せず、策定委員会資料にとどめる（確認事項No.71のとおり）</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.45（点3）</t>
+          <t>確認事項No.70（点3）</t>
         </is>
       </c>
     </row>
@@ -9713,17 +9739,17 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>計画値を0としたサービスに実績がある2件</t>
+          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>第10期は計画値を0とせず、算定値を置く（対計画比が算出され評価の対象となるようにする）</t>
+          <t>ケアプラン点検実施要領（案）は協議資料にとどめ素案に入れない</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.57（点3）</t>
+          <t>確認事項No.73（点3）</t>
         </is>
       </c>
     </row>
@@ -9738,17 +9764,17 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
+          <t>代表KPIと改善事項の再整理案</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護は自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+          <t>代表KPIと改善事項は当方の再整理案のままとする</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.58（点3）</t>
+          <t>確認事項No.75（点3）</t>
         </is>
       </c>
     </row>
@@ -9763,17 +9789,17 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
+          <t>介護リームスから抽出できる項目</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
+          <t>介護リームスから抽出できないものとして、代表KPI H03は未算定のままとする</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.63（点3）</t>
+          <t>確認事項No.76（点3）</t>
         </is>
       </c>
     </row>
@@ -9788,17 +9814,17 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位</t>
+          <t>北海道の評価指標⑥の団体別の公表値</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
+          <t>北海道の評価指標⑥の団体別の公表値を引用できないものとして、当該指標は計画本文に掲げない</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.65（点3）</t>
+          <t>確認事項No.77（点3）</t>
         </is>
       </c>
     </row>
@@ -9813,17 +9839,17 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>サービスガイドに掲載する事業所の範囲</t>
+          <t>グループホームびえいの郷の定員減の時期</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>サービスガイドに掲載する事業所の範囲は北海道の指定事業所一覧（最新のもの）による</t>
+          <t>北海道の名簿の定員のまま概算する</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.66（点3）</t>
+          <t>確認事項No.78（点3）</t>
         </is>
       </c>
     </row>
@@ -9838,17 +9864,17 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>算定方法の国の様式との整合（点検結果）</t>
+          <t>第5章の施策数の見直しの範囲</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
+          <t>第9期の19施策の体系を維持する（施策数を見直さない）</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.67（点3）</t>
+          <t>確認事項No.79（点3）</t>
         </is>
       </c>
     </row>
@@ -9863,17 +9889,17 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの自然体推計の再出力のお願い</t>
+          <t>代表KPI H16のデータ源（国保連の給付実績の明細情報）</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
+          <t>国保連の給付実績の明細を受領できないものとして、代表KPI H16は地域密着型サービスに限った確認件数を代理指標とする</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.68（点3）</t>
+          <t>確認事項No.81（点3）</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9914,17 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>交付金の全国順位の計画本文への掲載</t>
+          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>交付金の全国順位は計画本文に掲載せず、策定委員会資料にとどめる（確認事項No.71のとおり）</t>
+          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.70（点3）</t>
+          <t>確認事項No.95（点3）</t>
         </is>
       </c>
     </row>
@@ -9913,17 +9939,17 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
+          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）は協議資料にとどめ素案に入れない</t>
+          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.73（点3）</t>
+          <t>確認事項No.96（点3）</t>
         </is>
       </c>
     </row>
@@ -9938,17 +9964,17 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>代表KPIと改善事項の再整理案</t>
+          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>代表KPIと改善事項は当方の再整理案のままとする</t>
+          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.75（点3）</t>
+          <t>確認事項No.102（点3）</t>
         </is>
       </c>
     </row>
@@ -9963,17 +9989,17 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>介護リームスから抽出できる項目</t>
+          <t>地域ケア会議関係資料の取扱いの確認</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>介護リームスから抽出できないものとして、代表KPI H03は未算定のままとする</t>
+          <t>転載を禁ずる旨の記載がある2件は成果品に用いず、原典（厚労省の市町村マニュアル及び別冊事例集）のみを引く</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.76（点3）</t>
+          <t>確認事項No.122（点3）</t>
         </is>
       </c>
     </row>
@@ -9988,17 +10014,17 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥の団体別の公表値</t>
+          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥の団体別の公表値を引用できないものとして、当該指標は計画本文に掲げない</t>
+          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.77（点3）</t>
+          <t>確認事項No.124（点3）</t>
         </is>
       </c>
     </row>
@@ -10013,17 +10039,17 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>グループホームびえいの郷の定員減の時期</t>
+          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>北海道の名簿の定員のまま概算する</t>
+          <t>在宅生活改善調査の結果は「在宅で困難を抱える方の状況」として引き、在宅の認定者全体の割合としては引かない</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.78（点3）</t>
+          <t>確認事項No.140（点3）</t>
         </is>
       </c>
     </row>
@@ -10038,17 +10064,17 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第5章の施策数の見直しの範囲</t>
+          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策の体系を維持する（施策数を見直さない）</t>
+          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.79（点3）</t>
+          <t>確認事項No.149（点3）</t>
         </is>
       </c>
     </row>
@@ -10063,17 +10089,17 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H16のデータ源（国保連の給付実績の明細情報）</t>
+          <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>国保連の給付実績の明細を受領できないものとして、代表KPI H16は地域密着型サービスに限った確認件数を代理指標とする</t>
+          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.81（点3）</t>
+          <t>確認事項No.30（点3）</t>
         </is>
       </c>
     </row>
@@ -10088,17 +10114,17 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
+          <t>第9段階の乗率の経緯</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
+          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.95（点3）</t>
+          <t>確認事項No.34（点3）</t>
         </is>
       </c>
     </row>
@@ -10113,17 +10139,17 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+          <t>上川管内の保険者の所得段階数と乗率</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
+          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.96（点3）</t>
+          <t>確認事項No.35（点3）</t>
         </is>
       </c>
     </row>
@@ -10138,17 +10164,17 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
+          <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
+          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.102（点3）</t>
+          <t>確認事項No.36（点3）</t>
         </is>
       </c>
     </row>
@@ -10163,17 +10189,17 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議関係資料の取扱いの確認</t>
+          <t>令和9年4月に新設される区分を見込量に立てるか</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>転載を禁ずる旨の記載がある2件は成果品に用いず、原典（厚労省の市町村マニュアル及び別冊事例集）のみを引く</t>
+          <t>令和9年4月新設の3区分を0として立てる</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.122（点3）</t>
+          <t>確認事項No.115（点3）</t>
         </is>
       </c>
     </row>
@@ -10188,17 +10214,17 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
+          <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
+          <t>代表KPI H07・H08・H12・H16は代理指標への振替案のとおりとする</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.124（点3）</t>
+          <t>確認事項No.4（点2）</t>
         </is>
       </c>
     </row>
@@ -10213,17 +10239,17 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
+          <t>第9期の施策・事業実績</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果は「在宅で困難を抱える方の状況」として引き、在宅の認定者全体の割合としては引かない</t>
+          <t>第9期の施策・事業実績を受領できないものとして、公表資料（交付金の評価結果・総合事業の実施状況に関する調査・年報）により評価する</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.140（点3）</t>
+          <t>確認事項No.5（点2）</t>
         </is>
       </c>
     </row>
@@ -10238,17 +10264,17 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
+          <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
+          <t>3調査の点検事項は当方の判定のままとする</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.149（点3）</t>
+          <t>確認事項No.8（点2）</t>
         </is>
       </c>
     </row>
@@ -10263,17 +10289,17 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けた要介護度の変化</t>
+          <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
+          <t>会議日程及びパブリックコメントの期間は仕様書５の工程による</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.30（点3）</t>
+          <t>確認事項No.19（点2）</t>
         </is>
       </c>
     </row>
@@ -10288,17 +10314,17 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率の経緯</t>
+          <t>キックオフ会議資料への工程表の反映</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
+          <t>現行の工程表のまま進める</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.34（点3）</t>
+          <t>確認事項No.42（点2）</t>
         </is>
       </c>
     </row>
@@ -10313,17 +10339,17 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
+          <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
+          <t>告示を確認できないものとして、特別地域加算の判定を計画素案に書かず［要確認］のまま残す</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.35（点3）</t>
+          <t>確認事項No.1（点2）</t>
         </is>
       </c>
     </row>
@@ -10338,17 +10364,17 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績と収納率</t>
+          <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
+          <t>類似保険者との比較は公表されている同規模保険者40団体による</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.36（点3）</t>
+          <t>確認事項No.3（点2）</t>
         </is>
       </c>
     </row>
@@ -10363,17 +10389,17 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+          <t>交付金の評価調書</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月新設の3区分を0として立てる</t>
+          <t>評価調書を受領できないものとして、得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できない旨を注記する</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.115（点3）</t>
+          <t>確認事項No.6（点2）</t>
         </is>
       </c>
     </row>
@@ -10388,17 +10414,17 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16の代理指標</t>
+          <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16は代理指標への振替案のとおりとする</t>
+          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.4（点2）</t>
+          <t>確認事項No.9（点2）</t>
         </is>
       </c>
     </row>
@@ -10413,17 +10439,17 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績</t>
+          <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績を受領できないものとして、公表資料（交付金の評価結果・総合事業の実施状況に関する調査・年報）により評価する</t>
+          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.5（点2）</t>
+          <t>確認事項No.10（点2）</t>
         </is>
       </c>
     </row>
@@ -10438,17 +10464,17 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項の取扱い</t>
+          <t>町別の人口・世帯データ</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項は当方の判定のままとする</t>
+          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.8（点2）</t>
+          <t>確認事項No.11（点2）</t>
         </is>
       </c>
     </row>
@@ -10463,17 +10489,17 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>会議日程とパブリックコメントの期間</t>
+          <t>日常生活圏域別のデータ</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>会議日程及びパブリックコメントの期間は仕様書５の工程による</t>
+          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.19（点2）</t>
+          <t>確認事項No.12（点2）</t>
         </is>
       </c>
     </row>
@@ -10488,17 +10514,17 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料への工程表の反映</t>
+          <t>骨子案の内容の確認</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>現行の工程表のまま進める</t>
+          <t>骨子案は提出した内容のままとする</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.42（点2）</t>
+          <t>確認事項No.18（点2）</t>
         </is>
       </c>
     </row>
@@ -10513,17 +10539,17 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>特別地域加算の対象地域告示</t>
+          <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>告示を確認できないものとして、特別地域加算の判定を計画素案に書かず［要確認］のまま残す</t>
+          <t>北海道の評価指標の読替えは当方の案のままとする</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.1（点2）</t>
+          <t>確認事項No.22（点2）</t>
         </is>
       </c>
     </row>
@@ -10538,17 +10564,17 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較分析の対象</t>
+          <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較は公表されている同規模保険者40団体による</t>
+          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.3（点2）</t>
+          <t>確認事項No.27（点2）</t>
         </is>
       </c>
     </row>
@@ -10563,17 +10589,17 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価調書</t>
+          <t>調査対象者の範囲の確認</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>評価調書を受領できないものとして、得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できない旨を注記する</t>
+          <t>現に収録している調査対象者の範囲による</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.6（点2）</t>
+          <t>確認事項No.28（点2）</t>
         </is>
       </c>
     </row>
@@ -10588,17 +10614,17 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>調査の対象者範囲と回収率</t>
+          <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
+          <t>公表されている全国集計の値による</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.9（点2）</t>
+          <t>確認事項No.38（点2）</t>
         </is>
       </c>
     </row>
@@ -10613,17 +10639,17 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>介護人材実態調査の採用者数・退職者数</t>
+          <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
+          <t>令和8年9月25日の再提供により決着済み。再提供を受けたファイルの値（3町合計と円単位一致）による</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.10（点2）</t>
+          <t>確認事項No.46（点2）</t>
         </is>
       </c>
     </row>
@@ -10638,17 +10664,17 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>町別の人口・世帯データ</t>
+          <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
+          <t>総括表（保険者単位）を用い、計画作成支援ツールの実績値シートは比較のためにのみ用いる</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.11（点2）</t>
+          <t>確認事項No.47（点2）</t>
         </is>
       </c>
     </row>
@@ -10663,17 +10689,17 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域別のデータ</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
+          <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値による</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.12（点2）</t>
+          <t>確認事項No.48（点2）</t>
         </is>
       </c>
     </row>
@@ -10688,17 +10714,17 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>骨子案の内容の確認</t>
+          <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>骨子案は提出した内容のままとする</t>
+          <t>受領済みの年報・月報の値による</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.18（点2）</t>
+          <t>確認事項No.50（点2）</t>
         </is>
       </c>
     </row>
@@ -10713,17 +10739,17 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標の読替えの考え方</t>
+          <t>月報の値の接続のずれ（ご報告）</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標の読替えは当方の案のままとする</t>
+          <t>月報の値の接続のずれは記録として残し、計画本文には用いない</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.22（点2）</t>
+          <t>確認事項No.51（点2）</t>
         </is>
       </c>
     </row>
@@ -10738,17 +10764,17 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>令和4年度 健康とくらしの調査の集計表</t>
+          <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
+          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.27（点2）</t>
+          <t>確認事項No.52（点2）</t>
         </is>
       </c>
     </row>
@@ -10763,17 +10789,17 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>調査対象者の範囲の確認</t>
+          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>現に収録している調査対象者の範囲による</t>
+          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合は1億円あたり月額約▲310円となることを併記する</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.28（点2）</t>
+          <t>確認事項No.53（点2）</t>
         </is>
       </c>
     </row>
@@ -10788,17 +10814,17 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の令和6年・令和7年調査の結果</t>
+          <t>議事録の文書プロパティに個人名が再度入る</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>公表されている全国集計の値による</t>
+          <t>議事録は作成者名を落として再出力する（当方で対応する）</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.38（点2）</t>
+          <t>確認事項No.54（点2）</t>
         </is>
       </c>
     </row>
@@ -10813,17 +10839,17 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の給付費の集計が一致しない</t>
+          <t>議事録の表記に関するご提案3件</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月25日の再提供により決着済み。再提供を受けたファイルの値（3町合計と円単位一致）による</t>
+          <t>議事録の表記はご提案3件のとおり改める</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.46（点2）</t>
+          <t>確認事項No.55（点2）</t>
         </is>
       </c>
     </row>
@@ -10838,17 +10864,17 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの実績値シートの確認</t>
+          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>総括表（保険者単位）を用い、計画作成支援ツールの実績値シートは比較のためにのみ用いる</t>
+          <t>他団体の集計帳票6件は成果品に用いない</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.47（点2）</t>
+          <t>確認事項No.56（点2）</t>
         </is>
       </c>
     </row>
@@ -10863,17 +10889,17 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
+          <t>調整交付金の算定基礎の確認</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値による</t>
+          <t>現行の扱い（第9期の算定を再現し公表値6,428円と一致する扱い）による</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.48（点2）</t>
+          <t>確認事項No.59（点2）</t>
         </is>
       </c>
     </row>
@@ -10888,17 +10914,17 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>年報・月報の受領に伴う確認</t>
+          <t>交付金の評価項目と19施策の割当て</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>受領済みの年報・月報の値による</t>
+          <t>交付金の評価項目と19施策の割当ては当方の案のままとする</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.50（点2）</t>
+          <t>確認事項No.61（点2）</t>
         </is>
       </c>
     </row>
@@ -10913,17 +10939,17 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれ（ご報告）</t>
+          <t>職員個票のリストによる重複確認の可否</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれは記録として残し、計画本文には用いない</t>
+          <t>職員個票を突き合わせず、事業所への照会により重複を判別する</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.51（点2）</t>
+          <t>確認事項No.80（点2）</t>
         </is>
       </c>
     </row>
@@ -10938,17 +10964,17 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領に伴う確認</t>
+          <t>構成町との意見交換会の実施方法と町別データシート</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
+          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで進める</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.52（点2）</t>
+          <t>確認事項No.83（点2）</t>
         </is>
       </c>
     </row>
@@ -10963,17 +10989,17 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
+          <t>町別データシートの内容と配付</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合は1億円あたり月額約▲310円となることを併記する</t>
+          <t>町別データシートは現行の内容のまま配付する</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.53（点2）</t>
+          <t>確認事項No.85（点2）</t>
         </is>
       </c>
     </row>
@@ -10988,17 +11014,17 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>議事録の文書プロパティに個人名が再度入る</t>
+          <t>成果品の統合の方針</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>議事録は作成者名を落として再出力する（当方で対応する）</t>
+          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す（現行）</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.54（点2）</t>
+          <t>確認事項No.117（点2）</t>
         </is>
       </c>
     </row>
@@ -11013,17 +11039,17 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記に関するご提案3件</t>
+          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記はご提案3件のとおり改める</t>
+          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.55（点2）</t>
+          <t>確認事項No.138（点2）</t>
         </is>
       </c>
     </row>
@@ -11038,17 +11064,17 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
+          <t>健康とくらしの調査の個票の再提供の要否</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>他団体の集計帳票6件は成果品に用いない</t>
+          <t>健康とくらしの調査の個票の再提供を依頼しない（成果品は収録済みで内容が確定しており、現時点で不足がない）</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.56（点2）</t>
+          <t>確認事項No.139（点2）</t>
         </is>
       </c>
     </row>
@@ -11063,17 +11089,17 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>調整交付金の算定基礎の確認</t>
+          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>現行の扱い（第9期の算定を再現し公表値6,428円と一致する扱い）による</t>
+          <t>受領済みの画面の写しの範囲で概算し、確認できていない項目はその旨を明記する</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.59（点2）</t>
+          <t>確認事項No.148（点2）</t>
         </is>
       </c>
     </row>
@@ -11088,17 +11114,17 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当て</t>
+          <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当ては当方の案のままとする</t>
+          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.61（点2）</t>
+          <t>確認事項No.60（点2）</t>
         </is>
       </c>
     </row>
@@ -11113,17 +11139,17 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>職員個票のリストによる重複確認の可否</t>
+          <t>区域内に事業所がないサービスの住民向けの記載</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>職員個票を突き合わせず、事業所への照会により重複を判別する</t>
+          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.80（点2）</t>
+          <t>確認事項No.64（点2）</t>
         </is>
       </c>
     </row>
@@ -11138,17 +11164,17 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>構成町との意見交換会の実施方法と町別データシート</t>
+          <t>成果指向型配分枠（令和8年度新設）への対応</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで進める</t>
+          <t>成果指向型配分枠への対応状況を確認できないものとして、第10期の施策には位置づけず、確認でき次第加える</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.83（点2）</t>
+          <t>確認事項No.69（点2）</t>
         </is>
       </c>
     </row>
@@ -11163,17 +11189,17 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>町別データシートの内容と配付</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>町別データシートは現行の内容のまま配付する</t>
+          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.85（点2）</t>
+          <t>確認事項No.89（点2）</t>
         </is>
       </c>
     </row>
@@ -11188,17 +11214,17 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>成果品の統合の方針</t>
+          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す（現行）</t>
+          <t>第9期計画の本文及び前回調査の原集計表を受領できないものとして、前回調査との比較は割合のみとし、指標別の分母を確認できない旨を注記する</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.117（点2）</t>
+          <t>確認事項No.90（点2）</t>
         </is>
       </c>
     </row>
@@ -11213,17 +11239,17 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
+          <t>介護給付費通知及び給付実績の活用による確認等</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ</t>
+          <t>介護給付費通知の実施状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.138（点2）</t>
+          <t>確認事項No.91（点2）</t>
         </is>
       </c>
     </row>
@@ -11238,17 +11264,17 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供の要否</t>
+          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供を依頼しない（成果品は収録済みで内容が確定しており、現時点で不足がない）</t>
+          <t>認定調査の委託の状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.139（点2）</t>
+          <t>確認事項No.92（点2）</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11289,17 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
+          <t>令和9年4月1日から義務となる2件への対応</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>受領済みの画面の写しの範囲で概算し、確認できていない項目はその旨を明記する</t>
+          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.148（点2）</t>
+          <t>確認事項No.97（点2）</t>
         </is>
       </c>
     </row>
@@ -11288,17 +11314,17 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提（受託者案）</t>
+          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
+          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.60（点2）</t>
+          <t>確認事項No.99（点2）</t>
         </is>
       </c>
     </row>
@@ -11313,17 +11339,17 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスの住民向けの記載</t>
+          <t>補正しても外れるサービス6件の理由</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
+          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.64（点2）</t>
+          <t>確認事項No.108（点2）</t>
         </is>
       </c>
     </row>
@@ -11338,17 +11364,17 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠（令和8年度新設）への対応</t>
+          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠への対応状況を確認できないものとして、第10期の施策には位置づけず、確認でき次第加える</t>
+          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.69（点2）</t>
+          <t>確認事項No.111（点2）</t>
         </is>
       </c>
     </row>
@@ -11363,17 +11389,17 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
+          <t>施策2-5の代表KPIはO2（提起された地域課題のうち翌年度の事業・予算に反映されたものの割合）とする（当方案）</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.89（点2）</t>
+          <t>確認事項No.118（点2）</t>
         </is>
       </c>
     </row>
@@ -11388,17 +11414,17 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
+          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文及び前回調査の原集計表を受領できないものとして、前回調査との比較は割合のみとし、指標別の分母を確認できない旨を注記する</t>
+          <t>地域ケア会議の記録様式は協議資料にとどめ、令和9年度に整える</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.90（点2）</t>
+          <t>確認事項No.119（点2）</t>
         </is>
       </c>
     </row>
@@ -11413,17 +11439,17 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知及び給付実績の活用による確認等</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知の実施状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.91（点2）</t>
+          <t>確認事項No.120（点2）</t>
         </is>
       </c>
     </row>
@@ -11438,17 +11464,17 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
+          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>認定調査の委託の状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
+          <t>令和7年度の実施報告書により把握できる範囲で記述する</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.92（点2）</t>
+          <t>確認事項No.121（点2）</t>
         </is>
       </c>
     </row>
@@ -11463,17 +11489,17 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月1日から義務となる2件への対応</t>
+          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
+          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.97（点2）</t>
+          <t>確認事項No.125（点2）</t>
         </is>
       </c>
     </row>
@@ -11488,17 +11514,17 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
+          <t>見える化システムの総人口の設定を案Cに改めるか</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
+          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.99（点2）</t>
+          <t>確認事項No.127（点2）</t>
         </is>
       </c>
     </row>
@@ -11513,17 +11539,17 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れるサービス6件の理由</t>
+          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
+          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.108（点2）</t>
+          <t>確認事項No.133（点2）</t>
         </is>
       </c>
     </row>
@@ -11538,17 +11564,17 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
+          <t>画面の令和7年度と年報の月平均の食い違い</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
+          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.111（点2）</t>
+          <t>確認事項No.136（点2）</t>
         </is>
       </c>
     </row>
@@ -11563,17 +11589,17 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
+          <t>計画素案の未確定箇所の表示の統一</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIはO2（提起された地域課題のうち翌年度の事業・予算に反映されたものの割合）とする（当方案）</t>
+          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとする</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.118（点2）</t>
+          <t>確認事項No.143（点2）</t>
         </is>
       </c>
     </row>
@@ -11588,17 +11614,17 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
+          <t>計画素案 第2章第1節に町別の図を加えるか</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の記録様式は協議資料にとどめ、令和9年度に整える</t>
+          <t>計画素案 第2章第1節に町別の図を加えない。加筆分は協議用の資料にとどめる</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.119（点2）</t>
+          <t>確認事項No.154（点2）</t>
         </is>
       </c>
     </row>
@@ -11613,17 +11639,17 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
+          <t>中長期推計を令和12・27・32年度まで広げるか</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
+          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.120（点2）</t>
+          <t>確認事項No.157（点2）</t>
         </is>
       </c>
     </row>
@@ -11638,17 +11664,17 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
+          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の実施報告書により把握できる範囲で記述する</t>
+          <t>設問ごとの有効回答を分母とし、町別の値は掲げない（令和8年9月25日に是正済み）</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.121（点2）</t>
+          <t>確認事項No.158（点2）</t>
         </is>
       </c>
     </row>
@@ -11663,17 +11689,17 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
+          <t>東川町の通いの場の整備と担い手の確保</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
+          <t>現状のまま（東川町の整備を見込まない）第10期の目標値を置く</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.125（点2）</t>
+          <t>確認事項No.159（点2）</t>
         </is>
       </c>
     </row>
@@ -11688,17 +11714,17 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総人口の設定を案Cに改めるか</t>
+          <t>東川町の認知症サポーター養成講座の実施状況</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
+          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.127（点2）</t>
+          <t>確認事項No.160（点2）</t>
         </is>
       </c>
     </row>
@@ -11713,17 +11739,17 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+          <t>東川町のチームオレンジ事業の位置づけ</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
+          <t>東川町の取組として記述し3町展開は記述しない</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.133（点2）</t>
+          <t>確認事項No.161（点2）</t>
         </is>
       </c>
     </row>
@@ -11738,17 +11764,17 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度と年報の月平均の食い違い</t>
+          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
+          <t>令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.136（点2）</t>
+          <t>確認事項No.162（点2）</t>
         </is>
       </c>
     </row>
@@ -11763,17 +11789,17 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所の表示の統一</t>
+          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとする</t>
+          <t>美瑛町の取組として記述し3町展開は記述しない</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.143（点2）</t>
+          <t>確認事項No.163（点2）</t>
         </is>
       </c>
     </row>
@@ -11788,17 +11814,17 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えるか</t>
+          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えない。加筆分は協議用の資料にとどめる</t>
+          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.154（点2）</t>
+          <t>確認事項No.164（点2）</t>
         </is>
       </c>
     </row>
@@ -11813,17 +11839,17 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>中長期推計を令和12・27・32年度まで広げるか</t>
+          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
+          <t>現に確認できる取組の範囲で記述する</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.157（点2）</t>
+          <t>確認事項No.165（点2）</t>
         </is>
       </c>
     </row>
@@ -11838,17 +11864,17 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
+          <t>東神楽町の通いの場の維持</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>設問ごとの有効回答を分母とし、町別の値は掲げない（令和8年9月25日に是正済み）</t>
+          <t>令和6年度の水準が続くものとして目標値を置く</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.158（点2）</t>
+          <t>確認事項No.166（点2）</t>
         </is>
       </c>
     </row>
@@ -11863,17 +11889,17 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>東川町の通いの場の整備と担い手の確保</t>
+          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>現状のまま（東川町の整備を見込まない）第10期の目標値を置く</t>
+          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.159（点2）</t>
+          <t>確認事項No.167（点2）</t>
         </is>
       </c>
     </row>
@@ -11888,17 +11914,17 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>東川町の認知症サポーター養成講座の実施状況</t>
+          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
+          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.160（点2）</t>
+          <t>確認事項No.170（点2）</t>
         </is>
       </c>
     </row>
@@ -11913,17 +11939,17 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>東川町のチームオレンジ事業の位置づけ</t>
+          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>東川町の取組として記述し3町展開は記述しない</t>
+          <t>の当方の扱い＝掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.161（点2）</t>
+          <t>確認事項No.172（点2）</t>
         </is>
       </c>
     </row>
@@ -11938,17 +11964,17 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
+          <t>保険料算定の前提</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残す</t>
+          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.162（点2）</t>
+          <t>確認事項No.16（点2）</t>
         </is>
       </c>
     </row>
@@ -11963,17 +11989,17 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
+          <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の取組として記述し3町展開は記述しない</t>
+          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.163（点2）</t>
+          <t>確認事項No.2（点1）</t>
         </is>
       </c>
     </row>
@@ -11988,17 +12014,17 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
+          <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
+          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.164（点2）</t>
+          <t>確認事項No.13（点1）</t>
         </is>
       </c>
     </row>
@@ -12013,17 +12039,17 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
+          <t>人口推計の基礎とする系列</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述する</t>
+          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.165（点2）</t>
+          <t>確認事項No.14（点1）</t>
         </is>
       </c>
     </row>
@@ -12038,17 +12064,17 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の通いの場の維持</t>
+          <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の水準が続くものとして目標値を置く</t>
+          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.166（点2）</t>
+          <t>確認事項No.15（点1）</t>
         </is>
       </c>
     </row>
@@ -12063,17 +12089,17 @@
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
+          <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
+          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.167（点2）</t>
+          <t>確認事項No.17（点1）</t>
         </is>
       </c>
     </row>
@@ -12088,17 +12114,17 @@
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
+          <t>北海道・圏域との調整の場</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
+          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.170（点2）</t>
+          <t>確認事項No.20（点1）</t>
         </is>
       </c>
     </row>
@@ -12113,17 +12139,17 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
+          <t>成果品の仕様</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>の当方の扱い＝掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
+          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.172（点2）</t>
+          <t>確認事項No.21（点1）</t>
         </is>
       </c>
     </row>
@@ -12138,17 +12164,17 @@
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提</t>
+          <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
+          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.16（点2）</t>
+          <t>確認事項No.23（点1）</t>
         </is>
       </c>
     </row>
@@ -12163,17 +12189,17 @@
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
+          <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
+          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.2（点1）</t>
+          <t>確認事項No.26（点1）</t>
         </is>
       </c>
     </row>
@@ -12188,17 +12214,17 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域の判定資料</t>
+          <t>重度化の速度の前提</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
+          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.13（点1）</t>
+          <t>確認事項No.29（点1）</t>
         </is>
       </c>
     </row>
@@ -12213,17 +12239,17 @@
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎とする系列</t>
+          <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
+          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.14（点1）</t>
+          <t>確認事項No.31（点1）</t>
         </is>
       </c>
     </row>
@@ -12238,17 +12264,17 @@
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>認定者数の基準月と月次推移</t>
+          <t>統合した成果品の元の資料を残すか</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
+          <t>統合した成果品の元の資料を残す</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.15（点1）</t>
+          <t>確認事項No.144（点1）</t>
         </is>
       </c>
     </row>
@@ -12263,17 +12289,17 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>3町計画への共通指標の掲載</t>
+          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
+          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.17（点1）</t>
+          <t>確認事項No.156（点1）</t>
         </is>
       </c>
     </row>
@@ -12288,17 +12314,17 @@
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場</t>
+          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
+          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.20（点1）</t>
+          <t>確認事項No.169（点1）</t>
         </is>
       </c>
     </row>
@@ -12313,17 +12339,17 @@
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様</t>
+          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
+          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.21（点1）</t>
+          <t>確認事項No.171（点1）</t>
         </is>
       </c>
     </row>
@@ -12338,17 +12364,17 @@
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>事業所の定員・稼働率データ</t>
+          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
+          <t>の当方の扱い＝現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.23（点1）</t>
+          <t>確認事項No.173（点1）</t>
         </is>
       </c>
     </row>
@@ -12363,17 +12389,17 @@
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>認知症・医療介護連携の実績データ</t>
+          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
+          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.26（点1）</t>
+          <t>確認事項No.74（点1）</t>
         </is>
       </c>
     </row>
@@ -12388,17 +12414,17 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提</t>
+          <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
+          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.29（点1）</t>
+          <t>確認事項No.24（点0）</t>
         </is>
       </c>
     </row>
@@ -12413,240 +12439,40 @@
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の実施予定と推計での扱い</t>
+          <t>代表KPIの目標値の決定</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
+          <t>代表KPIの目標値は、令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置く</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.31（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="44" customHeight="1">
-      <c r="A120" s="5" t="n">
-        <v>115</v>
-      </c>
-      <c r="B120" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>統合した成果品の元の資料を残すか</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>統合した成果品の元の資料を残す</t>
-        </is>
-      </c>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.144（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="44" customHeight="1">
-      <c r="A121" s="5" t="n">
-        <v>116</v>
-      </c>
-      <c r="B121" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.156（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="44" customHeight="1">
-      <c r="A122" s="5" t="n">
-        <v>117</v>
-      </c>
-      <c r="B122" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.169（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="44" customHeight="1">
-      <c r="A123" s="5" t="n">
-        <v>118</v>
-      </c>
-      <c r="B123" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
-        </is>
-      </c>
-      <c r="E123" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.171（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="44" customHeight="1">
-      <c r="A124" s="5" t="n">
-        <v>119</v>
-      </c>
-      <c r="B124" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>の当方の扱い＝現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
-        </is>
-      </c>
-      <c r="E124" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.173（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="44" customHeight="1">
-      <c r="A125" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="B125" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
-        </is>
-      </c>
-      <c r="E125" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.74（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="44" customHeight="1">
-      <c r="A126" s="5" t="n">
-        <v>121</v>
-      </c>
-      <c r="B126" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>24時間対応サービスの確保方策の決定</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
-        </is>
-      </c>
-      <c r="E126" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.24（点0）</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="44" customHeight="1">
-      <c r="A127" s="5" t="n">
-        <v>122</v>
-      </c>
-      <c r="B127" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>代表KPIの目標値の決定</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t>代表KPIの目標値は、令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置く</t>
-        </is>
-      </c>
-      <c r="E127" s="6" t="inlineStr">
-        <is>
           <t>確認事項No.25（点0）</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="76" customHeight="1">
-      <c r="A128" s="13" t="inlineStr">
+    <row r="120" ht="76" customHeight="1">
+      <c r="A120" s="13" t="inlineStr">
         <is>
           <t>注1）「据え置き（区分A）」は、資料の受領を待たずに当方の側で確定できるものです。
 注2）「既定値で進める」は、決着しない場合の扱いを置けているため決定を待たずに作業を進められるものです。決定を受けた時点で見直します。
 注3）ここに現れないもの（既定値を置けていない確認事項）は、扱いを決めること自体が翌日の作業になります。02シートを見ます。
-注4）既定値のとおり計画素案へ反映し終えたもの38件（確認事項No.7・No.82・No.84・No.86・No.88・No.93・No.94・No.98・No.100・No.101・No.103・No.104・No.105・No.106・No.107・No.109・No.110・No.112・No.113・No.114・No.116・No.123・No.126・No.128・No.129・No.130・No.131・No.132・No.137・No.141・No.142・No.145・No.146・No.147・No.150・No.151・No.152・No.153）は、作業としては終わっているため本表から除いています。ご決定はなお待っています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="129"/>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="3" t="inlineStr">
+注4）既定値のとおり計画素案へ反映し終えたもの46件（確認事項No.7・No.33・No.39・No.40・No.43・No.45・No.57・No.58・No.63・No.82・No.84・No.86・No.88・No.93・No.94・No.98・No.100・No.101・No.103・No.104・No.105・No.106・No.107・No.109・No.110・No.112・No.113・No.114・No.116・No.123・No.126・No.128・No.129・No.130・No.131・No.132・No.137・No.141・No.142・No.145・No.146・No.147・No.150・No.151・No.152・No.153）は、作業としては終わっているため本表から除いています。ご決定はなお待っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121"/>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="3" t="inlineStr">
         <is>
           <t>2　先に扱いを決めるもの（既定値を置けていない）　0件</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="18" customHeight="1">
-      <c r="A131" s="20" t="inlineStr">
+    <row r="123" ht="18" customHeight="1">
+      <c r="A123" s="20" t="inlineStr">
         <is>
           <t>ありません。未決の確認事項の全件に扱いを置けています。</t>
         </is>
@@ -12654,12 +12480,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A122:E122"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A131:E131"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A128:E128"/>
-    <mergeCell ref="A130:E130"/>
+    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A120:E120"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12734,17 +12560,17 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階）</t>
+          <t>広域連合において行うべき事業の優先順位</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>第9期条例の16段階・乗率（公費軽減前）を据え置いて算定し、政令の公布後に再算定する</t>
+          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.33（点4）</t>
+          <t>確認事項No.65（点3）</t>
         </is>
       </c>
     </row>
@@ -12759,17 +12585,17 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
+          <t>サービスガイドに掲載する事業所の範囲</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>中間報告・施策体系新旧対照表・骨子案は提出した内容のままとする</t>
+          <t>サービスガイドに掲載する事業所の範囲は北海道の指定事業所一覧（最新のもの）による</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.39（点3）</t>
+          <t>確認事項No.66（点3）</t>
         </is>
       </c>
     </row>
@@ -12784,17 +12610,17 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の扱い</t>
+          <t>算定方法の国の様式との整合（点検結果）</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
+          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.40（点3）</t>
+          <t>確認事項No.67（点3）</t>
         </is>
       </c>
     </row>
@@ -12809,17 +12635,17 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>認定に要する日数の扱い</t>
+          <t>見える化システムの自然体推計の再出力のお願い</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の集計帳票による</t>
+          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.43（点3）</t>
+          <t>確認事項No.68（点3）</t>
         </is>
       </c>
     </row>
@@ -12834,17 +12660,17 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H15の分母の定義</t>
+          <t>交付金の全国順位の計画本文への掲載</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H15の分母は標準給付費見込額とする（受託者案）</t>
+          <t>交付金の全国順位は計画本文に掲載せず、策定委員会資料にとどめる（確認事項No.71のとおり）</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.45（点3）</t>
+          <t>確認事項No.70（点3）</t>
         </is>
       </c>
     </row>
@@ -12859,17 +12685,17 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>計画値を0としたサービスに実績がある2件</t>
+          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>第10期は計画値を0とせず、算定値を置く（対計画比が算出され評価の対象となるようにする）</t>
+          <t>ケアプラン点検実施要領（案）は協議資料にとどめ素案に入れない</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.57（点3）</t>
+          <t>確認事項No.73（点3）</t>
         </is>
       </c>
     </row>
@@ -12884,17 +12710,17 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
+          <t>代表KPIと改善事項の再整理案</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護は自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+          <t>代表KPIと改善事項は当方の再整理案のままとする</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.58（点3）</t>
+          <t>確認事項No.75（点3）</t>
         </is>
       </c>
     </row>
@@ -12909,17 +12735,17 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
+          <t>介護リームスから抽出できる項目</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
+          <t>介護リームスから抽出できないものとして、代表KPI H03は未算定のままとする</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.63（点3）</t>
+          <t>確認事項No.76（点3）</t>
         </is>
       </c>
     </row>
@@ -13365,7 +13191,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>122件（区分A 0・既定値 122）</t>
+          <t>114件（区分A 0・既定値 114）</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -749,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1234,20 +1234,38 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>749b920</t>
+          <t>413f8b9</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>業務内容別の進捗を作業項目の達成状況による算定に改め、重大6件を全文掲載</t>
+          <t>優先順位上位8件を既定値のとおり計画素案へ反映</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
       <c r="E23" s="6" t="inlineStr"/>
       <c r="F23" s="6" t="inlineStr"/>
     </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>749b920</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>業務内容別の進捗を作業項目の達成状況による算定に改め、重大6件を全文掲載</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
@@ -1255,12 +1273,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -749,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>413f8b9</t>
+          <t>02c7102</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>優先順位上位8件を既定値のとおり計画素案へ反映</t>
+          <t>人口推計コーホート分析の妥当性検証と受領資料の取込み</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
@@ -1252,20 +1252,38 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>749b920</t>
+          <t>413f8b9</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>業務内容別の進捗を作業項目の達成状況による算定に改め、重大6件を全文掲載</t>
+          <t>優先順位上位8件を既定値のとおり計画素案へ反映</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
       <c r="E24" s="6" t="inlineStr"/>
       <c r="F24" s="6" t="inlineStr"/>
     </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>749b920</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>業務内容別の進捗を作業項目の達成状況による算定に改め、重大6件を全文掲載</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
@@ -1277,8 +1295,8 @@
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1290,7 +1308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I188"/>
+  <dimension ref="A1:I189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1322,7 +1340,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　確認事項（決定を求めるもの）　160件</t>
+          <t>1　確認事項（決定を求めるもの）　161件</t>
         </is>
       </c>
     </row>
@@ -7189,17 +7207,18 @@
         <v>139</v>
       </c>
       <c r="B144" s="5" t="n">
-        <v>16</v>
+        <v>174</v>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提</t>
+          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第3節・第6節
-保険料算定表</t>
+          <t>人口推計コーホート分析の妥当性検証 07シート
+見える化へ入力する箇所と入力値 02シート
+計画素案 第2章第1節・第6章第1節</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -7209,7 +7228,7 @@
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G144" s="15" t="n">
@@ -7217,12 +7236,12 @@
       </c>
       <c r="H144" s="6" t="inlineStr">
         <is>
-          <t>止めている成果物 保険料（+2）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
+          <t>の当方の扱い＝案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
         </is>
       </c>
     </row>
@@ -7231,39 +7250,40 @@
         <v>140</v>
       </c>
       <c r="B145" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>保険料算定の前提</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>素案 第6章第3節・第6節
+保険料算定表</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G145" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C145" s="6" t="inlineStr">
-        <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
-        </is>
-      </c>
-      <c r="D145" s="6" t="inlineStr">
-        <is>
-          <t>素案 第1章第9節・第6章第4節</t>
-        </is>
-      </c>
-      <c r="E145" s="5" t="inlineStr">
-        <is>
-          <t>北海道</t>
-        </is>
-      </c>
-      <c r="F145" s="5" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G145" s="15" t="n">
-        <v>1</v>
-      </c>
       <c r="H145" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）</t>
+          <t>止めている成果物 保険料（+2）</t>
         </is>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
+          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
         </is>
       </c>
     </row>
@@ -7272,62 +7292,61 @@
         <v>141</v>
       </c>
       <c r="B146" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>特定地域の指定に係る意向表明の手続</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>素案 第1章第9節・第6章第4節</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G146" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" s="6" t="inlineStr">
+        <is>
+          <t>期限 当月（R8.10）（+1）</t>
+        </is>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="48" customHeight="1">
+      <c r="A147" s="5" t="n">
+        <v>142</v>
+      </c>
+      <c r="B147" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="C146" s="6" t="inlineStr">
+      <c r="C147" s="6" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
-      <c r="D146" s="6" t="inlineStr">
+      <c r="D147" s="6" t="inlineStr">
         <is>
           <t>素案 第1章第7節
 追加調査報告書 03シート
 住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
-      <c r="E146" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F146" s="5" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G146" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H146" s="6" t="inlineStr">
-        <is>
-          <t>期限 当月（R8.10）（+1）</t>
-        </is>
-      </c>
-      <c r="I146" s="6" t="inlineStr">
-        <is>
-          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="48" customHeight="1">
-      <c r="A147" s="5" t="n">
-        <v>142</v>
-      </c>
-      <c r="B147" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C147" s="6" t="inlineStr">
-        <is>
-          <t>人口推計の基礎とする系列</t>
-        </is>
-      </c>
-      <c r="D147" s="6" t="inlineStr">
-        <is>
-          <t>素案 第6章第1節
-将来推計</t>
-        </is>
-      </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
@@ -7348,7 +7367,7 @@
       </c>
       <c r="I147" s="6" t="inlineStr">
         <is>
-          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
+          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
         </is>
       </c>
     </row>
@@ -7357,11 +7376,11 @@
         <v>143</v>
       </c>
       <c r="B148" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>認定者数の基準月と月次推移</t>
+          <t>人口推計の基礎とする系列</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
@@ -7372,7 +7391,7 @@
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
@@ -7390,7 +7409,7 @@
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
-          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
+          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
         </is>
       </c>
     </row>
@@ -7399,22 +7418,22 @@
         <v>144</v>
       </c>
       <c r="B149" s="5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>3町計画への共通指標の掲載</t>
+          <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr">
         <is>
-          <t>素案 資料2
-3町協議資料</t>
+          <t>素案 第6章第1節
+将来推計</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
@@ -7432,7 +7451,7 @@
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
-          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
+          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
         </is>
       </c>
     </row>
@@ -7441,21 +7460,22 @@
         <v>145</v>
       </c>
       <c r="B150" s="5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場</t>
+          <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第4節</t>
+          <t>素案 資料2
+3町協議資料</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
@@ -7473,7 +7493,7 @@
       </c>
       <c r="I150" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
+          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
         </is>
       </c>
     </row>
@@ -7482,22 +7502,21 @@
         <v>146</v>
       </c>
       <c r="B151" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様</t>
+          <t>北海道・圏域との調整の場</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr">
         <is>
-          <t>計画書（印刷200部）
-概要版</t>
+          <t>素案 第6章第4節</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
@@ -7515,7 +7534,7 @@
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
+          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
         </is>
       </c>
     </row>
@@ -7524,22 +7543,22 @@
         <v>147</v>
       </c>
       <c r="B152" s="5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>事業所の定員・稼働率データ</t>
+          <t>成果品の仕様</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第3節・第6章第4節
-図21・図22</t>
+          <t>計画書（印刷200部）
+概要版</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
@@ -7557,7 +7576,7 @@
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
-          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
+          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
         </is>
       </c>
     </row>
@@ -7566,22 +7585,22 @@
         <v>148</v>
       </c>
       <c r="B153" s="5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>認知症・医療介護連携の実績データ</t>
+          <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
       <c r="D153" s="6" t="inlineStr">
         <is>
-          <t>素案 第5章 基本目標1・5
-図表集 認知症・医療連携</t>
+          <t>素案 第2章第3節・第6章第4節
+図21・図22</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
@@ -7599,7 +7618,7 @@
       </c>
       <c r="I153" s="6" t="inlineStr">
         <is>
-          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
+          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
         </is>
       </c>
     </row>
@@ -7608,22 +7627,22 @@
         <v>149</v>
       </c>
       <c r="B154" s="5" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提</t>
+          <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第1節
-認定者数・給付費の推計</t>
+          <t>素案 第5章 基本目標1・5
+図表集 認知症・医療連携</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町・北海道</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
@@ -7641,7 +7660,7 @@
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
+          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
         </is>
       </c>
     </row>
@@ -7650,17 +7669,17 @@
         <v>150</v>
       </c>
       <c r="B155" s="5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の実施予定と推計での扱い</t>
+          <t>重度化の速度の前提</t>
         </is>
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第2節・第5章・第7章
-給付費の推計</t>
+          <t>素案 第6章第1節
+認定者数・給付費の推計</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -7683,7 +7702,7 @@
       </c>
       <c r="I155" s="6" t="inlineStr">
         <is>
-          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
+          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
         </is>
       </c>
     </row>
@@ -7692,17 +7711,17 @@
         <v>151</v>
       </c>
       <c r="B156" s="5" t="n">
-        <v>128</v>
+        <v>31</v>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の実績見込み値を編集するか</t>
+          <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階
-サービス見込量の算定</t>
+          <t>素案 第6章第2節・第5章・第7章
+給付費の推計</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -7725,7 +7744,7 @@
       </c>
       <c r="I156" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
+          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
         </is>
       </c>
     </row>
@@ -7734,11 +7753,11 @@
         <v>152</v>
       </c>
       <c r="B157" s="5" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの利用率等の伸びの選択</t>
+          <t>令和8年度の実績見込み値を編集するか</t>
         </is>
       </c>
       <c r="D157" s="6" t="inlineStr">
@@ -7767,7 +7786,7 @@
       </c>
       <c r="I157" s="6" t="inlineStr">
         <is>
-          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
         </is>
       </c>
     </row>
@@ -7776,16 +7795,17 @@
         <v>153</v>
       </c>
       <c r="B158" s="5" t="n">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>統合した成果品の元の資料を残すか</t>
+          <t>見える化システムの利用率等の伸びの選択</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t>成果品一覧（納品時の構成）</t>
+          <t>将来推計 第2段階
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -7808,7 +7828,7 @@
       </c>
       <c r="I158" s="6" t="inlineStr">
         <is>
-          <t>統合した成果品の元の資料を残す</t>
+          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
         </is>
       </c>
     </row>
@@ -7817,17 +7837,16 @@
         <v>154</v>
       </c>
       <c r="B159" s="5" t="n">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
+          <t>統合した成果品の元の資料を残すか</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力
-将来推計 第3段階</t>
+          <t>成果品一覧（納品時の構成）</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -7850,7 +7869,7 @@
       </c>
       <c r="I159" s="6" t="inlineStr">
         <is>
-          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
+          <t>統合した成果品の元の資料を残す</t>
         </is>
       </c>
     </row>
@@ -7859,22 +7878,22 @@
         <v>155</v>
       </c>
       <c r="B160" s="5" t="n">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
+          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の取りまとめと第10期への反映 08シート・09シート
-10月 地域課題の整理と3町協議の確認事項</t>
+          <t>見える化システムへの入力
+将来推計 第3段階</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F160" s="5" t="inlineStr">
@@ -7892,7 +7911,7 @@
       </c>
       <c r="I160" s="6" t="inlineStr">
         <is>
-          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
+          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
         </is>
       </c>
     </row>
@@ -7901,27 +7920,27 @@
         <v>156</v>
       </c>
       <c r="B161" s="5" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
+          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr">
         <is>
-          <t>計画素案の記載内容の洗い出しと対比 08シート
-計画素案 全体</t>
+          <t>交付金評価の取りまとめと第10期への反映 08シート・09シート
+10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G161" s="15" t="n">
@@ -7929,12 +7948,12 @@
       </c>
       <c r="H161" s="6" t="inlineStr">
         <is>
-          <t>止めている成果物 計画素案（+1）</t>
+          <t>期限 当月（R8.10）（+1）</t>
         </is>
       </c>
       <c r="I161" s="6" t="inlineStr">
         <is>
-          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
+          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
         </is>
       </c>
     </row>
@@ -7943,17 +7962,17 @@
         <v>157</v>
       </c>
       <c r="B162" s="5" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
+          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>図表データ管理台帳 01シート・02シート
-計画素案 資料7／別冊の図表集</t>
+          <t>計画素案の記載内容の洗い出しと対比 08シート
+計画素案 全体</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -7976,7 +7995,7 @@
       </c>
       <c r="I162" s="6" t="inlineStr">
         <is>
-          <t>の当方の扱い＝現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
+          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
         </is>
       </c>
     </row>
@@ -7985,27 +8004,27 @@
         <v>158</v>
       </c>
       <c r="B163" s="5" t="n">
-        <v>74</v>
+        <v>173</v>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
+          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）9
-計画素案 第5章 基本目標5</t>
+          <t>図表データ管理台帳 01シート・02シート
+計画素案 資料7／別冊の図表集</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>北海道上川総合振興局</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
-          <t>R9.4</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G163" s="15" t="n">
@@ -8018,7 +8037,7 @@
       </c>
       <c r="I163" s="6" t="inlineStr">
         <is>
-          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
+          <t>の当方の扱い＝現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
         </is>
       </c>
     </row>
@@ -8027,40 +8046,40 @@
         <v>159</v>
       </c>
       <c r="B164" s="5" t="n">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスの確保方策の決定</t>
+          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第2節・第4節
-見込量表（3種別）</t>
+          <t>ケアプラン点検実施要領（案）9
+計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>北海道上川総合振興局</t>
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R9.4</t>
         </is>
       </c>
       <c r="G164" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H164" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I164" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
         </is>
       </c>
     </row>
@@ -8069,45 +8088,87 @@
         <v>160</v>
       </c>
       <c r="B165" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>24時間対応サービスの確保方策の決定</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="inlineStr">
+        <is>
+          <t>素案 第6章第2節・第4節
+見込量表（3種別）</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F165" s="5" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G165" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="48" customHeight="1">
+      <c r="A166" s="5" t="n">
+        <v>161</v>
+      </c>
+      <c r="B166" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="C165" s="6" t="inlineStr">
+      <c r="C166" s="6" t="inlineStr">
         <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="D165" s="6" t="inlineStr">
+      <c r="D166" s="6" t="inlineStr">
         <is>
           <t>素案 第4章第3節・第5章
 全16KPIの目標値</t>
         </is>
       </c>
-      <c r="E165" s="5" t="inlineStr">
+      <c r="E166" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="F165" s="5" t="inlineStr">
+      <c r="F166" s="5" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="G165" s="15" t="n">
+      <c r="G166" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H165" s="6" t="inlineStr">
+      <c r="H166" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="I165" s="6" t="inlineStr">
+      <c r="I166" s="6" t="inlineStr">
         <is>
           <t>代表KPIの目標値は、令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置く</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="56" customHeight="1">
-      <c r="A166" s="13" t="inlineStr">
+    <row r="167" ht="56" customHeight="1">
+      <c r="A167" s="13" t="inlineStr">
         <is>
           <t>注1）点が9以上を至急、6以上8以下を優先、5以下を通常とみます（03シート）。
 注2）「決着しない場合の当方の扱い」が空のものは、決まらないと当方の作業が止まります。 先に扱いを決めます。
@@ -8115,119 +8176,76 @@
         </is>
       </c>
     </row>
-    <row r="167"/>
-    <row r="168" ht="20" customHeight="1">
-      <c r="A168" s="3" t="inlineStr">
+    <row r="168"/>
+    <row r="169" ht="20" customHeight="1">
+      <c r="A169" s="3" t="inlineStr">
         <is>
           <t>2　資料提供依頼（資料の提供を求めるもの）　18件</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="30" customHeight="1">
-      <c r="A169" s="4" t="inlineStr">
+    <row r="170" ht="30" customHeight="1">
+      <c r="A170" s="4" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B169" s="4" t="inlineStr">
+      <c r="B170" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C169" s="4" t="inlineStr">
+      <c r="C170" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="D169" s="4" t="inlineStr">
+      <c r="D170" s="4" t="inlineStr">
         <is>
           <t>確定する主張</t>
         </is>
       </c>
-      <c r="E169" s="4" t="inlineStr">
+      <c r="E170" s="4" t="inlineStr">
         <is>
           <t>入手先</t>
         </is>
       </c>
-      <c r="F169" s="4" t="inlineStr">
+      <c r="F170" s="4" t="inlineStr">
         <is>
           <t>希望時期</t>
         </is>
       </c>
-      <c r="G169" s="4" t="inlineStr">
+      <c r="G170" s="4" t="inlineStr">
         <is>
           <t>優先</t>
         </is>
       </c>
-      <c r="H169" s="4" t="inlineStr">
+      <c r="H170" s="4" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="I169" s="4" t="inlineStr">
+      <c r="I170" s="4" t="inlineStr">
         <is>
           <t>領域</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="40" customHeight="1">
-      <c r="A170" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B170" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C170" s="6" t="inlineStr">
-        <is>
-          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
-        </is>
-      </c>
-      <c r="D170" s="6" t="inlineStr">
-        <is>
-          <t>第9期の評価の完成</t>
-        </is>
-      </c>
-      <c r="E170" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F170" s="5" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="G170" s="16" t="inlineStr">
-        <is>
-          <t>最高</t>
-        </is>
-      </c>
-      <c r="H170" s="5" t="inlineStr">
-        <is>
-          <t>一部受領</t>
-        </is>
-      </c>
-      <c r="I170" s="5" t="inlineStr">
-        <is>
-          <t>G</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B171" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
+          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
         </is>
       </c>
       <c r="D171" s="6" t="inlineStr">
         <is>
-          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
+          <t>第9期の評価の完成</t>
         </is>
       </c>
       <c r="E171" s="6" t="inlineStr">
@@ -8240,47 +8258,47 @@
           <t>R8.8</t>
         </is>
       </c>
-      <c r="G171" s="14" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="G171" s="16" t="inlineStr">
+        <is>
+          <t>最高</t>
         </is>
       </c>
       <c r="H171" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>一部受領</t>
         </is>
       </c>
       <c r="I171" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B172" s="5" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
+          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
         </is>
       </c>
       <c r="E172" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G172" s="14" t="inlineStr">
@@ -8290,35 +8308,35 @@
       </c>
       <c r="H172" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I172" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B173" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
         </is>
       </c>
       <c r="D173" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
+          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
       <c r="E173" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
@@ -8333,40 +8351,40 @@
       </c>
       <c r="H173" s="5" t="inlineStr">
         <is>
-          <t>代替により解消</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I173" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B174" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B174" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
+          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G174" s="14" t="inlineStr">
@@ -8376,35 +8394,35 @@
       </c>
       <c r="H174" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>代替により解消</t>
         </is>
       </c>
       <c r="I174" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B175" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B175" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>事業所・施設の定員と稼働の実績</t>
+          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t>稼働率の低下の有無、定員減少の経緯</t>
+          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
@@ -8419,35 +8437,35 @@
       </c>
       <c r="H175" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B176" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B176" s="5" t="n">
-        <v>8</v>
-      </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>未利用認定者の内訳とケアプランのサービス構成</t>
+          <t>事業所・施設の定員と稼働の実績</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
+          <t>稼働率の低下の有無、定員減少の経緯</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
@@ -8467,25 +8485,25 @@
       </c>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B177" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B177" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
+          <t>未利用認定者の内訳とケアプランのサービス構成</t>
         </is>
       </c>
       <c r="D177" s="6" t="inlineStr">
         <is>
-          <t>第9期の剰余額（現在は概算）</t>
+          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
@@ -8510,30 +8528,30 @@
       </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>E</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B178" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B178" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
+          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t>給付費の地域内還流の議論</t>
+          <t>第9期の剰余額（現在は概算）</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
@@ -8553,25 +8571,25 @@
       </c>
       <c r="I178" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B179" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
+          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
         </is>
       </c>
       <c r="D179" s="6" t="inlineStr">
         <is>
-          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
+          <t>給付費の地域内還流の議論</t>
         </is>
       </c>
       <c r="E179" s="6" t="inlineStr">
@@ -8596,30 +8614,30 @@
       </c>
       <c r="I179" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B180" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
+          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t>サービス種別ごとの見込量の様式</t>
+          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
@@ -8634,40 +8652,40 @@
       </c>
       <c r="H180" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B181" s="5" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
+          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
         </is>
       </c>
       <c r="D181" s="6" t="inlineStr">
         <is>
-          <t>第10期の段階設計と保険料算定</t>
+          <t>サービス種別ごとの見込量の様式</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>告示後</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G181" s="14" t="inlineStr">
@@ -8677,78 +8695,78 @@
       </c>
       <c r="H181" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I181" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B182" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>小学校区と日常生活圏域の対応関係</t>
+          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>圏域別の分析、圏域設定の見直し</t>
+          <t>第10期の段階設計と保険料算定</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>美瑛町・3町</t>
+          <t>国の情報</t>
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G182" s="15" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>告示後</t>
+        </is>
+      </c>
+      <c r="G182" s="14" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H182" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I182" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B183" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr">
         <is>
-          <t>評価の枠組みの整理</t>
+          <t>圏域別の分析、圏域設定の見直し</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>美瑛町・3町</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
@@ -8768,35 +8786,35 @@
       </c>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B184" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B184" s="5" t="n">
-        <v>16</v>
-      </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD49の指標定義</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>地域差指数の分解の可否</t>
+          <t>評価の枠組みの整理</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
-          <t>見える化システム・厚生労働省</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G184" s="15" t="inlineStr">
@@ -8806,40 +8824,40 @@
       </c>
       <c r="H184" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B185" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B185" s="5" t="n">
-        <v>20</v>
-      </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+          <t>見える化システムD49の指標定義</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
         <is>
-          <t>会議資料・委員会資料の記述の正確性</t>
+          <t>地域差指数の分解の可否</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>見える化システム・厚生労働省</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>随時</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G185" s="15" t="inlineStr">
@@ -8849,103 +8867,146 @@
       </c>
       <c r="H185" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I185" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B186" s="5" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
-          <t>中重度・軽度の認定率の推移</t>
+          <t>会議資料・委員会資料の記述の正確性</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>見える化システム</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G186" s="17" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>随時</t>
+        </is>
+      </c>
+      <c r="G186" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H186" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I186" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+        </is>
+      </c>
+      <c r="D187" s="6" t="inlineStr">
+        <is>
+          <t>中重度・軽度の認定率の推移</t>
+        </is>
+      </c>
+      <c r="E187" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム</t>
+        </is>
+      </c>
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G187" s="17" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H187" s="5" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I187" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="40" customHeight="1">
+      <c r="A188" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B187" s="5" t="n">
+      <c r="B188" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C187" s="6" t="inlineStr">
+      <c r="C188" s="6" t="inlineStr">
         <is>
           <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
-      <c r="D187" s="6" t="inlineStr">
+      <c r="D188" s="6" t="inlineStr">
         <is>
           <t>世帯構成の現状</t>
         </is>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="E188" s="6" t="inlineStr">
         <is>
           <t>総務省・3町</t>
         </is>
       </c>
-      <c r="F187" s="5" t="inlineStr">
+      <c r="F188" s="5" t="inlineStr">
         <is>
           <t>公表後</t>
         </is>
       </c>
-      <c r="G187" s="17" t="inlineStr">
+      <c r="G188" s="17" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H187" s="5" t="inlineStr">
+      <c r="H188" s="5" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="I187" s="5" t="inlineStr">
+      <c r="I188" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="188" ht="28" customHeight="1">
-      <c r="A188" s="13" t="inlineStr">
+    <row r="189" ht="28" customHeight="1">
+      <c r="A189" s="13" t="inlineStr">
         <is>
           <t>注）03シートの確認事項が「決定」を求めるものであるのに対し、本表は「資料の提供」を求めるものです。資料が届かない場合の扱いは04シートの区分で示しています。</t>
         </is>
@@ -8953,11 +9014,11 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A166:I166"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A169:I169"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A188:I188"/>
-    <mergeCell ref="A168:I168"/>
+    <mergeCell ref="A189:I189"/>
+    <mergeCell ref="A167:I167"/>
     <mergeCell ref="A4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9067,7 +9128,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>68件</t>
+          <t>69件</t>
         </is>
       </c>
     </row>
@@ -9159,7 +9220,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>91件</t>
+          <t>92件</t>
         </is>
       </c>
     </row>
@@ -9407,7 +9468,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>157件</t>
+          <t>158件</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -9566,7 +9627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9594,7 +9655,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　当方の作業だけで進められるもの　114件</t>
+          <t>1　当方の作業だけで進められるもの　115件</t>
         </is>
       </c>
     </row>
@@ -11982,17 +12043,17 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提</t>
+          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
+          <t>の当方の扱い＝案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.16（点2）</t>
+          <t>確認事項No.174（点2）</t>
         </is>
       </c>
     </row>
@@ -12007,17 +12068,17 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
+          <t>保険料算定の前提</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
+          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.2（点1）</t>
+          <t>確認事項No.16（点2）</t>
         </is>
       </c>
     </row>
@@ -12032,17 +12093,17 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域の判定資料</t>
+          <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
+          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.13（点1）</t>
+          <t>確認事項No.2（点1）</t>
         </is>
       </c>
     </row>
@@ -12057,17 +12118,17 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎とする系列</t>
+          <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
+          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.14（点1）</t>
+          <t>確認事項No.13（点1）</t>
         </is>
       </c>
     </row>
@@ -12082,17 +12143,17 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>認定者数の基準月と月次推移</t>
+          <t>人口推計の基礎とする系列</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
+          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.15（点1）</t>
+          <t>確認事項No.14（点1）</t>
         </is>
       </c>
     </row>
@@ -12107,17 +12168,17 @@
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>3町計画への共通指標の掲載</t>
+          <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
+          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.17（点1）</t>
+          <t>確認事項No.15（点1）</t>
         </is>
       </c>
     </row>
@@ -12132,17 +12193,17 @@
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場</t>
+          <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
+          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.20（点1）</t>
+          <t>確認事項No.17（点1）</t>
         </is>
       </c>
     </row>
@@ -12157,17 +12218,17 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様</t>
+          <t>北海道・圏域との調整の場</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
+          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.21（点1）</t>
+          <t>確認事項No.20（点1）</t>
         </is>
       </c>
     </row>
@@ -12182,17 +12243,17 @@
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>事業所の定員・稼働率データ</t>
+          <t>成果品の仕様</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
+          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.23（点1）</t>
+          <t>確認事項No.21（点1）</t>
         </is>
       </c>
     </row>
@@ -12207,17 +12268,17 @@
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>認知症・医療介護連携の実績データ</t>
+          <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
+          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.26（点1）</t>
+          <t>確認事項No.23（点1）</t>
         </is>
       </c>
     </row>
@@ -12232,17 +12293,17 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提</t>
+          <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
+          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.29（点1）</t>
+          <t>確認事項No.26（点1）</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12318,17 @@
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の実施予定と推計での扱い</t>
+          <t>重度化の速度の前提</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
+          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.31（点1）</t>
+          <t>確認事項No.29（点1）</t>
         </is>
       </c>
     </row>
@@ -12282,17 +12343,17 @@
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>統合した成果品の元の資料を残すか</t>
+          <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>統合した成果品の元の資料を残す</t>
+          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.144（点1）</t>
+          <t>確認事項No.31（点1）</t>
         </is>
       </c>
     </row>
@@ -12307,17 +12368,17 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
+          <t>統合した成果品の元の資料を残すか</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
+          <t>統合した成果品の元の資料を残す</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.156（点1）</t>
+          <t>確認事項No.144（点1）</t>
         </is>
       </c>
     </row>
@@ -12332,17 +12393,17 @@
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
+          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
+          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.169（点1）</t>
+          <t>確認事項No.156（点1）</t>
         </is>
       </c>
     </row>
@@ -12357,17 +12418,17 @@
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
+          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
+          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.171（点1）</t>
+          <t>確認事項No.169（点1）</t>
         </is>
       </c>
     </row>
@@ -12382,17 +12443,17 @@
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
+          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>の当方の扱い＝現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
+          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.173（点1）</t>
+          <t>確認事項No.171（点1）</t>
         </is>
       </c>
     </row>
@@ -12407,17 +12468,17 @@
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
+          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
+          <t>の当方の扱い＝現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.74（点1）</t>
+          <t>確認事項No.173（点1）</t>
         </is>
       </c>
     </row>
@@ -12432,17 +12493,17 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスの確保方策の決定</t>
+          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.24（点0）</t>
+          <t>確認事項No.74（点1）</t>
         </is>
       </c>
     </row>
@@ -12457,22 +12518,47 @@
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
+          <t>24時間対応サービスの確保方策の決定</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.24（点0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="44" customHeight="1">
+      <c r="A120" s="5" t="n">
+        <v>115</v>
+      </c>
+      <c r="B120" s="19" t="inlineStr">
+        <is>
+          <t>既定値で進める</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="D119" s="6" t="inlineStr">
+      <c r="D120" s="6" t="inlineStr">
         <is>
           <t>代表KPIの目標値は、令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置く</t>
         </is>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="E120" s="6" t="inlineStr">
         <is>
           <t>確認事項No.25（点0）</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="76" customHeight="1">
-      <c r="A120" s="13" t="inlineStr">
+    <row r="121" ht="76" customHeight="1">
+      <c r="A121" s="13" t="inlineStr">
         <is>
           <t>注1）「据え置き（区分A）」は、資料の受領を待たずに当方の側で確定できるものです。
 注2）「既定値で進める」は、決着しない場合の扱いを置けているため決定を待たずに作業を進められるものです。決定を受けた時点で見直します。
@@ -12481,16 +12567,16 @@
         </is>
       </c>
     </row>
-    <row r="121"/>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="3" t="inlineStr">
+    <row r="122"/>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="3" t="inlineStr">
         <is>
           <t>2　先に扱いを決めるもの（既定値を置けていない）　0件</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="18" customHeight="1">
-      <c r="A123" s="20" t="inlineStr">
+    <row r="124" ht="18" customHeight="1">
+      <c r="A124" s="20" t="inlineStr">
         <is>
           <t>ありません。未決の確認事項の全件に扱いを置けています。</t>
         </is>
@@ -12498,12 +12584,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A122:E122"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A121:E121"/>
     <mergeCell ref="A123:E123"/>
-    <mergeCell ref="A120:E120"/>
+    <mergeCell ref="A124:E124"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12929,12 +13015,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>No.1〜No.173 を数える</t>
+          <t>No.1〜No.174 を数える</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>173件／欠番 なし／重複 なし</t>
+          <t>174件／欠番 なし／重複 なし</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -12959,7 +13045,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>確認事項160件／資料提供依頼18件</t>
+          <t>確認事項161件／資料提供依頼18件</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -12984,7 +13070,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>160件／合わない なし</t>
+          <t>161件／合わない なし</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -13209,7 +13295,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>114件（区分A 0・既定値 114）</t>
+          <t>115件（区分A 0・既定値 115）</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -749,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>02c7102</t>
+          <t>c2ca41a</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>人口推計コーホート分析の妥当性検証と受領資料の取込み</t>
+          <t>外部レビュー（第2回）による妥当性検証の改訂と確認事項No.174の起票</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>413f8b9</t>
+          <t>02c7102</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>優先順位上位8件を既定値のとおり計画素案へ反映</t>
+          <t>人口推計コーホート分析の妥当性検証と受領資料の取込み</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
@@ -1270,20 +1270,38 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>749b920</t>
+          <t>413f8b9</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>業務内容別の進捗を作業項目の達成状況による算定に改め、重大6件を全文掲載</t>
+          <t>優先順位上位8件を既定値のとおり計画素案へ反映</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr"/>
       <c r="E25" s="6" t="inlineStr"/>
       <c r="F25" s="6" t="inlineStr"/>
     </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>749b920</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>業務内容別の進捗を作業項目の達成状況による算定に改め、重大6件を全文掲載</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
@@ -1294,8 +1312,8 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -1326,7 +1326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I189"/>
+  <dimension ref="A1:I192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1358,7 +1358,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　確認事項（決定を求めるもの）　161件</t>
+          <t>1　確認事項（決定を求めるもの）　164件</t>
         </is>
       </c>
     </row>
@@ -8064,27 +8064,26 @@
         <v>159</v>
       </c>
       <c r="B164" s="5" t="n">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
+          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）9
-計画素案 第5章 基本目標5</t>
+          <t>計画素案 第1章第9節5・第5章 基本目標1・基本目標4</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>北海道上川総合振興局</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
-          <t>R9.4</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G164" s="15" t="n">
@@ -8097,7 +8096,7 @@
       </c>
       <c r="I164" s="6" t="inlineStr">
         <is>
-          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
+          <t>の当方の扱い＝国が示す本格運用開始日（令和10年4月1日）までに完了することを前提として計画素案に記載し、年度ごとの工程は［要確認］として残す。事業所への周知は広域連合と3町が共同で行うものとして記載する</t>
         </is>
       </c>
     </row>
@@ -8106,17 +8105,16 @@
         <v>160</v>
       </c>
       <c r="B165" s="5" t="n">
-        <v>24</v>
+        <v>176</v>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスの確保方策の決定</t>
+          <t>介護サービス事業者経営情報データベースの公表結果の活用の範囲</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第2節・第4節
-見込量表（3種別）</t>
+          <t>計画素案 第1章第9節5・第5章 基本目標4</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -8126,20 +8124,20 @@
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="G165" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H165" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I165" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+          <t>の当方の扱い＝公表された区分のうち当区域の事業所の規模に近いものを参考として用い、区域内の事業所の経営状況を表すものとしては用いない。計画素案には活用の方針のみを記載し、数値は掲げない</t>
         </is>
       </c>
     </row>
@@ -8148,45 +8146,170 @@
         <v>161</v>
       </c>
       <c r="B166" s="5" t="n">
+        <v>177</v>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>都道府県との協定に基づく連携への関与</t>
+        </is>
+      </c>
+      <c r="D166" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第1章第9節5・第5章 基本目標3・基本目標4</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="F166" s="5" t="inlineStr">
+        <is>
+          <t>R8.12</t>
+        </is>
+      </c>
+      <c r="G166" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H166" s="6" t="inlineStr">
+        <is>
+          <t>止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t>の当方の扱い＝計画素案には北海道及び事業者とともに活用を検討する旨のみを記載し、具体の取組及び目標は国から市町村の役割が示された後に定める</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="48" customHeight="1">
+      <c r="A167" s="5" t="n">
+        <v>162</v>
+      </c>
+      <c r="B167" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
+        </is>
+      </c>
+      <c r="D167" s="6" t="inlineStr">
+        <is>
+          <t>ケアプラン点検実施要領（案）9
+計画素案 第5章 基本目標5</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>北海道上川総合振興局</t>
+        </is>
+      </c>
+      <c r="F167" s="5" t="inlineStr">
+        <is>
+          <t>R9.4</t>
+        </is>
+      </c>
+      <c r="G167" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H167" s="6" t="inlineStr">
+        <is>
+          <t>止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="48" customHeight="1">
+      <c r="A168" s="5" t="n">
+        <v>163</v>
+      </c>
+      <c r="B168" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>24時間対応サービスの確保方策の決定</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>素案 第6章第2節・第4節
+見込量表（3種別）</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F168" s="5" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G168" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="48" customHeight="1">
+      <c r="A169" s="5" t="n">
+        <v>164</v>
+      </c>
+      <c r="B169" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="C166" s="6" t="inlineStr">
+      <c r="C169" s="6" t="inlineStr">
         <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="D166" s="6" t="inlineStr">
+      <c r="D169" s="6" t="inlineStr">
         <is>
           <t>素案 第4章第3節・第5章
 全16KPIの目標値</t>
         </is>
       </c>
-      <c r="E166" s="5" t="inlineStr">
+      <c r="E169" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="F166" s="5" t="inlineStr">
+      <c r="F169" s="5" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="G166" s="15" t="n">
+      <c r="G169" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H166" s="6" t="inlineStr">
+      <c r="H169" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="I166" s="6" t="inlineStr">
+      <c r="I169" s="6" t="inlineStr">
         <is>
           <t>代表KPIの目標値は、令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置く</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="56" customHeight="1">
-      <c r="A167" s="13" t="inlineStr">
+    <row r="170" ht="56" customHeight="1">
+      <c r="A170" s="13" t="inlineStr">
         <is>
           <t>注1）点が9以上を至急、6以上8以下を優先、5以下を通常とみます（03シート）。
 注2）「決着しない場合の当方の扱い」が空のものは、決まらないと当方の作業が止まります。 先に扱いを決めます。
@@ -8194,205 +8317,76 @@
         </is>
       </c>
     </row>
-    <row r="168"/>
-    <row r="169" ht="20" customHeight="1">
-      <c r="A169" s="3" t="inlineStr">
+    <row r="171"/>
+    <row r="172" ht="20" customHeight="1">
+      <c r="A172" s="3" t="inlineStr">
         <is>
           <t>2　資料提供依頼（資料の提供を求めるもの）　18件</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="30" customHeight="1">
-      <c r="A170" s="4" t="inlineStr">
+    <row r="173" ht="30" customHeight="1">
+      <c r="A173" s="4" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B170" s="4" t="inlineStr">
+      <c r="B173" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C170" s="4" t="inlineStr">
+      <c r="C173" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="D170" s="4" t="inlineStr">
+      <c r="D173" s="4" t="inlineStr">
         <is>
           <t>確定する主張</t>
         </is>
       </c>
-      <c r="E170" s="4" t="inlineStr">
+      <c r="E173" s="4" t="inlineStr">
         <is>
           <t>入手先</t>
         </is>
       </c>
-      <c r="F170" s="4" t="inlineStr">
+      <c r="F173" s="4" t="inlineStr">
         <is>
           <t>希望時期</t>
         </is>
       </c>
-      <c r="G170" s="4" t="inlineStr">
+      <c r="G173" s="4" t="inlineStr">
         <is>
           <t>優先</t>
         </is>
       </c>
-      <c r="H170" s="4" t="inlineStr">
+      <c r="H173" s="4" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="I170" s="4" t="inlineStr">
+      <c r="I173" s="4" t="inlineStr">
         <is>
           <t>領域</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="40" customHeight="1">
-      <c r="A171" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B171" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C171" s="6" t="inlineStr">
-        <is>
-          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
-        </is>
-      </c>
-      <c r="D171" s="6" t="inlineStr">
-        <is>
-          <t>第9期の評価の完成</t>
-        </is>
-      </c>
-      <c r="E171" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F171" s="5" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="G171" s="16" t="inlineStr">
-        <is>
-          <t>最高</t>
-        </is>
-      </c>
-      <c r="H171" s="5" t="inlineStr">
-        <is>
-          <t>一部受領</t>
-        </is>
-      </c>
-      <c r="I171" s="5" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="40" customHeight="1">
-      <c r="A172" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B172" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C172" s="6" t="inlineStr">
-        <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
-        </is>
-      </c>
-      <c r="D172" s="6" t="inlineStr">
-        <is>
-          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
-        </is>
-      </c>
-      <c r="E172" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F172" s="5" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="G172" s="14" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H172" s="5" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="I172" s="5" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="40" customHeight="1">
-      <c r="A173" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B173" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C173" s="6" t="inlineStr">
-        <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
-        </is>
-      </c>
-      <c r="D173" s="6" t="inlineStr">
-        <is>
-          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
-        </is>
-      </c>
-      <c r="E173" s="6" t="inlineStr">
-        <is>
-          <t>3町</t>
-        </is>
-      </c>
-      <c r="F173" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G173" s="14" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H173" s="5" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I173" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B174" s="5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
+          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
+          <t>第9期の評価の完成</t>
         </is>
       </c>
       <c r="E174" s="6" t="inlineStr">
@@ -8402,17 +8396,17 @@
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G174" s="14" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="G174" s="16" t="inlineStr">
+        <is>
+          <t>最高</t>
         </is>
       </c>
       <c r="H174" s="5" t="inlineStr">
         <is>
-          <t>代替により解消</t>
+          <t>一部受領</t>
         </is>
       </c>
       <c r="I174" s="5" t="inlineStr">
@@ -8423,29 +8417,29 @@
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B175" s="5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
+          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
         </is>
       </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G175" s="14" t="inlineStr">
@@ -8460,35 +8454,35 @@
       </c>
       <c r="I175" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B176" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>事業所・施設の定員と稼働の実績</t>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>稼働率の低下の有無、定員減少の経緯</t>
+          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G176" s="14" t="inlineStr">
@@ -8503,25 +8497,25 @@
       </c>
       <c r="I176" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B177" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>未利用認定者の内訳とケアプランのサービス構成</t>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
         </is>
       </c>
       <c r="D177" s="6" t="inlineStr">
         <is>
-          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
+          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
         </is>
       </c>
       <c r="E177" s="6" t="inlineStr">
@@ -8531,7 +8525,7 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G177" s="14" t="inlineStr">
@@ -8541,35 +8535,35 @@
       </c>
       <c r="H177" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>代替により解消</t>
         </is>
       </c>
       <c r="I177" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B178" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
+          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t>第9期の剰余額（現在は概算）</t>
+          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
@@ -8584,35 +8578,35 @@
       </c>
       <c r="H178" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I178" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B179" s="5" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
+          <t>事業所・施設の定員と稼働の実績</t>
         </is>
       </c>
       <c r="D179" s="6" t="inlineStr">
         <is>
-          <t>給付費の地域内還流の議論</t>
+          <t>稼働率の低下の有無、定員減少の経緯</t>
         </is>
       </c>
       <c r="E179" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
@@ -8632,30 +8626,30 @@
       </c>
       <c r="I179" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B180" s="5" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
+          <t>未利用認定者の内訳とケアプランのサービス構成</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
+          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
@@ -8675,25 +8669,25 @@
       </c>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B181" s="5" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
+          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
         </is>
       </c>
       <c r="D181" s="6" t="inlineStr">
         <is>
-          <t>サービス種別ごとの見込量の様式</t>
+          <t>第9期の剰余額（現在は概算）</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
@@ -8713,40 +8707,40 @@
       </c>
       <c r="H181" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I181" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>H</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B182" s="5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
+          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>第10期の段階設計と保険料算定</t>
+          <t>給付費の地域内還流の議論</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>告示後</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G182" s="14" t="inlineStr">
@@ -8756,45 +8750,45 @@
       </c>
       <c r="H182" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I182" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B183" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>小学校区と日常生活圏域の対応関係</t>
+          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr">
         <is>
-          <t>圏域別の分析、圏域設定の見直し</t>
+          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>美瑛町・3町</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G183" s="15" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G183" s="14" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H183" s="5" t="inlineStr">
@@ -8804,25 +8798,25 @@
       </c>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B184" s="5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>評価の枠組みの整理</t>
+          <t>サービス種別ごとの見込量の様式</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -8832,55 +8826,55 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G184" s="15" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G184" s="14" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H184" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B185" s="5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD49の指標定義</t>
+          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
         <is>
-          <t>地域差指数の分解の可否</t>
+          <t>第10期の段階設計と保険料算定</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>見える化システム・厚生労働省</t>
+          <t>国の情報</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G185" s="15" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>告示後</t>
+        </is>
+      </c>
+      <c r="G185" s="14" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H185" s="5" t="inlineStr">
@@ -8890,35 +8884,35 @@
       </c>
       <c r="I185" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" s="5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B186" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+          <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
-          <t>会議資料・委員会資料の記述の正確性</t>
+          <t>圏域別の分析、圏域設定の見直し</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>美瑛町・3町</t>
         </is>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>随時</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G186" s="15" t="inlineStr">
@@ -8928,35 +8922,35 @@
       </c>
       <c r="H186" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I186" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" s="5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B187" s="5" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D187" s="6" t="inlineStr">
         <is>
-          <t>中重度・軽度の認定率の推移</t>
+          <t>評価の枠組みの整理</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>見える化システム</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F187" s="5" t="inlineStr">
@@ -8964,67 +8958,196 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G187" s="17" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="G187" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H187" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I187" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムD49の指標定義</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
+        <is>
+          <t>地域差指数の分解の可否</t>
+        </is>
+      </c>
+      <c r="E188" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム・厚生労働省</t>
+        </is>
+      </c>
+      <c r="F188" s="5" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G188" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H188" s="5" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I188" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="40" customHeight="1">
+      <c r="A189" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+        </is>
+      </c>
+      <c r="D189" s="6" t="inlineStr">
+        <is>
+          <t>会議資料・委員会資料の記述の正確性</t>
+        </is>
+      </c>
+      <c r="E189" s="6" t="inlineStr">
+        <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>随時</t>
+        </is>
+      </c>
+      <c r="G189" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H189" s="5" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+      <c r="I189" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="40" customHeight="1">
+      <c r="A190" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+        </is>
+      </c>
+      <c r="D190" s="6" t="inlineStr">
+        <is>
+          <t>中重度・軽度の認定率の推移</t>
+        </is>
+      </c>
+      <c r="E190" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム</t>
+        </is>
+      </c>
+      <c r="F190" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G190" s="17" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H190" s="5" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I190" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="40" customHeight="1">
+      <c r="A191" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B188" s="5" t="n">
+      <c r="B191" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C188" s="6" t="inlineStr">
+      <c r="C191" s="6" t="inlineStr">
         <is>
           <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
-      <c r="D188" s="6" t="inlineStr">
+      <c r="D191" s="6" t="inlineStr">
         <is>
           <t>世帯構成の現状</t>
         </is>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="E191" s="6" t="inlineStr">
         <is>
           <t>総務省・3町</t>
         </is>
       </c>
-      <c r="F188" s="5" t="inlineStr">
+      <c r="F191" s="5" t="inlineStr">
         <is>
           <t>公表後</t>
         </is>
       </c>
-      <c r="G188" s="17" t="inlineStr">
+      <c r="G191" s="17" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H188" s="5" t="inlineStr">
+      <c r="H191" s="5" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="I188" s="5" t="inlineStr">
+      <c r="I191" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="189" ht="28" customHeight="1">
-      <c r="A189" s="13" t="inlineStr">
+    <row r="192" ht="28" customHeight="1">
+      <c r="A192" s="13" t="inlineStr">
         <is>
           <t>注）03シートの確認事項が「決定」を求めるものであるのに対し、本表は「資料の提供」を求めるものです。資料が届かない場合の扱いは04シートの区分で示しています。</t>
         </is>
@@ -9032,11 +9155,11 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A172:I172"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A169:I169"/>
+    <mergeCell ref="A170:I170"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A189:I189"/>
-    <mergeCell ref="A167:I167"/>
+    <mergeCell ref="A192:I192"/>
     <mergeCell ref="A4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9238,7 +9361,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>92件</t>
+          <t>95件</t>
         </is>
       </c>
     </row>
@@ -9486,7 +9609,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>158件</t>
+          <t>161件</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -9645,7 +9768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9673,7 +9796,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　当方の作業だけで進められるもの　115件</t>
+          <t>1　当方の作業だけで進められるもの　118件</t>
         </is>
       </c>
     </row>
@@ -12511,17 +12634,17 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
+          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
+          <t>の当方の扱い＝国が示す本格運用開始日（令和10年4月1日）までに完了することを前提として計画素案に記載し、年度ごとの工程は［要確認］として残す。事業所への周知は広域連合と3町が共同で行うものとして記載する</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.74（点1）</t>
+          <t>確認事項No.175（点1）</t>
         </is>
       </c>
     </row>
@@ -12536,17 +12659,17 @@
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスの確保方策の決定</t>
+          <t>介護サービス事業者経営情報データベースの公表結果の活用の範囲</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+          <t>の当方の扱い＝公表された区分のうち当区域の事業所の規模に近いものを参考として用い、区域内の事業所の経営状況を表すものとしては用いない。計画素案には活用の方針のみを記載し、数値は掲げない</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.24（点0）</t>
+          <t>確認事項No.176（点1）</t>
         </is>
       </c>
     </row>
@@ -12561,22 +12684,97 @@
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
+          <t>都道府県との協定に基づく連携への関与</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>の当方の扱い＝計画素案には北海道及び事業者とともに活用を検討する旨のみを記載し、具体の取組及び目標は国から市町村の役割が示された後に定める</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.177（点1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="44" customHeight="1">
+      <c r="A121" s="5" t="n">
+        <v>116</v>
+      </c>
+      <c r="B121" s="19" t="inlineStr">
+        <is>
+          <t>既定値で進める</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.74（点1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="44" customHeight="1">
+      <c r="A122" s="5" t="n">
+        <v>117</v>
+      </c>
+      <c r="B122" s="19" t="inlineStr">
+        <is>
+          <t>既定値で進める</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>24時間対応サービスの確保方策の決定</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.24（点0）</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="44" customHeight="1">
+      <c r="A123" s="5" t="n">
+        <v>118</v>
+      </c>
+      <c r="B123" s="19" t="inlineStr">
+        <is>
+          <t>既定値で進める</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="D120" s="6" t="inlineStr">
+      <c r="D123" s="6" t="inlineStr">
         <is>
           <t>代表KPIの目標値は、令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置く</t>
         </is>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="E123" s="6" t="inlineStr">
         <is>
           <t>確認事項No.25（点0）</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="76" customHeight="1">
-      <c r="A121" s="13" t="inlineStr">
+    <row r="124" ht="76" customHeight="1">
+      <c r="A124" s="13" t="inlineStr">
         <is>
           <t>注1）「据え置き（区分A）」は、資料の受領を待たずに当方の側で確定できるものです。
 注2）「既定値で進める」は、決着しない場合の扱いを置けているため決定を待たずに作業を進められるものです。決定を受けた時点で見直します。
@@ -12585,16 +12783,16 @@
         </is>
       </c>
     </row>
-    <row r="122"/>
-    <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="3" t="inlineStr">
+    <row r="125"/>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="3" t="inlineStr">
         <is>
           <t>2　先に扱いを決めるもの（既定値を置けていない）　0件</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="18" customHeight="1">
-      <c r="A124" s="20" t="inlineStr">
+    <row r="127" ht="18" customHeight="1">
+      <c r="A127" s="20" t="inlineStr">
         <is>
           <t>ありません。未決の確認事項の全件に扱いを置けています。</t>
         </is>
@@ -12605,8 +12803,8 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A121:E121"/>
-    <mergeCell ref="A123:E123"/>
+    <mergeCell ref="A127:E127"/>
+    <mergeCell ref="A126:E126"/>
     <mergeCell ref="A124:E124"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13033,12 +13231,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>No.1〜No.174 を数える</t>
+          <t>No.1〜No.177 を数える</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>174件／欠番 なし／重複 なし</t>
+          <t>177件／欠番 なし／重複 なし</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -13063,7 +13261,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>確認事項161件／資料提供依頼18件</t>
+          <t>確認事項164件／資料提供依頼18件</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -13088,7 +13286,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>161件／合わない なし</t>
+          <t>164件／合わない なし</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -13313,7 +13511,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>115件（区分A 0・既定値 115）</t>
+          <t>118件（区分A 0・既定値 118）</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -583,7 +583,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>毎日の終わりにWBSの現況・ペンディングの優先順位・当方の作業だけで進められるもの・翌日の作業順位を1枚にしたものです。基準日 令和8年10月5日。内部保管。</t>
+          <t>毎日の終わりにWBSの現況・ペンディングの優先順位・当方の作業だけで進められるもの・翌日の作業順位を1枚にしたものです。基準日 令和8年10月7日。内部保管。</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -770,7 +770,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）ごとの進捗率と、前に報告した時点からの動きです。基準日 令和8年10月5日。</t>
+          <t>仕様書４（1）〜（12）ごとの進捗率と、前に報告した時点からの動きです。基準日 令和8年10月7日。</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>注1）進捗の記録の基準日は 令和8年10月5日 です。本表の基準日（令和8年10月5日）と違うときは、進捗の更新がまだ行われていません。
+          <t>注1）進捗の記録の基準日は 令和8年10月7日 です。本表の基準日（令和8年10月7日）と違うときは、進捗の更新がまだ行われていません。
 注2）進捗率を更新したら、更新前の値を記録へ移します。移さないと、過去の時点を記す資料（月次の報告・議事録）の数値が書き換わります。</t>
         </is>
       </c>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>c2ca41a</t>
+          <t>56a309f</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>外部レビュー（第2回）による妥当性検証の改訂と確認事項No.174の起票</t>
+          <t>意見交換会資料に時間配分と令和8年9月の制度の動向を加えた</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>02c7102</t>
+          <t>46b25f6</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>人口推計コーホート分析の妥当性検証と受領資料の取込み</t>
+          <t>事前打合せ資料に最低限の確認事項と時間配分を加えた（1〜2時間の枠）</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
@@ -1270,38 +1270,20 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>413f8b9</t>
+          <t>763e6ce</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>優先順位上位8件を既定値のとおり計画素案へ反映</t>
+          <t>令和8年9月18日 介護保険部会資料による計画素案の是正（指摘15件）</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr"/>
       <c r="E25" s="6" t="inlineStr"/>
       <c r="F25" s="6" t="inlineStr"/>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>749b920</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>業務内容別の進捗を作業項目の達成状況による算定に改め、重大6件を全文掲載</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="13" t="inlineStr">
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
@@ -1312,8 +1294,8 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1350,7 +1332,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>完了していない確認事項と資料提供依頼を、影響度の点の高い順に並べたものです。点の付け方は03シートに全て書いています。基準日 令和8年10月5日。</t>
+          <t>完了していない確認事項と資料提供依頼を、影響度の点の高い順に並べたものです。点の付け方は03シートに全て書いています。基準日 令和8年10月7日。</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2803,7 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第4節
+          <t>計画素案 第3章第4節
 図表集 27シート
 交付金評価指標と全国集計の受領点検 04シート</t>
         </is>
@@ -6730,7 +6712,7 @@
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章第3節・基本目標3・資料1
+          <t>計画素案 第4章第3節・第5章 基本目標3・資料1
 アンケート調査の集計分析報告書 02・14シート</t>
         </is>
       </c>
@@ -9192,7 +9174,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02シートの点は次の規則だけで付けています。規則を変えれば02シートの並びも変わります。基準日 令和8年10月5日。</t>
+          <t>02シートの点は次の規則だけで付けています。規則を変えれば02シートの並びも変わります。基準日 令和8年10月7日。</t>
         </is>
       </c>
     </row>
@@ -9768,7 +9750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9788,7 +9770,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>決定・資料の受領を待たずに当方の作業だけで進められるものです。基準日 令和8年10月5日。</t>
+          <t>決定・資料の受領を待たずに当方の作業だけで進められるものです。基準日 令和8年10月7日。</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9778,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　当方の作業だけで進められるもの　118件</t>
+          <t>1　当方の作業だけで進められるもの　102件</t>
         </is>
       </c>
     </row>
@@ -9834,17 +9816,17 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位</t>
+          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
+          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.65（点3）</t>
+          <t>確認事項No.124（点3）</t>
         </is>
       </c>
     </row>
@@ -9859,17 +9841,17 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>サービスガイドに掲載する事業所の範囲</t>
+          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>サービスガイドに掲載する事業所の範囲は北海道の指定事業所一覧（最新のもの）による</t>
+          <t>在宅生活改善調査の結果は「在宅で困難を抱える方の状況」として引き、在宅の認定者全体の割合としては引かない</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.66（点3）</t>
+          <t>確認事項No.140（点3）</t>
         </is>
       </c>
     </row>
@@ -9884,17 +9866,17 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>算定方法の国の様式との整合（点検結果）</t>
+          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
+          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.67（点3）</t>
+          <t>確認事項No.149（点3）</t>
         </is>
       </c>
     </row>
@@ -9909,17 +9891,17 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの自然体推計の再出力のお願い</t>
+          <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
+          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.68（点3）</t>
+          <t>確認事項No.30（点3）</t>
         </is>
       </c>
     </row>
@@ -9934,17 +9916,17 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>交付金の全国順位の計画本文への掲載</t>
+          <t>第9段階の乗率の経緯</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>交付金の全国順位は計画本文に掲載せず、策定委員会資料にとどめる（確認事項No.71のとおり）</t>
+          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.70（点3）</t>
+          <t>確認事項No.34（点3）</t>
         </is>
       </c>
     </row>
@@ -9959,17 +9941,17 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
+          <t>上川管内の保険者の所得段階数と乗率</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）は協議資料にとどめ素案に入れない</t>
+          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.73（点3）</t>
+          <t>確認事項No.35（点3）</t>
         </is>
       </c>
     </row>
@@ -9984,17 +9966,17 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>代表KPIと改善事項の再整理案</t>
+          <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>代表KPIと改善事項は当方の再整理案のままとする</t>
+          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.75（点3）</t>
+          <t>確認事項No.36（点3）</t>
         </is>
       </c>
     </row>
@@ -10009,17 +9991,17 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>介護リームスから抽出できる項目</t>
+          <t>令和9年4月に新設される区分を見込量に立てるか</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>介護リームスから抽出できないものとして、代表KPI H03は未算定のままとする</t>
+          <t>令和9年4月新設の3区分を0として立てる</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.76（点3）</t>
+          <t>確認事項No.115（点3）</t>
         </is>
       </c>
     </row>
@@ -10034,17 +10016,17 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥の団体別の公表値</t>
+          <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥の団体別の公表値を引用できないものとして、当該指標は計画本文に掲げない</t>
+          <t>代表KPI H07・H08・H12・H16は代理指標への振替案のとおりとする</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.77（点3）</t>
+          <t>確認事項No.4（点2）</t>
         </is>
       </c>
     </row>
@@ -10059,17 +10041,17 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>グループホームびえいの郷の定員減の時期</t>
+          <t>第9期の施策・事業実績</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>北海道の名簿の定員のまま概算する</t>
+          <t>第9期の施策・事業実績を受領できないものとして、公表資料（交付金の評価結果・総合事業の実施状況に関する調査・年報）により評価する</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.78（点3）</t>
+          <t>確認事項No.5（点2）</t>
         </is>
       </c>
     </row>
@@ -10084,17 +10066,17 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>第5章の施策数の見直しの範囲</t>
+          <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策の体系を維持する（施策数を見直さない）</t>
+          <t>3調査の点検事項は当方の判定のままとする</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.79（点3）</t>
+          <t>確認事項No.8（点2）</t>
         </is>
       </c>
     </row>
@@ -10109,17 +10091,17 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H16のデータ源（国保連の給付実績の明細情報）</t>
+          <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>国保連の給付実績の明細を受領できないものとして、代表KPI H16は地域密着型サービスに限った確認件数を代理指標とする</t>
+          <t>会議日程及びパブリックコメントの期間は仕様書５の工程による</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.81（点3）</t>
+          <t>確認事項No.19（点2）</t>
         </is>
       </c>
     </row>
@@ -10134,17 +10116,17 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
+          <t>キックオフ会議資料への工程表の反映</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
+          <t>現行の工程表のまま進める</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.95（点3）</t>
+          <t>確認事項No.42（点2）</t>
         </is>
       </c>
     </row>
@@ -10159,17 +10141,17 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+          <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
+          <t>告示を確認できないものとして、特別地域加算の判定を計画素案に書かず［要確認］のまま残す</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.96（点3）</t>
+          <t>確認事項No.1（点2）</t>
         </is>
       </c>
     </row>
@@ -10184,17 +10166,17 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
+          <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
+          <t>類似保険者との比較は公表されている同規模保険者40団体による</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.102（点3）</t>
+          <t>確認事項No.3（点2）</t>
         </is>
       </c>
     </row>
@@ -10209,17 +10191,17 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議関係資料の取扱いの確認</t>
+          <t>交付金の評価調書</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>転載を禁ずる旨の記載がある2件は成果品に用いず、原典（厚労省の市町村マニュアル及び別冊事例集）のみを引く</t>
+          <t>評価調書を受領できないものとして、得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できない旨を注記する</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.122（点3）</t>
+          <t>確認事項No.6（点2）</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10216,17 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
+          <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
+          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.124（点3）</t>
+          <t>確認事項No.9（点2）</t>
         </is>
       </c>
     </row>
@@ -10259,17 +10241,17 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
+          <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果は「在宅で困難を抱える方の状況」として引き、在宅の認定者全体の割合としては引かない</t>
+          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.140（点3）</t>
+          <t>確認事項No.10（点2）</t>
         </is>
       </c>
     </row>
@@ -10284,17 +10266,17 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
+          <t>町別の人口・世帯データ</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
+          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.149（点3）</t>
+          <t>確認事項No.11（点2）</t>
         </is>
       </c>
     </row>
@@ -10309,17 +10291,17 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けた要介護度の変化</t>
+          <t>日常生活圏域別のデータ</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
+          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.30（点3）</t>
+          <t>確認事項No.12（点2）</t>
         </is>
       </c>
     </row>
@@ -10334,17 +10316,17 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率の経緯</t>
+          <t>骨子案の内容の確認</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
+          <t>骨子案は提出した内容のままとする</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.34（点3）</t>
+          <t>確認事項No.18（点2）</t>
         </is>
       </c>
     </row>
@@ -10359,17 +10341,17 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
+          <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
+          <t>北海道の評価指標の読替えは当方の案のままとする</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.35（点3）</t>
+          <t>確認事項No.22（点2）</t>
         </is>
       </c>
     </row>
@@ -10384,17 +10366,17 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績と収納率</t>
+          <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
+          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.36（点3）</t>
+          <t>確認事項No.27（点2）</t>
         </is>
       </c>
     </row>
@@ -10409,17 +10391,17 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+          <t>調査対象者の範囲の確認</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月新設の3区分を0として立てる</t>
+          <t>現に収録している調査対象者の範囲による</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.115（点3）</t>
+          <t>確認事項No.28（点2）</t>
         </is>
       </c>
     </row>
@@ -10434,17 +10416,17 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16の代理指標</t>
+          <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16は代理指標への振替案のとおりとする</t>
+          <t>公表されている全国集計の値による</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.4（点2）</t>
+          <t>確認事項No.38（点2）</t>
         </is>
       </c>
     </row>
@@ -10459,17 +10441,17 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績</t>
+          <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績を受領できないものとして、公表資料（交付金の評価結果・総合事業の実施状況に関する調査・年報）により評価する</t>
+          <t>令和8年9月25日の再提供により決着済み。再提供を受けたファイルの値（3町合計と円単位一致）による</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.5（点2）</t>
+          <t>確認事項No.46（点2）</t>
         </is>
       </c>
     </row>
@@ -10484,17 +10466,17 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項の取扱い</t>
+          <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項は当方の判定のままとする</t>
+          <t>総括表（保険者単位）を用い、計画作成支援ツールの実績値シートは比較のためにのみ用いる</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.8（点2）</t>
+          <t>確認事項No.47（点2）</t>
         </is>
       </c>
     </row>
@@ -10509,17 +10491,17 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>会議日程とパブリックコメントの期間</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>会議日程及びパブリックコメントの期間は仕様書５の工程による</t>
+          <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値による</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.19（点2）</t>
+          <t>確認事項No.48（点2）</t>
         </is>
       </c>
     </row>
@@ -10534,17 +10516,17 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料への工程表の反映</t>
+          <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>現行の工程表のまま進める</t>
+          <t>受領済みの年報・月報の値による</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.42（点2）</t>
+          <t>確認事項No.50（点2）</t>
         </is>
       </c>
     </row>
@@ -10559,17 +10541,17 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>特別地域加算の対象地域告示</t>
+          <t>月報の値の接続のずれ（ご報告）</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>告示を確認できないものとして、特別地域加算の判定を計画素案に書かず［要確認］のまま残す</t>
+          <t>月報の値の接続のずれは記録として残し、計画本文には用いない</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.1（点2）</t>
+          <t>確認事項No.51（点2）</t>
         </is>
       </c>
     </row>
@@ -10584,17 +10566,17 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較分析の対象</t>
+          <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較は公表されている同規模保険者40団体による</t>
+          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.3（点2）</t>
+          <t>確認事項No.52（点2）</t>
         </is>
       </c>
     </row>
@@ -10609,17 +10591,17 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価調書</t>
+          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>評価調書を受領できないものとして、得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できない旨を注記する</t>
+          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合は1億円あたり月額約▲310円となることを併記する</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.6（点2）</t>
+          <t>確認事項No.53（点2）</t>
         </is>
       </c>
     </row>
@@ -10634,17 +10616,17 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>調査の対象者範囲と回収率</t>
+          <t>議事録の文書プロパティに個人名が再度入る</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
+          <t>議事録は作成者名を落として再出力する（当方で対応する）</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.9（点2）</t>
+          <t>確認事項No.54（点2）</t>
         </is>
       </c>
     </row>
@@ -10659,17 +10641,17 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>介護人材実態調査の採用者数・退職者数</t>
+          <t>議事録の表記に関するご提案3件</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
+          <t>議事録の表記はご提案3件のとおり改める</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.10（点2）</t>
+          <t>確認事項No.55（点2）</t>
         </is>
       </c>
     </row>
@@ -10684,17 +10666,17 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>町別の人口・世帯データ</t>
+          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
+          <t>他団体の集計帳票6件は成果品に用いない</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.11（点2）</t>
+          <t>確認事項No.56（点2）</t>
         </is>
       </c>
     </row>
@@ -10709,17 +10691,17 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域別のデータ</t>
+          <t>調整交付金の算定基礎の確認</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
+          <t>現行の扱い（第9期の算定を再現し公表値6,428円と一致する扱い）による</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.12（点2）</t>
+          <t>確認事項No.59（点2）</t>
         </is>
       </c>
     </row>
@@ -10734,17 +10716,17 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>骨子案の内容の確認</t>
+          <t>交付金の評価項目と19施策の割当て</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>骨子案は提出した内容のままとする</t>
+          <t>交付金の評価項目と19施策の割当ては当方の案のままとする</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.18（点2）</t>
+          <t>確認事項No.61（点2）</t>
         </is>
       </c>
     </row>
@@ -10759,17 +10741,17 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標の読替えの考え方</t>
+          <t>職員個票のリストによる重複確認の可否</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標の読替えは当方の案のままとする</t>
+          <t>職員個票を突き合わせず、事業所への照会により重複を判別する</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.22（点2）</t>
+          <t>確認事項No.80（点2）</t>
         </is>
       </c>
     </row>
@@ -10784,17 +10766,17 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>令和4年度 健康とくらしの調査の集計表</t>
+          <t>構成町との意見交換会の実施方法と町別データシート</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
+          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで進める</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.27（点2）</t>
+          <t>確認事項No.83（点2）</t>
         </is>
       </c>
     </row>
@@ -10809,17 +10791,17 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>調査対象者の範囲の確認</t>
+          <t>町別データシートの内容と配付</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>現に収録している調査対象者の範囲による</t>
+          <t>町別データシートは現行の内容のまま配付する</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.28（点2）</t>
+          <t>確認事項No.85（点2）</t>
         </is>
       </c>
     </row>
@@ -10834,17 +10816,17 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の令和6年・令和7年調査の結果</t>
+          <t>成果品の統合の方針</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>公表されている全国集計の値による</t>
+          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す（現行）</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.38（点2）</t>
+          <t>確認事項No.117（点2）</t>
         </is>
       </c>
     </row>
@@ -10859,17 +10841,17 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の給付費の集計が一致しない</t>
+          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月25日の再提供により決着済み。再提供を受けたファイルの値（3町合計と円単位一致）による</t>
+          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.46（点2）</t>
+          <t>確認事項No.138（点2）</t>
         </is>
       </c>
     </row>
@@ -10884,17 +10866,17 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの実績値シートの確認</t>
+          <t>健康とくらしの調査の個票の再提供の要否</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>総括表（保険者単位）を用い、計画作成支援ツールの実績値シートは比較のためにのみ用いる</t>
+          <t>健康とくらしの調査の個票の再提供を依頼しない（成果品は収録済みで内容が確定しており、現時点で不足がない）</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.47（点2）</t>
+          <t>確認事項No.139（点2）</t>
         </is>
       </c>
     </row>
@@ -10909,17 +10891,17 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
+          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値による</t>
+          <t>受領済みの画面の写しの範囲で概算し、確認できていない項目はその旨を明記する</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.48（点2）</t>
+          <t>確認事項No.148（点2）</t>
         </is>
       </c>
     </row>
@@ -10934,17 +10916,17 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>年報・月報の受領に伴う確認</t>
+          <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>受領済みの年報・月報の値による</t>
+          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.50（点2）</t>
+          <t>確認事項No.60（点2）</t>
         </is>
       </c>
     </row>
@@ -10959,17 +10941,17 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれ（ご報告）</t>
+          <t>区域内に事業所がないサービスの住民向けの記載</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれは記録として残し、計画本文には用いない</t>
+          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.51（点2）</t>
+          <t>確認事項No.64（点2）</t>
         </is>
       </c>
     </row>
@@ -10984,17 +10966,17 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領に伴う確認</t>
+          <t>成果指向型配分枠（令和8年度新設）への対応</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
+          <t>成果指向型配分枠への対応状況を確認できないものとして、第10期の施策には位置づけず、確認でき次第加える</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.52（点2）</t>
+          <t>確認事項No.69（点2）</t>
         </is>
       </c>
     </row>
@@ -11009,17 +10991,17 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合は1億円あたり月額約▲310円となることを併記する</t>
+          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.53（点2）</t>
+          <t>確認事項No.89（点2）</t>
         </is>
       </c>
     </row>
@@ -11034,17 +11016,17 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>議事録の文書プロパティに個人名が再度入る</t>
+          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>議事録は作成者名を落として再出力する（当方で対応する）</t>
+          <t>第9期計画の本文及び前回調査の原集計表を受領できないものとして、前回調査との比較は割合のみとし、指標別の分母を確認できない旨を注記する</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.54（点2）</t>
+          <t>確認事項No.90（点2）</t>
         </is>
       </c>
     </row>
@@ -11059,17 +11041,17 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記に関するご提案3件</t>
+          <t>介護給付費通知及び給付実績の活用による確認等</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記はご提案3件のとおり改める</t>
+          <t>介護給付費通知の実施状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.55（点2）</t>
+          <t>確認事項No.91（点2）</t>
         </is>
       </c>
     </row>
@@ -11084,17 +11066,17 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
+          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>他団体の集計帳票6件は成果品に用いない</t>
+          <t>認定調査の委託の状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.56（点2）</t>
+          <t>確認事項No.92（点2）</t>
         </is>
       </c>
     </row>
@@ -11109,17 +11091,17 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>調整交付金の算定基礎の確認</t>
+          <t>令和9年4月1日から義務となる2件への対応</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>現行の扱い（第9期の算定を再現し公表値6,428円と一致する扱い）による</t>
+          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.59（点2）</t>
+          <t>確認事項No.97（点2）</t>
         </is>
       </c>
     </row>
@@ -11134,17 +11116,17 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当て</t>
+          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当ては当方の案のままとする</t>
+          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.61（点2）</t>
+          <t>確認事項No.99（点2）</t>
         </is>
       </c>
     </row>
@@ -11159,17 +11141,17 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>職員個票のリストによる重複確認の可否</t>
+          <t>補正しても外れるサービス6件の理由</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>職員個票を突き合わせず、事業所への照会により重複を判別する</t>
+          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.80（点2）</t>
+          <t>確認事項No.108（点2）</t>
         </is>
       </c>
     </row>
@@ -11184,17 +11166,17 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>構成町との意見交換会の実施方法と町別データシート</t>
+          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで進める</t>
+          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.83（点2）</t>
+          <t>確認事項No.111（点2）</t>
         </is>
       </c>
     </row>
@@ -11209,17 +11191,17 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>町別データシートの内容と配付</t>
+          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>町別データシートは現行の内容のまま配付する</t>
+          <t>施策2-5の代表KPIはO2（提起された地域課題のうち翌年度の事業・予算に反映されたものの割合）とする（当方案）</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.85（点2）</t>
+          <t>確認事項No.118（点2）</t>
         </is>
       </c>
     </row>
@@ -11234,17 +11216,17 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>成果品の統合の方針</t>
+          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す（現行）</t>
+          <t>地域ケア会議の記録様式は協議資料にとどめ、令和9年度に整える</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.117（点2）</t>
+          <t>確認事項No.119（点2）</t>
         </is>
       </c>
     </row>
@@ -11259,17 +11241,17 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.138（点2）</t>
+          <t>確認事項No.120（点2）</t>
         </is>
       </c>
     </row>
@@ -11284,17 +11266,17 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供の要否</t>
+          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供を依頼しない（成果品は収録済みで内容が確定しており、現時点で不足がない）</t>
+          <t>令和7年度の実施報告書により把握できる範囲で記述する</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.139（点2）</t>
+          <t>確認事項No.121（点2）</t>
         </is>
       </c>
     </row>
@@ -11309,17 +11291,17 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
+          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>受領済みの画面の写しの範囲で概算し、確認できていない項目はその旨を明記する</t>
+          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.148（点2）</t>
+          <t>確認事項No.125（点2）</t>
         </is>
       </c>
     </row>
@@ -11334,17 +11316,17 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提（受託者案）</t>
+          <t>見える化システムの総人口の設定を案Cに改めるか</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
+          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.60（点2）</t>
+          <t>確認事項No.127（点2）</t>
         </is>
       </c>
     </row>
@@ -11359,17 +11341,17 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスの住民向けの記載</t>
+          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
+          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.64（点2）</t>
+          <t>確認事項No.133（点2）</t>
         </is>
       </c>
     </row>
@@ -11384,17 +11366,17 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠（令和8年度新設）への対応</t>
+          <t>画面の令和7年度と年報の月平均の食い違い</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠への対応状況を確認できないものとして、第10期の施策には位置づけず、確認でき次第加える</t>
+          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.69（点2）</t>
+          <t>確認事項No.136（点2）</t>
         </is>
       </c>
     </row>
@@ -11409,17 +11391,17 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+          <t>計画素案の未確定箇所の表示の統一</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
+          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとする</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.89（点2）</t>
+          <t>確認事項No.143（点2）</t>
         </is>
       </c>
     </row>
@@ -11434,17 +11416,17 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
+          <t>計画素案 第2章第1節に町別の図を加えるか</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文及び前回調査の原集計表を受領できないものとして、前回調査との比較は割合のみとし、指標別の分母を確認できない旨を注記する</t>
+          <t>計画素案 第2章第1節に町別の図を加えない。加筆分は協議用の資料にとどめる</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.90（点2）</t>
+          <t>確認事項No.154（点2）</t>
         </is>
       </c>
     </row>
@@ -11459,17 +11441,17 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知及び給付実績の活用による確認等</t>
+          <t>中長期推計を令和12・27・32年度まで広げるか</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知の実施状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
+          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.91（点2）</t>
+          <t>確認事項No.157（点2）</t>
         </is>
       </c>
     </row>
@@ -11484,17 +11466,17 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
+          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>認定調査の委託の状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
+          <t>設問ごとの有効回答を分母とし、町別の値は掲げない（令和8年9月25日に是正済み）</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.92（点2）</t>
+          <t>確認事項No.158（点2）</t>
         </is>
       </c>
     </row>
@@ -11509,17 +11491,17 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月1日から義務となる2件への対応</t>
+          <t>東川町の通いの場の整備と担い手の確保</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
+          <t>現状のまま（東川町の整備を見込まない）第10期の目標値を置く</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.97（点2）</t>
+          <t>確認事項No.159（点2）</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11516,17 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
+          <t>東川町の認知症サポーター養成講座の実施状況</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
+          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.99（点2）</t>
+          <t>確認事項No.160（点2）</t>
         </is>
       </c>
     </row>
@@ -11559,17 +11541,17 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れるサービス6件の理由</t>
+          <t>東川町のチームオレンジ事業の位置づけ</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
+          <t>東川町の取組として記述し3町展開は記述しない</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.108（点2）</t>
+          <t>確認事項No.161（点2）</t>
         </is>
       </c>
     </row>
@@ -11584,17 +11566,17 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
+          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
+          <t>令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.111（点2）</t>
+          <t>確認事項No.162（点2）</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11591,17 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
+          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIはO2（提起された地域課題のうち翌年度の事業・予算に反映されたものの割合）とする（当方案）</t>
+          <t>美瑛町の取組として記述し3町展開は記述しない</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.118（点2）</t>
+          <t>確認事項No.163（点2）</t>
         </is>
       </c>
     </row>
@@ -11634,17 +11616,17 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
+          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の記録様式は協議資料にとどめ、令和9年度に整える</t>
+          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.119（点2）</t>
+          <t>確認事項No.164（点2）</t>
         </is>
       </c>
     </row>
@@ -11659,17 +11641,17 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
+          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
+          <t>現に確認できる取組の範囲で記述する</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.120（点2）</t>
+          <t>確認事項No.165（点2）</t>
         </is>
       </c>
     </row>
@@ -11684,17 +11666,17 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
+          <t>東神楽町の通いの場の維持</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の実施報告書により把握できる範囲で記述する</t>
+          <t>令和6年度の水準が続くものとして目標値を置く</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.121（点2）</t>
+          <t>確認事項No.166（点2）</t>
         </is>
       </c>
     </row>
@@ -11709,17 +11691,17 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
+          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
+          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.125（点2）</t>
+          <t>確認事項No.167（点2）</t>
         </is>
       </c>
     </row>
@@ -11734,17 +11716,17 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総人口の設定を案Cに改めるか</t>
+          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
+          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.127（点2）</t>
+          <t>確認事項No.170（点2）</t>
         </is>
       </c>
     </row>
@@ -11759,17 +11741,17 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
+          <t>の当方の扱い＝掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.133（点2）</t>
+          <t>確認事項No.172（点2）</t>
         </is>
       </c>
     </row>
@@ -11784,17 +11766,17 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度と年報の月平均の食い違い</t>
+          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
+          <t>の当方の扱い＝案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.136（点2）</t>
+          <t>確認事項No.174（点2）</t>
         </is>
       </c>
     </row>
@@ -11809,17 +11791,17 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所の表示の統一</t>
+          <t>保険料算定の前提</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとする</t>
+          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.143（点2）</t>
+          <t>確認事項No.16（点2）</t>
         </is>
       </c>
     </row>
@@ -11834,17 +11816,17 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えるか</t>
+          <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えない。加筆分は協議用の資料にとどめる</t>
+          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.154（点2）</t>
+          <t>確認事項No.2（点1）</t>
         </is>
       </c>
     </row>
@@ -11859,17 +11841,17 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>中長期推計を令和12・27・32年度まで広げるか</t>
+          <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
+          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.157（点2）</t>
+          <t>確認事項No.13（点1）</t>
         </is>
       </c>
     </row>
@@ -11884,17 +11866,17 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
+          <t>人口推計の基礎とする系列</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>設問ごとの有効回答を分母とし、町別の値は掲げない（令和8年9月25日に是正済み）</t>
+          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.158（点2）</t>
+          <t>確認事項No.14（点1）</t>
         </is>
       </c>
     </row>
@@ -11909,17 +11891,17 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>東川町の通いの場の整備と担い手の確保</t>
+          <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>現状のまま（東川町の整備を見込まない）第10期の目標値を置く</t>
+          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.159（点2）</t>
+          <t>確認事項No.15（点1）</t>
         </is>
       </c>
     </row>
@@ -11934,17 +11916,17 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>東川町の認知症サポーター養成講座の実施状況</t>
+          <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
+          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.160（点2）</t>
+          <t>確認事項No.17（点1）</t>
         </is>
       </c>
     </row>
@@ -11959,17 +11941,17 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>東川町のチームオレンジ事業の位置づけ</t>
+          <t>北海道・圏域との調整の場</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>東川町の取組として記述し3町展開は記述しない</t>
+          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.161（点2）</t>
+          <t>確認事項No.20（点1）</t>
         </is>
       </c>
     </row>
@@ -11984,17 +11966,17 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
+          <t>成果品の仕様</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残す</t>
+          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.162（点2）</t>
+          <t>確認事項No.21（点1）</t>
         </is>
       </c>
     </row>
@@ -12009,17 +11991,17 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
+          <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の取組として記述し3町展開は記述しない</t>
+          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.163（点2）</t>
+          <t>確認事項No.23（点1）</t>
         </is>
       </c>
     </row>
@@ -12034,17 +12016,17 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
+          <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
+          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.164（点2）</t>
+          <t>確認事項No.26（点1）</t>
         </is>
       </c>
     </row>
@@ -12059,17 +12041,17 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
+          <t>重度化の速度の前提</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述する</t>
+          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.165（点2）</t>
+          <t>確認事項No.29（点1）</t>
         </is>
       </c>
     </row>
@@ -12084,17 +12066,17 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の通いの場の維持</t>
+          <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の水準が続くものとして目標値を置く</t>
+          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.166（点2）</t>
+          <t>確認事項No.31（点1）</t>
         </is>
       </c>
     </row>
@@ -12109,17 +12091,17 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
+          <t>統合した成果品の元の資料を残すか</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
+          <t>統合した成果品の元の資料を残す</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.167（点2）</t>
+          <t>確認事項No.144（点1）</t>
         </is>
       </c>
     </row>
@@ -12134,17 +12116,17 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
+          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
+          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.170（点2）</t>
+          <t>確認事項No.156（点1）</t>
         </is>
       </c>
     </row>
@@ -12159,17 +12141,17 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
+          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>の当方の扱い＝掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
+          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.172（点2）</t>
+          <t>確認事項No.169（点1）</t>
         </is>
       </c>
     </row>
@@ -12184,17 +12166,17 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
+          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>の当方の扱い＝案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
+          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.174（点2）</t>
+          <t>確認事項No.171（点1）</t>
         </is>
       </c>
     </row>
@@ -12209,17 +12191,17 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提</t>
+          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
+          <t>の当方の扱い＝現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.16（点2）</t>
+          <t>確認事項No.173（点1）</t>
         </is>
       </c>
     </row>
@@ -12234,17 +12216,17 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
+          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
+          <t>の当方の扱い＝国が示す本格運用開始日（令和10年4月1日）までに完了することを前提として計画素案に記載し、年度ごとの工程は［要確認］として残す。事業所への周知は広域連合と3町が共同で行うものとして記載する</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.2（点1）</t>
+          <t>確認事項No.175（点1）</t>
         </is>
       </c>
     </row>
@@ -12259,17 +12241,17 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域の判定資料</t>
+          <t>介護サービス事業者経営情報データベースの公表結果の活用の範囲</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
+          <t>の当方の扱い＝公表された区分のうち当区域の事業所の規模に近いものを参考として用い、区域内の事業所の経営状況を表すものとしては用いない。計画素案には活用の方針のみを記載し、数値は掲げない</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.13（点1）</t>
+          <t>確認事項No.176（点1）</t>
         </is>
       </c>
     </row>
@@ -12284,17 +12266,17 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎とする系列</t>
+          <t>都道府県との協定に基づく連携への関与</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
+          <t>の当方の扱い＝計画素案には北海道及び事業者とともに活用を検討する旨のみを記載し、具体の取組及び目標は国から市町村の役割が示された後に定める</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.14（点1）</t>
+          <t>確認事項No.177（点1）</t>
         </is>
       </c>
     </row>
@@ -12309,17 +12291,17 @@
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>認定者数の基準月と月次推移</t>
+          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
+          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.15（点1）</t>
+          <t>確認事項No.74（点1）</t>
         </is>
       </c>
     </row>
@@ -12334,17 +12316,17 @@
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>3町計画への共通指標の掲載</t>
+          <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
+          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.17（点1）</t>
+          <t>確認事項No.24（点0）</t>
         </is>
       </c>
     </row>
@@ -12359,440 +12341,40 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場</t>
+          <t>代表KPIの目標値の決定</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
+          <t>代表KPIの目標値は、令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置く</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.20（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="44" customHeight="1">
-      <c r="A108" s="5" t="n">
-        <v>103</v>
-      </c>
-      <c r="B108" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>成果品の仕様</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
-        </is>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.21（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="44" customHeight="1">
-      <c r="A109" s="5" t="n">
-        <v>104</v>
-      </c>
-      <c r="B109" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>事業所の定員・稼働率データ</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.23（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="44" customHeight="1">
-      <c r="A110" s="5" t="n">
-        <v>105</v>
-      </c>
-      <c r="B110" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>認知症・医療介護連携の実績データ</t>
-        </is>
-      </c>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
-        </is>
-      </c>
-      <c r="E110" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.26（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="44" customHeight="1">
-      <c r="A111" s="5" t="n">
-        <v>106</v>
-      </c>
-      <c r="B111" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>重度化の速度の前提</t>
-        </is>
-      </c>
-      <c r="D111" s="6" t="inlineStr">
-        <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
-        </is>
-      </c>
-      <c r="E111" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.29（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="44" customHeight="1">
-      <c r="A112" s="5" t="n">
-        <v>107</v>
-      </c>
-      <c r="B112" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>給付適正化の実施予定と推計での扱い</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr">
-        <is>
-          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
-        </is>
-      </c>
-      <c r="E112" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.31（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="44" customHeight="1">
-      <c r="A113" s="5" t="n">
-        <v>108</v>
-      </c>
-      <c r="B113" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>統合した成果品の元の資料を残すか</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>統合した成果品の元の資料を残す</t>
-        </is>
-      </c>
-      <c r="E113" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.144（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="44" customHeight="1">
-      <c r="A114" s="5" t="n">
-        <v>109</v>
-      </c>
-      <c r="B114" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
-        </is>
-      </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.156（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="44" customHeight="1">
-      <c r="A115" s="5" t="n">
-        <v>110</v>
-      </c>
-      <c r="B115" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr">
-        <is>
-          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
-        </is>
-      </c>
-      <c r="E115" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.169（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="44" customHeight="1">
-      <c r="A116" s="5" t="n">
-        <v>111</v>
-      </c>
-      <c r="B116" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
-        </is>
-      </c>
-      <c r="E116" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.171（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="44" customHeight="1">
-      <c r="A117" s="5" t="n">
-        <v>112</v>
-      </c>
-      <c r="B117" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>の当方の扱い＝現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
-        </is>
-      </c>
-      <c r="E117" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.173（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="44" customHeight="1">
-      <c r="A118" s="5" t="n">
-        <v>113</v>
-      </c>
-      <c r="B118" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>の当方の扱い＝国が示す本格運用開始日（令和10年4月1日）までに完了することを前提として計画素案に記載し、年度ごとの工程は［要確認］として残す。事業所への周知は広域連合と3町が共同で行うものとして記載する</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.175（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="44" customHeight="1">
-      <c r="A119" s="5" t="n">
-        <v>114</v>
-      </c>
-      <c r="B119" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>介護サービス事業者経営情報データベースの公表結果の活用の範囲</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>の当方の扱い＝公表された区分のうち当区域の事業所の規模に近いものを参考として用い、区域内の事業所の経営状況を表すものとしては用いない。計画素案には活用の方針のみを記載し、数値は掲げない</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.176（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="44" customHeight="1">
-      <c r="A120" s="5" t="n">
-        <v>115</v>
-      </c>
-      <c r="B120" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>都道府県との協定に基づく連携への関与</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>の当方の扱い＝計画素案には北海道及び事業者とともに活用を検討する旨のみを記載し、具体の取組及び目標は国から市町村の役割が示された後に定める</t>
-        </is>
-      </c>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.177（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="44" customHeight="1">
-      <c r="A121" s="5" t="n">
-        <v>116</v>
-      </c>
-      <c r="B121" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.74（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="44" customHeight="1">
-      <c r="A122" s="5" t="n">
-        <v>117</v>
-      </c>
-      <c r="B122" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>24時間対応サービスの確保方策の決定</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.24（点0）</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="44" customHeight="1">
-      <c r="A123" s="5" t="n">
-        <v>118</v>
-      </c>
-      <c r="B123" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>代表KPIの目標値の決定</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>代表KPIの目標値は、令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置く</t>
-        </is>
-      </c>
-      <c r="E123" s="6" t="inlineStr">
-        <is>
           <t>確認事項No.25（点0）</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="76" customHeight="1">
-      <c r="A124" s="13" t="inlineStr">
+    <row r="108" ht="76" customHeight="1">
+      <c r="A108" s="13" t="inlineStr">
         <is>
           <t>注1）「据え置き（区分A）」は、資料の受領を待たずに当方の側で確定できるものです。
 注2）「既定値で進める」は、決着しない場合の扱いを置けているため決定を待たずに作業を進められるものです。決定を受けた時点で見直します。
 注3）ここに現れないもの（既定値を置けていない確認事項）は、扱いを決めること自体が翌日の作業になります。02シートを見ます。
-注4）既定値のとおり計画素案へ反映し終えたもの46件（確認事項No.7・No.33・No.39・No.40・No.43・No.45・No.57・No.58・No.63・No.82・No.84・No.86・No.88・No.93・No.94・No.98・No.100・No.101・No.103・No.104・No.105・No.106・No.107・No.109・No.110・No.112・No.113・No.114・No.116・No.123・No.126・No.128・No.129・No.130・No.131・No.132・No.137・No.141・No.142・No.145・No.146・No.147・No.150・No.151・No.152・No.153）は、作業としては終わっているため本表から除いています。ご決定はなお待っています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="125"/>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="3" t="inlineStr">
+注4）既定値のとおり計画素案へ反映し終えたもの62件（確認事項No.7・No.33・No.39・No.40・No.43・No.45・No.57・No.58・No.63・No.65・No.66・No.67・No.68・No.70・No.73・No.75・No.76・No.77・No.78・No.79・No.81・No.82・No.84・No.86・No.88・No.93・No.94・No.95・No.96・No.98・No.100・No.101・No.102・No.103・No.104・No.105・No.106・No.107・No.109・No.110・No.112・No.113・No.114・No.116・No.122・No.123・No.126・No.128・No.129・No.130・No.131・No.132・No.137・No.141・No.142・No.145・No.146・No.147・No.150・No.151・No.152・No.153）は、作業としては終わっているため本表から除いています。ご決定はなお待っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109"/>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t>2　先に扱いを決めるもの（既定値を置けていない）　0件</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="18" customHeight="1">
-      <c r="A127" s="20" t="inlineStr">
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="20" t="inlineStr">
         <is>
           <t>ありません。未決の確認事項の全件に扱いを置けています。</t>
         </is>
@@ -12803,9 +12385,9 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A127:E127"/>
-    <mergeCell ref="A126:E126"/>
-    <mergeCell ref="A124:E124"/>
+    <mergeCell ref="A108:E108"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A110:E110"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12830,7 +12412,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>翌日（令和8年10月6日）の作業順位</t>
+          <t>翌日（令和8年10月8日）の作業順位</t>
         </is>
       </c>
     </row>
@@ -12880,17 +12462,17 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位</t>
+          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
+          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.65（点3）</t>
+          <t>確認事項No.124（点3）</t>
         </is>
       </c>
     </row>
@@ -12905,17 +12487,17 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>サービスガイドに掲載する事業所の範囲</t>
+          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>サービスガイドに掲載する事業所の範囲は北海道の指定事業所一覧（最新のもの）による</t>
+          <t>在宅生活改善調査の結果は「在宅で困難を抱える方の状況」として引き、在宅の認定者全体の割合としては引かない</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.66（点3）</t>
+          <t>確認事項No.140（点3）</t>
         </is>
       </c>
     </row>
@@ -12930,17 +12512,17 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>算定方法の国の様式との整合（点検結果）</t>
+          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
+          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.67（点3）</t>
+          <t>確認事項No.149（点3）</t>
         </is>
       </c>
     </row>
@@ -12955,17 +12537,17 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの自然体推計の再出力のお願い</t>
+          <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
+          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.68（点3）</t>
+          <t>確認事項No.30（点3）</t>
         </is>
       </c>
     </row>
@@ -12980,17 +12562,17 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>交付金の全国順位の計画本文への掲載</t>
+          <t>第9段階の乗率の経緯</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>交付金の全国順位は計画本文に掲載せず、策定委員会資料にとどめる（確認事項No.71のとおり）</t>
+          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.70（点3）</t>
+          <t>確認事項No.34（点3）</t>
         </is>
       </c>
     </row>
@@ -13005,17 +12587,17 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
+          <t>上川管内の保険者の所得段階数と乗率</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）は協議資料にとどめ素案に入れない</t>
+          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.73（点3）</t>
+          <t>確認事項No.35（点3）</t>
         </is>
       </c>
     </row>
@@ -13030,17 +12612,17 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>代表KPIと改善事項の再整理案</t>
+          <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>代表KPIと改善事項は当方の再整理案のままとする</t>
+          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.75（点3）</t>
+          <t>確認事項No.36（点3）</t>
         </is>
       </c>
     </row>
@@ -13055,17 +12637,17 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>介護リームスから抽出できる項目</t>
+          <t>令和9年4月に新設される区分を見込量に立てるか</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>介護リームスから抽出できないものとして、代表KPI H03は未算定のままとする</t>
+          <t>令和9年4月新設の3区分を0として立てる</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.76（点3）</t>
+          <t>確認事項No.115（点3）</t>
         </is>
       </c>
     </row>
@@ -13436,7 +13018,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>記録 令和8年10月5日／本表 令和8年10月5日</t>
+          <t>記録 令和8年10月7日／本表 令和8年10月7日</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -13511,7 +13093,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>118件（区分A 0・既定値 118）</t>
+          <t>102件（区分A 0・既定値 102）</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -749,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>56a309f</t>
+          <t>2225818</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>意見交換会資料に時間配分と令和8年9月の制度の動向を加えた</t>
+          <t>WBSを更新し、既定値のとおり16件を処理した（令和8年10月7日）</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>46b25f6</t>
+          <t>56a309f</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>事前打合せ資料に最低限の確認事項と時間配分を加えた（1〜2時間の枠）</t>
+          <t>意見交換会資料に時間配分と令和8年9月の制度の動向を加えた</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
@@ -1270,20 +1270,38 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>763e6ce</t>
+          <t>46b25f6</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月18日 介護保険部会資料による計画素案の是正（指摘15件）</t>
+          <t>事前打合せ資料に最低限の確認事項と時間配分を加えた（1〜2時間の枠）</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr"/>
       <c r="E25" s="6" t="inlineStr"/>
       <c r="F25" s="6" t="inlineStr"/>
     </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>763e6ce</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>令和8年9月18日 介護保険部会資料による計画素案の是正（指摘15件）</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
@@ -1294,8 +1312,8 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4028,7 +4046,7 @@
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>素案 第3章第2節・第3節・第5節
+          <t>素案 第3章第2節・第3節・第4節
 妥当性検証報告書 12シート</t>
         </is>
       </c>
@@ -9750,7 +9768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F111"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9778,7 +9796,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　当方の作業だけで進められるもの　102件</t>
+          <t>1　当方の作業だけで進められるもの　86件</t>
         </is>
       </c>
     </row>
@@ -9816,17 +9834,17 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
+          <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
+          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.124（点3）</t>
+          <t>確認事項No.9（点2）</t>
         </is>
       </c>
     </row>
@@ -9841,17 +9859,17 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
+          <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果は「在宅で困難を抱える方の状況」として引き、在宅の認定者全体の割合としては引かない</t>
+          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.140（点3）</t>
+          <t>確認事項No.10（点2）</t>
         </is>
       </c>
     </row>
@@ -9866,17 +9884,17 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
+          <t>町別の人口・世帯データ</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
+          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.149（点3）</t>
+          <t>確認事項No.11（点2）</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9909,17 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けた要介護度の変化</t>
+          <t>日常生活圏域別のデータ</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
+          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.30（点3）</t>
+          <t>確認事項No.12（点2）</t>
         </is>
       </c>
     </row>
@@ -9916,17 +9934,17 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率の経緯</t>
+          <t>骨子案の内容の確認</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
+          <t>骨子案は提出した内容のままとする</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.34（点3）</t>
+          <t>確認事項No.18（点2）</t>
         </is>
       </c>
     </row>
@@ -9941,17 +9959,17 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
+          <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
+          <t>北海道の評価指標の読替えは当方の案のままとする</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.35（点3）</t>
+          <t>確認事項No.22（点2）</t>
         </is>
       </c>
     </row>
@@ -9966,17 +9984,17 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績と収納率</t>
+          <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
+          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.36（点3）</t>
+          <t>確認事項No.27（点2）</t>
         </is>
       </c>
     </row>
@@ -9991,17 +10009,17 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+          <t>調査対象者の範囲の確認</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月新設の3区分を0として立てる</t>
+          <t>現に収録している調査対象者の範囲による</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.115（点3）</t>
+          <t>確認事項No.28（点2）</t>
         </is>
       </c>
     </row>
@@ -10016,17 +10034,17 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16の代理指標</t>
+          <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16は代理指標への振替案のとおりとする</t>
+          <t>公表されている全国集計の値による</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.4（点2）</t>
+          <t>確認事項No.38（点2）</t>
         </is>
       </c>
     </row>
@@ -10041,17 +10059,17 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績</t>
+          <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績を受領できないものとして、公表資料（交付金の評価結果・総合事業の実施状況に関する調査・年報）により評価する</t>
+          <t>令和8年9月25日の再提供により決着済み。再提供を受けたファイルの値（3町合計と円単位一致）による</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.5（点2）</t>
+          <t>確認事項No.46（点2）</t>
         </is>
       </c>
     </row>
@@ -10066,17 +10084,17 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項の取扱い</t>
+          <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項は当方の判定のままとする</t>
+          <t>総括表（保険者単位）を用い、計画作成支援ツールの実績値シートは比較のためにのみ用いる</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.8（点2）</t>
+          <t>確認事項No.47（点2）</t>
         </is>
       </c>
     </row>
@@ -10091,17 +10109,17 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>会議日程とパブリックコメントの期間</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>会議日程及びパブリックコメントの期間は仕様書５の工程による</t>
+          <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値による</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.19（点2）</t>
+          <t>確認事項No.48（点2）</t>
         </is>
       </c>
     </row>
@@ -10116,17 +10134,17 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料への工程表の反映</t>
+          <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>現行の工程表のまま進める</t>
+          <t>受領済みの年報・月報の値による</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.42（点2）</t>
+          <t>確認事項No.50（点2）</t>
         </is>
       </c>
     </row>
@@ -10141,17 +10159,17 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>特別地域加算の対象地域告示</t>
+          <t>月報の値の接続のずれ（ご報告）</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>告示を確認できないものとして、特別地域加算の判定を計画素案に書かず［要確認］のまま残す</t>
+          <t>月報の値の接続のずれは記録として残し、計画本文には用いない</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.1（点2）</t>
+          <t>確認事項No.51（点2）</t>
         </is>
       </c>
     </row>
@@ -10166,17 +10184,17 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較分析の対象</t>
+          <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較は公表されている同規模保険者40団体による</t>
+          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.3（点2）</t>
+          <t>確認事項No.52（点2）</t>
         </is>
       </c>
     </row>
@@ -10191,17 +10209,17 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価調書</t>
+          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>評価調書を受領できないものとして、得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できない旨を注記する</t>
+          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合は1億円あたり月額約▲310円となることを併記する</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.6（点2）</t>
+          <t>確認事項No.53（点2）</t>
         </is>
       </c>
     </row>
@@ -10216,17 +10234,17 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>調査の対象者範囲と回収率</t>
+          <t>議事録の文書プロパティに個人名が再度入る</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
+          <t>議事録は作成者名を落として再出力する（当方で対応する）</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.9（点2）</t>
+          <t>確認事項No.54（点2）</t>
         </is>
       </c>
     </row>
@@ -10241,17 +10259,17 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>介護人材実態調査の採用者数・退職者数</t>
+          <t>議事録の表記に関するご提案3件</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
+          <t>議事録の表記はご提案3件のとおり改める</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.10（点2）</t>
+          <t>確認事項No.55（点2）</t>
         </is>
       </c>
     </row>
@@ -10266,17 +10284,17 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>町別の人口・世帯データ</t>
+          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
+          <t>他団体の集計帳票6件は成果品に用いない</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.11（点2）</t>
+          <t>確認事項No.56（点2）</t>
         </is>
       </c>
     </row>
@@ -10291,17 +10309,17 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域別のデータ</t>
+          <t>調整交付金の算定基礎の確認</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
+          <t>現行の扱い（第9期の算定を再現し公表値6,428円と一致する扱い）による</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.12（点2）</t>
+          <t>確認事項No.59（点2）</t>
         </is>
       </c>
     </row>
@@ -10316,17 +10334,17 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>骨子案の内容の確認</t>
+          <t>交付金の評価項目と19施策の割当て</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>骨子案は提出した内容のままとする</t>
+          <t>交付金の評価項目と19施策の割当ては当方の案のままとする</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.18（点2）</t>
+          <t>確認事項No.61（点2）</t>
         </is>
       </c>
     </row>
@@ -10341,17 +10359,17 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標の読替えの考え方</t>
+          <t>職員個票のリストによる重複確認の可否</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標の読替えは当方の案のままとする</t>
+          <t>職員個票を突き合わせず、事業所への照会により重複を判別する</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.22（点2）</t>
+          <t>確認事項No.80（点2）</t>
         </is>
       </c>
     </row>
@@ -10366,17 +10384,17 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>令和4年度 健康とくらしの調査の集計表</t>
+          <t>構成町との意見交換会の実施方法と町別データシート</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
+          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで進める</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.27（点2）</t>
+          <t>確認事項No.83（点2）</t>
         </is>
       </c>
     </row>
@@ -10391,17 +10409,17 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>調査対象者の範囲の確認</t>
+          <t>町別データシートの内容と配付</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>現に収録している調査対象者の範囲による</t>
+          <t>町別データシートは現行の内容のまま配付する</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.28（点2）</t>
+          <t>確認事項No.85（点2）</t>
         </is>
       </c>
     </row>
@@ -10416,17 +10434,17 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の令和6年・令和7年調査の結果</t>
+          <t>成果品の統合の方針</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>公表されている全国集計の値による</t>
+          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す（現行）</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.38（点2）</t>
+          <t>確認事項No.117（点2）</t>
         </is>
       </c>
     </row>
@@ -10441,17 +10459,17 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の給付費の集計が一致しない</t>
+          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月25日の再提供により決着済み。再提供を受けたファイルの値（3町合計と円単位一致）による</t>
+          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.46（点2）</t>
+          <t>確認事項No.138（点2）</t>
         </is>
       </c>
     </row>
@@ -10466,17 +10484,17 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの実績値シートの確認</t>
+          <t>健康とくらしの調査の個票の再提供の要否</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>総括表（保険者単位）を用い、計画作成支援ツールの実績値シートは比較のためにのみ用いる</t>
+          <t>健康とくらしの調査の個票の再提供を依頼しない（成果品は収録済みで内容が確定しており、現時点で不足がない）</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.47（点2）</t>
+          <t>確認事項No.139（点2）</t>
         </is>
       </c>
     </row>
@@ -10491,17 +10509,17 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
+          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値による</t>
+          <t>受領済みの画面の写しの範囲で概算し、確認できていない項目はその旨を明記する</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.48（点2）</t>
+          <t>確認事項No.148（点2）</t>
         </is>
       </c>
     </row>
@@ -10516,17 +10534,17 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>年報・月報の受領に伴う確認</t>
+          <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>受領済みの年報・月報の値による</t>
+          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.50（点2）</t>
+          <t>確認事項No.60（点2）</t>
         </is>
       </c>
     </row>
@@ -10541,17 +10559,17 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれ（ご報告）</t>
+          <t>区域内に事業所がないサービスの住民向けの記載</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれは記録として残し、計画本文には用いない</t>
+          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.51（点2）</t>
+          <t>確認事項No.64（点2）</t>
         </is>
       </c>
     </row>
@@ -10566,17 +10584,17 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領に伴う確認</t>
+          <t>成果指向型配分枠（令和8年度新設）への対応</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
+          <t>成果指向型配分枠への対応状況を確認できないものとして、第10期の施策には位置づけず、確認でき次第加える</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.52（点2）</t>
+          <t>確認事項No.69（点2）</t>
         </is>
       </c>
     </row>
@@ -10591,17 +10609,17 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合は1億円あたり月額約▲310円となることを併記する</t>
+          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.53（点2）</t>
+          <t>確認事項No.89（点2）</t>
         </is>
       </c>
     </row>
@@ -10616,17 +10634,17 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>議事録の文書プロパティに個人名が再度入る</t>
+          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>議事録は作成者名を落として再出力する（当方で対応する）</t>
+          <t>第9期計画の本文及び前回調査の原集計表を受領できないものとして、前回調査との比較は割合のみとし、指標別の分母を確認できない旨を注記する</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.54（点2）</t>
+          <t>確認事項No.90（点2）</t>
         </is>
       </c>
     </row>
@@ -10641,17 +10659,17 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記に関するご提案3件</t>
+          <t>介護給付費通知及び給付実績の活用による確認等</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記はご提案3件のとおり改める</t>
+          <t>介護給付費通知の実施状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.55（点2）</t>
+          <t>確認事項No.91（点2）</t>
         </is>
       </c>
     </row>
@@ -10666,17 +10684,17 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
+          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>他団体の集計帳票6件は成果品に用いない</t>
+          <t>認定調査の委託の状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.56（点2）</t>
+          <t>確認事項No.92（点2）</t>
         </is>
       </c>
     </row>
@@ -10691,17 +10709,17 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>調整交付金の算定基礎の確認</t>
+          <t>令和9年4月1日から義務となる2件への対応</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>現行の扱い（第9期の算定を再現し公表値6,428円と一致する扱い）による</t>
+          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.59（点2）</t>
+          <t>確認事項No.97（点2）</t>
         </is>
       </c>
     </row>
@@ -10716,17 +10734,17 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当て</t>
+          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当ては当方の案のままとする</t>
+          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.61（点2）</t>
+          <t>確認事項No.99（点2）</t>
         </is>
       </c>
     </row>
@@ -10741,17 +10759,17 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>職員個票のリストによる重複確認の可否</t>
+          <t>補正しても外れるサービス6件の理由</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>職員個票を突き合わせず、事業所への照会により重複を判別する</t>
+          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.80（点2）</t>
+          <t>確認事項No.108（点2）</t>
         </is>
       </c>
     </row>
@@ -10766,17 +10784,17 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>構成町との意見交換会の実施方法と町別データシート</t>
+          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで進める</t>
+          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.83（点2）</t>
+          <t>確認事項No.111（点2）</t>
         </is>
       </c>
     </row>
@@ -10791,17 +10809,17 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>町別データシートの内容と配付</t>
+          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>町別データシートは現行の内容のまま配付する</t>
+          <t>施策2-5の代表KPIはO2（提起された地域課題のうち翌年度の事業・予算に反映されたものの割合）とする（当方案）</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.85（点2）</t>
+          <t>確認事項No.118（点2）</t>
         </is>
       </c>
     </row>
@@ -10816,17 +10834,17 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>成果品の統合の方針</t>
+          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す（現行）</t>
+          <t>地域ケア会議の記録様式は協議資料にとどめ、令和9年度に整える</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.117（点2）</t>
+          <t>確認事項No.119（点2）</t>
         </is>
       </c>
     </row>
@@ -10841,17 +10859,17 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.138（点2）</t>
+          <t>確認事項No.120（点2）</t>
         </is>
       </c>
     </row>
@@ -10866,17 +10884,17 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供の要否</t>
+          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供を依頼しない（成果品は収録済みで内容が確定しており、現時点で不足がない）</t>
+          <t>令和7年度の実施報告書により把握できる範囲で記述する</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.139（点2）</t>
+          <t>確認事項No.121（点2）</t>
         </is>
       </c>
     </row>
@@ -10891,17 +10909,17 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
+          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>受領済みの画面の写しの範囲で概算し、確認できていない項目はその旨を明記する</t>
+          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.148（点2）</t>
+          <t>確認事項No.125（点2）</t>
         </is>
       </c>
     </row>
@@ -10916,17 +10934,17 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提（受託者案）</t>
+          <t>見える化システムの総人口の設定を案Cに改めるか</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
+          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.60（点2）</t>
+          <t>確認事項No.127（点2）</t>
         </is>
       </c>
     </row>
@@ -10941,17 +10959,17 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスの住民向けの記載</t>
+          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
+          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.64（点2）</t>
+          <t>確認事項No.133（点2）</t>
         </is>
       </c>
     </row>
@@ -10966,17 +10984,17 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠（令和8年度新設）への対応</t>
+          <t>画面の令和7年度と年報の月平均の食い違い</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠への対応状況を確認できないものとして、第10期の施策には位置づけず、確認でき次第加える</t>
+          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.69（点2）</t>
+          <t>確認事項No.136（点2）</t>
         </is>
       </c>
     </row>
@@ -10991,17 +11009,17 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+          <t>計画素案の未確定箇所の表示の統一</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
+          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとする</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.89（点2）</t>
+          <t>確認事項No.143（点2）</t>
         </is>
       </c>
     </row>
@@ -11016,17 +11034,17 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
+          <t>計画素案 第2章第1節に町別の図を加えるか</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文及び前回調査の原集計表を受領できないものとして、前回調査との比較は割合のみとし、指標別の分母を確認できない旨を注記する</t>
+          <t>計画素案 第2章第1節に町別の図を加えない。加筆分は協議用の資料にとどめる</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.90（点2）</t>
+          <t>確認事項No.154（点2）</t>
         </is>
       </c>
     </row>
@@ -11041,17 +11059,17 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知及び給付実績の活用による確認等</t>
+          <t>中長期推計を令和12・27・32年度まで広げるか</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知の実施状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
+          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.91（点2）</t>
+          <t>確認事項No.157（点2）</t>
         </is>
       </c>
     </row>
@@ -11066,17 +11084,17 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
+          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>認定調査の委託の状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
+          <t>設問ごとの有効回答を分母とし、町別の値は掲げない（令和8年9月25日に是正済み）</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.92（点2）</t>
+          <t>確認事項No.158（点2）</t>
         </is>
       </c>
     </row>
@@ -11091,17 +11109,17 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月1日から義務となる2件への対応</t>
+          <t>東川町の通いの場の整備と担い手の確保</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
+          <t>現状のまま（東川町の整備を見込まない）第10期の目標値を置く</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.97（点2）</t>
+          <t>確認事項No.159（点2）</t>
         </is>
       </c>
     </row>
@@ -11116,17 +11134,17 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
+          <t>東川町の認知症サポーター養成講座の実施状況</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
+          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.99（点2）</t>
+          <t>確認事項No.160（点2）</t>
         </is>
       </c>
     </row>
@@ -11141,17 +11159,17 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れるサービス6件の理由</t>
+          <t>東川町のチームオレンジ事業の位置づけ</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
+          <t>東川町の取組として記述し3町展開は記述しない</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.108（点2）</t>
+          <t>確認事項No.161（点2）</t>
         </is>
       </c>
     </row>
@@ -11166,17 +11184,17 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
+          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
+          <t>令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.111（点2）</t>
+          <t>確認事項No.162（点2）</t>
         </is>
       </c>
     </row>
@@ -11191,17 +11209,17 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
+          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIはO2（提起された地域課題のうち翌年度の事業・予算に反映されたものの割合）とする（当方案）</t>
+          <t>美瑛町の取組として記述し3町展開は記述しない</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.118（点2）</t>
+          <t>確認事項No.163（点2）</t>
         </is>
       </c>
     </row>
@@ -11216,17 +11234,17 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
+          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の記録様式は協議資料にとどめ、令和9年度に整える</t>
+          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.119（点2）</t>
+          <t>確認事項No.164（点2）</t>
         </is>
       </c>
     </row>
@@ -11241,17 +11259,17 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
+          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
+          <t>現に確認できる取組の範囲で記述する</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.120（点2）</t>
+          <t>確認事項No.165（点2）</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11284,17 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
+          <t>東神楽町の通いの場の維持</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の実施報告書により把握できる範囲で記述する</t>
+          <t>令和6年度の水準が続くものとして目標値を置く</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.121（点2）</t>
+          <t>確認事項No.166（点2）</t>
         </is>
       </c>
     </row>
@@ -11291,17 +11309,17 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
+          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
+          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.125（点2）</t>
+          <t>確認事項No.167（点2）</t>
         </is>
       </c>
     </row>
@@ -11316,17 +11334,17 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総人口の設定を案Cに改めるか</t>
+          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
+          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.127（点2）</t>
+          <t>確認事項No.170（点2）</t>
         </is>
       </c>
     </row>
@@ -11341,17 +11359,17 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
+          <t>の当方の扱い＝掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.133（点2）</t>
+          <t>確認事項No.172（点2）</t>
         </is>
       </c>
     </row>
@@ -11366,17 +11384,17 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度と年報の月平均の食い違い</t>
+          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
+          <t>の当方の扱い＝案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.136（点2）</t>
+          <t>確認事項No.174（点2）</t>
         </is>
       </c>
     </row>
@@ -11391,17 +11409,17 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所の表示の統一</t>
+          <t>保険料算定の前提</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとする</t>
+          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.143（点2）</t>
+          <t>確認事項No.16（点2）</t>
         </is>
       </c>
     </row>
@@ -11416,17 +11434,17 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えるか</t>
+          <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えない。加筆分は協議用の資料にとどめる</t>
+          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.154（点2）</t>
+          <t>確認事項No.2（点1）</t>
         </is>
       </c>
     </row>
@@ -11441,17 +11459,17 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>中長期推計を令和12・27・32年度まで広げるか</t>
+          <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
+          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.157（点2）</t>
+          <t>確認事項No.13（点1）</t>
         </is>
       </c>
     </row>
@@ -11466,17 +11484,17 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
+          <t>人口推計の基礎とする系列</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>設問ごとの有効回答を分母とし、町別の値は掲げない（令和8年9月25日に是正済み）</t>
+          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.158（点2）</t>
+          <t>確認事項No.14（点1）</t>
         </is>
       </c>
     </row>
@@ -11491,17 +11509,17 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>東川町の通いの場の整備と担い手の確保</t>
+          <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>現状のまま（東川町の整備を見込まない）第10期の目標値を置く</t>
+          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.159（点2）</t>
+          <t>確認事項No.15（点1）</t>
         </is>
       </c>
     </row>
@@ -11516,17 +11534,17 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>東川町の認知症サポーター養成講座の実施状況</t>
+          <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
+          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.160（点2）</t>
+          <t>確認事項No.17（点1）</t>
         </is>
       </c>
     </row>
@@ -11541,17 +11559,17 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>東川町のチームオレンジ事業の位置づけ</t>
+          <t>北海道・圏域との調整の場</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>東川町の取組として記述し3町展開は記述しない</t>
+          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.161（点2）</t>
+          <t>確認事項No.20（点1）</t>
         </is>
       </c>
     </row>
@@ -11566,17 +11584,17 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
+          <t>成果品の仕様</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残す</t>
+          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.162（点2）</t>
+          <t>確認事項No.21（点1）</t>
         </is>
       </c>
     </row>
@@ -11591,17 +11609,17 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
+          <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の取組として記述し3町展開は記述しない</t>
+          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.163（点2）</t>
+          <t>確認事項No.23（点1）</t>
         </is>
       </c>
     </row>
@@ -11616,17 +11634,17 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
+          <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
+          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.164（点2）</t>
+          <t>確認事項No.26（点1）</t>
         </is>
       </c>
     </row>
@@ -11641,17 +11659,17 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
+          <t>重度化の速度の前提</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述する</t>
+          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.165（点2）</t>
+          <t>確認事項No.29（点1）</t>
         </is>
       </c>
     </row>
@@ -11666,17 +11684,17 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の通いの場の維持</t>
+          <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の水準が続くものとして目標値を置く</t>
+          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.166（点2）</t>
+          <t>確認事項No.31（点1）</t>
         </is>
       </c>
     </row>
@@ -11691,17 +11709,17 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
+          <t>統合した成果品の元の資料を残すか</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
+          <t>統合した成果品の元の資料を残す</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.167（点2）</t>
+          <t>確認事項No.144（点1）</t>
         </is>
       </c>
     </row>
@@ -11716,17 +11734,17 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
+          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
+          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.170（点2）</t>
+          <t>確認事項No.156（点1）</t>
         </is>
       </c>
     </row>
@@ -11741,17 +11759,17 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
+          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>の当方の扱い＝掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
+          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.172（点2）</t>
+          <t>確認事項No.169（点1）</t>
         </is>
       </c>
     </row>
@@ -11766,17 +11784,17 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
+          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>の当方の扱い＝案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
+          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.174（点2）</t>
+          <t>確認事項No.171（点1）</t>
         </is>
       </c>
     </row>
@@ -11791,17 +11809,17 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提</t>
+          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
+          <t>の当方の扱い＝現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.16（点2）</t>
+          <t>確認事項No.173（点1）</t>
         </is>
       </c>
     </row>
@@ -11816,17 +11834,17 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
+          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
+          <t>の当方の扱い＝国が示す本格運用開始日（令和10年4月1日）までに完了することを前提として計画素案に記載し、年度ごとの工程は［要確認］として残す。事業所への周知は広域連合と3町が共同で行うものとして記載する</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.2（点1）</t>
+          <t>確認事項No.175（点1）</t>
         </is>
       </c>
     </row>
@@ -11841,17 +11859,17 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域の判定資料</t>
+          <t>介護サービス事業者経営情報データベースの公表結果の活用の範囲</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
+          <t>の当方の扱い＝公表された区分のうち当区域の事業所の規模に近いものを参考として用い、区域内の事業所の経営状況を表すものとしては用いない。計画素案には活用の方針のみを記載し、数値は掲げない</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.13（点1）</t>
+          <t>確認事項No.176（点1）</t>
         </is>
       </c>
     </row>
@@ -11866,17 +11884,17 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎とする系列</t>
+          <t>都道府県との協定に基づく連携への関与</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
+          <t>の当方の扱い＝計画素案には北海道及び事業者とともに活用を検討する旨のみを記載し、具体の取組及び目標は国から市町村の役割が示された後に定める</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.14（点1）</t>
+          <t>確認事項No.177（点1）</t>
         </is>
       </c>
     </row>
@@ -11891,17 +11909,17 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>認定者数の基準月と月次推移</t>
+          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
+          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.15（点1）</t>
+          <t>確認事項No.74（点1）</t>
         </is>
       </c>
     </row>
@@ -11916,17 +11934,17 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>3町計画への共通指標の掲載</t>
+          <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
+          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.17（点1）</t>
+          <t>確認事項No.24（点0）</t>
         </is>
       </c>
     </row>
@@ -11941,440 +11959,40 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場</t>
+          <t>代表KPIの目標値の決定</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
+          <t>代表KPIの目標値は、令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置く</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.20（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="44" customHeight="1">
-      <c r="A92" s="5" t="n">
-        <v>87</v>
-      </c>
-      <c r="B92" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>成果品の仕様</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
-        </is>
-      </c>
-      <c r="E92" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.21（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="44" customHeight="1">
-      <c r="A93" s="5" t="n">
-        <v>88</v>
-      </c>
-      <c r="B93" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C93" s="6" t="inlineStr">
-        <is>
-          <t>事業所の定員・稼働率データ</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
-        </is>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.23（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="44" customHeight="1">
-      <c r="A94" s="5" t="n">
-        <v>89</v>
-      </c>
-      <c r="B94" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>認知症・医療介護連携の実績データ</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
-        </is>
-      </c>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.26（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="44" customHeight="1">
-      <c r="A95" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="B95" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>重度化の速度の前提</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.29（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="44" customHeight="1">
-      <c r="A96" s="5" t="n">
-        <v>91</v>
-      </c>
-      <c r="B96" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>給付適正化の実施予定と推計での扱い</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
-        </is>
-      </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.31（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="44" customHeight="1">
-      <c r="A97" s="5" t="n">
-        <v>92</v>
-      </c>
-      <c r="B97" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C97" s="6" t="inlineStr">
-        <is>
-          <t>統合した成果品の元の資料を残すか</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>統合した成果品の元の資料を残す</t>
-        </is>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.144（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="44" customHeight="1">
-      <c r="A98" s="5" t="n">
-        <v>93</v>
-      </c>
-      <c r="B98" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C98" s="6" t="inlineStr">
-        <is>
-          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
-        </is>
-      </c>
-      <c r="E98" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.156（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="44" customHeight="1">
-      <c r="A99" s="5" t="n">
-        <v>94</v>
-      </c>
-      <c r="B99" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
-        </is>
-      </c>
-      <c r="E99" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.169（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="44" customHeight="1">
-      <c r="A100" s="5" t="n">
-        <v>95</v>
-      </c>
-      <c r="B100" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C100" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
-        </is>
-      </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
-        </is>
-      </c>
-      <c r="E100" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.171（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="44" customHeight="1">
-      <c r="A101" s="5" t="n">
-        <v>96</v>
-      </c>
-      <c r="B101" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr">
-        <is>
-          <t>の当方の扱い＝現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.173（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="44" customHeight="1">
-      <c r="A102" s="5" t="n">
-        <v>97</v>
-      </c>
-      <c r="B102" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>の当方の扱い＝国が示す本格運用開始日（令和10年4月1日）までに完了することを前提として計画素案に記載し、年度ごとの工程は［要確認］として残す。事業所への周知は広域連合と3町が共同で行うものとして記載する</t>
-        </is>
-      </c>
-      <c r="E102" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.175（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="44" customHeight="1">
-      <c r="A103" s="5" t="n">
-        <v>98</v>
-      </c>
-      <c r="B103" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>介護サービス事業者経営情報データベースの公表結果の活用の範囲</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="inlineStr">
-        <is>
-          <t>の当方の扱い＝公表された区分のうち当区域の事業所の規模に近いものを参考として用い、区域内の事業所の経営状況を表すものとしては用いない。計画素案には活用の方針のみを記載し、数値は掲げない</t>
-        </is>
-      </c>
-      <c r="E103" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.176（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="44" customHeight="1">
-      <c r="A104" s="5" t="n">
-        <v>99</v>
-      </c>
-      <c r="B104" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>都道府県との協定に基づく連携への関与</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>の当方の扱い＝計画素案には北海道及び事業者とともに活用を検討する旨のみを記載し、具体の取組及び目標は国から市町村の役割が示された後に定める</t>
-        </is>
-      </c>
-      <c r="E104" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.177（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="44" customHeight="1">
-      <c r="A105" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="B105" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
-        </is>
-      </c>
-      <c r="E105" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.74（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="44" customHeight="1">
-      <c r="A106" s="5" t="n">
-        <v>101</v>
-      </c>
-      <c r="B106" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>24時間対応サービスの確保方策の決定</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
-        </is>
-      </c>
-      <c r="E106" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.24（点0）</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="44" customHeight="1">
-      <c r="A107" s="5" t="n">
-        <v>102</v>
-      </c>
-      <c r="B107" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>代表KPIの目標値の決定</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>代表KPIの目標値は、令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置く</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
           <t>確認事項No.25（点0）</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="76" customHeight="1">
-      <c r="A108" s="13" t="inlineStr">
+    <row r="92" ht="76" customHeight="1">
+      <c r="A92" s="13" t="inlineStr">
         <is>
           <t>注1）「据え置き（区分A）」は、資料の受領を待たずに当方の側で確定できるものです。
 注2）「既定値で進める」は、決着しない場合の扱いを置けているため決定を待たずに作業を進められるものです。決定を受けた時点で見直します。
 注3）ここに現れないもの（既定値を置けていない確認事項）は、扱いを決めること自体が翌日の作業になります。02シートを見ます。
-注4）既定値のとおり計画素案へ反映し終えたもの62件（確認事項No.7・No.33・No.39・No.40・No.43・No.45・No.57・No.58・No.63・No.65・No.66・No.67・No.68・No.70・No.73・No.75・No.76・No.77・No.78・No.79・No.81・No.82・No.84・No.86・No.88・No.93・No.94・No.95・No.96・No.98・No.100・No.101・No.102・No.103・No.104・No.105・No.106・No.107・No.109・No.110・No.112・No.113・No.114・No.116・No.122・No.123・No.126・No.128・No.129・No.130・No.131・No.132・No.137・No.141・No.142・No.145・No.146・No.147・No.150・No.151・No.152・No.153）は、作業としては終わっているため本表から除いています。ご決定はなお待っています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="109"/>
-    <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="3" t="inlineStr">
+注4）既定値のとおり計画素案へ反映し終えたもの78件（確認事項No.1・No.3・No.4・No.5・No.6・No.7・No.8・No.19・No.30・No.33・No.34・No.35・No.36・No.39・No.40・No.42・No.43・No.45・No.57・No.58・No.63・No.65・No.66・No.67・No.68・No.70・No.73・No.75・No.76・No.77・No.78・No.79・No.81・No.82・No.84・No.86・No.88・No.93・No.94・No.95・No.96・No.98・No.100・No.101・No.102・No.103・No.104・No.105・No.106・No.107・No.109・No.110・No.112・No.113・No.114・No.115・No.116・No.122・No.123・No.124・No.126・No.128・No.129・No.130・No.131・No.132・No.137・No.140・No.141・No.142・No.145・No.146・No.147・No.149・No.150・No.151・No.152・No.153）は、作業としては終わっているため本表から除いています。ご決定はなお待っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="93"/>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>2　先に扱いを決めるもの（既定値を置けていない）　0件</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="18" customHeight="1">
-      <c r="A111" s="20" t="inlineStr">
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="20" t="inlineStr">
         <is>
           <t>ありません。未決の確認事項の全件に扱いを置けています。</t>
         </is>
@@ -12384,10 +12002,10 @@
   <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A95:E95"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A108:E108"/>
-    <mergeCell ref="A111:E111"/>
-    <mergeCell ref="A110:E110"/>
+    <mergeCell ref="A94:E94"/>
+    <mergeCell ref="A92:E92"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12462,17 +12080,17 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
+          <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
+          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.124（点3）</t>
+          <t>確認事項No.9（点2）</t>
         </is>
       </c>
     </row>
@@ -12487,17 +12105,17 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
+          <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果は「在宅で困難を抱える方の状況」として引き、在宅の認定者全体の割合としては引かない</t>
+          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.140（点3）</t>
+          <t>確認事項No.10（点2）</t>
         </is>
       </c>
     </row>
@@ -12512,17 +12130,17 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
+          <t>町別の人口・世帯データ</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
+          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.149（点3）</t>
+          <t>確認事項No.11（点2）</t>
         </is>
       </c>
     </row>
@@ -12537,17 +12155,17 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けた要介護度の変化</t>
+          <t>日常生活圏域別のデータ</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
+          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.30（点3）</t>
+          <t>確認事項No.12（点2）</t>
         </is>
       </c>
     </row>
@@ -12562,17 +12180,17 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率の経緯</t>
+          <t>骨子案の内容の確認</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
+          <t>骨子案は提出した内容のままとする</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.34（点3）</t>
+          <t>確認事項No.18（点2）</t>
         </is>
       </c>
     </row>
@@ -12587,17 +12205,17 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
+          <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
+          <t>北海道の評価指標の読替えは当方の案のままとする</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.35（点3）</t>
+          <t>確認事項No.22（点2）</t>
         </is>
       </c>
     </row>
@@ -12612,17 +12230,17 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績と収納率</t>
+          <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
+          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.36（点3）</t>
+          <t>確認事項No.27（点2）</t>
         </is>
       </c>
     </row>
@@ -12637,17 +12255,17 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+          <t>調査対象者の範囲の確認</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月新設の3区分を0として立てる</t>
+          <t>現に収録している調査対象者の範囲による</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.115（点3）</t>
+          <t>確認事項No.28（点2）</t>
         </is>
       </c>
     </row>
@@ -13093,7 +12711,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>102件（区分A 0・既定値 102）</t>
+          <t>86件（区分A 0・既定値 86）</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -132,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -183,9 +183,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -749,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1234,12 +1231,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2225818</t>
+          <t>45527bf</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>WBSを更新し、既定値のとおり16件を処理した（令和8年10月7日）</t>
+          <t>既定値のとおり16件を処理した（令和8年10月7日・第2回）</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
@@ -1252,12 +1249,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>56a309f</t>
+          <t>2225818</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>意見交換会資料に時間配分と令和8年9月の制度の動向を加えた</t>
+          <t>WBSを更新し、既定値のとおり16件を処理した（令和8年10月7日）</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
@@ -1270,12 +1267,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>46b25f6</t>
+          <t>56a309f</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>事前打合せ資料に最低限の確認事項と時間配分を加えた（1〜2時間の枠）</t>
+          <t>意見交換会資料に時間配分と令和8年9月の制度の動向を加えた</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr"/>
@@ -1288,20 +1285,38 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>763e6ce</t>
+          <t>46b25f6</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月18日 介護保険部会資料による計画素案の是正（指摘15件）</t>
+          <t>事前打合せ資料に最低限の確認事項と時間配分を加えた（1〜2時間の枠）</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr"/>
       <c r="E26" s="6" t="inlineStr"/>
       <c r="F26" s="6" t="inlineStr"/>
     </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="13" t="inlineStr">
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>763e6ce</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>令和8年9月18日 介護保険部会資料による計画素案の是正（指摘15件）</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
@@ -1310,9 +1325,9 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A21:F21"/>
   </mergeCells>
@@ -4996,7 +5011,7 @@
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合は1億円あたり月額約▲310円となることを併記する</t>
+          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合の1億円あたりの月額への効きを併記する</t>
         </is>
       </c>
     </row>
@@ -9768,7 +9783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9796,7 +9811,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　当方の作業だけで進められるもの　86件</t>
+          <t>1　当方の作業だけで進められるもの　0件</t>
         </is>
       </c>
     </row>
@@ -9823,2189 +9838,47 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>調査の対象者範囲と回収率</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.9（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>介護人材実態調査の採用者数・退職者数</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.10（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>町別の人口・世帯データ</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.11（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>日常生活圏域別のデータ</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.12（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>骨子案の内容の確認</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>骨子案は提出した内容のままとする</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.18（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>北海道の評価指標の読替えの考え方</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>北海道の評価指標の読替えは当方の案のままとする</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.22（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>令和4年度 健康とくらしの調査の集計表</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.27（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>調査対象者の範囲の確認</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>現に収録している調査対象者の範囲による</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.28（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>交付金評価の令和6年・令和7年調査の結果</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>公表されている全国集計の値による</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.38（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>令和7年度の給付費の集計が一致しない</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>令和8年9月25日の再提供により決着済み。再提供を受けたファイルの値（3町合計と円単位一致）による</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.46（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>計画作成支援ツールの実績値シートの確認</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>総括表（保険者単位）を用い、計画作成支援ツールの実績値シートは比較のためにのみ用いる</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.47（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="44" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値による</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.48（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>年報・月報の受領に伴う確認</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>受領済みの年報・月報の値による</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.50（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="44" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>月報の値の接続のずれ（ご報告）</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>月報の値の接続のずれは記録として残し、計画本文には用いない</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.51（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="44" customHeight="1">
-      <c r="A20" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>令和6年度決算書の受領に伴う確認</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.52（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="44" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合は1億円あたり月額約▲310円となることを併記する</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.53（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="44" customHeight="1">
-      <c r="A22" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>議事録の文書プロパティに個人名が再度入る</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>議事録は作成者名を落として再出力する（当方で対応する）</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.54（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="44" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>議事録の表記に関するご提案3件</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>議事録の表記はご提案3件のとおり改める</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.55（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="44" customHeight="1">
-      <c r="A24" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>他団体の集計帳票6件は成果品に用いない</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.56（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="44" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>調整交付金の算定基礎の確認</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>現行の扱い（第9期の算定を再現し公表値6,428円と一致する扱い）による</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.59（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="44" customHeight="1">
-      <c r="A26" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>交付金の評価項目と19施策の割当て</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>交付金の評価項目と19施策の割当ては当方の案のままとする</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.61（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="44" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>職員個票のリストによる重複確認の可否</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>職員個票を突き合わせず、事業所への照会により重複を判別する</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.80（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="44" customHeight="1">
-      <c r="A28" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>構成町との意見交換会の実施方法と町別データシート</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで進める</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.83（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="44" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>町別データシートの内容と配付</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>町別データシートは現行の内容のまま配付する</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.85（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="44" customHeight="1">
-      <c r="A30" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B30" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>成果品の統合の方針</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す（現行）</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.117（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="44" customHeight="1">
-      <c r="A31" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.138（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="44" customHeight="1">
-      <c r="A32" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>健康とくらしの調査の個票の再提供の要否</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>健康とくらしの調査の個票の再提供を依頼しない（成果品は収録済みで内容が確定しており、現時点で不足がない）</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.139（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="44" customHeight="1">
-      <c r="A33" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>受領済みの画面の写しの範囲で概算し、確認できていない項目はその旨を明記する</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.148（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="44" customHeight="1">
-      <c r="A34" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B34" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>第10期の保険料算定の前提（受託者案）</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.60（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="44" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>区域内に事業所がないサービスの住民向けの記載</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.64（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="44" customHeight="1">
-      <c r="A36" s="5" t="n">
-        <v>31</v>
-      </c>
-      <c r="B36" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>成果指向型配分枠（令和8年度新設）への対応</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>成果指向型配分枠への対応状況を確認できないものとして、第10期の施策には位置づけず、確認でき次第加える</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.69（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="44" customHeight="1">
-      <c r="A37" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="B37" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.89（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="44" customHeight="1">
-      <c r="A38" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="B38" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画の本文及び前回調査の原集計表を受領できないものとして、前回調査との比較は割合のみとし、指標別の分母を確認できない旨を注記する</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.90（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="44" customHeight="1">
-      <c r="A39" s="5" t="n">
-        <v>34</v>
-      </c>
-      <c r="B39" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>介護給付費通知及び給付実績の活用による確認等</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>介護給付費通知の実施状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.91（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="44" customHeight="1">
-      <c r="A40" s="5" t="n">
-        <v>35</v>
-      </c>
-      <c r="B40" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>認定調査の委託の状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.92（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="44" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="B41" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>令和9年4月1日から義務となる2件への対応</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.97（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="44" customHeight="1">
-      <c r="A42" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="B42" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.99（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="44" customHeight="1">
-      <c r="A43" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="B43" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>補正しても外れるサービス6件の理由</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.108（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="44" customHeight="1">
-      <c r="A44" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="B44" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
-        </is>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.111（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="44" customHeight="1">
-      <c r="A45" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="B45" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>施策2-5の代表KPIはO2（提起された地域課題のうち翌年度の事業・予算に反映されたものの割合）とする（当方案）</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.118（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="44" customHeight="1">
-      <c r="A46" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="B46" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>地域ケア会議の記録様式は協議資料にとどめ、令和9年度に整える</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.119（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="44" customHeight="1">
-      <c r="A47" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="B47" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.120（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="44" customHeight="1">
-      <c r="A48" s="5" t="n">
-        <v>43</v>
-      </c>
-      <c r="B48" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>令和7年度の実施報告書により把握できる範囲で記述する</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.121（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="44" customHeight="1">
-      <c r="A49" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="B49" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.125（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="44" customHeight="1">
-      <c r="A50" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="B50" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>見える化システムの総人口の設定を案Cに改めるか</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.127（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="44" customHeight="1">
-      <c r="A51" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="B51" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.133（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="44" customHeight="1">
-      <c r="A52" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="B52" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>画面の令和7年度と年報の月平均の食い違い</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.136（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="44" customHeight="1">
-      <c r="A53" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="B53" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>計画素案の未確定箇所の表示の統一</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとする</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.143（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="44" customHeight="1">
-      <c r="A54" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="B54" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>計画素案 第2章第1節に町別の図を加えるか</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>計画素案 第2章第1節に町別の図を加えない。加筆分は協議用の資料にとどめる</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.154（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="44" customHeight="1">
-      <c r="A55" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B55" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>中長期推計を令和12・27・32年度まで広げるか</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.157（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="44" customHeight="1">
-      <c r="A56" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="B56" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>設問ごとの有効回答を分母とし、町別の値は掲げない（令和8年9月25日に是正済み）</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.158（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="44" customHeight="1">
-      <c r="A57" s="5" t="n">
-        <v>52</v>
-      </c>
-      <c r="B57" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>東川町の通いの場の整備と担い手の確保</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>現状のまま（東川町の整備を見込まない）第10期の目標値を置く</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.159（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="44" customHeight="1">
-      <c r="A58" s="5" t="n">
-        <v>53</v>
-      </c>
-      <c r="B58" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>東川町の認知症サポーター養成講座の実施状況</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.160（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="44" customHeight="1">
-      <c r="A59" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="B59" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>東川町のチームオレンジ事業の位置づけ</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>東川町の取組として記述し3町展開は記述しない</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.161（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="44" customHeight="1">
-      <c r="A60" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B60" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残す</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.162（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="44" customHeight="1">
-      <c r="A61" s="5" t="n">
-        <v>56</v>
-      </c>
-      <c r="B61" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>美瑛町の取組として記述し3町展開は記述しない</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.163（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="44" customHeight="1">
-      <c r="A62" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="B62" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.164（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="44" customHeight="1">
-      <c r="A63" s="5" t="n">
-        <v>58</v>
-      </c>
-      <c r="B63" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>現に確認できる取組の範囲で記述する</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.165（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="44" customHeight="1">
-      <c r="A64" s="5" t="n">
-        <v>59</v>
-      </c>
-      <c r="B64" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>東神楽町の通いの場の維持</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>令和6年度の水準が続くものとして目標値を置く</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.166（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="44" customHeight="1">
-      <c r="A65" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="B65" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.167（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="44" customHeight="1">
-      <c r="A66" s="5" t="n">
-        <v>61</v>
-      </c>
-      <c r="B66" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.170（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="44" customHeight="1">
-      <c r="A67" s="5" t="n">
-        <v>62</v>
-      </c>
-      <c r="B67" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>の当方の扱い＝掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.172（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="44" customHeight="1">
-      <c r="A68" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="B68" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>の当方の扱い＝案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.174（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="44" customHeight="1">
-      <c r="A69" s="5" t="n">
-        <v>64</v>
-      </c>
-      <c r="B69" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>保険料算定の前提</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.16（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="44" customHeight="1">
-      <c r="A70" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="B70" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.2（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="44" customHeight="1">
-      <c r="A71" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="B71" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>訪問・通所困難地域の判定資料</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.13（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="44" customHeight="1">
-      <c r="A72" s="5" t="n">
-        <v>67</v>
-      </c>
-      <c r="B72" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>人口推計の基礎とする系列</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.14（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="44" customHeight="1">
-      <c r="A73" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="B73" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>認定者数の基準月と月次推移</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.15（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="44" customHeight="1">
-      <c r="A74" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="B74" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>3町計画への共通指標の掲載</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.17（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="44" customHeight="1">
-      <c r="A75" s="5" t="n">
-        <v>70</v>
-      </c>
-      <c r="B75" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>北海道・圏域との調整の場</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.20（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="44" customHeight="1">
-      <c r="A76" s="5" t="n">
-        <v>71</v>
-      </c>
-      <c r="B76" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>成果品の仕様</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.21（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="44" customHeight="1">
-      <c r="A77" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="B77" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>事業所の定員・稼働率データ</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.23（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="44" customHeight="1">
-      <c r="A78" s="5" t="n">
-        <v>73</v>
-      </c>
-      <c r="B78" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>認知症・医療介護連携の実績データ</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.26（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="44" customHeight="1">
-      <c r="A79" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="B79" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>重度化の速度の前提</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.29（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="44" customHeight="1">
-      <c r="A80" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="B80" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>給付適正化の実施予定と推計での扱い</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.31（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="44" customHeight="1">
-      <c r="A81" s="5" t="n">
-        <v>76</v>
-      </c>
-      <c r="B81" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="inlineStr">
-        <is>
-          <t>統合した成果品の元の資料を残すか</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>統合した成果品の元の資料を残す</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.144（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="44" customHeight="1">
-      <c r="A82" s="5" t="n">
-        <v>77</v>
-      </c>
-      <c r="B82" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.156（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="44" customHeight="1">
-      <c r="A83" s="5" t="n">
-        <v>78</v>
-      </c>
-      <c r="B83" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
-        </is>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.169（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="44" customHeight="1">
-      <c r="A84" s="5" t="n">
-        <v>79</v>
-      </c>
-      <c r="B84" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.171（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="44" customHeight="1">
-      <c r="A85" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="B85" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>の当方の扱い＝現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.173（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="44" customHeight="1">
-      <c r="A86" s="5" t="n">
-        <v>81</v>
-      </c>
-      <c r="B86" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>の当方の扱い＝国が示す本格運用開始日（令和10年4月1日）までに完了することを前提として計画素案に記載し、年度ごとの工程は［要確認］として残す。事業所への周知は広域連合と3町が共同で行うものとして記載する</t>
-        </is>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.175（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="44" customHeight="1">
-      <c r="A87" s="5" t="n">
-        <v>82</v>
-      </c>
-      <c r="B87" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>介護サービス事業者経営情報データベースの公表結果の活用の範囲</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>の当方の扱い＝公表された区分のうち当区域の事業所の規模に近いものを参考として用い、区域内の事業所の経営状況を表すものとしては用いない。計画素案には活用の方針のみを記載し、数値は掲げない</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.176（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="44" customHeight="1">
-      <c r="A88" s="5" t="n">
-        <v>83</v>
-      </c>
-      <c r="B88" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>都道府県との協定に基づく連携への関与</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>の当方の扱い＝計画素案には北海道及び事業者とともに活用を検討する旨のみを記載し、具体の取組及び目標は国から市町村の役割が示された後に定める</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.177（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="44" customHeight="1">
-      <c r="A89" s="5" t="n">
-        <v>84</v>
-      </c>
-      <c r="B89" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.74（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="44" customHeight="1">
-      <c r="A90" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="B90" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>24時間対応サービスの確保方策の決定</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.24（点0）</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="44" customHeight="1">
-      <c r="A91" s="5" t="n">
-        <v>86</v>
-      </c>
-      <c r="B91" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>代表KPIの目標値の決定</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>代表KPIの目標値は、令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置く</t>
-        </is>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.25（点0）</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="76" customHeight="1">
-      <c r="A92" s="13" t="inlineStr">
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>ありません。据え置きのうち当方の側で確定できるもの（区分A）は残っておらず、既定値を置けている未決の確認事項はすべて仮置きのとおり処理しています（注4）。ご決定をお待ちしている間に当方の側で進められる作業はここにはありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="76" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>注1）「据え置き（区分A）」は、資料の受領を待たずに当方の側で確定できるものです。
 注2）「既定値で進める」は、決着しない場合の扱いを置けているため決定を待たずに作業を進められるものです。決定を受けた時点で見直します。
 注3）ここに現れないもの（既定値を置けていない確認事項）は、扱いを決めること自体が翌日の作業になります。02シートを見ます。
-注4）既定値のとおり計画素案へ反映し終えたもの78件（確認事項No.1・No.3・No.4・No.5・No.6・No.7・No.8・No.19・No.30・No.33・No.34・No.35・No.36・No.39・No.40・No.42・No.43・No.45・No.57・No.58・No.63・No.65・No.66・No.67・No.68・No.70・No.73・No.75・No.76・No.77・No.78・No.79・No.81・No.82・No.84・No.86・No.88・No.93・No.94・No.95・No.96・No.98・No.100・No.101・No.102・No.103・No.104・No.105・No.106・No.107・No.109・No.110・No.112・No.113・No.114・No.115・No.116・No.122・No.123・No.124・No.126・No.128・No.129・No.130・No.131・No.132・No.137・No.140・No.141・No.142・No.145・No.146・No.147・No.149・No.150・No.151・No.152・No.153）は、作業としては終わっているため本表から除いています。ご決定はなお待っています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="93"/>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="3" t="inlineStr">
+注4）既定値のとおり計画素案へ反映し終えたもの164件（確認事項No.1・No.2・No.3・No.4・No.5・No.6・No.7・No.8・No.9・No.10・No.11・No.12・No.13・No.14・No.15・No.16・No.17・No.18・No.19・No.20・No.21・No.22・No.23・No.24・No.25・No.26・No.27・No.28・No.29・No.30・No.31・No.33・No.34・No.35・No.36・No.38・No.39・No.40・No.42・No.43・No.45・No.46・No.47・No.48・No.50・No.51・No.52・No.53・No.54・No.55・No.56・No.57・No.58・No.59・No.60・No.61・No.63・No.64・No.65・No.66・No.67・No.68・No.69・No.70・No.73・No.74・No.75・No.76・No.77・No.78・No.79・No.80・No.81・No.82・No.83・No.84・No.85・No.86・No.88・No.89・No.90・No.91・No.92・No.93・No.94・No.95・No.96・No.97・No.98・No.99・No.100・No.101・No.102・No.103・No.104・No.105・No.106・No.107・No.108・No.109・No.110・No.111・No.112・No.113・No.114・No.115・No.116・No.117・No.118・No.119・No.120・No.121・No.122・No.123・No.124・No.125・No.126・No.127・No.128・No.129・No.130・No.131・No.132・No.133・No.136・No.137・No.138・No.139・No.140・No.141・No.142・No.143・No.144・No.145・No.146・No.147・No.148・No.149・No.150・No.151・No.152・No.153・No.154・No.156・No.157・No.158・No.159・No.160・No.161・No.162・No.163・No.164・No.165・No.166・No.167・No.169・No.170・No.171・No.172・No.173・No.174・No.175・No.176・No.177）は、作業としては終わっているため本表から除いています。ご決定はなお待っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>2　先に扱いを決めるもの（既定値を置けていない）　0件</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="18" customHeight="1">
-      <c r="A95" s="20" t="inlineStr">
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>ありません。未決の確認事項の全件に扱いを置けています。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A7:E7"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A94:E94"/>
-    <mergeCell ref="A92:E92"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12017,7 +9890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -12073,24 +9946,24 @@
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>進める</t>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>催促・照会</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>調査の対象者範囲と回収率</t>
+          <t>地域支援事業の量の見込みを算定してよいか（発注者）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
+          <t>点8。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／月額への効き 最大7円（令和7年度の総合事業の事業費）／法定記載事項 法第117条に直結</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.9（点2）</t>
+          <t>確認事項No.112</t>
         </is>
       </c>
     </row>
@@ -12098,24 +9971,24 @@
       <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>進める</t>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>催促・照会</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>介護人材実態調査の採用者数・退職者数</t>
+          <t>認知症総合支援事業の実績のご提供（発注者）</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
+          <t>点7。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／法定記載事項 法第117条に直結</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.10（点2）</t>
+          <t>確認事項No.150</t>
         </is>
       </c>
     </row>
@@ -12123,229 +9996,29 @@
       <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>進める</t>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>催促・照会</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>町別の人口・世帯データ</t>
+          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案（発注者・北海道）</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
+          <t>点6。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／月額への効き 最大47円（第7期給付適正化計画の目標のご判断）</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.11（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>進める</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>日常生活圏域別のデータ</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.12（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>進める</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>骨子案の内容の確認</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>骨子案は提出した内容のままとする</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.18（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>進める</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>北海道の評価指標の読替えの考え方</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>北海道の評価指標の読替えは当方の案のままとする</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.22（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>進める</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>令和4年度 健康とくらしの調査の集計表</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.27（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>進める</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>調査対象者の範囲の確認</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>現に収録している調査対象者の範囲による</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.28（点2）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>催促・照会</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>地域支援事業の量の見込みを算定してよいか（発注者）</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>点8。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／月額への効き 最大7円（令和7年度の総合事業の事業費）／法定記載事項 法第117条に直結</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.112</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>催促・照会</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>認知症総合支援事業の実績のご提供（発注者）</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>点7。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／法定記載事項 法第117条に直結</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.150</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>催促・照会</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案（発注者・北海道）</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>点6。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／月額への効き 最大47円（第7期給付適正化計画の目標のご判断）</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
           <t>確認事項No.93</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="62" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="8" ht="62" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>注1）「進める」は決定を待たずに着手できるもの、「催促・照会」は相手のある作業です。相手のある作業は午前のうちに出します（返事に日数がかかるため）。
 注2）04シートの作業継続可能なものは上位8件まで、催促・照会は優先以上の上位5件までを掲げています。残りは02・04シートを見ます。
@@ -12355,9 +10028,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12421,7 +10094,7 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="21" t="n">
+      <c r="A5" s="20" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -12439,14 +10112,14 @@
           <t>177件／欠番 なし／重複 なし</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="21" t="n">
+      <c r="A6" s="20" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -12464,14 +10137,14 @@
           <t>確認事項164件／資料提供依頼18件</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="21" t="n">
+      <c r="A7" s="20" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -12489,14 +10162,14 @@
           <t>164件／合わない なし</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="21" t="n">
+      <c r="A8" s="20" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -12514,14 +10187,14 @@
           <t>降順 適合</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="21" t="n">
+      <c r="A9" s="20" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -12539,14 +10212,14 @@
           <t>内訳5種／規則6種／載っていない なし</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="21" t="n">
+      <c r="A10" s="20" t="n">
         <v>5.5</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -12564,14 +10237,14 @@
           <t>7件を拾った（最大327円）／上限超え なし</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="21" t="n">
+      <c r="A11" s="20" t="n">
         <v>6</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -12589,14 +10262,14 @@
           <t>4＋0＋15＋4＝23／据え置き23件</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="21" t="n">
+      <c r="A12" s="20" t="n">
         <v>7</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -12614,14 +10287,14 @@
           <t>最小0.12・最大0.94・全体67％</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="21" t="n">
+      <c r="A13" s="20" t="n">
         <v>8</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -12639,14 +10312,14 @@
           <t>記録 令和8年10月7日／本表 令和8年10月7日</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="21" t="n">
+      <c r="A14" s="20" t="n">
         <v>9</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -12664,14 +10337,14 @@
           <t>記録9件（最新 令和8年9月28日）</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="20" t="n">
         <v>10</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -12686,17 +10359,17 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>11件（進める8・催促3）</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
+          <t>3件（進める0・催促3）</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="21" t="n">
+      <c r="A16" s="20" t="n">
         <v>11</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -12711,17 +10384,17 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>86件（区分A 0・既定値 86）</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
+          <t>0件（区分A 0・既定値 0）／据え置きの区分A 0件・既定値があり未処理 0件</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="21" t="n">
+      <c r="A17" s="20" t="n">
         <v>12</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -12739,14 +10412,14 @@
           <t>0件</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="21" t="n">
+      <c r="A18" s="20" t="n">
         <v>13</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -12764,14 +10437,14 @@
           <t>0件</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="21" t="n">
+      <c r="A19" s="20" t="n">
         <v>14</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -12789,14 +10462,14 @@
           <t>残り0件</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="21" t="n">
+      <c r="A20" s="20" t="n">
         <v>15</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -12814,7 +10487,7 @@
           <t>台帳にあり／古い記述 なし</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -12833,7 +10506,7 @@
           <t>適合16件・不適合0件</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -746,7 +746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>45527bf</t>
+          <t>6c405e7</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>既定値のとおり16件を処理した（令和8年10月7日・第2回）</t>
+          <t>既定値による処理を未決164件すべてまで進めた（令和8年10月7日）</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>2225818</t>
+          <t>45527bf</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>WBSを更新し、既定値のとおり16件を処理した（令和8年10月7日）</t>
+          <t>既定値のとおり16件を処理した（令和8年10月7日・第2回）</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>56a309f</t>
+          <t>2225818</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>意見交換会資料に時間配分と令和8年9月の制度の動向を加えた</t>
+          <t>WBSを更新し、既定値のとおり16件を処理した（令和8年10月7日）</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr"/>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>46b25f6</t>
+          <t>56a309f</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>事前打合せ資料に最低限の確認事項と時間配分を加えた（1〜2時間の枠）</t>
+          <t>意見交換会資料に時間配分と令和8年9月の制度の動向を加えた</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr"/>
@@ -1303,20 +1303,38 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>763e6ce</t>
+          <t>46b25f6</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月18日 介護保険部会資料による計画素案の是正（指摘15件）</t>
+          <t>事前打合せ資料に最低限の確認事項と時間配分を加えた（1〜2時間の枠）</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr"/>
       <c r="E27" s="6" t="inlineStr"/>
       <c r="F27" s="6" t="inlineStr"/>
     </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="13" t="inlineStr">
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>763e6ce</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>令和8年9月18日 介護保険部会資料による計画素案の是正（指摘15件）</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr"/>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
@@ -1325,11 +1343,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A29:F29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7231,7 +7249,7 @@
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
-          <t>の当方の扱い＝掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
+          <t>掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
         </is>
       </c>
     </row>
@@ -7274,7 +7292,7 @@
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
-          <t>の当方の扱い＝案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
+          <t>案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8088,7 @@
       </c>
       <c r="I163" s="6" t="inlineStr">
         <is>
-          <t>の当方の扱い＝現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
+          <t>現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
         </is>
       </c>
     </row>
@@ -8111,7 +8129,7 @@
       </c>
       <c r="I164" s="6" t="inlineStr">
         <is>
-          <t>の当方の扱い＝国が示す本格運用開始日（令和10年4月1日）までに完了することを前提として計画素案に記載し、年度ごとの工程は［要確認］として残す。事業所への周知は広域連合と3町が共同で行うものとして記載する</t>
+          <t>国が示す本格運用開始日（令和10年4月1日）までに完了することを前提として計画素案に記載し、年度ごとの工程は［要確認］として残す。事業所への周知は広域連合と3町が共同で行うものとして記載する</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8170,7 @@
       </c>
       <c r="I165" s="6" t="inlineStr">
         <is>
-          <t>の当方の扱い＝公表された区分のうち当区域の事業所の規模に近いものを参考として用い、区域内の事業所の経営状況を表すものとしては用いない。計画素案には活用の方針のみを記載し、数値は掲げない</t>
+          <t>公表された区分のうち当区域の事業所の規模に近いものを参考として用い、区域内の事業所の経営状況を表すものとしては用いない。計画素案には活用の方針のみを記載し、数値は掲げない</t>
         </is>
       </c>
     </row>
@@ -8193,7 +8211,7 @@
       </c>
       <c r="I166" s="6" t="inlineStr">
         <is>
-          <t>の当方の扱い＝計画素案には北海道及び事業者とともに活用を検討する旨のみを記載し、具体の取組及び目標は国から市町村の役割が示された後に定める</t>
+          <t>計画素案には北海道及び事業者とともに活用を検討する旨のみを記載し、具体の取組及び目標は国から市町村の役割が示された後に定める</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -132,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -183,6 +183,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -580,7 +583,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>毎日の終わりにWBSの現況・ペンディングの優先順位・当方の作業だけで進められるもの・翌日の作業順位を1枚にしたものです。基準日 令和8年10月7日。内部保管。</t>
+          <t>毎日の終わりにWBSの現況・ペンディングの優先順位・当方の作業だけで進められるもの・翌日の作業順位を1枚にしたものです。基準日 令和8年10月14日。内部保管。</t>
         </is>
       </c>
     </row>
@@ -746,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -767,7 +770,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）ごとの進捗率と、前に報告した時点からの動きです。基準日 令和8年10月7日。</t>
+          <t>仕様書４（1）〜（12）ごとの進捗率と、前に報告した時点からの動きです。基準日 令和8年10月14日。</t>
         </is>
       </c>
     </row>
@@ -1196,7 +1199,7 @@
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>注1）進捗の記録の基準日は 令和8年10月7日 です。本表の基準日（令和8年10月7日）と違うときは、進捗の更新がまだ行われていません。
+          <t>注1）進捗の記録の基準日は 令和8年10月14日 です。本表の基準日（令和8年10月14日）と違うときは、進捗の更新がまだ行われていません。
 注2）進捗率を更新したら、更新前の値を記録へ移します。移さないと、過去の時点を記す資料（月次の報告・議事録）の数値が書き換わります。</t>
         </is>
       </c>
@@ -1209,145 +1212,29 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="4" t="inlineStr"/>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>コミット</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>6c405e7</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>既定値による処理を未決164件すべてまで進めた（令和8年10月7日）</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr"/>
-      <c r="E23" s="6" t="inlineStr"/>
-      <c r="F23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>45527bf</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>既定値のとおり16件を処理した（令和8年10月7日・第2回）</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr"/>
-      <c r="E24" s="6" t="inlineStr"/>
-      <c r="F24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>2225818</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>WBSを更新し、既定値のとおり16件を処理した（令和8年10月7日）</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>56a309f</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>意見交換会資料に時間配分と令和8年9月の制度の動向を加えた</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>46b25f6</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>事前打合せ資料に最低限の確認事項と時間配分を加えた（1〜2時間の枠）</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>763e6ce</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>令和8年9月18日 介護保険部会資料による計画素案の是正（指摘15件）</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr"/>
-      <c r="E28" s="6" t="inlineStr"/>
-      <c r="F28" s="6" t="inlineStr"/>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>基準日のコミットはありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A29:F29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1359,7 +1246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I192"/>
+  <dimension ref="A1:I196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1383,7 +1270,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>完了していない確認事項と資料提供依頼を、影響度の点の高い順に並べたものです。点の付け方は03シートに全て書いています。基準日 令和8年10月7日。</t>
+          <t>完了していない確認事項と資料提供依頼を、影響度の点の高い順に並べたものです。点の付け方は03シートに全て書いています。基準日 令和8年10月14日。</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1278,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　確認事項（決定を求めるもの）　164件</t>
+          <t>1　確認事項（決定を求めるもの）　168件</t>
         </is>
       </c>
     </row>
@@ -4028,17 +3915,17 @@
         <v>62</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>4</v>
+        <v>181</v>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16の代理指標</t>
+          <t>介護保険法第117条ほか関係法令の条文のご提供</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>素案 第4章第3節・資料1
-全16KPIの4項目</t>
+          <t>計画素案 第1章第2節・第1章第5節・第1章第8節・第6章第5節
+計画素案の記載内容の洗い出しと対比 02シート</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -4048,20 +3935,20 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G67" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.8）（+2）</t>
+          <t>止めている成果物 計画素案（+1）／法定記載事項 法第117条に直結（+2）</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16は代理指標への振替案のとおりとする</t>
+          <t>条番号のみを記載し項番号及び号番号は記載しない。記載事項の点検は条文の番号ではなく記載事項の内容を単位として行い、条文を確認できていない箇所は［要確認］として残す</t>
         </is>
       </c>
     </row>
@@ -4070,17 +3957,17 @@
         <v>63</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績</t>
+          <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>素案 第3章第2節・第3節・第4節
-妥当性検証報告書 12シート</t>
+          <t>素案 第4章第3節・資料1
+全16KPIの4項目</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -4103,7 +3990,7 @@
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績を受領できないものとして、公表資料（交付金の評価結果・総合事業の実施状況に関する調査・年報）により評価する</t>
+          <t>代表KPI H07・H08・H12・H16は代理指標への振替案のとおりとする</t>
         </is>
       </c>
     </row>
@@ -4112,17 +3999,17 @@
         <v>64</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項の取扱い</t>
+          <t>第9期の施策・事業実績</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第5・6節
-H06・H11・H13・H14の基準値</t>
+          <t>素案 第3章第2節・第3節・第4節
+妥当性検証報告書 12シート</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -4145,7 +4032,7 @@
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項は当方の判定のままとする</t>
+          <t>第9期の施策・事業実績を受領できないものとして、公表資料（交付金の評価結果・総合事業の実施状況に関する調査・年報）により評価する</t>
         </is>
       </c>
     </row>
@@ -4154,17 +4041,17 @@
         <v>65</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>会議日程とパブリックコメントの期間</t>
+          <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>委員会資料原案
-パブリックコメント資料</t>
+          <t>素案 第2章第5・6節
+H06・H11・H13・H14の基準値</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -4187,7 +4074,7 @@
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>会議日程及びパブリックコメントの期間は仕様書５の工程による</t>
+          <t>3調査の点検事項は当方の判定のままとする</t>
         </is>
       </c>
     </row>
@@ -4196,21 +4083,22 @@
         <v>66</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料への工程表の反映</t>
+          <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料</t>
+          <t>委員会資料原案
+パブリックコメント資料</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
@@ -4228,7 +4116,7 @@
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>現行の工程表のまま進める</t>
+          <t>会議日程及びパブリックコメントの期間は仕様書５の工程による</t>
         </is>
       </c>
     </row>
@@ -4237,27 +4125,26 @@
         <v>67</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>特別地域加算の対象地域告示</t>
+          <t>キックオフ会議資料への工程表の反映</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第9節
-追加調査報告書 01シート</t>
+          <t>キックオフ会議資料</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G72" s="15" t="n">
@@ -4265,12 +4152,12 @@
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）</t>
+          <t>期限 超過（R8.8）（+2）</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>告示を確認できないものとして、特別地域加算の判定を計画素案に書かず［要確認］のまま残す</t>
+          <t>現行の工程表のまま進める</t>
         </is>
       </c>
     </row>
@@ -4279,22 +4166,22 @@
         <v>68</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較分析の対象</t>
+          <t>特別地域加算の対象地域告示</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第2節
-分析資料</t>
+          <t>素案 第1章第9節
+追加調査報告書 01シート</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
@@ -4312,7 +4199,7 @@
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較は公表されている同規模保険者40団体による</t>
+          <t>告示を確認できないものとして、特別地域加算の判定を計画素案に書かず［要確認］のまま残す</t>
         </is>
       </c>
     </row>
@@ -4321,17 +4208,17 @@
         <v>69</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価調書</t>
+          <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>素案 第3章第4節
-追加調査報告書 02シート</t>
+          <t>素案 第2章第2節
+分析資料</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -4354,7 +4241,7 @@
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
-          <t>評価調書を受領できないものとして、得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できない旨を注記する</t>
+          <t>類似保険者との比較は公表されている同規模保険者40団体による</t>
         </is>
       </c>
     </row>
@@ -4363,17 +4250,17 @@
         <v>70</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>調査の対象者範囲と回収率</t>
+          <t>交付金の評価調書</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第4〜6節
-クロス集計表</t>
+          <t>素案 第3章第4節
+追加調査報告書 02シート</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -4396,7 +4283,7 @@
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
+          <t>評価調書を受領できないものとして、得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できない旨を注記する</t>
         </is>
       </c>
     </row>
@@ -4405,17 +4292,17 @@
         <v>71</v>
       </c>
       <c r="B76" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>介護人材実態調査の採用者数・退職者数</t>
+          <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>素案 第4章第3節
-H14の基準値</t>
+          <t>素案 第2章第4〜6節
+クロス集計表</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -4438,7 +4325,7 @@
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
-          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
+          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
         </is>
       </c>
     </row>
@@ -4447,22 +4334,22 @@
         <v>72</v>
       </c>
       <c r="B77" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>町別の人口・世帯データ</t>
+          <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第1節
-図1・図2・図3</t>
+          <t>素案 第4章第3節
+H14の基準値</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
@@ -4480,7 +4367,7 @@
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
+          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
         </is>
       </c>
     </row>
@@ -4489,65 +4376,65 @@
         <v>73</v>
       </c>
       <c r="B78" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>町別の人口・世帯データ</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>素案 第2章第1節
+図1・図2・図3</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G78" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>期限 超過（R8.9）（+2）</t>
+        </is>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="48" customHeight="1">
+      <c r="A79" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B79" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C78" s="6" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>日常生活圏域別のデータ</t>
         </is>
       </c>
-      <c r="D78" s="6" t="inlineStr">
+      <c r="D79" s="6" t="inlineStr">
         <is>
           <t>素案 第1章第7節・第2章
 圏域別分析資料
 調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="E79" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G78" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H78" s="6" t="inlineStr">
-        <is>
-          <t>期限 超過（R8.9）（+2）</t>
-        </is>
-      </c>
-      <c r="I78" s="6" t="inlineStr">
-        <is>
-          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="48" customHeight="1">
-      <c r="A79" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="B79" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>骨子案の内容の確認</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>骨子案
-素案の次稿</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -4565,7 +4452,7 @@
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>骨子案は提出した内容のままとする</t>
+          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
         </is>
       </c>
     </row>
@@ -4574,22 +4461,22 @@
         <v>75</v>
       </c>
       <c r="B80" s="5" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標の読替えの考え方</t>
+          <t>骨子案の内容の確認</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第6節
-追加調査報告書 04シート</t>
+          <t>骨子案
+素案の次稿</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
@@ -4607,7 +4494,7 @@
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標の読替えは当方の案のままとする</t>
+          <t>骨子案は提出した内容のままとする</t>
         </is>
       </c>
     </row>
@@ -4616,22 +4503,22 @@
         <v>76</v>
       </c>
       <c r="B81" s="5" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>令和4年度 健康とくらしの調査の集計表</t>
+          <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析 14シート
-素案 第2章第4節</t>
+          <t>素案 第1章第6節
+追加調査報告書 04シート</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
@@ -4649,7 +4536,7 @@
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
+          <t>北海道の評価指標の読替えは当方の案のままとする</t>
         </is>
       </c>
     </row>
@@ -4658,17 +4545,17 @@
         <v>77</v>
       </c>
       <c r="B82" s="5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>調査対象者の範囲の確認</t>
+          <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析 13・14シート
-H06・H11の基準値</t>
+          <t>調査クロス集計・分析 14シート
+素案 第2章第4節</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -4691,7 +4578,7 @@
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
-          <t>現に収録している調査対象者の範囲による</t>
+          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4587,17 @@
         <v>78</v>
       </c>
       <c r="B83" s="5" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の令和6年・令和7年調査の結果</t>
+          <t>調査対象者の範囲の確認</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>素案 第3章第4節
-妥当性検証 所見18・19</t>
+          <t>調査クロス集計・分析 13・14シート
+H06・H11の基準値</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -4733,7 +4620,7 @@
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>公表されている全国集計の値による</t>
+          <t>現に収録している調査対象者の範囲による</t>
         </is>
       </c>
     </row>
@@ -4742,17 +4629,17 @@
         <v>79</v>
       </c>
       <c r="B84" s="5" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の給付費の集計が一致しない</t>
+          <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>給付実績データの受領点検
-将来推計 第2・3段階</t>
+          <t>素案 第3章第4節
+妥当性検証 所見18・19</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -4775,7 +4662,7 @@
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月25日の再提供により決着済み。再提供を受けたファイルの値（3町合計と円単位一致）による</t>
+          <t>公表されている全国集計の値による</t>
         </is>
       </c>
     </row>
@@ -4784,17 +4671,17 @@
         <v>80</v>
       </c>
       <c r="B85" s="5" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの実績値シートの確認</t>
+          <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>給付実績データの受領点検 04シート
-将来推計 第3段階</t>
+          <t>給付実績データの受領点検
+将来推計 第2・3段階</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -4817,7 +4704,7 @@
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
-          <t>総括表（保険者単位）を用い、計画作成支援ツールの実績値シートは比較のためにのみ用いる</t>
+          <t>令和8年9月25日の再提供により決着済み。再提供を受けたファイルの値（3町合計と円単位一致）による</t>
         </is>
       </c>
     </row>
@@ -4826,104 +4713,105 @@
         <v>81</v>
       </c>
       <c r="B86" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>計画作成支援ツールの実績値シートの確認</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>給付実績データの受領点検 04シート
+将来推計 第3段階</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G86" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>期限 超過（R8.9）（+2）</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>総括表（保険者単位）を用い、計画作成支援ツールの実績値シートは比較のためにのみ用いる</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="48" customHeight="1">
+      <c r="A87" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="B87" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="C86" s="6" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
         <is>
           <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
-      <c r="D86" s="6" t="inlineStr">
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>総合事業実施状況調査の受領点検
 素案 第3章第1節・第2節
 H05の基準値</t>
         </is>
       </c>
-      <c r="E86" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="inlineStr">
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G86" s="15" t="n">
+      <c r="G87" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="H86" s="6" t="inlineStr">
+      <c r="H87" s="6" t="inlineStr">
         <is>
           <t>期限 超過（R8.9）（+2）</t>
         </is>
       </c>
-      <c r="I86" s="6" t="inlineStr">
+      <c r="I87" s="6" t="inlineStr">
         <is>
           <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値による</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="48" customHeight="1">
-      <c r="A87" s="5" t="n">
-        <v>82</v>
-      </c>
-      <c r="B87" s="5" t="n">
+    <row r="88" ht="48" customHeight="1">
+      <c r="A88" s="5" t="n">
+        <v>83</v>
+      </c>
+      <c r="B88" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="C87" s="6" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
-      <c r="D87" s="6" t="inlineStr">
+      <c r="D88" s="6" t="inlineStr">
         <is>
           <t>年報月報の受領点検
 将来推計 第3段階
 素案 第6章第3節・第6節</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G87" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H87" s="6" t="inlineStr">
-        <is>
-          <t>期限 超過（R8.9）（+2）</t>
-        </is>
-      </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>受領済みの年報・月報の値による</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="48" customHeight="1">
-      <c r="A88" s="5" t="n">
-        <v>83</v>
-      </c>
-      <c r="B88" s="5" t="n">
-        <v>51</v>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>月報の値の接続のずれ（ご報告）</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>年報月報の受領点検 04シート</t>
-        </is>
-      </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
@@ -4944,7 +4832,7 @@
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれは記録として残し、計画本文には用いない</t>
+          <t>受領済みの年報・月報の値による</t>
         </is>
       </c>
     </row>
@@ -4953,17 +4841,16 @@
         <v>84</v>
       </c>
       <c r="B89" s="5" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領に伴う確認</t>
+          <t>月報の値の接続のずれ（ご報告）</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領点検 03シート
-素案 第6章第3節・第6節</t>
+          <t>年報月報の受領点検 04シート</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -4986,7 +4873,7 @@
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
-          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
+          <t>月報の値の接続のずれは記録として残し、計画本文には用いない</t>
         </is>
       </c>
     </row>
@@ -4995,62 +4882,62 @@
         <v>85</v>
       </c>
       <c r="B90" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度決算書の受領に伴う確認</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度決算書の受領点検 03シート
+素案 第6章第3節・第6節</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G90" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>期限 超過（R8.9）（+2）</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="48" customHeight="1">
+      <c r="A91" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="B91" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="C90" s="6" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
         </is>
       </c>
-      <c r="D90" s="6" t="inlineStr">
+      <c r="D91" s="6" t="inlineStr">
         <is>
           <t>基金条例の確認 02シート
 素案 第6章第6節
 将来推計 第3段階</t>
         </is>
       </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G90" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H90" s="6" t="inlineStr">
-        <is>
-          <t>期限 超過（R8.9）（+2）</t>
-        </is>
-      </c>
-      <c r="I90" s="6" t="inlineStr">
-        <is>
-          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合の1億円あたりの月額への効きを併記する</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="48" customHeight="1">
-      <c r="A91" s="5" t="n">
-        <v>86</v>
-      </c>
-      <c r="B91" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="C91" s="6" t="inlineStr">
-        <is>
-          <t>議事録の文書プロパティに個人名が再度入る</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>中間報告会議議事録
-業務工程管理表</t>
-        </is>
-      </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
@@ -5071,7 +4958,7 @@
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
-          <t>議事録は作成者名を落として再出力する（当方で対応する）</t>
+          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合の1億円あたりの月額への効きを併記する</t>
         </is>
       </c>
     </row>
@@ -5080,11 +4967,11 @@
         <v>87</v>
       </c>
       <c r="B92" s="5" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記に関するご提案3件</t>
+          <t>議事録の文書プロパティに個人名が再度入る</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -5113,7 +5000,7 @@
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記はご提案3件のとおり改める</t>
+          <t>議事録は作成者名を落として再出力する（当方で対応する）</t>
         </is>
       </c>
     </row>
@@ -5122,16 +5009,17 @@
         <v>88</v>
       </c>
       <c r="B93" s="5" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
+          <t>議事録の表記に関するご提案3件</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>見える化総括表の受領点検 00シート</t>
+          <t>中間報告会議議事録
+業務工程管理表</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -5154,7 +5042,7 @@
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>他団体の集計帳票6件は成果品に用いない</t>
+          <t>議事録の表記はご提案3件のとおり改める</t>
         </is>
       </c>
     </row>
@@ -5163,16 +5051,16 @@
         <v>89</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>調整交付金の算定基礎の確認</t>
+          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階 00・03シート</t>
+          <t>見える化総括表の受領点検 00シート</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -5195,7 +5083,7 @@
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
-          <t>現行の扱い（第9期の算定を再現し公表値6,428円と一致する扱い）による</t>
+          <t>他団体の集計帳票6件は成果品に用いない</t>
         </is>
       </c>
     </row>
@@ -5204,16 +5092,16 @@
         <v>90</v>
       </c>
       <c r="B95" s="5" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当て</t>
+          <t>調整交付金の算定基礎の確認</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>第9期施策別評価表 06シート</t>
+          <t>将来推計 第3段階 00・03シート</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -5236,7 +5124,7 @@
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当ては当方の案のままとする</t>
+          <t>現行の扱い（第9期の算定を再現し公表値6,428円と一致する扱い）による</t>
         </is>
       </c>
     </row>
@@ -5245,17 +5133,16 @@
         <v>91</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>職員個票のリストによる重複確認の可否</t>
+          <t>交付金の評価項目と19施策の割当て</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>内部確認結果への対応整理 03・08
-実施済み3調査の受領点検と集計 06・07</t>
+          <t>第9期施策別評価表 06シート</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -5278,7 +5165,7 @@
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
-          <t>職員個票を突き合わせず、事業所への照会により重複を判別する</t>
+          <t>交付金の評価項目と19施策の割当ては当方の案のままとする</t>
         </is>
       </c>
     </row>
@@ -5287,17 +5174,17 @@
         <v>92</v>
       </c>
       <c r="B97" s="5" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>構成町の一般会計繰入金の町別按分の方法</t>
+          <t>職員個票のリストによる重複確認の可否</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定（R8.9.26）
-構成町の意見への回答 4</t>
+          <t>内部確認結果への対応整理 03・08
+実施済み3調査の受領点検と集計 06・07</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -5307,7 +5194,7 @@
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>R8.9.24</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G97" s="15" t="n">
@@ -5315,12 +5202,12 @@
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9.24）（+2）</t>
+          <t>期限 超過（R8.9）（+2）</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
-          <t>町別への按分は広域連合の規約によるものであり算定できないため、構成町の一般会計繰入金は3町計の概算のみを示す（按分の方法のご教示を受けた時点で町別までお示しする）</t>
+          <t>職員個票を突き合わせず、事業所への照会により重複を判別する</t>
         </is>
       </c>
     </row>
@@ -5329,62 +5216,62 @@
         <v>93</v>
       </c>
       <c r="B98" s="5" t="n">
+        <v>82</v>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>構成町の一般会計繰入金の町別按分の方法</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量の算定（R8.9.26）
+構成町の意見への回答 4</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="inlineStr">
+        <is>
+          <t>R8.9.24</t>
+        </is>
+      </c>
+      <c r="G98" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>期限 超過（R8.9.24）（+2）</t>
+        </is>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>町別への按分は広域連合の規約によるものであり算定できないため、構成町の一般会計繰入金は3町計の概算のみを示す（按分の方法のご教示を受けた時点で町別までお示しする）</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="48" customHeight="1">
+      <c r="A99" s="5" t="n">
+        <v>94</v>
+      </c>
+      <c r="B99" s="5" t="n">
         <v>83</v>
       </c>
-      <c r="C98" s="6" t="inlineStr">
+      <c r="C99" s="6" t="inlineStr">
         <is>
           <t>構成町との意見交換会の実施方法と町別データシート</t>
         </is>
       </c>
-      <c r="D98" s="6" t="inlineStr">
+      <c r="D99" s="6" t="inlineStr">
         <is>
           <t>意見交換会資料
 町別データシート
 構成町の意見への回答 2・3</t>
         </is>
       </c>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G98" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H98" s="6" t="inlineStr">
-        <is>
-          <t>期限 超過（R8.9）（+2）</t>
-        </is>
-      </c>
-      <c r="I98" s="6" t="inlineStr">
-        <is>
-          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで進める</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="48" customHeight="1">
-      <c r="A99" s="5" t="n">
-        <v>94</v>
-      </c>
-      <c r="B99" s="5" t="n">
-        <v>85</v>
-      </c>
-      <c r="C99" s="6" t="inlineStr">
-        <is>
-          <t>町別データシートの内容と配付</t>
-        </is>
-      </c>
-      <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t>町別データシート
-構成町の意見への回答 2</t>
-        </is>
-      </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
@@ -5405,7 +5292,7 @@
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
-          <t>町別データシートは現行の内容のまま配付する</t>
+          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで進める</t>
         </is>
       </c>
     </row>
@@ -5414,22 +5301,22 @@
         <v>95</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>成果品の統合の方針</t>
+          <t>町別データシートの内容と配付</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>成果品一覧
-送付資料一覧</t>
+          <t>町別データシート
+構成町の意見への回答 2</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
@@ -5447,7 +5334,7 @@
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
-          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す（現行）</t>
+          <t>町別データシートは現行の内容のまま配付する</t>
         </is>
       </c>
     </row>
@@ -5456,17 +5343,17 @@
         <v>96</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
+          <t>成果品の統合の方針</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階・第3段階
-サービス見込量の算定</t>
+          <t>成果品一覧
+送付資料一覧</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -5489,7 +5376,7 @@
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
+          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す（現行）</t>
         </is>
       </c>
     </row>
@@ -5498,16 +5385,16 @@
         <v>97</v>
       </c>
       <c r="B102" s="5" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計方式は基本推計でよいか</t>
+          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階
+          <t>将来推計 第2段階・第3段階
 サービス見込量の算定</t>
         </is>
       </c>
@@ -5531,7 +5418,7 @@
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
-          <t>基本推計に近いP3で概算する</t>
+          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
         </is>
       </c>
     </row>
@@ -5540,11 +5427,11 @@
         <v>98</v>
       </c>
       <c r="B103" s="5" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
+          <t>見える化システムの推計方式は基本推計でよいか</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
@@ -5573,7 +5460,7 @@
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
-          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
+          <t>基本推計に近いP3で概算する</t>
         </is>
       </c>
     </row>
@@ -5582,16 +5469,17 @@
         <v>99</v>
       </c>
       <c r="B104" s="5" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
+          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階</t>
+          <t>将来推計 第2段階
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -5614,7 +5502,7 @@
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ</t>
+          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
         </is>
       </c>
     </row>
@@ -5623,16 +5511,16 @@
         <v>100</v>
       </c>
       <c r="B105" s="5" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供の要否</t>
+          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析の更新</t>
+          <t>将来推計 第2段階</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -5655,7 +5543,7 @@
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供を依頼しない（成果品は収録済みで内容が確定しており、現時点で不足がない）</t>
+          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ</t>
         </is>
       </c>
     </row>
@@ -5664,16 +5552,16 @@
         <v>101</v>
       </c>
       <c r="B106" s="5" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>第1次概算を既定値のまま出してよいか</t>
+          <t>健康とくらしの調査の個票の再提供の要否</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定</t>
+          <t>調査クロス集計・分析の更新</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -5696,7 +5584,7 @@
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
-          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
+          <t>健康とくらしの調査の個票の再提供を依頼しない（成果品は収録済みで内容が確定しており、現時点で不足がない）</t>
         </is>
       </c>
     </row>
@@ -5705,17 +5593,16 @@
         <v>102</v>
       </c>
       <c r="B107" s="5" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
+          <t>第1次概算を既定値のまま出してよいか</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>町別データシート
-サービス見込量の算定</t>
+          <t>サービス見込量の算定</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -5738,7 +5625,7 @@
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
+          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
         </is>
       </c>
     </row>
@@ -5747,16 +5634,16 @@
         <v>103</v>
       </c>
       <c r="B108" s="5" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの伸びの選択肢をどれとするか</t>
+          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力
+          <t>町別データシート
 サービス見込量の算定</t>
         </is>
       </c>
@@ -5780,7 +5667,7 @@
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
         </is>
       </c>
     </row>
@@ -5789,17 +5676,17 @@
         <v>104</v>
       </c>
       <c r="B109" s="5" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
+          <t>見える化システムの伸びの選択肢をどれとするか</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
           <t>見える化システムへの入力
-将来推計 第2段階</t>
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -5822,7 +5709,7 @@
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
-          <t>受領済みの画面の写しの範囲で概算し、確認できていない項目はその旨を明記する</t>
+          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
         </is>
       </c>
     </row>
@@ -5831,17 +5718,17 @@
         <v>105</v>
       </c>
       <c r="B110" s="5" t="n">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提（受託者案）</t>
+          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階 05・06シート
-計画素案 第6章第6節</t>
+          <t>見える化システムへの入力
+将来推計 第2段階</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -5851,7 +5738,7 @@
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G110" s="15" t="n">
@@ -5859,12 +5746,12 @@
       </c>
       <c r="H110" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）</t>
+          <t>期限 超過（R8.9）（+2）</t>
         </is>
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
-          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
+          <t>受領済みの画面の写しの範囲で概算し、確認できていない項目はその旨を明記する</t>
         </is>
       </c>
     </row>
@@ -5873,17 +5760,17 @@
         <v>106</v>
       </c>
       <c r="B111" s="5" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスの住民向けの記載</t>
+          <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>介護高齢者福祉サービスガイド_構成案
-計画素案 第6章第4節</t>
+          <t>将来推計 第3段階 05・06シート
+計画素案 第6章第6節</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -5906,7 +5793,7 @@
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
+          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
         </is>
       </c>
     </row>
@@ -5915,17 +5802,17 @@
         <v>107</v>
       </c>
       <c r="B112" s="5" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠（令和8年度新設）への対応</t>
+          <t>区域内に事業所がないサービスの住民向けの記載</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章
-交付金評価指標と全国集計の受領点検 06シート</t>
+          <t>介護高齢者福祉サービスガイド_構成案
+計画素案 第6章第4節</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -5948,7 +5835,7 @@
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠への対応状況を確認できないものとして、第10期の施策には位置づけず、確認でき次第加える</t>
+          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
         </is>
       </c>
     </row>
@@ -5957,17 +5844,17 @@
         <v>108</v>
       </c>
       <c r="B113" s="5" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+          <t>成果指向型配分枠（令和8年度新設）への対応</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節・第2章第8節・第5章・第6章第2節・第6章第4節
-ケアプラン点検実施要領</t>
+          <t>計画素案 第5章
+交付金評価指標と全国集計の受領点検 06シート</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -5990,7 +5877,7 @@
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
+          <t>成果指向型配分枠への対応状況を確認できないものとして、第10期の施策には位置づけず、確認でき次第加える</t>
         </is>
       </c>
     </row>
@@ -5999,62 +5886,62 @@
         <v>109</v>
       </c>
       <c r="B114" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第1章第9節・第2章第8節・第5章・第6章第2節・第6章第4節
+ケアプラン点検実施要領</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G114" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H114" s="6" t="inlineStr">
+        <is>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="48" customHeight="1">
+      <c r="A115" s="5" t="n">
+        <v>110</v>
+      </c>
+      <c r="B115" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="C114" s="6" t="inlineStr">
+      <c r="C115" s="6" t="inlineStr">
         <is>
           <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
         </is>
       </c>
-      <c r="D114" s="6" t="inlineStr">
+      <c r="D115" s="6" t="inlineStr">
         <is>
           <t>給付適正化計画の位置づけと追加検討事項 01シート
 計画素案 第5章 基本目標5・第2章第4節
 アンケート調査の分析 令和8年9月業務報告 第4節</t>
         </is>
       </c>
-      <c r="E114" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F114" s="5" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G114" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H114" s="6" t="inlineStr">
-        <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）</t>
-        </is>
-      </c>
-      <c r="I114" s="6" t="inlineStr">
-        <is>
-          <t>第9期計画の本文及び前回調査の原集計表を受領できないものとして、前回調査との比較は割合のみとし、指標別の分母を確認できない旨を注記する</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="48" customHeight="1">
-      <c r="A115" s="5" t="n">
-        <v>110</v>
-      </c>
-      <c r="B115" s="5" t="n">
-        <v>91</v>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>介護給付費通知及び給付実績の活用による確認等</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="inlineStr">
-        <is>
-          <t>給付適正化計画の位置づけと追加検討事項 02シート
-計画素案 第5章 基本目標5</t>
-        </is>
-      </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
@@ -6075,7 +5962,7 @@
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知の実施状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
+          <t>第9期計画の本文及び前回調査の原集計表を受領できないものとして、前回調査との比較は割合のみとし、指標別の分母を確認できない旨を注記する</t>
         </is>
       </c>
     </row>
@@ -6084,16 +5971,16 @@
         <v>111</v>
       </c>
       <c r="B116" s="5" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
+          <t>介護給付費通知及び給付実績の活用による確認等</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけと追加検討事項 04シート
+          <t>給付適正化計画の位置づけと追加検討事項 02シート
 計画素案 第5章 基本目標5</t>
         </is>
       </c>
@@ -6117,7 +6004,7 @@
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
-          <t>認定調査の委託の状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
+          <t>介護給付費通知の実施状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
         </is>
       </c>
     </row>
@@ -6126,108 +6013,108 @@
         <v>112</v>
       </c>
       <c r="B117" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>給付適正化計画の位置づけと追加検討事項 04シート
+計画素案 第5章 基本目標5</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G117" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H117" s="6" t="inlineStr">
+        <is>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>認定調査の委託の状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="48" customHeight="1">
+      <c r="A118" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="B118" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="C117" s="6" t="inlineStr">
+      <c r="C118" s="6" t="inlineStr">
         <is>
           <t>令和9年4月1日から義務となる2件への対応</t>
         </is>
       </c>
-      <c r="D117" s="6" t="inlineStr">
+      <c r="D118" s="6" t="inlineStr">
         <is>
           <t>計画素案 第1章第9節
 計画素案 第5章 基本目標3・4
 計画素案 第6章第4節3</t>
         </is>
       </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F117" s="5" t="inlineStr">
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G117" s="15" t="n">
+      <c r="G118" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="H117" s="6" t="inlineStr">
+      <c r="H118" s="6" t="inlineStr">
         <is>
           <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
-      <c r="I117" s="6" t="inlineStr">
+      <c r="I118" s="6" t="inlineStr">
         <is>
           <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="48" customHeight="1">
-      <c r="A118" s="5" t="n">
-        <v>113</v>
-      </c>
-      <c r="B118" s="5" t="n">
+    <row r="119" ht="48" customHeight="1">
+      <c r="A119" s="5" t="n">
+        <v>114</v>
+      </c>
+      <c r="B119" s="5" t="n">
         <v>99</v>
       </c>
-      <c r="C118" s="6" t="inlineStr">
+      <c r="C119" s="6" t="inlineStr">
         <is>
           <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
         </is>
       </c>
-      <c r="D118" s="6" t="inlineStr">
+      <c r="D119" s="6" t="inlineStr">
         <is>
           <t>計画素案 第6章第4節
 計画素案 第6章第2節2（2）
 地域密着型サービス基準省令の論点整理</t>
         </is>
       </c>
-      <c r="E118" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F118" s="5" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G118" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H118" s="6" t="inlineStr">
-        <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）</t>
-        </is>
-      </c>
-      <c r="I118" s="6" t="inlineStr">
-        <is>
-          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="48" customHeight="1">
-      <c r="A119" s="5" t="n">
-        <v>114</v>
-      </c>
-      <c r="B119" s="5" t="n">
-        <v>108</v>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>補正しても外れるサービス6件の理由</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>対計画比の偏りの補正試算
-計画素案 第6章第2節2</t>
-        </is>
-      </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
@@ -6245,7 +6132,7 @@
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
+          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
         </is>
       </c>
     </row>
@@ -6254,16 +6141,17 @@
         <v>115</v>
       </c>
       <c r="B120" s="5" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
+          <t>補正しても外れるサービス6件の理由</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第8節・第2章第3節6・第5章 基本目標2・第6章第2節</t>
+          <t>対計画比の偏りの補正試算
+計画素案 第6章第2節2</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -6286,7 +6174,7 @@
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
-          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
+          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
         </is>
       </c>
     </row>
@@ -6295,22 +6183,21 @@
         <v>116</v>
       </c>
       <c r="B121" s="5" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
+          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2
-第9期評価（施策2-5）</t>
+          <t>計画素案 第1章第8節・第2章第3節6・第5章 基本目標2・第6章第2節</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
@@ -6328,7 +6215,7 @@
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIはO2（提起された地域課題のうち翌年度の事業・予算に反映されたものの割合）とする（当方案）</t>
+          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
         </is>
       </c>
     </row>
@@ -6337,21 +6224,22 @@
         <v>117</v>
       </c>
       <c r="B122" s="5" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
+          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2</t>
+          <t>計画素案 第5章 基本目標2
+第9期評価（施策2-5）</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
@@ -6369,7 +6257,7 @@
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の記録様式は協議資料にとどめ、令和9年度に整える</t>
+          <t>施策2-5の代表KPIはO2（提起された地域課題のうち翌年度の事業・予算に反映されたものの割合）とする（当方案）</t>
         </is>
       </c>
     </row>
@@ -6378,16 +6266,16 @@
         <v>118</v>
       </c>
       <c r="B123" s="5" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
+          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2・第6章第4節4</t>
+          <t>計画素案 第5章 基本目標2</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -6410,7 +6298,7 @@
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
+          <t>地域ケア会議の記録様式は協議資料にとどめ、令和9年度に整える</t>
         </is>
       </c>
     </row>
@@ -6419,22 +6307,21 @@
         <v>119</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2
-第9期評価（施策2-5）</t>
+          <t>計画素案 第5章 基本目標2・第6章第4節4</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
@@ -6452,7 +6339,7 @@
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の実施報告書により把握できる範囲で記述する</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
         </is>
       </c>
     </row>
@@ -6461,22 +6348,22 @@
         <v>120</v>
       </c>
       <c r="B125" s="5" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
+          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節3・第6章第1節
-将来推計 第1段階・第2段階</t>
+          <t>計画素案 第5章 基本目標2
+第9期評価（施策2-5）</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
@@ -6494,7 +6381,7 @@
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
-          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
+          <t>令和7年度の実施報告書により把握できる範囲で記述する</t>
         </is>
       </c>
     </row>
@@ -6503,17 +6390,17 @@
         <v>121</v>
       </c>
       <c r="B126" s="5" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総人口の設定を案Cに改めるか</t>
+          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第1段階
-計画素案 第2章第1節・第6章第1節</t>
+          <t>計画素案 第2章第1節3・第6章第1節
+将来推計 第1段階・第2段階</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -6536,7 +6423,7 @@
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
-          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
+          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
         </is>
       </c>
     </row>
@@ -6545,22 +6432,22 @@
         <v>122</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+          <t>見える化システムの総人口の設定を案Cに改めるか</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階
-計画素案 第6章第4節2</t>
+          <t>将来推計 第1段階
+計画素案 第2章第1節・第6章第1節</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
@@ -6578,7 +6465,7 @@
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
+          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
         </is>
       </c>
     </row>
@@ -6587,22 +6474,22 @@
         <v>123</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度と年報の月平均の食い違い</t>
+          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
           <t>将来推計 第2段階
-計画素案 第6章第2節</t>
+計画素案 第6章第4節2</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
@@ -6620,7 +6507,7 @@
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
-          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
+          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
         </is>
       </c>
     </row>
@@ -6629,16 +6516,17 @@
         <v>124</v>
       </c>
       <c r="B129" s="5" t="n">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所の表示の統一</t>
+          <t>画面の令和7年度と年報の月平均の食い違い</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>計画素案（策定委員会用）</t>
+          <t>将来推計 第2段階
+計画素案 第6章第2節</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -6661,7 +6549,7 @@
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとする</t>
+          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
         </is>
       </c>
     </row>
@@ -6670,17 +6558,16 @@
         <v>125</v>
       </c>
       <c r="B130" s="5" t="n">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えるか</t>
+          <t>計画素案の未確定箇所の表示の統一</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節
-図表集</t>
+          <t>計画素案（策定委員会用）</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -6703,7 +6590,7 @@
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えない。加筆分は協議用の資料にとどめる</t>
+          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとする</t>
         </is>
       </c>
     </row>
@@ -6712,17 +6599,17 @@
         <v>126</v>
       </c>
       <c r="B131" s="5" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>中長期推計を令和12・27・32年度まで広げるか</t>
+          <t>計画素案 第2章第1節に町別の図を加えるか</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力
-計画素案 第6章第1節・第3節</t>
+          <t>計画素案 第2章第1節
+図表集</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -6745,7 +6632,7 @@
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
-          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
+          <t>計画素案 第2章第1節に町別の図を加えない。加筆分は協議用の資料にとどめる</t>
         </is>
       </c>
     </row>
@@ -6754,17 +6641,17 @@
         <v>127</v>
       </c>
       <c r="B132" s="5" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
+          <t>中長期推計を令和12・27・32年度まで広げるか</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・第5章 基本目標3・資料1
-アンケート調査の集計分析報告書 02・14シート</t>
+          <t>見える化システムへの入力
+計画素案 第6章第1節・第3節</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -6787,7 +6674,7 @@
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
-          <t>設問ごとの有効回答を分母とし、町別の値は掲げない（令和8年9月25日に是正済み）</t>
+          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
         </is>
       </c>
     </row>
@@ -6796,22 +6683,22 @@
         <v>128</v>
       </c>
       <c r="B133" s="5" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>東川町の通いの場の整備と担い手の確保</t>
+          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第3章第1節・第5章 基本目標2
-10月 地域課題の整理と3町協議の確認事項</t>
+          <t>計画素案 第4章第3節・第5章 基本目標3・資料1
+アンケート調査の集計分析報告書 02・14シート</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>発注者・東川町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
@@ -6829,7 +6716,7 @@
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
-          <t>現状のまま（東川町の整備を見込まない）第10期の目標値を置く</t>
+          <t>設問ごとの有効回答を分母とし、町別の値は掲げない（令和8年9月25日に是正済み）</t>
         </is>
       </c>
     </row>
@@ -6838,16 +6725,16 @@
         <v>129</v>
       </c>
       <c r="B134" s="5" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>東川町の認知症サポーター養成講座の実施状況</t>
+          <t>東川町の通いの場の整備と担い手の確保</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2
+          <t>計画素案 第3章第1節・第5章 基本目標2
 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
@@ -6871,7 +6758,7 @@
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
+          <t>現状のまま（東川町の整備を見込まない）第10期の目標値を置く</t>
         </is>
       </c>
     </row>
@@ -6880,11 +6767,11 @@
         <v>130</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>東川町のチームオレンジ事業の位置づけ</t>
+          <t>東川町の認知症サポーター養成講座の実施状況</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
@@ -6913,7 +6800,7 @@
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t>東川町の取組として記述し3町展開は記述しない</t>
+          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
         </is>
       </c>
     </row>
@@ -6922,11 +6809,11 @@
         <v>131</v>
       </c>
       <c r="B136" s="5" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
+          <t>東川町のチームオレンジ事業の位置づけ</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
@@ -6937,7 +6824,7 @@
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>発注者・美瑛町</t>
+          <t>発注者・東川町</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
@@ -6955,7 +6842,7 @@
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残す</t>
+          <t>東川町の取組として記述し3町展開は記述しない</t>
         </is>
       </c>
     </row>
@@ -6964,11 +6851,11 @@
         <v>132</v>
       </c>
       <c r="B137" s="5" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
+          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
@@ -6997,7 +6884,7 @@
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の取組として記述し3町展開は記述しない</t>
+          <t>令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残す</t>
         </is>
       </c>
     </row>
@@ -7006,16 +6893,16 @@
         <v>133</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
+          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第4節・第6章第5節
+          <t>計画素案 第5章 基本目標2
 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
@@ -7039,7 +6926,7 @@
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
+          <t>美瑛町の取組として記述し3町展開は記述しない</t>
         </is>
       </c>
     </row>
@@ -7048,16 +6935,16 @@
         <v>134</v>
       </c>
       <c r="B139" s="5" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
+          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2
+          <t>計画素案 第6章第4節・第6章第5節
 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
@@ -7081,7 +6968,7 @@
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述する</t>
+          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
         </is>
       </c>
     </row>
@@ -7090,22 +6977,22 @@
         <v>135</v>
       </c>
       <c r="B140" s="5" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の通いの場の維持</t>
+          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第3章第1節・第5章 基本目標2
+          <t>計画素案 第5章 基本目標2
 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>発注者・東神楽町</t>
+          <t>発注者・美瑛町</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
@@ -7123,7 +7010,7 @@
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の水準が続くものとして目標値を置く</t>
+          <t>現に確認できる取組の範囲で記述する</t>
         </is>
       </c>
     </row>
@@ -7132,16 +7019,16 @@
         <v>136</v>
       </c>
       <c r="B141" s="5" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
+          <t>東神楽町の通いの場の維持</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2
+          <t>計画素案 第3章第1節・第5章 基本目標2
 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
@@ -7165,7 +7052,7 @@
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
+          <t>令和6年度の水準が続くものとして目標値を置く</t>
         </is>
       </c>
     </row>
@@ -7174,22 +7061,22 @@
         <v>137</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
+          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>計画素案の記載内容の洗い出しと対比 06シート・07シート
-計画素案 第1章第6節・第2章第3節・第2章第6節・第3章第2節・第4章第3節・第6章第6節</t>
+          <t>計画素案 第5章 基本目標2
+10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・東神楽町</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
@@ -7207,7 +7094,7 @@
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
-          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
+          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
         </is>
       </c>
     </row>
@@ -7216,17 +7103,17 @@
         <v>138</v>
       </c>
       <c r="B143" s="5" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
+          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>図表データ管理台帳 03シート
-計画素案 第3章第4節・資料7</t>
+          <t>計画素案の記載内容の洗い出しと対比 06シート・07シート
+計画素案 第1章第6節・第2章第3節・第2章第6節・第3章第2節・第4章第3節・第6章第6節</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -7249,7 +7136,7 @@
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
-          <t>掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
+          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
         </is>
       </c>
     </row>
@@ -7258,70 +7145,70 @@
         <v>139</v>
       </c>
       <c r="B144" s="5" t="n">
+        <v>172</v>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>図表データ管理台帳 03シート
+計画素案 第3章第4節・資料7</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G144" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H144" s="6" t="inlineStr">
+        <is>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="48" customHeight="1">
+      <c r="A145" s="5" t="n">
+        <v>140</v>
+      </c>
+      <c r="B145" s="5" t="n">
         <v>174</v>
       </c>
-      <c r="C144" s="6" t="inlineStr">
+      <c r="C145" s="6" t="inlineStr">
         <is>
           <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
         </is>
       </c>
-      <c r="D144" s="6" t="inlineStr">
+      <c r="D145" s="6" t="inlineStr">
         <is>
           <t>人口推計コーホート分析の妥当性検証 07シート
 見える化へ入力する箇所と入力値 02シート
 計画素案 第2章第1節・第6章第1節</t>
         </is>
       </c>
-      <c r="E144" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F144" s="5" t="inlineStr">
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
         <is>
           <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G144" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H144" s="6" t="inlineStr">
-        <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）</t>
-        </is>
-      </c>
-      <c r="I144" s="6" t="inlineStr">
-        <is>
-          <t>案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="48" customHeight="1">
-      <c r="A145" s="5" t="n">
-        <v>140</v>
-      </c>
-      <c r="B145" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="C145" s="6" t="inlineStr">
-        <is>
-          <t>保険料算定の前提</t>
-        </is>
-      </c>
-      <c r="D145" s="6" t="inlineStr">
-        <is>
-          <t>素案 第6章第3節・第6節
-保険料算定表</t>
-        </is>
-      </c>
-      <c r="E145" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F145" s="5" t="inlineStr">
-        <is>
-          <t>R8.11</t>
         </is>
       </c>
       <c r="G145" s="15" t="n">
@@ -7329,12 +7216,12 @@
       </c>
       <c r="H145" s="6" t="inlineStr">
         <is>
-          <t>止めている成果物 保険料（+2）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
+          <t>案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
         </is>
       </c>
     </row>
@@ -7343,39 +7230,40 @@
         <v>141</v>
       </c>
       <c r="B146" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>保険料算定の前提</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>素案 第6章第3節・第6節
+保険料算定表</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F146" s="5" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G146" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C146" s="6" t="inlineStr">
-        <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr">
-        <is>
-          <t>素案 第1章第9節・第6章第4節</t>
-        </is>
-      </c>
-      <c r="E146" s="5" t="inlineStr">
-        <is>
-          <t>北海道</t>
-        </is>
-      </c>
-      <c r="F146" s="5" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G146" s="15" t="n">
-        <v>1</v>
-      </c>
       <c r="H146" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）</t>
+          <t>止めている成果物 保険料（+2）</t>
         </is>
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
+          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
         </is>
       </c>
     </row>
@@ -7384,62 +7272,61 @@
         <v>142</v>
       </c>
       <c r="B147" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>特定地域の指定に係る意向表明の手続</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>素案 第1章第9節・第6章第4節</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G147" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" s="6" t="inlineStr">
+        <is>
+          <t>期限 当月（R8.10）（+1）</t>
+        </is>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="48" customHeight="1">
+      <c r="A148" s="5" t="n">
+        <v>143</v>
+      </c>
+      <c r="B148" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="C147" s="6" t="inlineStr">
+      <c r="C148" s="6" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
-      <c r="D147" s="6" t="inlineStr">
+      <c r="D148" s="6" t="inlineStr">
         <is>
           <t>素案 第1章第7節
 追加調査報告書 03シート
 住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
-      <c r="E147" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F147" s="5" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G147" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H147" s="6" t="inlineStr">
-        <is>
-          <t>期限 当月（R8.10）（+1）</t>
-        </is>
-      </c>
-      <c r="I147" s="6" t="inlineStr">
-        <is>
-          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="48" customHeight="1">
-      <c r="A148" s="5" t="n">
-        <v>143</v>
-      </c>
-      <c r="B148" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C148" s="6" t="inlineStr">
-        <is>
-          <t>人口推計の基礎とする系列</t>
-        </is>
-      </c>
-      <c r="D148" s="6" t="inlineStr">
-        <is>
-          <t>素案 第6章第1節
-将来推計</t>
-        </is>
-      </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
           <t>発注者・3町</t>
@@ -7460,7 +7347,7 @@
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
-          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
+          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
         </is>
       </c>
     </row>
@@ -7469,11 +7356,11 @@
         <v>144</v>
       </c>
       <c r="B149" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>認定者数の基準月と月次推移</t>
+          <t>人口推計の基礎とする系列</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr">
@@ -7484,7 +7371,7 @@
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
@@ -7502,7 +7389,7 @@
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
-          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
+          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
         </is>
       </c>
     </row>
@@ -7511,22 +7398,22 @@
         <v>145</v>
       </c>
       <c r="B150" s="5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>3町計画への共通指標の掲載</t>
+          <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>素案 資料2
-3町協議資料</t>
+          <t>素案 第6章第1節
+将来推計</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
@@ -7544,7 +7431,7 @@
       </c>
       <c r="I150" s="6" t="inlineStr">
         <is>
-          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
+          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
         </is>
       </c>
     </row>
@@ -7553,21 +7440,22 @@
         <v>146</v>
       </c>
       <c r="B151" s="5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場</t>
+          <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第4節</t>
+          <t>素案 資料2
+3町協議資料</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
@@ -7585,7 +7473,7 @@
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
+          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
         </is>
       </c>
     </row>
@@ -7594,22 +7482,21 @@
         <v>147</v>
       </c>
       <c r="B152" s="5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様</t>
+          <t>北海道・圏域との調整の場</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>計画書（印刷200部）
-概要版</t>
+          <t>素案 第6章第4節</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
@@ -7627,7 +7514,7 @@
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
+          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
         </is>
       </c>
     </row>
@@ -7636,22 +7523,22 @@
         <v>148</v>
       </c>
       <c r="B153" s="5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>事業所の定員・稼働率データ</t>
+          <t>成果品の仕様</t>
         </is>
       </c>
       <c r="D153" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第3節・第6章第4節
-図21・図22</t>
+          <t>計画書（印刷200部）
+概要版</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
@@ -7669,7 +7556,7 @@
       </c>
       <c r="I153" s="6" t="inlineStr">
         <is>
-          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
+          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
         </is>
       </c>
     </row>
@@ -7678,22 +7565,22 @@
         <v>149</v>
       </c>
       <c r="B154" s="5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>認知症・医療介護連携の実績データ</t>
+          <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>素案 第5章 基本目標1・5
-図表集 認知症・医療連携</t>
+          <t>素案 第2章第3節・第6章第4節
+図21・図22</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
@@ -7711,7 +7598,7 @@
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
-          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
+          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
         </is>
       </c>
     </row>
@@ -7720,22 +7607,22 @@
         <v>150</v>
       </c>
       <c r="B155" s="5" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提</t>
+          <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第1節
-認定者数・給付費の推計</t>
+          <t>素案 第5章 基本目標1・5
+図表集 認知症・医療連携</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町・北海道</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
@@ -7753,7 +7640,7 @@
       </c>
       <c r="I155" s="6" t="inlineStr">
         <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
+          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
         </is>
       </c>
     </row>
@@ -7762,17 +7649,17 @@
         <v>151</v>
       </c>
       <c r="B156" s="5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の実施予定と推計での扱い</t>
+          <t>重度化の速度の前提</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第2節・第5章・第7章
-給付費の推計</t>
+          <t>素案 第6章第1節
+認定者数・給付費の推計</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -7795,7 +7682,7 @@
       </c>
       <c r="I156" s="6" t="inlineStr">
         <is>
-          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
+          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
         </is>
       </c>
     </row>
@@ -7804,17 +7691,17 @@
         <v>152</v>
       </c>
       <c r="B157" s="5" t="n">
-        <v>128</v>
+        <v>31</v>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の実績見込み値を編集するか</t>
+          <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
       <c r="D157" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階
-サービス見込量の算定</t>
+          <t>素案 第6章第2節・第5章・第7章
+給付費の推計</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -7837,7 +7724,7 @@
       </c>
       <c r="I157" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
+          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
         </is>
       </c>
     </row>
@@ -7846,11 +7733,11 @@
         <v>153</v>
       </c>
       <c r="B158" s="5" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの利用率等の伸びの選択</t>
+          <t>令和8年度の実績見込み値を編集するか</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
@@ -7879,7 +7766,7 @@
       </c>
       <c r="I158" s="6" t="inlineStr">
         <is>
-          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
         </is>
       </c>
     </row>
@@ -7888,16 +7775,17 @@
         <v>154</v>
       </c>
       <c r="B159" s="5" t="n">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>統合した成果品の元の資料を残すか</t>
+          <t>見える化システムの利用率等の伸びの選択</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr">
         <is>
-          <t>成果品一覧（納品時の構成）</t>
+          <t>将来推計 第2段階
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -7920,7 +7808,7 @@
       </c>
       <c r="I159" s="6" t="inlineStr">
         <is>
-          <t>統合した成果品の元の資料を残す</t>
+          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
         </is>
       </c>
     </row>
@@ -7929,17 +7817,16 @@
         <v>155</v>
       </c>
       <c r="B160" s="5" t="n">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
+          <t>統合した成果品の元の資料を残すか</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力
-将来推計 第3段階</t>
+          <t>成果品一覧（納品時の構成）</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -7962,7 +7849,7 @@
       </c>
       <c r="I160" s="6" t="inlineStr">
         <is>
-          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
+          <t>統合した成果品の元の資料を残す</t>
         </is>
       </c>
     </row>
@@ -7971,22 +7858,22 @@
         <v>156</v>
       </c>
       <c r="B161" s="5" t="n">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
+          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の取りまとめと第10期への反映 08シート・09シート
-10月 地域課題の整理と3町協議の確認事項</t>
+          <t>見える化システムへの入力
+将来推計 第3段階</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
@@ -8004,7 +7891,7 @@
       </c>
       <c r="I161" s="6" t="inlineStr">
         <is>
-          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
+          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
         </is>
       </c>
     </row>
@@ -8013,27 +7900,27 @@
         <v>157</v>
       </c>
       <c r="B162" s="5" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
+          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>計画素案の記載内容の洗い出しと対比 08シート
-計画素案 全体</t>
+          <t>交付金評価の取りまとめと第10期への反映 08シート・09シート
+10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G162" s="15" t="n">
@@ -8041,12 +7928,12 @@
       </c>
       <c r="H162" s="6" t="inlineStr">
         <is>
-          <t>止めている成果物 計画素案（+1）</t>
+          <t>期限 当月（R8.10）（+1）</t>
         </is>
       </c>
       <c r="I162" s="6" t="inlineStr">
         <is>
-          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
+          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
         </is>
       </c>
     </row>
@@ -8055,17 +7942,17 @@
         <v>158</v>
       </c>
       <c r="B163" s="5" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
+          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
         <is>
-          <t>図表データ管理台帳 01シート・02シート
-計画素案 資料7／別冊の図表集</t>
+          <t>計画素案の記載内容の洗い出しと対比 08シート
+計画素案 全体</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -8088,7 +7975,7 @@
       </c>
       <c r="I163" s="6" t="inlineStr">
         <is>
-          <t>現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
+          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
         </is>
       </c>
     </row>
@@ -8097,21 +7984,22 @@
         <v>159</v>
       </c>
       <c r="B164" s="5" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
+          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節5・第5章 基本目標1・基本目標4</t>
+          <t>図表データ管理台帳 01シート・02シート
+計画素案 資料7／別冊の図表集</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr">
@@ -8129,7 +8017,7 @@
       </c>
       <c r="I164" s="6" t="inlineStr">
         <is>
-          <t>国が示す本格運用開始日（令和10年4月1日）までに完了することを前提として計画素案に記載し、年度ごとの工程は［要確認］として残す。事業所への周知は広域連合と3町が共同で行うものとして記載する</t>
+          <t>現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
         </is>
       </c>
     </row>
@@ -8138,26 +8026,26 @@
         <v>160</v>
       </c>
       <c r="B165" s="5" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>介護サービス事業者経営情報データベースの公表結果の活用の範囲</t>
+          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節5・第5章 基本目標4</t>
+          <t>計画素案 第1章第9節5・第5章 基本目標1・基本目標4</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
-          <t>R8.12</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G165" s="15" t="n">
@@ -8170,7 +8058,7 @@
       </c>
       <c r="I165" s="6" t="inlineStr">
         <is>
-          <t>公表された区分のうち当区域の事業所の規模に近いものを参考として用い、区域内の事業所の経営状況を表すものとしては用いない。計画素案には活用の方針のみを記載し、数値は掲げない</t>
+          <t>国が示す本格運用開始日（令和10年4月1日）までに完了することを前提として計画素案に記載し、年度ごとの工程は［要確認］として残す。事業所への周知は広域連合と3町が共同で行うものとして記載する</t>
         </is>
       </c>
     </row>
@@ -8179,26 +8067,27 @@
         <v>161</v>
       </c>
       <c r="B166" s="5" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>都道府県との協定に基づく連携への関与</t>
+          <t>構成3町の高齢者福祉計画と市町村老人福祉計画の関係</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節5・第5章 基本目標3・基本目標4</t>
+          <t>計画素案 第1章第2節・第1章第8節
+計画素案の記載内容の洗い出しと対比 02シート</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
-          <t>R8.12</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G166" s="15" t="n">
@@ -8211,7 +8100,7 @@
       </c>
       <c r="I166" s="6" t="inlineStr">
         <is>
-          <t>計画素案には北海道及び事業者とともに活用を検討する旨のみを記載し、具体の取組及び目標は国から市町村の役割が示された後に定める</t>
+          <t>構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない</t>
         </is>
       </c>
     </row>
@@ -8220,27 +8109,27 @@
         <v>162</v>
       </c>
       <c r="B167" s="5" t="n">
-        <v>74</v>
+        <v>179</v>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
+          <t>成年後見制度の利用の促進に関する施策についての基本的な計画の策定状況</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）9
-計画素案 第5章 基本目標5</t>
+          <t>計画素案 第1章第2節・第5章 基本目標1
+計画素案の記載内容の洗い出しと対比 02シート</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>北海道上川総合振興局</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>R9.4</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G167" s="15" t="n">
@@ -8253,7 +8142,7 @@
       </c>
       <c r="I167" s="6" t="inlineStr">
         <is>
-          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
+          <t>同計画は構成3町が定めるものとして計画素案に記載し、本計画は介護保険法第117条第3項による権利擁護の施策（第5章 基本目標1）をもって接続する。中核機関の整備の状況は［要確認］として残す</t>
         </is>
       </c>
     </row>
@@ -8262,22 +8151,22 @@
         <v>163</v>
       </c>
       <c r="B168" s="5" t="n">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスの確保方策の決定</t>
+          <t>要配慮者利用施設の避難確保計画の対象施設と作成状況</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第2節・第4節
-見込量表（3種別）</t>
+          <t>計画素案 第1章第8節・第5章 基本目標5
+計画素案の記載内容の洗い出しと対比 02シート</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F168" s="5" t="inlineStr">
@@ -8286,16 +8175,16 @@
         </is>
       </c>
       <c r="G168" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H168" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I168" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+          <t>対象施設及び作成の状況を［要確認］として残し、第5章 基本目標5の主な事業に作成及び避難訓練の確認を置くにとどめ、達成目標に数値を掲げない。避難確保計画はBCPとは別の計画であり、BCPの策定率をもって作成の状況としない</t>
         </is>
       </c>
     </row>
@@ -8304,45 +8193,211 @@
         <v>164</v>
       </c>
       <c r="B169" s="5" t="n">
+        <v>176</v>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>介護サービス事業者経営情報データベースの公表結果の活用の範囲</t>
+        </is>
+      </c>
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第1章第9節5・第5章 基本目標4</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>R8.12</t>
+        </is>
+      </c>
+      <c r="G169" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" s="6" t="inlineStr">
+        <is>
+          <t>止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>公表された区分のうち当区域の事業所の規模に近いものを参考として用い、区域内の事業所の経営状況を表すものとしては用いない。計画素案には活用の方針のみを記載し、数値は掲げない</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="48" customHeight="1">
+      <c r="A170" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="B170" s="5" t="n">
+        <v>177</v>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>都道府県との協定に基づく連携への関与</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第1章第9節5・第5章 基本目標3・基本目標4</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="inlineStr">
+        <is>
+          <t>発注者・北海道</t>
+        </is>
+      </c>
+      <c r="F170" s="5" t="inlineStr">
+        <is>
+          <t>R8.12</t>
+        </is>
+      </c>
+      <c r="G170" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" s="6" t="inlineStr">
+        <is>
+          <t>止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t>計画素案には北海道及び事業者とともに活用を検討する旨のみを記載し、具体の取組及び目標は国から市町村の役割が示された後に定める</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="48" customHeight="1">
+      <c r="A171" s="5" t="n">
+        <v>166</v>
+      </c>
+      <c r="B171" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
+        </is>
+      </c>
+      <c r="D171" s="6" t="inlineStr">
+        <is>
+          <t>ケアプラン点検実施要領（案）9
+計画素案 第5章 基本目標5</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="inlineStr">
+        <is>
+          <t>北海道上川総合振興局</t>
+        </is>
+      </c>
+      <c r="F171" s="5" t="inlineStr">
+        <is>
+          <t>R9.4</t>
+        </is>
+      </c>
+      <c r="G171" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" s="6" t="inlineStr">
+        <is>
+          <t>止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I171" s="6" t="inlineStr">
+        <is>
+          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="48" customHeight="1">
+      <c r="A172" s="5" t="n">
+        <v>167</v>
+      </c>
+      <c r="B172" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>24時間対応サービスの確保方策の決定</t>
+        </is>
+      </c>
+      <c r="D172" s="6" t="inlineStr">
+        <is>
+          <t>素案 第6章第2節・第4節
+見込量表（3種別）</t>
+        </is>
+      </c>
+      <c r="E172" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F172" s="5" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G172" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I172" s="6" t="inlineStr">
+        <is>
+          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="48" customHeight="1">
+      <c r="A173" s="5" t="n">
+        <v>168</v>
+      </c>
+      <c r="B173" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="C169" s="6" t="inlineStr">
+      <c r="C173" s="6" t="inlineStr">
         <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="D169" s="6" t="inlineStr">
+      <c r="D173" s="6" t="inlineStr">
         <is>
           <t>素案 第4章第3節・第5章
 全16KPIの目標値</t>
         </is>
       </c>
-      <c r="E169" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F169" s="5" t="inlineStr">
+      <c r="E173" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F173" s="5" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="G169" s="15" t="n">
+      <c r="G173" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H169" s="6" t="inlineStr">
+      <c r="H173" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="I169" s="6" t="inlineStr">
+      <c r="I173" s="6" t="inlineStr">
         <is>
           <t>代表KPIの目標値は、令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置く</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="56" customHeight="1">
-      <c r="A170" s="13" t="inlineStr">
+    <row r="174" ht="56" customHeight="1">
+      <c r="A174" s="13" t="inlineStr">
         <is>
           <t>注1）点が9以上を至急、6以上8以下を優先、5以下を通常とみます（03シート）。
 注2）「決着しない場合の当方の扱い」が空のものは、決まらないと当方の作業が止まります。 先に扱いを決めます。
@@ -8350,301 +8405,129 @@
         </is>
       </c>
     </row>
-    <row r="171"/>
-    <row r="172" ht="20" customHeight="1">
-      <c r="A172" s="3" t="inlineStr">
+    <row r="175"/>
+    <row r="176" ht="20" customHeight="1">
+      <c r="A176" s="3" t="inlineStr">
         <is>
           <t>2　資料提供依頼（資料の提供を求めるもの）　18件</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="30" customHeight="1">
-      <c r="A173" s="4" t="inlineStr">
+    <row r="177" ht="30" customHeight="1">
+      <c r="A177" s="4" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B173" s="4" t="inlineStr">
+      <c r="B177" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C173" s="4" t="inlineStr">
+      <c r="C177" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="D173" s="4" t="inlineStr">
+      <c r="D177" s="4" t="inlineStr">
         <is>
           <t>確定する主張</t>
         </is>
       </c>
-      <c r="E173" s="4" t="inlineStr">
+      <c r="E177" s="4" t="inlineStr">
         <is>
           <t>入手先</t>
         </is>
       </c>
-      <c r="F173" s="4" t="inlineStr">
+      <c r="F177" s="4" t="inlineStr">
         <is>
           <t>希望時期</t>
         </is>
       </c>
-      <c r="G173" s="4" t="inlineStr">
+      <c r="G177" s="4" t="inlineStr">
         <is>
           <t>優先</t>
         </is>
       </c>
-      <c r="H173" s="4" t="inlineStr">
+      <c r="H177" s="4" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="I173" s="4" t="inlineStr">
+      <c r="I177" s="4" t="inlineStr">
         <is>
           <t>領域</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="40" customHeight="1">
-      <c r="A174" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B174" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C174" s="6" t="inlineStr">
-        <is>
-          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
-        </is>
-      </c>
-      <c r="D174" s="6" t="inlineStr">
-        <is>
-          <t>第9期の評価の完成</t>
-        </is>
-      </c>
-      <c r="E174" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F174" s="5" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="G174" s="16" t="inlineStr">
-        <is>
-          <t>最高</t>
-        </is>
-      </c>
-      <c r="H174" s="5" t="inlineStr">
-        <is>
-          <t>一部受領</t>
-        </is>
-      </c>
-      <c r="I174" s="5" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="40" customHeight="1">
-      <c r="A175" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B175" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C175" s="6" t="inlineStr">
-        <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
-        </is>
-      </c>
-      <c r="D175" s="6" t="inlineStr">
-        <is>
-          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
-        </is>
-      </c>
-      <c r="E175" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F175" s="5" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="G175" s="14" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H175" s="5" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="I175" s="5" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="40" customHeight="1">
-      <c r="A176" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B176" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C176" s="6" t="inlineStr">
-        <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
-        </is>
-      </c>
-      <c r="D176" s="6" t="inlineStr">
-        <is>
-          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
-        </is>
-      </c>
-      <c r="E176" s="6" t="inlineStr">
-        <is>
-          <t>3町</t>
-        </is>
-      </c>
-      <c r="F176" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G176" s="14" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H176" s="5" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I176" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="40" customHeight="1">
-      <c r="A177" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B177" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C177" s="6" t="inlineStr">
-        <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
-        </is>
-      </c>
-      <c r="D177" s="6" t="inlineStr">
-        <is>
-          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
-        </is>
-      </c>
-      <c r="E177" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F177" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G177" s="14" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H177" s="5" t="inlineStr">
-        <is>
-          <t>代替により解消</t>
-        </is>
-      </c>
-      <c r="I177" s="5" t="inlineStr">
-        <is>
-          <t>G</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B178" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
+          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
         </is>
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
+          <t>第9期の評価の完成</t>
         </is>
       </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G178" s="14" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="G178" s="16" t="inlineStr">
+        <is>
+          <t>最高</t>
         </is>
       </c>
       <c r="H178" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>一部受領</t>
         </is>
       </c>
       <c r="I178" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B179" s="5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>事業所・施設の定員と稼働の実績</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
         </is>
       </c>
       <c r="D179" s="6" t="inlineStr">
         <is>
-          <t>稼働率の低下の有無、定員減少の経緯</t>
+          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
         </is>
       </c>
       <c r="E179" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G179" s="14" t="inlineStr">
@@ -8654,40 +8537,40 @@
       </c>
       <c r="H179" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I179" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B180" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>未利用認定者の内訳とケアプランのサービス構成</t>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
         </is>
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
+          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G180" s="14" t="inlineStr">
@@ -8702,25 +8585,25 @@
       </c>
       <c r="I180" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" s="5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B181" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
         </is>
       </c>
       <c r="D181" s="6" t="inlineStr">
         <is>
-          <t>第9期の剰余額（現在は概算）</t>
+          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
@@ -8730,7 +8613,7 @@
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G181" s="14" t="inlineStr">
@@ -8740,30 +8623,30 @@
       </c>
       <c r="H181" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>代替により解消</t>
         </is>
       </c>
       <c r="I181" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" s="5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B182" s="5" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
+          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>給付費の地域内還流の議論</t>
+          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
@@ -8783,7 +8666,7 @@
       </c>
       <c r="H182" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I182" s="5" t="inlineStr">
@@ -8794,24 +8677,24 @@
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" s="5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B183" s="5" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
+          <t>事業所・施設の定員と稼働の実績</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr">
         <is>
-          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
+          <t>稼働率の低下の有無、定員減少の経緯</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
@@ -8837,19 +8720,19 @@
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" s="5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B184" s="5" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
+          <t>未利用認定者の内訳とケアプランのサービス構成</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>サービス種別ごとの見込量の様式</t>
+          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -8869,40 +8752,40 @@
       </c>
       <c r="H184" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" s="5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B185" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
+          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
         <is>
-          <t>第10期の段階設計と保険料算定</t>
+          <t>第9期の剰余額（現在は概算）</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>告示後</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G185" s="14" t="inlineStr">
@@ -8912,7 +8795,7 @@
       </c>
       <c r="H185" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I185" s="5" t="inlineStr">
@@ -8923,34 +8806,34 @@
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" s="5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B186" s="5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>小学校区と日常生活圏域の対応関係</t>
+          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
-          <t>圏域別の分析、圏域設定の見直し</t>
+          <t>給付費の地域内還流の議論</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>美瑛町・3町</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G186" s="15" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G186" s="14" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H186" s="5" t="inlineStr">
@@ -8960,40 +8843,40 @@
       </c>
       <c r="I186" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" s="5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B187" s="5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
         </is>
       </c>
       <c r="D187" s="6" t="inlineStr">
         <is>
-          <t>評価の枠組みの整理</t>
+          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G187" s="15" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G187" s="14" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H187" s="5" t="inlineStr">
@@ -9003,30 +8886,30 @@
       </c>
       <c r="I187" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" s="5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B188" s="5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD49の指標定義</t>
+          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
         <is>
-          <t>地域差指数の分解の可否</t>
+          <t>サービス種別ごとの見込量の様式</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>見える化システム・厚生労働省</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F188" s="5" t="inlineStr">
@@ -9034,85 +8917,85 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G188" s="15" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="G188" s="14" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H188" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I188" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" s="5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B189" s="5" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
         </is>
       </c>
       <c r="D189" s="6" t="inlineStr">
         <is>
-          <t>会議資料・委員会資料の記述の正確性</t>
+          <t>第10期の段階設計と保険料算定</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>国の情報</t>
         </is>
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>随時</t>
-        </is>
-      </c>
-      <c r="G189" s="15" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>告示後</t>
+        </is>
+      </c>
+      <c r="G189" s="14" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H189" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I189" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>H</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" s="5" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+          <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
-          <t>中重度・軽度の認定率の推移</t>
+          <t>圏域別の分析、圏域設定の見直し</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>見える化システム</t>
+          <t>美瑛町・3町</t>
         </is>
       </c>
       <c r="F190" s="5" t="inlineStr">
@@ -9120,67 +9003,239 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G190" s="17" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="G190" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H190" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I190" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C191" s="6" t="inlineStr">
+        <is>
+          <t>第9期の自己評価と北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="D191" s="6" t="inlineStr">
+        <is>
+          <t>評価の枠組みの整理</t>
+        </is>
+      </c>
+      <c r="E191" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G191" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H191" s="5" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I191" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="40" customHeight="1">
+      <c r="A192" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B192" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C192" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムD49の指標定義</t>
+        </is>
+      </c>
+      <c r="D192" s="6" t="inlineStr">
+        <is>
+          <t>地域差指数の分解の可否</t>
+        </is>
+      </c>
+      <c r="E192" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム・厚生労働省</t>
+        </is>
+      </c>
+      <c r="F192" s="5" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G192" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H192" s="5" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I192" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="40" customHeight="1">
+      <c r="A193" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B193" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C193" s="6" t="inlineStr">
+        <is>
+          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+        </is>
+      </c>
+      <c r="D193" s="6" t="inlineStr">
+        <is>
+          <t>会議資料・委員会資料の記述の正確性</t>
+        </is>
+      </c>
+      <c r="E193" s="6" t="inlineStr">
+        <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="F193" s="5" t="inlineStr">
+        <is>
+          <t>随時</t>
+        </is>
+      </c>
+      <c r="G193" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H193" s="5" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+      <c r="I193" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="40" customHeight="1">
+      <c r="A194" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B194" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C194" s="6" t="inlineStr">
+        <is>
+          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="inlineStr">
+        <is>
+          <t>中重度・軽度の認定率の推移</t>
+        </is>
+      </c>
+      <c r="E194" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム</t>
+        </is>
+      </c>
+      <c r="F194" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G194" s="17" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H194" s="5" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I194" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="40" customHeight="1">
+      <c r="A195" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B191" s="5" t="n">
+      <c r="B195" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C191" s="6" t="inlineStr">
+      <c r="C195" s="6" t="inlineStr">
         <is>
           <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
-      <c r="D191" s="6" t="inlineStr">
+      <c r="D195" s="6" t="inlineStr">
         <is>
           <t>世帯構成の現状</t>
         </is>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="E195" s="6" t="inlineStr">
         <is>
           <t>総務省・3町</t>
         </is>
       </c>
-      <c r="F191" s="5" t="inlineStr">
+      <c r="F195" s="5" t="inlineStr">
         <is>
           <t>公表後</t>
         </is>
       </c>
-      <c r="G191" s="17" t="inlineStr">
+      <c r="G195" s="17" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H191" s="5" t="inlineStr">
+      <c r="H195" s="5" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="I191" s="5" t="inlineStr">
+      <c r="I195" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="28" customHeight="1">
-      <c r="A192" s="13" t="inlineStr">
+    <row r="196" ht="28" customHeight="1">
+      <c r="A196" s="13" t="inlineStr">
         <is>
           <t>注）03シートの確認事項が「決定」を求めるものであるのに対し、本表は「資料の提供」を求めるものです。資料が届かない場合の扱いは04シートの区分で示しています。</t>
         </is>
@@ -9188,11 +9243,11 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A172:I172"/>
+    <mergeCell ref="A196:I196"/>
+    <mergeCell ref="A174:I174"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A170:I170"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A192:I192"/>
+    <mergeCell ref="A176:I176"/>
     <mergeCell ref="A4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9225,7 +9280,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02シートの点は次の規則だけで付けています。規則を変えれば02シートの並びも変わります。基準日 令和8年10月7日。</t>
+          <t>02シートの点は次の規則だけで付けています。規則を変えれば02シートの並びも変わります。基準日 令和8年10月14日。</t>
         </is>
       </c>
     </row>
@@ -9394,7 +9449,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>95件</t>
+          <t>99件</t>
         </is>
       </c>
     </row>
@@ -9486,7 +9541,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>8件</t>
+          <t>9件</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9697,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>161件</t>
+          <t>165件</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -9801,7 +9856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9821,7 +9876,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>決定・資料の受領を待たずに当方の作業だけで進められるものです。基準日 令和8年10月7日。</t>
+          <t>決定・資料の受領を待たずに当方の作業だけで進められるものです。基準日 令和8年10月14日。</t>
         </is>
       </c>
     </row>
@@ -9829,7 +9884,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　当方の作業だけで進められるもの　0件</t>
+          <t>1　当方の作業だけで進められるもの　4件</t>
         </is>
       </c>
     </row>
@@ -9856,15 +9911,108 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>ありません。据え置きのうち当方の側で確定できるもの（区分A）は残っておらず、既定値を置けている未決の確認事項はすべて仮置きのとおり処理しています（注4）。ご決定をお待ちしている間に当方の側で進められる作業はここにはありません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="76" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>既定値で進める</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>介護保険法第117条ほか関係法令の条文のご提供</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>条番号のみを記載し項番号及び号番号は記載しない。記載事項の点検は条文の番号ではなく記載事項の内容を単位として行い、条文を確認できていない箇所は［要確認］として残す</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.181（点3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>既定値で進める</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>構成3町の高齢者福祉計画と市町村老人福祉計画の関係</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.178（点1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>既定値で進める</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>成年後見制度の利用の促進に関する施策についての基本的な計画の策定状況</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>同計画は構成3町が定めるものとして計画素案に記載し、本計画は介護保険法第117条第3項による権利擁護の施策（第5章 基本目標1）をもって接続する。中核機関の整備の状況は［要確認］として残す</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.179（点1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>既定値で進める</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>要配慮者利用施設の避難確保計画の対象施設と作成状況</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>対象施設及び作成の状況を［要確認］として残し、第5章 基本目標5の主な事業に作成及び避難訓練の確認を置くにとどめ、達成目標に数値を掲げない。避難確保計画はBCPとは別の計画であり、BCPの策定率をもって作成の状況としない</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.180（点1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="76" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>注1）「据え置き（区分A）」は、資料の受領を待たずに当方の側で確定できるものです。
 注2）「既定値で進める」は、決着しない場合の扱いを置けているため決定を待たずに作業を進められるものです。決定を受けた時点で見直します。
@@ -9873,30 +10021,29 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="11"/>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>2　先に扱いを決めるもの（既定値を置けていない）　0件</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>ありません。未決の確認事項の全件に扱いを置けています。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A10:E10"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9908,7 +10055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9921,7 +10068,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>翌日（令和8年10月8日）の作業順位</t>
+          <t>翌日（令和8年10月15日）の作業順位</t>
         </is>
       </c>
     </row>
@@ -9964,24 +10111,24 @@
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>催促・照会</t>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>進める</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の量の見込みを算定してよいか（発注者）</t>
+          <t>介護保険法第117条ほか関係法令の条文のご提供</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>点8。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／月額への効き 最大7円（令和7年度の総合事業の事業費）／法定記載事項 法第117条に直結</t>
+          <t>条番号のみを記載し項番号及び号番号は記載しない。記載事項の点検は条文の番号ではなく記載事項の内容を単位として行い、条文を確認できていない箇所は［要確認］として残す</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.112</t>
+          <t>確認事項No.181（点3）</t>
         </is>
       </c>
     </row>
@@ -9989,24 +10136,24 @@
       <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>催促・照会</t>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>進める</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実績のご提供（発注者）</t>
+          <t>構成3町の高齢者福祉計画と市町村老人福祉計画の関係</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>点7。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／法定記載事項 法第117条に直結</t>
+          <t>構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.150</t>
+          <t>確認事項No.178（点1）</t>
         </is>
       </c>
     </row>
@@ -10014,29 +10161,129 @@
       <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>進める</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>成年後見制度の利用の促進に関する施策についての基本的な計画の策定状況</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>同計画は構成3町が定めるものとして計画素案に記載し、本計画は介護保険法第117条第3項による権利擁護の施策（第5章 基本目標1）をもって接続する。中核機関の整備の状況は［要確認］として残す</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.179（点1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>進める</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>要配慮者利用施設の避難確保計画の対象施設と作成状況</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>対象施設及び作成の状況を［要確認］として残し、第5章 基本目標5の主な事業に作成及び避難訓練の確認を置くにとどめ、達成目標に数値を掲げない。避難確保計画はBCPとは別の計画であり、BCPの策定率をもって作成の状況としない</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.180（点1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>催促・照会</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業の量の見込みを算定してよいか（発注者）</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>点8。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／月額への効き 最大7円（令和7年度の総合事業の事業費）／法定記載事項 法第117条に直結</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.112</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>催促・照会</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>認知症総合支援事業の実績のご提供（発注者）</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>点7。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／法定記載事項 法第117条に直結</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.150</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>催促・照会</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案（発注者・北海道）</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>点6。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／月額への効き 最大47円（第7期給付適正化計画の目標のご判断）</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>確認事項No.93</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="62" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+    <row r="12" ht="62" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>注1）「進める」は決定を待たずに着手できるもの、「催促・照会」は相手のある作業です。相手のある作業は午前のうちに出します（返事に日数がかかるため）。
 注2）04シートの作業継続可能なものは上位8件まで、催促・照会は優先以上の上位5件までを掲げています。残りは02・04シートを見ます。
@@ -10047,8 +10294,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10112,7 +10359,7 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="20" t="n">
+      <c r="A5" s="21" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -10122,22 +10369,22 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>No.1〜No.177 を数える</t>
+          <t>No.1〜No.181 を数える</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>177件／欠番 なし／重複 なし</t>
-        </is>
-      </c>
-      <c r="E5" s="21" t="inlineStr">
+          <t>181件／欠番 なし／重複 なし</t>
+        </is>
+      </c>
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="21" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -10152,17 +10399,17 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>確認事項164件／資料提供依頼18件</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
+          <t>確認事項168件／資料提供依頼18件</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="20" t="n">
+      <c r="A7" s="21" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -10177,17 +10424,17 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>164件／合わない なし</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
+          <t>168件／合わない なし</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="21" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -10205,14 +10452,14 @@
           <t>降順 適合</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="20" t="n">
+      <c r="A9" s="21" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -10230,14 +10477,14 @@
           <t>内訳5種／規則6種／載っていない なし</t>
         </is>
       </c>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="21" t="n">
         <v>5.5</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -10255,14 +10502,14 @@
           <t>7件を拾った（最大327円）／上限超え なし</t>
         </is>
       </c>
-      <c r="E10" s="21" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="20" t="n">
+      <c r="A11" s="21" t="n">
         <v>6</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -10280,14 +10527,14 @@
           <t>4＋0＋15＋4＝23／据え置き23件</t>
         </is>
       </c>
-      <c r="E11" s="21" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="20" t="n">
+      <c r="A12" s="21" t="n">
         <v>7</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -10305,14 +10552,14 @@
           <t>最小0.12・最大0.94・全体67％</t>
         </is>
       </c>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="20" t="n">
+      <c r="A13" s="21" t="n">
         <v>8</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -10327,17 +10574,17 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>記録 令和8年10月7日／本表 令和8年10月7日</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
+          <t>記録 令和8年10月14日／本表 令和8年10月14日</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="20" t="n">
+      <c r="A14" s="21" t="n">
         <v>9</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -10355,14 +10602,14 @@
           <t>記録9件（最新 令和8年9月28日）</t>
         </is>
       </c>
-      <c r="E14" s="21" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="20" t="n">
+      <c r="A15" s="21" t="n">
         <v>10</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -10377,17 +10624,17 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>3件（進める0・催促3）</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
+          <t>7件（進める4・催促3）</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="20" t="n">
+      <c r="A16" s="21" t="n">
         <v>11</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -10402,17 +10649,17 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>0件（区分A 0・既定値 0）／据え置きの区分A 0件・既定値があり未処理 0件</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
+          <t>4件（区分A 0・既定値 4）／据え置きの区分A 0件・既定値があり未処理 4件</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="20" t="n">
+      <c r="A17" s="21" t="n">
         <v>12</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -10430,14 +10677,14 @@
           <t>0件</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="20" t="n">
+      <c r="A18" s="21" t="n">
         <v>13</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -10455,14 +10702,14 @@
           <t>0件</t>
         </is>
       </c>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="20" t="n">
+      <c r="A19" s="21" t="n">
         <v>14</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -10480,14 +10727,14 @@
           <t>残り0件</t>
         </is>
       </c>
-      <c r="E19" s="21" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="20" t="n">
+      <c r="A20" s="21" t="n">
         <v>15</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -10505,7 +10752,7 @@
           <t>台帳にあり／古い記述 なし</t>
         </is>
       </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -10524,7 +10771,7 @@
           <t>適合16件・不適合0件</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>適合</t>
         </is>

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -749,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1212,27 +1212,53 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>基準日のコミットはありません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="13" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="4" t="inlineStr"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>コミット</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>86efc03</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>記載事項の網羅性を再整理し、関係法令の対比と素案への反映6件を加えた</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr"/>
+      <c r="E23" s="6" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A21:F21"/>
   </mergeCells>
@@ -1246,7 +1272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I196"/>
+  <dimension ref="A1:I199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1278,7 +1304,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　確認事項（決定を求めるもの）　168件</t>
+          <t>1　確認事項（決定を求めるもの）　171件</t>
         </is>
       </c>
     </row>
@@ -8275,27 +8301,27 @@
         <v>166</v>
       </c>
       <c r="B171" s="5" t="n">
-        <v>74</v>
+        <v>182</v>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
+          <t>介護給付費分科会の資料（原本）のご提供</t>
         </is>
       </c>
       <c r="D171" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）9
-計画素案 第5章 基本目標5</t>
+          <t>計画素案 第1章第9節6・第6章第2節・第6章第6節2・第6章第7節
+介護給付費分科会の論点整理の受領点検</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>北海道上川総合振興局</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
-          <t>R9.4</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="G171" s="15" t="n">
@@ -8308,7 +8334,7 @@
       </c>
       <c r="I171" s="6" t="inlineStr">
         <is>
-          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
+          <t>計画素案には国において検討されている事項があることまでを記載し、単位数・要件・施行時期を書かない。原本を確認できていないことを［要確認］として残し、改定率及び単価は令和7年度の実績で固定したまま概算する</t>
         </is>
       </c>
     </row>
@@ -8317,17 +8343,17 @@
         <v>167</v>
       </c>
       <c r="B172" s="5" t="n">
-        <v>24</v>
+        <v>183</v>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスの確保方策の決定</t>
+          <t>夜間対応型訪問介護の定期巡回・随時対応型への移行の扱い</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第2節・第4節
-見込量表（3種別）</t>
+          <t>計画素案 第6章第2節（2）・第6章第4節1
+サービス見込量の算定・見える化システムへの入力値</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -8337,20 +8363,20 @@
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="G172" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H172" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I172" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+          <t>現行の区分のまま夜間対応型訪問介護を実績なし（0）として立て、移行が検討されていることを計画素案の注に記載する。省令等が確定した時点で区分を組み替える</t>
         </is>
       </c>
     </row>
@@ -8359,45 +8385,171 @@
         <v>168</v>
       </c>
       <c r="B173" s="5" t="n">
+        <v>184</v>
+      </c>
+      <c r="C173" s="6" t="inlineStr">
+        <is>
+          <t>短期入所生活介護の季節利用及び長期利用の実態</t>
+        </is>
+      </c>
+      <c r="D173" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第6章第2節 注1-1・第6章第4節
+サービス見込量の算定（季節補正）</t>
+        </is>
+      </c>
+      <c r="E173" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町・事業者</t>
+        </is>
+      </c>
+      <c r="F173" s="5" t="inlineStr">
+        <is>
+          <t>R8.12</t>
+        </is>
+      </c>
+      <c r="G173" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H173" s="6" t="inlineStr">
+        <is>
+          <t>止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>令和7年度（12か月の完結年度）の実績により短期入所生活介護の見込量を算定し、季節補正を行わない（基準年度が完結年度であるため年度換算係数は1.0000となり効きは0円である）。季節利用の例外が示された時点で利用日数の置き方を確かめる</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="48" customHeight="1">
+      <c r="A174" s="5" t="n">
+        <v>169</v>
+      </c>
+      <c r="B174" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="C174" s="6" t="inlineStr">
+        <is>
+          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
+        </is>
+      </c>
+      <c r="D174" s="6" t="inlineStr">
+        <is>
+          <t>ケアプラン点検実施要領（案）9
+計画素案 第5章 基本目標5</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="inlineStr">
+        <is>
+          <t>北海道上川総合振興局</t>
+        </is>
+      </c>
+      <c r="F174" s="5" t="inlineStr">
+        <is>
+          <t>R9.4</t>
+        </is>
+      </c>
+      <c r="G174" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H174" s="6" t="inlineStr">
+        <is>
+          <t>止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I174" s="6" t="inlineStr">
+        <is>
+          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="48" customHeight="1">
+      <c r="A175" s="5" t="n">
+        <v>170</v>
+      </c>
+      <c r="B175" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>24時間対応サービスの確保方策の決定</t>
+        </is>
+      </c>
+      <c r="D175" s="6" t="inlineStr">
+        <is>
+          <t>素案 第6章第2節・第4節
+見込量表（3種別）</t>
+        </is>
+      </c>
+      <c r="E175" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F175" s="5" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G175" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="48" customHeight="1">
+      <c r="A176" s="5" t="n">
+        <v>171</v>
+      </c>
+      <c r="B176" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="C173" s="6" t="inlineStr">
+      <c r="C176" s="6" t="inlineStr">
         <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="D173" s="6" t="inlineStr">
+      <c r="D176" s="6" t="inlineStr">
         <is>
           <t>素案 第4章第3節・第5章
 全16KPIの目標値</t>
         </is>
       </c>
-      <c r="E173" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F173" s="5" t="inlineStr">
+      <c r="E176" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F176" s="5" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="G173" s="15" t="n">
+      <c r="G176" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H173" s="6" t="inlineStr">
+      <c r="H176" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="I173" s="6" t="inlineStr">
+      <c r="I176" s="6" t="inlineStr">
         <is>
           <t>代表KPIの目標値は、令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置く</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="56" customHeight="1">
-      <c r="A174" s="13" t="inlineStr">
+    <row r="177" ht="56" customHeight="1">
+      <c r="A177" s="13" t="inlineStr">
         <is>
           <t>注1）点が9以上を至急、6以上8以下を優先、5以下を通常とみます（03シート）。
 注2）「決着しない場合の当方の扱い」が空のものは、決まらないと当方の作業が止まります。 先に扱いを決めます。
@@ -8405,205 +8557,76 @@
         </is>
       </c>
     </row>
-    <row r="175"/>
-    <row r="176" ht="20" customHeight="1">
-      <c r="A176" s="3" t="inlineStr">
+    <row r="178"/>
+    <row r="179" ht="20" customHeight="1">
+      <c r="A179" s="3" t="inlineStr">
         <is>
           <t>2　資料提供依頼（資料の提供を求めるもの）　18件</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="30" customHeight="1">
-      <c r="A177" s="4" t="inlineStr">
+    <row r="180" ht="30" customHeight="1">
+      <c r="A180" s="4" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B177" s="4" t="inlineStr">
+      <c r="B180" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C177" s="4" t="inlineStr">
+      <c r="C180" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="D177" s="4" t="inlineStr">
+      <c r="D180" s="4" t="inlineStr">
         <is>
           <t>確定する主張</t>
         </is>
       </c>
-      <c r="E177" s="4" t="inlineStr">
+      <c r="E180" s="4" t="inlineStr">
         <is>
           <t>入手先</t>
         </is>
       </c>
-      <c r="F177" s="4" t="inlineStr">
+      <c r="F180" s="4" t="inlineStr">
         <is>
           <t>希望時期</t>
         </is>
       </c>
-      <c r="G177" s="4" t="inlineStr">
+      <c r="G180" s="4" t="inlineStr">
         <is>
           <t>優先</t>
         </is>
       </c>
-      <c r="H177" s="4" t="inlineStr">
+      <c r="H180" s="4" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="I177" s="4" t="inlineStr">
+      <c r="I180" s="4" t="inlineStr">
         <is>
           <t>領域</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="40" customHeight="1">
-      <c r="A178" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B178" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C178" s="6" t="inlineStr">
-        <is>
-          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
-        </is>
-      </c>
-      <c r="D178" s="6" t="inlineStr">
-        <is>
-          <t>第9期の評価の完成</t>
-        </is>
-      </c>
-      <c r="E178" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F178" s="5" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="G178" s="16" t="inlineStr">
-        <is>
-          <t>最高</t>
-        </is>
-      </c>
-      <c r="H178" s="5" t="inlineStr">
-        <is>
-          <t>一部受領</t>
-        </is>
-      </c>
-      <c r="I178" s="5" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="40" customHeight="1">
-      <c r="A179" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B179" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C179" s="6" t="inlineStr">
-        <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
-        </is>
-      </c>
-      <c r="D179" s="6" t="inlineStr">
-        <is>
-          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
-        </is>
-      </c>
-      <c r="E179" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F179" s="5" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="G179" s="14" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H179" s="5" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="I179" s="5" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="40" customHeight="1">
-      <c r="A180" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B180" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C180" s="6" t="inlineStr">
-        <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
-        </is>
-      </c>
-      <c r="D180" s="6" t="inlineStr">
-        <is>
-          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
-        </is>
-      </c>
-      <c r="E180" s="6" t="inlineStr">
-        <is>
-          <t>3町</t>
-        </is>
-      </c>
-      <c r="F180" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G180" s="14" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H180" s="5" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I180" s="5" t="inlineStr">
-        <is>
-          <t>A</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B181" s="5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
+          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
         </is>
       </c>
       <c r="D181" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
+          <t>第9期の評価の完成</t>
         </is>
       </c>
       <c r="E181" s="6" t="inlineStr">
@@ -8613,17 +8636,17 @@
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G181" s="14" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="G181" s="16" t="inlineStr">
+        <is>
+          <t>最高</t>
         </is>
       </c>
       <c r="H181" s="5" t="inlineStr">
         <is>
-          <t>代替により解消</t>
+          <t>一部受領</t>
         </is>
       </c>
       <c r="I181" s="5" t="inlineStr">
@@ -8634,29 +8657,29 @@
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B182" s="5" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
         </is>
       </c>
       <c r="D182" s="6" t="inlineStr">
         <is>
-          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
+          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
         </is>
       </c>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G182" s="14" t="inlineStr">
@@ -8671,35 +8694,35 @@
       </c>
       <c r="I182" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B183" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>事業所・施設の定員と稼働の実績</t>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr">
         <is>
-          <t>稼働率の低下の有無、定員減少の経緯</t>
+          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G183" s="14" t="inlineStr">
@@ -8714,25 +8737,25 @@
       </c>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B184" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>未利用認定者の内訳とケアプランのサービス構成</t>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
+          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -8742,7 +8765,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G184" s="14" t="inlineStr">
@@ -8752,35 +8775,35 @@
       </c>
       <c r="H184" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>代替により解消</t>
         </is>
       </c>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B185" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
+          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
         <is>
-          <t>第9期の剰余額（現在は概算）</t>
+          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr">
@@ -8795,35 +8818,35 @@
       </c>
       <c r="H185" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I185" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" s="5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B186" s="5" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
+          <t>事業所・施設の定員と稼働の実績</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
-          <t>給付費の地域内還流の議論</t>
+          <t>稼働率の低下の有無、定員減少の経緯</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F186" s="5" t="inlineStr">
@@ -8843,30 +8866,30 @@
       </c>
       <c r="I186" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B187" s="5" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
+          <t>未利用認定者の内訳とケアプランのサービス構成</t>
         </is>
       </c>
       <c r="D187" s="6" t="inlineStr">
         <is>
-          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
+          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F187" s="5" t="inlineStr">
@@ -8886,25 +8909,25 @@
       </c>
       <c r="I187" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" s="5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B188" s="5" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
+          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
         <is>
-          <t>サービス種別ごとの見込量の様式</t>
+          <t>第9期の剰余額（現在は概算）</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
@@ -8924,40 +8947,40 @@
       </c>
       <c r="H188" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I188" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>H</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" s="5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B189" s="5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
+          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
         </is>
       </c>
       <c r="D189" s="6" t="inlineStr">
         <is>
-          <t>第10期の段階設計と保険料算定</t>
+          <t>給付費の地域内還流の議論</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
-          <t>告示後</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G189" s="14" t="inlineStr">
@@ -8967,45 +8990,45 @@
       </c>
       <c r="H189" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I189" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" s="5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>小学校区と日常生活圏域の対応関係</t>
+          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
-          <t>圏域別の分析、圏域設定の見直し</t>
+          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>美瑛町・3町</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F190" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G190" s="15" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G190" s="14" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H190" s="5" t="inlineStr">
@@ -9015,25 +9038,25 @@
       </c>
       <c r="I190" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" s="5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B191" s="5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
         </is>
       </c>
       <c r="D191" s="6" t="inlineStr">
         <is>
-          <t>評価の枠組みの整理</t>
+          <t>サービス種別ごとの見込量の様式</t>
         </is>
       </c>
       <c r="E191" s="6" t="inlineStr">
@@ -9043,55 +9066,55 @@
       </c>
       <c r="F191" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G191" s="15" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G191" s="14" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H191" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I191" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B192" s="5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C192" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD49の指標定義</t>
+          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>地域差指数の分解の可否</t>
+          <t>第10期の段階設計と保険料算定</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>見える化システム・厚生労働省</t>
+          <t>国の情報</t>
         </is>
       </c>
       <c r="F192" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G192" s="15" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>告示後</t>
+        </is>
+      </c>
+      <c r="G192" s="14" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H192" s="5" t="inlineStr">
@@ -9101,35 +9124,35 @@
       </c>
       <c r="I192" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" s="5" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B193" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+          <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
       <c r="D193" s="6" t="inlineStr">
         <is>
-          <t>会議資料・委員会資料の記述の正確性</t>
+          <t>圏域別の分析、圏域設定の見直し</t>
         </is>
       </c>
       <c r="E193" s="6" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>美瑛町・3町</t>
         </is>
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
-          <t>随時</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G193" s="15" t="inlineStr">
@@ -9139,35 +9162,35 @@
       </c>
       <c r="H193" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I193" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" s="5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B194" s="5" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
-          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>中重度・軽度の認定率の推移</t>
+          <t>評価の枠組みの整理</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>見える化システム</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F194" s="5" t="inlineStr">
@@ -9175,67 +9198,196 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G194" s="17" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="G194" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I194" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B195" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C195" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムD49の指標定義</t>
+        </is>
+      </c>
+      <c r="D195" s="6" t="inlineStr">
+        <is>
+          <t>地域差指数の分解の可否</t>
+        </is>
+      </c>
+      <c r="E195" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム・厚生労働省</t>
+        </is>
+      </c>
+      <c r="F195" s="5" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G195" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H195" s="5" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I195" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="40" customHeight="1">
+      <c r="A196" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B196" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C196" s="6" t="inlineStr">
+        <is>
+          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+        </is>
+      </c>
+      <c r="D196" s="6" t="inlineStr">
+        <is>
+          <t>会議資料・委員会資料の記述の正確性</t>
+        </is>
+      </c>
+      <c r="E196" s="6" t="inlineStr">
+        <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="F196" s="5" t="inlineStr">
+        <is>
+          <t>随時</t>
+        </is>
+      </c>
+      <c r="G196" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H196" s="5" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+      <c r="I196" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="40" customHeight="1">
+      <c r="A197" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B197" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C197" s="6" t="inlineStr">
+        <is>
+          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+        </is>
+      </c>
+      <c r="D197" s="6" t="inlineStr">
+        <is>
+          <t>中重度・軽度の認定率の推移</t>
+        </is>
+      </c>
+      <c r="E197" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム</t>
+        </is>
+      </c>
+      <c r="F197" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G197" s="17" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H197" s="5" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I197" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="40" customHeight="1">
+      <c r="A198" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B195" s="5" t="n">
+      <c r="B198" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C195" s="6" t="inlineStr">
+      <c r="C198" s="6" t="inlineStr">
         <is>
           <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
-      <c r="D195" s="6" t="inlineStr">
+      <c r="D198" s="6" t="inlineStr">
         <is>
           <t>世帯構成の現状</t>
         </is>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="E198" s="6" t="inlineStr">
         <is>
           <t>総務省・3町</t>
         </is>
       </c>
-      <c r="F195" s="5" t="inlineStr">
+      <c r="F198" s="5" t="inlineStr">
         <is>
           <t>公表後</t>
         </is>
       </c>
-      <c r="G195" s="17" t="inlineStr">
+      <c r="G198" s="17" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H195" s="5" t="inlineStr">
+      <c r="H198" s="5" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="I195" s="5" t="inlineStr">
+      <c r="I198" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="28" customHeight="1">
-      <c r="A196" s="13" t="inlineStr">
+    <row r="199" ht="28" customHeight="1">
+      <c r="A199" s="13" t="inlineStr">
         <is>
           <t>注）03シートの確認事項が「決定」を求めるものであるのに対し、本表は「資料の提供」を求めるものです。資料が届かない場合の扱いは04シートの区分で示しています。</t>
         </is>
@@ -9243,11 +9395,11 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A196:I196"/>
-    <mergeCell ref="A174:I174"/>
+    <mergeCell ref="A179:I179"/>
+    <mergeCell ref="A199:I199"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A177:I177"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A176:I176"/>
     <mergeCell ref="A4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9449,7 +9601,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>99件</t>
+          <t>102件</t>
         </is>
       </c>
     </row>
@@ -9697,7 +9849,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>165件</t>
+          <t>168件</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -9856,7 +10008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -9884,7 +10036,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　当方の作業だけで進められるもの　4件</t>
+          <t>1　当方の作業だけで進められるもの　7件</t>
         </is>
       </c>
     </row>
@@ -10011,8 +10163,83 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="76" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>既定値で進める</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>介護給付費分科会の資料（原本）のご提供</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>計画素案には国において検討されている事項があることまでを記載し、単位数・要件・施行時期を書かない。原本を確認できていないことを［要確認］として残し、改定率及び単価は令和7年度の実績で固定したまま概算する</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.182（点1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>既定値で進める</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>夜間対応型訪問介護の定期巡回・随時対応型への移行の扱い</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>現行の区分のまま夜間対応型訪問介護を実績なし（0）として立て、移行が検討されていることを計画素案の注に記載する。省令等が確定した時点で区分を組み替える</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.183（点1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>既定値で進める</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>短期入所生活介護の季節利用及び長期利用の実態</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>令和7年度（12か月の完結年度）の実績により短期入所生活介護の見込量を算定し、季節補正を行わない（基準年度が完結年度であるため年度換算係数は1.0000となり効きは0円である）。季節利用の例外が示された時点で利用日数の置き方を確かめる</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.184（点1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="76" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>注1）「据え置き（区分A）」は、資料の受領を待たずに当方の側で確定できるものです。
 注2）「既定値で進める」は、決着しない場合の扱いを置けているため決定を待たずに作業を進められるものです。決定を受けた時点で見直します。
@@ -10021,16 +10248,16 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="14"/>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>2　先に扱いを決めるもの（既定値を置けていない）　0件</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>ありません。未決の確認事項の全件に扱いを置けています。</t>
         </is>
@@ -10039,9 +10266,9 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A15:E15"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A13:E13"/>
   </mergeCells>
@@ -10055,7 +10282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -10211,24 +10438,24 @@
       <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>催促・照会</t>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>進める</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の量の見込みを算定してよいか（発注者）</t>
+          <t>介護給付費分科会の資料（原本）のご提供</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>点8。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／月額への効き 最大7円（令和7年度の総合事業の事業費）／法定記載事項 法第117条に直結</t>
+          <t>計画素案には国において検討されている事項があることまでを記載し、単位数・要件・施行時期を書かない。原本を確認できていないことを［要確認］として残し、改定率及び単価は令和7年度の実績で固定したまま概算する</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.112</t>
+          <t>確認事項No.182（点1）</t>
         </is>
       </c>
     </row>
@@ -10236,24 +10463,24 @@
       <c r="A10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>催促・照会</t>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>進める</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実績のご提供（発注者）</t>
+          <t>夜間対応型訪問介護の定期巡回・随時対応型への移行の扱い</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>点7。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／法定記載事項 法第117条に直結</t>
+          <t>現行の区分のまま夜間対応型訪問介護を実績なし（0）として立て、移行が検討されていることを計画素案の注に記載する。省令等が確定した時点で区分を組み替える</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.150</t>
+          <t>確認事項No.183（点1）</t>
         </is>
       </c>
     </row>
@@ -10261,29 +10488,104 @@
       <c r="A11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>進める</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>短期入所生活介護の季節利用及び長期利用の実態</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>令和7年度（12か月の完結年度）の実績により短期入所生活介護の見込量を算定し、季節補正を行わない（基準年度が完結年度であるため年度換算係数は1.0000となり効きは0円である）。季節利用の例外が示された時点で利用日数の置き方を確かめる</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.184（点1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>催促・照会</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業の量の見込みを算定してよいか（発注者）</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>点8。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／月額への効き 最大7円（令和7年度の総合事業の事業費）／法定記載事項 法第117条に直結</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.112</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>催促・照会</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>認知症総合支援事業の実績のご提供（発注者）</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>点7。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／法定記載事項 法第117条に直結</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.150</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>催促・照会</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案（発注者・北海道）</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>点6。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／月額への効き 最大47円（第7期給付適正化計画の目標のご判断）</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>確認事項No.93</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="62" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+    <row r="15" ht="62" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>注1）「進める」は決定を待たずに着手できるもの、「催促・照会」は相手のある作業です。相手のある作業は午前のうちに出します（返事に日数がかかるため）。
 注2）04シートの作業継続可能なものは上位8件まで、催促・照会は優先以上の上位5件までを掲げています。残りは02・04シートを見ます。
@@ -10294,7 +10596,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A15:E15"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10369,12 +10671,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>No.1〜No.181 を数える</t>
+          <t>No.1〜No.184 を数える</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>181件／欠番 なし／重複 なし</t>
+          <t>184件／欠番 なし／重複 なし</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -10399,7 +10701,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>確認事項168件／資料提供依頼18件</t>
+          <t>確認事項171件／資料提供依頼18件</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -10424,7 +10726,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>168件／合わない なし</t>
+          <t>171件／合わない なし</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -10624,7 +10926,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>7件（進める4・催促3）</t>
+          <t>10件（進める7・催促3）</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -10649,7 +10951,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>4件（区分A 0・既定値 4）／据え置きの区分A 0件・既定値があり未処理 4件</t>
+          <t>7件（区分A 0・既定値 7）／据え置きの区分A 0件・既定値があり未処理 7件</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -749,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1234,20 +1234,38 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>86efc03</t>
+          <t>ba9572f</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>記載事項の網羅性を再整理し、関係法令の対比と素案への反映6件を加えた</t>
+          <t>介護給付費分科会の論点31件を受領点検し、軸C'として対比に加えた</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
       <c r="E23" s="6" t="inlineStr"/>
       <c r="F23" s="6" t="inlineStr"/>
     </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>86efc03</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>記載事項の網羅性を再整理し、関係法令の対比と素案への反映6件を加えた</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
@@ -1255,12 +1273,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8311,7 +8329,8 @@
       <c r="D171" s="6" t="inlineStr">
         <is>
           <t>計画素案 第1章第9節6・第6章第2節・第6章第6節2・第6章第7節
-介護給付費分科会の論点整理の受領点検</t>
+介護給付費分科会の論点整理の受領点検
+介護給付費分科会資料（原典）の受領点検</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -749,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>ba9572f</t>
+          <t>05a1acb</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>介護給付費分科会の論点31件を受領点検し、軸C'として対比に加えた</t>
+          <t>介護給付費分科会の資料（原典）の受領点検と計画素案への反映</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
@@ -1252,20 +1252,38 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>86efc03</t>
+          <t>ba9572f</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>記載事項の網羅性を再整理し、関係法令の対比と素案への反映6件を加えた</t>
+          <t>介護給付費分科会の論点31件を受領点検し、軸C'として対比に加えた</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
       <c r="E24" s="6" t="inlineStr"/>
       <c r="F24" s="6" t="inlineStr"/>
     </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>86efc03</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>記載事項の網羅性を再整理し、関係法令の対比と素案への反映6件を加えた</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
@@ -1277,8 +1295,8 @@
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -583,7 +583,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>毎日の終わりにWBSの現況・ペンディングの優先順位・当方の作業だけで進められるもの・翌日の作業順位を1枚にしたものです。基準日 令和8年10月14日。内部保管。</t>
+          <t>毎日の終わりにWBSの現況・ペンディングの優先順位・当方の作業だけで進められるもの・翌日の作業順位を1枚にしたものです。基準日 令和8年10月15日。内部保管。</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -770,7 +770,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）ごとの進捗率と、前に報告した時点からの動きです。基準日 令和8年10月14日。</t>
+          <t>仕様書４（1）〜（12）ごとの進捗率と、前に報告した時点からの動きです。基準日 令和8年10月15日。</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>注1）進捗の記録の基準日は 令和8年10月14日 です。本表の基準日（令和8年10月14日）と違うときは、進捗の更新がまだ行われていません。
+          <t>注1）進捗の記録の基準日は 令和8年10月15日 です。本表の基準日（令和8年10月15日）と違うときは、進捗の更新がまだ行われていません。
 注2）進捗率を更新したら、更新前の値を記録へ移します。移さないと、過去の時点を記す資料（月次の報告・議事録）の数値が書き換わります。</t>
         </is>
       </c>
@@ -1212,90 +1212,28 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="4" t="inlineStr"/>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>コミット</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>05a1acb</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>介護給付費分科会の資料（原典）の受領点検と計画素案への反映</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr"/>
-      <c r="E23" s="6" t="inlineStr"/>
-      <c r="F23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>ba9572f</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>介護給付費分科会の論点31件を受領点検し、軸C'として対比に加えた</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr"/>
-      <c r="E24" s="6" t="inlineStr"/>
-      <c r="F24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>86efc03</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>記載事項の網羅性を再整理し、関係法令の対比と素案への反映6件を加えた</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>基準日のコミットはありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1308,7 +1246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I199"/>
+  <dimension ref="A1:I201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1332,7 +1270,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>完了していない確認事項と資料提供依頼を、影響度の点の高い順に並べたものです。点の付け方は03シートに全て書いています。基準日 令和8年10月14日。</t>
+          <t>完了していない確認事項と資料提供依頼を、影響度の点の高い順に並べたものです。点の付け方は03シートに全て書いています。基準日 令和8年10月15日。</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1278,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　確認事項（決定を求めるもの）　171件</t>
+          <t>1　確認事項（決定を求めるもの）　173件</t>
         </is>
       </c>
     </row>
@@ -4010,7 +3948,7 @@
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>条番号のみを記載し項番号及び号番号は記載しない。記載事項の点検は条文の番号ではなく記載事項の内容を単位として行い、条文を確認できていない箇所は［要確認］として残す</t>
+          <t>条番号のみを記載し項番号及び号番号は記載しない。記載事項の点検は条文の番号ではなく記載事項の内容を単位として行い、条文を確認できていない箇所は［要確認］として残す。【令和8年10月14日】社会福祉法等の一部を改正する法律案要綱を確認したことにより、改正後の第117条第2項第3号・第4号、第3項第4号・第5号、第5項及び第14項の号及び項が確定した。引き続き必要なのは、①改正後の条文及び新旧対照表（要綱は改正事項の要旨であり条文の文言を確認できない）、②附則第3条から第77条までの経過措置（有料老人ホームの登録制に係る経過措置の内容）、③改正に係らない号（第2項第1号・第2号、第3項第1号から第3号まで）の条文である</t>
         </is>
       </c>
     </row>
@@ -8464,27 +8402,27 @@
         <v>169</v>
       </c>
       <c r="B174" s="5" t="n">
-        <v>74</v>
+        <v>185</v>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
+          <t>小規模市町村地域支援連携協働体制整備事業の対象となるかどうか</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）9
-計画素案 第5章 基本目標5</t>
+          <t>計画素案 第1章第9節2・第6章第3節2・第6章第6節
+サービス見込量の算定（地域支援事業費）</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>北海道上川総合振興局</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
-          <t>R9.4</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="G174" s="15" t="n">
@@ -8497,7 +8435,7 @@
       </c>
       <c r="I174" s="6" t="inlineStr">
         <is>
-          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
+          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す</t>
         </is>
       </c>
     </row>
@@ -8506,40 +8444,40 @@
         <v>170</v>
       </c>
       <c r="B175" s="5" t="n">
-        <v>24</v>
+        <v>186</v>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスの確保方策の決定</t>
+          <t>特定施設の定義の改正による区域内3施設の扱い</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第2節・第4節
-見込量表（3種別）</t>
+          <t>計画素案 第1章第9節2・第2章第3節・第6章第2節 注3・第6章第4節
+サービス見込量の算定（施設・居住系サービス）</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="G175" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H175" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I175" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+          <t>現行の指定の区分により特定施設入居者生活介護の見込量を算定し、定義の改正により対象となる施設の範囲が変わり得ることを計画素案の注に［要確認］として記載する</t>
         </is>
       </c>
     </row>
@@ -8548,45 +8486,129 @@
         <v>171</v>
       </c>
       <c r="B176" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
+        </is>
+      </c>
+      <c r="D176" s="6" t="inlineStr">
+        <is>
+          <t>ケアプラン点検実施要領（案）9
+計画素案 第5章 基本目標5</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="inlineStr">
+        <is>
+          <t>北海道上川総合振興局</t>
+        </is>
+      </c>
+      <c r="F176" s="5" t="inlineStr">
+        <is>
+          <t>R9.4</t>
+        </is>
+      </c>
+      <c r="G176" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" s="6" t="inlineStr">
+        <is>
+          <t>止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I176" s="6" t="inlineStr">
+        <is>
+          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="48" customHeight="1">
+      <c r="A177" s="5" t="n">
+        <v>172</v>
+      </c>
+      <c r="B177" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C177" s="6" t="inlineStr">
+        <is>
+          <t>24時間対応サービスの確保方策の決定</t>
+        </is>
+      </c>
+      <c r="D177" s="6" t="inlineStr">
+        <is>
+          <t>素案 第6章第2節・第4節
+見込量表（3種別）</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F177" s="5" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G177" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I177" s="6" t="inlineStr">
+        <is>
+          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="48" customHeight="1">
+      <c r="A178" s="5" t="n">
+        <v>173</v>
+      </c>
+      <c r="B178" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="C176" s="6" t="inlineStr">
+      <c r="C178" s="6" t="inlineStr">
         <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="D176" s="6" t="inlineStr">
+      <c r="D178" s="6" t="inlineStr">
         <is>
           <t>素案 第4章第3節・第5章
 全16KPIの目標値</t>
         </is>
       </c>
-      <c r="E176" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F176" s="5" t="inlineStr">
+      <c r="E178" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F178" s="5" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="G176" s="15" t="n">
+      <c r="G178" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H176" s="6" t="inlineStr">
+      <c r="H178" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="I176" s="6" t="inlineStr">
+      <c r="I178" s="6" t="inlineStr">
         <is>
           <t>代表KPIの目標値は、令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置く</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="56" customHeight="1">
-      <c r="A177" s="13" t="inlineStr">
+    <row r="179" ht="56" customHeight="1">
+      <c r="A179" s="13" t="inlineStr">
         <is>
           <t>注1）点が9以上を至急、6以上8以下を優先、5以下を通常とみます（03シート）。
 注2）「決着しない場合の当方の扱い」が空のものは、決まらないと当方の作業が止まります。 先に扱いを決めます。
@@ -8594,205 +8616,119 @@
         </is>
       </c>
     </row>
-    <row r="178"/>
-    <row r="179" ht="20" customHeight="1">
-      <c r="A179" s="3" t="inlineStr">
+    <row r="180"/>
+    <row r="181" ht="20" customHeight="1">
+      <c r="A181" s="3" t="inlineStr">
         <is>
           <t>2　資料提供依頼（資料の提供を求めるもの）　18件</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="30" customHeight="1">
-      <c r="A180" s="4" t="inlineStr">
+    <row r="182" ht="30" customHeight="1">
+      <c r="A182" s="4" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B180" s="4" t="inlineStr">
+      <c r="B182" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C180" s="4" t="inlineStr">
+      <c r="C182" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="D180" s="4" t="inlineStr">
+      <c r="D182" s="4" t="inlineStr">
         <is>
           <t>確定する主張</t>
         </is>
       </c>
-      <c r="E180" s="4" t="inlineStr">
+      <c r="E182" s="4" t="inlineStr">
         <is>
           <t>入手先</t>
         </is>
       </c>
-      <c r="F180" s="4" t="inlineStr">
+      <c r="F182" s="4" t="inlineStr">
         <is>
           <t>希望時期</t>
         </is>
       </c>
-      <c r="G180" s="4" t="inlineStr">
+      <c r="G182" s="4" t="inlineStr">
         <is>
           <t>優先</t>
         </is>
       </c>
-      <c r="H180" s="4" t="inlineStr">
+      <c r="H182" s="4" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="I180" s="4" t="inlineStr">
+      <c r="I182" s="4" t="inlineStr">
         <is>
           <t>領域</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="40" customHeight="1">
-      <c r="A181" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B181" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C181" s="6" t="inlineStr">
-        <is>
-          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
-        </is>
-      </c>
-      <c r="D181" s="6" t="inlineStr">
-        <is>
-          <t>第9期の評価の完成</t>
-        </is>
-      </c>
-      <c r="E181" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F181" s="5" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="G181" s="16" t="inlineStr">
-        <is>
-          <t>最高</t>
-        </is>
-      </c>
-      <c r="H181" s="5" t="inlineStr">
-        <is>
-          <t>一部受領</t>
-        </is>
-      </c>
-      <c r="I181" s="5" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="40" customHeight="1">
-      <c r="A182" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B182" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C182" s="6" t="inlineStr">
-        <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
-        </is>
-      </c>
-      <c r="D182" s="6" t="inlineStr">
-        <is>
-          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
-        </is>
-      </c>
-      <c r="E182" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F182" s="5" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="G182" s="14" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H182" s="5" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="I182" s="5" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B183" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
+          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr">
         <is>
-          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
+          <t>第9期の評価の完成</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G183" s="14" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="G183" s="16" t="inlineStr">
+        <is>
+          <t>最高</t>
         </is>
       </c>
       <c r="H183" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>一部受領</t>
         </is>
       </c>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B184" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
+          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
@@ -8802,7 +8738,7 @@
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G184" s="14" t="inlineStr">
@@ -8812,40 +8748,40 @@
       </c>
       <c r="H184" s="5" t="inlineStr">
         <is>
-          <t>代替により解消</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B185" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
         <is>
-          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
+          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G185" s="14" t="inlineStr">
@@ -8855,40 +8791,40 @@
       </c>
       <c r="H185" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I185" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B186" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>事業所・施設の定員と稼働の実績</t>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
-          <t>稼働率の低下の有無、定員減少の経緯</t>
+          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G186" s="14" t="inlineStr">
@@ -8898,35 +8834,35 @@
       </c>
       <c r="H186" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>代替により解消</t>
         </is>
       </c>
       <c r="I186" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B187" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>未利用認定者の内訳とケアプランのサービス構成</t>
+          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
         </is>
       </c>
       <c r="D187" s="6" t="inlineStr">
         <is>
-          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
+          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F187" s="5" t="inlineStr">
@@ -8941,35 +8877,35 @@
       </c>
       <c r="H187" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I187" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B188" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
+          <t>事業所・施設の定員と稼働の実績</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
         <is>
-          <t>第9期の剰余額（現在は概算）</t>
+          <t>稼働率の低下の有無、定員減少の経緯</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F188" s="5" t="inlineStr">
@@ -8989,30 +8925,30 @@
       </c>
       <c r="I188" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B189" s="5" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
+          <t>未利用認定者の内訳とケアプランのサービス構成</t>
         </is>
       </c>
       <c r="D189" s="6" t="inlineStr">
         <is>
-          <t>給付費の地域内還流の議論</t>
+          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F189" s="5" t="inlineStr">
@@ -9032,30 +8968,30 @@
       </c>
       <c r="I189" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
+          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
-          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
+          <t>第9期の剰余額（現在は概算）</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F190" s="5" t="inlineStr">
@@ -9075,30 +9011,30 @@
       </c>
       <c r="I190" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B191" s="5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
+          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
         </is>
       </c>
       <c r="D191" s="6" t="inlineStr">
         <is>
-          <t>サービス種別ごとの見込量の様式</t>
+          <t>給付費の地域内還流の議論</t>
         </is>
       </c>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F191" s="5" t="inlineStr">
@@ -9113,40 +9049,40 @@
       </c>
       <c r="H191" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I191" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B192" s="5" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C192" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
+          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>第10期の段階設計と保険料算定</t>
+          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F192" s="5" t="inlineStr">
         <is>
-          <t>告示後</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G192" s="14" t="inlineStr">
@@ -9156,126 +9092,126 @@
       </c>
       <c r="H192" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I192" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B193" s="5" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>小学校区と日常生活圏域の対応関係</t>
+          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
         </is>
       </c>
       <c r="D193" s="6" t="inlineStr">
         <is>
-          <t>圏域別の分析、圏域設定の見直し</t>
+          <t>サービス種別ごとの見込量の様式</t>
         </is>
       </c>
       <c r="E193" s="6" t="inlineStr">
         <is>
-          <t>美瑛町・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G193" s="15" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G193" s="14" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H193" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I193" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B194" s="5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>評価の枠組みの整理</t>
+          <t>第10期の段階設計と保険料算定</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>国の情報</t>
         </is>
       </c>
       <c r="F194" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G194" s="15" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>告示後</t>
+        </is>
+      </c>
+      <c r="G194" s="14" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I194" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B195" s="5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD49の指標定義</t>
+          <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
       <c r="D195" s="6" t="inlineStr">
         <is>
-          <t>地域差指数の分解の可否</t>
+          <t>圏域別の分析、圏域設定の見直し</t>
         </is>
       </c>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t>見える化システム・厚生労働省</t>
+          <t>美瑛町・3町</t>
         </is>
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G195" s="15" t="inlineStr">
@@ -9285,40 +9221,40 @@
       </c>
       <c r="H195" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I195" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B196" s="5" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C196" s="6" t="inlineStr">
         <is>
-          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
         <is>
-          <t>会議資料・委員会資料の記述の正確性</t>
+          <t>評価の枠組みの整理</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
-          <t>随時</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G196" s="15" t="inlineStr">
@@ -9328,45 +9264,45 @@
       </c>
       <c r="H196" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I196" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" s="5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B197" s="5" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+          <t>見える化システムD49の指標定義</t>
         </is>
       </c>
       <c r="D197" s="6" t="inlineStr">
         <is>
-          <t>中重度・軽度の認定率の推移</t>
+          <t>地域差指数の分解の可否</t>
         </is>
       </c>
       <c r="E197" s="6" t="inlineStr">
         <is>
-          <t>見える化システム</t>
+          <t>見える化システム・厚生労働省</t>
         </is>
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G197" s="17" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G197" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H197" s="5" t="inlineStr">
@@ -9376,55 +9312,141 @@
       </c>
       <c r="I197" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B198" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C198" s="6" t="inlineStr">
+        <is>
+          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+        </is>
+      </c>
+      <c r="D198" s="6" t="inlineStr">
+        <is>
+          <t>会議資料・委員会資料の記述の正確性</t>
+        </is>
+      </c>
+      <c r="E198" s="6" t="inlineStr">
+        <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="F198" s="5" t="inlineStr">
+        <is>
+          <t>随時</t>
+        </is>
+      </c>
+      <c r="G198" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H198" s="5" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+      <c r="I198" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="40" customHeight="1">
+      <c r="A199" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B199" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+        </is>
+      </c>
+      <c r="D199" s="6" t="inlineStr">
+        <is>
+          <t>中重度・軽度の認定率の推移</t>
+        </is>
+      </c>
+      <c r="E199" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム</t>
+        </is>
+      </c>
+      <c r="F199" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G199" s="17" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H199" s="5" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I199" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="40" customHeight="1">
+      <c r="A200" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B198" s="5" t="n">
+      <c r="B200" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C198" s="6" t="inlineStr">
+      <c r="C200" s="6" t="inlineStr">
         <is>
           <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
-      <c r="D198" s="6" t="inlineStr">
+      <c r="D200" s="6" t="inlineStr">
         <is>
           <t>世帯構成の現状</t>
         </is>
       </c>
-      <c r="E198" s="6" t="inlineStr">
+      <c r="E200" s="6" t="inlineStr">
         <is>
           <t>総務省・3町</t>
         </is>
       </c>
-      <c r="F198" s="5" t="inlineStr">
+      <c r="F200" s="5" t="inlineStr">
         <is>
           <t>公表後</t>
         </is>
       </c>
-      <c r="G198" s="17" t="inlineStr">
+      <c r="G200" s="17" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H198" s="5" t="inlineStr">
+      <c r="H200" s="5" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="I198" s="5" t="inlineStr">
+      <c r="I200" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="199" ht="28" customHeight="1">
-      <c r="A199" s="13" t="inlineStr">
+    <row r="201" ht="28" customHeight="1">
+      <c r="A201" s="13" t="inlineStr">
         <is>
           <t>注）03シートの確認事項が「決定」を求めるものであるのに対し、本表は「資料の提供」を求めるものです。資料が届かない場合の扱いは04シートの区分で示しています。</t>
         </is>
@@ -9433,11 +9455,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A179:I179"/>
-    <mergeCell ref="A199:I199"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A177:I177"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A181:I181"/>
     <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A201:I201"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9469,7 +9491,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02シートの点は次の規則だけで付けています。規則を変えれば02シートの並びも変わります。基準日 令和8年10月14日。</t>
+          <t>02シートの点は次の規則だけで付けています。規則を変えれば02シートの並びも変わります。基準日 令和8年10月15日。</t>
         </is>
       </c>
     </row>
@@ -9638,7 +9660,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>102件</t>
+          <t>104件</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9908,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>168件</t>
+          <t>170件</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -10045,7 +10067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -10065,7 +10087,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>決定・資料の受領を待たずに当方の作業だけで進められるものです。基準日 令和8年10月14日。</t>
+          <t>決定・資料の受領を待たずに当方の作業だけで進められるものです。基準日 令和8年10月15日。</t>
         </is>
       </c>
     </row>
@@ -10073,7 +10095,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　当方の作業だけで進められるもの　7件</t>
+          <t>1　当方の作業だけで進められるもの　9件</t>
         </is>
       </c>
     </row>
@@ -10116,7 +10138,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>条番号のみを記載し項番号及び号番号は記載しない。記載事項の点検は条文の番号ではなく記載事項の内容を単位として行い、条文を確認できていない箇所は［要確認］として残す</t>
+          <t>条番号のみを記載し項番号及び号番号は記載しない。記載事項の点検は条文の番号ではなく記載事項の内容を単位として行い、条文を確認できていない箇所は［要確認］として残す。【令和8年10月14日】社会福祉法等の一部を改正する法律案要綱を確認したことにより、改正後の第117条第2項第3号・第4号、第3項第4号・第5号、第5項及び第14項の号及び項が確定した。引き続き必要なのは、①改正後の条文及び新旧対照表（要綱は改正事項の要旨であり条文の文言を確認できない）、②附則第3条から第77条までの経過措置（有料老人ホームの登録制に係る経過措置の内容）、③改正に係らない号（第2項第1号・第2号、第3項第1号から第3号まで）の条文である</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -10275,8 +10297,58 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="76" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>既定値で進める</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>小規模市町村地域支援連携協働体制整備事業の対象となるかどうか</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.185（点1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>既定値で進める</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>特定施設の定義の改正による区域内3施設の扱い</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>現行の指定の区分により特定施設入居者生活介護の見込量を算定し、定義の改正により対象となる施設の範囲が変わり得ることを計画素案の注に［要確認］として記載する</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.186（点1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="76" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>注1）「据え置き（区分A）」は、資料の受領を待たずに当方の側で確定できるものです。
 注2）「既定値で進める」は、決着しない場合の扱いを置けているため決定を待たずに作業を進められるものです。決定を受けた時点で見直します。
@@ -10285,16 +10357,16 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="16"/>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>2　先に扱いを決めるもの（既定値を置けていない）　0件</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>ありません。未決の確認事項の全件に扱いを置けています。</t>
         </is>
@@ -10304,10 +10376,10 @@
   <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10319,7 +10391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -10332,7 +10404,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>翌日（令和8年10月15日）の作業順位</t>
+          <t>翌日（令和8年10月16日）の作業順位</t>
         </is>
       </c>
     </row>
@@ -10387,7 +10459,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>条番号のみを記載し項番号及び号番号は記載しない。記載事項の点検は条文の番号ではなく記載事項の内容を単位として行い、条文を確認できていない箇所は［要確認］として残す</t>
+          <t>条番号のみを記載し項番号及び号番号は記載しない。記載事項の点検は条文の番号ではなく記載事項の内容を単位として行い、条文を確認できていない箇所は［要確認］として残す。【令和8年10月14日】社会福祉法等の一部を改正する法律案要綱を確認したことにより、改正後の第117条第2項第3号・第4号、第3項第4号・第5号、第5項及び第14項の号及び項が確定した。引き続き必要なのは、①改正後の条文及び新旧対照表（要綱は改正事項の要旨であり条文の文言を確認できない）、②附則第3条から第77条までの経過措置（有料老人ホームの登録制に係る経過措置の内容）、③改正に係らない号（第2項第1号・第2号、第3項第1号から第3号まで）の条文である</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -10550,24 +10622,24 @@
       <c r="A12" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>催促・照会</t>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>進める</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の量の見込みを算定してよいか（発注者）</t>
+          <t>小規模市町村地域支援連携協働体制整備事業の対象となるかどうか</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>点8。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／月額への効き 最大7円（令和7年度の総合事業の事業費）／法定記載事項 法第117条に直結</t>
+          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.112</t>
+          <t>確認事項No.185（点1）</t>
         </is>
       </c>
     </row>
@@ -10582,17 +10654,17 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>認知症総合支援事業の実績のご提供（発注者）</t>
+          <t>地域支援事業の量の見込みを算定してよいか（発注者）</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>点7。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／法定記載事項 法第117条に直結</t>
+          <t>点8。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／月額への効き 最大7円（令和7年度の総合事業の事業費）／法定記載事項 法第117条に直結</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.150</t>
+          <t>確認事項No.112</t>
         </is>
       </c>
     </row>
@@ -10607,22 +10679,47 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
+          <t>認知症総合支援事業の実績のご提供（発注者）</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>点7。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／法定記載事項 法第117条に直結</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.150</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>催促・照会</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
           <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案（発注者・北海道）</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>点6。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／月額への効き 最大47円（第7期給付適正化計画の目標のご判断）</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>確認事項No.93</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="62" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="16" ht="62" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>注1）「進める」は決定を待たずに着手できるもの、「催促・照会」は相手のある作業です。相手のある作業は午前のうちに出します（返事に日数がかかるため）。
 注2）04シートの作業継続可能なものは上位8件まで、催促・照会は優先以上の上位5件までを掲げています。残りは02・04シートを見ます。
@@ -10632,8 +10729,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A15:E15"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10708,12 +10805,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>No.1〜No.184 を数える</t>
+          <t>No.1〜No.186 を数える</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>184件／欠番 なし／重複 なし</t>
+          <t>186件／欠番 なし／重複 なし</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -10738,7 +10835,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>確認事項171件／資料提供依頼18件</t>
+          <t>確認事項173件／資料提供依頼18件</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -10763,7 +10860,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>171件／合わない なし</t>
+          <t>173件／合わない なし</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -10913,7 +11010,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>記録 令和8年10月14日／本表 令和8年10月14日</t>
+          <t>記録 令和8年10月15日／本表 令和8年10月15日</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -10963,7 +11060,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>10件（進める7・催促3）</t>
+          <t>11件（進める8・催促3）</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -10988,7 +11085,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>7件（区分A 0・既定値 7）／据え置きの区分A 0件・既定値があり未処理 7件</t>
+          <t>9件（区分A 0・既定値 9）／据え置きの区分A 0件・既定値があり未処理 9件</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -749,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1212,27 +1212,53 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>基準日のコミットはありません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="13" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="4" t="inlineStr"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>コミット</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>b224cc4</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>社会福祉法等改正法の法律案要綱（原典）の受領点検と計画素案への反映</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr"/>
+      <c r="E23" s="6" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A21:F21"/>
   </mergeCells>
@@ -1246,7 +1272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I201"/>
+  <dimension ref="A1:I200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1278,7 +1304,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　確認事項（決定を求めるもの）　173件</t>
+          <t>1　確認事項（決定を求めるもの）　172件</t>
         </is>
       </c>
     </row>
@@ -3948,7 +3974,7 @@
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>条番号のみを記載し項番号及び号番号は記載しない。記載事項の点検は条文の番号ではなく記載事項の内容を単位として行い、条文を確認できていない箇所は［要確認］として残す。【令和8年10月14日】社会福祉法等の一部を改正する法律案要綱を確認したことにより、改正後の第117条第2項第3号・第4号、第3項第4号・第5号、第5項及び第14項の号及び項が確定した。引き続き必要なのは、①改正後の条文及び新旧対照表（要綱は改正事項の要旨であり条文の文言を確認できない）、②附則第3条から第77条までの経過措置（有料老人ホームの登録制に係る経過措置の内容）、③改正に係らない号（第2項第1号・第2号、第3項第1号から第3号まで）の条文である</t>
+          <t>条番号のみを記載し項番号及び号番号は記載しない。記載事項の点検は条文の番号ではなく記載事項の内容を単位として行い、条文を確認できていない箇所は［要確認］として残す。【令和8年10月14日】社会福祉法等の一部を改正する法律案要綱を確認したことにより、改正後の第117条第2項第3号・第4号、第3項第4号・第5号、第5項及び第14項の号及び項が確定した。引き続き必要なのは、①改正後の条文及び新旧対照表（要綱は改正事項の要旨であり条文の文言を確認できない）、②附則第3条から第77条までの経過措置（有料老人ホームの登録制に係る経過措置の内容）、③改正に係らない号（第2項第1号・第2号、第3項第1号から第3号まで）の条文である。【令和8年10月15日　大きく解決】社会福祉法等の一部を改正する法律案の新旧対照条文（全353頁）を確認した。改正後の介護保険法第117条（第2項第3号・第4号、第3項第3号・第4号・第4号の2・第5号・第6号・第7号・第9号、第5項、第9項、第14項）、第115条の48（支援会議）、第118条第2項・第8項・第9項並びに第120条の3から第120条の5まで（協議会）の内容が確定した。介護保険法の改正は第3条関係（令和9年4月1日又は1年6月以内）と第4条関係（2年以内又は3年以内）の2つに分かれる。新たに分かった主なものは、①第3項第3号は改正前からあり、量が第2項第3号へ移ったうえで費用の額及び保険料の水準が残ること（量は定めるものとされる事項、費用の額及び保険料の水準は定めるよう努めるものとされる事項）、②第3項第9号（入居定員総数）は改正前からあり、第5項第1号（勘案事項）との二重の構造であること、③第5項及び第14項の対象はいずれも第2項第1号から第3号までであること、④第115条の48の会議は改正後「支援会議」と称し構成員として地域包括支援センターが明示されること、⑤第118条第2項により都道府県介護保険事業支援計画にも中長期的な推計が定めるものとされること、⑥第117条第3項第6号・第7号及び第115条の49に指定登録施設介護支援の事業が加わること（3年以内）である。計画素案15箇所に反映した。引き続き必要なのは、①参照条文（001685804）の条文の内容（受領したものは画像であり文字の層がないため読み取れない）、②附則第3条から第77条までの経過措置、③認知症基本法ほか関係法令の条文（確認No.149）である</t>
         </is>
       </c>
     </row>
@@ -4166,22 +4192,22 @@
         <v>68</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>特別地域加算の対象地域告示</t>
+          <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第9節
-追加調査報告書 01シート</t>
+          <t>素案 第2章第2節
+分析資料</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
@@ -4199,7 +4225,7 @@
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>告示を確認できないものとして、特別地域加算の判定を計画素案に書かず［要確認］のまま残す</t>
+          <t>類似保険者との比較は公表されている同規模保険者40団体による</t>
         </is>
       </c>
     </row>
@@ -4208,17 +4234,17 @@
         <v>69</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較分析の対象</t>
+          <t>交付金の評価調書</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第2節
-分析資料</t>
+          <t>素案 第3章第4節
+追加調査報告書 02シート</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -4241,7 +4267,7 @@
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較は公表されている同規模保険者40団体による</t>
+          <t>評価調書を受領できないものとして、得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できない旨を注記する</t>
         </is>
       </c>
     </row>
@@ -4250,17 +4276,17 @@
         <v>70</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価調書</t>
+          <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>素案 第3章第4節
-追加調査報告書 02シート</t>
+          <t>素案 第2章第4〜6節
+クロス集計表</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -4283,7 +4309,7 @@
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>評価調書を受領できないものとして、得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できない旨を注記する</t>
+          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
         </is>
       </c>
     </row>
@@ -4292,17 +4318,17 @@
         <v>71</v>
       </c>
       <c r="B76" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>調査の対象者範囲と回収率</t>
+          <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第4〜6節
-クロス集計表</t>
+          <t>素案 第4章第3節
+H14の基準値</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
@@ -4325,7 +4351,7 @@
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
-          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
+          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
         </is>
       </c>
     </row>
@@ -4334,22 +4360,22 @@
         <v>72</v>
       </c>
       <c r="B77" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>介護人材実態調査の採用者数・退職者数</t>
+          <t>町別の人口・世帯データ</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>素案 第4章第3節
-H14の基準値</t>
+          <t>素案 第2章第1節
+図1・図2・図3</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
@@ -4367,7 +4393,7 @@
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
+          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
         </is>
       </c>
     </row>
@@ -4376,17 +4402,18 @@
         <v>73</v>
       </c>
       <c r="B78" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>町別の人口・世帯データ</t>
+          <t>日常生活圏域別のデータ</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第1節
-図1・図2・図3</t>
+          <t>素案 第1章第7節・第2章
+圏域別分析資料
+調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
@@ -4409,7 +4436,7 @@
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
-          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
+          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
         </is>
       </c>
     </row>
@@ -4418,23 +4445,22 @@
         <v>74</v>
       </c>
       <c r="B79" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域別のデータ</t>
+          <t>骨子案の内容の確認</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第7節・第2章
-圏域別分析資料
-調査クロス集計・分析 01・18シート</t>
+          <t>骨子案
+素案の次稿</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -4452,7 +4478,7 @@
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
+          <t>骨子案は提出した内容のままとする</t>
         </is>
       </c>
     </row>
@@ -4461,22 +4487,22 @@
         <v>75</v>
       </c>
       <c r="B80" s="5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>骨子案の内容の確認</t>
+          <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>骨子案
-素案の次稿</t>
+          <t>素案 第1章第6節
+追加調査報告書 04シート</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
@@ -4494,7 +4520,7 @@
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>骨子案は提出した内容のままとする</t>
+          <t>北海道の評価指標の読替えは当方の案のままとする</t>
         </is>
       </c>
     </row>
@@ -4503,22 +4529,22 @@
         <v>76</v>
       </c>
       <c r="B81" s="5" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標の読替えの考え方</t>
+          <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第6節
-追加調査報告書 04シート</t>
+          <t>調査クロス集計・分析 14シート
+素案 第2章第4節</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
@@ -4536,7 +4562,7 @@
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標の読替えは当方の案のままとする</t>
+          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
         </is>
       </c>
     </row>
@@ -4545,17 +4571,17 @@
         <v>77</v>
       </c>
       <c r="B82" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>令和4年度 健康とくらしの調査の集計表</t>
+          <t>調査対象者の範囲の確認</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析 14シート
-素案 第2章第4節</t>
+          <t>調査クロス集計・分析 13・14シート
+H06・H11の基準値</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -4578,7 +4604,7 @@
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
-          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
+          <t>現に収録している調査対象者の範囲による</t>
         </is>
       </c>
     </row>
@@ -4587,17 +4613,17 @@
         <v>78</v>
       </c>
       <c r="B83" s="5" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>調査対象者の範囲の確認</t>
+          <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析 13・14シート
-H06・H11の基準値</t>
+          <t>素案 第3章第4節
+妥当性検証 所見18・19</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -4620,7 +4646,7 @@
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>現に収録している調査対象者の範囲による</t>
+          <t>公表されている全国集計の値による</t>
         </is>
       </c>
     </row>
@@ -4629,17 +4655,17 @@
         <v>79</v>
       </c>
       <c r="B84" s="5" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の令和6年・令和7年調査の結果</t>
+          <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>素案 第3章第4節
-妥当性検証 所見18・19</t>
+          <t>給付実績データの受領点検
+将来推計 第2・3段階</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -4662,7 +4688,7 @@
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
-          <t>公表されている全国集計の値による</t>
+          <t>令和8年9月25日の再提供により決着済み。再提供を受けたファイルの値（3町合計と円単位一致）による</t>
         </is>
       </c>
     </row>
@@ -4671,17 +4697,17 @@
         <v>80</v>
       </c>
       <c r="B85" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の給付費の集計が一致しない</t>
+          <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>給付実績データの受領点検
-将来推計 第2・3段階</t>
+          <t>給付実績データの受領点検 04シート
+将来推計 第3段階</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -4704,7 +4730,7 @@
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月25日の再提供により決着済み。再提供を受けたファイルの値（3町合計と円単位一致）による</t>
+          <t>総括表（保険者単位）を用い、計画作成支援ツールの実績値シートは比較のためにのみ用いる</t>
         </is>
       </c>
     </row>
@@ -4713,17 +4739,18 @@
         <v>81</v>
       </c>
       <c r="B86" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの実績値シートの確認</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>給付実績データの受領点検 04シート
-将来推計 第3段階</t>
+          <t>総合事業実施状況調査の受領点検
+素案 第3章第1節・第2節
+H05の基準値</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -4746,7 +4773,7 @@
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>総括表（保険者単位）を用い、計画作成支援ツールの実績値シートは比較のためにのみ用いる</t>
+          <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値による</t>
         </is>
       </c>
     </row>
@@ -4755,18 +4782,18 @@
         <v>82</v>
       </c>
       <c r="B87" s="5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
+          <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>総合事業実施状況調査の受領点検
-素案 第3章第1節・第2節
-H05の基準値</t>
+          <t>年報月報の受領点検
+将来推計 第3段階
+素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -4789,7 +4816,7 @@
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
-          <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値による</t>
+          <t>受領済みの年報・月報の値による</t>
         </is>
       </c>
     </row>
@@ -4798,18 +4825,16 @@
         <v>83</v>
       </c>
       <c r="B88" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>年報・月報の受領に伴う確認</t>
+          <t>月報の値の接続のずれ（ご報告）</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>年報月報の受領点検
-将来推計 第3段階
-素案 第6章第3節・第6節</t>
+          <t>年報月報の受領点検 04シート</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -4832,7 +4857,7 @@
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
-          <t>受領済みの年報・月報の値による</t>
+          <t>月報の値の接続のずれは記録として残し、計画本文には用いない</t>
         </is>
       </c>
     </row>
@@ -4841,16 +4866,17 @@
         <v>84</v>
       </c>
       <c r="B89" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれ（ご報告）</t>
+          <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>年報月報の受領点検 04シート</t>
+          <t>令和6年度決算書の受領点検 03シート
+素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -4873,7 +4899,7 @@
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれは記録として残し、計画本文には用いない</t>
+          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
         </is>
       </c>
     </row>
@@ -4882,17 +4908,18 @@
         <v>85</v>
       </c>
       <c r="B90" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領に伴う確認</t>
+          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領点検 03シート
-素案 第6章第3節・第6節</t>
+          <t>基金条例の確認 02シート
+素案 第6章第6節
+将来推計 第3段階</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -4915,7 +4942,7 @@
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
-          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
+          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合の1億円あたりの月額への効きを併記する</t>
         </is>
       </c>
     </row>
@@ -4924,18 +4951,17 @@
         <v>86</v>
       </c>
       <c r="B91" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
+          <t>議事録の文書プロパティに個人名が再度入る</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
         <is>
-          <t>基金条例の確認 02シート
-素案 第6章第6節
-将来推計 第3段階</t>
+          <t>中間報告会議議事録
+業務工程管理表</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
@@ -4958,7 +4984,7 @@
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合の1億円あたりの月額への効きを併記する</t>
+          <t>議事録は作成者名を落として再出力する（当方で対応する）</t>
         </is>
       </c>
     </row>
@@ -4967,11 +4993,11 @@
         <v>87</v>
       </c>
       <c r="B92" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>議事録の文書プロパティに個人名が再度入る</t>
+          <t>議事録の表記に関するご提案3件</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -5000,7 +5026,7 @@
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
-          <t>議事録は作成者名を落として再出力する（当方で対応する）</t>
+          <t>議事録の表記はご提案3件のとおり改める</t>
         </is>
       </c>
     </row>
@@ -5009,17 +5035,16 @@
         <v>88</v>
       </c>
       <c r="B93" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記に関するご提案3件</t>
+          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>中間報告会議議事録
-業務工程管理表</t>
+          <t>見える化総括表の受領点検 00シート</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -5042,7 +5067,7 @@
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記はご提案3件のとおり改める</t>
+          <t>他団体の集計帳票6件は成果品に用いない</t>
         </is>
       </c>
     </row>
@@ -5051,16 +5076,16 @@
         <v>89</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
+          <t>調整交付金の算定基礎の確認</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>見える化総括表の受領点検 00シート</t>
+          <t>将来推計 第3段階 00・03シート</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -5083,7 +5108,7 @@
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
-          <t>他団体の集計帳票6件は成果品に用いない</t>
+          <t>現行の扱い（第9期の算定を再現し公表値6,428円と一致する扱い）による</t>
         </is>
       </c>
     </row>
@@ -5092,16 +5117,16 @@
         <v>90</v>
       </c>
       <c r="B95" s="5" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>調整交付金の算定基礎の確認</t>
+          <t>交付金の評価項目と19施策の割当て</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階 00・03シート</t>
+          <t>第9期施策別評価表 06シート</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -5124,7 +5149,7 @@
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
-          <t>現行の扱い（第9期の算定を再現し公表値6,428円と一致する扱い）による</t>
+          <t>交付金の評価項目と19施策の割当ては当方の案のままとする</t>
         </is>
       </c>
     </row>
@@ -5133,16 +5158,17 @@
         <v>91</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当て</t>
+          <t>職員個票のリストによる重複確認の可否</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>第9期施策別評価表 06シート</t>
+          <t>内部確認結果への対応整理 03・08
+実施済み3調査の受領点検と集計 06・07</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -5165,7 +5191,7 @@
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当ては当方の案のままとする</t>
+          <t>職員個票を突き合わせず、事業所への照会により重複を判別する</t>
         </is>
       </c>
     </row>
@@ -5174,17 +5200,17 @@
         <v>92</v>
       </c>
       <c r="B97" s="5" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>職員個票のリストによる重複確認の可否</t>
+          <t>構成町の一般会計繰入金の町別按分の方法</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>内部確認結果への対応整理 03・08
-実施済み3調査の受領点検と集計 06・07</t>
+          <t>サービス見込量の算定（R8.9.26）
+構成町の意見への回答 4</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
@@ -5194,7 +5220,7 @@
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.9.24</t>
         </is>
       </c>
       <c r="G97" s="15" t="n">
@@ -5202,12 +5228,12 @@
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）</t>
+          <t>期限 超過（R8.9.24）（+2）</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
-          <t>職員個票を突き合わせず、事業所への照会により重複を判別する</t>
+          <t>町別への按分は広域連合の規約によるものであり算定できないため、構成町の一般会計繰入金は3町計の概算のみを示す（按分の方法のご教示を受けた時点で町別までお示しする）</t>
         </is>
       </c>
     </row>
@@ -5216,27 +5242,28 @@
         <v>93</v>
       </c>
       <c r="B98" s="5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>構成町の一般会計繰入金の町別按分の方法</t>
+          <t>構成町との意見交換会の実施方法と町別データシート</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定（R8.9.26）
-構成町の意見への回答 4</t>
+          <t>意見交換会資料
+町別データシート
+構成町の意見への回答 2・3</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>R8.9.24</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G98" s="15" t="n">
@@ -5244,12 +5271,12 @@
       </c>
       <c r="H98" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9.24）（+2）</t>
+          <t>期限 超過（R8.9）（+2）</t>
         </is>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
-          <t>町別への按分は広域連合の規約によるものであり算定できないため、構成町の一般会計繰入金は3町計の概算のみを示す（按分の方法のご教示を受けた時点で町別までお示しする）</t>
+          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで進める</t>
         </is>
       </c>
     </row>
@@ -5258,18 +5285,17 @@
         <v>94</v>
       </c>
       <c r="B99" s="5" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>構成町との意見交換会の実施方法と町別データシート</t>
+          <t>町別データシートの内容と配付</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>意見交換会資料
-町別データシート
-構成町の意見への回答 2・3</t>
+          <t>町別データシート
+構成町の意見への回答 2</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
@@ -5292,7 +5318,7 @@
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
-          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで進める</t>
+          <t>町別データシートは現行の内容のまま配付する</t>
         </is>
       </c>
     </row>
@@ -5301,22 +5327,22 @@
         <v>95</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>町別データシートの内容と配付</t>
+          <t>成果品の統合の方針</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>町別データシート
-構成町の意見への回答 2</t>
+          <t>成果品一覧
+送付資料一覧</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
@@ -5334,7 +5360,7 @@
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
-          <t>町別データシートは現行の内容のまま配付する</t>
+          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す（現行）</t>
         </is>
       </c>
     </row>
@@ -5343,17 +5369,17 @@
         <v>96</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>成果品の統合の方針</t>
+          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>成果品一覧
-送付資料一覧</t>
+          <t>将来推計 第2段階・第3段階
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
@@ -5376,7 +5402,7 @@
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
-          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す（現行）</t>
+          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
         </is>
       </c>
     </row>
@@ -5385,16 +5411,16 @@
         <v>97</v>
       </c>
       <c r="B102" s="5" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
+          <t>見える化システムの推計方式は基本推計でよいか</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階・第3段階
+          <t>将来推計 第2段階
 サービス見込量の算定</t>
         </is>
       </c>
@@ -5418,7 +5444,7 @@
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
+          <t>基本推計に近いP3で概算する</t>
         </is>
       </c>
     </row>
@@ -5427,11 +5453,11 @@
         <v>98</v>
       </c>
       <c r="B103" s="5" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計方式は基本推計でよいか</t>
+          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
@@ -5460,7 +5486,7 @@
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
-          <t>基本推計に近いP3で概算する</t>
+          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
         </is>
       </c>
     </row>
@@ -5469,17 +5495,16 @@
         <v>99</v>
       </c>
       <c r="B104" s="5" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
+          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階
-サービス見込量の算定</t>
+          <t>将来推計 第2段階</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -5502,7 +5527,7 @@
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
-          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
+          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ</t>
         </is>
       </c>
     </row>
@@ -5511,16 +5536,16 @@
         <v>100</v>
       </c>
       <c r="B105" s="5" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
+          <t>健康とくらしの調査の個票の再提供の要否</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階</t>
+          <t>調査クロス集計・分析の更新</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -5543,7 +5568,7 @@
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ</t>
+          <t>健康とくらしの調査の個票の再提供を依頼しない（成果品は収録済みで内容が確定しており、現時点で不足がない）</t>
         </is>
       </c>
     </row>
@@ -5552,16 +5577,16 @@
         <v>101</v>
       </c>
       <c r="B106" s="5" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供の要否</t>
+          <t>第1次概算を既定値のまま出してよいか</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析の更新</t>
+          <t>サービス見込量の算定</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -5584,7 +5609,7 @@
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供を依頼しない（成果品は収録済みで内容が確定しており、現時点で不足がない）</t>
+          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
         </is>
       </c>
     </row>
@@ -5593,16 +5618,17 @@
         <v>102</v>
       </c>
       <c r="B107" s="5" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>第1次概算を既定値のまま出してよいか</t>
+          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定</t>
+          <t>町別データシート
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
@@ -5625,7 +5651,7 @@
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
-          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
+          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
         </is>
       </c>
     </row>
@@ -5634,16 +5660,16 @@
         <v>103</v>
       </c>
       <c r="B108" s="5" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
+          <t>見える化システムの伸びの選択肢をどれとするか</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>町別データシート
+          <t>見える化システムへの入力
 サービス見込量の算定</t>
         </is>
       </c>
@@ -5667,7 +5693,7 @@
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
+          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
         </is>
       </c>
     </row>
@@ -5676,17 +5702,17 @@
         <v>104</v>
       </c>
       <c r="B109" s="5" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの伸びの選択肢をどれとするか</t>
+          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
           <t>見える化システムへの入力
-サービス見込量の算定</t>
+将来推計 第2段階</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -5709,7 +5735,7 @@
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>受領済みの画面の写しの範囲で概算し、確認できていない項目はその旨を明記する</t>
         </is>
       </c>
     </row>
@@ -5718,17 +5744,17 @@
         <v>105</v>
       </c>
       <c r="B110" s="5" t="n">
-        <v>148</v>
+        <v>60</v>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
+          <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力
-将来推計 第2段階</t>
+          <t>将来推計 第3段階 05・06シート
+計画素案 第6章第6節</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -5738,7 +5764,7 @@
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G110" s="15" t="n">
@@ -5746,12 +5772,12 @@
       </c>
       <c r="H110" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
-          <t>受領済みの画面の写しの範囲で概算し、確認できていない項目はその旨を明記する</t>
+          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
         </is>
       </c>
     </row>
@@ -5760,17 +5786,17 @@
         <v>106</v>
       </c>
       <c r="B111" s="5" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提（受託者案）</t>
+          <t>区域内に事業所がないサービスの住民向けの記載</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階 05・06シート
-計画素案 第6章第6節</t>
+          <t>介護高齢者福祉サービスガイド_構成案
+計画素案 第6章第4節</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -5793,7 +5819,7 @@
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
-          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
+          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
         </is>
       </c>
     </row>
@@ -5802,17 +5828,17 @@
         <v>107</v>
       </c>
       <c r="B112" s="5" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスの住民向けの記載</t>
+          <t>成果指向型配分枠（令和8年度新設）への対応</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>介護高齢者福祉サービスガイド_構成案
-計画素案 第6章第4節</t>
+          <t>計画素案 第5章
+交付金評価指標と全国集計の受領点検 06シート</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -5835,7 +5861,7 @@
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
+          <t>成果指向型配分枠への対応状況を確認できないものとして、第10期の施策には位置づけず、確認でき次第加える</t>
         </is>
       </c>
     </row>
@@ -5844,17 +5870,17 @@
         <v>108</v>
       </c>
       <c r="B113" s="5" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠（令和8年度新設）への対応</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章
-交付金評価指標と全国集計の受領点検 06シート</t>
+          <t>計画素案 第1章第9節・第2章第8節・第5章・第6章第2節・第6章第4節
+ケアプラン点検実施要領</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -5877,7 +5903,7 @@
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠への対応状況を確認できないものとして、第10期の施策には位置づけず、確認でき次第加える</t>
+          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
         </is>
       </c>
     </row>
@@ -5886,17 +5912,18 @@
         <v>109</v>
       </c>
       <c r="B114" s="5" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節・第2章第8節・第5章・第6章第2節・第6章第4節
-ケアプラン点検実施要領</t>
+          <t>給付適正化計画の位置づけと追加検討事項 01シート
+計画素案 第5章 基本目標5・第2章第4節
+アンケート調査の分析 令和8年9月業務報告 第4節</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -5919,7 +5946,7 @@
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
+          <t>第9期計画の本文及び前回調査の原集計表を受領できないものとして、前回調査との比較は割合のみとし、指標別の分母を確認できない旨を注記する</t>
         </is>
       </c>
     </row>
@@ -5928,18 +5955,17 @@
         <v>110</v>
       </c>
       <c r="B115" s="5" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
+          <t>介護給付費通知及び給付実績の活用による確認等</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけと追加検討事項 01シート
-計画素案 第5章 基本目標5・第2章第4節
-アンケート調査の分析 令和8年9月業務報告 第4節</t>
+          <t>給付適正化計画の位置づけと追加検討事項 02シート
+計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
@@ -5962,7 +5988,7 @@
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文及び前回調査の原集計表を受領できないものとして、前回調査との比較は割合のみとし、指標別の分母を確認できない旨を注記する</t>
+          <t>介護給付費通知の実施状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
         </is>
       </c>
     </row>
@@ -5971,16 +5997,16 @@
         <v>111</v>
       </c>
       <c r="B116" s="5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知及び給付実績の活用による確認等</t>
+          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけと追加検討事項 02シート
+          <t>給付適正化計画の位置づけと追加検討事項 04シート
 計画素案 第5章 基本目標5</t>
         </is>
       </c>
@@ -6004,7 +6030,7 @@
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知の実施状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
+          <t>認定調査の委託の状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
         </is>
       </c>
     </row>
@@ -6013,17 +6039,18 @@
         <v>112</v>
       </c>
       <c r="B117" s="5" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
+          <t>令和9年4月1日から義務となる2件への対応</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけと追加検討事項 04シート
-計画素案 第5章 基本目標5</t>
+          <t>計画素案 第1章第9節
+計画素案 第5章 基本目標3・4
+計画素案 第6章第4節3</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -6046,7 +6073,7 @@
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
-          <t>認定調査の委託の状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
+          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
         </is>
       </c>
     </row>
@@ -6055,18 +6082,18 @@
         <v>113</v>
       </c>
       <c r="B118" s="5" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月1日から義務となる2件への対応</t>
+          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節
-計画素案 第5章 基本目標3・4
-計画素案 第6章第4節3</t>
+          <t>計画素案 第6章第4節
+計画素案 第6章第2節2（2）
+地域密着型サービス基準省令の論点整理</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
@@ -6089,7 +6116,7 @@
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
-          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
+          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
         </is>
       </c>
     </row>
@@ -6098,23 +6125,22 @@
         <v>114</v>
       </c>
       <c r="B119" s="5" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
+          <t>補正しても外れるサービス6件の理由</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第4節
-計画素案 第6章第2節2（2）
-地域密着型サービス基準省令の論点整理</t>
+          <t>対計画比の偏りの補正試算
+計画素案 第6章第2節2</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
@@ -6132,7 +6158,7 @@
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
+          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
         </is>
       </c>
     </row>
@@ -6141,17 +6167,16 @@
         <v>115</v>
       </c>
       <c r="B120" s="5" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れるサービス6件の理由</t>
+          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>対計画比の偏りの補正試算
-計画素案 第6章第2節2</t>
+          <t>計画素案 第1章第8節・第2章第3節6・第5章 基本目標2・第6章第2節</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
@@ -6174,7 +6199,7 @@
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
+          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
         </is>
       </c>
     </row>
@@ -6183,21 +6208,22 @@
         <v>116</v>
       </c>
       <c r="B121" s="5" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
+          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第8節・第2章第3節6・第5章 基本目標2・第6章第2節</t>
+          <t>計画素案 第5章 基本目標2
+第9期評価（施策2-5）</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
@@ -6215,7 +6241,7 @@
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
-          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
+          <t>施策2-5の代表KPIはO2（提起された地域課題のうち翌年度の事業・予算に反映されたものの割合）とする（当方案）</t>
         </is>
       </c>
     </row>
@@ -6224,22 +6250,21 @@
         <v>117</v>
       </c>
       <c r="B122" s="5" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
+          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2
-第9期評価（施策2-5）</t>
+          <t>計画素案 第5章 基本目標2</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
@@ -6257,7 +6282,7 @@
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIはO2（提起された地域課題のうち翌年度の事業・予算に反映されたものの割合）とする（当方案）</t>
+          <t>地域ケア会議の記録様式は協議資料にとどめ、令和9年度に整える</t>
         </is>
       </c>
     </row>
@@ -6266,16 +6291,16 @@
         <v>118</v>
       </c>
       <c r="B123" s="5" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2</t>
+          <t>計画素案 第5章 基本目標2・第6章第4節4</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -6298,7 +6323,7 @@
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の記録様式は協議資料にとどめ、令和9年度に整える</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
         </is>
       </c>
     </row>
@@ -6307,21 +6332,22 @@
         <v>119</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
+          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2・第6章第4節4</t>
+          <t>計画素案 第5章 基本目標2
+第9期評価（施策2-5）</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
@@ -6339,7 +6365,7 @@
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
+          <t>令和7年度の実施報告書により把握できる範囲で記述する</t>
         </is>
       </c>
     </row>
@@ -6348,22 +6374,22 @@
         <v>120</v>
       </c>
       <c r="B125" s="5" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
+          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2
-第9期評価（施策2-5）</t>
+          <t>計画素案 第2章第1節3・第6章第1節
+将来推計 第1段階・第2段階</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F125" s="5" t="inlineStr">
@@ -6381,7 +6407,7 @@
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の実施報告書により把握できる範囲で記述する</t>
+          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
         </is>
       </c>
     </row>
@@ -6390,17 +6416,17 @@
         <v>121</v>
       </c>
       <c r="B126" s="5" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
+          <t>見える化システムの総人口の設定を案Cに改めるか</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節3・第6章第1節
-将来推計 第1段階・第2段階</t>
+          <t>将来推計 第1段階
+計画素案 第2章第1節・第6章第1節</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
@@ -6423,7 +6449,7 @@
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
-          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
+          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
         </is>
       </c>
     </row>
@@ -6432,22 +6458,22 @@
         <v>122</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総人口の設定を案Cに改めるか</t>
+          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第1段階
-計画素案 第2章第1節・第6章第1節</t>
+          <t>将来推計 第2段階
+計画素案 第6章第4節2</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
@@ -6465,7 +6491,7 @@
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
+          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
         </is>
       </c>
     </row>
@@ -6474,22 +6500,22 @@
         <v>123</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+          <t>画面の令和7年度と年報の月平均の食い違い</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
           <t>将来推計 第2段階
-計画素案 第6章第4節2</t>
+計画素案 第6章第2節</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F128" s="5" t="inlineStr">
@@ -6507,7 +6533,7 @@
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
+          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
         </is>
       </c>
     </row>
@@ -6516,17 +6542,16 @@
         <v>124</v>
       </c>
       <c r="B129" s="5" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度と年報の月平均の食い違い</t>
+          <t>計画素案の未確定箇所の表示の統一</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階
-計画素案 第6章第2節</t>
+          <t>計画素案（策定委員会用）</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -6549,7 +6574,7 @@
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
+          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとする</t>
         </is>
       </c>
     </row>
@@ -6558,16 +6583,17 @@
         <v>125</v>
       </c>
       <c r="B130" s="5" t="n">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所の表示の統一</t>
+          <t>計画素案 第2章第1節に町別の図を加えるか</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>計画素案（策定委員会用）</t>
+          <t>計画素案 第2章第1節
+図表集</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -6590,7 +6616,7 @@
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
-          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとする</t>
+          <t>計画素案 第2章第1節に町別の図を加えない。加筆分は協議用の資料にとどめる</t>
         </is>
       </c>
     </row>
@@ -6599,17 +6625,17 @@
         <v>126</v>
       </c>
       <c r="B131" s="5" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えるか</t>
+          <t>中長期推計を令和12・27・32年度まで広げるか</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節
-図表集</t>
+          <t>見える化システムへの入力
+計画素案 第6章第1節・第3節</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -6632,7 +6658,7 @@
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えない。加筆分は協議用の資料にとどめる</t>
+          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
         </is>
       </c>
     </row>
@@ -6641,17 +6667,17 @@
         <v>127</v>
       </c>
       <c r="B132" s="5" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>中長期推計を令和12・27・32年度まで広げるか</t>
+          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力
-計画素案 第6章第1節・第3節</t>
+          <t>計画素案 第4章第3節・第5章 基本目標3・資料1
+アンケート調査の集計分析報告書 02・14シート</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
@@ -6674,7 +6700,7 @@
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
-          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
+          <t>設問ごとの有効回答を分母とし、町別の値は掲げない（令和8年9月25日に是正済み）</t>
         </is>
       </c>
     </row>
@@ -6683,22 +6709,22 @@
         <v>128</v>
       </c>
       <c r="B133" s="5" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
+          <t>東川町の通いの場の整備と担い手の確保</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・第5章 基本目標3・資料1
-アンケート調査の集計分析報告書 02・14シート</t>
+          <t>計画素案 第3章第1節・第5章 基本目標2
+10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・東川町</t>
         </is>
       </c>
       <c r="F133" s="5" t="inlineStr">
@@ -6716,7 +6742,7 @@
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
-          <t>設問ごとの有効回答を分母とし、町別の値は掲げない（令和8年9月25日に是正済み）</t>
+          <t>現状のまま（東川町の整備を見込まない）第10期の目標値を置く</t>
         </is>
       </c>
     </row>
@@ -6725,16 +6751,16 @@
         <v>129</v>
       </c>
       <c r="B134" s="5" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>東川町の通いの場の整備と担い手の確保</t>
+          <t>東川町の認知症サポーター養成講座の実施状況</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第3章第1節・第5章 基本目標2
+          <t>計画素案 第5章 基本目標2
 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
@@ -6758,7 +6784,7 @@
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
-          <t>現状のまま（東川町の整備を見込まない）第10期の目標値を置く</t>
+          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
         </is>
       </c>
     </row>
@@ -6767,11 +6793,11 @@
         <v>130</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>東川町の認知症サポーター養成講座の実施状況</t>
+          <t>東川町のチームオレンジ事業の位置づけ</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
@@ -6800,7 +6826,7 @@
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
+          <t>東川町の取組として記述し3町展開は記述しない</t>
         </is>
       </c>
     </row>
@@ -6809,11 +6835,11 @@
         <v>131</v>
       </c>
       <c r="B136" s="5" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>東川町のチームオレンジ事業の位置づけ</t>
+          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
@@ -6824,7 +6850,7 @@
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>発注者・東川町</t>
+          <t>発注者・美瑛町</t>
         </is>
       </c>
       <c r="F136" s="5" t="inlineStr">
@@ -6842,7 +6868,7 @@
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
-          <t>東川町の取組として記述し3町展開は記述しない</t>
+          <t>令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残す</t>
         </is>
       </c>
     </row>
@@ -6851,11 +6877,11 @@
         <v>132</v>
       </c>
       <c r="B137" s="5" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
+          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
@@ -6884,7 +6910,7 @@
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残す</t>
+          <t>美瑛町の取組として記述し3町展開は記述しない</t>
         </is>
       </c>
     </row>
@@ -6893,16 +6919,16 @@
         <v>133</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
+          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2
+          <t>計画素案 第6章第4節・第6章第5節
 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
@@ -6926,7 +6952,7 @@
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の取組として記述し3町展開は記述しない</t>
+          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
         </is>
       </c>
     </row>
@@ -6935,16 +6961,16 @@
         <v>134</v>
       </c>
       <c r="B139" s="5" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
+          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第4節・第6章第5節
+          <t>計画素案 第5章 基本目標2
 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
@@ -6968,7 +6994,7 @@
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
+          <t>現に確認できる取組の範囲で記述する</t>
         </is>
       </c>
     </row>
@@ -6977,22 +7003,22 @@
         <v>135</v>
       </c>
       <c r="B140" s="5" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
+          <t>東神楽町の通いの場の維持</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2
+          <t>計画素案 第3章第1節・第5章 基本目標2
 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>発注者・美瑛町</t>
+          <t>発注者・東神楽町</t>
         </is>
       </c>
       <c r="F140" s="5" t="inlineStr">
@@ -7010,7 +7036,7 @@
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述する</t>
+          <t>令和6年度の水準が続くものとして目標値を置く</t>
         </is>
       </c>
     </row>
@@ -7019,16 +7045,16 @@
         <v>136</v>
       </c>
       <c r="B141" s="5" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の通いの場の維持</t>
+          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第3章第1節・第5章 基本目標2
+          <t>計画素案 第5章 基本目標2
 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
@@ -7052,7 +7078,7 @@
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の水準が続くものとして目標値を置く</t>
+          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
         </is>
       </c>
     </row>
@@ -7061,22 +7087,22 @@
         <v>137</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
+          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2
-10月 地域課題の整理と3町協議の確認事項</t>
+          <t>計画素案の記載内容の洗い出しと対比 06シート・07シート
+計画素案 第1章第6節・第2章第3節・第2章第6節・第3章第2節・第4章第3節・第6章第6節</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>発注者・東神楽町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F142" s="5" t="inlineStr">
@@ -7094,7 +7120,7 @@
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
+          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
         </is>
       </c>
     </row>
@@ -7103,17 +7129,17 @@
         <v>138</v>
       </c>
       <c r="B143" s="5" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
+          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>計画素案の記載内容の洗い出しと対比 06シート・07シート
-計画素案 第1章第6節・第2章第3節・第2章第6節・第3章第2節・第4章第3節・第6章第6節</t>
+          <t>図表データ管理台帳 03シート
+計画素案 第3章第4節・資料7</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -7136,7 +7162,7 @@
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
-          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
+          <t>掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
         </is>
       </c>
     </row>
@@ -7145,17 +7171,18 @@
         <v>139</v>
       </c>
       <c r="B144" s="5" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
+          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>図表データ管理台帳 03シート
-計画素案 第3章第4節・資料7</t>
+          <t>人口推計コーホート分析の妥当性検証 07シート
+見える化へ入力する箇所と入力値 02シート
+計画素案 第2章第1節・第6章第1節</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -7178,7 +7205,7 @@
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
-          <t>掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
+          <t>案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
         </is>
       </c>
     </row>
@@ -7187,18 +7214,17 @@
         <v>140</v>
       </c>
       <c r="B145" s="5" t="n">
-        <v>174</v>
+        <v>16</v>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
+          <t>保険料算定の前提</t>
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr">
         <is>
-          <t>人口推計コーホート分析の妥当性検証 07シート
-見える化へ入力する箇所と入力値 02シート
-計画素案 第2章第1節・第6章第1節</t>
+          <t>素案 第6章第3節・第6節
+保険料算定表</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
@@ -7208,7 +7234,7 @@
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G145" s="15" t="n">
@@ -7216,12 +7242,12 @@
       </c>
       <c r="H145" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）</t>
+          <t>止めている成果物 保険料（+2）</t>
         </is>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
-          <t>案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
+          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
         </is>
       </c>
     </row>
@@ -7230,40 +7256,39 @@
         <v>141</v>
       </c>
       <c r="B146" s="5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提</t>
+          <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第3節・第6節
-保険料算定表</t>
+          <t>素案 第1章第9節・第6章第4節</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G146" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H146" s="6" t="inlineStr">
         <is>
-          <t>止めている成果物 保険料（+2）</t>
+          <t>期限 当月（R8.10）（+1）</t>
         </is>
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
+          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
         </is>
       </c>
     </row>
@@ -7272,21 +7297,23 @@
         <v>142</v>
       </c>
       <c r="B147" s="5" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
+          <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第9節・第6章第4節</t>
+          <t>素案 第1章第7節
+追加調査報告書 03シート
+住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F147" s="5" t="inlineStr">
@@ -7304,7 +7331,7 @@
       </c>
       <c r="I147" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
+          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
         </is>
       </c>
     </row>
@@ -7313,18 +7340,17 @@
         <v>143</v>
       </c>
       <c r="B148" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域の判定資料</t>
+          <t>人口推計の基礎とする系列</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第7節
-追加調査報告書 03シート
-住まいと施設の公表名簿との突合 08シート</t>
+          <t>素案 第6章第1節
+将来推計</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
@@ -7347,7 +7373,7 @@
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
-          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
+          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
         </is>
       </c>
     </row>
@@ -7356,11 +7382,11 @@
         <v>144</v>
       </c>
       <c r="B149" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎とする系列</t>
+          <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr">
@@ -7371,7 +7397,7 @@
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
@@ -7389,7 +7415,7 @@
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
-          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
+          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
         </is>
       </c>
     </row>
@@ -7398,22 +7424,22 @@
         <v>145</v>
       </c>
       <c r="B150" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>認定者数の基準月と月次推移</t>
+          <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第1節
-将来推計</t>
+          <t>素案 資料2
+3町協議資料</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
@@ -7431,7 +7457,7 @@
       </c>
       <c r="I150" s="6" t="inlineStr">
         <is>
-          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
+          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
         </is>
       </c>
     </row>
@@ -7440,22 +7466,21 @@
         <v>146</v>
       </c>
       <c r="B151" s="5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>3町計画への共通指標の掲載</t>
+          <t>北海道・圏域との調整の場</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr">
         <is>
-          <t>素案 資料2
-3町協議資料</t>
+          <t>素案 第6章第4節</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
@@ -7473,7 +7498,7 @@
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
-          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
+          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
         </is>
       </c>
     </row>
@@ -7482,21 +7507,22 @@
         <v>147</v>
       </c>
       <c r="B152" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場</t>
+          <t>成果品の仕様</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第4節</t>
+          <t>計画書（印刷200部）
+概要版</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
@@ -7514,7 +7540,7 @@
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
+          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
         </is>
       </c>
     </row>
@@ -7523,22 +7549,22 @@
         <v>148</v>
       </c>
       <c r="B153" s="5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様</t>
+          <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
       <c r="D153" s="6" t="inlineStr">
         <is>
-          <t>計画書（印刷200部）
-概要版</t>
+          <t>素案 第2章第3節・第6章第4節
+図21・図22</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
@@ -7556,7 +7582,7 @@
       </c>
       <c r="I153" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
+          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
         </is>
       </c>
     </row>
@@ -7565,22 +7591,22 @@
         <v>149</v>
       </c>
       <c r="B154" s="5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>事業所の定員・稼働率データ</t>
+          <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第3節・第6章第4節
-図21・図22</t>
+          <t>素案 第5章 基本目標1・5
+図表集 認知症・医療連携</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者・3町・北海道</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
@@ -7598,7 +7624,7 @@
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
-          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
+          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
         </is>
       </c>
     </row>
@@ -7607,22 +7633,22 @@
         <v>150</v>
       </c>
       <c r="B155" s="5" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>認知症・医療介護連携の実績データ</t>
+          <t>重度化の速度の前提</t>
         </is>
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
-          <t>素案 第5章 基本目標1・5
-図表集 認知症・医療連携</t>
+          <t>素案 第6章第1節
+認定者数・給付費の推計</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F155" s="5" t="inlineStr">
@@ -7640,7 +7666,7 @@
       </c>
       <c r="I155" s="6" t="inlineStr">
         <is>
-          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
+          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
         </is>
       </c>
     </row>
@@ -7649,17 +7675,17 @@
         <v>151</v>
       </c>
       <c r="B156" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提</t>
+          <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第1節
-認定者数・給付費の推計</t>
+          <t>素案 第6章第2節・第5章・第7章
+給付費の推計</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -7682,7 +7708,7 @@
       </c>
       <c r="I156" s="6" t="inlineStr">
         <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
+          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
         </is>
       </c>
     </row>
@@ -7691,17 +7717,17 @@
         <v>152</v>
       </c>
       <c r="B157" s="5" t="n">
-        <v>31</v>
+        <v>128</v>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の実施予定と推計での扱い</t>
+          <t>令和8年度の実績見込み値を編集するか</t>
         </is>
       </c>
       <c r="D157" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第2節・第5章・第7章
-給付費の推計</t>
+          <t>将来推計 第2段階
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -7724,7 +7750,7 @@
       </c>
       <c r="I157" s="6" t="inlineStr">
         <is>
-          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
+          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
         </is>
       </c>
     </row>
@@ -7733,11 +7759,11 @@
         <v>153</v>
       </c>
       <c r="B158" s="5" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の実績見込み値を編集するか</t>
+          <t>見える化システムの利用率等の伸びの選択</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
@@ -7766,7 +7792,7 @@
       </c>
       <c r="I158" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
+          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
         </is>
       </c>
     </row>
@@ -7775,17 +7801,16 @@
         <v>154</v>
       </c>
       <c r="B159" s="5" t="n">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの利用率等の伸びの選択</t>
+          <t>統合した成果品の元の資料を残すか</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階
-サービス見込量の算定</t>
+          <t>成果品一覧（納品時の構成）</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -7808,7 +7833,7 @@
       </c>
       <c r="I159" s="6" t="inlineStr">
         <is>
-          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>統合した成果品の元の資料を残す</t>
         </is>
       </c>
     </row>
@@ -7817,16 +7842,17 @@
         <v>155</v>
       </c>
       <c r="B160" s="5" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>統合した成果品の元の資料を残すか</t>
+          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>成果品一覧（納品時の構成）</t>
+          <t>見える化システムへの入力
+将来推計 第3段階</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -7849,7 +7875,7 @@
       </c>
       <c r="I160" s="6" t="inlineStr">
         <is>
-          <t>統合した成果品の元の資料を残す</t>
+          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
         </is>
       </c>
     </row>
@@ -7858,22 +7884,22 @@
         <v>156</v>
       </c>
       <c r="B161" s="5" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
+          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力
-将来推計 第3段階</t>
+          <t>交付金評価の取りまとめと第10期への反映 08シート・09シート
+10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
@@ -7891,7 +7917,7 @@
       </c>
       <c r="I161" s="6" t="inlineStr">
         <is>
-          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
+          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
         </is>
       </c>
     </row>
@@ -7900,27 +7926,27 @@
         <v>157</v>
       </c>
       <c r="B162" s="5" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
+          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の取りまとめと第10期への反映 08シート・09シート
-10月 地域課題の整理と3町協議の確認事項</t>
+          <t>計画素案の記載内容の洗い出しと対比 08シート
+計画素案 全体</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G162" s="15" t="n">
@@ -7928,12 +7954,12 @@
       </c>
       <c r="H162" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）</t>
+          <t>止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I162" s="6" t="inlineStr">
         <is>
-          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
+          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
         </is>
       </c>
     </row>
@@ -7942,17 +7968,17 @@
         <v>158</v>
       </c>
       <c r="B163" s="5" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
+          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
         <is>
-          <t>計画素案の記載内容の洗い出しと対比 08シート
-計画素案 全体</t>
+          <t>図表データ管理台帳 01シート・02シート
+計画素案 資料7／別冊の図表集</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
@@ -7975,7 +8001,7 @@
       </c>
       <c r="I163" s="6" t="inlineStr">
         <is>
-          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
+          <t>現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
         </is>
       </c>
     </row>
@@ -7984,22 +8010,21 @@
         <v>159</v>
       </c>
       <c r="B164" s="5" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
+          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>図表データ管理台帳 01シート・02シート
-計画素案 資料7／別冊の図表集</t>
+          <t>計画素案 第1章第9節5・第5章 基本目標1・基本目標4</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F164" s="5" t="inlineStr">
@@ -8017,7 +8042,7 @@
       </c>
       <c r="I164" s="6" t="inlineStr">
         <is>
-          <t>現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
+          <t>国が示す本格運用開始日（令和10年4月1日）までに完了することを前提として計画素案に記載し、年度ごとの工程は［要確認］として残す。事業所への周知は広域連合と3町が共同で行うものとして記載する</t>
         </is>
       </c>
     </row>
@@ -8026,16 +8051,17 @@
         <v>160</v>
       </c>
       <c r="B165" s="5" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
+          <t>構成3町の高齢者福祉計画と市町村老人福祉計画の関係</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節5・第5章 基本目標1・基本目標4</t>
+          <t>計画素案 第1章第2節・第1章第8節
+計画素案の記載内容の洗い出しと対比 02シート</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
@@ -8058,7 +8084,7 @@
       </c>
       <c r="I165" s="6" t="inlineStr">
         <is>
-          <t>国が示す本格運用開始日（令和10年4月1日）までに完了することを前提として計画素案に記載し、年度ごとの工程は［要確認］として残す。事業所への周知は広域連合と3町が共同で行うものとして記載する</t>
+          <t>構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない</t>
         </is>
       </c>
     </row>
@@ -8067,16 +8093,16 @@
         <v>161</v>
       </c>
       <c r="B166" s="5" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画と市町村老人福祉計画の関係</t>
+          <t>成年後見制度の利用の促進に関する施策についての基本的な計画の策定状況</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第2節・第1章第8節
+          <t>計画素案 第1章第2節・第5章 基本目標1
 計画素案の記載内容の洗い出しと対比 02シート</t>
         </is>
       </c>
@@ -8100,7 +8126,7 @@
       </c>
       <c r="I166" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない</t>
+          <t>同計画は構成3町が定めるものとして計画素案に記載し、本計画は介護保険法第117条第3項による権利擁護の施策（第5章 基本目標1）をもって接続する。中核機関の整備の状況は［要確認］として残す</t>
         </is>
       </c>
     </row>
@@ -8109,16 +8135,16 @@
         <v>162</v>
       </c>
       <c r="B167" s="5" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>成年後見制度の利用の促進に関する施策についての基本的な計画の策定状況</t>
+          <t>要配慮者利用施設の避難確保計画の対象施設と作成状況</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第2節・第5章 基本目標1
+          <t>計画素案 第1章第8節・第5章 基本目標5
 計画素案の記載内容の洗い出しと対比 02シート</t>
         </is>
       </c>
@@ -8142,7 +8168,7 @@
       </c>
       <c r="I167" s="6" t="inlineStr">
         <is>
-          <t>同計画は構成3町が定めるものとして計画素案に記載し、本計画は介護保険法第117条第3項による権利擁護の施策（第5章 基本目標1）をもって接続する。中核機関の整備の状況は［要確認］として残す</t>
+          <t>対象施設及び作成の状況を［要確認］として残し、第5章 基本目標5の主な事業に作成及び避難訓練の確認を置くにとどめ、達成目標に数値を掲げない。避難確保計画はBCPとは別の計画であり、BCPの策定率をもって作成の状況としない</t>
         </is>
       </c>
     </row>
@@ -8151,27 +8177,26 @@
         <v>163</v>
       </c>
       <c r="B168" s="5" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>要配慮者利用施設の避難確保計画の対象施設と作成状況</t>
+          <t>介護サービス事業者経営情報データベースの公表結果の活用の範囲</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第8節・第5章 基本目標5
-計画素案の記載内容の洗い出しと対比 02シート</t>
+          <t>計画素案 第1章第9節5・第5章 基本目標4</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="G168" s="15" t="n">
@@ -8184,7 +8209,7 @@
       </c>
       <c r="I168" s="6" t="inlineStr">
         <is>
-          <t>対象施設及び作成の状況を［要確認］として残し、第5章 基本目標5の主な事業に作成及び避難訓練の確認を置くにとどめ、達成目標に数値を掲げない。避難確保計画はBCPとは別の計画であり、BCPの策定率をもって作成の状況としない</t>
+          <t>公表された区分のうち当区域の事業所の規模に近いものを参考として用い、区域内の事業所の経営状況を表すものとしては用いない。計画素案には活用の方針のみを記載し、数値は掲げない</t>
         </is>
       </c>
     </row>
@@ -8193,21 +8218,21 @@
         <v>164</v>
       </c>
       <c r="B169" s="5" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>介護サービス事業者経営情報データベースの公表結果の活用の範囲</t>
+          <t>都道府県との協定に基づく連携への関与</t>
         </is>
       </c>
       <c r="D169" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節5・第5章 基本目標4</t>
+          <t>計画素案 第1章第9節5・第5章 基本目標3・基本目標4</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F169" s="5" t="inlineStr">
@@ -8225,7 +8250,7 @@
       </c>
       <c r="I169" s="6" t="inlineStr">
         <is>
-          <t>公表された区分のうち当区域の事業所の規模に近いものを参考として用い、区域内の事業所の経営状況を表すものとしては用いない。計画素案には活用の方針のみを記載し、数値は掲げない</t>
+          <t>計画素案には北海道及び事業者とともに活用を検討する旨のみを記載し、具体の取組及び目標は国から市町村の役割が示された後に定める</t>
         </is>
       </c>
     </row>
@@ -8234,21 +8259,23 @@
         <v>165</v>
       </c>
       <c r="B170" s="5" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
-          <t>都道府県との協定に基づく連携への関与</t>
+          <t>介護給付費分科会の資料（原本）のご提供</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節5・第5章 基本目標3・基本目標4</t>
+          <t>計画素案 第1章第9節6・第6章第2節・第6章第6節2・第6章第7節
+介護給付費分科会の論点整理の受領点検
+介護給付費分科会資料（原典）の受領点検</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F170" s="5" t="inlineStr">
@@ -8266,7 +8293,7 @@
       </c>
       <c r="I170" s="6" t="inlineStr">
         <is>
-          <t>計画素案には北海道及び事業者とともに活用を検討する旨のみを記載し、具体の取組及び目標は国から市町村の役割が示された後に定める</t>
+          <t>計画素案には国において検討されている事項があることまでを記載し、単位数・要件・施行時期を書かない。原本を確認できていないことを［要確認］として残し、改定率及び単価は令和7年度の実績で固定したまま概算する</t>
         </is>
       </c>
     </row>
@@ -8275,18 +8302,17 @@
         <v>166</v>
       </c>
       <c r="B171" s="5" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>介護給付費分科会の資料（原本）のご提供</t>
+          <t>夜間対応型訪問介護の定期巡回・随時対応型への移行の扱い</t>
         </is>
       </c>
       <c r="D171" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節6・第6章第2節・第6章第6節2・第6章第7節
-介護給付費分科会の論点整理の受領点検
-介護給付費分科会資料（原典）の受領点検</t>
+          <t>計画素案 第6章第2節（2）・第6章第4節1
+サービス見込量の算定・見える化システムへの入力値</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -8309,7 +8335,7 @@
       </c>
       <c r="I171" s="6" t="inlineStr">
         <is>
-          <t>計画素案には国において検討されている事項があることまでを記載し、単位数・要件・施行時期を書かない。原本を確認できていないことを［要確認］として残し、改定率及び単価は令和7年度の実績で固定したまま概算する</t>
+          <t>現行の区分のまま夜間対応型訪問介護を実績なし（0）として立て、移行が検討されていることを計画素案の注に記載する。省令等が確定した時点で区分を組み替える</t>
         </is>
       </c>
     </row>
@@ -8318,22 +8344,22 @@
         <v>167</v>
       </c>
       <c r="B172" s="5" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>夜間対応型訪問介護の定期巡回・随時対応型への移行の扱い</t>
+          <t>短期入所生活介護の季節利用及び長期利用の実態</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節（2）・第6章第4節1
-サービス見込量の算定・見える化システムへの入力値</t>
+          <t>計画素案 第6章第2節 注1-1・第6章第4節
+サービス見込量の算定（季節補正）</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町・事業者</t>
         </is>
       </c>
       <c r="F172" s="5" t="inlineStr">
@@ -8351,7 +8377,7 @@
       </c>
       <c r="I172" s="6" t="inlineStr">
         <is>
-          <t>現行の区分のまま夜間対応型訪問介護を実績なし（0）として立て、移行が検討されていることを計画素案の注に記載する。省令等が確定した時点で区分を組み替える</t>
+          <t>令和7年度（12か月の完結年度）の実績により短期入所生活介護の見込量を算定し、季節補正を行わない（基準年度が完結年度であるため年度換算係数は1.0000となり効きは0円である）。季節利用の例外が示された時点で利用日数の置き方を確かめる</t>
         </is>
       </c>
     </row>
@@ -8360,22 +8386,22 @@
         <v>168</v>
       </c>
       <c r="B173" s="5" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>短期入所生活介護の季節利用及び長期利用の実態</t>
+          <t>小規模市町村地域支援連携協働体制整備事業の対象となるかどうか</t>
         </is>
       </c>
       <c r="D173" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節 注1-1・第6章第4節
-サービス見込量の算定（季節補正）</t>
+          <t>計画素案 第1章第9節2・第6章第3節2・第6章第6節
+サービス見込量の算定（地域支援事業費）</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・事業者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
@@ -8393,7 +8419,7 @@
       </c>
       <c r="I173" s="6" t="inlineStr">
         <is>
-          <t>令和7年度（12か月の完結年度）の実績により短期入所生活介護の見込量を算定し、季節補正を行わない（基準年度が完結年度であるため年度換算係数は1.0000となり効きは0円である）。季節利用の例外が示された時点で利用日数の置き方を確かめる</t>
+          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す。【令和8年10月15日】新旧対照条文により社会福祉法第106条の12（新設）の内容を確かめた。小規模市町村が本事業を実施する場合、介護保険法第122条の2（第3項を除く。地域支援事業に係る国の交付金）並びに第123条第3項及び第4項（都道府県の負担）の規定の適用について、第122条の2第1項の「費用」から本事業として行う社会福祉法第106条の6第2項第3号イに掲げる事業に要する費用を除き、第123条第4項の「費用」から同条第2項第1号イ及び第3号ロに掲げる事業に要する費用を除くこととされている。重層的支援体制整備事業（社会福祉法第106条の4）と同じ構造である。除かれるのは国の交付金及び都道府県の負担の対象となる費用であり、当該費用は社会福祉法による交付金等により支弁されることとなる。除かれる事業の内容（第106条の6第2項第1号イ・第3号イ・第3号ロ）は確かめていない。小規模市町村の基準は厚生労働省令で定められるため、①（該当の有無）は引き続き確認を要する</t>
         </is>
       </c>
     </row>
@@ -8402,22 +8428,22 @@
         <v>169</v>
       </c>
       <c r="B174" s="5" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>小規模市町村地域支援連携協働体制整備事業の対象となるかどうか</t>
+          <t>特定施設の定義の改正による区域内3施設の扱い</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節2・第6章第3節2・第6章第6節
-サービス見込量の算定（地域支援事業費）</t>
+          <t>計画素案 第1章第9節2・第2章第3節・第6章第2節 注3・第6章第4節
+サービス見込量の算定（施設・居住系サービス）</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
@@ -8435,7 +8461,7 @@
       </c>
       <c r="I174" s="6" t="inlineStr">
         <is>
-          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す</t>
+          <t>現行の指定の区分により特定施設入居者生活介護の見込量を算定し、定義の改正により対象となる施設の範囲が変わり得ることを計画素案の注に［要確認］として記載する。【令和8年10月15日】新旧対照条文により、現行の第8条第11項が「有料老人ホームその他厚生労働省令で定める施設であって、第20項に規定する地域密着型特定施設でないもの」であり、改正により「有料老人ホーム」が「老人福祉法第29条の18第5項に規定する登録有料老人ホーム」に置き換わることを確かめた。すなわち登録有料老人ホームを定義に加えるものではなく、登録を受けない有料老人ホームは特定施設に当たらなくなる。計画素案 第1章第9節2の記述を「定義に加える」から「有料老人ホームを登録有料老人ホームに改める」に是正した</t>
         </is>
       </c>
     </row>
@@ -8444,27 +8470,27 @@
         <v>170</v>
       </c>
       <c r="B175" s="5" t="n">
-        <v>186</v>
+        <v>74</v>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>特定施設の定義の改正による区域内3施設の扱い</t>
+          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節2・第2章第3節・第6章第2節 注3・第6章第4節
-サービス見込量の算定（施設・居住系サービス）</t>
+          <t>ケアプラン点検実施要領（案）9
+計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>北海道上川総合振興局</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>R8.12</t>
+          <t>R9.4</t>
         </is>
       </c>
       <c r="G175" s="15" t="n">
@@ -8477,7 +8503,7 @@
       </c>
       <c r="I175" s="6" t="inlineStr">
         <is>
-          <t>現行の指定の区分により特定施設入居者生活介護の見込量を算定し、定義の改正により対象となる施設の範囲が変わり得ることを計画素案の注に［要確認］として記載する</t>
+          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
         </is>
       </c>
     </row>
@@ -8486,40 +8512,40 @@
         <v>171</v>
       </c>
       <c r="B176" s="5" t="n">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
+          <t>24時間対応サービスの確保方策の決定</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）9
-計画素案 第5章 基本目標5</t>
+          <t>素案 第6章第2節・第4節
+見込量表（3種別）</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>北海道上川総合振興局</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>R9.4</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G176" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H176" s="6" t="inlineStr">
         <is>
-          <t>止めている成果物 計画素案（+1）</t>
+          <t>―</t>
         </is>
       </c>
       <c r="I176" s="6" t="inlineStr">
         <is>
-          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
+          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
         </is>
       </c>
     </row>
@@ -8528,17 +8554,17 @@
         <v>172</v>
       </c>
       <c r="B177" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスの確保方策の決定</t>
+          <t>代表KPIの目標値の決定</t>
         </is>
       </c>
       <c r="D177" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第2節・第4節
-見込量表（3種別）</t>
+          <t>素案 第4章第3節・第5章
+全16KPIの目標値</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
@@ -8548,7 +8574,7 @@
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="G177" s="15" t="n">
@@ -8561,54 +8587,12 @@
       </c>
       <c r="I177" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="48" customHeight="1">
-      <c r="A178" s="5" t="n">
-        <v>173</v>
-      </c>
-      <c r="B178" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="C178" s="6" t="inlineStr">
-        <is>
-          <t>代表KPIの目標値の決定</t>
-        </is>
-      </c>
-      <c r="D178" s="6" t="inlineStr">
-        <is>
-          <t>素案 第4章第3節・第5章
-全16KPIの目標値</t>
-        </is>
-      </c>
-      <c r="E178" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F178" s="5" t="inlineStr">
-        <is>
-          <t>R8.12</t>
-        </is>
-      </c>
-      <c r="G178" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H178" s="6" t="inlineStr">
-        <is>
-          <t>―</t>
-        </is>
-      </c>
-      <c r="I178" s="6" t="inlineStr">
-        <is>
           <t>代表KPIの目標値は、令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置く</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="56" customHeight="1">
-      <c r="A179" s="13" t="inlineStr">
+    <row r="178" ht="56" customHeight="1">
+      <c r="A178" s="13" t="inlineStr">
         <is>
           <t>注1）点が9以上を至急、6以上8以下を優先、5以下を通常とみます（03シート）。
 注2）「決着しない場合の当方の扱い」が空のものは、決まらないと当方の作業が止まります。 先に扱いを決めます。
@@ -8616,76 +8600,119 @@
         </is>
       </c>
     </row>
-    <row r="180"/>
-    <row r="181" ht="20" customHeight="1">
-      <c r="A181" s="3" t="inlineStr">
+    <row r="179"/>
+    <row r="180" ht="20" customHeight="1">
+      <c r="A180" s="3" t="inlineStr">
         <is>
           <t>2　資料提供依頼（資料の提供を求めるもの）　18件</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="30" customHeight="1">
-      <c r="A182" s="4" t="inlineStr">
+    <row r="181" ht="30" customHeight="1">
+      <c r="A181" s="4" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B182" s="4" t="inlineStr">
+      <c r="B181" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C182" s="4" t="inlineStr">
+      <c r="C181" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="D182" s="4" t="inlineStr">
+      <c r="D181" s="4" t="inlineStr">
         <is>
           <t>確定する主張</t>
         </is>
       </c>
-      <c r="E182" s="4" t="inlineStr">
+      <c r="E181" s="4" t="inlineStr">
         <is>
           <t>入手先</t>
         </is>
       </c>
-      <c r="F182" s="4" t="inlineStr">
+      <c r="F181" s="4" t="inlineStr">
         <is>
           <t>希望時期</t>
         </is>
       </c>
-      <c r="G182" s="4" t="inlineStr">
+      <c r="G181" s="4" t="inlineStr">
         <is>
           <t>優先</t>
         </is>
       </c>
-      <c r="H182" s="4" t="inlineStr">
+      <c r="H181" s="4" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="I182" s="4" t="inlineStr">
+      <c r="I181" s="4" t="inlineStr">
         <is>
           <t>領域</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="40" customHeight="1">
+      <c r="A182" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B182" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
+        </is>
+      </c>
+      <c r="D182" s="6" t="inlineStr">
+        <is>
+          <t>第9期の評価の完成</t>
+        </is>
+      </c>
+      <c r="E182" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F182" s="5" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="G182" s="16" t="inlineStr">
+        <is>
+          <t>最高</t>
+        </is>
+      </c>
+      <c r="H182" s="5" t="inlineStr">
+        <is>
+          <t>一部受領</t>
+        </is>
+      </c>
+      <c r="I182" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B183" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr">
         <is>
-          <t>第9期の評価の完成</t>
+          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
@@ -8698,47 +8725,47 @@
           <t>R8.8</t>
         </is>
       </c>
-      <c r="G183" s="16" t="inlineStr">
-        <is>
-          <t>最高</t>
+      <c r="G183" s="14" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H183" s="5" t="inlineStr">
         <is>
-          <t>一部受領</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B184" s="5" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
+          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G184" s="14" t="inlineStr">
@@ -8748,35 +8775,35 @@
       </c>
       <c r="H184" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B185" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
         <is>
-          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
+          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr">
@@ -8791,40 +8818,40 @@
       </c>
       <c r="H185" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>代替により解消</t>
         </is>
       </c>
       <c r="I185" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B186" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
+          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
+          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G186" s="14" t="inlineStr">
@@ -8834,35 +8861,35 @@
       </c>
       <c r="H186" s="5" t="inlineStr">
         <is>
-          <t>代替により解消</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I186" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B187" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
+          <t>事業所・施設の定員と稼働の実績</t>
         </is>
       </c>
       <c r="D187" s="6" t="inlineStr">
         <is>
-          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
+          <t>稼働率の低下の有無、定員減少の経緯</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F187" s="5" t="inlineStr">
@@ -8877,35 +8904,35 @@
       </c>
       <c r="H187" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I187" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B188" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>事業所・施設の定員と稼働の実績</t>
+          <t>未利用認定者の内訳とケアプランのサービス構成</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
         <is>
-          <t>稼働率の低下の有無、定員減少の経緯</t>
+          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F188" s="5" t="inlineStr">
@@ -8925,25 +8952,25 @@
       </c>
       <c r="I188" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B189" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>未利用認定者の内訳とケアプランのサービス構成</t>
+          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
         </is>
       </c>
       <c r="D189" s="6" t="inlineStr">
         <is>
-          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
+          <t>第9期の剰余額（現在は概算）</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
@@ -8968,30 +8995,30 @@
       </c>
       <c r="I189" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
+          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
-          <t>第9期の剰余額（現在は概算）</t>
+          <t>給付費の地域内還流の議論</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F190" s="5" t="inlineStr">
@@ -9011,25 +9038,25 @@
       </c>
       <c r="I190" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B191" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
+          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
         </is>
       </c>
       <c r="D191" s="6" t="inlineStr">
         <is>
-          <t>給付費の地域内還流の議論</t>
+          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
         </is>
       </c>
       <c r="E191" s="6" t="inlineStr">
@@ -9054,30 +9081,30 @@
       </c>
       <c r="I191" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B192" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C192" s="6" t="inlineStr">
         <is>
-          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
+          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
+          <t>サービス種別ごとの見込量の様式</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F192" s="5" t="inlineStr">
@@ -9092,40 +9119,40 @@
       </c>
       <c r="H192" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I192" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B193" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B193" s="5" t="n">
-        <v>19</v>
-      </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
+          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
         </is>
       </c>
       <c r="D193" s="6" t="inlineStr">
         <is>
-          <t>サービス種別ごとの見込量の様式</t>
+          <t>第10期の段階設計と保険料算定</t>
         </is>
       </c>
       <c r="E193" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>国の情報</t>
         </is>
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>告示後</t>
         </is>
       </c>
       <c r="G193" s="14" t="inlineStr">
@@ -9135,78 +9162,78 @@
       </c>
       <c r="H193" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I193" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>H</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B194" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B194" s="5" t="n">
-        <v>11</v>
-      </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
+          <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>第10期の段階設計と保険料算定</t>
+          <t>圏域別の分析、圏域設定の見直し</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>美瑛町・3町</t>
         </is>
       </c>
       <c r="F194" s="5" t="inlineStr">
         <is>
-          <t>告示後</t>
-        </is>
-      </c>
-      <c r="G194" s="14" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G194" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I194" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B195" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>小学校区と日常生活圏域の対応関係</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D195" s="6" t="inlineStr">
         <is>
-          <t>圏域別の分析、圏域設定の見直し</t>
+          <t>評価の枠組みの整理</t>
         </is>
       </c>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t>美瑛町・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F195" s="5" t="inlineStr">
@@ -9226,35 +9253,35 @@
       </c>
       <c r="I195" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B196" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C196" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>見える化システムD49の指標定義</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
         <is>
-          <t>評価の枠組みの整理</t>
+          <t>地域差指数の分解の可否</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>見える化システム・厚生労働省</t>
         </is>
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G196" s="15" t="inlineStr">
@@ -9264,40 +9291,40 @@
       </c>
       <c r="H196" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I196" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B197" s="5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD49の指標定義</t>
+          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
         </is>
       </c>
       <c r="D197" s="6" t="inlineStr">
         <is>
-          <t>地域差指数の分解の可否</t>
+          <t>会議資料・委員会資料の記述の正確性</t>
         </is>
       </c>
       <c r="E197" s="6" t="inlineStr">
         <is>
-          <t>見える化システム・厚生労働省</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>随時</t>
         </is>
       </c>
       <c r="G197" s="15" t="inlineStr">
@@ -9307,83 +9334,83 @@
       </c>
       <c r="H197" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I197" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B198" s="5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C198" s="6" t="inlineStr">
         <is>
-          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>会議資料・委員会資料の記述の正確性</t>
+          <t>中重度・軽度の認定率の推移</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>見える化システム</t>
         </is>
       </c>
       <c r="F198" s="5" t="inlineStr">
         <is>
-          <t>随時</t>
-        </is>
-      </c>
-      <c r="G198" s="15" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G198" s="17" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H198" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I198" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B199" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+          <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
       <c r="D199" s="6" t="inlineStr">
         <is>
-          <t>中重度・軽度の認定率の推移</t>
+          <t>世帯構成の現状</t>
         </is>
       </c>
       <c r="E199" s="6" t="inlineStr">
         <is>
-          <t>見える化システム</t>
+          <t>総務省・3町</t>
         </is>
       </c>
       <c r="F199" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>公表後</t>
         </is>
       </c>
       <c r="G199" s="17" t="inlineStr">
@@ -9398,55 +9425,12 @@
       </c>
       <c r="I199" s="5" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="200" ht="40" customHeight="1">
-      <c r="A200" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B200" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C200" s="6" t="inlineStr">
-        <is>
-          <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
-        </is>
-      </c>
-      <c r="D200" s="6" t="inlineStr">
-        <is>
-          <t>世帯構成の現状</t>
-        </is>
-      </c>
-      <c r="E200" s="6" t="inlineStr">
-        <is>
-          <t>総務省・3町</t>
-        </is>
-      </c>
-      <c r="F200" s="5" t="inlineStr">
-        <is>
-          <t>公表後</t>
-        </is>
-      </c>
-      <c r="G200" s="17" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="H200" s="5" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I200" s="5" t="inlineStr">
-        <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="28" customHeight="1">
-      <c r="A201" s="13" t="inlineStr">
+    <row r="200" ht="28" customHeight="1">
+      <c r="A200" s="13" t="inlineStr">
         <is>
           <t>注）03シートの確認事項が「決定」を求めるものであるのに対し、本表は「資料の提供」を求めるものです。資料が届かない場合の扱いは04シートの区分で示しています。</t>
         </is>
@@ -9454,12 +9438,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A179:I179"/>
+    <mergeCell ref="A180:I180"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A178:I178"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A181:I181"/>
+    <mergeCell ref="A200:I200"/>
     <mergeCell ref="A4:I4"/>
-    <mergeCell ref="A201:I201"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9545,7 +9529,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>85件</t>
+          <t>84件</t>
         </is>
       </c>
     </row>
@@ -9908,7 +9892,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>170件</t>
+          <t>169件</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -10138,7 +10122,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>条番号のみを記載し項番号及び号番号は記載しない。記載事項の点検は条文の番号ではなく記載事項の内容を単位として行い、条文を確認できていない箇所は［要確認］として残す。【令和8年10月14日】社会福祉法等の一部を改正する法律案要綱を確認したことにより、改正後の第117条第2項第3号・第4号、第3項第4号・第5号、第5項及び第14項の号及び項が確定した。引き続き必要なのは、①改正後の条文及び新旧対照表（要綱は改正事項の要旨であり条文の文言を確認できない）、②附則第3条から第77条までの経過措置（有料老人ホームの登録制に係る経過措置の内容）、③改正に係らない号（第2項第1号・第2号、第3項第1号から第3号まで）の条文である</t>
+          <t>条番号のみを記載し項番号及び号番号は記載しない。記載事項の点検は条文の番号ではなく記載事項の内容を単位として行い、条文を確認できていない箇所は［要確認］として残す。【令和8年10月14日】社会福祉法等の一部を改正する法律案要綱を確認したことにより、改正後の第117条第2項第3号・第4号、第3項第4号・第5号、第5項及び第14項の号及び項が確定した。引き続き必要なのは、①改正後の条文及び新旧対照表（要綱は改正事項の要旨であり条文の文言を確認できない）、②附則第3条から第77条までの経過措置（有料老人ホームの登録制に係る経過措置の内容）、③改正に係らない号（第2項第1号・第2号、第3項第1号から第3号まで）の条文である。【令和8年10月15日　大きく解決】社会福祉法等の一部を改正する法律案の新旧対照条文（全353頁）を確認した。改正後の介護保険法第117条（第2項第3号・第4号、第3項第3号・第4号・第4号の2・第5号・第6号・第7号・第9号、第5項、第9項、第14項）、第115条の48（支援会議）、第118条第2項・第8項・第9項並びに第120条の3から第120条の5まで（協議会）の内容が確定した。介護保険法の改正は第3条関係（令和9年4月1日又は1年6月以内）と第4条関係（2年以内又は3年以内）の2つに分かれる。新たに分かった主なものは、①第3項第3号は改正前からあり、量が第2項第3号へ移ったうえで費用の額及び保険料の水準が残ること（量は定めるものとされる事項、費用の額及び保険料の水準は定めるよう努めるものとされる事項）、②第3項第9号（入居定員総数）は改正前からあり、第5項第1号（勘案事項）との二重の構造であること、③第5項及び第14項の対象はいずれも第2項第1号から第3号までであること、④第115条の48の会議は改正後「支援会議」と称し構成員として地域包括支援センターが明示されること、⑤第118条第2項により都道府県介護保険事業支援計画にも中長期的な推計が定めるものとされること、⑥第117条第3項第6号・第7号及び第115条の49に指定登録施設介護支援の事業が加わること（3年以内）である。計画素案15箇所に反映した。引き続き必要なのは、①参照条文（001685804）の条文の内容（受領したものは画像であり文字の層がないため読み取れない）、②附則第3条から第77条までの経過措置、③認知症基本法ほか関係法令の条文（確認No.149）である</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -10313,7 +10297,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す</t>
+          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す。【令和8年10月15日】新旧対照条文により社会福祉法第106条の12（新設）の内容を確かめた。小規模市町村が本事業を実施する場合、介護保険法第122条の2（第3項を除く。地域支援事業に係る国の交付金）並びに第123条第3項及び第4項（都道府県の負担）の規定の適用について、第122条の2第1項の「費用」から本事業として行う社会福祉法第106条の6第2項第3号イに掲げる事業に要する費用を除き、第123条第4項の「費用」から同条第2項第1号イ及び第3号ロに掲げる事業に要する費用を除くこととされている。重層的支援体制整備事業（社会福祉法第106条の4）と同じ構造である。除かれるのは国の交付金及び都道府県の負担の対象となる費用であり、当該費用は社会福祉法による交付金等により支弁されることとなる。除かれる事業の内容（第106条の6第2項第1号イ・第3号イ・第3号ロ）は確かめていない。小規模市町村の基準は厚生労働省令で定められるため、①（該当の有無）は引き続き確認を要する</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -10338,7 +10322,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>現行の指定の区分により特定施設入居者生活介護の見込量を算定し、定義の改正により対象となる施設の範囲が変わり得ることを計画素案の注に［要確認］として記載する</t>
+          <t>現行の指定の区分により特定施設入居者生活介護の見込量を算定し、定義の改正により対象となる施設の範囲が変わり得ることを計画素案の注に［要確認］として記載する。【令和8年10月15日】新旧対照条文により、現行の第8条第11項が「有料老人ホームその他厚生労働省令で定める施設であって、第20項に規定する地域密着型特定施設でないもの」であり、改正により「有料老人ホーム」が「老人福祉法第29条の18第5項に規定する登録有料老人ホーム」に置き換わることを確かめた。すなわち登録有料老人ホームを定義に加えるものではなく、登録を受けない有料老人ホームは特定施設に当たらなくなる。計画素案 第1章第9節2の記述を「定義に加える」から「有料老人ホームを登録有料老人ホームに改める」に是正した</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -10353,7 +10337,7 @@
           <t>注1）「据え置き（区分A）」は、資料の受領を待たずに当方の側で確定できるものです。
 注2）「既定値で進める」は、決着しない場合の扱いを置けているため決定を待たずに作業を進められるものです。決定を受けた時点で見直します。
 注3）ここに現れないもの（既定値を置けていない確認事項）は、扱いを決めること自体が翌日の作業になります。02シートを見ます。
-注4）既定値のとおり計画素案へ反映し終えたもの164件（確認事項No.1・No.2・No.3・No.4・No.5・No.6・No.7・No.8・No.9・No.10・No.11・No.12・No.13・No.14・No.15・No.16・No.17・No.18・No.19・No.20・No.21・No.22・No.23・No.24・No.25・No.26・No.27・No.28・No.29・No.30・No.31・No.33・No.34・No.35・No.36・No.38・No.39・No.40・No.42・No.43・No.45・No.46・No.47・No.48・No.50・No.51・No.52・No.53・No.54・No.55・No.56・No.57・No.58・No.59・No.60・No.61・No.63・No.64・No.65・No.66・No.67・No.68・No.69・No.70・No.73・No.74・No.75・No.76・No.77・No.78・No.79・No.80・No.81・No.82・No.83・No.84・No.85・No.86・No.88・No.89・No.90・No.91・No.92・No.93・No.94・No.95・No.96・No.97・No.98・No.99・No.100・No.101・No.102・No.103・No.104・No.105・No.106・No.107・No.108・No.109・No.110・No.111・No.112・No.113・No.114・No.115・No.116・No.117・No.118・No.119・No.120・No.121・No.122・No.123・No.124・No.125・No.126・No.127・No.128・No.129・No.130・No.131・No.132・No.133・No.136・No.137・No.138・No.139・No.140・No.141・No.142・No.143・No.144・No.145・No.146・No.147・No.148・No.149・No.150・No.151・No.152・No.153・No.154・No.156・No.157・No.158・No.159・No.160・No.161・No.162・No.163・No.164・No.165・No.166・No.167・No.169・No.170・No.171・No.172・No.173・No.174・No.175・No.176・No.177）は、作業としては終わっているため本表から除いています。ご決定はなお待っています。</t>
+注4）既定値のとおり計画素案へ反映し終えたもの163件（確認事項No.2・No.3・No.4・No.5・No.6・No.7・No.8・No.9・No.10・No.11・No.12・No.13・No.14・No.15・No.16・No.17・No.18・No.19・No.20・No.21・No.22・No.23・No.24・No.25・No.26・No.27・No.28・No.29・No.30・No.31・No.33・No.34・No.35・No.36・No.38・No.39・No.40・No.42・No.43・No.45・No.46・No.47・No.48・No.50・No.51・No.52・No.53・No.54・No.55・No.56・No.57・No.58・No.59・No.60・No.61・No.63・No.64・No.65・No.66・No.67・No.68・No.69・No.70・No.73・No.74・No.75・No.76・No.77・No.78・No.79・No.80・No.81・No.82・No.83・No.84・No.85・No.86・No.88・No.89・No.90・No.91・No.92・No.93・No.94・No.95・No.96・No.97・No.98・No.99・No.100・No.101・No.102・No.103・No.104・No.105・No.106・No.107・No.108・No.109・No.110・No.111・No.112・No.113・No.114・No.115・No.116・No.117・No.118・No.119・No.120・No.121・No.122・No.123・No.124・No.125・No.126・No.127・No.128・No.129・No.130・No.131・No.132・No.133・No.136・No.137・No.138・No.139・No.140・No.141・No.142・No.143・No.144・No.145・No.146・No.147・No.148・No.149・No.150・No.151・No.152・No.153・No.154・No.156・No.157・No.158・No.159・No.160・No.161・No.162・No.163・No.164・No.165・No.166・No.167・No.169・No.170・No.171・No.172・No.173・No.174・No.175・No.176・No.177）は、作業としては終わっているため本表から除いています。ご決定はなお待っています。</t>
         </is>
       </c>
     </row>
@@ -10459,7 +10443,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>条番号のみを記載し項番号及び号番号は記載しない。記載事項の点検は条文の番号ではなく記載事項の内容を単位として行い、条文を確認できていない箇所は［要確認］として残す。【令和8年10月14日】社会福祉法等の一部を改正する法律案要綱を確認したことにより、改正後の第117条第2項第3号・第4号、第3項第4号・第5号、第5項及び第14項の号及び項が確定した。引き続き必要なのは、①改正後の条文及び新旧対照表（要綱は改正事項の要旨であり条文の文言を確認できない）、②附則第3条から第77条までの経過措置（有料老人ホームの登録制に係る経過措置の内容）、③改正に係らない号（第2項第1号・第2号、第3項第1号から第3号まで）の条文である</t>
+          <t>条番号のみを記載し項番号及び号番号は記載しない。記載事項の点検は条文の番号ではなく記載事項の内容を単位として行い、条文を確認できていない箇所は［要確認］として残す。【令和8年10月14日】社会福祉法等の一部を改正する法律案要綱を確認したことにより、改正後の第117条第2項第3号・第4号、第3項第4号・第5号、第5項及び第14項の号及び項が確定した。引き続き必要なのは、①改正後の条文及び新旧対照表（要綱は改正事項の要旨であり条文の文言を確認できない）、②附則第3条から第77条までの経過措置（有料老人ホームの登録制に係る経過措置の内容）、③改正に係らない号（第2項第1号・第2号、第3項第1号から第3号まで）の条文である。【令和8年10月15日　大きく解決】社会福祉法等の一部を改正する法律案の新旧対照条文（全353頁）を確認した。改正後の介護保険法第117条（第2項第3号・第4号、第3項第3号・第4号・第4号の2・第5号・第6号・第7号・第9号、第5項、第9項、第14項）、第115条の48（支援会議）、第118条第2項・第8項・第9項並びに第120条の3から第120条の5まで（協議会）の内容が確定した。介護保険法の改正は第3条関係（令和9年4月1日又は1年6月以内）と第4条関係（2年以内又は3年以内）の2つに分かれる。新たに分かった主なものは、①第3項第3号は改正前からあり、量が第2項第3号へ移ったうえで費用の額及び保険料の水準が残ること（量は定めるものとされる事項、費用の額及び保険料の水準は定めるよう努めるものとされる事項）、②第3項第9号（入居定員総数）は改正前からあり、第5項第1号（勘案事項）との二重の構造であること、③第5項及び第14項の対象はいずれも第2項第1号から第3号までであること、④第115条の48の会議は改正後「支援会議」と称し構成員として地域包括支援センターが明示されること、⑤第118条第2項により都道府県介護保険事業支援計画にも中長期的な推計が定めるものとされること、⑥第117条第3項第6号・第7号及び第115条の49に指定登録施設介護支援の事業が加わること（3年以内）である。計画素案15箇所に反映した。引き続き必要なのは、①参照条文（001685804）の条文の内容（受領したものは画像であり文字の層がないため読み取れない）、②附則第3条から第77条までの経過措置、③認知症基本法ほか関係法令の条文（確認No.149）である</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -10634,7 +10618,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す</t>
+          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す。【令和8年10月15日】新旧対照条文により社会福祉法第106条の12（新設）の内容を確かめた。小規模市町村が本事業を実施する場合、介護保険法第122条の2（第3項を除く。地域支援事業に係る国の交付金）並びに第123条第3項及び第4項（都道府県の負担）の規定の適用について、第122条の2第1項の「費用」から本事業として行う社会福祉法第106条の6第2項第3号イに掲げる事業に要する費用を除き、第123条第4項の「費用」から同条第2項第1号イ及び第3号ロに掲げる事業に要する費用を除くこととされている。重層的支援体制整備事業（社会福祉法第106条の4）と同じ構造である。除かれるのは国の交付金及び都道府県の負担の対象となる費用であり、当該費用は社会福祉法による交付金等により支弁されることとなる。除かれる事業の内容（第106条の6第2項第1号イ・第3号イ・第3号ロ）は確かめていない。小規模市町村の基準は厚生労働省令で定められるため、①（該当の有無）は引き続き確認を要する</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -10835,7 +10819,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>確認事項173件／資料提供依頼18件</t>
+          <t>確認事項172件／資料提供依頼18件</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -10860,7 +10844,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>173件／合わない なし</t>
+          <t>172件／合わない なし</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -749,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1234,20 +1234,38 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>b224cc4</t>
+          <t>dcf60dd</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等改正法の法律案要綱（原典）の受領点検と計画素案への反映</t>
+          <t>改正後の条文及び特定地域の原典受領点検と計画素案への反映</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
       <c r="E23" s="6" t="inlineStr"/>
       <c r="F23" s="6" t="inlineStr"/>
     </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>b224cc4</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>社会福祉法等改正法の法律案要綱（原典）の受領点検と計画素案への反映</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
@@ -1255,12 +1273,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1272,7 +1290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I200"/>
+  <dimension ref="A1:I201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1304,7 +1322,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　確認事項（決定を求めるもの）　172件</t>
+          <t>1　確認事項（決定を求めるもの）　173件</t>
         </is>
       </c>
     </row>
@@ -1573,22 +1591,21 @@
         <v>6</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設の必要利用定員総数を定めるか</t>
+          <t>認知症基本法第13条の市町村認知症施策推進計画をどう扱うか</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定
-計画素案 第6章第4節4</t>
+          <t>計画素案 第1章第2節・第5章 基本目標2</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -1606,7 +1623,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設の必要利用定員総数を定めないまま概算する</t>
+          <t>案B（3町がそれぞれ市町村計画を策定する）のまま素案に反映する</t>
         </is>
       </c>
     </row>
@@ -1615,21 +1632,22 @@
         <v>7</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法第13条の市町村認知症施策推進計画をどう扱うか</t>
+          <t>第6章第2節の見込量の表に何を掲げるか</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第2節・第5章 基本目標2</t>
+          <t>計画素案 第6章第2節・第3節
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1647,7 +1665,7 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>案B（3町がそれぞれ市町村計画を策定する）のまま素案に反映する</t>
+          <t>計画素案 第6章第2節に利用回（日）数を、第3節2に介護予防・日常生活支援総合事業及び一般介護予防事業の量の見込みを掲げた現行のまま確定する。必要利用定員総数の第2節への再掲は行わない（第4節4による）</t>
         </is>
       </c>
     </row>
@@ -1656,27 +1674,28 @@
         <v>8</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の見込量の表に何を掲げるか</t>
+          <t>東川町の施設整備・サービス提供方針</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節・第3節
-サービス見込量の算定</t>
+          <t>サービス見込量 第2次概算
+計画素案 第2章第2節・第6章第2節・第4節
+構成町の意見への回答 6</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・東川町</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G13" s="15" t="n">
@@ -1684,12 +1703,12 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）／法定記載事項 法第117条に直結（+2）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節に利用回（日）数を、第3節2に介護予防・日常生活支援総合事業及び一般介護予防事業の量の見込みを掲げた現行のまま確定する。必要利用定員総数の第2節への再掲は行わない（第4節4による）</t>
+          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残す</t>
         </is>
       </c>
     </row>
@@ -1698,23 +1717,23 @@
         <v>9</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>東川町の施設整備・サービス提供方針</t>
+          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
           <t>サービス見込量 第2次概算
-計画素案 第2章第2節・第6章第2節・第4節
-構成町の意見への回答 6</t>
+将来推計 第3段階
+計画素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>発注者・東川町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1732,7 +1751,7 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ、本文は［要協議］のまま残す</t>
+          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
         </is>
       </c>
     </row>
@@ -1741,11 +1760,11 @@
         <v>10</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
+          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1775,7 +1794,7 @@
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。令和8年度の水準を反映した場合の差（月額＋99円）は据え置きの一覧に示す</t>
+          <t>単価を令和7年度で固定する（安全側）。実績の趨勢を置いた場合の差は据え置きの一覧及び計画素案 第6章第6節2に示す</t>
         </is>
       </c>
     </row>
@@ -1784,18 +1803,18 @@
         <v>11</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
+          <t>令和22年度までの中長期推計をどこまで算定するか</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
           <t>サービス見込量 第2次概算
 将来推計 第3段階
-計画素案 第6章第3節・第6節</t>
+計画素案 第2章第8節・第6章第2節</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1818,7 +1837,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>単価を令和7年度で固定する（安全側）。実績の趨勢を置いた場合の差は据え置きの一覧及び計画素案 第6章第6節2に示す</t>
+          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
         </is>
       </c>
     </row>
@@ -1827,23 +1846,22 @@
         <v>12</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>令和22年度までの中長期推計をどこまで算定するか</t>
+          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
           <t>サービス見込量 第2次概算
-将来推計 第3段階
-計画素案 第2章第8節・第6章第2節</t>
+計画素案 第6章第2節・第4節</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1861,7 +1879,7 @@
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>計画本文に掲げる中長期推計は令和17年度・令和22年度とし、見込量・給付費・保険料のいずれも単価を令和7年度で固定して算定する</t>
+          <t>供給の制約（人材）を見込量に反映しない（需要のみで算定する）</t>
         </is>
       </c>
     </row>
@@ -1870,22 +1888,22 @@
         <v>13</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>介護人材の確保状況を供給の制約として見込量に反映するか</t>
+          <t>町別の人口の将来推計を計画本文に掲げるか</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
           <t>サービス見込量 第2次概算
-計画素案 第6章第2節・第4節</t>
+計画素案 第2章第1節・第6章第1節</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -1903,7 +1921,7 @@
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>供給の制約（人材）を見込量に反映しない（需要のみで算定する）</t>
+          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
         </is>
       </c>
     </row>
@@ -1912,11 +1930,11 @@
         <v>14</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>町別の人口の将来推計を計画本文に掲げるか</t>
+          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1945,7 +1963,7 @@
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>町別の将来推計は計画本文に掲げない（令和8年9月10日の了承のとおり）</t>
+          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
         </is>
       </c>
     </row>
@@ -1954,17 +1972,16 @@
         <v>15</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>153</v>
+        <v>7</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法を案Cからコーホート変化率法に改めるか</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算
-計画素案 第2章第1節・第6章第1節</t>
+          <t>素案 第1章第6節・第3章第4節</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1974,20 +1991,20 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G20" s="15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）</t>
+          <t>期限 超過（R8.9）（+2）／法定記載事項 法第117条に直結（+2）</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>人口の将来推計の方法は案Cのままとする。コーホート変化率法には採らない</t>
+          <t>第9期の自己評価と北海道への報告の実績を確認できないものとして、第10期の進行管理に自己評価の仕組みを置く</t>
         </is>
       </c>
     </row>
@@ -1996,16 +2013,17 @@
         <v>16</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>7</v>
+        <v>105</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>施策反映を行うか。行う場合の対象と歯止め</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第6節・第3章第4節</t>
+          <t>サービス見込量の算定
+計画素案 第4章第3節・第6章第2節</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -2023,12 +2041,12 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／法定記載事項 法第117条に直結（+2）</t>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）／月額への効き 最大13円（施策の達成目標のご判断）（+1）</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績を確認できないものとして、第10期の進行管理に自己評価の仕組みを置く</t>
+          <t>施策反映を行わないまま概算する（安全側）</t>
         </is>
       </c>
     </row>
@@ -2037,17 +2055,17 @@
         <v>17</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行うか。行う場合の対象と歯止め</t>
+          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定
-計画素案 第4章第3節・第6章第2節</t>
+          <t>将来推計 第2段階
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -2065,12 +2083,12 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）／月額への効き 最大13円（施策の達成目標のご判断）（+1）</t>
+          <t>期限 超過（R8.9）（+2）／月額への効き 最大327円（第10期の介護報酬改定率）（+4）／当方で動かせるか 国の告示・公布待ち（-2）</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行わないまま概算する（安全側）</t>
+          <t>1人1月あたり給付費は令和7年度で固定して概算する（単価の趨勢を織り込まないことによる効きは計画素案 第6章第6節2に掲げる）</t>
         </is>
       </c>
     </row>
@@ -2079,17 +2097,18 @@
         <v>18</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
+          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階
-サービス見込量の算定</t>
+          <t>計画素案 第6章第6節
+将来推計 第3段階
+保険料算定式の国の様式との対照</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -2099,7 +2118,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G23" s="15" t="n">
@@ -2107,12 +2126,12 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／月額への効き 最大327円（第10期の介護報酬改定率）（+4）／当方で動かせるか 国の告示・公布待ち（-2）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 保険料（+2）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費は令和7年度で固定して概算する（単価の趨勢を織り込まないことによる効きは計画素案 第6章第6節2に掲げる）</t>
+          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
         </is>
       </c>
     </row>
@@ -2121,18 +2140,17 @@
         <v>19</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の交付見込額の保険料収納必要額からの控除</t>
+          <t>給付適正化計画の位置づけ（案Bの採用）と毎年度の目標の記載場所</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第6節
-将来推計 第3段階
-保険料算定式の国の様式との対照</t>
+          <t>計画素案 第1章第2節・第5章 基本目標5・資料5
+給付適正化計画の位置づけと追加検討事項</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -2150,12 +2168,12 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 保険料（+2）／止めている成果物 計画素案（+1）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）／法定記載事項 法第117条に直結（+2）</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）から保険者機能強化推進事業費及び保険者努力支援事業費を除く現行の方法を採り、保険料収納必要額からの控除は行わない（二重控除を避けるため）</t>
+          <t>給付適正化計画の位置づけは案B（第9期と同じく施策として置き、施策名のかっこ書きで第7期給付適正化計画であることを示す）のままとする（令和8年9月10日 了承済み）</t>
         </is>
       </c>
     </row>
@@ -2164,17 +2182,17 @@
         <v>20</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけ（案Bの採用）と毎年度の目標の記載場所</t>
+          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第2節・第5章 基本目標5・資料5
-給付適正化計画の位置づけと追加検討事項</t>
+          <t>サービス見込量の算定
+計画素案 第5章 基本目標5・第6章第2節</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -2192,12 +2210,12 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）／法定記載事項 法第117条に直結（+2）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）／月額への効き 最大327円（第10期の介護報酬改定率）（+4）／当方で動かせるか 国の告示・公布待ち（-2）</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけは案B（第9期と同じく施策として置き、施策名のかっこ書きで第7期給付適正化計画であることを示す）のままとする（令和8年9月10日 了承済み）</t>
+          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
         </is>
       </c>
     </row>
@@ -2206,27 +2224,27 @@
         <v>21</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>110</v>
+        <v>33</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
+          <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定
-計画素案 第5章 基本目標5・第6章第2節</t>
+          <t>第10期の段階設計
+保険料の算定</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>国の情報</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>告示後</t>
         </is>
       </c>
       <c r="G26" s="15" t="n">
@@ -2234,12 +2252,12 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）／月額への効き 最大327円（第10期の介護報酬改定率）（+4）／当方で動かせるか 国の告示・公布待ち（-2）</t>
+          <t>止めている成果物 保険料（+2）／月額への効き 最大290円（第10期の政令）（+4）／当方で動かせるか 国の告示・公布待ち（-2）</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
+          <t>第9期条例の16段階・乗率（公費軽減前）を据え置いて算定し、政令の公布後に再算定する</t>
         </is>
       </c>
     </row>
@@ -2248,40 +2266,41 @@
         <v>22</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階）</t>
+          <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>第10期の段階設計
-保険料の算定</t>
+          <t>計画骨子案
+施策体系新旧対照表
+計画素案 第4章・第5章</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>告示後</t>
+          <t>R8.9.2</t>
         </is>
       </c>
       <c r="G27" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>止めている成果物 保険料（+2）／月額への効き 最大290円（第10期の政令）（+4）／当方で動かせるか 国の告示・公布待ち（-2）</t>
+          <t>期限 超過（R8.9.2）（+2）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>第9期条例の16段階・乗率（公費軽減前）を据え置いて算定し、政令の公布後に再算定する</t>
+          <t>中間報告・施策体系新旧対照表・骨子案は提出した内容のままとする</t>
         </is>
       </c>
     </row>
@@ -2290,28 +2309,27 @@
         <v>23</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>中間報告・施策体系新旧対照表・骨子案のご確認</t>
+          <t>社会資源一覧の従業員数の重複計上の扱い</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>計画骨子案
-施策体系新旧対照表
-計画素案 第4章・第5章</t>
+          <t>従業員数の重複計上の整理
+計画素案 第2章第3節・第6章第2節</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>R8.9.2</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G28" s="15" t="n">
@@ -2319,12 +2337,12 @@
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9.2）（+2）／止めている成果物 計画素案（+1）</t>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>中間報告・施策体系新旧対照表・骨子案は提出した内容のままとする</t>
+          <t>社会資源一覧の従業員数は施設単位の実人数を用い、延べの値は用いない（同一の施設が複数のサービスで登録されている分を除く）。介護人材実態調査の採用者数・離職者数も同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
         </is>
       </c>
     </row>
@@ -2333,22 +2351,22 @@
         <v>24</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数の重複計上の扱い</t>
+          <t>認定に要する日数の扱い</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>従業員数の重複計上の整理
-計画素案 第2章第3節・第6章第2節</t>
+          <t>中間報告 第3節
+計画素案 第2章・第5章</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -2366,7 +2384,7 @@
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>社会資源一覧の従業員数は施設単位の実人数を用い、延べの値は用いない（同一の施設が複数のサービスで登録されている分を除く）。介護人材実態調査の採用者数・離職者数も同一法人の重複計上分を除いた採用83人・離職65人を用いる</t>
+          <t>令和8年8月28日受領の集計帳票による</t>
         </is>
       </c>
     </row>
@@ -2375,17 +2393,17 @@
         <v>25</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>認定に要する日数の扱い</t>
+          <t>代表KPI H15の分母の定義</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>中間報告 第3節
-計画素案 第2章・第5章</t>
+          <t>計画素案 第4章 資料1
+中間報告 第3節</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2408,7 +2426,7 @@
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月28日受領の集計帳票による</t>
+          <t>代表KPI H15の分母は標準給付費見込額とする（受託者案）</t>
         </is>
       </c>
     </row>
@@ -2417,17 +2435,17 @@
         <v>26</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H15の分母の定義</t>
+          <t>計画値を0としたサービスに実績がある2件</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章 資料1
-中間報告 第3節</t>
+          <t>見える化総括表の受領点検 02シート
+計画素案 第4章</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -2450,7 +2468,7 @@
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H15の分母は標準給付費見込額とする（受託者案）</t>
+          <t>第10期は計画値を0とせず、算定値を置く（対計画比が算出され評価の対象となるようにする）</t>
         </is>
       </c>
     </row>
@@ -2459,11 +2477,11 @@
         <v>27</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>計画値を0としたサービスに実績がある2件</t>
+          <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -2492,7 +2510,7 @@
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>第10期は計画値を0とせず、算定値を置く（対計画比が算出され評価の対象となるようにする）</t>
+          <t>定期巡回・随時対応型訪問介護看護は自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
         </is>
       </c>
     </row>
@@ -2501,17 +2519,18 @@
         <v>28</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護の第10期の取扱い</t>
+          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>見える化総括表の受領点検 02シート
-計画素案 第4章</t>
+          <t>人口推計の基礎の変更_総合戦略ベース
+将来推計 第1〜3段階
+計画素案 第2章第1節・第6章</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -2534,7 +2553,7 @@
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護は自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
         </is>
       </c>
     </row>
@@ -2543,18 +2562,18 @@
         <v>29</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎を総合戦略とするご指示への対応</t>
+          <t>広域連合において行うべき事業の優先順位</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎の変更_総合戦略ベース
-将来推計 第1〜3段階
-計画素案 第2章第1節・第6章</t>
+          <t>広域連合において行うべき事業の優先順位
+介護高齢者福祉サービスガイド_構成案
+計画素案 第5章・第6章第3節2</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2577,7 +2596,7 @@
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎は案C（総合戦略＋住民基本台帳の趨勢）のままとする。案A・案Bは対比の記録として残す</t>
+          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
         </is>
       </c>
     </row>
@@ -2586,18 +2605,18 @@
         <v>30</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位</t>
+          <t>サービスガイドに掲載する事業所の範囲</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位
-介護高齢者福祉サービスガイド_構成案
-計画素案 第5章・第6章第3節2</t>
+          <t>介護高齢者福祉サービスガイド_構成案
+3町の社会資源一覧との突合 06シート
+計画素案 第2章第3節</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -2620,7 +2639,7 @@
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>広域連合において行うべき事業の優先順位は当方の案のままとする</t>
+          <t>サービスガイドに掲載する事業所の範囲は北海道の指定事業所一覧（最新のもの）による</t>
         </is>
       </c>
     </row>
@@ -2629,18 +2648,18 @@
         <v>31</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>サービスガイドに掲載する事業所の範囲</t>
+          <t>算定方法の国の様式との整合（点検結果）</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>介護高齢者福祉サービスガイド_構成案
-3町の社会資源一覧との突合 06シート
-計画素案 第2章第3節</t>
+          <t>算定方法の整合確認（国と見える化）
+将来推計 第2段階・第3段階
+計画素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2663,7 +2682,7 @@
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>サービスガイドに掲載する事業所の範囲は北海道の指定事業所一覧（最新のもの）による</t>
+          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
         </is>
       </c>
     </row>
@@ -2672,18 +2691,18 @@
         <v>32</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>算定方法の国の様式との整合（点検結果）</t>
+          <t>見える化システムの自然体推計の再出力のお願い</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>算定方法の整合確認（国と見える化）
-将来推計 第2段階・第3段階
-計画素案 第6章第3節・第6節</t>
+          <t>将来推計 第3段階 01シート
+算定方法の整合確認 04シート・07シート
+計画素案 第6章第3節</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2706,7 +2725,7 @@
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>当方の算定のまま進め、国の様式との対応は協議用の資料に対照表として掲げる</t>
+          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
         </is>
       </c>
     </row>
@@ -2715,18 +2734,18 @@
         <v>33</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの自然体推計の再出力のお願い</t>
+          <t>交付金の全国順位の計画本文への掲載</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階 01シート
-算定方法の整合確認 04シート・07シート
-計画素案 第6章第3節</t>
+          <t>計画素案 第3章第4節
+図表集 27シート
+交付金評価指標と全国集計の受領点検 04シート</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -2749,7 +2768,7 @@
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>再出力を受けられないものとして、当方の要介護度別の算定による見込量を用いる</t>
+          <t>交付金の全国順位は計画本文に掲載せず、策定委員会資料にとどめる（確認事項No.71のとおり）</t>
         </is>
       </c>
     </row>
@@ -2758,23 +2777,22 @@
         <v>34</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>交付金の全国順位の計画本文への掲載</t>
+          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第3章第4節
-図表集 27シート
-交付金評価指標と全国集計の受領点検 04シート</t>
+          <t>ケアプラン点検実施要領（案）
+計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
@@ -2792,7 +2810,7 @@
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>交付金の全国順位は計画本文に掲載せず、策定委員会資料にとどめる（確認事項No.71のとおり）</t>
+          <t>ケアプラン点検実施要領（案）は協議資料にとどめ素案に入れない</t>
         </is>
       </c>
     </row>
@@ -2801,56 +2819,14 @@
         <v>35</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）の確定に要する事項</t>
+          <t>代表KPIと改善事項の再整理案</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>ケアプラン点検実施要領（案）
-計画素案 第5章 基本目標5</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G40" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
-        </is>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>ケアプラン点検実施要領（案）は協議資料にとどめ素案に入れない</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="48" customHeight="1">
-      <c r="A41" s="5" t="n">
-        <v>36</v>
-      </c>
-      <c r="B41" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>代表KPIと改善事項の再整理案</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>計画素案 第4章第3節・第5章・資料1
 骨子案 第4節
@@ -2858,6 +2834,48 @@
 代表KPIの振替案と確認事項の精査</t>
         </is>
       </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G40" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>代表KPIと改善事項は当方の再整理案のままとする</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="48" customHeight="1">
+      <c r="A41" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>76</v>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>介護リームスから抽出できる項目</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第4章第3節・資料1
+図表集31シート</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
@@ -2878,7 +2896,7 @@
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>代表KPIと改善事項は当方の再整理案のままとする</t>
+          <t>介護リームスから抽出できないものとして、代表KPI H03は未算定のままとする</t>
         </is>
       </c>
     </row>
@@ -2887,22 +2905,22 @@
         <v>37</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>介護リームスから抽出できる項目</t>
+          <t>北海道の評価指標⑥の団体別の公表値</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
           <t>計画素案 第4章第3節・資料1
-図表集31シート</t>
+内部確認結果への対応整理 04</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -2920,7 +2938,7 @@
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>介護リームスから抽出できないものとして、代表KPI H03は未算定のままとする</t>
+          <t>北海道の評価指標⑥の団体別の公表値を引用できないものとして、当該指標は計画本文に掲げない</t>
         </is>
       </c>
     </row>
@@ -2929,22 +2947,22 @@
         <v>38</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥の団体別の公表値</t>
+          <t>グループホームびえいの郷の定員減の時期</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・資料1
-内部確認結果への対応整理 04</t>
+          <t>計画素案 第2章第3節・第6章第2節
+将来推計 第2・第3段階</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・美瑛町</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -2962,7 +2980,7 @@
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標⑥の団体別の公表値を引用できないものとして、当該指標は計画本文に掲げない</t>
+          <t>北海道の名簿の定員のまま概算する</t>
         </is>
       </c>
     </row>
@@ -2971,22 +2989,22 @@
         <v>39</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>グループホームびえいの郷の定員減の時期</t>
+          <t>第5章の施策数の見直しの範囲</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第3節・第6章第2節
-将来推計 第2・第3段階</t>
+          <t>計画素案 第5章
+骨子案 第5節</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>発注者・美瑛町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -3004,7 +3022,7 @@
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>北海道の名簿の定員のまま概算する</t>
+          <t>第9期の19施策の体系を維持する（施策数を見直さない）</t>
         </is>
       </c>
     </row>
@@ -3013,17 +3031,18 @@
         <v>40</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第5章の施策数の見直しの範囲</t>
+          <t>代表KPI H16のデータ源（国保連の給付実績の明細情報）</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章
-骨子案 第5節</t>
+          <t>計画素案 第4章第3節・第5章 基本目標5・資料1
+給付実績データの受領点検 05
+内部確認結果への対応整理 04・09</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -3046,7 +3065,7 @@
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>第9期の19施策の体系を維持する（施策数を見直さない）</t>
+          <t>国保連の給付実績の明細を受領できないものとして、代表KPI H16は地域密着型サービスに限った確認件数を代理指標とする</t>
         </is>
       </c>
     </row>
@@ -3055,18 +3074,17 @@
         <v>41</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H16のデータ源（国保連の給付実績の明細情報）</t>
+          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・第5章 基本目標5・資料1
-給付実績データの受領点検 05
-内部確認結果への対応整理 04・09</t>
+          <t>地域密着型サービス基準省令の論点整理
+計画素案 第6章第4節</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -3089,7 +3107,7 @@
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>国保連の給付実績の明細を受領できないものとして、代表KPI H16は地域密着型サービスに限った確認件数を代理指標とする</t>
+          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
         </is>
       </c>
     </row>
@@ -3098,22 +3116,23 @@
         <v>42</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>大雪地区広域連合の指定地域密着型サービスの基準条例のご提供</t>
+          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>地域密着型サービス基準省令の論点整理
-計画素案 第6章第4節</t>
+          <t>計画素案 第2章第3節6
+計画素案 第6章第4節4
+地域密着型サービス基準省令の論点整理</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
@@ -3131,7 +3150,7 @@
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>基準条例を受領できないものとして、省令の基準により論点を整理するにとどめ、計画素案には条例の内容を書かない</t>
+          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
         </is>
       </c>
     </row>
@@ -3140,23 +3159,23 @@
         <v>43</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の共同生活住居数と、くるみの郷の定員</t>
+          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第3節6
-計画素案 第6章第4節4
-地域密着型サービス基準省令の論点整理</t>
+          <t>計画素案 第6章第4節1
+計画素案 第6章第2節2（2）
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
@@ -3174,7 +3193,7 @@
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員は99人＋［要確認］のまま掲げる</t>
+          <t>省令上の類型を計画に掲げないまま概算する</t>
         </is>
       </c>
     </row>
@@ -3183,18 +3202,18 @@
         <v>44</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
+          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第4節1
-計画素案 第6章第2節2（2）
-サービス見込量の算定</t>
+          <t>サービス見込量の算定
+将来推計 第3段階
+計画素案 第6章第2節・第3節・第6節</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -3217,7 +3236,7 @@
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>省令上の類型を計画に掲げないまま概算する</t>
+          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）により、要介護度別の伸びで概算する</t>
         </is>
       </c>
     </row>
@@ -3226,18 +3245,17 @@
         <v>45</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
+          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定
-将来推計 第3段階
-計画素案 第6章第2節・第3節・第6節</t>
+          <t>計画素案 第6章第2節2
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -3260,7 +3278,7 @@
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）により、要介護度別の伸びで概算する</t>
+          <t>計画素案 第6章第2節の表は当方の算定（令和7年度の実績に要介護度別の認定者数の伸びを乗じたもの）による値とし、見える化システムの自然体推計による値は第6節2に対比として掲げる</t>
         </is>
       </c>
     </row>
@@ -3269,17 +3287,17 @@
         <v>46</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
+          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節2
-サービス見込量の算定</t>
+          <t>サービス見込量の算定
+計画素案 第6章第2節2</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -3302,7 +3320,7 @@
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節の表は当方の算定（令和7年度の実績に要介護度別の認定者数の伸びを乗じたもの）による値とし、見える化システムの自然体推計による値は第6節2に対比として掲げる</t>
+          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
         </is>
       </c>
     </row>
@@ -3311,16 +3329,17 @@
         <v>47</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの令和8年度の月数と予防訪問看護の計上</t>
+          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
           <t>サービス見込量の算定
+将来推計 第3段階
 計画素案 第6章第2節2</t>
         </is>
       </c>
@@ -3344,7 +3363,7 @@
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
-          <t>②は確認できないものとして、令和8年度を基準年度に用いない</t>
+          <t>令和8年度を基準年度に用いず、季節補正も行わないまま概算する</t>
         </is>
       </c>
     </row>
@@ -3353,23 +3372,22 @@
         <v>48</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
+          <t>施設・居住系の実績の減少を将来へ延長するか</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
           <t>サービス見込量の算定
-将来推計 第3段階
-計画素案 第6章第2節2</t>
+計画素案 第6章第4節4</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
@@ -3387,7 +3405,7 @@
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節補正も行わないまま概算する</t>
+          <t>施設・居住系の実績の減少を将来へ延長しないまま概算する</t>
         </is>
       </c>
     </row>
@@ -3396,22 +3414,22 @@
         <v>49</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長するか</t>
+          <t>地域ケア会議関係資料の取扱いの確認</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定
-計画素案 第6章第4節4</t>
+          <t>地域ケア会議の受領点検とKPI設計案
+計画素案 第5章 基本目標2</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
@@ -3429,7 +3447,7 @@
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長しないまま概算する</t>
+          <t>転載を禁ずる旨の記載がある2件は成果品に用いず、原典（厚労省の市町村マニュアル及び別冊事例集）のみを引く</t>
         </is>
       </c>
     </row>
@@ -3438,17 +3456,17 @@
         <v>50</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議関係資料の取扱いの確認</t>
+          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の受領点検とKPI設計案
-計画素案 第5章 基本目標2</t>
+          <t>将来推計 第2段階
+計画素案 第6章第2節・第4節</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -3471,7 +3489,7 @@
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>転載を禁ずる旨の記載がある2件は成果品に用いず、原典（厚労省の市町村マニュアル及び別冊事例集）のみを引く</t>
+          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
         </is>
       </c>
     </row>
@@ -3480,17 +3498,16 @@
         <v>51</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系サービス利用者数の伸びの参考シートの有無</t>
+          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階
-計画素案 第6章第2節・第4節</t>
+          <t>計画素案 第2章第4節・第4章第3節</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
@@ -3513,7 +3530,7 @@
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>参考シートを受領できないものとして、施設・居住系の伸びは当方の要介護度別の算定（令和7年度の利用率を固定）による。画面の伸びの選択は「令和6年度→令和7年度の伸び」とする</t>
+          <t>在宅生活改善調査の結果は「在宅で困難を抱える方の状況」として引き、在宅の認定者全体の割合としては引かない</t>
         </is>
       </c>
     </row>
@@ -3522,16 +3539,17 @@
         <v>52</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果を在宅の認定者全体に当てはめないこと</t>
+          <t>区域を越えた施設利用の扱い</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第4節・第4章第3節</t>
+          <t>計画素案 第6章第4節4
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
@@ -3554,7 +3572,7 @@
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査の結果は「在宅で困難を抱える方の状況」として引き、在宅の認定者全体の割合としては引かない</t>
+          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
         </is>
       </c>
     </row>
@@ -3563,17 +3581,17 @@
         <v>53</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>区域を越えた施設利用の扱い</t>
+          <t>見込量の伸びを要介護度別に改めてよいか</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第4節4
-サービス見込量の算定</t>
+          <t>サービス見込量の算定
+計画素案 第6章第2節</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
@@ -3596,7 +3614,7 @@
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
+          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
         </is>
       </c>
     </row>
@@ -3605,17 +3623,17 @@
         <v>54</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを要介護度別に改めてよいか</t>
+          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定
-計画素案 第6章第2節</t>
+          <t>計画素案 第1章第2節・第5章 基本目標2
+認知症施策推進計画の位置づけと見込量への反映</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
@@ -3638,7 +3656,7 @@
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
+          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
         </is>
       </c>
     </row>
@@ -3647,17 +3665,17 @@
         <v>55</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文ほか認知症施策の根拠資料のご提供</t>
+          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第2節・第5章 基本目標2
-認知症施策推進計画の位置づけと見込量への反映</t>
+          <t>サービス見込量の算定
+計画素案 第6章第2節</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
@@ -3680,7 +3698,7 @@
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>認知症基本法の条文を受領できないものとして、計画素案には条番号のみを書き項番号は［要確認］のまま残す</t>
+          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
         </is>
       </c>
     </row>
@@ -3689,17 +3707,17 @@
         <v>56</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>151</v>
+        <v>30</v>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
+          <t>施設入所者と在宅者を分けた要介護度の変化</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定
-計画素案 第6章第2節</t>
+          <t>重度化の速度の前提
+保険料と施策評価の他団体比較 05シート</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
@@ -3709,7 +3727,7 @@
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G61" s="15" t="n">
@@ -3717,12 +3735,12 @@
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）／止めている成果物 計画素案（+1）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 保険料（+2）</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
+          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
         </is>
       </c>
     </row>
@@ -3731,17 +3749,17 @@
         <v>57</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けた要介護度の変化</t>
+          <t>第9段階の乗率の経緯</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提
-保険料と施策評価の他団体比較 05シート</t>
+          <t>第10期の段階設計
+保険料の所得段階と低所得者軽減の検証 08シート</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -3764,7 +3782,7 @@
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>施設入所者と在宅者を分けずに算定する（分けるための要介護度の変化のデータがないため）</t>
+          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
         </is>
       </c>
     </row>
@@ -3773,22 +3791,21 @@
         <v>58</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第9段階の乗率の経緯</t>
+          <t>上川管内の保険者の所得段階数と乗率</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>第10期の段階設計
-保険料の所得段階と低所得者軽減の検証 08シート</t>
+          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
@@ -3806,7 +3823,7 @@
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>経緯を確認できないものとして、第9期条例の乗率をそのまま用いる</t>
+          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
         </is>
       </c>
     </row>
@@ -3815,21 +3832,23 @@
         <v>59</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率</t>
+          <t>所得段階別被保険者数の実績と収納率</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>保険料の所得段階と低所得者軽減の検証 05シート</t>
+          <t>所得段階別被保険者数の推計
+保険料の算定
+素案 第6章第7節</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
@@ -3847,7 +3866,7 @@
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>上川管内の保険者の所得段階数と乗率の比較は掲げない</t>
+          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
         </is>
       </c>
     </row>
@@ -3856,23 +3875,22 @@
         <v>60</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の実績と収納率</t>
+          <t>令和9年4月に新設される区分を見込量に立てるか</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>所得段階別被保険者数の推計
-保険料の算定
-素案 第6章第7節</t>
+          <t>サービス見込量 第2次概算
+計画素案 第1章第9節・第6章第2節・第4節</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
@@ -3885,12 +3903,12 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 保険料（+2）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）／当方で動かせるか 国の告示・公布待ち（-2）</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の所得段階別構成比と予定収納率0.99による</t>
+          <t>令和9年4月新設の3区分を0として立てる</t>
         </is>
       </c>
     </row>
@@ -3899,27 +3917,26 @@
         <v>61</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+          <t>医療法等の一部を改正する法律による介護保険法の改正の施行の状況</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第2次概算
-計画素案 第1章第9節・第6章第2節・第4節</t>
+          <t>計画素案 第1章第8節・第1章第9節1・第1章第9節6</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="G66" s="15" t="n">
@@ -3927,12 +3944,12 @@
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 概算（+3）／止めている成果物 計画素案（+1）／当方で動かせるか 国の告示・公布待ち（-2）</t>
+          <t>止めている成果物 計画素案（+1）／法定記載事項 法第117条に直結（+2）</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月新設の3区分を0として立てる</t>
+          <t>医療との連携は第5章 基本目標1及び第6章第5節の記述により扱い、医療法の協議の結果の考慮については施行の時期を確認できていない旨を［要確認］として記載する</t>
         </is>
       </c>
     </row>
@@ -3941,17 +3958,17 @@
         <v>62</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>181</v>
+        <v>4</v>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第117条ほか関係法令の条文のご提供</t>
+          <t>代表KPI H07・H08・H12・H16の代理指標</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第2節・第1章第5節・第1章第8節・第6章第5節
-計画素案の記載内容の洗い出しと対比 02シート</t>
+          <t>素案 第4章第3節・資料1
+全16KPIの4項目</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -3961,20 +3978,20 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G67" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>止めている成果物 計画素案（+1）／法定記載事項 法第117条に直結（+2）</t>
+          <t>期限 超過（R8.8）（+2）</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>条番号のみを記載し項番号及び号番号は記載しない。記載事項の点検は条文の番号ではなく記載事項の内容を単位として行い、条文を確認できていない箇所は［要確認］として残す。【令和8年10月14日】社会福祉法等の一部を改正する法律案要綱を確認したことにより、改正後の第117条第2項第3号・第4号、第3項第4号・第5号、第5項及び第14項の号及び項が確定した。引き続き必要なのは、①改正後の条文及び新旧対照表（要綱は改正事項の要旨であり条文の文言を確認できない）、②附則第3条から第77条までの経過措置（有料老人ホームの登録制に係る経過措置の内容）、③改正に係らない号（第2項第1号・第2号、第3項第1号から第3号まで）の条文である。【令和8年10月15日　大きく解決】社会福祉法等の一部を改正する法律案の新旧対照条文（全353頁）を確認した。改正後の介護保険法第117条（第2項第3号・第4号、第3項第3号・第4号・第4号の2・第5号・第6号・第7号・第9号、第5項、第9項、第14項）、第115条の48（支援会議）、第118条第2項・第8項・第9項並びに第120条の3から第120条の5まで（協議会）の内容が確定した。介護保険法の改正は第3条関係（令和9年4月1日又は1年6月以内）と第4条関係（2年以内又は3年以内）の2つに分かれる。新たに分かった主なものは、①第3項第3号は改正前からあり、量が第2項第3号へ移ったうえで費用の額及び保険料の水準が残ること（量は定めるものとされる事項、費用の額及び保険料の水準は定めるよう努めるものとされる事項）、②第3項第9号（入居定員総数）は改正前からあり、第5項第1号（勘案事項）との二重の構造であること、③第5項及び第14項の対象はいずれも第2項第1号から第3号までであること、④第115条の48の会議は改正後「支援会議」と称し構成員として地域包括支援センターが明示されること、⑤第118条第2項により都道府県介護保険事業支援計画にも中長期的な推計が定めるものとされること、⑥第117条第3項第6号・第7号及び第115条の49に指定登録施設介護支援の事業が加わること（3年以内）である。計画素案15箇所に反映した。引き続き必要なのは、①参照条文（001685804）の条文の内容（受領したものは画像であり文字の層がないため読み取れない）、②附則第3条から第77条までの経過措置、③認知症基本法ほか関係法令の条文（確認No.149）である</t>
+          <t>代表KPI H07・H08・H12・H16は代理指標への振替案のとおりとする</t>
         </is>
       </c>
     </row>
@@ -3983,17 +4000,17 @@
         <v>63</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16の代理指標</t>
+          <t>第9期の施策・事業実績</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>素案 第4章第3節・資料1
-全16KPIの4項目</t>
+          <t>素案 第3章第2節・第3節・第4節
+妥当性検証報告書 12シート</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -4016,7 +4033,7 @@
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>代表KPI H07・H08・H12・H16は代理指標への振替案のとおりとする</t>
+          <t>第9期の施策・事業実績を受領できないものとして、公表資料（交付金の評価結果・総合事業の実施状況に関する調査・年報）により評価する</t>
         </is>
       </c>
     </row>
@@ -4025,17 +4042,17 @@
         <v>64</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績</t>
+          <t>3調査の点検事項の取扱い</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>素案 第3章第2節・第3節・第4節
-妥当性検証報告書 12シート</t>
+          <t>素案 第2章第5・6節
+H06・H11・H13・H14の基準値</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -4058,7 +4075,7 @@
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>第9期の施策・事業実績を受領できないものとして、公表資料（交付金の評価結果・総合事業の実施状況に関する調査・年報）により評価する</t>
+          <t>3調査の点検事項は当方の判定のままとする</t>
         </is>
       </c>
     </row>
@@ -4067,17 +4084,17 @@
         <v>65</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項の取扱い</t>
+          <t>会議日程とパブリックコメントの期間</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第5・6節
-H06・H11・H13・H14の基準値</t>
+          <t>委員会資料原案
+パブリックコメント資料</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -4100,7 +4117,7 @@
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>3調査の点検事項は当方の判定のままとする</t>
+          <t>会議日程及びパブリックコメントの期間は仕様書５の工程による</t>
         </is>
       </c>
     </row>
@@ -4109,22 +4126,21 @@
         <v>66</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>会議日程とパブリックコメントの期間</t>
+          <t>キックオフ会議資料への工程表の反映</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>委員会資料原案
-パブリックコメント資料</t>
+          <t>キックオフ会議資料</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
@@ -4142,7 +4158,7 @@
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>会議日程及びパブリックコメントの期間は仕様書５の工程による</t>
+          <t>現行の工程表のまま進める</t>
         </is>
       </c>
     </row>
@@ -4151,26 +4167,27 @@
         <v>67</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料への工程表の反映</t>
+          <t>類似保険者との比較分析の対象</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>キックオフ会議資料</t>
+          <t>素案 第2章第2節
+分析資料</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G72" s="15" t="n">
@@ -4178,12 +4195,12 @@
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.8）（+2）</t>
+          <t>期限 超過（R8.9）（+2）</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>現行の工程表のまま進める</t>
+          <t>類似保険者との比較は公表されている同規模保険者40団体による</t>
         </is>
       </c>
     </row>
@@ -4192,17 +4209,17 @@
         <v>68</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較分析の対象</t>
+          <t>交付金の評価調書</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第2節
-分析資料</t>
+          <t>素案 第3章第4節
+追加調査報告書 02シート</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
@@ -4225,7 +4242,7 @@
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較は公表されている同規模保険者40団体による</t>
+          <t>評価調書を受領できないものとして、得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できない旨を注記する</t>
         </is>
       </c>
     </row>
@@ -4234,17 +4251,17 @@
         <v>69</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価調書</t>
+          <t>調査の対象者範囲と回収率</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>素案 第3章第4節
-追加調査報告書 02シート</t>
+          <t>素案 第2章第4〜6節
+クロス集計表</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
@@ -4267,7 +4284,7 @@
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
-          <t>評価調書を受領できないものとして、得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できない旨を注記する</t>
+          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
         </is>
       </c>
     </row>
@@ -4276,17 +4293,17 @@
         <v>70</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>調査の対象者範囲と回収率</t>
+          <t>介護人材実態調査の採用者数・退職者数</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第4〜6節
-クロス集計表</t>
+          <t>素案 第4章第3節
+H14の基準値</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
@@ -4309,7 +4326,7 @@
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>現に収録している対象者範囲・回収率による。設問ごとに分母が異なることを注記する</t>
+          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
         </is>
       </c>
     </row>
@@ -4318,22 +4335,22 @@
         <v>71</v>
       </c>
       <c r="B76" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>介護人材実態調査の採用者数・退職者数</t>
+          <t>町別の人口・世帯データ</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>素案 第4章第3節
-H14の基準値</t>
+          <t>素案 第2章第1節
+図1・図2・図3</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
@@ -4351,7 +4368,7 @@
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
-          <t>採用83人・離職65人（同一法人の重複を除いた値）による。代表KPI H14は、分母となる各年9月30日現在の在籍者数を確認できないため未算定のままとする</t>
+          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
         </is>
       </c>
     </row>
@@ -4360,17 +4377,18 @@
         <v>72</v>
       </c>
       <c r="B77" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>町別の人口・世帯データ</t>
+          <t>日常生活圏域別のデータ</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第1節
-図1・図2・図3</t>
+          <t>素案 第1章第7節・第2章
+圏域別分析資料
+調査クロス集計・分析 01・18シート</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
@@ -4393,7 +4411,7 @@
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>住民基本台帳（各年1月1日現在）の町別人口により本文を確定する</t>
+          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
         </is>
       </c>
     </row>
@@ -4402,23 +4420,22 @@
         <v>73</v>
       </c>
       <c r="B78" s="5" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域別のデータ</t>
+          <t>骨子案の内容の確認</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第7節・第2章
-圏域別分析資料
-調査クロス集計・分析 01・18シート</t>
+          <t>骨子案
+素案の次稿</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
@@ -4436,7 +4453,7 @@
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域を3町（3圏域）とする案のまま概算する</t>
+          <t>骨子案は提出した内容のままとする</t>
         </is>
       </c>
     </row>
@@ -4445,22 +4462,22 @@
         <v>74</v>
       </c>
       <c r="B79" s="5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>骨子案の内容の確認</t>
+          <t>北海道の評価指標の読替えの考え方</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
         <is>
-          <t>骨子案
-素案の次稿</t>
+          <t>素案 第1章第6節
+追加調査報告書 04シート</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
@@ -4478,7 +4495,7 @@
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>骨子案は提出した内容のままとする</t>
+          <t>北海道の評価指標の読替えは当方の案のままとする</t>
         </is>
       </c>
     </row>
@@ -4487,22 +4504,22 @@
         <v>75</v>
       </c>
       <c r="B80" s="5" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標の読替えの考え方</t>
+          <t>令和4年度 健康とくらしの調査の集計表</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第6節
-追加調査報告書 04シート</t>
+          <t>調査クロス集計・分析 14シート
+素案 第2章第4節</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
@@ -4520,7 +4537,7 @@
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>北海道の評価指標の読替えは当方の案のままとする</t>
+          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
         </is>
       </c>
     </row>
@@ -4529,17 +4546,17 @@
         <v>76</v>
       </c>
       <c r="B81" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>令和4年度 健康とくらしの調査の集計表</t>
+          <t>調査対象者の範囲の確認</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析 14シート
-素案 第2章第4節</t>
+          <t>調査クロス集計・分析 13・14シート
+H06・H11の基準値</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -4562,7 +4579,7 @@
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>令和4年度の集計表を受領できないものとして、前回比較は第9期計画の本文に掲げられた指標に限る</t>
+          <t>現に収録している調査対象者の範囲による</t>
         </is>
       </c>
     </row>
@@ -4571,17 +4588,17 @@
         <v>77</v>
       </c>
       <c r="B82" s="5" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>調査対象者の範囲の確認</t>
+          <t>交付金評価の令和6年・令和7年調査の結果</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析 13・14シート
-H06・H11の基準値</t>
+          <t>素案 第3章第4節
+妥当性検証 所見18・19</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
@@ -4604,7 +4621,7 @@
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
-          <t>現に収録している調査対象者の範囲による</t>
+          <t>公表されている全国集計の値による</t>
         </is>
       </c>
     </row>
@@ -4613,17 +4630,17 @@
         <v>78</v>
       </c>
       <c r="B83" s="5" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の令和6年・令和7年調査の結果</t>
+          <t>令和7年度の給付費の集計が一致しない</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
         <is>
-          <t>素案 第3章第4節
-妥当性検証 所見18・19</t>
+          <t>給付実績データの受領点検
+将来推計 第2・3段階</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
@@ -4646,7 +4663,7 @@
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>公表されている全国集計の値による</t>
+          <t>令和8年9月25日の再提供により決着済み。再提供を受けたファイルの値（3町合計と円単位一致）による</t>
         </is>
       </c>
     </row>
@@ -4655,17 +4672,17 @@
         <v>79</v>
       </c>
       <c r="B84" s="5" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の給付費の集計が一致しない</t>
+          <t>計画作成支援ツールの実績値シートの確認</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
         <is>
-          <t>給付実績データの受領点検
-将来推計 第2・3段階</t>
+          <t>給付実績データの受領点検 04シート
+将来推計 第3段階</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
@@ -4688,7 +4705,7 @@
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月25日の再提供により決着済み。再提供を受けたファイルの値（3町合計と円単位一致）による</t>
+          <t>総括表（保険者単位）を用い、計画作成支援ツールの実績値シートは比較のためにのみ用いる</t>
         </is>
       </c>
     </row>
@@ -4697,17 +4714,18 @@
         <v>80</v>
       </c>
       <c r="B85" s="5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールの実績値シートの確認</t>
+          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
         <is>
-          <t>給付実績データの受領点検 04シート
-将来推計 第3段階</t>
+          <t>総合事業実施状況調査の受領点検
+素案 第3章第1節・第2節
+H05の基準値</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
@@ -4730,7 +4748,7 @@
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
-          <t>総括表（保険者単位）を用い、計画作成支援ツールの実績値シートは比較のためにのみ用いる</t>
+          <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値による</t>
         </is>
       </c>
     </row>
@@ -4739,18 +4757,18 @@
         <v>81</v>
       </c>
       <c r="B86" s="5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査（令和6年度）の確認</t>
+          <t>年報・月報の受領に伴う確認</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>総合事業実施状況調査の受領点検
-素案 第3章第1節・第2節
-H05の基準値</t>
+          <t>年報月報の受領点検
+将来推計 第3段階
+素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
@@ -4773,7 +4791,7 @@
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>収録済みの令和6年度の総合事業の実施状況に関する調査の値による</t>
+          <t>受領済みの年報・月報の値による</t>
         </is>
       </c>
     </row>
@@ -4782,18 +4800,16 @@
         <v>82</v>
       </c>
       <c r="B87" s="5" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>年報・月報の受領に伴う確認</t>
+          <t>月報の値の接続のずれ（ご報告）</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
         <is>
-          <t>年報月報の受領点検
-将来推計 第3段階
-素案 第6章第3節・第6節</t>
+          <t>年報月報の受領点検 04シート</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -4816,7 +4832,7 @@
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
-          <t>受領済みの年報・月報の値による</t>
+          <t>月報の値の接続のずれは記録として残し、計画本文には用いない</t>
         </is>
       </c>
     </row>
@@ -4825,16 +4841,17 @@
         <v>83</v>
       </c>
       <c r="B88" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれ（ご報告）</t>
+          <t>令和6年度決算書の受領に伴う確認</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>年報月報の受領点検 04シート</t>
+          <t>令和6年度決算書の受領点検 03シート
+素案 第6章第3節・第6節</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
@@ -4857,7 +4874,7 @@
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
-          <t>月報の値の接続のずれは記録として残し、計画本文には用いない</t>
+          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
         </is>
       </c>
     </row>
@@ -4866,17 +4883,18 @@
         <v>84</v>
       </c>
       <c r="B89" s="5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領に伴う確認</t>
+          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
         <is>
-          <t>令和6年度決算書の受領点検 03シート
-素案 第6章第3節・第6節</t>
+          <t>基金条例の確認 02シート
+素案 第6章第6節
+将来推計 第3段階</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
@@ -4899,7 +4917,7 @@
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
-          <t>名称・科目は令和6年度決算書の表記による（総額に影響しない）</t>
+          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合の1億円あたりの月額への効きを併記する</t>
         </is>
       </c>
     </row>
@@ -4908,18 +4926,17 @@
         <v>85</v>
       </c>
       <c r="B90" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金の積立ての上限と取崩方針</t>
+          <t>議事録の文書プロパティに個人名が再度入る</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>基金条例の確認 02シート
-素案 第6章第6節
-将来推計 第3段階</t>
+          <t>中間報告会議議事録
+業務工程管理表</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
@@ -4942,7 +4959,7 @@
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業財政調整基金を取り崩さないものとして算定する（安全側）。取り崩す場合の1億円あたりの月額への効きを併記する</t>
+          <t>議事録は作成者名を落として再出力する（当方で対応する）</t>
         </is>
       </c>
     </row>
@@ -4951,11 +4968,11 @@
         <v>86</v>
       </c>
       <c r="B91" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>議事録の文書プロパティに個人名が再度入る</t>
+          <t>議事録の表記に関するご提案3件</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -4984,7 +5001,7 @@
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
-          <t>議事録は作成者名を落として再出力する（当方で対応する）</t>
+          <t>議事録の表記はご提案3件のとおり改める</t>
         </is>
       </c>
     </row>
@@ -4993,17 +5010,16 @@
         <v>87</v>
       </c>
       <c r="B92" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記に関するご提案3件</t>
+          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>中間報告会議議事録
-業務工程管理表</t>
+          <t>見える化総括表の受領点検 00シート</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
@@ -5026,7 +5042,7 @@
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
-          <t>議事録の表記はご提案3件のとおり改める</t>
+          <t>他団体の集計帳票6件は成果品に用いない</t>
         </is>
       </c>
     </row>
@@ -5035,16 +5051,16 @@
         <v>88</v>
       </c>
       <c r="B93" s="5" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>令和8年8月31日受領の要介護認定集計帳票6件が他団体のもの</t>
+          <t>調整交付金の算定基礎の確認</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
         <is>
-          <t>見える化総括表の受領点検 00シート</t>
+          <t>将来推計 第3段階 00・03シート</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
@@ -5067,7 +5083,7 @@
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>他団体の集計帳票6件は成果品に用いない</t>
+          <t>現行の扱い（第9期の算定を再現し公表値6,428円と一致する扱い）による</t>
         </is>
       </c>
     </row>
@@ -5076,16 +5092,16 @@
         <v>89</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>調整交付金の算定基礎の確認</t>
+          <t>交付金の評価項目と19施策の割当て</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階 00・03シート</t>
+          <t>第9期施策別評価表 06シート</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
@@ -5108,7 +5124,7 @@
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
-          <t>現行の扱い（第9期の算定を再現し公表値6,428円と一致する扱い）による</t>
+          <t>交付金の評価項目と19施策の割当ては当方の案のままとする</t>
         </is>
       </c>
     </row>
@@ -5117,16 +5133,17 @@
         <v>90</v>
       </c>
       <c r="B95" s="5" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当て</t>
+          <t>職員個票のリストによる重複確認の可否</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
         <is>
-          <t>第9期施策別評価表 06シート</t>
+          <t>内部確認結果への対応整理 03・08
+実施済み3調査の受領点検と集計 06・07</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
@@ -5149,7 +5166,7 @@
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
-          <t>交付金の評価項目と19施策の割当ては当方の案のままとする</t>
+          <t>職員個票を突き合わせず、事業所への照会により重複を判別する</t>
         </is>
       </c>
     </row>
@@ -5158,17 +5175,17 @@
         <v>91</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>職員個票のリストによる重複確認の可否</t>
+          <t>構成町の一般会計繰入金の町別按分の方法</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>内部確認結果への対応整理 03・08
-実施済み3調査の受領点検と集計 06・07</t>
+          <t>サービス見込量の算定（R8.9.26）
+構成町の意見への回答 4</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
@@ -5178,7 +5195,7 @@
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.9.24</t>
         </is>
       </c>
       <c r="G96" s="15" t="n">
@@ -5186,12 +5203,12 @@
       </c>
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）</t>
+          <t>期限 超過（R8.9.24）（+2）</t>
         </is>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
-          <t>職員個票を突き合わせず、事業所への照会により重複を判別する</t>
+          <t>町別への按分は広域連合の規約によるものであり算定できないため、構成町の一般会計繰入金は3町計の概算のみを示す（按分の方法のご教示を受けた時点で町別までお示しする）</t>
         </is>
       </c>
     </row>
@@ -5200,27 +5217,28 @@
         <v>92</v>
       </c>
       <c r="B97" s="5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>構成町の一般会計繰入金の町別按分の方法</t>
+          <t>構成町との意見交換会の実施方法と町別データシート</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定（R8.9.26）
-構成町の意見への回答 4</t>
+          <t>意見交換会資料
+町別データシート
+構成町の意見への回答 2・3</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>R8.9.24</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G97" s="15" t="n">
@@ -5228,12 +5246,12 @@
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9.24）（+2）</t>
+          <t>期限 超過（R8.9）（+2）</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
-          <t>町別への按分は広域連合の規約によるものであり算定できないため、構成町の一般会計繰入金は3町計の概算のみを示す（按分の方法のご教示を受けた時点で町別までお示しする）</t>
+          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで進める</t>
         </is>
       </c>
     </row>
@@ -5242,18 +5260,17 @@
         <v>93</v>
       </c>
       <c r="B98" s="5" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>構成町との意見交換会の実施方法と町別データシート</t>
+          <t>町別データシートの内容と配付</t>
         </is>
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>意見交換会資料
-町別データシート
-構成町の意見への回答 2・3</t>
+          <t>町別データシート
+構成町の意見への回答 2</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
@@ -5276,7 +5293,7 @@
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
-          <t>3町合同の意見交換会（10月上旬）と町ごとの個別協議（10月中旬〜下旬）の2段構えで進める</t>
+          <t>町別データシートは現行の内容のまま配付する</t>
         </is>
       </c>
     </row>
@@ -5285,22 +5302,22 @@
         <v>94</v>
       </c>
       <c r="B99" s="5" t="n">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>町別データシートの内容と配付</t>
+          <t>成果品の統合の方針</t>
         </is>
       </c>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>町別データシート
-構成町の意見への回答 2</t>
+          <t>成果品一覧
+送付資料一覧</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
@@ -5318,7 +5335,7 @@
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
-          <t>町別データシートは現行の内容のまま配付する</t>
+          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す（現行）</t>
         </is>
       </c>
     </row>
@@ -5327,17 +5344,17 @@
         <v>95</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>成果品の統合の方針</t>
+          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>成果品一覧
-送付資料一覧</t>
+          <t>将来推計 第2段階・第3段階
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
@@ -5360,7 +5377,7 @@
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
-          <t>見込量算定の4成果品を統合報告書に束ね、元の4件も残す（現行）</t>
+          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
         </is>
       </c>
     </row>
@@ -5369,16 +5386,16 @@
         <v>96</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
+          <t>見える化システムの推計方式は基本推計でよいか</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階・第3段階
+          <t>将来推計 第2段階
 サービス見込量の算定</t>
         </is>
       </c>
@@ -5402,7 +5419,7 @@
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
+          <t>基本推計に近いP3で概算する</t>
         </is>
       </c>
     </row>
@@ -5411,11 +5428,11 @@
         <v>97</v>
       </c>
       <c r="B102" s="5" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計方式は基本推計でよいか</t>
+          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
@@ -5444,7 +5461,7 @@
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
-          <t>基本推計に近いP3で概算する</t>
+          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
         </is>
       </c>
     </row>
@@ -5453,17 +5470,16 @@
         <v>98</v>
       </c>
       <c r="B103" s="5" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
+          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
         </is>
       </c>
       <c r="D103" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階
-サービス見込量の算定</t>
+          <t>将来推計 第2段階</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
@@ -5486,7 +5502,7 @@
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
-          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
+          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ</t>
         </is>
       </c>
     </row>
@@ -5495,16 +5511,16 @@
         <v>99</v>
       </c>
       <c r="B104" s="5" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目が画面にあるか</t>
+          <t>健康とくらしの調査の個票の再提供の要否</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階</t>
+          <t>調査クロス集計・分析の更新</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
@@ -5527,7 +5543,7 @@
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
-          <t>認定者数の実績見込み値を編集する項目がないものとして、認定率の伸びに「令和6年度→令和7年度の伸び」を選ぶ</t>
+          <t>健康とくらしの調査の個票の再提供を依頼しない（成果品は収録済みで内容が確定しており、現時点で不足がない）</t>
         </is>
       </c>
     </row>
@@ -5536,16 +5552,16 @@
         <v>100</v>
       </c>
       <c r="B105" s="5" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供の要否</t>
+          <t>第1次概算を既定値のまま出してよいか</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析の更新</t>
+          <t>サービス見込量の算定</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
@@ -5568,7 +5584,7 @@
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の個票の再提供を依頼しない（成果品は収録済みで内容が確定しており、現時点で不足がない）</t>
+          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
         </is>
       </c>
     </row>
@@ -5577,16 +5593,17 @@
         <v>101</v>
       </c>
       <c r="B106" s="5" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>第1次概算を既定値のまま出してよいか</t>
+          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定</t>
+          <t>町別データシート
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
@@ -5609,7 +5626,7 @@
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
-          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
+          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
         </is>
       </c>
     </row>
@@ -5618,16 +5635,16 @@
         <v>102</v>
       </c>
       <c r="B107" s="5" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
+          <t>見える化システムの伸びの選択肢をどれとするか</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>町別データシート
+          <t>見える化システムへの入力
 サービス見込量の算定</t>
         </is>
       </c>
@@ -5651,7 +5668,7 @@
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
+          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
         </is>
       </c>
     </row>
@@ -5660,17 +5677,17 @@
         <v>103</v>
       </c>
       <c r="B108" s="5" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの伸びの選択肢をどれとするか</t>
+          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
           <t>見える化システムへの入力
-サービス見込量の算定</t>
+将来推計 第2段階</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
@@ -5693,7 +5710,7 @@
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>受領済みの画面の写しの範囲で概算し、確認できていない項目はその旨を明記する</t>
         </is>
       </c>
     </row>
@@ -5702,17 +5719,17 @@
         <v>104</v>
       </c>
       <c r="B109" s="5" t="n">
-        <v>148</v>
+        <v>60</v>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの操作手引・認証後画面の写しのご提供</t>
+          <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力
-将来推計 第2段階</t>
+          <t>将来推計 第3段階 05・06シート
+計画素案 第6章第6節</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
@@ -5722,7 +5739,7 @@
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G109" s="15" t="n">
@@ -5730,12 +5747,12 @@
       </c>
       <c r="H109" s="6" t="inlineStr">
         <is>
-          <t>期限 超過（R8.9）（+2）</t>
+          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
-          <t>受領済みの画面の写しの範囲で概算し、確認できていない項目はその旨を明記する</t>
+          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
         </is>
       </c>
     </row>
@@ -5744,17 +5761,17 @@
         <v>105</v>
       </c>
       <c r="B110" s="5" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提（受託者案）</t>
+          <t>区域内に事業所がないサービスの住民向けの記載</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第3段階 05・06シート
-計画素案 第6章第6節</t>
+          <t>介護高齢者福祉サービスガイド_構成案
+計画素案 第6章第4節</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
@@ -5777,7 +5794,7 @@
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
-          <t>当方案（単価を令和7年度で固定・施策反映を行わない・給付適正化を織り込まない・基金を取り崩さない）による。いずれも安全側であり、月額は下限に近い値となる</t>
+          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
         </is>
       </c>
     </row>
@@ -5786,17 +5803,17 @@
         <v>106</v>
       </c>
       <c r="B111" s="5" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスの住民向けの記載</t>
+          <t>成果指向型配分枠（令和8年度新設）への対応</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
         <is>
-          <t>介護高齢者福祉サービスガイド_構成案
-計画素案 第6章第4節</t>
+          <t>計画素案 第5章
+交付金評価指標と全国集計の受領点検 06シート</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
@@ -5819,7 +5836,7 @@
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
-          <t>区域内に事業所がないサービスは、区域外の事業所を利用できる旨を住民向けの記載に書く</t>
+          <t>成果指向型配分枠への対応状況を確認できないものとして、第10期の施策には位置づけず、確認でき次第加える</t>
         </is>
       </c>
     </row>
@@ -5828,17 +5845,17 @@
         <v>107</v>
       </c>
       <c r="B112" s="5" t="n">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠（令和8年度新設）への対応</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章
-交付金評価指標と全国集計の受領点検 06シート</t>
+          <t>計画素案 第1章第9節・第2章第8節・第5章・第6章第2節・第6章第4節
+ケアプラン点検実施要領</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
@@ -5861,7 +5878,7 @@
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
-          <t>成果指向型配分枠への対応状況を確認できないものとして、第10期の施策には位置づけず、確認でき次第加える</t>
+          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
         </is>
       </c>
     </row>
@@ -5870,17 +5887,18 @@
         <v>108</v>
       </c>
       <c r="B113" s="5" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節・第2章第8節・第5章・第6章第2節・第6章第4節
-ケアプラン点検実施要領</t>
+          <t>給付適正化計画の位置づけと追加検討事項 01シート
+計画素案 第5章 基本目標5・第2章第4節
+アンケート調査の分析 令和8年9月業務報告 第4節</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -5903,7 +5921,7 @@
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節2の7件の整理のまま進め、政令・省令・報酬改定の公表後に再照合する</t>
+          <t>第9期計画の本文及び前回調査の原集計表を受領できないものとして、前回調査との比較は割合のみとし、指標別の分母を確認できない旨を注記する</t>
         </is>
       </c>
     </row>
@@ -5912,18 +5930,17 @@
         <v>109</v>
       </c>
       <c r="B114" s="5" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文（電子データ）及び前回調査の原集計表の提供</t>
+          <t>介護給付費通知及び給付実績の活用による確認等</t>
         </is>
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけと追加検討事項 01シート
-計画素案 第5章 基本目標5・第2章第4節
-アンケート調査の分析 令和8年9月業務報告 第4節</t>
+          <t>給付適正化計画の位置づけと追加検討事項 02シート
+計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
@@ -5946,7 +5963,7 @@
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
-          <t>第9期計画の本文及び前回調査の原集計表を受領できないものとして、前回調査との比較は割合のみとし、指標別の分母を確認できない旨を注記する</t>
+          <t>介護給付費通知の実施状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
         </is>
       </c>
     </row>
@@ -5955,16 +5972,16 @@
         <v>110</v>
       </c>
       <c r="B115" s="5" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知及び給付実績の活用による確認等</t>
+          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけと追加検討事項 02シート
+          <t>給付適正化計画の位置づけと追加検討事項 04シート
 計画素案 第5章 基本目標5</t>
         </is>
       </c>
@@ -5988,7 +6005,7 @@
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
-          <t>介護給付費通知の実施状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
+          <t>認定調査の委託の状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
         </is>
       </c>
     </row>
@@ -5997,17 +6014,18 @@
         <v>111</v>
       </c>
       <c r="B116" s="5" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>認定調査の指定居宅介護支援事業所等への委託の状況</t>
+          <t>令和9年4月1日から義務となる2件への対応</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>給付適正化計画の位置づけと追加検討事項 04シート
-計画素案 第5章 基本目標5</t>
+          <t>計画素案 第1章第9節
+計画素案 第5章 基本目標3・4
+計画素案 第6章第4節3</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
@@ -6030,7 +6048,7 @@
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
-          <t>認定調査の委託の状況を確認できないものとして、第7期給付適正化計画には現行の取組のまま位置づける</t>
+          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
         </is>
       </c>
     </row>
@@ -6039,18 +6057,18 @@
         <v>112</v>
       </c>
       <c r="B117" s="5" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月1日から義務となる2件への対応</t>
+          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
         </is>
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節
-計画素案 第5章 基本目標3・4
-計画素案 第6章第4節3</t>
+          <t>計画素案 第6章第4節
+計画素案 第6章第2節2（2）
+地域密着型サービス基準省令の論点整理</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
@@ -6073,7 +6091,7 @@
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
-          <t>条例の対応規定を確認できないものとして、計画素案には省令の定めと対象事業所数（協力医療機関10・生産性向上委員会15）のみを書く</t>
+          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
         </is>
       </c>
     </row>
@@ -6082,23 +6100,22 @@
         <v>113</v>
       </c>
       <c r="B118" s="5" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における小規模多機能型居宅介護の定員超過の特例の取扱い</t>
+          <t>補正しても外れるサービス6件の理由</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第4節
-計画素案 第6章第2節2（2）
-地域密着型サービス基準省令の論点整理</t>
+          <t>対計画比の偏りの補正試算
+計画素案 第6章第2節2</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
@@ -6116,7 +6133,7 @@
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
-          <t>過疎地域における定員超過の特例を用いないものとして見込量を算定する</t>
+          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
         </is>
       </c>
     </row>
@@ -6125,17 +6142,16 @@
         <v>114</v>
       </c>
       <c r="B119" s="5" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れるサービス6件の理由</t>
+          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>対計画比の偏りの補正試算
-計画素案 第6章第2節2</t>
+          <t>計画素案 第1章第8節・第2章第3節6・第5章 基本目標2・第6章第2節</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
@@ -6158,7 +6174,7 @@
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
-          <t>補正しても外れる6件は趨勢ではなく供給・制度の問題として注記する</t>
+          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
         </is>
       </c>
     </row>
@@ -6167,21 +6183,22 @@
         <v>115</v>
       </c>
       <c r="B120" s="5" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>過年度の趨勢に現れない要因の扱い（認知症施策・高齢者向け住まいほか）</t>
+          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第8節・第2章第3節6・第5章 基本目標2・第6章第2節</t>
+          <t>計画素案 第5章 基本目標2
+第9期評価（施策2-5）</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
@@ -6199,7 +6216,7 @@
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
-          <t>趨勢に現れない要因は向きのみを注記し、数値には織り込まない</t>
+          <t>施策2-5の代表KPIはO2（提起された地域課題のうち翌年度の事業・予算に反映されたものの割合）とする（当方案）</t>
         </is>
       </c>
     </row>
@@ -6208,22 +6225,21 @@
         <v>116</v>
       </c>
       <c r="B121" s="5" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIを「施策化への転換率」とするか</t>
+          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2
-第9期評価（施策2-5）</t>
+          <t>計画素案 第5章 基本目標2</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
@@ -6241,7 +6257,7 @@
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
-          <t>施策2-5の代表KPIはO2（提起された地域課題のうち翌年度の事業・予算に反映されたものの割合）とする（当方案）</t>
+          <t>地域ケア会議の記録様式は協議資料にとどめ、令和9年度に整える</t>
         </is>
       </c>
     </row>
@@ -6250,16 +6266,16 @@
         <v>117</v>
       </c>
       <c r="B122" s="5" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の3町共通の記録様式を整えてよいか</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2</t>
+          <t>計画素案 第5章 基本目標2・第6章第4節4</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -6282,7 +6298,7 @@
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の記録様式は協議資料にとどめ、令和9年度に整える</t>
+          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
         </is>
       </c>
     </row>
@@ -6291,21 +6307,22 @@
         <v>118</v>
       </c>
       <c r="B123" s="5" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けて計数するか</t>
+          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2・第6章第4節4</t>
+          <t>計画素案 第5章 基本目標2
+第9期評価（施策2-5）</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
@@ -6323,7 +6340,7 @@
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
-          <t>地域ケア個別会議と地域ケア推進会議を分けずに計数する</t>
+          <t>令和7年度の実施報告書により把握できる範囲で記述する</t>
         </is>
       </c>
     </row>
@@ -6332,22 +6349,22 @@
         <v>119</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>3町の地域ケア会議の実績（令和6〜8年度）のご提供</t>
+          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
         </is>
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2
-第9期評価（施策2-5）</t>
+          <t>計画素案 第2章第1節3・第6章第1節
+将来推計 第1段階・第2段階</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F124" s="5" t="inlineStr">
@@ -6365,7 +6382,7 @@
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の実施報告書により把握できる範囲で記述する</t>
+          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
         </is>
       </c>
     </row>
@@ -6374,17 +6391,17 @@
         <v>120</v>
       </c>
       <c r="B125" s="5" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>将来推計の参考シートの認定率が総括表の認定率と一致しないこと</t>
+          <t>見える化システムの総人口の設定を案Cに改めるか</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節3・第6章第1節
-将来推計 第1段階・第2段階</t>
+          <t>将来推計 第1段階
+計画素案 第2章第1節・第6章第1節</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
@@ -6407,7 +6424,7 @@
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
-          <t>計画素案は年報による21.826％を用い、参考シートの20.84％は用いない。差は時点の違いとして注記する</t>
+          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
         </is>
       </c>
     </row>
@@ -6416,22 +6433,22 @@
         <v>121</v>
       </c>
       <c r="B126" s="5" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの総人口の設定を案Cに改めるか</t>
+          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第1段階
-計画素案 第2章第1節・第6章第1節</t>
+          <t>将来推計 第2段階
+計画素案 第6章第4節2</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F126" s="5" t="inlineStr">
@@ -6449,7 +6466,7 @@
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
-          <t>人口の設定を案Cに改める（入力値は算定済み）。改められない場合は画面の社人研推計のままとし、当方の算定との差（第1号被保険者数で＋31人から＋134人）を注記する</t>
+          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
         </is>
       </c>
     </row>
@@ -6458,22 +6475,22 @@
         <v>122</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>介護老人保健施設の令和8年度の減少をどう見るか</t>
+          <t>画面の令和7年度と年報の月平均の食い違い</t>
         </is>
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
           <t>将来推計 第2段階
-計画素案 第6章第4節2</t>
+計画素案 第6章第2節</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F127" s="5" t="inlineStr">
@@ -6491,7 +6508,7 @@
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の月報（4〜7月）は基準年度に用いず、令和7年度を基準として概算する</t>
+          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
         </is>
       </c>
     </row>
@@ -6500,17 +6517,16 @@
         <v>123</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>画面の令和7年度と年報の月平均の食い違い</t>
+          <t>計画素案の未確定箇所の表示の統一</t>
         </is>
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階
-計画素案 第6章第2節</t>
+          <t>計画素案（策定委員会用）</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
@@ -6533,7 +6549,7 @@
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
-          <t>年報の値を用いる（総括表・給付費と内的整合が取れているため）。画面の値は用いず、2％以上食い違う3区分を注記する</t>
+          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとする</t>
         </is>
       </c>
     </row>
@@ -6542,16 +6558,17 @@
         <v>124</v>
       </c>
       <c r="B129" s="5" t="n">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所の表示の統一</t>
+          <t>計画素案 第2章第1節に町別の図を加えるか</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>計画素案（策定委員会用）</t>
+          <t>計画素案 第2章第1節
+図表集</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
@@ -6574,7 +6591,7 @@
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>未確定箇所の表示は［要協議］［要確認］［要内訳］の3種のままとする</t>
+          <t>計画素案 第2章第1節に町別の図を加えない。加筆分は協議用の資料にとどめる</t>
         </is>
       </c>
     </row>
@@ -6583,17 +6600,17 @@
         <v>125</v>
       </c>
       <c r="B130" s="5" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えるか</t>
+          <t>中長期推計を令和12・27・32年度まで広げるか</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節
-図表集</t>
+          <t>見える化システムへの入力
+計画素案 第6章第1節・第3節</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
@@ -6616,7 +6633,7 @@
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第2章第1節に町別の図を加えない。加筆分は協議用の資料にとどめる</t>
+          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
         </is>
       </c>
     </row>
@@ -6625,17 +6642,17 @@
         <v>126</v>
       </c>
       <c r="B131" s="5" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>中長期推計を令和12・27・32年度まで広げるか</t>
+          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
         </is>
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力
-計画素案 第6章第1節・第3節</t>
+          <t>計画素案 第4章第3節・第5章 基本目標3・資料1
+アンケート調査の集計分析報告書 02・14シート</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
@@ -6658,7 +6675,7 @@
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
-          <t>算定の側だけを令和12・27・32年度まで広げ、計画本文に掲げる中長期は令和17年度・令和22年度のままとする</t>
+          <t>設問ごとの有効回答を分母とし、町別の値は掲げない（令和8年9月25日に是正済み）</t>
         </is>
       </c>
     </row>
@@ -6667,22 +6684,22 @@
         <v>127</v>
       </c>
       <c r="B132" s="5" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査による代表KPI2項目の分母と町別の示し方</t>
+          <t>東川町の通いの場の整備と担い手の確保</t>
         </is>
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第4章第3節・第5章 基本目標3・資料1
-アンケート調査の集計分析報告書 02・14シート</t>
+          <t>計画素案 第3章第1節・第5章 基本目標2
+10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・東川町</t>
         </is>
       </c>
       <c r="F132" s="5" t="inlineStr">
@@ -6700,7 +6717,7 @@
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
-          <t>設問ごとの有効回答を分母とし、町別の値は掲げない（令和8年9月25日に是正済み）</t>
+          <t>現状のまま（東川町の整備を見込まない）第10期の目標値を置く</t>
         </is>
       </c>
     </row>
@@ -6709,16 +6726,16 @@
         <v>128</v>
       </c>
       <c r="B133" s="5" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>東川町の通いの場の整備と担い手の確保</t>
+          <t>東川町の認知症サポーター養成講座の実施状況</t>
         </is>
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第3章第1節・第5章 基本目標2
+          <t>計画素案 第5章 基本目標2
 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
@@ -6742,7 +6759,7 @@
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
-          <t>現状のまま（東川町の整備を見込まない）第10期の目標値を置く</t>
+          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
         </is>
       </c>
     </row>
@@ -6751,11 +6768,11 @@
         <v>129</v>
       </c>
       <c r="B134" s="5" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>東川町の認知症サポーター養成講座の実施状況</t>
+          <t>東川町のチームオレンジ事業の位置づけ</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
@@ -6784,7 +6801,7 @@
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
+          <t>東川町の取組として記述し3町展開は記述しない</t>
         </is>
       </c>
     </row>
@@ -6793,11 +6810,11 @@
         <v>130</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>東川町のチームオレンジ事業の位置づけ</t>
+          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
@@ -6808,7 +6825,7 @@
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>発注者・東川町</t>
+          <t>発注者・美瑛町</t>
         </is>
       </c>
       <c r="F135" s="5" t="inlineStr">
@@ -6826,7 +6843,7 @@
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t>東川町の取組として記述し3町展開は記述しない</t>
+          <t>令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残す</t>
         </is>
       </c>
     </row>
@@ -6835,11 +6852,11 @@
         <v>131</v>
       </c>
       <c r="B136" s="5" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の認知症初期集中支援推進事業の再開の見通し</t>
+          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
@@ -6868,7 +6885,7 @@
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
-          <t>令和7年度の実施状況のとおり記述し、再開の時期は［要協議］のまま残す</t>
+          <t>美瑛町の取組として記述し3町展開は記述しない</t>
         </is>
       </c>
     </row>
@@ -6877,16 +6894,16 @@
         <v>132</v>
       </c>
       <c r="B137" s="5" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域リハビリテーション活動支援事業の3町展開</t>
+          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
         </is>
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2
+          <t>計画素案 第6章第4節・第6章第5節
 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
@@ -6910,7 +6927,7 @@
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の取組として記述し3町展開は記述しない</t>
+          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
         </is>
       </c>
     </row>
@@ -6919,16 +6936,16 @@
         <v>133</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の地域密着型介護老人福祉施設の整備方針</t>
+          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第4節・第6章第5節
+          <t>計画素案 第5章 基本目標2
 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
@@ -6952,7 +6969,7 @@
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
-          <t>現定員の据え置き案を掲げ本文は［要協議］のまま残す</t>
+          <t>現に確認できる取組の範囲で記述する</t>
         </is>
       </c>
     </row>
@@ -6961,22 +6978,22 @@
         <v>134</v>
       </c>
       <c r="B139" s="5" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の難聴高齢者の早期発見・早期介入の取組</t>
+          <t>東神楽町の通いの場の維持</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2
+          <t>計画素案 第3章第1節・第5章 基本目標2
 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>発注者・美瑛町</t>
+          <t>発注者・東神楽町</t>
         </is>
       </c>
       <c r="F139" s="5" t="inlineStr">
@@ -6994,7 +7011,7 @@
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述する</t>
+          <t>令和6年度の水準が続くものとして目標値を置く</t>
         </is>
       </c>
     </row>
@@ -7003,16 +7020,16 @@
         <v>135</v>
       </c>
       <c r="B140" s="5" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の通いの場の維持</t>
+          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
         </is>
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第3章第1節・第5章 基本目標2
+          <t>計画素案 第5章 基本目標2
 10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
@@ -7036,7 +7053,7 @@
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
-          <t>令和6年度の水準が続くものとして目標値を置く</t>
+          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
         </is>
       </c>
     </row>
@@ -7045,22 +7062,22 @@
         <v>136</v>
       </c>
       <c r="B141" s="5" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>東神楽町の認知症サポーター・ステップアップ講座の実施状況</t>
+          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
         </is>
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第5章 基本目標2
-10月 地域課題の整理と3町協議の確認事項</t>
+          <t>計画素案の記載内容の洗い出しと対比 06シート・07シート
+計画素案 第1章第6節・第2章第3節・第2章第6節・第3章第2節・第4章第3節・第6章第6節</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>発注者・東神楽町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F141" s="5" t="inlineStr">
@@ -7078,7 +7095,7 @@
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
-          <t>現に確認できる取組の範囲で記述し目標値は置かない</t>
+          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
         </is>
       </c>
     </row>
@@ -7087,17 +7104,17 @@
         <v>137</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>計画素案に独自に加えた記載のうち、打合せ協議用へ移すもの</t>
+          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>計画素案の記載内容の洗い出しと対比 06シート・07シート
-計画素案 第1章第6節・第2章第3節・第2章第6節・第3章第2節・第4章第3節・第6章第6節</t>
+          <t>図表データ管理台帳 03シート
+計画素案 第3章第4節・資料7</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
@@ -7120,7 +7137,7 @@
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
-          <t>計画素案から協議用の成果品へ移す8件は移し、「協議」判定の15件はそのまま素案に残す（令和8年9月29日 ご指示のとおり）</t>
+          <t>掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
         </is>
       </c>
     </row>
@@ -7129,17 +7146,18 @@
         <v>138</v>
       </c>
       <c r="B143" s="5" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価を示す図の計画本文への掲載</t>
+          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr">
         <is>
-          <t>図表データ管理台帳 03シート
-計画素案 第3章第4節・資料7</t>
+          <t>人口推計コーホート分析の妥当性検証 07シート
+見える化へ入力する箇所と入力値 02シート
+計画素案 第2章第1節・第6章第1節</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
@@ -7162,7 +7180,7 @@
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
-          <t>掲載しない（図表番号一覧のとおり策定委員会の資料にとどめる）。得点0が「取組がない」のか「要件を満たさない」のか「報告していない」のかは公表資料から判別できないため、掲載する場合もその旨を注記する</t>
+          <t>案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
         </is>
       </c>
     </row>
@@ -7171,18 +7189,17 @@
         <v>139</v>
       </c>
       <c r="B144" s="5" t="n">
-        <v>174</v>
+        <v>16</v>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>人口及び第1号被保険者数の入力値をどの系列にそろえるか（内部整合）</t>
+          <t>保険料算定の前提</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>人口推計コーホート分析の妥当性検証 07シート
-見える化へ入力する箇所と入力値 02シート
-計画素案 第2章第1節・第6章第1節</t>
+          <t>素案 第6章第3節・第6節
+保険料算定表</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
@@ -7192,7 +7209,7 @@
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G144" s="15" t="n">
@@ -7200,12 +7217,12 @@
       </c>
       <c r="H144" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）／止めている成果物 計画素案（+1）</t>
+          <t>止めている成果物 保険料（+2）</t>
         </is>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
-          <t>案C（①）による。計画素案 第6章第1節の将来推計は令和8年9月10日のご了承のとおり案Cのままとし、見える化システムへの入力値も案Cにそろえる。②③を採る場合は、総人口・男女別6階級・第2号被保険者数のすべてを同じ系列から作り直す</t>
+          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
         </is>
       </c>
     </row>
@@ -7214,40 +7231,39 @@
         <v>140</v>
       </c>
       <c r="B145" s="5" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提</t>
+          <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第3節・第6節
-保険料算定表</t>
+          <t>素案 第1章第9節・第6章第4節</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G145" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H145" s="6" t="inlineStr">
         <is>
-          <t>止めている成果物 保険料（+2）</t>
+          <t>期限 当月（R8.10）（+1）</t>
         </is>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.60と同じ前提（単価固定・施策反映なし・適正化を織り込まない・基金取崩しなし）による</t>
+          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
         </is>
       </c>
     </row>
@@ -7256,21 +7272,23 @@
         <v>141</v>
       </c>
       <c r="B146" s="5" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
+          <t>訪問・通所困難地域の判定資料</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第9節・第6章第4節</t>
+          <t>素案 第1章第7節
+追加調査報告書 03シート
+住まいと施設の公表名簿との突合 08シート</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F146" s="5" t="inlineStr">
@@ -7288,7 +7306,7 @@
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明を行わないものとして記載し、省令等の確定後に改める</t>
+          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
         </is>
       </c>
     </row>
@@ -7297,18 +7315,17 @@
         <v>142</v>
       </c>
       <c r="B147" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域の判定資料</t>
+          <t>人口推計の基礎とする系列</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr">
         <is>
-          <t>素案 第1章第7節
-追加調査報告書 03シート
-住まいと施設の公表名簿との突合 08シート</t>
+          <t>素案 第6章第1節
+将来推計</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
@@ -7331,7 +7348,7 @@
       </c>
       <c r="I147" s="6" t="inlineStr">
         <is>
-          <t>北海道の指定事業所一覧の「通常の事業の実施地域」により判定する</t>
+          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
         </is>
       </c>
     </row>
@@ -7340,11 +7357,11 @@
         <v>143</v>
       </c>
       <c r="B148" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>人口推計の基礎とする系列</t>
+          <t>認定者数の基準月と月次推移</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
@@ -7355,7 +7372,7 @@
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F148" s="5" t="inlineStr">
@@ -7373,7 +7390,7 @@
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
-          <t>案C（総合戦略＋住民基本台帳の実績趨勢）のまま確定する</t>
+          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
         </is>
       </c>
     </row>
@@ -7382,22 +7399,22 @@
         <v>144</v>
       </c>
       <c r="B149" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>認定者数の基準月と月次推移</t>
+          <t>3町計画への共通指標の掲載</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第1節
-将来推計</t>
+          <t>素案 資料2
+3町協議資料</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F149" s="5" t="inlineStr">
@@ -7415,7 +7432,7 @@
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
-          <t>認定者数は年報の年度末（3月31日）を基準とし、月次推移は計画本文に掲げない</t>
+          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
         </is>
       </c>
     </row>
@@ -7424,22 +7441,21 @@
         <v>145</v>
       </c>
       <c r="B150" s="5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>3町計画への共通指標の掲載</t>
+          <t>北海道・圏域との調整の場</t>
         </is>
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>素案 資料2
-3町協議資料</t>
+          <t>素案 第6章第4節</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F150" s="5" t="inlineStr">
@@ -7457,7 +7473,7 @@
       </c>
       <c r="I150" s="6" t="inlineStr">
         <is>
-          <t>広域連合の代表KPI16項目を掲げ、3町計画への掲載は求めない</t>
+          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
         </is>
       </c>
     </row>
@@ -7466,21 +7482,22 @@
         <v>146</v>
       </c>
       <c r="B151" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場</t>
+          <t>成果品の仕様</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第4節</t>
+          <t>計画書（印刷200部）
+概要版</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F151" s="5" t="inlineStr">
@@ -7498,7 +7515,7 @@
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
-          <t>北海道・圏域との調整の場が設けられないものとして、北海道の第9期支援計画との整合により記載する</t>
+          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
         </is>
       </c>
     </row>
@@ -7507,22 +7524,22 @@
         <v>147</v>
       </c>
       <c r="B152" s="5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様</t>
+          <t>事業所の定員・稼働率データ</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>計画書（印刷200部）
-概要版</t>
+          <t>素案 第2章第3節・第6章第4節
+図21・図22</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F152" s="5" t="inlineStr">
@@ -7540,7 +7557,7 @@
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
-          <t>成果品の仕様は仕様書の定め（計画書 印刷200部・編集可能な電子データ及びPDF）による</t>
+          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
         </is>
       </c>
     </row>
@@ -7549,22 +7566,22 @@
         <v>148</v>
       </c>
       <c r="B153" s="5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>事業所の定員・稼働率データ</t>
+          <t>認知症・医療介護連携の実績データ</t>
         </is>
       </c>
       <c r="D153" s="6" t="inlineStr">
         <is>
-          <t>素案 第2章第3節・第6章第4節
-図21・図22</t>
+          <t>素案 第5章 基本目標1・5
+図表集 認知症・医療連携</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者・3町・北海道</t>
         </is>
       </c>
       <c r="F153" s="5" t="inlineStr">
@@ -7582,7 +7599,7 @@
       </c>
       <c r="I153" s="6" t="inlineStr">
         <is>
-          <t>北海道の各名簿及び介護サービス情報公表システムの定員による</t>
+          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
         </is>
       </c>
     </row>
@@ -7591,22 +7608,22 @@
         <v>149</v>
       </c>
       <c r="B154" s="5" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>認知症・医療介護連携の実績データ</t>
+          <t>重度化の速度の前提</t>
         </is>
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>素案 第5章 基本目標1・5
-図表集 認知症・医療連携</t>
+          <t>素案 第6章第1節
+認定者数・給付費の推計</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F154" s="5" t="inlineStr">
@@ -7624,7 +7641,7 @@
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
-          <t>現に受領している交付金評価結果と実施報告書の範囲で記述する</t>
+          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
         </is>
       </c>
     </row>
@@ -7633,17 +7650,17 @@
         <v>150</v>
       </c>
       <c r="B155" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>重度化の速度の前提</t>
+          <t>給付適正化の実施予定と推計での扱い</t>
         </is>
       </c>
       <c r="D155" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第1節
-認定者数・給付費の推計</t>
+          <t>素案 第6章第2節・第5章・第7章
+給付費の推計</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
@@ -7666,7 +7683,7 @@
       </c>
       <c r="I155" s="6" t="inlineStr">
         <is>
-          <t>年齢階級ごとの要介護度の構成を令和7年度末の実績で固定する（重度化は人口の高齢化による分のみを見込む）</t>
+          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
         </is>
       </c>
     </row>
@@ -7675,17 +7692,17 @@
         <v>151</v>
       </c>
       <c r="B156" s="5" t="n">
-        <v>31</v>
+        <v>128</v>
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>給付適正化の実施予定と推計での扱い</t>
+          <t>令和8年度の実績見込み値を編集するか</t>
         </is>
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第2節・第5章・第7章
-給付費の推計</t>
+          <t>将来推計 第2段階
+サービス見込量の算定</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -7708,7 +7725,7 @@
       </c>
       <c r="I156" s="6" t="inlineStr">
         <is>
-          <t>給付適正化による抑制を推計に織り込まない（安全側）。対象4サービスは総給付費の7.70％であり、10％抑制でも月額▲47円であることを併記する</t>
+          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
         </is>
       </c>
     </row>
@@ -7717,11 +7734,11 @@
         <v>152</v>
       </c>
       <c r="B157" s="5" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>令和8年度の実績見込み値を編集するか</t>
+          <t>見える化システムの利用率等の伸びの選択</t>
         </is>
       </c>
       <c r="D157" s="6" t="inlineStr">
@@ -7750,7 +7767,7 @@
       </c>
       <c r="I157" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
+          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
         </is>
       </c>
     </row>
@@ -7759,17 +7776,16 @@
         <v>153</v>
       </c>
       <c r="B158" s="5" t="n">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの利用率等の伸びの選択</t>
+          <t>統合した成果品の元の資料を残すか</t>
         </is>
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t>将来推計 第2段階
-サービス見込量の算定</t>
+          <t>成果品一覧（納品時の構成）</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -7792,7 +7808,7 @@
       </c>
       <c r="I158" s="6" t="inlineStr">
         <is>
-          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>統合した成果品の元の資料を残す</t>
         </is>
       </c>
     </row>
@@ -7801,16 +7817,17 @@
         <v>154</v>
       </c>
       <c r="B159" s="5" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>統合した成果品の元の資料を残すか</t>
+          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
         </is>
       </c>
       <c r="D159" s="6" t="inlineStr">
         <is>
-          <t>成果品一覧（納品時の構成）</t>
+          <t>見える化システムへの入力
+将来推計 第3段階</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -7833,7 +7850,7 @@
       </c>
       <c r="I159" s="6" t="inlineStr">
         <is>
-          <t>統合した成果品の元の資料を残す</t>
+          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
         </is>
       </c>
     </row>
@@ -7842,22 +7859,22 @@
         <v>155</v>
       </c>
       <c r="B160" s="5" t="n">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>所得段階別第1号被保険者数の将来8年度分を当方で算定してよいか</t>
+          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
         </is>
       </c>
       <c r="D160" s="6" t="inlineStr">
         <is>
-          <t>見える化システムへの入力
-将来推計 第3段階</t>
+          <t>交付金評価の取りまとめと第10期への反映 08シート・09シート
+10月 地域課題の整理と3町協議の確認事項</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F160" s="5" t="inlineStr">
@@ -7875,7 +7892,7 @@
       </c>
       <c r="I160" s="6" t="inlineStr">
         <is>
-          <t>当方の算定（16段階×8年度）による。所得段階の設定は弾力化を選ぶ</t>
+          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
         </is>
       </c>
     </row>
@@ -7884,27 +7901,27 @@
         <v>156</v>
       </c>
       <c r="B161" s="5" t="n">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>構成町により得点が分かれている項目の区域内での取扱い</t>
+          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
         </is>
       </c>
       <c r="D161" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の取りまとめと第10期への反映 08シート・09シート
-10月 地域課題の整理と3町協議の確認事項</t>
+          <t>計画素案の記載内容の洗い出しと対比 08シート
+計画素案 全体</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G161" s="15" t="n">
@@ -7912,12 +7929,12 @@
       </c>
       <c r="H161" s="6" t="inlineStr">
         <is>
-          <t>期限 当月（R8.10）（+1）</t>
+          <t>止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I161" s="6" t="inlineStr">
         <is>
-          <t>町ごとの取組の状況をそのまま記述し、区域内での統一は計画に位置づけない。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由とするものではない</t>
+          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
         </is>
       </c>
     </row>
@@ -7926,17 +7943,17 @@
         <v>157</v>
       </c>
       <c r="B162" s="5" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>第9期計画にない体裁の取扱い（小見出し【　】ほか）</t>
+          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>計画素案の記載内容の洗い出しと対比 08シート
-計画素案 全体</t>
+          <t>図表データ管理台帳 01シート・02シート
+計画素案 資料7／別冊の図表集</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -7959,7 +7976,7 @@
       </c>
       <c r="I162" s="6" t="inlineStr">
         <is>
-          <t>第9期計画にない体裁は現在のままとし、計画として確定する前に改めてお諮りする（令和8年9月29日 ご指示により保留）</t>
+          <t>現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
         </is>
       </c>
     </row>
@@ -7968,22 +7985,21 @@
         <v>158</v>
       </c>
       <c r="B163" s="5" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>計画本文の図と別冊の図表集の対応（作りが異なるもの・図表集にないもの）</t>
+          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
         <is>
-          <t>図表データ管理台帳 01シート・02シート
-計画素案 資料7／別冊の図表集</t>
+          <t>計画素案 第1章第9節5・第5章 基本目標1・基本目標4</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F163" s="5" t="inlineStr">
@@ -8001,7 +8017,7 @@
       </c>
       <c r="I163" s="6" t="inlineStr">
         <is>
-          <t>現行のまま（③は本文の図を計画に載せ、図表集の図は参考として残す。④は本文の図の数値を図表データ管理台帳で管理する）。いずれも保険料・見込量の算定には影響しない</t>
+          <t>国が示す本格運用開始日（令和10年4月1日）までに完了することを前提として計画素案に記載し、年度ごとの工程は［要確認］として残す。事業所への周知は広域連合と3町が共同で行うものとして記載する</t>
         </is>
       </c>
     </row>
@@ -8010,16 +8026,17 @@
         <v>159</v>
       </c>
       <c r="B164" s="5" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>介護情報基盤及びケアプランデータ連携への対応の工程</t>
+          <t>構成3町の高齢者福祉計画と市町村老人福祉計画の関係</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節5・第5章 基本目標1・基本目標4</t>
+          <t>計画素案 第1章第2節・第1章第8節
+計画素案の記載内容の洗い出しと対比 02シート</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
@@ -8042,7 +8059,7 @@
       </c>
       <c r="I164" s="6" t="inlineStr">
         <is>
-          <t>国が示す本格運用開始日（令和10年4月1日）までに完了することを前提として計画素案に記載し、年度ごとの工程は［要確認］として残す。事業所への周知は広域連合と3町が共同で行うものとして記載する</t>
+          <t>構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない【令和8年10月15日】参照条文により、介護保険法第117条第7項が「老人福祉法第20条の8第1項に規定する市町村老人福祉計画と一体のものとして作成されなければならない」ことを定めていることを確かめた。条及び項は第20条の8第1項である。老人福祉法そのものの条文は参照条文に収録されていない（第18条及び第20条の6のみ）ため、同条の内容及び市町村老人福祉計画の記載事項はなお確認できていない</t>
         </is>
       </c>
     </row>
@@ -8051,16 +8068,16 @@
         <v>160</v>
       </c>
       <c r="B165" s="5" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画と市町村老人福祉計画の関係</t>
+          <t>成年後見制度の利用の促進に関する施策についての基本的な計画の策定状況</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第2節・第1章第8節
+          <t>計画素案 第1章第2節・第5章 基本目標1
 計画素案の記載内容の洗い出しと対比 02シート</t>
         </is>
       </c>
@@ -8084,7 +8101,7 @@
       </c>
       <c r="I165" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない</t>
+          <t>同計画は構成3町が定めるものとして計画素案に記載し、本計画は介護保険法第117条第3項による権利擁護の施策（第5章 基本目標1）をもって接続する。中核機関の整備の状況は［要確認］として残す</t>
         </is>
       </c>
     </row>
@@ -8093,16 +8110,16 @@
         <v>161</v>
       </c>
       <c r="B166" s="5" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>成年後見制度の利用の促進に関する施策についての基本的な計画の策定状況</t>
+          <t>要配慮者利用施設の避難確保計画の対象施設と作成状況</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第2節・第5章 基本目標1
+          <t>計画素案 第1章第8節・第5章 基本目標5
 計画素案の記載内容の洗い出しと対比 02シート</t>
         </is>
       </c>
@@ -8126,7 +8143,7 @@
       </c>
       <c r="I166" s="6" t="inlineStr">
         <is>
-          <t>同計画は構成3町が定めるものとして計画素案に記載し、本計画は介護保険法第117条第3項による権利擁護の施策（第5章 基本目標1）をもって接続する。中核機関の整備の状況は［要確認］として残す</t>
+          <t>対象施設及び作成の状況を［要確認］として残し、第5章 基本目標5の主な事業に作成及び避難訓練の確認を置くにとどめ、達成目標に数値を掲げない。避難確保計画はBCPとは別の計画であり、BCPの策定率をもって作成の状況としない</t>
         </is>
       </c>
     </row>
@@ -8135,27 +8152,26 @@
         <v>162</v>
       </c>
       <c r="B167" s="5" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>要配慮者利用施設の避難確保計画の対象施設と作成状況</t>
+          <t>介護サービス事業者経営情報データベースの公表結果の活用の範囲</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第8節・第5章 基本目標5
-計画素案の記載内容の洗い出しと対比 02シート</t>
+          <t>計画素案 第1章第9節5・第5章 基本目標4</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="G167" s="15" t="n">
@@ -8168,7 +8184,7 @@
       </c>
       <c r="I167" s="6" t="inlineStr">
         <is>
-          <t>対象施設及び作成の状況を［要確認］として残し、第5章 基本目標5の主な事業に作成及び避難訓練の確認を置くにとどめ、達成目標に数値を掲げない。避難確保計画はBCPとは別の計画であり、BCPの策定率をもって作成の状況としない</t>
+          <t>公表された区分のうち当区域の事業所の規模に近いものを参考として用い、区域内の事業所の経営状況を表すものとしては用いない。計画素案には活用の方針のみを記載し、数値は掲げない</t>
         </is>
       </c>
     </row>
@@ -8177,21 +8193,21 @@
         <v>163</v>
       </c>
       <c r="B168" s="5" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>介護サービス事業者経営情報データベースの公表結果の活用の範囲</t>
+          <t>都道府県との協定に基づく連携への関与</t>
         </is>
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節5・第5章 基本目標4</t>
+          <t>計画素案 第1章第9節5・第5章 基本目標3・基本目標4</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F168" s="5" t="inlineStr">
@@ -8209,7 +8225,7 @@
       </c>
       <c r="I168" s="6" t="inlineStr">
         <is>
-          <t>公表された区分のうち当区域の事業所の規模に近いものを参考として用い、区域内の事業所の経営状況を表すものとしては用いない。計画素案には活用の方針のみを記載し、数値は掲げない</t>
+          <t>計画素案には北海道及び事業者とともに活用を検討する旨のみを記載し、具体の取組及び目標は国から市町村の役割が示された後に定める</t>
         </is>
       </c>
     </row>
@@ -8218,21 +8234,23 @@
         <v>164</v>
       </c>
       <c r="B169" s="5" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>都道府県との協定に基づく連携への関与</t>
+          <t>介護給付費分科会の資料（原本）のご提供</t>
         </is>
       </c>
       <c r="D169" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節5・第5章 基本目標3・基本目標4</t>
+          <t>計画素案 第1章第9節6・第6章第2節・第6章第6節2・第6章第7節
+介護給付費分科会の論点整理の受領点検
+介護給付費分科会資料（原典）の受領点検</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F169" s="5" t="inlineStr">
@@ -8250,7 +8268,7 @@
       </c>
       <c r="I169" s="6" t="inlineStr">
         <is>
-          <t>計画素案には北海道及び事業者とともに活用を検討する旨のみを記載し、具体の取組及び目標は国から市町村の役割が示された後に定める</t>
+          <t>計画素案には国において検討されている事項があることまでを記載し、単位数・要件・施行時期を書かない。原本を確認できていないことを［要確認］として残し、改定率及び単価は令和7年度の実績で固定したまま概算する</t>
         </is>
       </c>
     </row>
@@ -8259,18 +8277,17 @@
         <v>165</v>
       </c>
       <c r="B170" s="5" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
-          <t>介護給付費分科会の資料（原本）のご提供</t>
+          <t>夜間対応型訪問介護の定期巡回・随時対応型への移行の扱い</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節6・第6章第2節・第6章第6節2・第6章第7節
-介護給付費分科会の論点整理の受領点検
-介護給付費分科会資料（原典）の受領点検</t>
+          <t>計画素案 第6章第2節（2）・第6章第4節1
+サービス見込量の算定・見える化システムへの入力値</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -8293,7 +8310,7 @@
       </c>
       <c r="I170" s="6" t="inlineStr">
         <is>
-          <t>計画素案には国において検討されている事項があることまでを記載し、単位数・要件・施行時期を書かない。原本を確認できていないことを［要確認］として残し、改定率及び単価は令和7年度の実績で固定したまま概算する</t>
+          <t>現行の区分のまま夜間対応型訪問介護を実績なし（0）として立て、移行が検討されていることを計画素案の注に記載する。省令等が確定した時点で区分を組み替える</t>
         </is>
       </c>
     </row>
@@ -8302,22 +8319,22 @@
         <v>166</v>
       </c>
       <c r="B171" s="5" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>夜間対応型訪問介護の定期巡回・随時対応型への移行の扱い</t>
+          <t>短期入所生活介護の季節利用及び長期利用の実態</t>
         </is>
       </c>
       <c r="D171" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節（2）・第6章第4節1
-サービス見込量の算定・見える化システムへの入力値</t>
+          <t>計画素案 第6章第2節 注1-1・第6章第4節
+サービス見込量の算定（季節補正）</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町・事業者</t>
         </is>
       </c>
       <c r="F171" s="5" t="inlineStr">
@@ -8335,7 +8352,7 @@
       </c>
       <c r="I171" s="6" t="inlineStr">
         <is>
-          <t>現行の区分のまま夜間対応型訪問介護を実績なし（0）として立て、移行が検討されていることを計画素案の注に記載する。省令等が確定した時点で区分を組み替える</t>
+          <t>令和7年度（12か月の完結年度）の実績により短期入所生活介護の見込量を算定し、季節補正を行わない（基準年度が完結年度であるため年度換算係数は1.0000となり効きは0円である）。季節利用の例外が示された時点で利用日数の置き方を確かめる</t>
         </is>
       </c>
     </row>
@@ -8344,22 +8361,22 @@
         <v>167</v>
       </c>
       <c r="B172" s="5" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>短期入所生活介護の季節利用及び長期利用の実態</t>
+          <t>小規模市町村地域支援連携協働体制整備事業の対象となるかどうか</t>
         </is>
       </c>
       <c r="D172" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節 注1-1・第6章第4節
-サービス見込量の算定（季節補正）</t>
+          <t>計画素案 第1章第9節2・第6章第3節2・第6章第6節
+サービス見込量の算定（地域支援事業費）</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町・事業者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F172" s="5" t="inlineStr">
@@ -8377,7 +8394,7 @@
       </c>
       <c r="I172" s="6" t="inlineStr">
         <is>
-          <t>令和7年度（12か月の完結年度）の実績により短期入所生活介護の見込量を算定し、季節補正を行わない（基準年度が完結年度であるため年度換算係数は1.0000となり効きは0円である）。季節利用の例外が示された時点で利用日数の置き方を確かめる</t>
+          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す。【令和8年10月15日】新旧対照条文により社会福祉法第106条の12（新設）の内容を確かめた。小規模市町村が本事業を実施する場合、介護保険法第122条の2（第3項を除く。地域支援事業に係る国の交付金）並びに第123条第3項及び第4項（都道府県の負担）の規定の適用について、第122条の2第1項の「費用」から本事業として行う社会福祉法第106条の6第2項第3号イに掲げる事業に要する費用を除き、第123条第4項の「費用」から同条第2項第1号イ及び第3号ロに掲げる事業に要する費用を除くこととされている。重層的支援体制整備事業（社会福祉法第106条の4）と同じ構造である。除かれるのは国の交付金及び都道府県の負担の対象となる費用であり、当該費用は社会福祉法による交付金等により支弁されることとなる。除かれる事業の内容（第106条の6第2項第1号イ・第3号イ・第3号ロ）は確かめていない。小規模市町村の基準は厚生労働省令で定められるため、①（該当の有無）は引き続き確認を要する【令和8年10月15日】参照条文には社会福祉法第106条の3（包括的な支援体制の整備）までが収録されており、第106条の6は改正法により新設される規定であるため現れない。本件は進んでいない</t>
         </is>
       </c>
     </row>
@@ -8386,22 +8403,22 @@
         <v>168</v>
       </c>
       <c r="B173" s="5" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>小規模市町村地域支援連携協働体制整備事業の対象となるかどうか</t>
+          <t>特定施設の定義の改正による区域内3施設の扱い</t>
         </is>
       </c>
       <c r="D173" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節2・第6章第3節2・第6章第6節
-サービス見込量の算定（地域支援事業費）</t>
+          <t>計画素案 第1章第9節2・第2章第3節・第6章第2節 注3・第6章第4節
+サービス見込量の算定（施設・居住系サービス）</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F173" s="5" t="inlineStr">
@@ -8419,7 +8436,7 @@
       </c>
       <c r="I173" s="6" t="inlineStr">
         <is>
-          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す。【令和8年10月15日】新旧対照条文により社会福祉法第106条の12（新設）の内容を確かめた。小規模市町村が本事業を実施する場合、介護保険法第122条の2（第3項を除く。地域支援事業に係る国の交付金）並びに第123条第3項及び第4項（都道府県の負担）の規定の適用について、第122条の2第1項の「費用」から本事業として行う社会福祉法第106条の6第2項第3号イに掲げる事業に要する費用を除き、第123条第4項の「費用」から同条第2項第1号イ及び第3号ロに掲げる事業に要する費用を除くこととされている。重層的支援体制整備事業（社会福祉法第106条の4）と同じ構造である。除かれるのは国の交付金及び都道府県の負担の対象となる費用であり、当該費用は社会福祉法による交付金等により支弁されることとなる。除かれる事業の内容（第106条の6第2項第1号イ・第3号イ・第3号ロ）は確かめていない。小規模市町村の基準は厚生労働省令で定められるため、①（該当の有無）は引き続き確認を要する</t>
+          <t>現行の指定の区分により特定施設入居者生活介護の見込量を算定し、定義の改正により対象となる施設の範囲が変わり得ることを計画素案の注に［要確認］として記載する。【令和8年10月15日】新旧対照条文により、現行の第8条第11項が「有料老人ホームその他厚生労働省令で定める施設であって、第20項に規定する地域密着型特定施設でないもの」であり、改正により「有料老人ホーム」が「老人福祉法第29条の18第5項に規定する登録有料老人ホーム」に置き換わることを確かめた。すなわち登録有料老人ホームを定義に加えるものではなく、登録を受けない有料老人ホームは特定施設に当たらなくなる。計画素案 第1章第9節2の記述を「定義に加える」から「有料老人ホームを登録有料老人ホームに改める」に是正した。【令和8年10月15日】参照条文により、現行の第8条第11項が「有料老人ホームその他厚生労働省令で定める施設であって地域密着型特定施設でないもの」であることを2つ目の原典で確かめた。また同条第21項により、介護専用型特定施設はその入居者が要介護者、その配偶者その他厚生労働省令で定める者に限られるものであり、類型は入居の要件により定まることが分かった</t>
         </is>
       </c>
     </row>
@@ -8428,22 +8445,22 @@
         <v>169</v>
       </c>
       <c r="B174" s="5" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>特定施設の定義の改正による区域内3施設の扱い</t>
+          <t>「特定地域支援事業支援額」の内容</t>
         </is>
       </c>
       <c r="D174" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第1章第9節2・第2章第3節・第6章第2節 注3・第6章第4節
-サービス見込量の算定（施設・居住系サービス）</t>
+          <t>計画素案 第1章第9節1・第6章第3節2・第6章第6節
+サービス見込量の算定（地域支援事業費）</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F174" s="5" t="inlineStr">
@@ -8461,7 +8478,7 @@
       </c>
       <c r="I174" s="6" t="inlineStr">
         <is>
-          <t>現行の指定の区分により特定施設入居者生活介護の見込量を算定し、定義の改正により対象となる施設の範囲が変わり得ることを計画素案の注に［要確認］として記載する。【令和8年10月15日】新旧対照条文により、現行の第8条第11項が「有料老人ホームその他厚生労働省令で定める施設であって、第20項に規定する地域密着型特定施設でないもの」であり、改正により「有料老人ホーム」が「老人福祉法第29条の18第5項に規定する登録有料老人ホーム」に置き換わることを確かめた。すなわち登録有料老人ホームを定義に加えるものではなく、登録を受けない有料老人ホームは特定施設に当たらなくなる。計画素案 第1章第9節2の記述を「定義に加える」から「有料老人ホームを登録有料老人ホームに改める」に是正した</t>
+          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、特定地域支援事業支援額を織り込まない。内容が示された時点で財源の区分を確かめ、再算定する</t>
         </is>
       </c>
     </row>
@@ -8470,27 +8487,27 @@
         <v>170</v>
       </c>
       <c r="B175" s="5" t="n">
-        <v>74</v>
+        <v>188</v>
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
+          <t>地域支援事業費の政令で定める額</t>
         </is>
       </c>
       <c r="D175" s="6" t="inlineStr">
         <is>
-          <t>ケアプラン点検実施要領（案）9
-計画素案 第5章 基本目標5</t>
+          <t>計画素案 第6章第3節2・第6章第6節
+サービス見込量の算定（地域支援事業費）</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>北海道上川総合振興局</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
-          <t>R9.4</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="G175" s="15" t="n">
@@ -8503,7 +8520,7 @@
       </c>
       <c r="I175" s="6" t="inlineStr">
         <is>
-          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
+          <t>令和6年度決算の水準を据え置いたまま算定し、政令で定める額との関係を確かめていない旨を計画素案の注に［要確認］として記載する</t>
         </is>
       </c>
     </row>
@@ -8512,40 +8529,40 @@
         <v>171</v>
       </c>
       <c r="B176" s="5" t="n">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスの確保方策の決定</t>
+          <t>有料老人ホーム等の家賃等の情報収集（北海道）</t>
         </is>
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第2節・第4節
-見込量表（3種別）</t>
+          <t>ケアプラン点検実施要領（案）9
+計画素案 第5章 基本目標5</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>北海道上川総合振興局</t>
         </is>
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R9.4</t>
         </is>
       </c>
       <c r="G176" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H176" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>止めている成果物 計画素案（+1）</t>
         </is>
       </c>
       <c r="I176" s="6" t="inlineStr">
         <is>
-          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+          <t>北海道が家賃等の情報収集を行っていないものとして、第10期の施策に位置づけない</t>
         </is>
       </c>
     </row>
@@ -8554,45 +8571,87 @@
         <v>172</v>
       </c>
       <c r="B177" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C177" s="6" t="inlineStr">
+        <is>
+          <t>24時間対応サービスの確保方策の決定</t>
+        </is>
+      </c>
+      <c r="D177" s="6" t="inlineStr">
+        <is>
+          <t>素案 第6章第2節・第4節
+見込量表（3種別）</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F177" s="5" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G177" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" s="6" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="I177" s="6" t="inlineStr">
+        <is>
+          <t>24時間対応サービスは自然体の算定値を置き、整備による上乗せは行わない（安全側）</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="48" customHeight="1">
+      <c r="A178" s="5" t="n">
+        <v>173</v>
+      </c>
+      <c r="B178" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="C177" s="6" t="inlineStr">
+      <c r="C178" s="6" t="inlineStr">
         <is>
           <t>代表KPIの目標値の決定</t>
         </is>
       </c>
-      <c r="D177" s="6" t="inlineStr">
+      <c r="D178" s="6" t="inlineStr">
         <is>
           <t>素案 第4章第3節・第5章
 全16KPIの目標値</t>
         </is>
       </c>
-      <c r="E177" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F177" s="5" t="inlineStr">
+      <c r="E178" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F178" s="5" t="inlineStr">
         <is>
           <t>R8.12</t>
         </is>
       </c>
-      <c r="G177" s="15" t="n">
+      <c r="G178" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H177" s="6" t="inlineStr">
+      <c r="H178" s="6" t="inlineStr">
         <is>
           <t>―</t>
         </is>
       </c>
-      <c r="I177" s="6" t="inlineStr">
+      <c r="I178" s="6" t="inlineStr">
         <is>
           <t>代表KPIの目標値は、令和9年度を基準値の把握に充て、令和10年度・令和11年度に目標値を置く</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="56" customHeight="1">
-      <c r="A178" s="13" t="inlineStr">
+    <row r="179" ht="56" customHeight="1">
+      <c r="A179" s="13" t="inlineStr">
         <is>
           <t>注1）点が9以上を至急、6以上8以下を優先、5以下を通常とみます（03シート）。
 注2）「決着しない場合の当方の扱い」が空のものは、決まらないと当方の作業が止まります。 先に扱いを決めます。
@@ -8600,119 +8659,76 @@
         </is>
       </c>
     </row>
-    <row r="179"/>
-    <row r="180" ht="20" customHeight="1">
-      <c r="A180" s="3" t="inlineStr">
+    <row r="180"/>
+    <row r="181" ht="20" customHeight="1">
+      <c r="A181" s="3" t="inlineStr">
         <is>
           <t>2　資料提供依頼（資料の提供を求めるもの）　18件</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="30" customHeight="1">
-      <c r="A181" s="4" t="inlineStr">
+    <row r="182" ht="30" customHeight="1">
+      <c r="A182" s="4" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B181" s="4" t="inlineStr">
+      <c r="B182" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C181" s="4" t="inlineStr">
+      <c r="C182" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="D181" s="4" t="inlineStr">
+      <c r="D182" s="4" t="inlineStr">
         <is>
           <t>確定する主張</t>
         </is>
       </c>
-      <c r="E181" s="4" t="inlineStr">
+      <c r="E182" s="4" t="inlineStr">
         <is>
           <t>入手先</t>
         </is>
       </c>
-      <c r="F181" s="4" t="inlineStr">
+      <c r="F182" s="4" t="inlineStr">
         <is>
           <t>希望時期</t>
         </is>
       </c>
-      <c r="G181" s="4" t="inlineStr">
+      <c r="G182" s="4" t="inlineStr">
         <is>
           <t>優先</t>
         </is>
       </c>
-      <c r="H181" s="4" t="inlineStr">
+      <c r="H182" s="4" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="I181" s="4" t="inlineStr">
+      <c r="I182" s="4" t="inlineStr">
         <is>
           <t>領域</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="40" customHeight="1">
-      <c r="A182" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B182" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C182" s="6" t="inlineStr">
-        <is>
-          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
-        </is>
-      </c>
-      <c r="D182" s="6" t="inlineStr">
-        <is>
-          <t>第9期の評価の完成</t>
-        </is>
-      </c>
-      <c r="E182" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F182" s="5" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="G182" s="16" t="inlineStr">
-        <is>
-          <t>最高</t>
-        </is>
-      </c>
-      <c r="H182" s="5" t="inlineStr">
-        <is>
-          <t>一部受領</t>
-        </is>
-      </c>
-      <c r="I182" s="5" t="inlineStr">
-        <is>
-          <t>G</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B183" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
+          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
         </is>
       </c>
       <c r="D183" s="6" t="inlineStr">
         <is>
-          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
+          <t>第9期の評価の完成</t>
         </is>
       </c>
       <c r="E183" s="6" t="inlineStr">
@@ -8725,47 +8741,47 @@
           <t>R8.8</t>
         </is>
       </c>
-      <c r="G183" s="14" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="G183" s="16" t="inlineStr">
+        <is>
+          <t>最高</t>
         </is>
       </c>
       <c r="H183" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>一部受領</t>
         </is>
       </c>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B184" s="5" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
         </is>
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
+          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
         </is>
       </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G184" s="14" t="inlineStr">
@@ -8775,35 +8791,35 @@
       </c>
       <c r="H184" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B185" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
         </is>
       </c>
       <c r="D185" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
+          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="F185" s="5" t="inlineStr">
@@ -8818,40 +8834,40 @@
       </c>
       <c r="H185" s="5" t="inlineStr">
         <is>
-          <t>代替により解消</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I185" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B186" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B186" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
         </is>
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
-          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
+          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
         </is>
       </c>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G186" s="14" t="inlineStr">
@@ -8861,35 +8877,35 @@
       </c>
       <c r="H186" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>代替により解消</t>
         </is>
       </c>
       <c r="I186" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B187" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B187" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="C187" s="6" t="inlineStr">
         <is>
-          <t>事業所・施設の定員と稼働の実績</t>
+          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
         </is>
       </c>
       <c r="D187" s="6" t="inlineStr">
         <is>
-          <t>稼働率の低下の有無、定員減少の経緯</t>
+          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
         </is>
       </c>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F187" s="5" t="inlineStr">
@@ -8904,35 +8920,35 @@
       </c>
       <c r="H187" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I187" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B188" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B188" s="5" t="n">
-        <v>8</v>
-      </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>未利用認定者の内訳とケアプランのサービス構成</t>
+          <t>事業所・施設の定員と稼働の実績</t>
         </is>
       </c>
       <c r="D188" s="6" t="inlineStr">
         <is>
-          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
+          <t>稼働率の低下の有無、定員減少の経緯</t>
         </is>
       </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F188" s="5" t="inlineStr">
@@ -8952,25 +8968,25 @@
       </c>
       <c r="I188" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B189" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B189" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
+          <t>未利用認定者の内訳とケアプランのサービス構成</t>
         </is>
       </c>
       <c r="D189" s="6" t="inlineStr">
         <is>
-          <t>第9期の剰余額（現在は概算）</t>
+          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
         </is>
       </c>
       <c r="E189" s="6" t="inlineStr">
@@ -8995,30 +9011,30 @@
       </c>
       <c r="I189" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>E</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B190" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B190" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
+          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
         </is>
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
-          <t>給付費の地域内還流の議論</t>
+          <t>第9期の剰余額（現在は概算）</t>
         </is>
       </c>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F190" s="5" t="inlineStr">
@@ -9038,25 +9054,25 @@
       </c>
       <c r="I190" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B191" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
+          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
         </is>
       </c>
       <c r="D191" s="6" t="inlineStr">
         <is>
-          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
+          <t>給付費の地域内還流の議論</t>
         </is>
       </c>
       <c r="E191" s="6" t="inlineStr">
@@ -9081,30 +9097,30 @@
       </c>
       <c r="I191" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B192" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C192" s="6" t="inlineStr">
         <is>
-          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
+          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
         </is>
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>サービス種別ごとの見込量の様式</t>
+          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
         </is>
       </c>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F192" s="5" t="inlineStr">
@@ -9119,40 +9135,40 @@
       </c>
       <c r="H192" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I192" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B193" s="5" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
+          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
         </is>
       </c>
       <c r="D193" s="6" t="inlineStr">
         <is>
-          <t>第10期の段階設計と保険料算定</t>
+          <t>サービス種別ごとの見込量の様式</t>
         </is>
       </c>
       <c r="E193" s="6" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
-          <t>告示後</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G193" s="14" t="inlineStr">
@@ -9162,78 +9178,78 @@
       </c>
       <c r="H193" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I193" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B194" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
-          <t>小学校区と日常生活圏域の対応関係</t>
+          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>圏域別の分析、圏域設定の見直し</t>
+          <t>第10期の段階設計と保険料算定</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>美瑛町・3町</t>
+          <t>国の情報</t>
         </is>
       </c>
       <c r="F194" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G194" s="15" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>告示後</t>
+        </is>
+      </c>
+      <c r="G194" s="14" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H194" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I194" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B195" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
       <c r="D195" s="6" t="inlineStr">
         <is>
-          <t>評価の枠組みの整理</t>
+          <t>圏域別の分析、圏域設定の見直し</t>
         </is>
       </c>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>美瑛町・3町</t>
         </is>
       </c>
       <c r="F195" s="5" t="inlineStr">
@@ -9253,35 +9269,35 @@
       </c>
       <c r="I195" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B196" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B196" s="5" t="n">
-        <v>16</v>
-      </c>
       <c r="C196" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD49の指標定義</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D196" s="6" t="inlineStr">
         <is>
-          <t>地域差指数の分解の可否</t>
+          <t>評価の枠組みの整理</t>
         </is>
       </c>
       <c r="E196" s="6" t="inlineStr">
         <is>
-          <t>見える化システム・厚生労働省</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G196" s="15" t="inlineStr">
@@ -9291,40 +9307,40 @@
       </c>
       <c r="H196" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I196" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B197" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B197" s="5" t="n">
-        <v>20</v>
-      </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+          <t>見える化システムD49の指標定義</t>
         </is>
       </c>
       <c r="D197" s="6" t="inlineStr">
         <is>
-          <t>会議資料・委員会資料の記述の正確性</t>
+          <t>地域差指数の分解の可否</t>
         </is>
       </c>
       <c r="E197" s="6" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>見える化システム・厚生労働省</t>
         </is>
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
-          <t>随時</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G197" s="15" t="inlineStr">
@@ -9334,103 +9350,146 @@
       </c>
       <c r="H197" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I197" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B198" s="5" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C198" s="6" t="inlineStr">
         <is>
-          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
         </is>
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>中重度・軽度の認定率の推移</t>
+          <t>会議資料・委員会資料の記述の正確性</t>
         </is>
       </c>
       <c r="E198" s="6" t="inlineStr">
         <is>
-          <t>見える化システム</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F198" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G198" s="17" t="inlineStr">
-        <is>
-          <t>低</t>
+          <t>随時</t>
+        </is>
+      </c>
+      <c r="G198" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H198" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I198" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B199" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+        </is>
+      </c>
+      <c r="D199" s="6" t="inlineStr">
+        <is>
+          <t>中重度・軽度の認定率の推移</t>
+        </is>
+      </c>
+      <c r="E199" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム</t>
+        </is>
+      </c>
+      <c r="F199" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G199" s="17" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H199" s="5" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I199" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="40" customHeight="1">
+      <c r="A200" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B199" s="5" t="n">
+      <c r="B200" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C199" s="6" t="inlineStr">
+      <c r="C200" s="6" t="inlineStr">
         <is>
           <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
-      <c r="D199" s="6" t="inlineStr">
+      <c r="D200" s="6" t="inlineStr">
         <is>
           <t>世帯構成の現状</t>
         </is>
       </c>
-      <c r="E199" s="6" t="inlineStr">
+      <c r="E200" s="6" t="inlineStr">
         <is>
           <t>総務省・3町</t>
         </is>
       </c>
-      <c r="F199" s="5" t="inlineStr">
+      <c r="F200" s="5" t="inlineStr">
         <is>
           <t>公表後</t>
         </is>
       </c>
-      <c r="G199" s="17" t="inlineStr">
+      <c r="G200" s="17" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H199" s="5" t="inlineStr">
+      <c r="H200" s="5" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="I199" s="5" t="inlineStr">
+      <c r="I200" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="28" customHeight="1">
-      <c r="A200" s="13" t="inlineStr">
+    <row r="201" ht="28" customHeight="1">
+      <c r="A201" s="13" t="inlineStr">
         <is>
           <t>注）03シートの確認事項が「決定」を求めるものであるのに対し、本表は「資料の提供」を求めるものです。資料が届かない場合の扱いは04シートの区分で示しています。</t>
         </is>
@@ -9438,12 +9497,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A180:I180"/>
+    <mergeCell ref="A179:I179"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A178:I178"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A200:I200"/>
+    <mergeCell ref="A181:I181"/>
     <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A201:I201"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9529,7 +9588,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>84件</t>
+          <t>83件</t>
         </is>
       </c>
     </row>
@@ -9644,7 +9703,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>104件</t>
+          <t>105件</t>
         </is>
       </c>
     </row>
@@ -9736,7 +9795,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>9件</t>
+          <t>8件</t>
         </is>
       </c>
     </row>
@@ -9892,7 +9951,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>169件</t>
+          <t>170件</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -10051,7 +10110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -10079,7 +10138,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　当方の作業だけで進められるもの　9件</t>
+          <t>1　当方の作業だけで進められるもの　11件</t>
         </is>
       </c>
     </row>
@@ -10117,17 +10176,17 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第117条ほか関係法令の条文のご提供</t>
+          <t>医療法等の一部を改正する法律による介護保険法の改正の施行の状況</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>条番号のみを記載し項番号及び号番号は記載しない。記載事項の点検は条文の番号ではなく記載事項の内容を単位として行い、条文を確認できていない箇所は［要確認］として残す。【令和8年10月14日】社会福祉法等の一部を改正する法律案要綱を確認したことにより、改正後の第117条第2項第3号・第4号、第3項第4号・第5号、第5項及び第14項の号及び項が確定した。引き続き必要なのは、①改正後の条文及び新旧対照表（要綱は改正事項の要旨であり条文の文言を確認できない）、②附則第3条から第77条までの経過措置（有料老人ホームの登録制に係る経過措置の内容）、③改正に係らない号（第2項第1号・第2号、第3項第1号から第3号まで）の条文である。【令和8年10月15日　大きく解決】社会福祉法等の一部を改正する法律案の新旧対照条文（全353頁）を確認した。改正後の介護保険法第117条（第2項第3号・第4号、第3項第3号・第4号・第4号の2・第5号・第6号・第7号・第9号、第5項、第9項、第14項）、第115条の48（支援会議）、第118条第2項・第8項・第9項並びに第120条の3から第120条の5まで（協議会）の内容が確定した。介護保険法の改正は第3条関係（令和9年4月1日又は1年6月以内）と第4条関係（2年以内又は3年以内）の2つに分かれる。新たに分かった主なものは、①第3項第3号は改正前からあり、量が第2項第3号へ移ったうえで費用の額及び保険料の水準が残ること（量は定めるものとされる事項、費用の額及び保険料の水準は定めるよう努めるものとされる事項）、②第3項第9号（入居定員総数）は改正前からあり、第5項第1号（勘案事項）との二重の構造であること、③第5項及び第14項の対象はいずれも第2項第1号から第3号までであること、④第115条の48の会議は改正後「支援会議」と称し構成員として地域包括支援センターが明示されること、⑤第118条第2項により都道府県介護保険事業支援計画にも中長期的な推計が定めるものとされること、⑥第117条第3項第6号・第7号及び第115条の49に指定登録施設介護支援の事業が加わること（3年以内）である。計画素案15箇所に反映した。引き続き必要なのは、①参照条文（001685804）の条文の内容（受領したものは画像であり文字の層がないため読み取れない）、②附則第3条から第77条までの経過措置、③認知症基本法ほか関係法令の条文（確認No.149）である</t>
+          <t>医療との連携は第5章 基本目標1及び第6章第5節の記述により扱い、医療法の協議の結果の考慮については施行の時期を確認できていない旨を［要確認］として記載する</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.181（点3）</t>
+          <t>確認事項No.189（点3）</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10206,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない</t>
+          <t>構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない【令和8年10月15日】参照条文により、介護保険法第117条第7項が「老人福祉法第20条の8第1項に規定する市町村老人福祉計画と一体のものとして作成されなければならない」ことを定めていることを確かめた。条及び項は第20条の8第1項である。老人福祉法そのものの条文は参照条文に収録されていない（第18条及び第20条の6のみ）ため、同条の内容及び市町村老人福祉計画の記載事項はなお確認できていない</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -10297,7 +10356,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す。【令和8年10月15日】新旧対照条文により社会福祉法第106条の12（新設）の内容を確かめた。小規模市町村が本事業を実施する場合、介護保険法第122条の2（第3項を除く。地域支援事業に係る国の交付金）並びに第123条第3項及び第4項（都道府県の負担）の規定の適用について、第122条の2第1項の「費用」から本事業として行う社会福祉法第106条の6第2項第3号イに掲げる事業に要する費用を除き、第123条第4項の「費用」から同条第2項第1号イ及び第3号ロに掲げる事業に要する費用を除くこととされている。重層的支援体制整備事業（社会福祉法第106条の4）と同じ構造である。除かれるのは国の交付金及び都道府県の負担の対象となる費用であり、当該費用は社会福祉法による交付金等により支弁されることとなる。除かれる事業の内容（第106条の6第2項第1号イ・第3号イ・第3号ロ）は確かめていない。小規模市町村の基準は厚生労働省令で定められるため、①（該当の有無）は引き続き確認を要する</t>
+          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す。【令和8年10月15日】新旧対照条文により社会福祉法第106条の12（新設）の内容を確かめた。小規模市町村が本事業を実施する場合、介護保険法第122条の2（第3項を除く。地域支援事業に係る国の交付金）並びに第123条第3項及び第4項（都道府県の負担）の規定の適用について、第122条の2第1項の「費用」から本事業として行う社会福祉法第106条の6第2項第3号イに掲げる事業に要する費用を除き、第123条第4項の「費用」から同条第2項第1号イ及び第3号ロに掲げる事業に要する費用を除くこととされている。重層的支援体制整備事業（社会福祉法第106条の4）と同じ構造である。除かれるのは国の交付金及び都道府県の負担の対象となる費用であり、当該費用は社会福祉法による交付金等により支弁されることとなる。除かれる事業の内容（第106条の6第2項第1号イ・第3号イ・第3号ロ）は確かめていない。小規模市町村の基準は厚生労働省令で定められるため、①（該当の有無）は引き続き確認を要する【令和8年10月15日】参照条文には社会福祉法第106条の3（包括的な支援体制の整備）までが収録されており、第106条の6は改正法により新設される規定であるため現れない。本件は進んでいない</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -10322,7 +10381,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>現行の指定の区分により特定施設入居者生活介護の見込量を算定し、定義の改正により対象となる施設の範囲が変わり得ることを計画素案の注に［要確認］として記載する。【令和8年10月15日】新旧対照条文により、現行の第8条第11項が「有料老人ホームその他厚生労働省令で定める施設であって、第20項に規定する地域密着型特定施設でないもの」であり、改正により「有料老人ホーム」が「老人福祉法第29条の18第5項に規定する登録有料老人ホーム」に置き換わることを確かめた。すなわち登録有料老人ホームを定義に加えるものではなく、登録を受けない有料老人ホームは特定施設に当たらなくなる。計画素案 第1章第9節2の記述を「定義に加える」から「有料老人ホームを登録有料老人ホームに改める」に是正した</t>
+          <t>現行の指定の区分により特定施設入居者生活介護の見込量を算定し、定義の改正により対象となる施設の範囲が変わり得ることを計画素案の注に［要確認］として記載する。【令和8年10月15日】新旧対照条文により、現行の第8条第11項が「有料老人ホームその他厚生労働省令で定める施設であって、第20項に規定する地域密着型特定施設でないもの」であり、改正により「有料老人ホーム」が「老人福祉法第29条の18第5項に規定する登録有料老人ホーム」に置き換わることを確かめた。すなわち登録有料老人ホームを定義に加えるものではなく、登録を受けない有料老人ホームは特定施設に当たらなくなる。計画素案 第1章第9節2の記述を「定義に加える」から「有料老人ホームを登録有料老人ホームに改める」に是正した。【令和8年10月15日】参照条文により、現行の第8条第11項が「有料老人ホームその他厚生労働省令で定める施設であって地域密着型特定施設でないもの」であることを2つ目の原典で確かめた。また同条第21項により、介護専用型特定施設はその入居者が要介護者、その配偶者その他厚生労働省令で定める者に限られるものであり、類型は入居の要件により定まることが分かった</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -10331,26 +10390,76 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="76" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>既定値で進める</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>「特定地域支援事業支援額」の内容</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、特定地域支援事業支援額を織り込まない。内容が示された時点で財源の区分を確かめ、再算定する</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.187（点1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>既定値で進める</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費の政令で定める額</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>令和6年度決算の水準を据え置いたまま算定し、政令で定める額との関係を確かめていない旨を計画素案の注に［要確認］として記載する</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.188（点1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="76" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>注1）「据え置き（区分A）」は、資料の受領を待たずに当方の側で確定できるものです。
 注2）「既定値で進める」は、決着しない場合の扱いを置けているため決定を待たずに作業を進められるものです。決定を受けた時点で見直します。
 注3）ここに現れないもの（既定値を置けていない確認事項）は、扱いを決めること自体が翌日の作業になります。02シートを見ます。
-注4）既定値のとおり計画素案へ反映し終えたもの163件（確認事項No.2・No.3・No.4・No.5・No.6・No.7・No.8・No.9・No.10・No.11・No.12・No.13・No.14・No.15・No.16・No.17・No.18・No.19・No.20・No.21・No.22・No.23・No.24・No.25・No.26・No.27・No.28・No.29・No.30・No.31・No.33・No.34・No.35・No.36・No.38・No.39・No.40・No.42・No.43・No.45・No.46・No.47・No.48・No.50・No.51・No.52・No.53・No.54・No.55・No.56・No.57・No.58・No.59・No.60・No.61・No.63・No.64・No.65・No.66・No.67・No.68・No.69・No.70・No.73・No.74・No.75・No.76・No.77・No.78・No.79・No.80・No.81・No.82・No.83・No.84・No.85・No.86・No.88・No.89・No.90・No.91・No.92・No.93・No.94・No.95・No.96・No.97・No.98・No.99・No.100・No.101・No.102・No.103・No.104・No.105・No.106・No.107・No.108・No.109・No.110・No.111・No.112・No.113・No.114・No.115・No.116・No.117・No.118・No.119・No.120・No.121・No.122・No.123・No.124・No.125・No.126・No.127・No.128・No.129・No.130・No.131・No.132・No.133・No.136・No.137・No.138・No.139・No.140・No.141・No.142・No.143・No.144・No.145・No.146・No.147・No.148・No.149・No.150・No.151・No.152・No.153・No.154・No.156・No.157・No.158・No.159・No.160・No.161・No.162・No.163・No.164・No.165・No.166・No.167・No.169・No.170・No.171・No.172・No.173・No.174・No.175・No.176・No.177）は、作業としては終わっているため本表から除いています。ご決定はなお待っています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+注4）既定値のとおり計画素案へ反映し終えたもの162件（確認事項No.2・No.3・No.4・No.5・No.6・No.7・No.8・No.9・No.10・No.11・No.12・No.13・No.14・No.15・No.16・No.17・No.18・No.19・No.20・No.21・No.22・No.23・No.24・No.25・No.26・No.27・No.28・No.29・No.30・No.31・No.33・No.34・No.35・No.36・No.38・No.39・No.40・No.42・No.43・No.45・No.46・No.47・No.48・No.50・No.51・No.52・No.53・No.54・No.55・No.56・No.57・No.58・No.59・No.60・No.61・No.63・No.64・No.65・No.66・No.67・No.68・No.69・No.70・No.73・No.74・No.75・No.76・No.77・No.78・No.79・No.80・No.81・No.82・No.83・No.84・No.85・No.86・No.88・No.89・No.90・No.91・No.92・No.93・No.94・No.95・No.96・No.97・No.98・No.99・No.100・No.101・No.102・No.103・No.104・No.105・No.106・No.107・No.108・No.109・No.110・No.111・No.112・No.114・No.115・No.116・No.117・No.118・No.119・No.120・No.121・No.122・No.123・No.124・No.125・No.126・No.127・No.128・No.129・No.130・No.131・No.132・No.133・No.136・No.137・No.138・No.139・No.140・No.141・No.142・No.143・No.144・No.145・No.146・No.147・No.148・No.149・No.150・No.151・No.152・No.153・No.154・No.156・No.157・No.158・No.159・No.160・No.161・No.162・No.163・No.164・No.165・No.166・No.167・No.169・No.170・No.171・No.172・No.173・No.174・No.175・No.176・No.177）は、作業としては終わっているため本表から除いています。ご決定はなお待っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>2　先に扱いを決めるもの（既定値を置けていない）　0件</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>ありません。未決の確認事項の全件に扱いを置けています。</t>
         </is>
@@ -10360,10 +10469,10 @@
   <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A19:E19"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10438,17 +10547,17 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第117条ほか関係法令の条文のご提供</t>
+          <t>医療法等の一部を改正する法律による介護保険法の改正の施行の状況</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>条番号のみを記載し項番号及び号番号は記載しない。記載事項の点検は条文の番号ではなく記載事項の内容を単位として行い、条文を確認できていない箇所は［要確認］として残す。【令和8年10月14日】社会福祉法等の一部を改正する法律案要綱を確認したことにより、改正後の第117条第2項第3号・第4号、第3項第4号・第5号、第5項及び第14項の号及び項が確定した。引き続き必要なのは、①改正後の条文及び新旧対照表（要綱は改正事項の要旨であり条文の文言を確認できない）、②附則第3条から第77条までの経過措置（有料老人ホームの登録制に係る経過措置の内容）、③改正に係らない号（第2項第1号・第2号、第3項第1号から第3号まで）の条文である。【令和8年10月15日　大きく解決】社会福祉法等の一部を改正する法律案の新旧対照条文（全353頁）を確認した。改正後の介護保険法第117条（第2項第3号・第4号、第3項第3号・第4号・第4号の2・第5号・第6号・第7号・第9号、第5項、第9項、第14項）、第115条の48（支援会議）、第118条第2項・第8項・第9項並びに第120条の3から第120条の5まで（協議会）の内容が確定した。介護保険法の改正は第3条関係（令和9年4月1日又は1年6月以内）と第4条関係（2年以内又は3年以内）の2つに分かれる。新たに分かった主なものは、①第3項第3号は改正前からあり、量が第2項第3号へ移ったうえで費用の額及び保険料の水準が残ること（量は定めるものとされる事項、費用の額及び保険料の水準は定めるよう努めるものとされる事項）、②第3項第9号（入居定員総数）は改正前からあり、第5項第1号（勘案事項）との二重の構造であること、③第5項及び第14項の対象はいずれも第2項第1号から第3号までであること、④第115条の48の会議は改正後「支援会議」と称し構成員として地域包括支援センターが明示されること、⑤第118条第2項により都道府県介護保険事業支援計画にも中長期的な推計が定めるものとされること、⑥第117条第3項第6号・第7号及び第115条の49に指定登録施設介護支援の事業が加わること（3年以内）である。計画素案15箇所に反映した。引き続き必要なのは、①参照条文（001685804）の条文の内容（受領したものは画像であり文字の層がないため読み取れない）、②附則第3条から第77条までの経過措置、③認知症基本法ほか関係法令の条文（確認No.149）である</t>
+          <t>医療との連携は第5章 基本目標1及び第6章第5節の記述により扱い、医療法の協議の結果の考慮については施行の時期を確認できていない旨を［要確認］として記載する</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.181（点3）</t>
+          <t>確認事項No.189（点3）</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10577,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない</t>
+          <t>構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない【令和8年10月15日】参照条文により、介護保険法第117条第7項が「老人福祉法第20条の8第1項に規定する市町村老人福祉計画と一体のものとして作成されなければならない」ことを定めていることを確かめた。条及び項は第20条の8第1項である。老人福祉法そのものの条文は参照条文に収録されていない（第18条及び第20条の6のみ）ため、同条の内容及び市町村老人福祉計画の記載事項はなお確認できていない</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -10618,7 +10727,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す。【令和8年10月15日】新旧対照条文により社会福祉法第106条の12（新設）の内容を確かめた。小規模市町村が本事業を実施する場合、介護保険法第122条の2（第3項を除く。地域支援事業に係る国の交付金）並びに第123条第3項及び第4項（都道府県の負担）の規定の適用について、第122条の2第1項の「費用」から本事業として行う社会福祉法第106条の6第2項第3号イに掲げる事業に要する費用を除き、第123条第4項の「費用」から同条第2項第1号イ及び第3号ロに掲げる事業に要する費用を除くこととされている。重層的支援体制整備事業（社会福祉法第106条の4）と同じ構造である。除かれるのは国の交付金及び都道府県の負担の対象となる費用であり、当該費用は社会福祉法による交付金等により支弁されることとなる。除かれる事業の内容（第106条の6第2項第1号イ・第3号イ・第3号ロ）は確かめていない。小規模市町村の基準は厚生労働省令で定められるため、①（該当の有無）は引き続き確認を要する</t>
+          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す。【令和8年10月15日】新旧対照条文により社会福祉法第106条の12（新設）の内容を確かめた。小規模市町村が本事業を実施する場合、介護保険法第122条の2（第3項を除く。地域支援事業に係る国の交付金）並びに第123条第3項及び第4項（都道府県の負担）の規定の適用について、第122条の2第1項の「費用」から本事業として行う社会福祉法第106条の6第2項第3号イに掲げる事業に要する費用を除き、第123条第4項の「費用」から同条第2項第1号イ及び第3号ロに掲げる事業に要する費用を除くこととされている。重層的支援体制整備事業（社会福祉法第106条の4）と同じ構造である。除かれるのは国の交付金及び都道府県の負担の対象となる費用であり、当該費用は社会福祉法による交付金等により支弁されることとなる。除かれる事業の内容（第106条の6第2項第1号イ・第3号イ・第3号ロ）は確かめていない。小規模市町村の基準は厚生労働省令で定められるため、①（該当の有無）は引き続き確認を要する【令和8年10月15日】参照条文には社会福祉法第106条の3（包括的な支援体制の整備）までが収録されており、第106条の6は改正法により新設される規定であるため現れない。本件は進んでいない</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -10789,12 +10898,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>No.1〜No.186 を数える</t>
+          <t>No.1〜No.189 を数える</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>186件／欠番 なし／重複 なし</t>
+          <t>189件／欠番 なし／重複 なし</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -10819,7 +10928,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>確認事項172件／資料提供依頼18件</t>
+          <t>確認事項173件／資料提供依頼18件</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -10844,7 +10953,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>172件／合わない なし</t>
+          <t>173件／合わない なし</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -11069,7 +11178,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>9件（区分A 0・既定値 9）／据え置きの区分A 0件・既定値があり未処理 9件</t>
+          <t>11件（区分A 0・既定値 11）／据え置きの区分A 0件・既定値があり未処理 11件</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -749,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>dcf60dd</t>
+          <t>ff183f2</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>改正後の条文及び特定地域の原典受領点検と計画素案への反映</t>
+          <t>確認事項の資料徴求の区分と参照条文の受領点検</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
@@ -1252,20 +1252,38 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>b224cc4</t>
+          <t>dcf60dd</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等改正法の法律案要綱（原典）の受領点検と計画素案への反映</t>
+          <t>改正後の条文及び特定地域の原典受領点検と計画素案への反映</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
       <c r="E24" s="6" t="inlineStr"/>
       <c r="F24" s="6" t="inlineStr"/>
     </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>b224cc4</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>社会福祉法等改正法の法律案要綱（原典）の受領点検と計画素案への反映</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
@@ -1277,8 +1295,8 @@
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -583,7 +583,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>毎日の終わりにWBSの現況・ペンディングの優先順位・当方の作業だけで進められるもの・翌日の作業順位を1枚にしたものです。基準日 令和8年10月15日。内部保管。</t>
+          <t>毎日の終わりにWBSの現況・ペンディングの優先順位・当方の作業だけで進められるもの・翌日の作業順位を1枚にしたものです。基準日 令和8年10月16日。内部保管。</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -770,7 +770,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）ごとの進捗率と、前に報告した時点からの動きです。基準日 令和8年10月15日。</t>
+          <t>仕様書４（1）〜（12）ごとの進捗率と、前に報告した時点からの動きです。基準日 令和8年10月16日。</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>注1）進捗の記録の基準日は 令和8年10月15日 です。本表の基準日（令和8年10月15日）と違うときは、進捗の更新がまだ行われていません。
+          <t>注1）進捗の記録の基準日は 令和8年10月16日 です。本表の基準日（令和8年10月16日）と違うときは、進捗の更新がまだ行われていません。
 注2）進捗率を更新したら、更新前の値を記録へ移します。移さないと、過去の時点を記す資料（月次の報告・議事録）の数値が書き換わります。</t>
         </is>
       </c>
@@ -1212,90 +1212,28 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="4" t="inlineStr"/>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>コミット</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>ff183f2</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>確認事項の資料徴求の区分と参照条文の受領点検</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr"/>
-      <c r="E23" s="6" t="inlineStr"/>
-      <c r="F23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>dcf60dd</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>改正後の条文及び特定地域の原典受領点検と計画素案への反映</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr"/>
-      <c r="E24" s="6" t="inlineStr"/>
-      <c r="F24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>b224cc4</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>社会福祉法等改正法の法律案要綱（原典）の受領点検と計画素案への反映</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>基準日のコミットはありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1332,7 +1270,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>完了していない確認事項と資料提供依頼を、影響度の点の高い順に並べたものです。点の付け方は03シートに全て書いています。基準日 令和8年10月15日。</t>
+          <t>完了していない確認事項と資料提供依頼を、影響度の点の高い順に並べたものです。点の付け方は03シートに全て書いています。基準日 令和8年10月16日。</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8015,7 @@
       </c>
       <c r="I164" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない【令和8年10月15日】参照条文により、介護保険法第117条第7項が「老人福祉法第20条の8第1項に規定する市町村老人福祉計画と一体のものとして作成されなければならない」ことを定めていることを確かめた。条及び項は第20条の8第1項である。老人福祉法そのものの条文は参照条文に収録されていない（第18条及び第20条の6のみ）ため、同条の内容及び市町村老人福祉計画の記載事項はなお確認できていない</t>
+          <t>構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8350,7 @@
       </c>
       <c r="I172" s="6" t="inlineStr">
         <is>
-          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す。【令和8年10月15日】新旧対照条文により社会福祉法第106条の12（新設）の内容を確かめた。小規模市町村が本事業を実施する場合、介護保険法第122条の2（第3項を除く。地域支援事業に係る国の交付金）並びに第123条第3項及び第4項（都道府県の負担）の規定の適用について、第122条の2第1項の「費用」から本事業として行う社会福祉法第106条の6第2項第3号イに掲げる事業に要する費用を除き、第123条第4項の「費用」から同条第2項第1号イ及び第3号ロに掲げる事業に要する費用を除くこととされている。重層的支援体制整備事業（社会福祉法第106条の4）と同じ構造である。除かれるのは国の交付金及び都道府県の負担の対象となる費用であり、当該費用は社会福祉法による交付金等により支弁されることとなる。除かれる事業の内容（第106条の6第2項第1号イ・第3号イ・第3号ロ）は確かめていない。小規模市町村の基準は厚生労働省令で定められるため、①（該当の有無）は引き続き確認を要する【令和8年10月15日】参照条文には社会福祉法第106条の3（包括的な支援体制の整備）までが収録されており、第106条の6は改正法により新設される規定であるため現れない。本件は進んでいない</t>
+          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す</t>
         </is>
       </c>
     </row>
@@ -8454,7 +8392,7 @@
       </c>
       <c r="I173" s="6" t="inlineStr">
         <is>
-          <t>現行の指定の区分により特定施設入居者生活介護の見込量を算定し、定義の改正により対象となる施設の範囲が変わり得ることを計画素案の注に［要確認］として記載する。【令和8年10月15日】新旧対照条文により、現行の第8条第11項が「有料老人ホームその他厚生労働省令で定める施設であって、第20項に規定する地域密着型特定施設でないもの」であり、改正により「有料老人ホーム」が「老人福祉法第29条の18第5項に規定する登録有料老人ホーム」に置き換わることを確かめた。すなわち登録有料老人ホームを定義に加えるものではなく、登録を受けない有料老人ホームは特定施設に当たらなくなる。計画素案 第1章第9節2の記述を「定義に加える」から「有料老人ホームを登録有料老人ホームに改める」に是正した。【令和8年10月15日】参照条文により、現行の第8条第11項が「有料老人ホームその他厚生労働省令で定める施設であって地域密着型特定施設でないもの」であることを2つ目の原典で確かめた。また同条第21項により、介護専用型特定施設はその入居者が要介護者、その配偶者その他厚生労働省令で定める者に限られるものであり、類型は入居の要件により定まることが分かった</t>
+          <t>現行の指定の区分により特定施設入居者生活介護の見込量を算定し、定義の改正により対象となる施設の範囲が変わり得ることを計画素案の注に［要確認］として記載する</t>
         </is>
       </c>
     </row>
@@ -9552,7 +9490,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02シートの点は次の規則だけで付けています。規則を変えれば02シートの並びも変わります。基準日 令和8年10月15日。</t>
+          <t>02シートの点は次の規則だけで付けています。規則を変えれば02シートの並びも変わります。基準日 令和8年10月16日。</t>
         </is>
       </c>
     </row>
@@ -10128,7 +10066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -10148,7 +10086,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>決定・資料の受領を待たずに当方の作業だけで進められるものです。基準日 令和8年10月15日。</t>
+          <t>決定・資料の受領を待たずに当方の作業だけで進められるものです。基準日 令和8年10月16日。</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10094,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　当方の作業だけで進められるもの　11件</t>
+          <t>1　当方の作業だけで進められるもの　2件</t>
         </is>
       </c>
     </row>
@@ -10219,265 +10157,40 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画と市町村老人福祉計画の関係</t>
+          <t>「特定地域支援事業支援額」の内容</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない【令和8年10月15日】参照条文により、介護保険法第117条第7項が「老人福祉法第20条の8第1項に規定する市町村老人福祉計画と一体のものとして作成されなければならない」ことを定めていることを確かめた。条及び項は第20条の8第1項である。老人福祉法そのものの条文は参照条文に収録されていない（第18条及び第20条の6のみ）ため、同条の内容及び市町村老人福祉計画の記載事項はなお確認できていない</t>
+          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、特定地域支援事業支援額を織り込まない。内容が示された時点で財源の区分を確かめ、再算定する</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.178（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>成年後見制度の利用の促進に関する施策についての基本的な計画の策定状況</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>同計画は構成3町が定めるものとして計画素案に記載し、本計画は介護保険法第117条第3項による権利擁護の施策（第5章 基本目標1）をもって接続する。中核機関の整備の状況は［要確認］として残す</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.179（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>要配慮者利用施設の避難確保計画の対象施設と作成状況</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>対象施設及び作成の状況を［要確認］として残し、第5章 基本目標5の主な事業に作成及び避難訓練の確認を置くにとどめ、達成目標に数値を掲げない。避難確保計画はBCPとは別の計画であり、BCPの策定率をもって作成の状況としない</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.180（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>介護給付費分科会の資料（原本）のご提供</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>計画素案には国において検討されている事項があることまでを記載し、単位数・要件・施行時期を書かない。原本を確認できていないことを［要確認］として残し、改定率及び単価は令和7年度の実績で固定したまま概算する</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.182（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>夜間対応型訪問介護の定期巡回・随時対応型への移行の扱い</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>現行の区分のまま夜間対応型訪問介護を実績なし（0）として立て、移行が検討されていることを計画素案の注に記載する。省令等が確定した時点で区分を組み替える</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.183（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>短期入所生活介護の季節利用及び長期利用の実態</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>令和7年度（12か月の完結年度）の実績により短期入所生活介護の見込量を算定し、季節補正を行わない（基準年度が完結年度であるため年度換算係数は1.0000となり効きは0円である）。季節利用の例外が示された時点で利用日数の置き方を確かめる</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.184（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>小規模市町村地域支援連携協働体制整備事業の対象となるかどうか</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す。【令和8年10月15日】新旧対照条文により社会福祉法第106条の12（新設）の内容を確かめた。小規模市町村が本事業を実施する場合、介護保険法第122条の2（第3項を除く。地域支援事業に係る国の交付金）並びに第123条第3項及び第4項（都道府県の負担）の規定の適用について、第122条の2第1項の「費用」から本事業として行う社会福祉法第106条の6第2項第3号イに掲げる事業に要する費用を除き、第123条第4項の「費用」から同条第2項第1号イ及び第3号ロに掲げる事業に要する費用を除くこととされている。重層的支援体制整備事業（社会福祉法第106条の4）と同じ構造である。除かれるのは国の交付金及び都道府県の負担の対象となる費用であり、当該費用は社会福祉法による交付金等により支弁されることとなる。除かれる事業の内容（第106条の6第2項第1号イ・第3号イ・第3号ロ）は確かめていない。小規模市町村の基準は厚生労働省令で定められるため、①（該当の有無）は引き続き確認を要する【令和8年10月15日】参照条文には社会福祉法第106条の3（包括的な支援体制の整備）までが収録されており、第106条の6は改正法により新設される規定であるため現れない。本件は進んでいない</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.185（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>特定施設の定義の改正による区域内3施設の扱い</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>現行の指定の区分により特定施設入居者生活介護の見込量を算定し、定義の改正により対象となる施設の範囲が変わり得ることを計画素案の注に［要確認］として記載する。【令和8年10月15日】新旧対照条文により、現行の第8条第11項が「有料老人ホームその他厚生労働省令で定める施設であって、第20項に規定する地域密着型特定施設でないもの」であり、改正により「有料老人ホーム」が「老人福祉法第29条の18第5項に規定する登録有料老人ホーム」に置き換わることを確かめた。すなわち登録有料老人ホームを定義に加えるものではなく、登録を受けない有料老人ホームは特定施設に当たらなくなる。計画素案 第1章第9節2の記述を「定義に加える」から「有料老人ホームを登録有料老人ホームに改める」に是正した。【令和8年10月15日】参照条文により、現行の第8条第11項が「有料老人ホームその他厚生労働省令で定める施設であって地域密着型特定施設でないもの」であることを2つ目の原典で確かめた。また同条第21項により、介護専用型特定施設はその入居者が要介護者、その配偶者その他厚生労働省令で定める者に限られるものであり、類型は入居の要件により定まることが分かった</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.186（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>「特定地域支援事業支援額」の内容</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、特定地域支援事業支援額を織り込まない。内容が示された時点で財源の区分を確かめ、再算定する</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
           <t>確認事項No.187（点1）</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>地域支援事業費の政令で定める額</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>令和6年度決算の水準を据え置いたまま算定し、政令で定める額との関係を確かめていない旨を計画素案の注に［要確認］として記載する</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.188（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="76" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+    <row r="8" ht="76" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>注1）「据え置き（区分A）」は、資料の受領を待たずに当方の側で確定できるものです。
 注2）「既定値で進める」は、決着しない場合の扱いを置けているため決定を待たずに作業を進められるものです。決定を受けた時点で見直します。
 注3）ここに現れないもの（既定値を置けていない確認事項）は、扱いを決めること自体が翌日の作業になります。02シートを見ます。
-注4）既定値のとおり計画素案へ反映し終えたもの162件（確認事項No.2・No.3・No.4・No.5・No.6・No.7・No.8・No.9・No.10・No.11・No.12・No.13・No.14・No.15・No.16・No.17・No.18・No.19・No.20・No.21・No.22・No.23・No.24・No.25・No.26・No.27・No.28・No.29・No.30・No.31・No.33・No.34・No.35・No.36・No.38・No.39・No.40・No.42・No.43・No.45・No.46・No.47・No.48・No.50・No.51・No.52・No.53・No.54・No.55・No.56・No.57・No.58・No.59・No.60・No.61・No.63・No.64・No.65・No.66・No.67・No.68・No.69・No.70・No.73・No.74・No.75・No.76・No.77・No.78・No.79・No.80・No.81・No.82・No.83・No.84・No.85・No.86・No.88・No.89・No.90・No.91・No.92・No.93・No.94・No.95・No.96・No.97・No.98・No.99・No.100・No.101・No.102・No.103・No.104・No.105・No.106・No.107・No.108・No.109・No.110・No.111・No.112・No.114・No.115・No.116・No.117・No.118・No.119・No.120・No.121・No.122・No.123・No.124・No.125・No.126・No.127・No.128・No.129・No.130・No.131・No.132・No.133・No.136・No.137・No.138・No.139・No.140・No.141・No.142・No.143・No.144・No.145・No.146・No.147・No.148・No.149・No.150・No.151・No.152・No.153・No.154・No.156・No.157・No.158・No.159・No.160・No.161・No.162・No.163・No.164・No.165・No.166・No.167・No.169・No.170・No.171・No.172・No.173・No.174・No.175・No.176・No.177）は、作業としては終わっているため本表から除いています。ご決定はなお待っています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+注4）既定値のとおり計画素案へ反映し終えたもの171件（確認事項No.2・No.3・No.4・No.5・No.6・No.7・No.8・No.9・No.10・No.11・No.12・No.13・No.14・No.15・No.16・No.17・No.18・No.19・No.20・No.21・No.22・No.23・No.24・No.25・No.26・No.27・No.28・No.29・No.30・No.31・No.33・No.34・No.35・No.36・No.38・No.39・No.40・No.42・No.43・No.45・No.46・No.47・No.48・No.50・No.51・No.52・No.53・No.54・No.55・No.56・No.57・No.58・No.59・No.60・No.61・No.63・No.64・No.65・No.66・No.67・No.68・No.69・No.70・No.73・No.74・No.75・No.76・No.77・No.78・No.79・No.80・No.81・No.82・No.83・No.84・No.85・No.86・No.88・No.89・No.90・No.91・No.92・No.93・No.94・No.95・No.96・No.97・No.98・No.99・No.100・No.101・No.102・No.103・No.104・No.105・No.106・No.107・No.108・No.109・No.110・No.111・No.112・No.114・No.115・No.116・No.117・No.118・No.119・No.120・No.121・No.122・No.123・No.124・No.125・No.126・No.127・No.128・No.129・No.130・No.131・No.132・No.133・No.136・No.137・No.138・No.139・No.140・No.141・No.142・No.143・No.144・No.145・No.146・No.147・No.148・No.149・No.150・No.151・No.152・No.153・No.154・No.156・No.157・No.158・No.159・No.160・No.161・No.162・No.163・No.164・No.165・No.166・No.167・No.169・No.170・No.171・No.172・No.173・No.174・No.175・No.176・No.177・No.178・No.179・No.180・No.182・No.183・No.184・No.185・No.186・No.188）は、作業としては終わっているため本表から除いています。ご決定はなお待っています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>2　先に扱いを決めるもの（既定値を置けていない）　0件</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>ありません。未決の確認事項の全件に扱いを置けています。</t>
         </is>
@@ -10487,10 +10200,10 @@
   <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A10:E10"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10502,7 +10215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -10515,7 +10228,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>翌日（令和8年10月16日）の作業順位</t>
+          <t>翌日（令和8年10月17日）の作業順位</t>
         </is>
       </c>
     </row>
@@ -10590,17 +10303,17 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画と市町村老人福祉計画の関係</t>
+          <t>「特定地域支援事業支援額」の内容</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>構成3町の高齢者福祉計画が市町村老人福祉計画に当たることを計画素案に記載し、一体のものとして作成する方法は共通KPIと役割分担表による接続とする旨を［要協議］として残す。老人福祉事業の量の目標は3町の計画に委ね、本計画には掲げない【令和8年10月15日】参照条文により、介護保険法第117条第7項が「老人福祉法第20条の8第1項に規定する市町村老人福祉計画と一体のものとして作成されなければならない」ことを定めていることを確かめた。条及び項は第20条の8第1項である。老人福祉法そのものの条文は参照条文に収録されていない（第18条及び第20条の6のみ）ため、同条の内容及び市町村老人福祉計画の記載事項はなお確認できていない</t>
+          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、特定地域支援事業支援額を織り込まない。内容が示された時点で財源の区分を確かめ、再算定する</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.178（点1）</t>
+          <t>確認事項No.187（点1）</t>
         </is>
       </c>
     </row>
@@ -10608,24 +10321,24 @@
       <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>進める</t>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>催促・照会</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>成年後見制度の利用の促進に関する施策についての基本的な計画の策定状況</t>
+          <t>地域支援事業の量の見込みを算定してよいか（発注者）</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>同計画は構成3町が定めるものとして計画素案に記載し、本計画は介護保険法第117条第3項による権利擁護の施策（第5章 基本目標1）をもって接続する。中核機関の整備の状況は［要確認］として残す</t>
+          <t>点8。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／月額への効き 最大7円（令和7年度の総合事業の事業費）／法定記載事項 法第117条に直結</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.179（点1）</t>
+          <t>確認事項No.112</t>
         </is>
       </c>
     </row>
@@ -10633,24 +10346,24 @@
       <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>進める</t>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>催促・照会</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>要配慮者利用施設の避難確保計画の対象施設と作成状況</t>
+          <t>認知症総合支援事業の実績のご提供（発注者）</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>対象施設及び作成の状況を［要確認］として残し、第5章 基本目標5の主な事業に作成及び避難訓練の確認を置くにとどめ、達成目標に数値を掲げない。避難確保計画はBCPとは別の計画であり、BCPの策定率をもって作成の状況としない</t>
+          <t>点7。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／法定記載事項 法第117条に直結</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.180（点1）</t>
+          <t>確認事項No.150</t>
         </is>
       </c>
     </row>
@@ -10658,179 +10371,29 @@
       <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>進める</t>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>催促・照会</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>介護給付費分科会の資料（原本）のご提供</t>
+          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案（発注者・北海道）</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>計画素案には国において検討されている事項があることまでを記載し、単位数・要件・施行時期を書かない。原本を確認できていないことを［要確認］として残し、改定率及び単価は令和7年度の実績で固定したまま概算する</t>
+          <t>点6。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／月額への効き 最大47円（第7期給付適正化計画の目標のご判断）</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.182（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>進める</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>夜間対応型訪問介護の定期巡回・随時対応型への移行の扱い</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>現行の区分のまま夜間対応型訪問介護を実績なし（0）として立て、移行が検討されていることを計画素案の注に記載する。省令等が確定した時点で区分を組み替える</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.183（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>進める</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>短期入所生活介護の季節利用及び長期利用の実態</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>令和7年度（12か月の完結年度）の実績により短期入所生活介護の見込量を算定し、季節補正を行わない（基準年度が完結年度であるため年度換算係数は1.0000となり効きは0円である）。季節利用の例外が示された時点で利用日数の置き方を確かめる</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.184（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>進める</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>小規模市町村地域支援連携協働体制整備事業の対象となるかどうか</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>現行の地域支援事業費（令和6年度決算による据え置き）により算定し、本事業を実施しないものとして扱う。厚生労働省令が示された時点で該当の有無を確かめ、該当する場合は費用の支弁の構造を改めて算定し直す。【令和8年10月15日】新旧対照条文により社会福祉法第106条の12（新設）の内容を確かめた。小規模市町村が本事業を実施する場合、介護保険法第122条の2（第3項を除く。地域支援事業に係る国の交付金）並びに第123条第3項及び第4項（都道府県の負担）の規定の適用について、第122条の2第1項の「費用」から本事業として行う社会福祉法第106条の6第2項第3号イに掲げる事業に要する費用を除き、第123条第4項の「費用」から同条第2項第1号イ及び第3号ロに掲げる事業に要する費用を除くこととされている。重層的支援体制整備事業（社会福祉法第106条の4）と同じ構造である。除かれるのは国の交付金及び都道府県の負担の対象となる費用であり、当該費用は社会福祉法による交付金等により支弁されることとなる。除かれる事業の内容（第106条の6第2項第1号イ・第3号イ・第3号ロ）は確かめていない。小規模市町村の基準は厚生労働省令で定められるため、①（該当の有無）は引き続き確認を要する【令和8年10月15日】参照条文には社会福祉法第106条の3（包括的な支援体制の整備）までが収録されており、第106条の6は改正法により新設される規定であるため現れない。本件は進んでいない</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.185（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>催促・照会</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>地域支援事業の量の見込みを算定してよいか（発注者）</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>点8。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／月額への効き 最大7円（令和7年度の総合事業の事業費）／法定記載事項 法第117条に直結</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.112</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>催促・照会</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>認知症総合支援事業の実績のご提供（発注者）</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>点7。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／法定記載事項 法第117条に直結</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.150</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>催促・照会</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>財政調整交付金の算定における給付適正化主要3事業の取組状況の勘案（発注者・北海道）</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>点6。期限 当月（R8.10）／止めている成果物 概算／止めている成果物 計画素案／月額への効き 最大47円（第7期給付適正化計画の目標のご判断）</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
           <t>確認事項No.93</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="62" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="10" ht="62" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>注1）「進める」は決定を待たずに着手できるもの、「催促・照会」は相手のある作業です。相手のある作業は午前のうちに出します（返事に日数がかかるため）。
 注2）04シートの作業継続可能なものは上位8件まで、催促・照会は優先以上の上位5件までを掲げています。残りは02・04シートを見ます。
@@ -10840,8 +10403,8 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A10:E10"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11121,7 +10684,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>記録 令和8年10月15日／本表 令和8年10月15日</t>
+          <t>記録 令和8年10月16日／本表 令和8年10月16日</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -11171,7 +10734,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>11件（進める8・催促3）</t>
+          <t>5件（進める2・催促3）</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -11196,7 +10759,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>11件（区分A 0・既定値 11）／据え置きの区分A 0件・既定値があり未処理 11件</t>
+          <t>2件（区分A 0・既定値 2）／据え置きの区分A 0件・既定値があり未処理 2件</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -749,7 +749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -835,7 +835,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>▲9pt</t>
+          <t>±0pt</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>▲3pt</t>
+          <t>±0pt</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>▲20pt</t>
+          <t>±0pt</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>▲5pt</t>
+          <t>±0pt</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>▲18pt</t>
+          <t>±0pt</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>▲49pt</t>
+          <t>＋10pt</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>▲36pt</t>
+          <t>±0pt</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>＋30pt</t>
+          <t>±0pt</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>＋12pt</t>
+          <t>±0pt</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>▲28pt</t>
+          <t>±0pt</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="C18" s="11" t="n">
-        <v>0.6679563492063492</v>
+        <v>0.6779563492063492</v>
       </c>
       <c r="D18" s="10" t="inlineStr"/>
       <c r="E18" s="10" t="inlineStr"/>
@@ -1212,27 +1212,53 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>基準日のコミットはありません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="13" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="4" t="inlineStr"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>コミット</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>a8c96dc</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>WBSを基準日 令和8年10月16日で更新し、既定値と件数の切り出しを是正</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr"/>
+      <c r="E23" s="6" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A21:F21"/>
   </mergeCells>
@@ -10659,7 +10685,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>最小0.12・最大0.94・全体67％</t>
+          <t>最小0.12・最大0.94・全体68％</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -10709,7 +10735,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>記録9件（最新 令和8年9月28日）</t>
+          <t>記録10件（最新 令和8年9月28日）</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -132,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -172,13 +172,13 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -186,6 +186,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -752,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1215,27 +1218,53 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>基準日のコミットはありません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="14" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="4" t="inlineStr"/>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>コミット</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>2e2a16e</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>受託者案による確定のご了承（令和8年10月19日）を台帳・工程・WBSへ反映</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr"/>
+      <c r="E23" s="6" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A21:F21"/>
   </mergeCells>
@@ -1249,7 +1278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1281,7 +1310,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　確認事項（決定を求めるもの）　0件</t>
+          <t>1　確認事項（決定を求めるもの）　1件</t>
         </is>
       </c>
     </row>
@@ -1332,8 +1361,49 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>190</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム B5・B6 の【他地域と比較】の出力における比較地域</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第3章第4節2・認定率の年齢調整分析</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>計画本文には</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>注1）点が9以上を至急、6以上8以下を優先、5以下を通常とみます（03シート）。
 注2）「決着しない場合の当方の扱い」が空のものは、決まらないと当方の作業が止まります。 先に扱いを決めます。
@@ -1341,119 +1411,76 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>2　資料提供依頼（資料の提供を求めるもの）　18件</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="8"/>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2　資料提供依頼（資料の提供を求めるもの）　16件</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>確定する主張</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>入手先</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>希望時期</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>優先</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>領域</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>第9期の評価の完成</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="G10" s="15" t="inlineStr">
-        <is>
-          <t>最高</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>一部受領</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>G</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
+          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
+          <t>第9期の評価の完成</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -1468,83 +1495,83 @@
       </c>
       <c r="G11" s="16" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>最高</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>一部受領</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
+          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
+          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1552,85 +1579,85 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>代替により解消</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
+          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>代替により解消</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="5" t="n">
-        <v>7</v>
-      </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>事業所・施設の定員と稼働の実績</t>
+          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>稼働率の低下の有無、定員減少の経緯</t>
+          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1638,42 +1665,42 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G15" s="17" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B16" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B16" s="5" t="n">
-        <v>8</v>
-      </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>未利用認定者の内訳とケアプランのサービス構成</t>
+          <t>事業所・施設の定員と稼働の実績</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
+          <t>稼働率の低下の有無、定員減少の経緯</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -1681,7 +1708,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G16" s="17" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1693,25 +1720,25 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B17" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B17" s="5" t="n">
-        <v>9</v>
-      </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
+          <t>未利用認定者の内訳とケアプランのサービス構成</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>第9期の剰余額（現在は概算）</t>
+          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -1724,7 +1751,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G17" s="17" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1736,30 +1763,30 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>E</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B18" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B18" s="5" t="n">
-        <v>17</v>
-      </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
+          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>給付費の地域内還流の議論</t>
+          <t>第9期の剰余額（現在は概算）</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -1767,7 +1794,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1779,25 +1806,25 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>H</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
+          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
+          <t>給付費の地域内還流の議論</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1810,7 +1837,7 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G19" s="17" t="inlineStr">
         <is>
           <t>高</t>
         </is>
@@ -1822,30 +1849,30 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
+          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>サービス種別ごとの見込量の様式</t>
+          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -1853,128 +1880,128 @@
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G20" s="17" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
+          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>第10期の段階設計と保険料算定</t>
+          <t>サービス種別ごとの見込量の様式</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>告示後</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G21" s="17" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>小学校区と日常生活圏域の対応関係</t>
+          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>圏域別の分析、圏域設定の見直し</t>
+          <t>第10期の段階設計と保険料算定</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>美瑛町・3町</t>
+          <t>国の情報</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>告示後</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>評価の枠組みの整理</t>
+          <t>圏域別の分析、圏域設定の見直し</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>美瑛町・3町</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -1982,7 +2009,7 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G23" s="17" t="inlineStr">
+      <c r="G23" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -1994,56 +2021,56 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B24" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B24" s="5" t="n">
-        <v>16</v>
-      </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>見える化システムD49の指標定義</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>地域差指数の分解の可否</t>
+          <t>評価の枠組みの整理</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>見える化システム・厚生労働省</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G24" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" s="5" t="n">
         <v>20</v>
@@ -2068,7 +2095,7 @@
           <t>随時</t>
         </is>
       </c>
-      <c r="G25" s="17" t="inlineStr">
+      <c r="G25" s="15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
@@ -2086,29 +2113,29 @@
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>見える化B5a・B6a・B6bの令和8年3月末の値</t>
+          <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>中重度・軽度の認定率の推移</t>
+          <t>世帯構成の現状</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>見える化システム</t>
+          <t>総務省・3町</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>公表後</t>
         </is>
       </c>
       <c r="G26" s="18" t="inlineStr">
@@ -2123,55 +2150,12 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="40" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>世帯構成の現状</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>総務省・3町</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>公表後</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="14" t="inlineStr">
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>注）03シートの確認事項が「決定」を求めるものであるのに対し、本表は「資料の提供」を求めるものです。資料が届かない場合の扱いは04シートの区分で示しています。</t>
         </is>
@@ -2179,11 +2163,11 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A7:I7"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A28:I28"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A27:I27"/>
     <mergeCell ref="A4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2265,7 +2249,7 @@
           <t>回答期限が基準日の月より前（超過している）</t>
         </is>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>2</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -2288,7 +2272,7 @@
           <t>回答期限が基準日と同じ月</t>
         </is>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2334,7 +2318,7 @@
           <t>概算（第1次・第2次）を止めている</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="16" t="n">
         <v>3</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2357,7 +2341,7 @@
           <t>保険料に関わるものを止めている</t>
         </is>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -2380,12 +2364,12 @@
           <t>計画素案を止めている</t>
         </is>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>0件</t>
+          <t>1件</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2387,7 @@
           <t>据え置きに紐づき月額100円以上を動かし得る</t>
         </is>
       </c>
-      <c r="D12" s="15" t="n">
+      <c r="D12" s="16" t="n">
         <v>4</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -2426,7 +2410,7 @@
           <t>同 50円以上100円未満</t>
         </is>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>2</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -2449,7 +2433,7 @@
           <t>同 50円未満（効きの記載がある）</t>
         </is>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>1</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -2472,7 +2456,7 @@
           <t>介護保険法第117条の記載事項に直結する</t>
         </is>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -2495,7 +2479,7 @@
           <t>決着しない場合の当方の扱いを置けていない</t>
         </is>
       </c>
-      <c r="D16" s="15" t="n">
+      <c r="D16" s="16" t="n">
         <v>3</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -2571,7 +2555,7 @@
       <c r="A22" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>至急</t>
         </is>
@@ -2596,7 +2580,7 @@
       <c r="A23" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>優先</t>
         </is>
@@ -2621,7 +2605,7 @@
       <c r="A24" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
@@ -2633,7 +2617,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>0件</t>
+          <t>1件</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -2727,7 +2711,7 @@
       <c r="A30" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -2820,7 +2804,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　当方の作業だけで進められるもの　0件</t>
+          <t>1　当方の作業だけで進められるもの　1件</t>
         </is>
       </c>
     </row>
@@ -2847,10 +2831,28 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>ありません。据え置きのうち当方の側で確定できるもの（区分A）は残っておらず、既定値を置けている未決の確認事項はすべて仮置きのとおり処理しています（注4）。ご決定をお待ちしている間に当方の側で進められる作業はここにはありません。</t>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>既定値で進める</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>見える化システム B5・B6 の【他地域と比較】の出力における比較地域</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>計画本文には</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.190（点1）</t>
         </is>
       </c>
     </row>
@@ -2873,20 +2875,19 @@
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>ありません。未決の確認事項の全件に扱いを置けています。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A7:E7"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A6:E6"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2899,7 +2900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2955,24 +2956,24 @@
       <c r="A5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>催促・照会</t>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>進める</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算（発注者）</t>
+          <t>見える化システム B5・B6 の【他地域と比較】の出力における比較地域</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>優先度最高・希望時期R8.8。第9期の評価の完成</t>
+          <t>計画本文には</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13</t>
+          <t>確認事項No.190（点1）</t>
         </is>
       </c>
     </row>
@@ -2980,24 +2981,24 @@
       <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>催促・照会</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（発注者）</t>
+          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算（発注者）</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>優先度高・希望時期R8.8。4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
+          <t>優先度最高・希望時期R8.8。第9期の評価の完成</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.14</t>
+          <t>資料提供依頼No.13</t>
         </is>
       </c>
     </row>
@@ -3005,24 +3006,24 @@
       <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>催促・照会</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）（3町）</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（発注者）</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>優先度高・希望時期R8.9。東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
+          <t>優先度高・希望時期R8.8。4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.3</t>
+          <t>資料提供依頼No.14</t>
         </is>
       </c>
     </row>
@@ -3030,24 +3031,24 @@
       <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>催促・照会</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）（発注者）</t>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）（3町）</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>優先度高・希望時期R8.9。交付金評価の解釈、W144の要因、評価対象期間</t>
+          <t>優先度高・希望時期R8.9。東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.5</t>
+          <t>資料提供依頼No.3</t>
         </is>
       </c>
     </row>
@@ -3055,29 +3056,54 @@
       <c r="A9" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>催促・照会</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）（発注者）</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>優先度高・希望時期R8.9。交付金評価の解釈、W144の要因、評価対象期間</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>資料提供依頼No.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>催促・照会</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
           <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）（発注者・国保連）</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>優先度高・希望時期R8.10。給付水準の要因（区域外利用との関係は無相関と判明）</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>資料提供依頼No.6</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="76" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
+    <row r="11" ht="76" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>注1）「進める」は決定を待たずに着手できるもの、「催促・照会」は相手のある作業です。相手のある作業は午前のうちに出します（返事に日数がかかるため）。
 注2）04シートの作業継続可能なものは上位8件まで、催促・照会は優先以上の上位5件までを掲げています。残りは02・04シートを見ます。
@@ -3086,294 +3112,294 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="12"/>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>2　国の公布を待つもの　13件</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="21" t="inlineStr">
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>令和8年10月19日のご了承により受託者案で確定しましたが、保険料に関わる国の政令・省令・告示の公布後に再算定するものです。催促できないため翌日の作業には挙げていません。公布を確かめた時点で算定をやり直します。</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="4" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="4" t="inlineStr"/>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>確認事項</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>何を待つか</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>特定地域の基準（厚生労働省令）及び対象地域の指定</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="5" t="n">
-        <v>33</v>
-      </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階）</t>
+          <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>第10期の所得段階・乗率・第1号被保険者負担割合（政令）</t>
+          <t>特定地域の基準（厚生労働省令）及び対象地域の指定</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提（受託者案）</t>
+          <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提（報酬改定率・負担割合・基金の取崩し）</t>
+          <t>第10期の所得段階・乗率・第1号被保険者負担割合（政令）</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+          <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等改正法の政令・省令及び介護報酬改定</t>
+          <t>保険料算定の前提（報酬改定率・負担割合・基金の取崩し）</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>令和8年度介護報酬改定の単価への反映</t>
+          <t>社会福祉法等改正法の政令・省令及び介護報酬改定</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
+          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>令和9年度介護報酬改定の改定率（告示）</t>
+          <t>令和8年度介護報酬改定の単価への反映</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月新設の3区分（省令・告示）</t>
+          <t>令和9年度介護報酬改定の改定率（告示）</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>137</v>
+        <v>115</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
+          <t>令和9年4月に新設される区分を見込量に立てるか</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の年度（報酬改定の告示）</t>
+          <t>令和9年4月新設の3区分（省令・告示）</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>176</v>
+        <v>137</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>介護サービス事業者経営情報データベースの公表結果の活用の範囲</t>
+          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>介護サービス事業者経営情報データベースの分析結果の公表</t>
+          <t>1人1月あたり給付費の年度（報酬改定の告示）</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>夜間対応型訪問介護の定期巡回・随時対応型への移行の扱い</t>
+          <t>介護サービス事業者経営情報データベースの公表結果の活用の範囲</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>夜間対応型訪問介護の移行に係る省令等</t>
+          <t>介護サービス事業者経営情報データベースの分析結果の公表</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>小規模市町村地域支援連携協働体制整備事業の対象となるかどうか</t>
+          <t>夜間対応型訪問介護の定期巡回・随時対応型への移行の扱い</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>小規模市町村の基準（厚生労働省令）</t>
+          <t>夜間対応型訪問介護の移行に係る省令等</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費の政令で定める額</t>
+          <t>小規模市町村地域支援連携協働体制整備事業の対象となるかどうか</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費の政令で定める額</t>
+          <t>小規模市町村の基準（厚生労働省令）</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>188</v>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費の政令で定める額</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費の政令で定める額</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr"/>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B27" s="5" t="n">
+      <c r="B28" s="5" t="n">
         <v>189</v>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>医療法等の一部を改正する法律による介護保険法の改正の施行の状況</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>医療法等改正法による改正の施行の日（政令）</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr"/>
+      <c r="E28" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A10:E10"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3437,7 +3463,7 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="22" t="n">
+      <c r="A5" s="23" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -3447,22 +3473,22 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>No.1〜No.189 を数える</t>
+          <t>No.1〜No.190 を数える</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>189件／欠番 なし／重複 なし</t>
-        </is>
-      </c>
-      <c r="E5" s="23" t="inlineStr">
+          <t>190件／欠番 なし／重複 なし</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="22" t="n">
+      <c r="A6" s="23" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -3477,17 +3503,17 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>確認事項0件／資料提供依頼18件</t>
-        </is>
-      </c>
-      <c r="E6" s="23" t="inlineStr">
+          <t>確認事項1件／資料提供依頼16件</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="22" t="n">
+      <c r="A7" s="23" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
@@ -3502,17 +3528,17 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>0件／合わない なし</t>
-        </is>
-      </c>
-      <c r="E7" s="23" t="inlineStr">
+          <t>1件／合わない なし</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="22" t="n">
+      <c r="A8" s="23" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -3530,14 +3556,14 @@
           <t>降順 適合</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="22" t="n">
+      <c r="A9" s="23" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -3552,17 +3578,17 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>内訳0種／規則6種／載っていない なし</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="inlineStr">
+          <t>内訳1種／規則6種／載っていない なし</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="22" t="n">
+      <c r="A10" s="23" t="n">
         <v>5.5</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -3580,14 +3606,14 @@
           <t>7件を拾った（最大327円）／上限超え なし</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="22" t="n">
+      <c r="A11" s="23" t="n">
         <v>6</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -3605,14 +3631,14 @@
           <t>4＋0＋15＋4＝23／据え置き23件</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="22" t="n">
+      <c r="A12" s="23" t="n">
         <v>7</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -3630,14 +3656,14 @@
           <t>最小0.12・最大1.00・全体75％</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="22" t="n">
+      <c r="A13" s="23" t="n">
         <v>8</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -3655,14 +3681,14 @@
           <t>記録 令和8年10月19日／本表 令和8年10月19日</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="22" t="n">
+      <c r="A14" s="23" t="n">
         <v>9</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
@@ -3680,14 +3706,14 @@
           <t>記録11件（最新 令和8年9月28日）</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="22" t="n">
+      <c r="A15" s="23" t="n">
         <v>10</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
@@ -3702,17 +3728,17 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>5件（進める0・催促5）</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="inlineStr">
+          <t>6件（進める1・催促5）</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="22" t="n">
+      <c r="A16" s="23" t="n">
         <v>11</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
@@ -3727,17 +3753,17 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>0件（区分A 0・既定値 0）／据え置きの区分A 0件・既定値があり未処理 0件</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="inlineStr">
+          <t>1件（区分A 0・既定値 1）／据え置きの区分A 0件・既定値があり未処理 1件</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="22" t="n">
+      <c r="A17" s="23" t="n">
         <v>12</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -3755,14 +3781,14 @@
           <t>0件</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="22" t="n">
+      <c r="A18" s="23" t="n">
         <v>13</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
@@ -3780,14 +3806,14 @@
           <t>0件</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="22" t="n">
+      <c r="A19" s="23" t="n">
         <v>14</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
@@ -3805,14 +3831,14 @@
           <t>残り0件</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="22" t="n">
+      <c r="A20" s="23" t="n">
         <v>15</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -3830,7 +3856,7 @@
           <t>台帳にあり／古い記述 なし</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="24" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -3849,7 +3875,7 @@
           <t>適合16件・不適合0件</t>
         </is>
       </c>
-      <c r="E21" s="24" t="inlineStr">
+      <c r="E21" s="25" t="inlineStr">
         <is>
           <t>適合</t>
         </is>

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -589,7 +589,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>毎日の終わりにWBSの現況・ペンディングの優先順位・当方の作業だけで進められるもの・翌日の作業順位を1枚にしたものです。基準日 令和8年10月19日。内部保管。</t>
+          <t>毎日の終わりにWBSの現況・ペンディングの優先順位・当方の作業だけで進められるもの・翌日の作業順位を1枚にしたものです。基準日 令和8年10月20日。内部保管。</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -776,7 +776,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）ごとの進捗率と、前に報告した時点からの動きです。基準日 令和8年10月19日。</t>
+          <t>仕様書４（1）〜（12）ごとの進捗率と、前に報告した時点からの動きです。基準日 令和8年10月20日。</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>注1）進捗の記録の基準日は 令和8年10月19日 です。本表の基準日（令和8年10月19日）と違うときは、進捗の更新がまだ行われていません。
+          <t>注1）進捗の記録の基準日は 令和8年10月20日 です。本表の基準日（令和8年10月20日）と違うときは、進捗の更新がまだ行われていません。
 注2）進捗率を更新したら、更新前の値を記録へ移します。移さないと、過去の時点を記す資料（月次の報告・議事録）の数値が書き換わります。</t>
         </is>
       </c>
@@ -1240,20 +1240,38 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2e2a16e</t>
+          <t>7b14b4b</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>受託者案による確定のご了承（令和8年10月19日）を台帳・工程・WBSへ反映</t>
+          <t>原典による条例の根拠条文・関係法令・第9期計画の確認（data_jobun.py）</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
       <c r="E23" s="6" t="inlineStr"/>
       <c r="F23" s="6" t="inlineStr"/>
     </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="14" t="inlineStr">
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>9ef4079</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>外部接続の実測と記録の是正（CLAUDE.md §4・§5）</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
@@ -1261,12 +1279,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1278,7 +1296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1302,7 +1320,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>完了していない確認事項と資料提供依頼を、影響度の点の高い順に並べたものです。点の付け方は03シートに全て書いています。基準日 令和8年10月19日。</t>
+          <t>完了していない確認事項と資料提供依頼を、影響度の点の高い順に並べたものです。点の付け方は03シートに全て書いています。基準日 令和8年10月20日。</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1433,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2　資料提供依頼（資料の提供を求めるもの）　16件</t>
+          <t>2　資料提供依頼（資料の提供を求めるもの）　17件</t>
         </is>
       </c>
     </row>
@@ -2073,26 +2091,26 @@
         <v>15</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+          <t>第9期（令和6〜8年度）の保険料率を定める介護保険条例</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>会議資料・委員会資料の記述の正確性</t>
+          <t>所得段階と乗率の確定、保険料の算定</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>随時</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
@@ -2102,12 +2120,12 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>E</t>
         </is>
       </c>
     </row>
@@ -2116,46 +2134,89 @@
         <v>16</v>
       </c>
       <c r="B26" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>会議資料・委員会資料の記述の正確性</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>随時</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B27" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>世帯構成の現状</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>総務省・3町</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>公表後</t>
         </is>
       </c>
-      <c r="G26" s="18" t="inlineStr">
+      <c r="G27" s="18" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="14" t="inlineStr">
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>注）03シートの確認事項が「決定」を求めるものであるのに対し、本表は「資料の提供」を求めるものです。資料が届かない場合の扱いは04シートの区分で示しています。</t>
         </is>
@@ -2165,9 +2226,9 @@
   <mergeCells count="6">
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A28:I28"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A9:I9"/>
-    <mergeCell ref="A27:I27"/>
     <mergeCell ref="A4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2200,7 +2261,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02シートの点は次の規則だけで付けています。規則を変えれば02シートの並びも変わります。基準日 令和8年10月19日。</t>
+          <t>02シートの点は次の規則だけで付けています。規則を変えれば02シートの並びも変わります。基準日 令和8年10月20日。</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2857,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>決定・資料の受領を待たずに当方の作業だけで進められるものです。基準日 令和8年10月19日。</t>
+          <t>決定・資料の受領を待たずに当方の作業だけで進められるものです。基準日 令和8年10月20日。</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2974,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>翌日（令和8年10月20日）の作業順位</t>
+          <t>翌日（令和8年10月21日）の作業順位</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3564,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>確認事項1件／資料提供依頼16件</t>
+          <t>確認事項1件／資料提供依頼17件</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -3678,7 +3739,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>記録 令和8年10月19日／本表 令和8年10月19日</t>
+          <t>記録 令和8年10月20日／本表 令和8年10月20日</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -755,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>7b14b4b</t>
+          <t>86520e6</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>原典による条例の根拠条文・関係法令・第9期計画の確認（data_jobun.py）</t>
+          <t>例規集により条例を確認し確認事項No.95を解決</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
@@ -1258,20 +1258,38 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>9ef4079</t>
+          <t>7b14b4b</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>外部接続の実測と記録の是正（CLAUDE.md §4・§5）</t>
+          <t>原典による条例の根拠条文・関係法令・第9期計画の確認（data_jobun.py）</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
       <c r="E24" s="6" t="inlineStr"/>
       <c r="F24" s="6" t="inlineStr"/>
     </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>9ef4079</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>外部接続の実測と記録の是正（CLAUDE.md §4・§5）</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
@@ -1283,8 +1301,8 @@
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -755,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>86520e6</t>
+          <t>b6c37e1</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>例規集により条例を確認し確認事項No.95を解決</t>
+          <t>北海道の第10期計画の骨子（案）と道作成指針（案）を確認</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>7b14b4b</t>
+          <t>86520e6</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>原典による条例の根拠条文・関係法令・第9期計画の確認（data_jobun.py）</t>
+          <t>例規集により条例を確認し確認事項No.95を解決</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
@@ -1276,20 +1276,38 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>9ef4079</t>
+          <t>7b14b4b</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>外部接続の実測と記録の是正（CLAUDE.md §4・§5）</t>
+          <t>原典による条例の根拠条文・関係法令・第9期計画の確認（data_jobun.py）</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr"/>
       <c r="E25" s="6" t="inlineStr"/>
       <c r="F25" s="6" t="inlineStr"/>
     </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="14" t="inlineStr">
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>9ef4079</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>外部接続の実測と記録の是正（CLAUDE.md §4・§5）</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr"/>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
@@ -1300,8 +1318,8 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -589,7 +589,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>毎日の終わりにWBSの現況・ペンディングの優先順位・当方の作業だけで進められるもの・翌日の作業順位を1枚にしたものです。基準日 令和8年10月20日。内部保管。</t>
+          <t>毎日の終わりにWBSの現況・ペンディングの優先順位・当方の作業だけで進められるもの・翌日の作業順位を1枚にしたものです。基準日 令和8年10月21日。内部保管。</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -776,7 +776,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）ごとの進捗率と、前に報告した時点からの動きです。基準日 令和8年10月20日。</t>
+          <t>仕様書４（1）〜（12）ごとの進捗率と、前に報告した時点からの動きです。基準日 令和8年10月21日。</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>注1）進捗の記録の基準日は 令和8年10月20日 です。本表の基準日（令和8年10月20日）と違うときは、進捗の更新がまだ行われていません。
+          <t>注1）進捗の記録の基準日は 令和8年10月21日 です。本表の基準日（令和8年10月21日）と違うときは、進捗の更新がまだ行われていません。
 注2）進捗率を更新したら、更新前の値を記録へ移します。移さないと、過去の時点を記す資料（月次の報告・議事録）の数値が書き換わります。</t>
         </is>
       </c>
@@ -1218,107 +1218,27 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="4" t="inlineStr"/>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>コミット</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr"/>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>b6c37e1</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>北海道の第10期計画の骨子（案）と道作成指針（案）を確認</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr"/>
-      <c r="E23" s="6" t="inlineStr"/>
-      <c r="F23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>86520e6</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>例規集により条例を確認し確認事項No.95を解決</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr"/>
-      <c r="E24" s="6" t="inlineStr"/>
-      <c r="F24" s="6" t="inlineStr"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>7b14b4b</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>原典による条例の根拠条文・関係法令・第9期計画の確認（data_jobun.py）</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>9ef4079</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>外部接続の実測と記録の是正（CLAUDE.md §4・§5）</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="14" t="inlineStr">
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>基準日のコミットはありません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>注）進捗の理由は、この記録をもとに書きます。何をしたかではなくそれにより何が確定したかを書きます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A22:F22"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A21:F21"/>
   </mergeCells>
@@ -1332,7 +1252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1356,7 +1276,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>完了していない確認事項と資料提供依頼を、影響度の点の高い順に並べたものです。点の付け方は03シートに全て書いています。基準日 令和8年10月20日。</t>
+          <t>完了していない確認事項と資料提供依頼を、影響度の点の高い順に並べたものです。点の付け方は03シートに全て書いています。基準日 令和8年10月21日。</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1389,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>2　資料提供依頼（資料の提供を求めるもの）　17件</t>
+          <t>2　資料提供依頼（資料の提供を求めるもの）　18件</t>
         </is>
       </c>
     </row>
@@ -1998,26 +1918,26 @@
         <v>12</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
+          <t>見える化システムの事業所分析機能の出力</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>第10期の段階設計と保険料算定</t>
+          <t>事業所の定員と稼働の実績、供給の制約（人材）、施設・居住系の実績の減少の読み方</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>告示後</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
@@ -2032,7 +1952,7 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2041,41 +1961,41 @@
         <v>13</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>小学校区と日常生活圏域の対応関係</t>
+          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>圏域別の分析、圏域設定の見直し</t>
+          <t>第10期の段階設計と保険料算定</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>美瑛町・3町</t>
+          <t>国の情報</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G23" s="15" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>告示後</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
     </row>
@@ -2084,21 +2004,21 @@
         <v>14</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>評価の枠組みの整理</t>
+          <t>圏域別の分析、圏域設定の見直し</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>美瑛町・3町</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -2118,7 +2038,7 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>I</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2047,16 @@
         <v>15</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第9期（令和6〜8年度）の保険料率を定める介護保険条例</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>所得段階と乗率の確定、保険料の算定</t>
+          <t>評価の枠組みの整理</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -2146,7 +2066,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
@@ -2156,12 +2076,12 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
     </row>
@@ -2170,26 +2090,26 @@
         <v>16</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+          <t>第9期（令和6〜8年度）の保険料率を定める介護保険条例</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>会議資料・委員会資料の記述の正確性</t>
+          <t>所得段階と乗率の確定、保険料の算定</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>随時</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G26" s="15" t="inlineStr">
@@ -2199,12 +2119,12 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>E</t>
         </is>
       </c>
     </row>
@@ -2213,46 +2133,89 @@
         <v>17</v>
       </c>
       <c r="B27" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>会議資料・委員会資料の記述の正確性</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>随時</t>
+        </is>
+      </c>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B28" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>世帯構成の現状</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>総務省・3町</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>公表後</t>
         </is>
       </c>
-      <c r="G27" s="18" t="inlineStr">
+      <c r="G28" s="18" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="14" t="inlineStr">
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>注）03シートの確認事項が「決定」を求めるものであるのに対し、本表は「資料の提供」を求めるものです。資料が届かない場合の扱いは04シートの区分で示しています。</t>
         </is>
@@ -2260,9 +2223,9 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A29:I29"/>
     <mergeCell ref="A7:I7"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A28:I28"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A9:I9"/>
     <mergeCell ref="A4:I4"/>
@@ -2297,7 +2260,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02シートの点は次の規則だけで付けています。規則を変えれば02シートの並びも変わります。基準日 令和8年10月20日。</t>
+          <t>02シートの点は次の規則だけで付けています。規則を変えれば02シートの並びも変わります。基準日 令和8年10月21日。</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2856,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>決定・資料の受領を待たずに当方の作業だけで進められるものです。基準日 令和8年10月20日。</t>
+          <t>決定・資料の受領を待たずに当方の作業だけで進められるものです。基準日 令和8年10月21日。</t>
         </is>
       </c>
     </row>
@@ -3010,7 +2973,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>翌日（令和8年10月21日）の作業順位</t>
+          <t>翌日（令和8年10月22日）の作業順位</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3563,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>確認事項1件／資料提供依頼17件</t>
+          <t>確認事項1件／資料提供依頼18件</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -3775,7 +3738,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>記録 令和8年10月20日／本表 令和8年10月20日</t>
+          <t>記録 令和8年10月21日／本表 令和8年10月21日</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -589,7 +589,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>毎日の終わりにWBSの現況・ペンディングの優先順位・当方の作業だけで進められるもの・翌日の作業順位を1枚にしたものです。基準日 令和8年10月21日。内部保管。</t>
+          <t>毎日の終わりにWBSの現況・ペンディングの優先順位・当方の作業だけで進められるもの・翌日の作業順位を1枚にしたものです。基準日 令和8年10月23日。内部保管。</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）ごとの進捗率と、前に報告した時点からの動きです。基準日 令和8年10月21日。</t>
+          <t>仕様書４（1）〜（12）ごとの進捗率と、前に報告した時点からの動きです。基準日 令和8年10月23日。</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>注1）進捗の記録の基準日は 令和8年10月21日 です。本表の基準日（令和8年10月21日）と違うときは、進捗の更新がまだ行われていません。
+          <t>注1）進捗の記録の基準日は 令和8年10月23日 です。本表の基準日（令和8年10月23日）と違うときは、進捗の更新がまだ行われていません。
 注2）進捗率を更新したら、更新前の値を記録へ移します。移さないと、過去の時点を記す資料（月次の報告・議事録）の数値が書き換わります。</t>
         </is>
       </c>
@@ -1252,7 +1252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1276,7 +1276,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>完了していない確認事項と資料提供依頼を、影響度の点の高い順に並べたものです。点の付け方は03シートに全て書いています。基準日 令和8年10月21日。</t>
+          <t>完了していない確認事項と資料提供依頼を、影響度の点の高い順に並べたものです。点の付け方は03シートに全て書いています。基準日 令和8年10月23日。</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　確認事項（決定を求めるもの）　1件</t>
+          <t>1　確認事項（決定を求めるもの）　3件</t>
         </is>
       </c>
     </row>
@@ -1376,8 +1376,92 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>191</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの令和8年度の実績見込みに用いる月の起点と終期</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量の算定
+計画素案 第6章第2節</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>当方の算定は令和7年度（12か月）を基準年度としており令和8年度を数量の基準に用いないため、見込量及び保険料に影響はない。令和8年度の月数についての記述は、ご提供いただいた月報による4か月のまま置き、システムの計算値とは起点が異なる旨を注記する</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>192</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムに入力する地域支援事業費の額の作り方</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量の算定
+計画素案 第6章第3節2・第6章第6節</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>止めている成果物 計画素案（+1）</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費は令和6年度決算の水準を据え置いて算定し、額が決算によるものであること及び国の様式がいう対象経費支出予定額とは範囲が異なる旨を計画素案 第6章第3節2に注記する</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>注1）点が9以上を至急、6以上8以下を優先、5以下を通常とみます（03シート）。
 注2）「決着しない場合の当方の扱い」が空のものは、決まらないと当方の作業が止まります。 先に扱いを決めます。
@@ -1385,205 +1469,119 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2　資料提供依頼（資料の提供を求めるもの）　18件</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10"/>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2　資料提供依頼（資料の提供を求めるもの）　23件</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>確定する主張</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>入手先</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>希望時期</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>優先</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>領域</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>第9期の評価の完成</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>最高</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>一部受領</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>F</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
+          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
+          <t>第9期の評価の完成</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="G13" s="16" t="inlineStr">
+        <is>
+          <t>最高</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>一部受領</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
+          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1593,7 +1591,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
@@ -1603,40 +1601,40 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>代替により解消</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
+          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G15" s="17" t="inlineStr">
@@ -1646,40 +1644,40 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>事業所・施設の定員と稼働の実績</t>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>稼働率の低下の有無、定員減少の経緯</t>
+          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
@@ -1689,35 +1687,35 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>代替により解消</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>未利用認定者の内訳とケアプランのサービス構成</t>
+          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
+          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1732,35 +1730,35 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
+          <t>事業所・施設の定員と稼働の実績</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>第9期の剰余額（現在は概算）</t>
+          <t>稼働率の低下の有無、定員減少の経緯</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -1780,30 +1778,30 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
+          <t>未利用認定者の内訳とケアプランのサービス構成</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>給付費の地域内還流の議論</t>
+          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -1823,30 +1821,30 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
+          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
+          <t>第9期の剰余額（現在は概算）</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -1866,30 +1864,30 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>H</t>
         </is>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
+          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>サービス種別ごとの見込量の様式</t>
+          <t>給付費の地域内還流の議論</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -1904,40 +1902,40 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの事業所分析機能の出力</t>
+          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>事業所の定員と稼働の実績、供給の制約（人材）、施設・居住系の実績の減少の読み方</t>
+          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G22" s="17" t="inlineStr">
@@ -1947,40 +1945,40 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
+          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>第10期の段階設計と保険料算定</t>
+          <t>サービス種別ごとの見込量の様式</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>告示後</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G23" s="17" t="inlineStr">
@@ -1990,73 +1988,73 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>小学校区と日常生活圏域の対応関係</t>
+          <t>見える化システムの事業所分析機能の出力</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>圏域別の分析、圏域設定の見直し</t>
+          <t>事業所の定員と稼働の実績、供給の制約（人材）、施設・居住系の実績の減少の読み方</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>美瑛町・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G24" s="15" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>見える化システムの地方公共団体向け利用マニュアル</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>評価の枠組みの整理</t>
+          <t>将来推計の入力値、施設・居住系の画面から先へ進めない件</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
@@ -2066,55 +2064,55 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G25" s="15" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第9期（令和6〜8年度）の保険料率を定める介護保険条例</t>
+          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>所得段階と乗率の確定、保険料の算定</t>
+          <t>第10期の段階設計と保険料算定</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>国の情報</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
-        </is>
-      </c>
-      <c r="G26" s="15" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>告示後</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
@@ -2124,35 +2122,35 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+          <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>会議資料・委員会資料の記述の正確性</t>
+          <t>圏域別の分析、圏域設定の見直し</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>美瑛町・3町</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>随時</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
@@ -2162,60 +2160,361 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>第9期の自己評価と北海道への報告の実績</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>評価の枠組みの整理</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>第9期（令和6〜8年度）の保険料率を定める介護保険条例</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>所得段階と乗率の確定、保険料の算定</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B30" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの第10期新機能の出力</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>類似保険者との比較分析、区域外の事業所の利用、日常生活圏域の設定、伸びの選択</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの地域分析・検討シート（比較地域を設定したもの）</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>類似保険者との比較分析、地域分析・検討シートの記載</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>要介護認定適正化事業の業務分析データ</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>第7期給付適正化計画の主要3事業の基準値、調整交付金の一定の取組による減額の判定</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>R8.12</t>
+        </is>
+      </c>
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>会議資料・委員会資料の記述の正確性</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>受託者</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>随時</t>
+        </is>
+      </c>
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムのB7・B8（要介護者の状況）の出力</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>計画素案 第2章第1節3（認知症高齢者の状況）</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G34" s="18" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B35" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>世帯構成の現状</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>総務省・3町</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>公表後</t>
         </is>
       </c>
-      <c r="G28" s="18" t="inlineStr">
+      <c r="G35" s="18" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="14" t="inlineStr">
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>注）03シートの確認事項が「決定」を求めるものであるのに対し、本表は「資料の提供」を求めるものです。資料が届かない場合の扱いは04シートの区分で示しています。</t>
         </is>
@@ -2223,9 +2522,9 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A7:I7"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A36:I36"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A9:I9"/>
     <mergeCell ref="A4:I4"/>
@@ -2260,7 +2559,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02シートの点は次の規則だけで付けています。規則を変えれば02シートの並びも変わります。基準日 令和8年10月21日。</t>
+          <t>02シートの点は次の規則だけで付けています。規則を変えれば02シートの並びも変わります。基準日 令和8年10月23日。</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2728,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>1件</t>
+          <t>3件</t>
         </is>
       </c>
     </row>
@@ -2677,7 +2976,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>1件</t>
+          <t>3件</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -2836,7 +3135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2856,7 +3155,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>決定・資料の受領を待たずに当方の作業だけで進められるものです。基準日 令和8年10月21日。</t>
+          <t>決定・資料の受領を待たずに当方の作業だけで進められるものです。基準日 令和8年10月23日。</t>
         </is>
       </c>
     </row>
@@ -2864,7 +3163,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　当方の作業だけで進められるもの　1件</t>
+          <t>1　当方の作業だけで進められるもの　3件</t>
         </is>
       </c>
     </row>
@@ -2916,8 +3215,58 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="76" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>既定値で進める</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの令和8年度の実績見込みに用いる月の起点と終期</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>当方の算定は令和7年度（12か月）を基準年度としており令和8年度を数量の基準に用いないため、見込量及び保険料に影響はない。令和8年度の月数についての記述は、ご提供いただいた月報による4か月のまま置き、システムの計算値とは起点が異なる旨を注記する</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.191（点1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>既定値で進める</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムに入力する地域支援事業費の額の作り方</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費は令和6年度決算の水準を据え置いて算定し、額が決算によるものであること及び国の様式がいう対象経費支出予定額とは範囲が異なる旨を計画素案 第6章第3節2に注記する</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>確認事項No.192（点1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="76" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>注1）「据え置き（区分A）」は、資料の受領を待たずに当方の側で確定できるものです。
 注2）「既定値で進める」は、決着しない場合の扱いを置けているため決定を待たずに作業を進められるものです。決定を受けた時点で見直します。
@@ -2926,16 +3275,16 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="10"/>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>2　先に扱いを決めるもの（既定値を置けていない）　0件</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="21" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>ありません。未決の確認事項の全件に扱いを置けています。</t>
         </is>
@@ -2944,10 +3293,10 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A7:E7"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2960,7 +3309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2973,7 +3322,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>翌日（令和8年10月22日）の作業順位</t>
+          <t>翌日（令和8年10月24日）の作業順位</t>
         </is>
       </c>
     </row>
@@ -3041,24 +3390,24 @@
       <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>催促・照会</t>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>進める</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算（発注者）</t>
+          <t>見える化システムの令和8年度の実績見込みに用いる月の起点と終期</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>優先度最高・希望時期R8.8。第9期の評価の完成</t>
+          <t>当方の算定は令和7年度（12か月）を基準年度としており令和8年度を数量の基準に用いないため、見込量及び保険料に影響はない。令和8年度の月数についての記述は、ご提供いただいた月報による4か月のまま置き、システムの計算値とは起点が異なる旨を注記する</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13</t>
+          <t>確認事項No.191（点1）</t>
         </is>
       </c>
     </row>
@@ -3066,24 +3415,24 @@
       <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>催促・照会</t>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>進める</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（発注者）</t>
+          <t>見える化システムに入力する地域支援事業費の額の作り方</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>優先度高・希望時期R8.8。4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
+          <t>地域支援事業費は令和6年度決算の水準を据え置いて算定し、額が決算によるものであること及び国の様式がいう対象経費支出予定額とは範囲が異なる旨を計画素案 第6章第3節2に注記する</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.14</t>
+          <t>確認事項No.192（点1）</t>
         </is>
       </c>
     </row>
@@ -3098,17 +3447,17 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）（3町）</t>
+          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算（発注者）</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>優先度高・希望時期R8.9。東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
+          <t>優先度最高・希望時期R8.8。第9期の評価の完成</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.3</t>
+          <t>資料提供依頼No.13</t>
         </is>
       </c>
     </row>
@@ -3123,17 +3472,17 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）（発注者）</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（発注者）</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>優先度高・希望時期R8.9。交付金評価の解釈、W144の要因、評価対象期間</t>
+          <t>優先度高・希望時期R8.8。4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.5</t>
+          <t>資料提供依頼No.14</t>
         </is>
       </c>
     </row>
@@ -3148,22 +3497,72 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）（3町）</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>優先度高・希望時期R8.9。東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>資料提供依頼No.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>催促・照会</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）（発注者）</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>優先度高・希望時期R8.9。交付金評価の解釈、W144の要因、評価対象期間</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>資料提供依頼No.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>催促・照会</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
           <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）（発注者・国保連）</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>優先度高・希望時期R8.10。給付水準の要因（区域外利用との関係は無相関と判明）</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>資料提供依頼No.6</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="76" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
+    <row r="13" ht="76" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>注1）「進める」は決定を待たずに着手できるもの、「催促・照会」は相手のある作業です。相手のある作業は午前のうちに出します（返事に日数がかかるため）。
 注2）04シートの作業継続可能なものは上位8件まで、催促・照会は優先以上の上位5件までを掲げています。残りは02・04シートを見ます。
@@ -3172,294 +3571,294 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14"/>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>2　国の公布を待つもの　13件</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="22" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="22" t="inlineStr">
         <is>
           <t>令和8年10月19日のご了承により受託者案で確定しましたが、保険料に関わる国の政令・省令・告示の公布後に再算定するものです。催促できないため翌日の作業には挙げていません。公布を確かめた時点で算定をやり直します。</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="4" t="inlineStr"/>
-      <c r="B15" s="4" t="inlineStr">
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="4" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>確認事項</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>何を待つか</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>特定地域の基準（厚生労働省令）及び対象地域の指定</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr"/>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B17" s="5" t="n">
-        <v>33</v>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>第10期の政令改正の内容（所得段階）</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>第10期の所得段階・乗率・第1号被保険者負担割合（政令）</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提（受託者案）</t>
+          <t>特定地域の指定に係る意向表明の手続</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提（報酬改定率・負担割合・基金の取崩し）</t>
+          <t>特定地域の基準（厚生労働省令）及び対象地域の指定</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+          <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等改正法の政令・省令及び介護報酬改定</t>
+          <t>第10期の所得段階・乗率・第1号被保険者負担割合（政令）</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>104</v>
+        <v>60</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
+          <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>令和8年度介護報酬改定の単価への反映</t>
+          <t>保険料算定の前提（報酬改定率・負担割合・基金の取崩し）</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>令和9年度介護報酬改定の改定率（告示）</t>
+          <t>社会福祉法等改正法の政令・省令及び介護報酬改定</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月新設の3区分（省令・告示）</t>
+          <t>令和8年度介護報酬改定の単価への反映</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
+          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の年度（報酬改定の告示）</t>
+          <t>令和9年度介護報酬改定の改定率（告示）</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>176</v>
+        <v>115</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>介護サービス事業者経営情報データベースの公表結果の活用の範囲</t>
+          <t>令和9年4月に新設される区分を見込量に立てるか</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>介護サービス事業者経営情報データベースの分析結果の公表</t>
+          <t>令和9年4月新設の3区分（省令・告示）</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>夜間対応型訪問介護の定期巡回・随時対応型への移行の扱い</t>
+          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>夜間対応型訪問介護の移行に係る省令等</t>
+          <t>1人1月あたり給付費の年度（報酬改定の告示）</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>小規模市町村地域支援連携協働体制整備事業の対象となるかどうか</t>
+          <t>介護サービス事業者経営情報データベースの公表結果の活用の範囲</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>小規模市町村の基準（厚生労働省令）</t>
+          <t>介護サービス事業者経営情報データベースの分析結果の公表</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費の政令で定める額</t>
+          <t>夜間対応型訪問介護の定期巡回・随時対応型への移行の扱い</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費の政令で定める額</t>
+          <t>夜間対応型訪問介護の移行に係る省令等</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>185</v>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>小規模市町村地域支援連携協働体制整備事業の対象となるかどうか</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>小規模市町村の基準（厚生労働省令）</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>188</v>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費の政令で定める額</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費の政令で定める額</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B30" s="5" t="n">
         <v>189</v>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>医療法等の一部を改正する法律による介護保険法の改正の施行の状況</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>医療法等改正法による改正の施行の日（政令）</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr"/>
+      <c r="E30" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A15:E15"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A13:E13"/>
-    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3533,12 +3932,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>No.1〜No.190 を数える</t>
+          <t>No.1〜No.192 を数える</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>190件／欠番 なし／重複 なし</t>
+          <t>192件／欠番 なし／重複 なし</t>
         </is>
       </c>
       <c r="E5" s="24" t="inlineStr">
@@ -3563,7 +3962,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>確認事項1件／資料提供依頼18件</t>
+          <t>確認事項3件／資料提供依頼23件</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -3588,7 +3987,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>1件／合わない なし</t>
+          <t>3件／合わない なし</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
@@ -3738,7 +4137,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>記録 令和8年10月21日／本表 令和8年10月21日</t>
+          <t>記録 令和8年10月23日／本表 令和8年10月23日</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
@@ -3788,7 +4187,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>6件（進める1・催促5）</t>
+          <t>8件（進める3・催促5）</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -3813,7 +4212,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>1件（区分A 0・既定値 1）／据え置きの区分A 0件・既定値があり未処理 1件</t>
+          <t>3件（区分A 0・既定値 3）／据え置きの区分A 0件・既定値があり未処理 3件</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">

--- a/output/第10期計画_日次の状況と翌日の作業順位.xlsx
+++ b/output/第10期計画_日次の状況と翌日の作業順位.xlsx
@@ -589,7 +589,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>毎日の終わりにWBSの現況・ペンディングの優先順位・当方の作業だけで進められるもの・翌日の作業順位を1枚にしたものです。基準日 令和8年10月23日。内部保管。</t>
+          <t>毎日の終わりにWBSの現況・ペンディングの優先順位・当方の作業だけで進められるもの・翌日の作業順位を1枚にしたものです。基準日 令和8年10月24日。内部保管。</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>仕様書４（1）〜（12）ごとの進捗率と、前に報告した時点からの動きです。基準日 令和8年10月23日。</t>
+          <t>仕様書４（1）〜（12）ごとの進捗率と、前に報告した時点からの動きです。基準日 令和8年10月24日。</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>注1）進捗の記録の基準日は 令和8年10月23日 です。本表の基準日（令和8年10月23日）と違うときは、進捗の更新がまだ行われていません。
+          <t>注1）進捗の記録の基準日は 令和8年10月24日 です。本表の基準日（令和8年10月24日）と違うときは、進捗の更新がまだ行われていません。
 注2）進捗率を更新したら、更新前の値を記録へ移します。移さないと、過去の時点を記す資料（月次の報告・議事録）の数値が書き換わります。</t>
         </is>
       </c>
@@ -1252,7 +1252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1276,7 +1276,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>完了していない確認事項と資料提供依頼を、影響度の点の高い順に並べたものです。点の付け方は03シートに全て書いています。基準日 令和8年10月23日。</t>
+          <t>完了していない確認事項と資料提供依頼を、影響度の点の高い順に並べたものです。点の付け方は03シートに全て書いています。基準日 令和8年10月24日。</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　確認事項（決定を求めるもの）　3件</t>
+          <t>1　確認事項（決定を求めるもの）　2件</t>
         </is>
       </c>
     </row>
@@ -1381,17 +1381,17 @@
         <v>2</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの令和8年度の実績見込みに用いる月の起点と終期</t>
+          <t>都道府県へ推計データを提出する際に入力する「改正介護保険法を踏まえた第10期計画の策定における取組」の回答</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定
-計画素案 第6章第2節</t>
+          <t>計画素案 第6章第1節・第6章第3節2・第6章第4節1・第6章第5節
+見える化システムへの入力</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="G7" s="15" t="n">
@@ -1414,54 +1414,12 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>当方の算定は令和7年度（12か月）を基準年度としており令和8年度を数量の基準に用いないため、見込量及び保険料に影響はない。令和8年度の月数についての記述は、ご提供いただいた月報による4か月のまま置き、システムの計算値とは起点が異なる旨を注記する</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>192</v>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>見える化システムに入力する地域支援事業費の額の作り方</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>サービス見込量の算定
-計画素案 第6章第3節2・第6章第6節</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>R8.11</t>
-        </is>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>止めている成果物 計画素案（+1）</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>地域支援事業費は令和6年度決算の水準を据え置いて算定し、額が決算によるものであること及び国の様式がいう対象経費支出予定額とは範囲が異なる旨を計画素案 第6章第3節2に注記する</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="56" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+          <t>（1）ア・イは計画本文に掲げている令和17年度及び令和22年度により「2040年度」及び「その他の年度」を選び、ウは計画素案に現に記述のある事項（施設・事業所の開設廃止等による影響、有料老人ホーム及び登録住宅の入居定員総数や入居者の状況、介護予防・日常生活圏域ニーズ調査や在宅介護実態調査等を通じて把握した状況）を選ぶ案を示す。（2）及び（3）は実施の状況を当方が確かめられないため案を示すにとどめ、入力そのものは発注者が行う</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>注1）点が9以上を至急、6以上8以下を優先、5以下を通常とみます（03シート）。
 注2）「決着しない場合の当方の扱い」が空のものは、決まらないと当方の作業が止まります。 先に扱いを決めます。
@@ -1469,76 +1427,119 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>2　資料提供依頼（資料の提供を求めるもの）　23件</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="9"/>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2　資料提供依頼（資料の提供を求めるもの）　22件</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>順</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>資料</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>確定する主張</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>入手先</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>希望時期</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>優先</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>状態</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>領域</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>第9期の評価の完成</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>最高</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>一部受領</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>第9期の評価の完成</t>
+          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -1551,47 +1552,47 @@
           <t>R8.8</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>最高</t>
+      <c r="G13" s="17" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>一部受領</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分</t>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
+          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G14" s="17" t="inlineStr">
@@ -1601,35 +1602,35 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
+          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1644,40 +1645,40 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>代替により解消</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
+          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>交付金評価の解釈、W144の要因、評価対象期間</t>
+          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G16" s="17" t="inlineStr">
@@ -1687,35 +1688,35 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>代替により解消</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）</t>
+          <t>事業所・施設の定員と稼働の実績</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>給付水準の要因（区域外利用との関係は無相関と判明）</t>
+          <t>稼働率の低下の有無、定員減少の経緯</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1730,35 +1731,35 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>事業所・施設の定員と稼働の実績</t>
+          <t>未利用認定者の内訳とケアプランのサービス構成</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>稼働率の低下の有無、定員減少の経緯</t>
+          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -1778,25 +1779,25 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>未利用認定者の内訳とケアプランのサービス構成</t>
+          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>利用率低下の要因、訪問と通所の代替関係、要介護5の受給率低下の要因</t>
+          <t>第9期の剰余額（現在は概算）</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1821,30 +1822,30 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>H</t>
         </is>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>決算書及び介護給付費準備基金の積立・取崩実績</t>
+          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>第9期の剰余額（現在は概算）</t>
+          <t>給付費の地域内還流の議論</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -1864,25 +1865,25 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
+          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>給付費の地域内還流の議論</t>
+          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1907,30 +1908,30 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>指定事業所台帳（区域外事業所の所在地、区域内の地域密着型事業所）</t>
+          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>区域外利用の内訳、認知症対応型共同生活介護の区域内定員、居所変更実態調査の定員ベースの把握率</t>
+          <t>サービス種別ごとの見込量の様式</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -1945,30 +1946,30 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>居住系・施設サービスの種別別受給者数と総合事業の実績</t>
+          <t>第10期必要入所（利用）定員、入居定員総数調査票</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>サービス種別ごとの見込量の様式</t>
+          <t>計画素案 第6章第4節4（必要利用定員総数）、日常生活圏域ごとの必要利用定員総数の様式</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1978,7 +1979,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G23" s="17" t="inlineStr">
@@ -1988,40 +1989,40 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの事業所分析機能の出力</t>
+          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>事業所の定員と稼働の実績、供給の制約（人材）、施設・居住系の実績の減少の読み方</t>
+          <t>第10期の段階設計と保険料算定</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>国の情報</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>告示後</t>
         </is>
       </c>
       <c r="G24" s="17" t="inlineStr">
@@ -2036,121 +2037,121 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>H</t>
         </is>
       </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの地方公共団体向け利用マニュアル</t>
+          <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>将来推計の入力値、施設・居住系の画面から先へ進めない件</t>
+          <t>圏域別の分析、圏域設定の見直し</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>美瑛町・3町</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階・乗率・負担割合）</t>
+          <t>第9期の自己評価と北海道への報告の実績</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>第10期の段階設計と保険料算定</t>
+          <t>評価の枠組みの整理</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>告示後</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>高</t>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>小学校区と日常生活圏域の対応関係</t>
+          <t>第9期（令和6〜8年度）の保険料率を定める介護保険条例</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>圏域別の分析、圏域設定の見直し</t>
+          <t>所得段階と乗率の確定、保険料の算定</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>美瑛町・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
@@ -2160,30 +2161,30 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>E</t>
         </is>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績</t>
+          <t>見える化システムの第10期新機能の出力</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>評価の枠組みの整理</t>
+          <t>類似保険者との比較分析、区域外の事業所の利用、日常生活圏域の設定、伸びの選択</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -2193,7 +2194,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="G28" s="15" t="inlineStr">
@@ -2203,30 +2204,30 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A</t>
         </is>
       </c>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第9期（令和6〜8年度）の保険料率を定める介護保険条例</t>
+          <t>見える化システムの地域分析・検討シート（比較地域を設定したもの）</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>所得段階と乗率の確定、保険料の算定</t>
+          <t>類似保険者との比較分析、地域分析・検討シートの記載</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -2251,25 +2252,25 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの第10期新機能の出力</t>
+          <t>要介護認定適正化事業の業務分析データ</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較分析、区域外の事業所の利用、日常生活圏域の設定、伸びの選択</t>
+          <t>第7期給付適正化計画の主要3事業の基準値、調整交付金の一定の取組による減額の判定</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -2279,7 +2280,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="G30" s="15" t="inlineStr">
@@ -2294,35 +2295,35 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの地域分析・検討シート（比較地域を設定したもの）</t>
+          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>類似保険者との比較分析、地域分析・検討シートの記載</t>
+          <t>会議資料・委員会資料の記述の正確性</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>随時</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
@@ -2332,30 +2333,30 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>要介護認定適正化事業の業務分析データ</t>
+          <t>見える化システムのB7・B8（要介護者の状況）の出力</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>第7期給付適正化計画の主要3事業の基準値、調整交付金の一定の取組による減額の判定</t>
+          <t>計画素案 第2章第1節3（認知症高齢者の状況）</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -2365,12 +2366,12 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>R8.12</t>
-        </is>
-      </c>
-      <c r="G32" s="15" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="G32" s="18" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -2386,135 +2387,49 @@
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>（受託者の作業）会議資料・委員会資料の作成時の留保の照合</t>
+          <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>会議資料・委員会資料の記述の正確性</t>
+          <t>世帯構成の現状</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>総務省・3町</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>随時</t>
-        </is>
-      </c>
-      <c r="G33" s="15" t="inlineStr">
-        <is>
-          <t>中</t>
+          <t>公表後</t>
+        </is>
+      </c>
+      <c r="G33" s="18" t="inlineStr">
+        <is>
+          <t>低</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>―</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="40" customHeight="1">
-      <c r="A34" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B34" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>見える化システムのB7・B8（要介護者の状況）の出力</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>計画素案 第2章第1節3（認知症高齢者の状況）</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>R8.11</t>
-        </is>
-      </c>
-      <c r="G34" s="18" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="40" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B35" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>世帯構成の現状</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>総務省・3町</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>公表後</t>
-        </is>
-      </c>
-      <c r="G35" s="18" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="14" t="inlineStr">
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>注）03シートの確認事項が「決定」を求めるものであるのに対し、本表は「資料の提供」を求めるものです。資料が届かない場合の扱いは04シートの区分で示しています。</t>
         </is>
@@ -2523,10 +2438,10 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A11:I11"/>
-    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A10:I10"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="A34:I34"/>
     <mergeCell ref="A4:I4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2559,7 +2474,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02シートの点は次の規則だけで付けています。規則を変えれば02シートの並びも変わります。基準日 令和8年10月23日。</t>
+          <t>02シートの点は次の規則だけで付けています。規則を変えれば02シートの並びも変わります。基準日 令和8年10月24日。</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2643,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>3件</t>
+          <t>2件</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2891,7 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>3件</t>
+          <t>2件</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -3135,7 +3050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3155,7 +3070,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>決定・資料の受領を待たずに当方の作業だけで進められるものです。基準日 令和8年10月23日。</t>
+          <t>決定・資料の受領を待たずに当方の作業だけで進められるものです。基準日 令和8年10月24日。</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3078,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1　当方の作業だけで進められるもの　3件</t>
+          <t>1　当方の作業だけで進められるもの　2件</t>
         </is>
       </c>
     </row>
@@ -3226,47 +3141,22 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの令和8年度の実績見込みに用いる月の起点と終期</t>
+          <t>都道府県へ推計データを提出する際に入力する「改正介護保険法を踏まえた第10期計画の策定における取組」の回答</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>当方の算定は令和7年度（12か月）を基準年度としており令和8年度を数量の基準に用いないため、見込量及び保険料に影響はない。令和8年度の月数についての記述は、ご提供いただいた月報による4か月のまま置き、システムの計算値とは起点が異なる旨を注記する</t>
+          <t>（1）ア・イは計画本文に掲げている令和17年度及び令和22年度により「2040年度」及び「その他の年度」を選び、ウは計画素案に現に記述のある事項（施設・事業所の開設廃止等による影響、有料老人ホーム及び登録住宅の入居定員総数や入居者の状況、介護予防・日常生活圏域ニーズ調査や在宅介護実態調査等を通じて把握した状況）を選ぶ案を示す。（2）及び（3）は実施の状況を当方が確かめられないため案を示すにとどめ、入力そのものは発注者が行う</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.191（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>既定値で進める</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>見える化システムに入力する地域支援事業費の額の作り方</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>地域支援事業費は令和6年度決算の水準を据え置いて算定し、額が決算によるものであること及び国の様式がいう対象経費支出予定額とは範囲が異なる旨を計画素案 第6章第3節2に注記する</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>確認事項No.192（点1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="76" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
+          <t>確認事項No.193（点1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="76" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>注1）「据え置き（区分A）」は、資料の受領を待たずに当方の側で確定できるものです。
 注2）「既定値で進める」は、決着しない場合の扱いを置けているため決定を待たずに作業を進められるものです。決定を受けた時点で見直します。
@@ -3275,16 +3165,16 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="9"/>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>2　先に扱いを決めるもの（既定値を置けていない）　0件</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="21" t="inlineStr">
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>ありません。未決の確認事項の全件に扱いを置けています。</t>
         </is>
@@ -3293,11 +3183,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A10:E10"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A11:E11"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3309,7 +3199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3322,7 +3212,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>翌日（令和8年10月24日）の作業順位</t>
+          <t>翌日（令和8年10月25日）の作業順位</t>
         </is>
       </c>
     </row>
@@ -3397,17 +3287,17 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの令和8年度の実績見込みに用いる月の起点と終期</t>
+          <t>都道府県へ推計データを提出する際に入力する「改正介護保険法を踏まえた第10期計画の策定における取組」の回答</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>当方の算定は令和7年度（12か月）を基準年度としており令和8年度を数量の基準に用いないため、見込量及び保険料に影響はない。令和8年度の月数についての記述は、ご提供いただいた月報による4か月のまま置き、システムの計算値とは起点が異なる旨を注記する</t>
+          <t>（1）ア・イは計画本文に掲げている令和17年度及び令和22年度により「2040年度」及び「その他の年度」を選び、ウは計画素案に現に記述のある事項（施設・事業所の開設廃止等による影響、有料老人ホーム及び登録住宅の入居定員総数や入居者の状況、介護予防・日常生活圏域ニーズ調査や在宅介護実態調査等を通じて把握した状況）を選ぶ案を示す。（2）及び（3）は実施の状況を当方が確かめられないため案を示すにとどめ、入力そのものは発注者が行う</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.191（点1）</t>
+          <t>確認事項No.193（点1）</t>
         </is>
       </c>
     </row>
@@ -3415,24 +3305,24 @@
       <c r="A7" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>進める</t>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>催促・照会</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>見える化システムに入力する地域支援事業費の額の作り方</t>
+          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算（発注者）</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費は令和6年度決算の水準を据え置いて算定し、額が決算によるものであること及び国の様式がいう対象経費支出予定額とは範囲が異なる旨を計画素案 第6章第3節2に注記する</t>
+          <t>優先度最高・希望時期R8.8。第9期の評価の完成</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>確認事項No.192（点1）</t>
+          <t>資料提供依頼No.13</t>
         </is>
       </c>
     </row>
@@ -3447,17 +3337,17 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>令和6〜8年度の施策・事業実績、事業量、対象実人数、予算・決算（発注者）</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（発注者）</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>優先度最高・希望時期R8.8。第9期の評価の完成</t>
+          <t>優先度高・希望時期R8.8。4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.13</t>
+          <t>資料提供依頼No.14</t>
         </is>
       </c>
     </row>
@@ -3472,17 +3362,17 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（発注者）</t>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）（3町）</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>優先度高・希望時期R8.8。4調査横断のクロス集計、H06・H11・H13・H14の基準値</t>
+          <t>優先度高・希望時期R8.9。東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.14</t>
+          <t>資料提供依頼No.3</t>
         </is>
       </c>
     </row>
@@ -3497,17 +3387,17 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）（3町）</t>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）（発注者）</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>優先度高・希望時期R8.9。東川町の人口推計の乖離の要因、第10期の人口推計の基礎</t>
+          <t>優先度高・希望時期R8.9。交付金評価の解釈、W144の要因、評価対象期間</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.3</t>
+          <t>資料提供依頼No.5</t>
         </is>
       </c>
     </row>
@@ -3522,47 +3412,22 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）（発注者）</t>
+          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）（発注者・国保連）</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>優先度高・希望時期R8.9。交付金評価の解釈、W144の要因、評価対象期間</t>
+          <t>優先度高・希望時期R8.10。給付水準の要因（区域外利用との関係は無相関と判明）</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>資料提供依頼No.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>催促・照会</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>国民健康保険団体連合会の給付実績情報と指定事業所台帳（一部解消）（発注者・国保連）</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>優先度高・希望時期R8.10。給付水準の要因（区域外利用との関係は無相関と判明）</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
           <t>資料提供依頼No.6</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="76" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
+    <row r="12" ht="76" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>注1）「進める」は決定を待たずに着手できるもの、「催促・照会」は相手のある作業です。相手のある作業は午前のうちに出します（返事に日数がかかるため）。
 注2）04シートの作業継続可能なものは上位8件まで、催促・照会は優先以上の上位5件までを掲げています。残りは02・04シートを見ます。
@@ -3571,294 +3436,294 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="13"/>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>2　国の公布を待つもの　13件</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="22" t="inlineStr">
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>令和8年10月19日のご了承により受託者案で確定しましたが、保険料に関わる国の政令・省令・告示の公布後に再算定するものです。催促できないため翌日の作業には挙げていません。公布を確かめた時点で算定をやり直します。</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="4" t="inlineStr"/>
-      <c r="B17" s="4" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="4" t="inlineStr"/>
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>確認事項</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>何を待つか</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>特定地域の指定に係る意向表明の手続</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>特定地域の基準（厚生労働省令）及び対象地域の指定</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>特定地域の指定に係る意向表明の手続</t>
+          <t>第10期の政令改正の内容（所得段階）</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>特定地域の基準（厚生労働省令）及び対象地域の指定</t>
+          <t>第10期の所得段階・乗率・第1号被保険者負担割合（政令）</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第10期の政令改正の内容（所得段階）</t>
+          <t>第10期の保険料算定の前提（受託者案）</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>第10期の所得段階・乗率・第1号被保険者負担割合（政令）</t>
+          <t>保険料算定の前提（報酬改定率・負担割合・基金の取崩し）</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第10期の保険料算定の前提（受託者案）</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>保険料算定の前提（報酬改定率・負担割合・基金の取崩し）</t>
+          <t>社会福祉法等改正法の政令・省令及び介護報酬改定</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）の反映</t>
+          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等改正法の政令・省令及び介護報酬改定</t>
+          <t>令和8年度介護報酬改定の単価への反映</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr"/>
     </row>
     <row r="22" ht="32" customHeight="1">
       <c r="A22" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、令和8年度の水準を反映するか</t>
+          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>令和8年度介護報酬改定の単価への反映</t>
+          <t>令和9年度介護報酬改定の改定率（告示）</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第10期の単価を令和7年度で固定するか、実績の趨勢を置くか</t>
+          <t>令和9年4月に新設される区分を見込量に立てるか</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>令和9年度介護報酬改定の改定率（告示）</t>
+          <t>令和9年4月新設の3区分（省令・告示）</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月に新設される区分を見込量に立てるか</t>
+          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>令和9年4月新設の3区分（省令・告示）</t>
+          <t>1人1月あたり給付費の年度（報酬改定の告示）</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
+          <t>介護サービス事業者経営情報データベースの公表結果の活用の範囲</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の年度（報酬改定の告示）</t>
+          <t>介護サービス事業者経営情報データベースの分析結果の公表</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr"/>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>介護サービス事業者経営情報データベースの公表結果の活用の範囲</t>
+          <t>夜間対応型訪問介護の定期巡回・随時対応型への移行の扱い</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>介護サービス事業者経営情報データベースの分析結果の公表</t>
+          <t>夜間対応型訪問介護の移行に係る省令等</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>夜間対応型訪問介護の定期巡回・随時対応型への移行の扱い</t>
+          <t>小規模市町村地域支援連携協働体制整備事業の対象となるかどうか</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>夜間対応型訪問介護の移行に係る省令等</t>
+          <t>小規模市町村の基準（厚生労働省令）</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr"/>
     </row>
     <row r="28" ht="32" customHeight="1">
       <c r="A28" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>小規模市町村地域支援連携協働体制整備事業の対象となるかどうか</t>
+          <t>地域支援事業費の政令で定める額</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>小規模市町村の基準（厚生労働省令）</t>
+          <t>地域支援事業費の政令で定める額</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費の政令で定める額</t>
+          <t>医療法等の一部を改正する法律による介護保険法の改正の施行の状況</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費の政令で定める額</t>
+          <t>医療法等改正法による改正の施行の日（政令）</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>189</v>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>医療法等の一部を改正する法律による介護保険法の改正の施行の状況</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>医療法等改正法による改正の施行の日（政令）</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3932,12 +3797,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>No.1〜No.192 を数える</t>
+          <t>No.1〜No.193 を数える</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>192件／欠番 なし／重複 なし</t>
+          <t>193件／欠番 なし／重複 なし</t>
         </is>
       </c>
       <c r="E5" s="24" t="inlineStr">
@@ -3962,7 +3827,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>確認事項3件／資料提供依頼23件</t>
+          <t>確認事項2件／資料提供依頼22件</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -3987,7 +3852,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>3件／合わない なし</t>
+          <t>2件／合わない なし</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
@@ -4137,7 +4002,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>記録 令和8年10月23日／本表 令和8年10月23日</t>
+          <t>記録 令和8年10月24日／本表 令和8年10月24日</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
@@ -4187,7 +4052,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>8件（進める3・催促5）</t>
+          <t>7件（進める2・催促5）</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
@@ -4212,7 +4077,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>3件（区分A 0・既定値 3）／据え置きの区分A 0件・既定値があり未処理 3件</t>
+          <t>2件（区分A 0・既定値 2）／据え置きの区分A 0件・既定値があり未処理 2件</t>
         </is>
       </c>
       <c r="E16" s="24" t="inlineStr">
